--- a/reports/backend/Excel/Automation_Test_Report.xlsx
+++ b/reports/backend/Excel/Automation_Test_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="514">
   <si>
     <t>#</t>
   </si>
@@ -35,36 +35,36 @@
     <t>PASSED</t>
   </si>
   <si>
+    <t>0.000</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Smart Admission Backend — Authentication Tests BT-002 | Firebase config has authDomain</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — Authentication Tests BT-003 | Firebase config has projectId</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — Authentication Tests BT-004 | Firebase config has storageBucket</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — Authentication Tests BT-005 | Firebase config has messagingSenderId</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — Authentication Tests BT-006 | Firebase config has appId</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — Authentication Tests BT-007 | Firebase config projectId matches authDomain prefix</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — Authentication Tests BT-008 | Firebase config has all 6 required fields</t>
+  </si>
+  <si>
     <t>0.001</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>Smart Admission Backend — Authentication Tests BT-002 | Firebase config has authDomain</t>
-  </si>
-  <si>
-    <t>0.000</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — Authentication Tests BT-003 | Firebase config has projectId</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — Authentication Tests BT-004 | Firebase config has storageBucket</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — Authentication Tests BT-005 | Firebase config has messagingSenderId</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — Authentication Tests BT-006 | Firebase config has appId</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — Authentication Tests BT-007 | Firebase config projectId matches authDomain prefix</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — Authentication Tests BT-008 | Firebase config has all 6 required fields</t>
-  </si>
-  <si>
     <t>Smart Admission Backend — Authentication Tests BT-009 | Firebase config fields are non-empty strings</t>
   </si>
   <si>
@@ -584,825 +584,828 @@
     <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #180</t>
   </si>
   <si>
+    <t>0.070</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #181</t>
+  </si>
+  <si>
+    <t>0.050</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #182</t>
+  </si>
+  <si>
+    <t>0.081</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #183</t>
+  </si>
+  <si>
+    <t>0.104</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #184</t>
+  </si>
+  <si>
+    <t>0.032</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #185</t>
+  </si>
+  <si>
+    <t>0.108</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #186</t>
+  </si>
+  <si>
+    <t>0.101</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #187</t>
+  </si>
+  <si>
+    <t>0.021</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #188</t>
+  </si>
+  <si>
+    <t>0.053</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #189</t>
+  </si>
+  <si>
+    <t>0.026</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #190</t>
+  </si>
+  <si>
+    <t>0.060</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #191</t>
+  </si>
+  <si>
+    <t>0.109</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #192</t>
+  </si>
+  <si>
+    <t>0.034</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #193</t>
+  </si>
+  <si>
+    <t>0.076</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #194</t>
+  </si>
+  <si>
+    <t>0.030</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #195</t>
+  </si>
+  <si>
+    <t>0.039</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #196</t>
+  </si>
+  <si>
+    <t>0.087</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #197</t>
+  </si>
+  <si>
+    <t>0.031</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #198</t>
+  </si>
+  <si>
+    <t>0.069</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #199</t>
+  </si>
+  <si>
+    <t>0.113</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #200</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #201</t>
+  </si>
+  <si>
+    <t>0.102</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #202</t>
+  </si>
+  <si>
+    <t>0.045</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #203</t>
+  </si>
+  <si>
+    <t>0.094</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #204</t>
+  </si>
+  <si>
+    <t>0.116</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #205</t>
+  </si>
+  <si>
+    <t>0.075</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #206</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #207</t>
+  </si>
+  <si>
+    <t>0.046</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #208</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #209</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #210</t>
+  </si>
+  <si>
+    <t>0.048</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #211</t>
+  </si>
+  <si>
+    <t>0.095</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #212</t>
+  </si>
+  <si>
+    <t>0.059</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #213</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #214</t>
+  </si>
+  <si>
+    <t>0.118</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #215</t>
+  </si>
+  <si>
+    <t>0.080</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #216</t>
+  </si>
+  <si>
     <t>0.096</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #181</t>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #217</t>
+  </si>
+  <si>
+    <t>0.115</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #218</t>
+  </si>
+  <si>
+    <t>0.117</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #219</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #220</t>
+  </si>
+  <si>
+    <t>0.074</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #221</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #222</t>
+  </si>
+  <si>
+    <t>0.054</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #223</t>
+  </si>
+  <si>
+    <t>0.028</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #224</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #225</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #226</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #227</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #228</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #229</t>
+  </si>
+  <si>
+    <t>0.066</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #230</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #231</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #232</t>
+  </si>
+  <si>
+    <t>0.041</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #233</t>
+  </si>
+  <si>
+    <t>0.083</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #234</t>
+  </si>
+  <si>
+    <t>0.079</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #235</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #236</t>
+  </si>
+  <si>
+    <t>0.064</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #237</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #238</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #239</t>
+  </si>
+  <si>
+    <t>0.029</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #240</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #241</t>
+  </si>
+  <si>
+    <t>0.097</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #242</t>
+  </si>
+  <si>
+    <t>0.103</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #243</t>
+  </si>
+  <si>
+    <t>0.024</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #244</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #245</t>
+  </si>
+  <si>
+    <t>0.077</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #246</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #247</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #248</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #249</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #250</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #251</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #252</t>
+  </si>
+  <si>
+    <t>0.110</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #253</t>
+  </si>
+  <si>
+    <t>0.111</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #254</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #255</t>
   </si>
   <si>
     <t>0.071</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #182</t>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #256</t>
+  </si>
+  <si>
+    <t>0.043</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #257</t>
+  </si>
+  <si>
+    <t>0.051</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #258</t>
+  </si>
+  <si>
+    <t>0.033</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #259</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #260</t>
+  </si>
+  <si>
+    <t>0.093</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #261</t>
+  </si>
+  <si>
+    <t>0.062</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #262</t>
+  </si>
+  <si>
+    <t>0.119</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #263</t>
+  </si>
+  <si>
+    <t>0.042</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #264</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #265</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #266</t>
+  </si>
+  <si>
+    <t>0.055</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #267</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #268</t>
+  </si>
+  <si>
+    <t>0.085</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #269</t>
+  </si>
+  <si>
+    <t>0.106</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #270</t>
+  </si>
+  <si>
+    <t>0.025</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #271</t>
   </si>
   <si>
     <t>0.067</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #183</t>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #272</t>
+  </si>
+  <si>
+    <t>0.089</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #273</t>
+  </si>
+  <si>
+    <t>0.056</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #274</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #275</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #276</t>
   </si>
   <si>
     <t>0.037</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #184</t>
-  </si>
-  <si>
-    <t>0.117</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #185</t>
-  </si>
-  <si>
-    <t>0.064</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #186</t>
-  </si>
-  <si>
-    <t>0.109</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #187</t>
-  </si>
-  <si>
-    <t>0.046</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #188</t>
-  </si>
-  <si>
-    <t>0.099</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #189</t>
-  </si>
-  <si>
-    <t>0.040</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #190</t>
-  </si>
-  <si>
-    <t>0.033</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #191</t>
-  </si>
-  <si>
-    <t>0.024</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #192</t>
-  </si>
-  <si>
-    <t>0.048</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #193</t>
-  </si>
-  <si>
-    <t>0.056</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #194</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #195</t>
-  </si>
-  <si>
-    <t>0.053</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #196</t>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #277</t>
+  </si>
+  <si>
+    <t>0.058</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #278</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #279</t>
+  </si>
+  <si>
+    <t>0.027</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #280</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #281</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #282</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #283</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #284</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #285</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #286</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #287</t>
+  </si>
+  <si>
+    <t>0.065</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #288</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #289</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #290</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #291</t>
+  </si>
+  <si>
+    <t>0.020</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #292</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #293</t>
+  </si>
+  <si>
+    <t>0.114</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #294</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #295</t>
+  </si>
+  <si>
+    <t>0.047</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #296</t>
+  </si>
+  <si>
+    <t>0.088</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #297</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #298</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #299</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #300</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #301</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #302</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #303</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #304</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #305</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #306</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #307</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #308</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #309</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #310</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #311</t>
+  </si>
+  <si>
+    <t>0.082</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #312</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #313</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #314</t>
+  </si>
+  <si>
+    <t>0.035</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #315</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #316</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #317</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #318</t>
+  </si>
+  <si>
+    <t>0.112</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #319</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #320</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #321</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #322</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #323</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #324</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #325</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #326</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #327</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #328</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #329</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #330</t>
+  </si>
+  <si>
+    <t>0.092</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #331</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #332</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #333</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #334</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #335</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #336</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #337</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #338</t>
+  </si>
+  <si>
+    <t>0.044</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #339</t>
+  </si>
+  <si>
+    <t>0.061</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #340</t>
+  </si>
+  <si>
+    <t>0.086</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #341</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #342</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #343</t>
+  </si>
+  <si>
+    <t>0.072</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #344</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #345</t>
+  </si>
+  <si>
+    <t>0.052</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #346</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #347</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #348</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #349</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #350</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #351</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #352</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #353</t>
+  </si>
+  <si>
+    <t>0.038</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #354</t>
   </si>
   <si>
     <t>0.084</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #197</t>
-  </si>
-  <si>
-    <t>0.094</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #198</t>
-  </si>
-  <si>
-    <t>0.049</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #199</t>
-  </si>
-  <si>
-    <t>0.107</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #200</t>
-  </si>
-  <si>
-    <t>0.087</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #201</t>
-  </si>
-  <si>
-    <t>0.038</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #202</t>
-  </si>
-  <si>
-    <t>0.050</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #203</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #204</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #205</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #206</t>
-  </si>
-  <si>
-    <t>0.027</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #207</t>
-  </si>
-  <si>
-    <t>0.020</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #208</t>
-  </si>
-  <si>
-    <t>0.060</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #209</t>
-  </si>
-  <si>
-    <t>0.065</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #210</t>
-  </si>
-  <si>
-    <t>0.057</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #211</t>
-  </si>
-  <si>
-    <t>0.112</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #212</t>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #355</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #356</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #357</t>
+  </si>
+  <si>
+    <t>0.098</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #358</t>
   </si>
   <si>
     <t>0.068</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #213</t>
-  </si>
-  <si>
-    <t>0.041</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #214</t>
-  </si>
-  <si>
-    <t>0.101</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #215</t>
-  </si>
-  <si>
-    <t>0.102</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #216</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #217</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #218</t>
-  </si>
-  <si>
-    <t>0.043</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #219</t>
-  </si>
-  <si>
-    <t>0.114</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #220</t>
-  </si>
-  <si>
-    <t>0.098</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #221</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #222</t>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #359</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #360</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #361</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #362</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #363</t>
+  </si>
+  <si>
+    <t>0.073</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #364</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #365</t>
   </si>
   <si>
     <t>0.022</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #223</t>
-  </si>
-  <si>
-    <t>0.081</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #224</t>
-  </si>
-  <si>
-    <t>0.095</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #225</t>
-  </si>
-  <si>
-    <t>0.034</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #226</t>
-  </si>
-  <si>
-    <t>0.111</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #227</t>
-  </si>
-  <si>
-    <t>0.093</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #228</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #229</t>
-  </si>
-  <si>
-    <t>0.110</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #230</t>
-  </si>
-  <si>
-    <t>0.028</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #231</t>
-  </si>
-  <si>
-    <t>0.030</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #232</t>
-  </si>
-  <si>
-    <t>0.119</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #233</t>
-  </si>
-  <si>
-    <t>0.032</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #234</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #235</t>
-  </si>
-  <si>
-    <t>0.103</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #236</t>
-  </si>
-  <si>
-    <t>0.051</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #237</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #238</t>
-  </si>
-  <si>
-    <t>0.104</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #239</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #240</t>
-  </si>
-  <si>
-    <t>0.116</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #241</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #242</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #243</t>
-  </si>
-  <si>
-    <t>0.072</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #244</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #245</t>
-  </si>
-  <si>
-    <t>0.039</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #246</t>
-  </si>
-  <si>
-    <t>0.035</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #247</t>
-  </si>
-  <si>
-    <t>0.079</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #248</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #249</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #250</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #251</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #252</t>
-  </si>
-  <si>
-    <t>0.080</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #253</t>
-  </si>
-  <si>
-    <t>0.025</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #254</t>
-  </si>
-  <si>
-    <t>0.086</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #255</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #256</t>
-  </si>
-  <si>
-    <t>0.077</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #257</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #258</t>
-  </si>
-  <si>
-    <t>0.031</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #259</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #260</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #261</t>
-  </si>
-  <si>
-    <t>0.059</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #262</t>
-  </si>
-  <si>
-    <t>0.082</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #263</t>
-  </si>
-  <si>
-    <t>0.105</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #264</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #265</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #266</t>
-  </si>
-  <si>
-    <t>0.113</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #267</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #268</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #269</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #270</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #271</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #272</t>
-  </si>
-  <si>
-    <t>0.078</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #273</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #274</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #275</t>
-  </si>
-  <si>
-    <t>0.045</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #276</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #277</t>
-  </si>
-  <si>
-    <t>0.092</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #278</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #279</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #280</t>
-  </si>
-  <si>
-    <t>0.069</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #281</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #282</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #283</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #284</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #285</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #286</t>
-  </si>
-  <si>
-    <t>0.074</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #287</t>
-  </si>
-  <si>
-    <t>0.076</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #288</t>
-  </si>
-  <si>
-    <t>0.108</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #289</t>
-  </si>
-  <si>
-    <t>0.118</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #290</t>
-  </si>
-  <si>
-    <t>0.054</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #291</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #292</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #293</t>
-  </si>
-  <si>
-    <t>0.026</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #294</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #295</t>
-  </si>
-  <si>
-    <t>0.042</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #296</t>
-  </si>
-  <si>
-    <t>0.029</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #297</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #298</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #299</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #300</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #301</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #302</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #303</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #304</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #305</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #306</t>
-  </si>
-  <si>
-    <t>0.085</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #307</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #308</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #309</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #310</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #311</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #312</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #313</t>
-  </si>
-  <si>
-    <t>0.044</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #314</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #315</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #316</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #317</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #318</t>
-  </si>
-  <si>
-    <t>0.075</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #319</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #320</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #321</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #322</t>
-  </si>
-  <si>
-    <t>0.115</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #323</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #324</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #325</t>
-  </si>
-  <si>
-    <t>0.062</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #326</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #327</t>
-  </si>
-  <si>
-    <t>0.021</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #328</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #329</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #330</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #331</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #332</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #333</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #334</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #335</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #336</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #337</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #338</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #339</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #340</t>
-  </si>
-  <si>
-    <t>0.100</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #341</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #342</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #343</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #344</t>
-  </si>
-  <si>
-    <t>0.023</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #345</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #346</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #347</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #348</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #349</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #350</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #351</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #352</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #353</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #354</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #355</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #356</t>
-  </si>
-  <si>
-    <t>0.036</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #357</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #358</t>
-  </si>
-  <si>
-    <t>0.055</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #359</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #360</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #361</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #362</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #363</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #364</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #365</t>
-  </si>
-  <si>
     <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #366</t>
   </si>
   <si>
     <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #367</t>
   </si>
   <si>
-    <t>0.073</t>
-  </si>
-  <si>
     <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #368</t>
   </si>
   <si>
@@ -1427,13 +1430,13 @@
     <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #375</t>
   </si>
   <si>
-    <t>0.070</t>
+    <t>0.063</t>
   </si>
   <si>
     <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #376</t>
   </si>
   <si>
-    <t>0.047</t>
+    <t>0.091</t>
   </si>
   <si>
     <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #377</t>
@@ -1463,9 +1466,6 @@
     <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #385</t>
   </si>
   <si>
-    <t>0.066</t>
-  </si>
-  <si>
     <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #386</t>
   </si>
   <si>
@@ -1475,9 +1475,6 @@
     <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #388</t>
   </si>
   <si>
-    <t>0.058</t>
-  </si>
-  <si>
     <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #389</t>
   </si>
   <si>
@@ -1520,13 +1517,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>11</t>
+    <t>12</t>
   </si>
   <si>
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 12:04:48 UTC</t>
+    <t>2026-06-23 13:17:23 UTC</t>
   </si>
   <si>
     <t>Branch</t>
@@ -1538,7 +1535,7 @@
     <t>Commit</t>
   </si>
   <si>
-    <t>348580a</t>
+    <t>cfbb4d3</t>
   </si>
   <si>
     <t>Total</t>
@@ -1993,7 +1990,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -2004,13 +2001,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -2021,7 +2018,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>6</v>
@@ -2038,13 +2035,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -2055,13 +2052,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -2072,13 +2069,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -2089,13 +2086,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" t="s">
         <v>16</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" t="s">
-        <v>10</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -2112,7 +2109,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -2129,7 +2126,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -2146,7 +2143,7 @@
         <v>6</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -2163,7 +2160,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -2180,7 +2177,7 @@
         <v>6</v>
       </c>
       <c r="D14" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -2197,7 +2194,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -2214,7 +2211,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -2231,7 +2228,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -2248,7 +2245,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -2265,7 +2262,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -2282,7 +2279,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -2299,7 +2296,7 @@
         <v>6</v>
       </c>
       <c r="D21" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -2316,7 +2313,7 @@
         <v>6</v>
       </c>
       <c r="D22" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -2333,7 +2330,7 @@
         <v>6</v>
       </c>
       <c r="D23" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -2350,7 +2347,7 @@
         <v>6</v>
       </c>
       <c r="D24" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -2367,7 +2364,7 @@
         <v>6</v>
       </c>
       <c r="D25" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -2384,7 +2381,7 @@
         <v>6</v>
       </c>
       <c r="D26" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -2401,7 +2398,7 @@
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -2418,7 +2415,7 @@
         <v>6</v>
       </c>
       <c r="D28" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -2452,7 +2449,7 @@
         <v>6</v>
       </c>
       <c r="D30" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -2469,7 +2466,7 @@
         <v>6</v>
       </c>
       <c r="D31" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -2486,7 +2483,7 @@
         <v>6</v>
       </c>
       <c r="D32" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -2503,7 +2500,7 @@
         <v>6</v>
       </c>
       <c r="D33" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -2520,7 +2517,7 @@
         <v>6</v>
       </c>
       <c r="D34" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -2537,7 +2534,7 @@
         <v>6</v>
       </c>
       <c r="D35" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -2554,7 +2551,7 @@
         <v>6</v>
       </c>
       <c r="D36" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -2571,7 +2568,7 @@
         <v>6</v>
       </c>
       <c r="D37" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -2588,7 +2585,7 @@
         <v>6</v>
       </c>
       <c r="D38" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -2605,7 +2602,7 @@
         <v>6</v>
       </c>
       <c r="D39" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -2622,7 +2619,7 @@
         <v>6</v>
       </c>
       <c r="D40" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -2639,7 +2636,7 @@
         <v>6</v>
       </c>
       <c r="D41" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -2656,7 +2653,7 @@
         <v>6</v>
       </c>
       <c r="D42" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -2673,7 +2670,7 @@
         <v>6</v>
       </c>
       <c r="D43" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -2690,7 +2687,7 @@
         <v>6</v>
       </c>
       <c r="D44" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -2707,7 +2704,7 @@
         <v>6</v>
       </c>
       <c r="D45" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -2724,7 +2721,7 @@
         <v>6</v>
       </c>
       <c r="D46" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -2741,7 +2738,7 @@
         <v>6</v>
       </c>
       <c r="D47" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -2758,7 +2755,7 @@
         <v>6</v>
       </c>
       <c r="D48" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -2775,7 +2772,7 @@
         <v>6</v>
       </c>
       <c r="D49" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -2792,7 +2789,7 @@
         <v>6</v>
       </c>
       <c r="D50" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -2809,7 +2806,7 @@
         <v>6</v>
       </c>
       <c r="D51" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -2826,7 +2823,7 @@
         <v>6</v>
       </c>
       <c r="D52" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -2843,7 +2840,7 @@
         <v>6</v>
       </c>
       <c r="D53" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -2860,7 +2857,7 @@
         <v>6</v>
       </c>
       <c r="D54" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -2877,7 +2874,7 @@
         <v>6</v>
       </c>
       <c r="D55" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
@@ -2894,7 +2891,7 @@
         <v>6</v>
       </c>
       <c r="D56" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -2911,7 +2908,7 @@
         <v>6</v>
       </c>
       <c r="D57" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -2928,7 +2925,7 @@
         <v>6</v>
       </c>
       <c r="D58" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -2945,7 +2942,7 @@
         <v>6</v>
       </c>
       <c r="D59" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
@@ -2962,7 +2959,7 @@
         <v>6</v>
       </c>
       <c r="D60" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
@@ -2979,7 +2976,7 @@
         <v>6</v>
       </c>
       <c r="D61" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
@@ -3013,7 +3010,7 @@
         <v>6</v>
       </c>
       <c r="D63" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
@@ -3030,7 +3027,7 @@
         <v>6</v>
       </c>
       <c r="D64" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E64" t="s">
         <v>8</v>
@@ -3047,7 +3044,7 @@
         <v>6</v>
       </c>
       <c r="D65" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E65" t="s">
         <v>8</v>
@@ -3064,7 +3061,7 @@
         <v>6</v>
       </c>
       <c r="D66" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
@@ -3081,7 +3078,7 @@
         <v>6</v>
       </c>
       <c r="D67" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
@@ -3098,7 +3095,7 @@
         <v>6</v>
       </c>
       <c r="D68" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
@@ -3115,7 +3112,7 @@
         <v>6</v>
       </c>
       <c r="D69" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E69" t="s">
         <v>8</v>
@@ -3132,7 +3129,7 @@
         <v>6</v>
       </c>
       <c r="D70" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
@@ -3149,7 +3146,7 @@
         <v>6</v>
       </c>
       <c r="D71" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
@@ -3166,7 +3163,7 @@
         <v>6</v>
       </c>
       <c r="D72" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
@@ -3183,7 +3180,7 @@
         <v>6</v>
       </c>
       <c r="D73" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E73" t="s">
         <v>8</v>
@@ -3200,7 +3197,7 @@
         <v>6</v>
       </c>
       <c r="D74" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E74" t="s">
         <v>8</v>
@@ -3217,7 +3214,7 @@
         <v>6</v>
       </c>
       <c r="D75" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
@@ -3234,7 +3231,7 @@
         <v>6</v>
       </c>
       <c r="D76" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E76" t="s">
         <v>8</v>
@@ -3268,7 +3265,7 @@
         <v>6</v>
       </c>
       <c r="D78" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
@@ -3285,7 +3282,7 @@
         <v>6</v>
       </c>
       <c r="D79" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E79" t="s">
         <v>8</v>
@@ -3302,7 +3299,7 @@
         <v>6</v>
       </c>
       <c r="D80" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E80" t="s">
         <v>8</v>
@@ -3319,7 +3316,7 @@
         <v>6</v>
       </c>
       <c r="D81" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
@@ -3336,7 +3333,7 @@
         <v>6</v>
       </c>
       <c r="D82" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
@@ -3353,7 +3350,7 @@
         <v>6</v>
       </c>
       <c r="D83" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E83" t="s">
         <v>8</v>
@@ -3370,7 +3367,7 @@
         <v>6</v>
       </c>
       <c r="D84" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
@@ -3387,7 +3384,7 @@
         <v>6</v>
       </c>
       <c r="D85" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
@@ -3404,7 +3401,7 @@
         <v>6</v>
       </c>
       <c r="D86" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
@@ -3421,7 +3418,7 @@
         <v>6</v>
       </c>
       <c r="D87" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E87" t="s">
         <v>8</v>
@@ -3438,7 +3435,7 @@
         <v>6</v>
       </c>
       <c r="D88" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E88" t="s">
         <v>8</v>
@@ -3455,7 +3452,7 @@
         <v>6</v>
       </c>
       <c r="D89" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
@@ -3472,7 +3469,7 @@
         <v>6</v>
       </c>
       <c r="D90" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E90" t="s">
         <v>8</v>
@@ -3489,7 +3486,7 @@
         <v>6</v>
       </c>
       <c r="D91" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E91" t="s">
         <v>8</v>
@@ -3506,7 +3503,7 @@
         <v>6</v>
       </c>
       <c r="D92" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E92" t="s">
         <v>8</v>
@@ -3523,7 +3520,7 @@
         <v>6</v>
       </c>
       <c r="D93" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E93" t="s">
         <v>8</v>
@@ -3540,7 +3537,7 @@
         <v>6</v>
       </c>
       <c r="D94" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E94" t="s">
         <v>8</v>
@@ -3557,7 +3554,7 @@
         <v>6</v>
       </c>
       <c r="D95" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E95" t="s">
         <v>8</v>
@@ -3574,7 +3571,7 @@
         <v>6</v>
       </c>
       <c r="D96" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E96" t="s">
         <v>8</v>
@@ -3591,7 +3588,7 @@
         <v>6</v>
       </c>
       <c r="D97" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E97" t="s">
         <v>8</v>
@@ -3608,7 +3605,7 @@
         <v>6</v>
       </c>
       <c r="D98" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E98" t="s">
         <v>8</v>
@@ -3625,7 +3622,7 @@
         <v>6</v>
       </c>
       <c r="D99" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
@@ -3642,7 +3639,7 @@
         <v>6</v>
       </c>
       <c r="D100" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E100" t="s">
         <v>8</v>
@@ -3659,7 +3656,7 @@
         <v>6</v>
       </c>
       <c r="D101" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E101" t="s">
         <v>8</v>
@@ -3676,7 +3673,7 @@
         <v>6</v>
       </c>
       <c r="D102" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E102" t="s">
         <v>8</v>
@@ -3693,7 +3690,7 @@
         <v>6</v>
       </c>
       <c r="D103" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E103" t="s">
         <v>8</v>
@@ -3710,7 +3707,7 @@
         <v>6</v>
       </c>
       <c r="D104" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E104" t="s">
         <v>8</v>
@@ -3727,7 +3724,7 @@
         <v>6</v>
       </c>
       <c r="D105" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E105" t="s">
         <v>8</v>
@@ -3744,7 +3741,7 @@
         <v>6</v>
       </c>
       <c r="D106" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E106" t="s">
         <v>8</v>
@@ -3761,7 +3758,7 @@
         <v>6</v>
       </c>
       <c r="D107" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
@@ -3778,7 +3775,7 @@
         <v>6</v>
       </c>
       <c r="D108" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E108" t="s">
         <v>8</v>
@@ -3795,7 +3792,7 @@
         <v>6</v>
       </c>
       <c r="D109" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E109" t="s">
         <v>8</v>
@@ -3812,7 +3809,7 @@
         <v>6</v>
       </c>
       <c r="D110" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E110" t="s">
         <v>8</v>
@@ -3829,7 +3826,7 @@
         <v>6</v>
       </c>
       <c r="D111" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E111" t="s">
         <v>8</v>
@@ -3846,7 +3843,7 @@
         <v>6</v>
       </c>
       <c r="D112" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E112" t="s">
         <v>8</v>
@@ -3863,7 +3860,7 @@
         <v>6</v>
       </c>
       <c r="D113" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E113" t="s">
         <v>8</v>
@@ -3880,7 +3877,7 @@
         <v>6</v>
       </c>
       <c r="D114" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E114" t="s">
         <v>8</v>
@@ -3897,7 +3894,7 @@
         <v>6</v>
       </c>
       <c r="D115" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E115" t="s">
         <v>8</v>
@@ -3914,7 +3911,7 @@
         <v>6</v>
       </c>
       <c r="D116" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E116" t="s">
         <v>8</v>
@@ -3931,7 +3928,7 @@
         <v>6</v>
       </c>
       <c r="D117" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E117" t="s">
         <v>8</v>
@@ -3948,7 +3945,7 @@
         <v>6</v>
       </c>
       <c r="D118" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E118" t="s">
         <v>8</v>
@@ -3965,7 +3962,7 @@
         <v>6</v>
       </c>
       <c r="D119" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E119" t="s">
         <v>8</v>
@@ -3982,7 +3979,7 @@
         <v>6</v>
       </c>
       <c r="D120" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E120" t="s">
         <v>8</v>
@@ -4016,7 +4013,7 @@
         <v>6</v>
       </c>
       <c r="D122" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E122" t="s">
         <v>8</v>
@@ -4033,7 +4030,7 @@
         <v>6</v>
       </c>
       <c r="D123" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E123" t="s">
         <v>8</v>
@@ -4050,7 +4047,7 @@
         <v>6</v>
       </c>
       <c r="D124" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E124" t="s">
         <v>8</v>
@@ -4067,7 +4064,7 @@
         <v>6</v>
       </c>
       <c r="D125" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E125" t="s">
         <v>8</v>
@@ -4084,7 +4081,7 @@
         <v>6</v>
       </c>
       <c r="D126" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E126" t="s">
         <v>8</v>
@@ -4101,7 +4098,7 @@
         <v>6</v>
       </c>
       <c r="D127" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E127" t="s">
         <v>8</v>
@@ -4118,7 +4115,7 @@
         <v>6</v>
       </c>
       <c r="D128" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E128" t="s">
         <v>8</v>
@@ -4135,7 +4132,7 @@
         <v>6</v>
       </c>
       <c r="D129" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E129" t="s">
         <v>8</v>
@@ -4152,7 +4149,7 @@
         <v>6</v>
       </c>
       <c r="D130" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E130" t="s">
         <v>8</v>
@@ -4169,7 +4166,7 @@
         <v>6</v>
       </c>
       <c r="D131" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E131" t="s">
         <v>8</v>
@@ -4186,7 +4183,7 @@
         <v>6</v>
       </c>
       <c r="D132" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E132" t="s">
         <v>8</v>
@@ -4203,7 +4200,7 @@
         <v>6</v>
       </c>
       <c r="D133" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E133" t="s">
         <v>8</v>
@@ -4220,7 +4217,7 @@
         <v>6</v>
       </c>
       <c r="D134" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E134" t="s">
         <v>8</v>
@@ -4237,7 +4234,7 @@
         <v>6</v>
       </c>
       <c r="D135" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E135" t="s">
         <v>8</v>
@@ -4254,7 +4251,7 @@
         <v>6</v>
       </c>
       <c r="D136" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E136" t="s">
         <v>8</v>
@@ -4271,7 +4268,7 @@
         <v>6</v>
       </c>
       <c r="D137" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E137" t="s">
         <v>8</v>
@@ -4288,7 +4285,7 @@
         <v>6</v>
       </c>
       <c r="D138" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E138" t="s">
         <v>8</v>
@@ -4305,7 +4302,7 @@
         <v>6</v>
       </c>
       <c r="D139" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E139" t="s">
         <v>8</v>
@@ -4322,7 +4319,7 @@
         <v>6</v>
       </c>
       <c r="D140" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E140" t="s">
         <v>8</v>
@@ -4339,7 +4336,7 @@
         <v>6</v>
       </c>
       <c r="D141" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E141" t="s">
         <v>8</v>
@@ -4356,7 +4353,7 @@
         <v>6</v>
       </c>
       <c r="D142" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E142" t="s">
         <v>8</v>
@@ -4373,7 +4370,7 @@
         <v>6</v>
       </c>
       <c r="D143" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E143" t="s">
         <v>8</v>
@@ -4390,7 +4387,7 @@
         <v>6</v>
       </c>
       <c r="D144" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E144" t="s">
         <v>8</v>
@@ -4407,7 +4404,7 @@
         <v>6</v>
       </c>
       <c r="D145" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E145" t="s">
         <v>8</v>
@@ -4424,7 +4421,7 @@
         <v>6</v>
       </c>
       <c r="D146" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E146" t="s">
         <v>8</v>
@@ -4441,7 +4438,7 @@
         <v>6</v>
       </c>
       <c r="D147" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E147" t="s">
         <v>8</v>
@@ -4458,7 +4455,7 @@
         <v>6</v>
       </c>
       <c r="D148" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E148" t="s">
         <v>8</v>
@@ -4475,7 +4472,7 @@
         <v>6</v>
       </c>
       <c r="D149" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E149" t="s">
         <v>8</v>
@@ -4492,7 +4489,7 @@
         <v>6</v>
       </c>
       <c r="D150" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E150" t="s">
         <v>8</v>
@@ -4509,7 +4506,7 @@
         <v>6</v>
       </c>
       <c r="D151" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E151" t="s">
         <v>8</v>
@@ -4526,7 +4523,7 @@
         <v>6</v>
       </c>
       <c r="D152" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E152" t="s">
         <v>8</v>
@@ -4543,7 +4540,7 @@
         <v>6</v>
       </c>
       <c r="D153" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E153" t="s">
         <v>8</v>
@@ -4560,7 +4557,7 @@
         <v>6</v>
       </c>
       <c r="D154" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E154" t="s">
         <v>8</v>
@@ -4577,7 +4574,7 @@
         <v>6</v>
       </c>
       <c r="D155" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E155" t="s">
         <v>8</v>
@@ -4594,7 +4591,7 @@
         <v>6</v>
       </c>
       <c r="D156" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E156" t="s">
         <v>8</v>
@@ -4611,7 +4608,7 @@
         <v>6</v>
       </c>
       <c r="D157" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E157" t="s">
         <v>8</v>
@@ -4628,7 +4625,7 @@
         <v>6</v>
       </c>
       <c r="D158" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E158" t="s">
         <v>8</v>
@@ -4645,7 +4642,7 @@
         <v>6</v>
       </c>
       <c r="D159" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E159" t="s">
         <v>8</v>
@@ -4662,7 +4659,7 @@
         <v>6</v>
       </c>
       <c r="D160" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E160" t="s">
         <v>8</v>
@@ -4679,7 +4676,7 @@
         <v>6</v>
       </c>
       <c r="D161" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E161" t="s">
         <v>8</v>
@@ -4696,7 +4693,7 @@
         <v>6</v>
       </c>
       <c r="D162" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E162" t="s">
         <v>8</v>
@@ -4713,7 +4710,7 @@
         <v>6</v>
       </c>
       <c r="D163" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E163" t="s">
         <v>8</v>
@@ -4730,7 +4727,7 @@
         <v>6</v>
       </c>
       <c r="D164" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E164" t="s">
         <v>8</v>
@@ -4747,7 +4744,7 @@
         <v>6</v>
       </c>
       <c r="D165" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E165" t="s">
         <v>8</v>
@@ -4764,7 +4761,7 @@
         <v>6</v>
       </c>
       <c r="D166" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E166" t="s">
         <v>8</v>
@@ -4781,7 +4778,7 @@
         <v>6</v>
       </c>
       <c r="D167" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E167" t="s">
         <v>8</v>
@@ -4798,7 +4795,7 @@
         <v>6</v>
       </c>
       <c r="D168" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E168" t="s">
         <v>8</v>
@@ -4815,7 +4812,7 @@
         <v>6</v>
       </c>
       <c r="D169" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E169" t="s">
         <v>8</v>
@@ -4832,7 +4829,7 @@
         <v>6</v>
       </c>
       <c r="D170" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E170" t="s">
         <v>8</v>
@@ -4849,7 +4846,7 @@
         <v>6</v>
       </c>
       <c r="D171" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E171" t="s">
         <v>8</v>
@@ -4866,7 +4863,7 @@
         <v>6</v>
       </c>
       <c r="D172" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E172" t="s">
         <v>8</v>
@@ -4883,7 +4880,7 @@
         <v>6</v>
       </c>
       <c r="D173" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E173" t="s">
         <v>8</v>
@@ -4900,7 +4897,7 @@
         <v>6</v>
       </c>
       <c r="D174" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E174" t="s">
         <v>8</v>
@@ -4917,7 +4914,7 @@
         <v>6</v>
       </c>
       <c r="D175" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E175" t="s">
         <v>8</v>
@@ -4934,7 +4931,7 @@
         <v>6</v>
       </c>
       <c r="D176" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E176" t="s">
         <v>8</v>
@@ -4951,7 +4948,7 @@
         <v>6</v>
       </c>
       <c r="D177" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E177" t="s">
         <v>8</v>
@@ -4968,7 +4965,7 @@
         <v>6</v>
       </c>
       <c r="D178" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E178" t="s">
         <v>8</v>
@@ -4985,7 +4982,7 @@
         <v>6</v>
       </c>
       <c r="D179" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E179" t="s">
         <v>8</v>
@@ -5002,7 +4999,7 @@
         <v>6</v>
       </c>
       <c r="D180" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E180" t="s">
         <v>8</v>
@@ -5019,7 +5016,7 @@
         <v>6</v>
       </c>
       <c r="D181" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E181" t="s">
         <v>8</v>
@@ -5274,7 +5271,7 @@
         <v>6</v>
       </c>
       <c r="D196" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="E196" t="s">
         <v>8</v>
@@ -5285,13 +5282,13 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D197" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E197" t="s">
         <v>8</v>
@@ -5302,13 +5299,13 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D198" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E198" t="s">
         <v>8</v>
@@ -5319,13 +5316,13 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D199" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E199" t="s">
         <v>8</v>
@@ -5336,13 +5333,13 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D200" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E200" t="s">
         <v>8</v>
@@ -5353,13 +5350,13 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D201" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E201" t="s">
         <v>8</v>
@@ -5370,13 +5367,13 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D202" t="s">
-        <v>229</v>
+        <v>200</v>
       </c>
       <c r="E202" t="s">
         <v>8</v>
@@ -5427,7 +5424,7 @@
         <v>6</v>
       </c>
       <c r="D205" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="E205" t="s">
         <v>8</v>
@@ -5438,13 +5435,13 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D206" t="s">
-        <v>196</v>
+        <v>237</v>
       </c>
       <c r="E206" t="s">
         <v>8</v>
@@ -5455,13 +5452,13 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D207" t="s">
-        <v>194</v>
+        <v>239</v>
       </c>
       <c r="E207" t="s">
         <v>8</v>
@@ -5472,13 +5469,13 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
+        <v>240</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D208" t="s">
         <v>237</v>
-      </c>
-      <c r="C208" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D208" t="s">
-        <v>238</v>
       </c>
       <c r="E208" t="s">
         <v>8</v>
@@ -5489,13 +5486,13 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D209" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E209" t="s">
         <v>8</v>
@@ -5506,13 +5503,13 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D210" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E210" t="s">
         <v>8</v>
@@ -5523,13 +5520,13 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D211" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="E211" t="s">
         <v>8</v>
@@ -5597,7 +5594,7 @@
         <v>6</v>
       </c>
       <c r="D215" t="s">
-        <v>252</v>
+        <v>212</v>
       </c>
       <c r="E215" t="s">
         <v>8</v>
@@ -5608,13 +5605,13 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
+        <v>252</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D216" t="s">
         <v>253</v>
-      </c>
-      <c r="C216" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D216" t="s">
-        <v>254</v>
       </c>
       <c r="E216" t="s">
         <v>8</v>
@@ -5625,13 +5622,13 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
+        <v>254</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D217" t="s">
         <v>255</v>
-      </c>
-      <c r="C217" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D217" t="s">
-        <v>256</v>
       </c>
       <c r="E217" t="s">
         <v>8</v>
@@ -5642,13 +5639,13 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
+        <v>256</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D218" t="s">
         <v>257</v>
-      </c>
-      <c r="C218" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D218" t="s">
-        <v>221</v>
       </c>
       <c r="E218" t="s">
         <v>8</v>
@@ -5665,7 +5662,7 @@
         <v>6</v>
       </c>
       <c r="D219" t="s">
-        <v>196</v>
+        <v>259</v>
       </c>
       <c r="E219" t="s">
         <v>8</v>
@@ -5676,13 +5673,13 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D220" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E220" t="s">
         <v>8</v>
@@ -5693,13 +5690,13 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D221" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="E221" t="s">
         <v>8</v>
@@ -5733,7 +5730,7 @@
         <v>6</v>
       </c>
       <c r="D223" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="E223" t="s">
         <v>8</v>
@@ -5784,7 +5781,7 @@
         <v>6</v>
       </c>
       <c r="D226" t="s">
-        <v>271</v>
+        <v>235</v>
       </c>
       <c r="E226" t="s">
         <v>8</v>
@@ -5795,13 +5792,13 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D227" t="s">
-        <v>273</v>
+        <v>198</v>
       </c>
       <c r="E227" t="s">
         <v>8</v>
@@ -5812,13 +5809,13 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D228" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="E228" t="s">
         <v>8</v>
@@ -5829,13 +5826,13 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D229" t="s">
-        <v>277</v>
+        <v>204</v>
       </c>
       <c r="E229" t="s">
         <v>8</v>
@@ -5846,7 +5843,7 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>6</v>
@@ -5863,13 +5860,13 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D231" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="E231" t="s">
         <v>8</v>
@@ -5880,13 +5877,13 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D232" t="s">
-        <v>282</v>
+        <v>220</v>
       </c>
       <c r="E232" t="s">
         <v>8</v>
@@ -5897,13 +5894,13 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D233" t="s">
-        <v>284</v>
+        <v>196</v>
       </c>
       <c r="E233" t="s">
         <v>8</v>
@@ -5914,13 +5911,13 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D234" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="E234" t="s">
         <v>8</v>
@@ -5931,13 +5928,13 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D235" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="E235" t="s">
         <v>8</v>
@@ -5948,13 +5945,13 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D236" t="s">
-        <v>194</v>
+        <v>284</v>
       </c>
       <c r="E236" t="s">
         <v>8</v>
@@ -5965,13 +5962,13 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D237" t="s">
-        <v>291</v>
+        <v>216</v>
       </c>
       <c r="E237" t="s">
         <v>8</v>
@@ -5982,13 +5979,13 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D238" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="E238" t="s">
         <v>8</v>
@@ -5999,13 +5996,13 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D239" t="s">
-        <v>267</v>
+        <v>194</v>
       </c>
       <c r="E239" t="s">
         <v>8</v>
@@ -6016,13 +6013,13 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D240" t="s">
-        <v>296</v>
+        <v>259</v>
       </c>
       <c r="E240" t="s">
         <v>8</v>
@@ -6033,13 +6030,13 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D241" t="s">
-        <v>208</v>
+        <v>291</v>
       </c>
       <c r="E241" t="s">
         <v>8</v>
@@ -6050,13 +6047,13 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D242" t="s">
-        <v>299</v>
+        <v>190</v>
       </c>
       <c r="E242" t="s">
         <v>8</v>
@@ -6067,13 +6064,13 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D243" t="s">
-        <v>225</v>
+        <v>294</v>
       </c>
       <c r="E243" t="s">
         <v>8</v>
@@ -6084,13 +6081,13 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D244" t="s">
-        <v>214</v>
+        <v>296</v>
       </c>
       <c r="E244" t="s">
         <v>8</v>
@@ -6101,13 +6098,13 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D245" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="E245" t="s">
         <v>8</v>
@@ -6118,13 +6115,13 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D246" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="E246" t="s">
         <v>8</v>
@@ -6135,13 +6132,13 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D247" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="E247" t="s">
         <v>8</v>
@@ -6152,13 +6149,13 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D248" t="s">
-        <v>308</v>
+        <v>248</v>
       </c>
       <c r="E248" t="s">
         <v>8</v>
@@ -6169,13 +6166,13 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D249" t="s">
-        <v>310</v>
+        <v>267</v>
       </c>
       <c r="E249" t="s">
         <v>8</v>
@@ -6186,13 +6183,13 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D250" t="s">
-        <v>264</v>
+        <v>237</v>
       </c>
       <c r="E250" t="s">
         <v>8</v>
@@ -6203,13 +6200,13 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D251" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E251" t="s">
         <v>8</v>
@@ -6220,13 +6217,13 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D252" t="s">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="E252" t="s">
         <v>8</v>
@@ -6237,13 +6234,13 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D253" t="s">
-        <v>244</v>
+        <v>298</v>
       </c>
       <c r="E253" t="s">
         <v>8</v>
@@ -6254,13 +6251,13 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D254" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E254" t="s">
         <v>8</v>
@@ -6271,13 +6268,13 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D255" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="E255" t="s">
         <v>8</v>
@@ -6288,13 +6285,13 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D256" t="s">
-        <v>320</v>
+        <v>259</v>
       </c>
       <c r="E256" t="s">
         <v>8</v>
@@ -6305,13 +6302,13 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D257" t="s">
-        <v>254</v>
+        <v>314</v>
       </c>
       <c r="E257" t="s">
         <v>8</v>
@@ -6322,13 +6319,13 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D258" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="E258" t="s">
         <v>8</v>
@@ -6339,13 +6336,13 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D259" t="s">
-        <v>262</v>
+        <v>318</v>
       </c>
       <c r="E259" t="s">
         <v>8</v>
@@ -6356,13 +6353,13 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D260" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="E260" t="s">
         <v>8</v>
@@ -6373,13 +6370,13 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D261" t="s">
-        <v>308</v>
+        <v>224</v>
       </c>
       <c r="E261" t="s">
         <v>8</v>
@@ -6390,13 +6387,13 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D262" t="s">
-        <v>273</v>
+        <v>323</v>
       </c>
       <c r="E262" t="s">
         <v>8</v>
@@ -6407,13 +6404,13 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D263" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="E263" t="s">
         <v>8</v>
@@ -6424,13 +6421,13 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D264" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="E264" t="s">
         <v>8</v>
@@ -6441,13 +6438,13 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D265" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E265" t="s">
         <v>8</v>
@@ -6458,13 +6455,13 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D266" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E266" t="s">
         <v>8</v>
@@ -6475,13 +6472,13 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D267" t="s">
-        <v>248</v>
+        <v>298</v>
       </c>
       <c r="E267" t="s">
         <v>8</v>
@@ -6492,13 +6489,13 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D268" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="E268" t="s">
         <v>8</v>
@@ -6509,13 +6506,13 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D269" t="s">
-        <v>318</v>
+        <v>264</v>
       </c>
       <c r="E269" t="s">
         <v>8</v>
@@ -6526,13 +6523,13 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D270" t="s">
-        <v>291</v>
+        <v>336</v>
       </c>
       <c r="E270" t="s">
         <v>8</v>
@@ -6543,13 +6540,13 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D271" t="s">
-        <v>225</v>
+        <v>338</v>
       </c>
       <c r="E271" t="s">
         <v>8</v>
@@ -6560,13 +6557,13 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D272" t="s">
-        <v>264</v>
+        <v>340</v>
       </c>
       <c r="E272" t="s">
         <v>8</v>
@@ -6577,13 +6574,13 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D273" t="s">
-        <v>280</v>
+        <v>342</v>
       </c>
       <c r="E273" t="s">
         <v>8</v>
@@ -6594,13 +6591,13 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
+        <v>343</v>
+      </c>
+      <c r="C274" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D274" t="s">
         <v>344</v>
-      </c>
-      <c r="C274" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D274" t="s">
-        <v>345</v>
       </c>
       <c r="E274" t="s">
         <v>8</v>
@@ -6611,13 +6608,13 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
+        <v>345</v>
+      </c>
+      <c r="C275" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D275" t="s">
         <v>346</v>
-      </c>
-      <c r="C275" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D275" t="s">
-        <v>269</v>
       </c>
       <c r="E275" t="s">
         <v>8</v>
@@ -6634,7 +6631,7 @@
         <v>6</v>
       </c>
       <c r="D276" t="s">
-        <v>262</v>
+        <v>200</v>
       </c>
       <c r="E276" t="s">
         <v>8</v>
@@ -6651,7 +6648,7 @@
         <v>6</v>
       </c>
       <c r="D277" t="s">
-        <v>349</v>
+        <v>257</v>
       </c>
       <c r="E277" t="s">
         <v>8</v>
@@ -6662,13 +6659,13 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
+        <v>349</v>
+      </c>
+      <c r="C278" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D278" t="s">
         <v>350</v>
-      </c>
-      <c r="C278" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D278" t="s">
-        <v>229</v>
       </c>
       <c r="E278" t="s">
         <v>8</v>
@@ -6702,7 +6699,7 @@
         <v>6</v>
       </c>
       <c r="D280" t="s">
-        <v>246</v>
+        <v>287</v>
       </c>
       <c r="E280" t="s">
         <v>8</v>
@@ -6719,7 +6716,7 @@
         <v>6</v>
       </c>
       <c r="D281" t="s">
-        <v>275</v>
+        <v>355</v>
       </c>
       <c r="E281" t="s">
         <v>8</v>
@@ -6730,13 +6727,13 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D282" t="s">
-        <v>356</v>
+        <v>291</v>
       </c>
       <c r="E282" t="s">
         <v>8</v>
@@ -6753,7 +6750,7 @@
         <v>6</v>
       </c>
       <c r="D283" t="s">
-        <v>306</v>
+        <v>214</v>
       </c>
       <c r="E283" t="s">
         <v>8</v>
@@ -6770,7 +6767,7 @@
         <v>6</v>
       </c>
       <c r="D284" t="s">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="E284" t="s">
         <v>8</v>
@@ -6787,7 +6784,7 @@
         <v>6</v>
       </c>
       <c r="D285" t="s">
-        <v>293</v>
+        <v>267</v>
       </c>
       <c r="E285" t="s">
         <v>8</v>
@@ -6804,7 +6801,7 @@
         <v>6</v>
       </c>
       <c r="D286" t="s">
-        <v>264</v>
+        <v>237</v>
       </c>
       <c r="E286" t="s">
         <v>8</v>
@@ -6821,7 +6818,7 @@
         <v>6</v>
       </c>
       <c r="D287" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E287" t="s">
         <v>8</v>
@@ -6838,7 +6835,7 @@
         <v>6</v>
       </c>
       <c r="D288" t="s">
-        <v>363</v>
+        <v>323</v>
       </c>
       <c r="E288" t="s">
         <v>8</v>
@@ -6849,13 +6846,13 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
+        <v>363</v>
+      </c>
+      <c r="C289" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D289" t="s">
         <v>364</v>
-      </c>
-      <c r="C289" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D289" t="s">
-        <v>365</v>
       </c>
       <c r="E289" t="s">
         <v>8</v>
@@ -6866,13 +6863,13 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D290" t="s">
-        <v>367</v>
+        <v>301</v>
       </c>
       <c r="E290" t="s">
         <v>8</v>
@@ -6883,13 +6880,13 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D291" t="s">
-        <v>369</v>
+        <v>309</v>
       </c>
       <c r="E291" t="s">
         <v>8</v>
@@ -6900,13 +6897,13 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D292" t="s">
-        <v>371</v>
+        <v>233</v>
       </c>
       <c r="E292" t="s">
         <v>8</v>
@@ -6917,13 +6914,13 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D293" t="s">
-        <v>318</v>
+        <v>369</v>
       </c>
       <c r="E293" t="s">
         <v>8</v>
@@ -6934,13 +6931,13 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D294" t="s">
-        <v>260</v>
+        <v>318</v>
       </c>
       <c r="E294" t="s">
         <v>8</v>
@@ -6951,13 +6948,13 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D295" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="E295" t="s">
         <v>8</v>
@@ -6968,13 +6965,13 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D296" t="s">
-        <v>190</v>
+        <v>287</v>
       </c>
       <c r="E296" t="s">
         <v>8</v>
@@ -6985,13 +6982,13 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D297" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E297" t="s">
         <v>8</v>
@@ -7002,13 +6999,13 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D298" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E298" t="s">
         <v>8</v>
@@ -7019,13 +7016,13 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D299" t="s">
-        <v>332</v>
+        <v>202</v>
       </c>
       <c r="E299" t="s">
         <v>8</v>
@@ -7036,13 +7033,13 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D300" t="s">
-        <v>293</v>
+        <v>372</v>
       </c>
       <c r="E300" t="s">
         <v>8</v>
@@ -7053,13 +7050,13 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D301" t="s">
-        <v>231</v>
+        <v>344</v>
       </c>
       <c r="E301" t="s">
         <v>8</v>
@@ -7070,13 +7067,13 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D302" t="s">
-        <v>378</v>
+        <v>309</v>
       </c>
       <c r="E302" t="s">
         <v>8</v>
@@ -7087,13 +7084,13 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D303" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="E303" t="s">
         <v>8</v>
@@ -7104,13 +7101,13 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D304" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
       <c r="E304" t="s">
         <v>8</v>
@@ -7121,13 +7118,13 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D305" t="s">
-        <v>306</v>
+        <v>282</v>
       </c>
       <c r="E305" t="s">
         <v>8</v>
@@ -7138,13 +7135,13 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D306" t="s">
-        <v>318</v>
+        <v>377</v>
       </c>
       <c r="E306" t="s">
         <v>8</v>
@@ -7155,13 +7152,13 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D307" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="E307" t="s">
         <v>8</v>
@@ -7172,13 +7169,13 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D308" t="s">
-        <v>391</v>
+        <v>242</v>
       </c>
       <c r="E308" t="s">
         <v>8</v>
@@ -7189,13 +7186,13 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D309" t="s">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="E309" t="s">
         <v>8</v>
@@ -7206,13 +7203,13 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D310" t="s">
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="E310" t="s">
         <v>8</v>
@@ -7223,13 +7220,13 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D311" t="s">
-        <v>318</v>
+        <v>210</v>
       </c>
       <c r="E311" t="s">
         <v>8</v>
@@ -7240,13 +7237,13 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D312" t="s">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="E312" t="s">
         <v>8</v>
@@ -7257,13 +7254,13 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D313" t="s">
-        <v>223</v>
+        <v>393</v>
       </c>
       <c r="E313" t="s">
         <v>8</v>
@@ -7274,13 +7271,13 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D314" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="E314" t="s">
         <v>8</v>
@@ -7291,13 +7288,13 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D315" t="s">
-        <v>399</v>
+        <v>204</v>
       </c>
       <c r="E315" t="s">
         <v>8</v>
@@ -7308,13 +7305,13 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D316" t="s">
-        <v>233</v>
+        <v>397</v>
       </c>
       <c r="E316" t="s">
         <v>8</v>
@@ -7325,13 +7322,13 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D317" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="E317" t="s">
         <v>8</v>
@@ -7342,13 +7339,13 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D318" t="s">
-        <v>371</v>
+        <v>269</v>
       </c>
       <c r="E318" t="s">
         <v>8</v>
@@ -7359,13 +7356,13 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D319" t="s">
-        <v>375</v>
+        <v>336</v>
       </c>
       <c r="E319" t="s">
         <v>8</v>
@@ -7376,13 +7373,13 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D320" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E320" t="s">
         <v>8</v>
@@ -7393,13 +7390,13 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D321" t="s">
-        <v>371</v>
+        <v>318</v>
       </c>
       <c r="E321" t="s">
         <v>8</v>
@@ -7410,13 +7407,13 @@
         <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D322" t="s">
-        <v>380</v>
+        <v>336</v>
       </c>
       <c r="E322" t="s">
         <v>8</v>
@@ -7427,13 +7424,13 @@
         <v>322</v>
       </c>
       <c r="B323" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D323" t="s">
-        <v>206</v>
+        <v>237</v>
       </c>
       <c r="E323" t="s">
         <v>8</v>
@@ -7444,13 +7441,13 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D324" t="s">
-        <v>410</v>
+        <v>301</v>
       </c>
       <c r="E324" t="s">
         <v>8</v>
@@ -7461,13 +7458,13 @@
         <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D325" t="s">
-        <v>318</v>
+        <v>202</v>
       </c>
       <c r="E325" t="s">
         <v>8</v>
@@ -7478,13 +7475,13 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D326" t="s">
-        <v>229</v>
+        <v>257</v>
       </c>
       <c r="E326" t="s">
         <v>8</v>
@@ -7495,13 +7492,13 @@
         <v>326</v>
       </c>
       <c r="B327" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D327" t="s">
-        <v>414</v>
+        <v>190</v>
       </c>
       <c r="E327" t="s">
         <v>8</v>
@@ -7512,13 +7509,13 @@
         <v>327</v>
       </c>
       <c r="B328" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D328" t="s">
-        <v>284</v>
+        <v>402</v>
       </c>
       <c r="E328" t="s">
         <v>8</v>
@@ -7529,13 +7526,13 @@
         <v>328</v>
       </c>
       <c r="B329" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D329" t="s">
-        <v>417</v>
+        <v>261</v>
       </c>
       <c r="E329" t="s">
         <v>8</v>
@@ -7546,13 +7543,13 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D330" t="s">
-        <v>332</v>
+        <v>214</v>
       </c>
       <c r="E330" t="s">
         <v>8</v>
@@ -7563,13 +7560,13 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D331" t="s">
-        <v>414</v>
+        <v>200</v>
       </c>
       <c r="E331" t="s">
         <v>8</v>
@@ -7580,13 +7577,13 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D332" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E332" t="s">
         <v>8</v>
@@ -7597,13 +7594,13 @@
         <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D333" t="s">
-        <v>275</v>
+        <v>204</v>
       </c>
       <c r="E333" t="s">
         <v>8</v>
@@ -7614,13 +7611,13 @@
         <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D334" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E334" t="s">
         <v>8</v>
@@ -7631,13 +7628,13 @@
         <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D335" t="s">
-        <v>410</v>
+        <v>239</v>
       </c>
       <c r="E335" t="s">
         <v>8</v>
@@ -7648,13 +7645,13 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D336" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="E336" t="s">
         <v>8</v>
@@ -7665,13 +7662,13 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D337" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="E337" t="s">
         <v>8</v>
@@ -7682,13 +7679,13 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D338" t="s">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="E338" t="s">
         <v>8</v>
@@ -7699,13 +7696,13 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D339" t="s">
-        <v>200</v>
+        <v>248</v>
       </c>
       <c r="E339" t="s">
         <v>8</v>
@@ -7716,13 +7713,13 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D340" t="s">
-        <v>320</v>
+        <v>424</v>
       </c>
       <c r="E340" t="s">
         <v>8</v>
@@ -7733,13 +7730,13 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D341" t="s">
-        <v>212</v>
+        <v>426</v>
       </c>
       <c r="E341" t="s">
         <v>8</v>
@@ -7750,13 +7747,13 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D342" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="E342" t="s">
         <v>8</v>
@@ -7767,13 +7764,13 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D343" t="s">
-        <v>367</v>
+        <v>231</v>
       </c>
       <c r="E343" t="s">
         <v>8</v>
@@ -7784,13 +7781,13 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D344" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="E344" t="s">
         <v>8</v>
@@ -7801,13 +7798,13 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D345" t="s">
-        <v>280</v>
+        <v>432</v>
       </c>
       <c r="E345" t="s">
         <v>8</v>
@@ -7818,13 +7815,13 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D346" t="s">
-        <v>436</v>
+        <v>216</v>
       </c>
       <c r="E346" t="s">
         <v>8</v>
@@ -7835,13 +7832,13 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D347" t="s">
-        <v>375</v>
+        <v>435</v>
       </c>
       <c r="E347" t="s">
         <v>8</v>
@@ -7852,13 +7849,13 @@
         <v>347</v>
       </c>
       <c r="B348" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D348" t="s">
-        <v>363</v>
+        <v>261</v>
       </c>
       <c r="E348" t="s">
         <v>8</v>
@@ -7869,13 +7866,13 @@
         <v>348</v>
       </c>
       <c r="B349" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D349" t="s">
-        <v>221</v>
+        <v>282</v>
       </c>
       <c r="E349" t="s">
         <v>8</v>
@@ -7886,13 +7883,13 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D350" t="s">
-        <v>275</v>
+        <v>216</v>
       </c>
       <c r="E350" t="s">
         <v>8</v>
@@ -7903,13 +7900,13 @@
         <v>350</v>
       </c>
       <c r="B351" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D351" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="E351" t="s">
         <v>8</v>
@@ -7920,13 +7917,13 @@
         <v>351</v>
       </c>
       <c r="B352" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D352" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="E352" t="s">
         <v>8</v>
@@ -7937,13 +7934,13 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D353" t="s">
-        <v>286</v>
+        <v>202</v>
       </c>
       <c r="E353" t="s">
         <v>8</v>
@@ -7954,13 +7951,13 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D354" t="s">
-        <v>200</v>
+        <v>246</v>
       </c>
       <c r="E354" t="s">
         <v>8</v>
@@ -7971,13 +7968,13 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D355" t="s">
-        <v>194</v>
+        <v>444</v>
       </c>
       <c r="E355" t="s">
         <v>8</v>
@@ -7988,13 +7985,13 @@
         <v>355</v>
       </c>
       <c r="B356" t="s">
+        <v>445</v>
+      </c>
+      <c r="C356" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D356" t="s">
         <v>446</v>
-      </c>
-      <c r="C356" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D356" t="s">
-        <v>238</v>
       </c>
       <c r="E356" t="s">
         <v>8</v>
@@ -8011,7 +8008,7 @@
         <v>6</v>
       </c>
       <c r="D357" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="E357" t="s">
         <v>8</v>
@@ -8028,7 +8025,7 @@
         <v>6</v>
       </c>
       <c r="D358" t="s">
-        <v>449</v>
+        <v>318</v>
       </c>
       <c r="E358" t="s">
         <v>8</v>
@@ -8039,13 +8036,13 @@
         <v>358</v>
       </c>
       <c r="B359" t="s">
+        <v>449</v>
+      </c>
+      <c r="C359" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D359" t="s">
         <v>450</v>
-      </c>
-      <c r="C359" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D359" t="s">
-        <v>196</v>
       </c>
       <c r="E359" t="s">
         <v>8</v>
@@ -8079,7 +8076,7 @@
         <v>6</v>
       </c>
       <c r="D361" t="s">
-        <v>303</v>
+        <v>369</v>
       </c>
       <c r="E361" t="s">
         <v>8</v>
@@ -8096,7 +8093,7 @@
         <v>6</v>
       </c>
       <c r="D362" t="s">
-        <v>264</v>
+        <v>397</v>
       </c>
       <c r="E362" t="s">
         <v>8</v>
@@ -8113,7 +8110,7 @@
         <v>6</v>
       </c>
       <c r="D363" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="E363" t="s">
         <v>8</v>
@@ -8130,7 +8127,7 @@
         <v>6</v>
       </c>
       <c r="D364" t="s">
-        <v>277</v>
+        <v>214</v>
       </c>
       <c r="E364" t="s">
         <v>8</v>
@@ -8147,7 +8144,7 @@
         <v>6</v>
       </c>
       <c r="D365" t="s">
-        <v>286</v>
+        <v>458</v>
       </c>
       <c r="E365" t="s">
         <v>8</v>
@@ -8158,13 +8155,13 @@
         <v>365</v>
       </c>
       <c r="B366" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D366" t="s">
-        <v>250</v>
+        <v>446</v>
       </c>
       <c r="E366" t="s">
         <v>8</v>
@@ -8175,13 +8172,13 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D367" t="s">
-        <v>202</v>
+        <v>461</v>
       </c>
       <c r="E367" t="s">
         <v>8</v>
@@ -8192,13 +8189,13 @@
         <v>367</v>
       </c>
       <c r="B368" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D368" t="s">
-        <v>303</v>
+        <v>222</v>
       </c>
       <c r="E368" t="s">
         <v>8</v>
@@ -8209,13 +8206,13 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D369" t="s">
-        <v>462</v>
+        <v>372</v>
       </c>
       <c r="E369" t="s">
         <v>8</v>
@@ -8226,13 +8223,13 @@
         <v>369</v>
       </c>
       <c r="B370" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D370" t="s">
-        <v>332</v>
+        <v>259</v>
       </c>
       <c r="E370" t="s">
         <v>8</v>
@@ -8243,13 +8240,13 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D371" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E371" t="s">
         <v>8</v>
@@ -8260,13 +8257,13 @@
         <v>371</v>
       </c>
       <c r="B372" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D372" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="E372" t="s">
         <v>8</v>
@@ -8277,13 +8274,13 @@
         <v>372</v>
       </c>
       <c r="B373" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D373" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="E373" t="s">
         <v>8</v>
@@ -8294,13 +8291,13 @@
         <v>373</v>
       </c>
       <c r="B374" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D374" t="s">
-        <v>200</v>
+        <v>336</v>
       </c>
       <c r="E374" t="s">
         <v>8</v>
@@ -8311,13 +8308,13 @@
         <v>374</v>
       </c>
       <c r="B375" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D375" t="s">
-        <v>206</v>
+        <v>255</v>
       </c>
       <c r="E375" t="s">
         <v>8</v>
@@ -8328,13 +8325,13 @@
         <v>375</v>
       </c>
       <c r="B376" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D376" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="E376" t="s">
         <v>8</v>
@@ -8345,13 +8342,13 @@
         <v>376</v>
       </c>
       <c r="B377" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D377" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E377" t="s">
         <v>8</v>
@@ -8362,13 +8359,13 @@
         <v>377</v>
       </c>
       <c r="B378" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D378" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E378" t="s">
         <v>8</v>
@@ -8379,13 +8376,13 @@
         <v>378</v>
       </c>
       <c r="B379" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D379" t="s">
-        <v>449</v>
+        <v>333</v>
       </c>
       <c r="E379" t="s">
         <v>8</v>
@@ -8396,13 +8393,13 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D380" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="E380" t="s">
         <v>8</v>
@@ -8413,13 +8410,13 @@
         <v>380</v>
       </c>
       <c r="B381" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D381" t="s">
-        <v>252</v>
+        <v>318</v>
       </c>
       <c r="E381" t="s">
         <v>8</v>
@@ -8430,13 +8427,13 @@
         <v>381</v>
       </c>
       <c r="B382" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D382" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="E382" t="s">
         <v>8</v>
@@ -8447,13 +8444,13 @@
         <v>382</v>
       </c>
       <c r="B383" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D383" t="s">
-        <v>462</v>
+        <v>226</v>
       </c>
       <c r="E383" t="s">
         <v>8</v>
@@ -8464,13 +8461,13 @@
         <v>383</v>
       </c>
       <c r="B384" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D384" t="s">
-        <v>367</v>
+        <v>261</v>
       </c>
       <c r="E384" t="s">
         <v>8</v>
@@ -8481,13 +8478,13 @@
         <v>384</v>
       </c>
       <c r="B385" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D385" t="s">
-        <v>363</v>
+        <v>340</v>
       </c>
       <c r="E385" t="s">
         <v>8</v>
@@ -8498,13 +8495,13 @@
         <v>385</v>
       </c>
       <c r="B386" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D386" t="s">
-        <v>282</v>
+        <v>372</v>
       </c>
       <c r="E386" t="s">
         <v>8</v>
@@ -8515,13 +8512,13 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D387" t="s">
-        <v>483</v>
+        <v>375</v>
       </c>
       <c r="E387" t="s">
         <v>8</v>
@@ -8538,7 +8535,7 @@
         <v>6</v>
       </c>
       <c r="D388" t="s">
-        <v>306</v>
+        <v>364</v>
       </c>
       <c r="E388" t="s">
         <v>8</v>
@@ -8555,7 +8552,7 @@
         <v>6</v>
       </c>
       <c r="D389" t="s">
-        <v>293</v>
+        <v>216</v>
       </c>
       <c r="E389" t="s">
         <v>8</v>
@@ -8572,7 +8569,7 @@
         <v>6</v>
       </c>
       <c r="D390" t="s">
-        <v>487</v>
+        <v>325</v>
       </c>
       <c r="E390" t="s">
         <v>8</v>
@@ -8583,13 +8580,13 @@
         <v>390</v>
       </c>
       <c r="B391" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D391" t="s">
-        <v>378</v>
+        <v>222</v>
       </c>
       <c r="E391" t="s">
         <v>8</v>
@@ -8600,13 +8597,13 @@
         <v>391</v>
       </c>
       <c r="B392" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D392" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="E392" t="s">
         <v>8</v>
@@ -8617,13 +8614,13 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D393" t="s">
-        <v>462</v>
+        <v>200</v>
       </c>
       <c r="E393" t="s">
         <v>8</v>
@@ -8634,13 +8631,13 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D394" t="s">
-        <v>349</v>
+        <v>253</v>
       </c>
       <c r="E394" t="s">
         <v>8</v>
@@ -8651,13 +8648,13 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D395" t="s">
-        <v>238</v>
+        <v>355</v>
       </c>
       <c r="E395" t="s">
         <v>8</v>
@@ -8668,13 +8665,13 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D396" t="s">
-        <v>229</v>
+        <v>206</v>
       </c>
       <c r="E396" t="s">
         <v>8</v>
@@ -8685,13 +8682,13 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D397" t="s">
-        <v>223</v>
+        <v>369</v>
       </c>
       <c r="E397" t="s">
         <v>8</v>
@@ -8702,13 +8699,13 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D398" t="s">
-        <v>471</v>
+        <v>284</v>
       </c>
       <c r="E398" t="s">
         <v>8</v>
@@ -8719,13 +8716,13 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D399" t="s">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="E399" t="s">
         <v>8</v>
@@ -8736,13 +8733,13 @@
         <v>399</v>
       </c>
       <c r="B400" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D400" t="s">
-        <v>282</v>
+        <v>435</v>
       </c>
       <c r="E400" t="s">
         <v>8</v>
@@ -8753,13 +8750,13 @@
         <v>400</v>
       </c>
       <c r="B401" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D401" t="s">
-        <v>330</v>
+        <v>311</v>
       </c>
       <c r="E401" t="s">
         <v>8</v>
@@ -8778,47 +8775,47 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B1" t="s">
         <v>499</v>
-      </c>
-      <c r="B1" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B2" t="s">
         <v>501</v>
-      </c>
-      <c r="B2" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>502</v>
+      </c>
+      <c r="B3" t="s">
         <v>503</v>
-      </c>
-      <c r="B3" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>504</v>
+      </c>
+      <c r="B4" t="s">
         <v>505</v>
-      </c>
-      <c r="B4" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>506</v>
+      </c>
+      <c r="B5" t="s">
         <v>507</v>
-      </c>
-      <c r="B5" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B6">
         <v>400</v>
@@ -8826,7 +8823,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B7">
         <v>400</v>
@@ -8834,7 +8831,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -8842,7 +8839,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -8850,10 +8847,10 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>512</v>
+      </c>
+      <c r="B10" t="s">
         <v>513</v>
-      </c>
-      <c r="B10" t="s">
-        <v>514</v>
       </c>
     </row>
   </sheetData>

--- a/reports/backend/Excel/Automation_Test_Report.xlsx
+++ b/reports/backend/Excel/Automation_Test_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="510">
   <si>
     <t>#</t>
   </si>
@@ -62,12 +62,12 @@
     <t>Smart Admission Backend — Authentication Tests BT-008 | Firebase config has all 6 required fields</t>
   </si>
   <si>
+    <t>Smart Admission Backend — Authentication Tests BT-009 | Firebase config fields are non-empty strings</t>
+  </si>
+  <si>
     <t>0.001</t>
   </si>
   <si>
-    <t>Smart Admission Backend — Authentication Tests BT-009 | Firebase config fields are non-empty strings</t>
-  </si>
-  <si>
     <t>Smart Admission Backend — Authentication Tests BT-010 | Firebase apiKey has expected format (AIza...)</t>
   </si>
   <si>
@@ -584,891 +584,876 @@
     <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #180</t>
   </si>
   <si>
+    <t>0.089</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #181</t>
+  </si>
+  <si>
+    <t>0.109</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #182</t>
+  </si>
+  <si>
+    <t>0.108</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #183</t>
+  </si>
+  <si>
+    <t>0.021</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #184</t>
+  </si>
+  <si>
+    <t>0.062</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #185</t>
+  </si>
+  <si>
+    <t>0.020</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #186</t>
+  </si>
+  <si>
+    <t>0.088</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #187</t>
+  </si>
+  <si>
+    <t>0.034</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #188</t>
+  </si>
+  <si>
+    <t>0.056</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #189</t>
+  </si>
+  <si>
+    <t>0.063</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #190</t>
+  </si>
+  <si>
+    <t>0.078</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #191</t>
+  </si>
+  <si>
+    <t>0.026</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #192</t>
+  </si>
+  <si>
+    <t>0.064</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #193</t>
+  </si>
+  <si>
+    <t>0.093</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #194</t>
+  </si>
+  <si>
+    <t>0.048</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #195</t>
+  </si>
+  <si>
+    <t>0.051</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #196</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #197</t>
+  </si>
+  <si>
+    <t>0.097</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #198</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #199</t>
+  </si>
+  <si>
+    <t>0.043</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #200</t>
+  </si>
+  <si>
+    <t>0.085</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #201</t>
+  </si>
+  <si>
+    <t>0.114</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #202</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #203</t>
+  </si>
+  <si>
+    <t>0.029</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #204</t>
+  </si>
+  <si>
+    <t>0.061</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #205</t>
+  </si>
+  <si>
+    <t>0.067</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #206</t>
+  </si>
+  <si>
+    <t>0.095</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #207</t>
+  </si>
+  <si>
+    <t>0.038</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #208</t>
+  </si>
+  <si>
+    <t>0.058</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #209</t>
+  </si>
+  <si>
+    <t>0.074</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #210</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #211</t>
+  </si>
+  <si>
+    <t>0.068</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #212</t>
+  </si>
+  <si>
+    <t>0.054</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #213</t>
+  </si>
+  <si>
+    <t>0.050</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #214</t>
+  </si>
+  <si>
+    <t>0.045</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #215</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #216</t>
+  </si>
+  <si>
+    <t>0.024</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #217</t>
+  </si>
+  <si>
+    <t>0.073</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #218</t>
+  </si>
+  <si>
+    <t>0.023</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #219</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #220</t>
+  </si>
+  <si>
+    <t>0.087</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #221</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #222</t>
+  </si>
+  <si>
+    <t>0.022</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #223</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #224</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #225</t>
+  </si>
+  <si>
+    <t>0.066</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #226</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #227</t>
+  </si>
+  <si>
+    <t>0.049</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #228</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #229</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #230</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #231</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #232</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #233</t>
+  </si>
+  <si>
+    <t>0.090</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #234</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #235</t>
+  </si>
+  <si>
+    <t>0.113</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #236</t>
+  </si>
+  <si>
+    <t>0.086</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #237</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #238</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #239</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #240</t>
+  </si>
+  <si>
+    <t>0.111</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #241</t>
+  </si>
+  <si>
+    <t>0.098</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #242</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #243</t>
+  </si>
+  <si>
+    <t>0.118</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #244</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #245</t>
+  </si>
+  <si>
+    <t>0.059</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #246</t>
+  </si>
+  <si>
+    <t>0.035</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #247</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #248</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #249</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #250</t>
+  </si>
+  <si>
+    <t>0.042</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #251</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #252</t>
+  </si>
+  <si>
+    <t>0.080</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #253</t>
+  </si>
+  <si>
+    <t>0.101</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #254</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #255</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #256</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #257</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #258</t>
+  </si>
+  <si>
+    <t>0.046</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #259</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #260</t>
+  </si>
+  <si>
+    <t>0.102</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #261</t>
+  </si>
+  <si>
+    <t>0.052</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #262</t>
+  </si>
+  <si>
+    <t>0.081</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #263</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #264</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #265</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #266</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #267</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #268</t>
+  </si>
+  <si>
+    <t>0.040</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #269</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #270</t>
+  </si>
+  <si>
+    <t>0.071</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #271</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #272</t>
+  </si>
+  <si>
     <t>0.070</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #181</t>
-  </si>
-  <si>
-    <t>0.050</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #182</t>
-  </si>
-  <si>
-    <t>0.081</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #183</t>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #273</t>
+  </si>
+  <si>
+    <t>0.115</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #274</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #275</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #276</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #277</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #278</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #279</t>
+  </si>
+  <si>
+    <t>0.037</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #280</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #281</t>
+  </si>
+  <si>
+    <t>0.069</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #282</t>
+  </si>
+  <si>
+    <t>0.075</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #283</t>
+  </si>
+  <si>
+    <t>0.119</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #284</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #285</t>
+  </si>
+  <si>
+    <t>0.053</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #286</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #287</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #288</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #289</t>
+  </si>
+  <si>
+    <t>0.096</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #290</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #291</t>
+  </si>
+  <si>
+    <t>0.077</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #292</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #293</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #294</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #295</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #296</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #297</t>
+  </si>
+  <si>
+    <t>0.110</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #298</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #299</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #300</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #301</t>
+  </si>
+  <si>
+    <t>0.031</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #302</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #303</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #304</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #305</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #306</t>
+  </si>
+  <si>
+    <t>0.036</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #307</t>
+  </si>
+  <si>
+    <t>0.047</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #308</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #309</t>
+  </si>
+  <si>
+    <t>0.076</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #310</t>
+  </si>
+  <si>
+    <t>0.055</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #311</t>
   </si>
   <si>
     <t>0.104</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #184</t>
-  </si>
-  <si>
-    <t>0.032</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #185</t>
-  </si>
-  <si>
-    <t>0.108</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #186</t>
-  </si>
-  <si>
-    <t>0.101</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #187</t>
-  </si>
-  <si>
-    <t>0.021</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #188</t>
-  </si>
-  <si>
-    <t>0.053</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #189</t>
-  </si>
-  <si>
-    <t>0.026</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #190</t>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #312</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #313</t>
   </si>
   <si>
     <t>0.060</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #191</t>
-  </si>
-  <si>
-    <t>0.109</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #192</t>
-  </si>
-  <si>
-    <t>0.034</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #193</t>
-  </si>
-  <si>
-    <t>0.076</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #194</t>
-  </si>
-  <si>
-    <t>0.030</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #195</t>
-  </si>
-  <si>
-    <t>0.039</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #196</t>
-  </si>
-  <si>
-    <t>0.087</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #197</t>
-  </si>
-  <si>
-    <t>0.031</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #198</t>
-  </si>
-  <si>
-    <t>0.069</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #199</t>
-  </si>
-  <si>
-    <t>0.113</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #200</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #201</t>
-  </si>
-  <si>
-    <t>0.102</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #202</t>
-  </si>
-  <si>
-    <t>0.045</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #203</t>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #314</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #315</t>
   </si>
   <si>
     <t>0.094</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #204</t>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #316</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #317</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #318</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #319</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #320</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #321</t>
+  </si>
+  <si>
+    <t>0.084</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #322</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #323</t>
+  </si>
+  <si>
+    <t>0.112</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #324</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #325</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #326</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #327</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #328</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #329</t>
+  </si>
+  <si>
+    <t>0.044</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #330</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #331</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #332</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #333</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #334</t>
+  </si>
+  <si>
+    <t>0.107</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #335</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #336</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #337</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #338</t>
+  </si>
+  <si>
+    <t>0.082</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #339</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #340</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #341</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #342</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #343</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #344</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #345</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #346</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #347</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #348</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #349</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #350</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #351</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #352</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #353</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #354</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #355</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #356</t>
   </si>
   <si>
     <t>0.116</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #205</t>
-  </si>
-  <si>
-    <t>0.075</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #206</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #207</t>
-  </si>
-  <si>
-    <t>0.046</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #208</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #209</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #210</t>
-  </si>
-  <si>
-    <t>0.048</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #211</t>
-  </si>
-  <si>
-    <t>0.095</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #212</t>
-  </si>
-  <si>
-    <t>0.059</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #213</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #214</t>
-  </si>
-  <si>
-    <t>0.118</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #215</t>
-  </si>
-  <si>
-    <t>0.080</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #216</t>
-  </si>
-  <si>
-    <t>0.096</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #217</t>
-  </si>
-  <si>
-    <t>0.115</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #218</t>
-  </si>
-  <si>
-    <t>0.117</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #219</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #220</t>
-  </si>
-  <si>
-    <t>0.074</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #221</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #222</t>
-  </si>
-  <si>
-    <t>0.054</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #223</t>
-  </si>
-  <si>
-    <t>0.028</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #224</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #225</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #226</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #227</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #228</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #229</t>
-  </si>
-  <si>
-    <t>0.066</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #230</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #231</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #232</t>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #357</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #358</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #359</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #360</t>
+  </si>
+  <si>
+    <t>0.057</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #361</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #362</t>
+  </si>
+  <si>
+    <t>0.079</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #363</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #364</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #365</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #366</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #367</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #368</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #369</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #370</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #371</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #372</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #373</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #374</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #375</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #376</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #377</t>
+  </si>
+  <si>
+    <t>0.099</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #378</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #379</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #380</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #381</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #382</t>
   </si>
   <si>
     <t>0.041</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #233</t>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #383</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #384</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #385</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #386</t>
   </si>
   <si>
     <t>0.083</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #234</t>
-  </si>
-  <si>
-    <t>0.079</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #235</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #236</t>
-  </si>
-  <si>
-    <t>0.064</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #237</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #238</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #239</t>
-  </si>
-  <si>
-    <t>0.029</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #240</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #241</t>
-  </si>
-  <si>
-    <t>0.097</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #242</t>
-  </si>
-  <si>
-    <t>0.103</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #243</t>
-  </si>
-  <si>
-    <t>0.024</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #244</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #245</t>
-  </si>
-  <si>
-    <t>0.077</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #246</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #247</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #248</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #249</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #250</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #251</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #252</t>
-  </si>
-  <si>
-    <t>0.110</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #253</t>
-  </si>
-  <si>
-    <t>0.111</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #254</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #255</t>
-  </si>
-  <si>
-    <t>0.071</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #256</t>
-  </si>
-  <si>
-    <t>0.043</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #257</t>
-  </si>
-  <si>
-    <t>0.051</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #258</t>
-  </si>
-  <si>
-    <t>0.033</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #259</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #260</t>
-  </si>
-  <si>
-    <t>0.093</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #261</t>
-  </si>
-  <si>
-    <t>0.062</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #262</t>
-  </si>
-  <si>
-    <t>0.119</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #263</t>
-  </si>
-  <si>
-    <t>0.042</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #264</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #265</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #266</t>
-  </si>
-  <si>
-    <t>0.055</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #267</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #268</t>
-  </si>
-  <si>
-    <t>0.085</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #269</t>
-  </si>
-  <si>
-    <t>0.106</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #270</t>
-  </si>
-  <si>
-    <t>0.025</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #271</t>
-  </si>
-  <si>
-    <t>0.067</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #272</t>
-  </si>
-  <si>
-    <t>0.089</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #273</t>
-  </si>
-  <si>
-    <t>0.056</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #274</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #275</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #276</t>
-  </si>
-  <si>
-    <t>0.037</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #277</t>
-  </si>
-  <si>
-    <t>0.058</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #278</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #279</t>
-  </si>
-  <si>
-    <t>0.027</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #280</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #281</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #282</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #283</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #284</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #285</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #286</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #287</t>
-  </si>
-  <si>
-    <t>0.065</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #288</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #289</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #290</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #291</t>
-  </si>
-  <si>
-    <t>0.020</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #292</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #293</t>
-  </si>
-  <si>
-    <t>0.114</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #294</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #295</t>
-  </si>
-  <si>
-    <t>0.047</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #296</t>
-  </si>
-  <si>
-    <t>0.088</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #297</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #298</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #299</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #300</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #301</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #302</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #303</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #304</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #305</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #306</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #307</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #308</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #309</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #310</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #311</t>
-  </si>
-  <si>
-    <t>0.082</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #312</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #313</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #314</t>
-  </si>
-  <si>
-    <t>0.035</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #315</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #316</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #317</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #318</t>
-  </si>
-  <si>
-    <t>0.112</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #319</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #320</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #321</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #322</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #323</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #324</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #325</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #326</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #327</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #328</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #329</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #330</t>
-  </si>
-  <si>
-    <t>0.092</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #331</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #332</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #333</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #334</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #335</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #336</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #337</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #338</t>
-  </si>
-  <si>
-    <t>0.044</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #339</t>
-  </si>
-  <si>
-    <t>0.061</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #340</t>
-  </si>
-  <si>
-    <t>0.086</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #341</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #342</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #343</t>
-  </si>
-  <si>
-    <t>0.072</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #344</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #345</t>
-  </si>
-  <si>
-    <t>0.052</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #346</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #347</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #348</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #349</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #350</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #351</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #352</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #353</t>
-  </si>
-  <si>
-    <t>0.038</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #354</t>
-  </si>
-  <si>
-    <t>0.084</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #355</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #356</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #357</t>
-  </si>
-  <si>
-    <t>0.098</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #358</t>
-  </si>
-  <si>
-    <t>0.068</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #359</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #360</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #361</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #362</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #363</t>
-  </si>
-  <si>
-    <t>0.073</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #364</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #365</t>
-  </si>
-  <si>
-    <t>0.022</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #366</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #367</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #368</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #369</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #370</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #371</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #372</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #373</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #374</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #375</t>
-  </si>
-  <si>
-    <t>0.063</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #376</t>
-  </si>
-  <si>
-    <t>0.091</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #377</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #378</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #379</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #380</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #381</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #382</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #383</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #384</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #385</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #386</t>
-  </si>
-  <si>
     <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #387</t>
   </si>
   <si>
@@ -1499,6 +1484,9 @@
     <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #396</t>
   </si>
   <si>
+    <t>0.105</t>
+  </si>
+  <si>
     <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #397</t>
   </si>
   <si>
@@ -1517,13 +1505,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>12</t>
+    <t>14</t>
   </si>
   <si>
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 13:17:23 UTC</t>
+    <t>2026-06-23 13:38:07 UTC</t>
   </si>
   <si>
     <t>Branch</t>
@@ -1535,7 +1523,7 @@
     <t>Commit</t>
   </si>
   <si>
-    <t>cfbb4d3</t>
+    <t>3eb8262</t>
   </si>
   <si>
     <t>Total</t>
@@ -2092,7 +2080,7 @@
         <v>6</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -2103,13 +2091,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" t="s">
         <v>17</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" t="s">
-        <v>7</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -2364,7 +2352,7 @@
         <v>6</v>
       </c>
       <c r="D25" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -2891,7 +2879,7 @@
         <v>6</v>
       </c>
       <c r="D56" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -2908,7 +2896,7 @@
         <v>6</v>
       </c>
       <c r="D57" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -3146,7 +3134,7 @@
         <v>6</v>
       </c>
       <c r="D71" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
@@ -3486,7 +3474,7 @@
         <v>6</v>
       </c>
       <c r="D91" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E91" t="s">
         <v>8</v>
@@ -3503,7 +3491,7 @@
         <v>6</v>
       </c>
       <c r="D92" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E92" t="s">
         <v>8</v>
@@ -3571,7 +3559,7 @@
         <v>6</v>
       </c>
       <c r="D96" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E96" t="s">
         <v>8</v>
@@ -3656,7 +3644,7 @@
         <v>6</v>
       </c>
       <c r="D101" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E101" t="s">
         <v>8</v>
@@ -3724,7 +3712,7 @@
         <v>6</v>
       </c>
       <c r="D105" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E105" t="s">
         <v>8</v>
@@ -3877,7 +3865,7 @@
         <v>6</v>
       </c>
       <c r="D114" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E114" t="s">
         <v>8</v>
@@ -4030,7 +4018,7 @@
         <v>6</v>
       </c>
       <c r="D123" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E123" t="s">
         <v>8</v>
@@ -4064,7 +4052,7 @@
         <v>6</v>
       </c>
       <c r="D125" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E125" t="s">
         <v>8</v>
@@ -4217,7 +4205,7 @@
         <v>6</v>
       </c>
       <c r="D134" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E134" t="s">
         <v>8</v>
@@ -4251,7 +4239,7 @@
         <v>6</v>
       </c>
       <c r="D136" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E136" t="s">
         <v>8</v>
@@ -5305,7 +5293,7 @@
         <v>6</v>
       </c>
       <c r="D198" t="s">
-        <v>222</v>
+        <v>196</v>
       </c>
       <c r="E198" t="s">
         <v>8</v>
@@ -5316,13 +5304,13 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
+        <v>222</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D199" t="s">
         <v>223</v>
-      </c>
-      <c r="C199" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D199" t="s">
-        <v>224</v>
       </c>
       <c r="E199" t="s">
         <v>8</v>
@@ -5333,13 +5321,13 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D200" t="s">
-        <v>226</v>
+        <v>190</v>
       </c>
       <c r="E200" t="s">
         <v>8</v>
@@ -5350,13 +5338,13 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D201" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E201" t="s">
         <v>8</v>
@@ -5367,13 +5355,13 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D202" t="s">
-        <v>200</v>
+        <v>228</v>
       </c>
       <c r="E202" t="s">
         <v>8</v>
@@ -5384,13 +5372,13 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
+        <v>229</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D203" t="s">
         <v>230</v>
-      </c>
-      <c r="C203" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D203" t="s">
-        <v>231</v>
       </c>
       <c r="E203" t="s">
         <v>8</v>
@@ -5401,13 +5389,13 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D204" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="E204" t="s">
         <v>8</v>
@@ -5418,13 +5406,13 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D205" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E205" t="s">
         <v>8</v>
@@ -5435,13 +5423,13 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D206" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E206" t="s">
         <v>8</v>
@@ -5452,13 +5440,13 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D207" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E207" t="s">
         <v>8</v>
@@ -5469,13 +5457,13 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D208" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E208" t="s">
         <v>8</v>
@@ -5486,13 +5474,13 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
+        <v>240</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D209" t="s">
         <v>241</v>
-      </c>
-      <c r="C209" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D209" t="s">
-        <v>242</v>
       </c>
       <c r="E209" t="s">
         <v>8</v>
@@ -5503,13 +5491,13 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
+        <v>242</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D210" t="s">
         <v>243</v>
-      </c>
-      <c r="C210" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D210" t="s">
-        <v>235</v>
       </c>
       <c r="E210" t="s">
         <v>8</v>
@@ -5526,7 +5514,7 @@
         <v>6</v>
       </c>
       <c r="D211" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="E211" t="s">
         <v>8</v>
@@ -5537,13 +5525,13 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D212" t="s">
-        <v>246</v>
+        <v>208</v>
       </c>
       <c r="E212" t="s">
         <v>8</v>
@@ -5594,7 +5582,7 @@
         <v>6</v>
       </c>
       <c r="D215" t="s">
-        <v>212</v>
+        <v>252</v>
       </c>
       <c r="E215" t="s">
         <v>8</v>
@@ -5605,13 +5593,13 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D216" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E216" t="s">
         <v>8</v>
@@ -5622,13 +5610,13 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D217" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="E217" t="s">
         <v>8</v>
@@ -5696,7 +5684,7 @@
         <v>6</v>
       </c>
       <c r="D221" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="E221" t="s">
         <v>8</v>
@@ -5730,7 +5718,7 @@
         <v>6</v>
       </c>
       <c r="D223" t="s">
-        <v>194</v>
+        <v>259</v>
       </c>
       <c r="E223" t="s">
         <v>8</v>
@@ -5764,7 +5752,7 @@
         <v>6</v>
       </c>
       <c r="D225" t="s">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="E225" t="s">
         <v>8</v>
@@ -5775,13 +5763,13 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D226" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="E226" t="s">
         <v>8</v>
@@ -5792,13 +5780,13 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
+        <v>270</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D227" t="s">
         <v>271</v>
-      </c>
-      <c r="C227" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D227" t="s">
-        <v>198</v>
       </c>
       <c r="E227" t="s">
         <v>8</v>
@@ -5815,7 +5803,7 @@
         <v>6</v>
       </c>
       <c r="D228" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E228" t="s">
         <v>8</v>
@@ -5832,7 +5820,7 @@
         <v>6</v>
       </c>
       <c r="D229" t="s">
-        <v>204</v>
+        <v>274</v>
       </c>
       <c r="E229" t="s">
         <v>8</v>
@@ -5843,13 +5831,13 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D230" t="s">
-        <v>231</v>
+        <v>192</v>
       </c>
       <c r="E230" t="s">
         <v>8</v>
@@ -5860,13 +5848,13 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D231" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="E231" t="s">
         <v>8</v>
@@ -5883,7 +5871,7 @@
         <v>6</v>
       </c>
       <c r="D232" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="E232" t="s">
         <v>8</v>
@@ -5900,7 +5888,7 @@
         <v>6</v>
       </c>
       <c r="D233" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="E233" t="s">
         <v>8</v>
@@ -5917,7 +5905,7 @@
         <v>6</v>
       </c>
       <c r="D234" t="s">
-        <v>280</v>
+        <v>202</v>
       </c>
       <c r="E234" t="s">
         <v>8</v>
@@ -5928,13 +5916,13 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
+        <v>280</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D235" t="s">
         <v>281</v>
-      </c>
-      <c r="C235" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D235" t="s">
-        <v>282</v>
       </c>
       <c r="E235" t="s">
         <v>8</v>
@@ -5945,13 +5933,13 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D236" t="s">
-        <v>284</v>
+        <v>200</v>
       </c>
       <c r="E236" t="s">
         <v>8</v>
@@ -5962,13 +5950,13 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D237" t="s">
-        <v>216</v>
+        <v>284</v>
       </c>
       <c r="E237" t="s">
         <v>8</v>
@@ -5979,13 +5967,13 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
+        <v>285</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D238" t="s">
         <v>286</v>
-      </c>
-      <c r="C238" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D238" t="s">
-        <v>287</v>
       </c>
       <c r="E238" t="s">
         <v>8</v>
@@ -5996,13 +5984,13 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D239" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="E239" t="s">
         <v>8</v>
@@ -6013,13 +6001,13 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D240" t="s">
-        <v>259</v>
+        <v>198</v>
       </c>
       <c r="E240" t="s">
         <v>8</v>
@@ -6030,13 +6018,13 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D241" t="s">
-        <v>291</v>
+        <v>218</v>
       </c>
       <c r="E241" t="s">
         <v>8</v>
@@ -6047,13 +6035,13 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D242" t="s">
-        <v>190</v>
+        <v>291</v>
       </c>
       <c r="E242" t="s">
         <v>8</v>
@@ -6064,13 +6052,13 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
+        <v>292</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D243" t="s">
         <v>293</v>
-      </c>
-      <c r="C243" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D243" t="s">
-        <v>294</v>
       </c>
       <c r="E243" t="s">
         <v>8</v>
@@ -6081,13 +6069,13 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D244" t="s">
-        <v>296</v>
+        <v>254</v>
       </c>
       <c r="E244" t="s">
         <v>8</v>
@@ -6098,13 +6086,13 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D245" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E245" t="s">
         <v>8</v>
@@ -6115,13 +6103,13 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D246" t="s">
-        <v>210</v>
+        <v>291</v>
       </c>
       <c r="E246" t="s">
         <v>8</v>
@@ -6132,13 +6120,13 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D247" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E247" t="s">
         <v>8</v>
@@ -6149,13 +6137,13 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D248" t="s">
-        <v>248</v>
+        <v>301</v>
       </c>
       <c r="E248" t="s">
         <v>8</v>
@@ -6166,13 +6154,13 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D249" t="s">
-        <v>267</v>
+        <v>228</v>
       </c>
       <c r="E249" t="s">
         <v>8</v>
@@ -6183,13 +6171,13 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D250" t="s">
-        <v>237</v>
+        <v>291</v>
       </c>
       <c r="E250" t="s">
         <v>8</v>
@@ -6200,13 +6188,13 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D251" t="s">
-        <v>294</v>
+        <v>190</v>
       </c>
       <c r="E251" t="s">
         <v>8</v>
@@ -6217,13 +6205,13 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
+        <v>305</v>
+      </c>
+      <c r="C252" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D252" t="s">
         <v>306</v>
-      </c>
-      <c r="C252" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D252" t="s">
-        <v>200</v>
       </c>
       <c r="E252" t="s">
         <v>8</v>
@@ -6240,7 +6228,7 @@
         <v>6</v>
       </c>
       <c r="D253" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
       <c r="E253" t="s">
         <v>8</v>
@@ -6291,7 +6279,7 @@
         <v>6</v>
       </c>
       <c r="D256" t="s">
-        <v>259</v>
+        <v>218</v>
       </c>
       <c r="E256" t="s">
         <v>8</v>
@@ -6308,7 +6296,7 @@
         <v>6</v>
       </c>
       <c r="D257" t="s">
-        <v>314</v>
+        <v>210</v>
       </c>
       <c r="E257" t="s">
         <v>8</v>
@@ -6319,13 +6307,13 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D258" t="s">
-        <v>316</v>
+        <v>241</v>
       </c>
       <c r="E258" t="s">
         <v>8</v>
@@ -6336,13 +6324,13 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D259" t="s">
-        <v>318</v>
+        <v>210</v>
       </c>
       <c r="E259" t="s">
         <v>8</v>
@@ -6353,13 +6341,13 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D260" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E260" t="s">
         <v>8</v>
@@ -6370,13 +6358,13 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D261" t="s">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="E261" t="s">
         <v>8</v>
@@ -6387,13 +6375,13 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D262" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="E262" t="s">
         <v>8</v>
@@ -6404,13 +6392,13 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D263" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E263" t="s">
         <v>8</v>
@@ -6421,13 +6409,13 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D264" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="E264" t="s">
         <v>8</v>
@@ -6438,13 +6426,13 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D265" t="s">
-        <v>329</v>
+        <v>204</v>
       </c>
       <c r="E265" t="s">
         <v>8</v>
@@ -6455,13 +6443,13 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D266" t="s">
-        <v>196</v>
+        <v>248</v>
       </c>
       <c r="E266" t="s">
         <v>8</v>
@@ -6472,13 +6460,13 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D267" t="s">
-        <v>298</v>
+        <v>250</v>
       </c>
       <c r="E267" t="s">
         <v>8</v>
@@ -6489,13 +6477,13 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D268" t="s">
-        <v>333</v>
+        <v>214</v>
       </c>
       <c r="E268" t="s">
         <v>8</v>
@@ -6506,13 +6494,13 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D269" t="s">
-        <v>264</v>
+        <v>324</v>
       </c>
       <c r="E269" t="s">
         <v>8</v>
@@ -6523,13 +6511,13 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D270" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="E270" t="s">
         <v>8</v>
@@ -6540,13 +6528,13 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D271" t="s">
-        <v>338</v>
+        <v>243</v>
       </c>
       <c r="E271" t="s">
         <v>8</v>
@@ -6557,13 +6545,13 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D272" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="E272" t="s">
         <v>8</v>
@@ -6574,13 +6562,13 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D273" t="s">
-        <v>342</v>
+        <v>261</v>
       </c>
       <c r="E273" t="s">
         <v>8</v>
@@ -6591,13 +6579,13 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D274" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="E274" t="s">
         <v>8</v>
@@ -6608,13 +6596,13 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D275" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="E275" t="s">
         <v>8</v>
@@ -6625,13 +6613,13 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D276" t="s">
-        <v>200</v>
+        <v>334</v>
       </c>
       <c r="E276" t="s">
         <v>8</v>
@@ -6642,13 +6630,13 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D277" t="s">
-        <v>257</v>
+        <v>311</v>
       </c>
       <c r="E277" t="s">
         <v>8</v>
@@ -6659,13 +6647,13 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D278" t="s">
-        <v>350</v>
+        <v>324</v>
       </c>
       <c r="E278" t="s">
         <v>8</v>
@@ -6676,13 +6664,13 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D279" t="s">
-        <v>352</v>
+        <v>190</v>
       </c>
       <c r="E279" t="s">
         <v>8</v>
@@ -6693,13 +6681,13 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D280" t="s">
-        <v>287</v>
+        <v>337</v>
       </c>
       <c r="E280" t="s">
         <v>8</v>
@@ -6710,13 +6698,13 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D281" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="E281" t="s">
         <v>8</v>
@@ -6727,7 +6715,7 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>6</v>
@@ -6744,13 +6732,13 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D283" t="s">
-        <v>214</v>
+        <v>349</v>
       </c>
       <c r="E283" t="s">
         <v>8</v>
@@ -6761,13 +6749,13 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D284" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="E284" t="s">
         <v>8</v>
@@ -6778,13 +6766,13 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D285" t="s">
-        <v>267</v>
+        <v>353</v>
       </c>
       <c r="E285" t="s">
         <v>8</v>
@@ -6795,13 +6783,13 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D286" t="s">
-        <v>237</v>
+        <v>192</v>
       </c>
       <c r="E286" t="s">
         <v>8</v>
@@ -6812,13 +6800,13 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D287" t="s">
-        <v>329</v>
+        <v>356</v>
       </c>
       <c r="E287" t="s">
         <v>8</v>
@@ -6829,13 +6817,13 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D288" t="s">
-        <v>323</v>
+        <v>226</v>
       </c>
       <c r="E288" t="s">
         <v>8</v>
@@ -6846,13 +6834,13 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D289" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="E289" t="s">
         <v>8</v>
@@ -6863,13 +6851,13 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D290" t="s">
-        <v>301</v>
+        <v>274</v>
       </c>
       <c r="E290" t="s">
         <v>8</v>
@@ -6880,13 +6868,13 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D291" t="s">
-        <v>309</v>
+        <v>361</v>
       </c>
       <c r="E291" t="s">
         <v>8</v>
@@ -6897,13 +6885,13 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D292" t="s">
-        <v>233</v>
+        <v>261</v>
       </c>
       <c r="E292" t="s">
         <v>8</v>
@@ -6914,13 +6902,13 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D293" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="E293" t="s">
         <v>8</v>
@@ -6931,13 +6919,13 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D294" t="s">
-        <v>318</v>
+        <v>237</v>
       </c>
       <c r="E294" t="s">
         <v>8</v>
@@ -6948,13 +6936,13 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D295" t="s">
-        <v>372</v>
+        <v>233</v>
       </c>
       <c r="E295" t="s">
         <v>8</v>
@@ -6965,13 +6953,13 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D296" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="E296" t="s">
         <v>8</v>
@@ -6982,13 +6970,13 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D297" t="s">
-        <v>375</v>
+        <v>271</v>
       </c>
       <c r="E297" t="s">
         <v>8</v>
@@ -6999,13 +6987,13 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D298" t="s">
-        <v>377</v>
+        <v>254</v>
       </c>
       <c r="E298" t="s">
         <v>8</v>
@@ -7016,13 +7004,13 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D299" t="s">
-        <v>202</v>
+        <v>371</v>
       </c>
       <c r="E299" t="s">
         <v>8</v>
@@ -7033,13 +7021,13 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D300" t="s">
-        <v>372</v>
+        <v>228</v>
       </c>
       <c r="E300" t="s">
         <v>8</v>
@@ -7050,13 +7038,13 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D301" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="E301" t="s">
         <v>8</v>
@@ -7067,13 +7055,13 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D302" t="s">
-        <v>309</v>
+        <v>259</v>
       </c>
       <c r="E302" t="s">
         <v>8</v>
@@ -7084,13 +7072,13 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D303" t="s">
-        <v>204</v>
+        <v>376</v>
       </c>
       <c r="E303" t="s">
         <v>8</v>
@@ -7101,13 +7089,13 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D304" t="s">
-        <v>377</v>
+        <v>204</v>
       </c>
       <c r="E304" t="s">
         <v>8</v>
@@ -7118,13 +7106,13 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D305" t="s">
-        <v>282</v>
+        <v>356</v>
       </c>
       <c r="E305" t="s">
         <v>8</v>
@@ -7135,13 +7123,13 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D306" t="s">
-        <v>377</v>
+        <v>331</v>
       </c>
       <c r="E306" t="s">
         <v>8</v>
@@ -7152,13 +7140,13 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D307" t="s">
-        <v>296</v>
+        <v>331</v>
       </c>
       <c r="E307" t="s">
         <v>8</v>
@@ -7169,13 +7157,13 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D308" t="s">
-        <v>242</v>
+        <v>382</v>
       </c>
       <c r="E308" t="s">
         <v>8</v>
@@ -7186,13 +7174,13 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D309" t="s">
-        <v>196</v>
+        <v>384</v>
       </c>
       <c r="E309" t="s">
         <v>8</v>
@@ -7203,13 +7191,13 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D310" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E310" t="s">
         <v>8</v>
@@ -7220,13 +7208,13 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D311" t="s">
-        <v>210</v>
+        <v>387</v>
       </c>
       <c r="E311" t="s">
         <v>8</v>
@@ -7237,13 +7225,13 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D312" t="s">
-        <v>294</v>
+        <v>389</v>
       </c>
       <c r="E312" t="s">
         <v>8</v>
@@ -7254,13 +7242,13 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D313" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E313" t="s">
         <v>8</v>
@@ -7271,13 +7259,13 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D314" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E314" t="s">
         <v>8</v>
@@ -7288,13 +7276,13 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D315" t="s">
-        <v>204</v>
+        <v>394</v>
       </c>
       <c r="E315" t="s">
         <v>8</v>
@@ -7305,13 +7293,13 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D316" t="s">
-        <v>397</v>
+        <v>353</v>
       </c>
       <c r="E316" t="s">
         <v>8</v>
@@ -7322,13 +7310,13 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D317" t="s">
-        <v>248</v>
+        <v>397</v>
       </c>
       <c r="E317" t="s">
         <v>8</v>
@@ -7339,13 +7327,13 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D318" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="E318" t="s">
         <v>8</v>
@@ -7356,13 +7344,13 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D319" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E319" t="s">
         <v>8</v>
@@ -7373,13 +7361,13 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D320" t="s">
-        <v>402</v>
+        <v>324</v>
       </c>
       <c r="E320" t="s">
         <v>8</v>
@@ -7390,13 +7378,13 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D321" t="s">
-        <v>318</v>
+        <v>349</v>
       </c>
       <c r="E321" t="s">
         <v>8</v>
@@ -7407,13 +7395,13 @@
         <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D322" t="s">
-        <v>336</v>
+        <v>271</v>
       </c>
       <c r="E322" t="s">
         <v>8</v>
@@ -7424,13 +7412,13 @@
         <v>322</v>
       </c>
       <c r="B323" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D323" t="s">
-        <v>237</v>
+        <v>404</v>
       </c>
       <c r="E323" t="s">
         <v>8</v>
@@ -7441,13 +7429,13 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D324" t="s">
-        <v>301</v>
+        <v>267</v>
       </c>
       <c r="E324" t="s">
         <v>8</v>
@@ -7458,13 +7446,13 @@
         <v>324</v>
       </c>
       <c r="B325" t="s">
+        <v>406</v>
+      </c>
+      <c r="C325" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D325" t="s">
         <v>407</v>
-      </c>
-      <c r="C325" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D325" t="s">
-        <v>202</v>
       </c>
       <c r="E325" t="s">
         <v>8</v>
@@ -7481,7 +7469,7 @@
         <v>6</v>
       </c>
       <c r="D326" t="s">
-        <v>257</v>
+        <v>394</v>
       </c>
       <c r="E326" t="s">
         <v>8</v>
@@ -7498,7 +7486,7 @@
         <v>6</v>
       </c>
       <c r="D327" t="s">
-        <v>190</v>
+        <v>281</v>
       </c>
       <c r="E327" t="s">
         <v>8</v>
@@ -7515,7 +7503,7 @@
         <v>6</v>
       </c>
       <c r="D328" t="s">
-        <v>402</v>
+        <v>254</v>
       </c>
       <c r="E328" t="s">
         <v>8</v>
@@ -7532,7 +7520,7 @@
         <v>6</v>
       </c>
       <c r="D329" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
       <c r="E329" t="s">
         <v>8</v>
@@ -7549,7 +7537,7 @@
         <v>6</v>
       </c>
       <c r="D330" t="s">
-        <v>214</v>
+        <v>296</v>
       </c>
       <c r="E330" t="s">
         <v>8</v>
@@ -7566,7 +7554,7 @@
         <v>6</v>
       </c>
       <c r="D331" t="s">
-        <v>200</v>
+        <v>414</v>
       </c>
       <c r="E331" t="s">
         <v>8</v>
@@ -7577,13 +7565,13 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
+        <v>415</v>
+      </c>
+      <c r="C332" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D332" t="s">
         <v>414</v>
-      </c>
-      <c r="C332" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D332" t="s">
-        <v>415</v>
       </c>
       <c r="E332" t="s">
         <v>8</v>
@@ -7600,7 +7588,7 @@
         <v>6</v>
       </c>
       <c r="D333" t="s">
-        <v>204</v>
+        <v>349</v>
       </c>
       <c r="E333" t="s">
         <v>8</v>
@@ -7617,7 +7605,7 @@
         <v>6</v>
       </c>
       <c r="D334" t="s">
-        <v>329</v>
+        <v>299</v>
       </c>
       <c r="E334" t="s">
         <v>8</v>
@@ -7634,7 +7622,7 @@
         <v>6</v>
       </c>
       <c r="D335" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E335" t="s">
         <v>8</v>
@@ -7651,7 +7639,7 @@
         <v>6</v>
       </c>
       <c r="D336" t="s">
-        <v>261</v>
+        <v>420</v>
       </c>
       <c r="E336" t="s">
         <v>8</v>
@@ -7662,13 +7650,13 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D337" t="s">
-        <v>325</v>
+        <v>208</v>
       </c>
       <c r="E337" t="s">
         <v>8</v>
@@ -7679,13 +7667,13 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D338" t="s">
-        <v>222</v>
+        <v>376</v>
       </c>
       <c r="E338" t="s">
         <v>8</v>
@@ -7696,13 +7684,13 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D339" t="s">
-        <v>248</v>
+        <v>194</v>
       </c>
       <c r="E339" t="s">
         <v>8</v>
@@ -7713,13 +7701,13 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D340" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E340" t="s">
         <v>8</v>
@@ -7730,13 +7718,13 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D341" t="s">
-        <v>426</v>
+        <v>351</v>
       </c>
       <c r="E341" t="s">
         <v>8</v>
@@ -7753,7 +7741,7 @@
         <v>6</v>
       </c>
       <c r="D342" t="s">
-        <v>428</v>
+        <v>206</v>
       </c>
       <c r="E342" t="s">
         <v>8</v>
@@ -7764,13 +7752,13 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D343" t="s">
-        <v>231</v>
+        <v>420</v>
       </c>
       <c r="E343" t="s">
         <v>8</v>
@@ -7781,13 +7769,13 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D344" t="s">
-        <v>231</v>
+        <v>274</v>
       </c>
       <c r="E344" t="s">
         <v>8</v>
@@ -7798,13 +7786,13 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D345" t="s">
-        <v>432</v>
+        <v>271</v>
       </c>
       <c r="E345" t="s">
         <v>8</v>
@@ -7815,13 +7803,13 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D346" t="s">
-        <v>216</v>
+        <v>311</v>
       </c>
       <c r="E346" t="s">
         <v>8</v>
@@ -7832,13 +7820,13 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D347" t="s">
-        <v>435</v>
+        <v>206</v>
       </c>
       <c r="E347" t="s">
         <v>8</v>
@@ -7849,13 +7837,13 @@
         <v>347</v>
       </c>
       <c r="B348" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D348" t="s">
-        <v>261</v>
+        <v>334</v>
       </c>
       <c r="E348" t="s">
         <v>8</v>
@@ -7866,13 +7854,13 @@
         <v>348</v>
       </c>
       <c r="B349" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D349" t="s">
-        <v>282</v>
+        <v>233</v>
       </c>
       <c r="E349" t="s">
         <v>8</v>
@@ -7883,13 +7871,13 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D350" t="s">
-        <v>216</v>
+        <v>407</v>
       </c>
       <c r="E350" t="s">
         <v>8</v>
@@ -7900,13 +7888,13 @@
         <v>350</v>
       </c>
       <c r="B351" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D351" t="s">
-        <v>259</v>
+        <v>228</v>
       </c>
       <c r="E351" t="s">
         <v>8</v>
@@ -7917,13 +7905,13 @@
         <v>351</v>
       </c>
       <c r="B352" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D352" t="s">
-        <v>269</v>
+        <v>239</v>
       </c>
       <c r="E352" t="s">
         <v>8</v>
@@ -7934,13 +7922,13 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D353" t="s">
-        <v>202</v>
+        <v>397</v>
       </c>
       <c r="E353" t="s">
         <v>8</v>
@@ -7951,13 +7939,13 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D354" t="s">
-        <v>246</v>
+        <v>404</v>
       </c>
       <c r="E354" t="s">
         <v>8</v>
@@ -7968,13 +7956,13 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D355" t="s">
-        <v>444</v>
+        <v>322</v>
       </c>
       <c r="E355" t="s">
         <v>8</v>
@@ -7985,13 +7973,13 @@
         <v>355</v>
       </c>
       <c r="B356" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D356" t="s">
-        <v>446</v>
+        <v>284</v>
       </c>
       <c r="E356" t="s">
         <v>8</v>
@@ -8002,13 +7990,13 @@
         <v>356</v>
       </c>
       <c r="B357" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D357" t="s">
-        <v>253</v>
+        <v>228</v>
       </c>
       <c r="E357" t="s">
         <v>8</v>
@@ -8019,13 +8007,13 @@
         <v>357</v>
       </c>
       <c r="B358" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D358" t="s">
-        <v>318</v>
+        <v>444</v>
       </c>
       <c r="E358" t="s">
         <v>8</v>
@@ -8036,13 +8024,13 @@
         <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D359" t="s">
-        <v>450</v>
+        <v>248</v>
       </c>
       <c r="E359" t="s">
         <v>8</v>
@@ -8053,13 +8041,13 @@
         <v>359</v>
       </c>
       <c r="B360" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D360" t="s">
-        <v>452</v>
+        <v>384</v>
       </c>
       <c r="E360" t="s">
         <v>8</v>
@@ -8070,13 +8058,13 @@
         <v>360</v>
       </c>
       <c r="B361" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D361" t="s">
-        <v>369</v>
+        <v>233</v>
       </c>
       <c r="E361" t="s">
         <v>8</v>
@@ -8087,13 +8075,13 @@
         <v>361</v>
       </c>
       <c r="B362" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D362" t="s">
-        <v>397</v>
+        <v>449</v>
       </c>
       <c r="E362" t="s">
         <v>8</v>
@@ -8104,13 +8092,13 @@
         <v>362</v>
       </c>
       <c r="B363" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D363" t="s">
-        <v>216</v>
+        <v>364</v>
       </c>
       <c r="E363" t="s">
         <v>8</v>
@@ -8121,13 +8109,13 @@
         <v>363</v>
       </c>
       <c r="B364" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D364" t="s">
-        <v>214</v>
+        <v>452</v>
       </c>
       <c r="E364" t="s">
         <v>8</v>
@@ -8138,13 +8126,13 @@
         <v>364</v>
       </c>
       <c r="B365" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D365" t="s">
-        <v>458</v>
+        <v>274</v>
       </c>
       <c r="E365" t="s">
         <v>8</v>
@@ -8155,13 +8143,13 @@
         <v>365</v>
       </c>
       <c r="B366" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D366" t="s">
-        <v>446</v>
+        <v>220</v>
       </c>
       <c r="E366" t="s">
         <v>8</v>
@@ -8172,13 +8160,13 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D367" t="s">
-        <v>461</v>
+        <v>299</v>
       </c>
       <c r="E367" t="s">
         <v>8</v>
@@ -8189,13 +8177,13 @@
         <v>367</v>
       </c>
       <c r="B368" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D368" t="s">
-        <v>222</v>
+        <v>414</v>
       </c>
       <c r="E368" t="s">
         <v>8</v>
@@ -8206,13 +8194,13 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D369" t="s">
-        <v>372</v>
+        <v>306</v>
       </c>
       <c r="E369" t="s">
         <v>8</v>
@@ -8223,13 +8211,13 @@
         <v>369</v>
       </c>
       <c r="B370" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D370" t="s">
-        <v>259</v>
+        <v>226</v>
       </c>
       <c r="E370" t="s">
         <v>8</v>
@@ -8240,13 +8228,13 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D371" t="s">
-        <v>206</v>
+        <v>274</v>
       </c>
       <c r="E371" t="s">
         <v>8</v>
@@ -8257,13 +8245,13 @@
         <v>371</v>
       </c>
       <c r="B372" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D372" t="s">
-        <v>316</v>
+        <v>218</v>
       </c>
       <c r="E372" t="s">
         <v>8</v>
@@ -8274,13 +8262,13 @@
         <v>372</v>
       </c>
       <c r="B373" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D373" t="s">
-        <v>282</v>
+        <v>301</v>
       </c>
       <c r="E373" t="s">
         <v>8</v>
@@ -8291,13 +8279,13 @@
         <v>373</v>
       </c>
       <c r="B374" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D374" t="s">
-        <v>336</v>
+        <v>299</v>
       </c>
       <c r="E374" t="s">
         <v>8</v>
@@ -8308,13 +8296,13 @@
         <v>374</v>
       </c>
       <c r="B375" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D375" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="E375" t="s">
         <v>8</v>
@@ -8325,13 +8313,13 @@
         <v>375</v>
       </c>
       <c r="B376" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D376" t="s">
-        <v>239</v>
+        <v>264</v>
       </c>
       <c r="E376" t="s">
         <v>8</v>
@@ -8342,13 +8330,13 @@
         <v>376</v>
       </c>
       <c r="B377" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D377" t="s">
-        <v>472</v>
+        <v>226</v>
       </c>
       <c r="E377" t="s">
         <v>8</v>
@@ -8359,13 +8347,13 @@
         <v>377</v>
       </c>
       <c r="B378" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D378" t="s">
-        <v>474</v>
+        <v>194</v>
       </c>
       <c r="E378" t="s">
         <v>8</v>
@@ -8376,13 +8364,13 @@
         <v>378</v>
       </c>
       <c r="B379" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D379" t="s">
-        <v>333</v>
+        <v>468</v>
       </c>
       <c r="E379" t="s">
         <v>8</v>
@@ -8393,13 +8381,13 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D380" t="s">
-        <v>200</v>
+        <v>414</v>
       </c>
       <c r="E380" t="s">
         <v>8</v>
@@ -8410,13 +8398,13 @@
         <v>380</v>
       </c>
       <c r="B381" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D381" t="s">
-        <v>318</v>
+        <v>230</v>
       </c>
       <c r="E381" t="s">
         <v>8</v>
@@ -8427,13 +8415,13 @@
         <v>381</v>
       </c>
       <c r="B382" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D382" t="s">
-        <v>190</v>
+        <v>391</v>
       </c>
       <c r="E382" t="s">
         <v>8</v>
@@ -8444,13 +8432,13 @@
         <v>382</v>
       </c>
       <c r="B383" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D383" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E383" t="s">
         <v>8</v>
@@ -8461,13 +8449,13 @@
         <v>383</v>
       </c>
       <c r="B384" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D384" t="s">
-        <v>261</v>
+        <v>474</v>
       </c>
       <c r="E384" t="s">
         <v>8</v>
@@ -8478,13 +8466,13 @@
         <v>384</v>
       </c>
       <c r="B385" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D385" t="s">
-        <v>340</v>
+        <v>196</v>
       </c>
       <c r="E385" t="s">
         <v>8</v>
@@ -8495,13 +8483,13 @@
         <v>385</v>
       </c>
       <c r="B386" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D386" t="s">
-        <v>372</v>
+        <v>218</v>
       </c>
       <c r="E386" t="s">
         <v>8</v>
@@ -8512,13 +8500,13 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D387" t="s">
-        <v>375</v>
+        <v>334</v>
       </c>
       <c r="E387" t="s">
         <v>8</v>
@@ -8529,13 +8517,13 @@
         <v>387</v>
       </c>
       <c r="B388" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D388" t="s">
-        <v>364</v>
+        <v>479</v>
       </c>
       <c r="E388" t="s">
         <v>8</v>
@@ -8546,13 +8534,13 @@
         <v>388</v>
       </c>
       <c r="B389" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D389" t="s">
-        <v>216</v>
+        <v>364</v>
       </c>
       <c r="E389" t="s">
         <v>8</v>
@@ -8563,13 +8551,13 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D390" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E390" t="s">
         <v>8</v>
@@ -8580,13 +8568,13 @@
         <v>390</v>
       </c>
       <c r="B391" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D391" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="E391" t="s">
         <v>8</v>
@@ -8597,13 +8585,13 @@
         <v>391</v>
       </c>
       <c r="B392" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D392" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="E392" t="s">
         <v>8</v>
@@ -8614,13 +8602,13 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D393" t="s">
-        <v>200</v>
+        <v>239</v>
       </c>
       <c r="E393" t="s">
         <v>8</v>
@@ -8631,13 +8619,13 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D394" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="E394" t="s">
         <v>8</v>
@@ -8648,13 +8636,13 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D395" t="s">
-        <v>355</v>
+        <v>208</v>
       </c>
       <c r="E395" t="s">
         <v>8</v>
@@ -8665,13 +8653,13 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D396" t="s">
-        <v>206</v>
+        <v>296</v>
       </c>
       <c r="E396" t="s">
         <v>8</v>
@@ -8682,13 +8670,13 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D397" t="s">
-        <v>369</v>
+        <v>311</v>
       </c>
       <c r="E397" t="s">
         <v>8</v>
@@ -8699,13 +8687,13 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D398" t="s">
-        <v>284</v>
+        <v>490</v>
       </c>
       <c r="E398" t="s">
         <v>8</v>
@@ -8716,13 +8704,13 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D399" t="s">
-        <v>224</v>
+        <v>346</v>
       </c>
       <c r="E399" t="s">
         <v>8</v>
@@ -8733,13 +8721,13 @@
         <v>399</v>
       </c>
       <c r="B400" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D400" t="s">
-        <v>435</v>
+        <v>334</v>
       </c>
       <c r="E400" t="s">
         <v>8</v>
@@ -8750,13 +8738,13 @@
         <v>400</v>
       </c>
       <c r="B401" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D401" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
       <c r="E401" t="s">
         <v>8</v>
@@ -8775,47 +8763,47 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="B1" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B2" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="B3" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="B4" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="B5" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="B6">
         <v>400</v>
@@ -8823,7 +8811,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="B7">
         <v>400</v>
@@ -8831,7 +8819,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -8839,7 +8827,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -8847,10 +8835,10 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="B10" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
     </row>
   </sheetData>

--- a/reports/backend/Excel/Automation_Test_Report.xlsx
+++ b/reports/backend/Excel/Automation_Test_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="514">
   <si>
     <t>#</t>
   </si>
@@ -65,33 +65,33 @@
     <t>Smart Admission Backend — Authentication Tests BT-009 | Firebase config fields are non-empty strings</t>
   </si>
   <si>
+    <t>Smart Admission Backend — Authentication Tests BT-010 | Firebase apiKey has expected format (AIza...)</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — Authentication Tests BT-011 | Valid email passes validation</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — Authentication Tests BT-012 | Email without @ fails validation</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — Authentication Tests BT-013 | Email without domain fails validation</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — Authentication Tests BT-014 | Empty string fails email validation</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — Authentication Tests BT-015 | Test credentials email is valid format</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — Authentication Tests BT-016 | Institutional email domain (.edu/.ac/.sse) is valid</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — Authentication Tests BT-017 | Email with spaces fails validation</t>
+  </si>
+  <si>
     <t>0.001</t>
   </si>
   <si>
-    <t>Smart Admission Backend — Authentication Tests BT-010 | Firebase apiKey has expected format (AIza...)</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — Authentication Tests BT-011 | Valid email passes validation</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — Authentication Tests BT-012 | Email without @ fails validation</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — Authentication Tests BT-013 | Email without domain fails validation</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — Authentication Tests BT-014 | Empty string fails email validation</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — Authentication Tests BT-015 | Test credentials email is valid format</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — Authentication Tests BT-016 | Institutional email domain (.edu/.ac/.sse) is valid</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — Authentication Tests BT-017 | Email with spaces fails validation</t>
-  </si>
-  <si>
     <t>Smart Admission Backend — Authentication Tests BT-018 | Email with multiple @ fails validation</t>
   </si>
   <si>
@@ -584,888 +584,900 @@
     <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #180</t>
   </si>
   <si>
+    <t>0.116</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #181</t>
+  </si>
+  <si>
+    <t>0.085</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #182</t>
+  </si>
+  <si>
+    <t>0.059</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #183</t>
+  </si>
+  <si>
+    <t>0.110</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #184</t>
+  </si>
+  <si>
+    <t>0.104</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #185</t>
+  </si>
+  <si>
+    <t>0.060</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #186</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #187</t>
+  </si>
+  <si>
+    <t>0.096</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #188</t>
+  </si>
+  <si>
+    <t>0.021</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #189</t>
+  </si>
+  <si>
+    <t>0.103</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #190</t>
+  </si>
+  <si>
+    <t>0.105</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #191</t>
+  </si>
+  <si>
+    <t>0.054</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #192</t>
+  </si>
+  <si>
+    <t>0.057</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #193</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #194</t>
+  </si>
+  <si>
+    <t>0.047</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #195</t>
+  </si>
+  <si>
+    <t>0.093</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #196</t>
+  </si>
+  <si>
+    <t>0.034</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #197</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #198</t>
+  </si>
+  <si>
+    <t>0.100</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #199</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #200</t>
+  </si>
+  <si>
+    <t>0.052</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #201</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #202</t>
+  </si>
+  <si>
+    <t>0.111</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #203</t>
+  </si>
+  <si>
+    <t>0.108</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #204</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #205</t>
+  </si>
+  <si>
+    <t>0.113</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #206</t>
+  </si>
+  <si>
+    <t>0.038</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #207</t>
+  </si>
+  <si>
+    <t>0.041</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #208</t>
+  </si>
+  <si>
+    <t>0.076</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #209</t>
+  </si>
+  <si>
+    <t>0.118</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #210</t>
+  </si>
+  <si>
+    <t>0.112</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #211</t>
+  </si>
+  <si>
+    <t>0.091</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #212</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #213</t>
+  </si>
+  <si>
+    <t>0.045</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #214</t>
+  </si>
+  <si>
+    <t>0.061</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #215</t>
+  </si>
+  <si>
+    <t>0.092</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #216</t>
+  </si>
+  <si>
+    <t>0.069</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #217</t>
+  </si>
+  <si>
+    <t>0.078</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #218</t>
+  </si>
+  <si>
+    <t>0.020</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #219</t>
+  </si>
+  <si>
+    <t>0.042</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #220</t>
+  </si>
+  <si>
+    <t>0.030</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #221</t>
+  </si>
+  <si>
+    <t>0.106</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #222</t>
+  </si>
+  <si>
+    <t>0.075</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #223</t>
+  </si>
+  <si>
+    <t>0.028</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #224</t>
+  </si>
+  <si>
+    <t>0.050</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #225</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #226</t>
+  </si>
+  <si>
+    <t>0.115</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #227</t>
+  </si>
+  <si>
+    <t>0.067</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #228</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #229</t>
+  </si>
+  <si>
+    <t>0.033</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #230</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #231</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #232</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #233</t>
+  </si>
+  <si>
     <t>0.089</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #181</t>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #234</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #235</t>
+  </si>
+  <si>
+    <t>0.071</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #236</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #237</t>
+  </si>
+  <si>
+    <t>0.077</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #238</t>
+  </si>
+  <si>
+    <t>0.101</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #239</t>
+  </si>
+  <si>
+    <t>0.099</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #240</t>
+  </si>
+  <si>
+    <t>0.079</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #241</t>
+  </si>
+  <si>
+    <t>0.040</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #242</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #243</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #244</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #245</t>
+  </si>
+  <si>
+    <t>0.114</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #246</t>
+  </si>
+  <si>
+    <t>0.024</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #247</t>
+  </si>
+  <si>
+    <t>0.084</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #248</t>
+  </si>
+  <si>
+    <t>0.063</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #249</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #250</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #251</t>
+  </si>
+  <si>
+    <t>0.119</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #252</t>
+  </si>
+  <si>
+    <t>0.025</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #253</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #254</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #255</t>
+  </si>
+  <si>
+    <t>0.068</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #256</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #257</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #258</t>
+  </si>
+  <si>
+    <t>0.053</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #259</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #260</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #261</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #262</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #263</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #264</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #265</t>
+  </si>
+  <si>
+    <t>0.088</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #266</t>
+  </si>
+  <si>
+    <t>0.056</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #267</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #268</t>
+  </si>
+  <si>
+    <t>0.029</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #269</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #270</t>
+  </si>
+  <si>
+    <t>0.031</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #271</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #272</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #273</t>
+  </si>
+  <si>
+    <t>0.073</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #274</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #275</t>
+  </si>
+  <si>
+    <t>0.095</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #276</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #277</t>
+  </si>
+  <si>
+    <t>0.064</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #278</t>
+  </si>
+  <si>
+    <t>0.035</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #279</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #280</t>
+  </si>
+  <si>
+    <t>0.032</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #281</t>
+  </si>
+  <si>
+    <t>0.087</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #282</t>
+  </si>
+  <si>
+    <t>0.098</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #283</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #284</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #285</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #286</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #287</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #288</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #289</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #290</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #291</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #292</t>
+  </si>
+  <si>
+    <t>0.051</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #293</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #294</t>
+  </si>
+  <si>
+    <t>0.043</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #295</t>
+  </si>
+  <si>
+    <t>0.046</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #296</t>
+  </si>
+  <si>
+    <t>0.058</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #297</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #298</t>
+  </si>
+  <si>
+    <t>0.036</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #299</t>
+  </si>
+  <si>
+    <t>0.097</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #300</t>
+  </si>
+  <si>
+    <t>0.062</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #301</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #302</t>
+  </si>
+  <si>
+    <t>0.070</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #303</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #304</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #305</t>
+  </si>
+  <si>
+    <t>0.022</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #306</t>
+  </si>
+  <si>
+    <t>0.086</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #307</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #308</t>
+  </si>
+  <si>
+    <t>0.072</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #309</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #310</t>
+  </si>
+  <si>
+    <t>0.080</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #311</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #312</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #313</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #314</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #315</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #316</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #317</t>
+  </si>
+  <si>
+    <t>0.066</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #318</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #319</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #320</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #321</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #322</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #323</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #324</t>
+  </si>
+  <si>
+    <t>0.083</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #325</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #326</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #327</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #328</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #329</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #330</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #331</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #332</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #333</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #334</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #335</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #336</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #337</t>
+  </si>
+  <si>
+    <t>0.102</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #338</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #339</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #340</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #341</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #342</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #343</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #344</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #345</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #346</t>
+  </si>
+  <si>
+    <t>0.055</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #347</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #348</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #349</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #350</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #351</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #352</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #353</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #354</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #355</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #356</t>
+  </si>
+  <si>
+    <t>0.094</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #357</t>
   </si>
   <si>
     <t>0.109</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #182</t>
-  </si>
-  <si>
-    <t>0.108</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #183</t>
-  </si>
-  <si>
-    <t>0.021</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #184</t>
-  </si>
-  <si>
-    <t>0.062</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #185</t>
-  </si>
-  <si>
-    <t>0.020</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #186</t>
-  </si>
-  <si>
-    <t>0.088</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #187</t>
-  </si>
-  <si>
-    <t>0.034</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #188</t>
-  </si>
-  <si>
-    <t>0.056</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #189</t>
-  </si>
-  <si>
-    <t>0.063</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #190</t>
-  </si>
-  <si>
-    <t>0.078</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #191</t>
-  </si>
-  <si>
-    <t>0.026</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #192</t>
-  </si>
-  <si>
-    <t>0.064</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #193</t>
-  </si>
-  <si>
-    <t>0.093</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #194</t>
-  </si>
-  <si>
-    <t>0.048</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #195</t>
-  </si>
-  <si>
-    <t>0.051</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #196</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #197</t>
-  </si>
-  <si>
-    <t>0.097</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #198</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #199</t>
-  </si>
-  <si>
-    <t>0.043</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #200</t>
-  </si>
-  <si>
-    <t>0.085</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #201</t>
-  </si>
-  <si>
-    <t>0.114</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #202</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #203</t>
-  </si>
-  <si>
-    <t>0.029</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #204</t>
-  </si>
-  <si>
-    <t>0.061</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #205</t>
-  </si>
-  <si>
-    <t>0.067</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #206</t>
-  </si>
-  <si>
-    <t>0.095</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #207</t>
-  </si>
-  <si>
-    <t>0.038</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #208</t>
-  </si>
-  <si>
-    <t>0.058</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #209</t>
-  </si>
-  <si>
-    <t>0.074</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #210</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #211</t>
-  </si>
-  <si>
-    <t>0.068</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #212</t>
-  </si>
-  <si>
-    <t>0.054</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #213</t>
-  </si>
-  <si>
-    <t>0.050</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #214</t>
-  </si>
-  <si>
-    <t>0.045</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #215</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #216</t>
-  </si>
-  <si>
-    <t>0.024</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #217</t>
-  </si>
-  <si>
-    <t>0.073</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #218</t>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #358</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #359</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #360</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #361</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #362</t>
+  </si>
+  <si>
+    <t>0.044</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #363</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #364</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #365</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #366</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #367</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #368</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #369</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #370</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #371</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #372</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #373</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #374</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #375</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #376</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #377</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #378</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #379</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #380</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #381</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #382</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #383</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #384</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #385</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #386</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #387</t>
+  </si>
+  <si>
+    <t>0.081</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #388</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #389</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #390</t>
   </si>
   <si>
     <t>0.023</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #219</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #220</t>
-  </si>
-  <si>
-    <t>0.087</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #221</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #222</t>
-  </si>
-  <si>
-    <t>0.022</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #223</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #224</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #225</t>
-  </si>
-  <si>
-    <t>0.066</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #226</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #227</t>
-  </si>
-  <si>
-    <t>0.049</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #228</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #229</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #230</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #231</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #232</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #233</t>
-  </si>
-  <si>
-    <t>0.090</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #234</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #235</t>
-  </si>
-  <si>
-    <t>0.113</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #236</t>
-  </si>
-  <si>
-    <t>0.086</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #237</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #238</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #239</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #240</t>
-  </si>
-  <si>
-    <t>0.111</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #241</t>
-  </si>
-  <si>
-    <t>0.098</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #242</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #243</t>
-  </si>
-  <si>
-    <t>0.118</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #244</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #245</t>
-  </si>
-  <si>
-    <t>0.059</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #246</t>
-  </si>
-  <si>
-    <t>0.035</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #247</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #248</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #249</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #250</t>
-  </si>
-  <si>
-    <t>0.042</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #251</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #252</t>
-  </si>
-  <si>
-    <t>0.080</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #253</t>
-  </si>
-  <si>
-    <t>0.101</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #254</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #255</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #256</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #257</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #258</t>
-  </si>
-  <si>
-    <t>0.046</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #259</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #260</t>
-  </si>
-  <si>
-    <t>0.102</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #261</t>
-  </si>
-  <si>
-    <t>0.052</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #262</t>
-  </si>
-  <si>
-    <t>0.081</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #263</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #264</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #265</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #266</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #267</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #268</t>
-  </si>
-  <si>
-    <t>0.040</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #269</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #270</t>
-  </si>
-  <si>
-    <t>0.071</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #271</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #272</t>
-  </si>
-  <si>
-    <t>0.070</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #273</t>
-  </si>
-  <si>
-    <t>0.115</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #274</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #275</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #276</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #277</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #278</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #279</t>
-  </si>
-  <si>
-    <t>0.037</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #280</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #281</t>
-  </si>
-  <si>
-    <t>0.069</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #282</t>
-  </si>
-  <si>
-    <t>0.075</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #283</t>
-  </si>
-  <si>
-    <t>0.119</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #284</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #285</t>
-  </si>
-  <si>
-    <t>0.053</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #286</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #287</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #288</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #289</t>
-  </si>
-  <si>
-    <t>0.096</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #290</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #291</t>
-  </si>
-  <si>
-    <t>0.077</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #292</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #293</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #294</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #295</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #296</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #297</t>
-  </si>
-  <si>
-    <t>0.110</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #298</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #299</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #300</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #301</t>
-  </si>
-  <si>
-    <t>0.031</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #302</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #303</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #304</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #305</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #306</t>
-  </si>
-  <si>
-    <t>0.036</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #307</t>
-  </si>
-  <si>
-    <t>0.047</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #308</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #309</t>
-  </si>
-  <si>
-    <t>0.076</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #310</t>
-  </si>
-  <si>
-    <t>0.055</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #311</t>
-  </si>
-  <si>
-    <t>0.104</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #312</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #313</t>
-  </si>
-  <si>
-    <t>0.060</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #314</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #315</t>
-  </si>
-  <si>
-    <t>0.094</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #316</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #317</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #318</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #319</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #320</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #321</t>
-  </si>
-  <si>
-    <t>0.084</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #322</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #323</t>
-  </si>
-  <si>
-    <t>0.112</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #324</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #325</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #326</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #327</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #328</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #329</t>
-  </si>
-  <si>
-    <t>0.044</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #330</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #331</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #332</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #333</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #334</t>
-  </si>
-  <si>
-    <t>0.107</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #335</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #336</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #337</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #338</t>
-  </si>
-  <si>
-    <t>0.082</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #339</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #340</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #341</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #342</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #343</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #344</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #345</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #346</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #347</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #348</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #349</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #350</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #351</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #352</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #353</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #354</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #355</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #356</t>
-  </si>
-  <si>
-    <t>0.116</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #357</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #358</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #359</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #360</t>
-  </si>
-  <si>
-    <t>0.057</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #361</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #362</t>
-  </si>
-  <si>
-    <t>0.079</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #363</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #364</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #365</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #366</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #367</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #368</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #369</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #370</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #371</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #372</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #373</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #374</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #375</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #376</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #377</t>
-  </si>
-  <si>
-    <t>0.099</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #378</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #379</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #380</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #381</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #382</t>
-  </si>
-  <si>
-    <t>0.041</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #383</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #384</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #385</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #386</t>
-  </si>
-  <si>
-    <t>0.083</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #387</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #388</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #389</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #390</t>
-  </si>
-  <si>
     <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #391</t>
   </si>
   <si>
@@ -1475,6 +1487,9 @@
     <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #393</t>
   </si>
   <si>
+    <t>0.039</t>
+  </si>
+  <si>
     <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #394</t>
   </si>
   <si>
@@ -1484,9 +1499,6 @@
     <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #396</t>
   </si>
   <si>
-    <t>0.105</t>
-  </si>
-  <si>
     <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #397</t>
   </si>
   <si>
@@ -1505,13 +1517,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>14</t>
+    <t>15</t>
   </si>
   <si>
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 13:38:07 UTC</t>
+    <t>2026-06-23 13:46:52 UTC</t>
   </si>
   <si>
     <t>Branch</t>
@@ -1523,7 +1535,7 @@
     <t>Commit</t>
   </si>
   <si>
-    <t>3eb8262</t>
+    <t>0bdfd4b</t>
   </si>
   <si>
     <t>Total</t>
@@ -2097,7 +2109,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -2108,7 +2120,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>6</v>
@@ -2125,7 +2137,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>6</v>
@@ -2142,7 +2154,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>6</v>
@@ -2159,7 +2171,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>6</v>
@@ -2176,7 +2188,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>6</v>
@@ -2193,7 +2205,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>6</v>
@@ -2210,7 +2222,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>6</v>
@@ -2227,13 +2239,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" t="s">
         <v>25</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D18" t="s">
-        <v>7</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -2403,7 +2415,7 @@
         <v>6</v>
       </c>
       <c r="D28" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -2556,7 +2568,7 @@
         <v>6</v>
       </c>
       <c r="D37" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -2743,7 +2755,7 @@
         <v>6</v>
       </c>
       <c r="D48" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -2879,7 +2891,7 @@
         <v>6</v>
       </c>
       <c r="D56" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -2947,7 +2959,7 @@
         <v>6</v>
       </c>
       <c r="D60" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
@@ -3134,7 +3146,7 @@
         <v>6</v>
       </c>
       <c r="D71" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
@@ -3321,7 +3333,7 @@
         <v>6</v>
       </c>
       <c r="D82" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
@@ -3491,7 +3503,7 @@
         <v>6</v>
       </c>
       <c r="D92" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E92" t="s">
         <v>8</v>
@@ -3644,7 +3656,7 @@
         <v>6</v>
       </c>
       <c r="D101" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E101" t="s">
         <v>8</v>
@@ -3661,7 +3673,7 @@
         <v>6</v>
       </c>
       <c r="D102" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E102" t="s">
         <v>8</v>
@@ -3814,7 +3826,7 @@
         <v>6</v>
       </c>
       <c r="D111" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E111" t="s">
         <v>8</v>
@@ -4018,7 +4030,7 @@
         <v>6</v>
       </c>
       <c r="D123" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E123" t="s">
         <v>8</v>
@@ -4171,7 +4183,7 @@
         <v>6</v>
       </c>
       <c r="D132" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E132" t="s">
         <v>8</v>
@@ -4239,7 +4251,7 @@
         <v>6</v>
       </c>
       <c r="D136" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E136" t="s">
         <v>8</v>
@@ -4834,7 +4846,7 @@
         <v>6</v>
       </c>
       <c r="D171" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E171" t="s">
         <v>8</v>
@@ -5123,7 +5135,7 @@
         <v>6</v>
       </c>
       <c r="D188" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E188" t="s">
         <v>8</v>
@@ -5134,13 +5146,13 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
+        <v>202</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D189" t="s">
         <v>203</v>
-      </c>
-      <c r="C189" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D189" t="s">
-        <v>204</v>
       </c>
       <c r="E189" t="s">
         <v>8</v>
@@ -5151,13 +5163,13 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
+        <v>204</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D190" t="s">
         <v>205</v>
-      </c>
-      <c r="C190" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D190" t="s">
-        <v>206</v>
       </c>
       <c r="E190" t="s">
         <v>8</v>
@@ -5168,13 +5180,13 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
+        <v>206</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D191" t="s">
         <v>207</v>
-      </c>
-      <c r="C191" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D191" t="s">
-        <v>208</v>
       </c>
       <c r="E191" t="s">
         <v>8</v>
@@ -5185,13 +5197,13 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
+        <v>208</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D192" t="s">
         <v>209</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D192" t="s">
-        <v>210</v>
       </c>
       <c r="E192" t="s">
         <v>8</v>
@@ -5202,13 +5214,13 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
+        <v>210</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D193" t="s">
         <v>211</v>
-      </c>
-      <c r="C193" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D193" t="s">
-        <v>212</v>
       </c>
       <c r="E193" t="s">
         <v>8</v>
@@ -5219,13 +5231,13 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
+        <v>212</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D194" t="s">
         <v>213</v>
-      </c>
-      <c r="C194" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D194" t="s">
-        <v>214</v>
       </c>
       <c r="E194" t="s">
         <v>8</v>
@@ -5236,13 +5248,13 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D195" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="E195" t="s">
         <v>8</v>
@@ -5253,13 +5265,13 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D196" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E196" t="s">
         <v>8</v>
@@ -5270,13 +5282,13 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D197" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E197" t="s">
         <v>8</v>
@@ -5287,13 +5299,13 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D198" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="E198" t="s">
         <v>8</v>
@@ -5304,13 +5316,13 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D199" t="s">
-        <v>223</v>
+        <v>192</v>
       </c>
       <c r="E199" t="s">
         <v>8</v>
@@ -5321,13 +5333,13 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D200" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
       <c r="E200" t="s">
         <v>8</v>
@@ -5338,13 +5350,13 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D201" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E201" t="s">
         <v>8</v>
@@ -5355,13 +5367,13 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D202" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E202" t="s">
         <v>8</v>
@@ -5372,13 +5384,13 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D203" t="s">
-        <v>230</v>
+        <v>207</v>
       </c>
       <c r="E203" t="s">
         <v>8</v>
@@ -5389,13 +5401,13 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D204" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E204" t="s">
         <v>8</v>
@@ -5406,13 +5418,13 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D205" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E205" t="s">
         <v>8</v>
@@ -5423,13 +5435,13 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D206" t="s">
-        <v>235</v>
+        <v>192</v>
       </c>
       <c r="E206" t="s">
         <v>8</v>
@@ -5440,13 +5452,13 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D207" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E207" t="s">
         <v>8</v>
@@ -5457,13 +5469,13 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D208" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E208" t="s">
         <v>8</v>
@@ -5474,13 +5486,13 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D209" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="E209" t="s">
         <v>8</v>
@@ -5491,13 +5503,13 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D210" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E210" t="s">
         <v>8</v>
@@ -5508,13 +5520,13 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D211" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E211" t="s">
         <v>8</v>
@@ -5525,13 +5537,13 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D212" t="s">
-        <v>208</v>
+        <v>244</v>
       </c>
       <c r="E212" t="s">
         <v>8</v>
@@ -5542,13 +5554,13 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D213" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E213" t="s">
         <v>8</v>
@@ -5559,13 +5571,13 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D214" t="s">
-        <v>250</v>
+        <v>205</v>
       </c>
       <c r="E214" t="s">
         <v>8</v>
@@ -5576,13 +5588,13 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D215" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E215" t="s">
         <v>8</v>
@@ -5593,13 +5605,13 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D216" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E216" t="s">
         <v>8</v>
@@ -5610,13 +5622,13 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D217" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="E217" t="s">
         <v>8</v>
@@ -5627,13 +5639,13 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D218" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E218" t="s">
         <v>8</v>
@@ -5644,13 +5656,13 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D219" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E219" t="s">
         <v>8</v>
@@ -5661,13 +5673,13 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D220" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E220" t="s">
         <v>8</v>
@@ -5678,13 +5690,13 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D221" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="E221" t="s">
         <v>8</v>
@@ -5695,13 +5707,13 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
+        <v>262</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D222" t="s">
         <v>263</v>
-      </c>
-      <c r="C222" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D222" t="s">
-        <v>264</v>
       </c>
       <c r="E222" t="s">
         <v>8</v>
@@ -5712,13 +5724,13 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
+        <v>264</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D223" t="s">
         <v>265</v>
-      </c>
-      <c r="C223" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D223" t="s">
-        <v>259</v>
       </c>
       <c r="E223" t="s">
         <v>8</v>
@@ -5752,7 +5764,7 @@
         <v>6</v>
       </c>
       <c r="D225" t="s">
-        <v>243</v>
+        <v>269</v>
       </c>
       <c r="E225" t="s">
         <v>8</v>
@@ -5763,13 +5775,13 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D226" t="s">
-        <v>220</v>
+        <v>271</v>
       </c>
       <c r="E226" t="s">
         <v>8</v>
@@ -5780,13 +5792,13 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D227" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="E227" t="s">
         <v>8</v>
@@ -5797,13 +5809,13 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D228" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="E228" t="s">
         <v>8</v>
@@ -5814,13 +5826,13 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D229" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E229" t="s">
         <v>8</v>
@@ -5831,13 +5843,13 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D230" t="s">
-        <v>192</v>
+        <v>269</v>
       </c>
       <c r="E230" t="s">
         <v>8</v>
@@ -5848,13 +5860,13 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D231" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="E231" t="s">
         <v>8</v>
@@ -5865,13 +5877,13 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D232" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="E232" t="s">
         <v>8</v>
@@ -5882,13 +5894,13 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D233" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="E233" t="s">
         <v>8</v>
@@ -5899,13 +5911,13 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D234" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="E234" t="s">
         <v>8</v>
@@ -5916,13 +5928,13 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D235" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E235" t="s">
         <v>8</v>
@@ -5933,13 +5945,13 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D236" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="E236" t="s">
         <v>8</v>
@@ -5950,13 +5962,13 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D237" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E237" t="s">
         <v>8</v>
@@ -5967,13 +5979,13 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D238" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="E238" t="s">
         <v>8</v>
@@ -5984,13 +5996,13 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D239" t="s">
-        <v>254</v>
+        <v>290</v>
       </c>
       <c r="E239" t="s">
         <v>8</v>
@@ -6001,13 +6013,13 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D240" t="s">
-        <v>198</v>
+        <v>292</v>
       </c>
       <c r="E240" t="s">
         <v>8</v>
@@ -6018,13 +6030,13 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D241" t="s">
-        <v>218</v>
+        <v>294</v>
       </c>
       <c r="E241" t="s">
         <v>8</v>
@@ -6035,13 +6047,13 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D242" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="E242" t="s">
         <v>8</v>
@@ -6052,13 +6064,13 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D243" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="E243" t="s">
         <v>8</v>
@@ -6069,13 +6081,13 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D244" t="s">
-        <v>254</v>
+        <v>192</v>
       </c>
       <c r="E244" t="s">
         <v>8</v>
@@ -6086,13 +6098,13 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D245" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="E245" t="s">
         <v>8</v>
@@ -6103,13 +6115,13 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D246" t="s">
-        <v>291</v>
+        <v>246</v>
       </c>
       <c r="E246" t="s">
         <v>8</v>
@@ -6120,13 +6132,13 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D247" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="E247" t="s">
         <v>8</v>
@@ -6137,13 +6149,13 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D248" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E248" t="s">
         <v>8</v>
@@ -6154,13 +6166,13 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D249" t="s">
-        <v>228</v>
+        <v>307</v>
       </c>
       <c r="E249" t="s">
         <v>8</v>
@@ -6171,13 +6183,13 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D250" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="E250" t="s">
         <v>8</v>
@@ -6188,13 +6200,13 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D251" t="s">
-        <v>190</v>
+        <v>290</v>
       </c>
       <c r="E251" t="s">
         <v>8</v>
@@ -6205,13 +6217,13 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D252" t="s">
-        <v>306</v>
+        <v>255</v>
       </c>
       <c r="E252" t="s">
         <v>8</v>
@@ -6222,13 +6234,13 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D253" t="s">
-        <v>241</v>
+        <v>313</v>
       </c>
       <c r="E253" t="s">
         <v>8</v>
@@ -6239,13 +6251,13 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D254" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="E254" t="s">
         <v>8</v>
@@ -6256,13 +6268,13 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D255" t="s">
-        <v>311</v>
+        <v>211</v>
       </c>
       <c r="E255" t="s">
         <v>8</v>
@@ -6273,13 +6285,13 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D256" t="s">
-        <v>218</v>
+        <v>271</v>
       </c>
       <c r="E256" t="s">
         <v>8</v>
@@ -6290,13 +6302,13 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D257" t="s">
-        <v>210</v>
+        <v>319</v>
       </c>
       <c r="E257" t="s">
         <v>8</v>
@@ -6307,13 +6319,13 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D258" t="s">
-        <v>241</v>
+        <v>287</v>
       </c>
       <c r="E258" t="s">
         <v>8</v>
@@ -6324,13 +6336,13 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D259" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E259" t="s">
         <v>8</v>
@@ -6341,13 +6353,13 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D260" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="E260" t="s">
         <v>8</v>
@@ -6358,13 +6370,13 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D261" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="E261" t="s">
         <v>8</v>
@@ -6375,13 +6387,13 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D262" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="E262" t="s">
         <v>8</v>
@@ -6392,13 +6404,13 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D263" t="s">
-        <v>322</v>
+        <v>261</v>
       </c>
       <c r="E263" t="s">
         <v>8</v>
@@ -6409,13 +6421,13 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D264" t="s">
-        <v>324</v>
+        <v>196</v>
       </c>
       <c r="E264" t="s">
         <v>8</v>
@@ -6426,13 +6438,13 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D265" t="s">
-        <v>204</v>
+        <v>244</v>
       </c>
       <c r="E265" t="s">
         <v>8</v>
@@ -6443,13 +6455,13 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D266" t="s">
-        <v>248</v>
+        <v>220</v>
       </c>
       <c r="E266" t="s">
         <v>8</v>
@@ -6460,13 +6472,13 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D267" t="s">
-        <v>250</v>
+        <v>331</v>
       </c>
       <c r="E267" t="s">
         <v>8</v>
@@ -6477,13 +6489,13 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D268" t="s">
-        <v>214</v>
+        <v>333</v>
       </c>
       <c r="E268" t="s">
         <v>8</v>
@@ -6494,13 +6506,13 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D269" t="s">
-        <v>324</v>
+        <v>244</v>
       </c>
       <c r="E269" t="s">
         <v>8</v>
@@ -6511,13 +6523,13 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D270" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="E270" t="s">
         <v>8</v>
@@ -6528,13 +6540,13 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D271" t="s">
-        <v>243</v>
+        <v>331</v>
       </c>
       <c r="E271" t="s">
         <v>8</v>
@@ -6545,13 +6557,13 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D272" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="E272" t="s">
         <v>8</v>
@@ -6562,13 +6574,13 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D273" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="E273" t="s">
         <v>8</v>
@@ -6579,13 +6591,13 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D274" t="s">
-        <v>337</v>
+        <v>246</v>
       </c>
       <c r="E274" t="s">
         <v>8</v>
@@ -6596,13 +6608,13 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D275" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="E275" t="s">
         <v>8</v>
@@ -6613,13 +6625,13 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D276" t="s">
-        <v>334</v>
+        <v>209</v>
       </c>
       <c r="E276" t="s">
         <v>8</v>
@@ -6630,13 +6642,13 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D277" t="s">
-        <v>311</v>
+        <v>346</v>
       </c>
       <c r="E277" t="s">
         <v>8</v>
@@ -6647,13 +6659,13 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D278" t="s">
-        <v>324</v>
+        <v>194</v>
       </c>
       <c r="E278" t="s">
         <v>8</v>
@@ -6664,13 +6676,13 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D279" t="s">
-        <v>190</v>
+        <v>349</v>
       </c>
       <c r="E279" t="s">
         <v>8</v>
@@ -6681,13 +6693,13 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D280" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="E280" t="s">
         <v>8</v>
@@ -6698,13 +6710,13 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D281" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="E281" t="s">
         <v>8</v>
@@ -6715,13 +6727,13 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D282" t="s">
-        <v>291</v>
+        <v>354</v>
       </c>
       <c r="E282" t="s">
         <v>8</v>
@@ -6732,13 +6744,13 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D283" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="E283" t="s">
         <v>8</v>
@@ -6749,13 +6761,13 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D284" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="E284" t="s">
         <v>8</v>
@@ -6766,13 +6778,13 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D285" t="s">
-        <v>353</v>
+        <v>218</v>
       </c>
       <c r="E285" t="s">
         <v>8</v>
@@ -6783,13 +6795,13 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D286" t="s">
-        <v>192</v>
+        <v>346</v>
       </c>
       <c r="E286" t="s">
         <v>8</v>
@@ -6800,13 +6812,13 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D287" t="s">
-        <v>356</v>
+        <v>236</v>
       </c>
       <c r="E287" t="s">
         <v>8</v>
@@ -6817,13 +6829,13 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D288" t="s">
-        <v>226</v>
+        <v>190</v>
       </c>
       <c r="E288" t="s">
         <v>8</v>
@@ -6834,13 +6846,13 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D289" t="s">
-        <v>351</v>
+        <v>242</v>
       </c>
       <c r="E289" t="s">
         <v>8</v>
@@ -6851,13 +6863,13 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D290" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="E290" t="s">
         <v>8</v>
@@ -6868,13 +6880,13 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D291" t="s">
-        <v>361</v>
+        <v>261</v>
       </c>
       <c r="E291" t="s">
         <v>8</v>
@@ -6885,13 +6897,13 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D292" t="s">
-        <v>261</v>
+        <v>226</v>
       </c>
       <c r="E292" t="s">
         <v>8</v>
@@ -6902,13 +6914,13 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D293" t="s">
-        <v>364</v>
+        <v>231</v>
       </c>
       <c r="E293" t="s">
         <v>8</v>
@@ -6919,13 +6931,13 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D294" t="s">
-        <v>237</v>
+        <v>369</v>
       </c>
       <c r="E294" t="s">
         <v>8</v>
@@ -6936,13 +6948,13 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D295" t="s">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="E295" t="s">
         <v>8</v>
@@ -6953,13 +6965,13 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D296" t="s">
-        <v>271</v>
+        <v>372</v>
       </c>
       <c r="E296" t="s">
         <v>8</v>
@@ -6970,13 +6982,13 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D297" t="s">
-        <v>271</v>
+        <v>374</v>
       </c>
       <c r="E297" t="s">
         <v>8</v>
@@ -6987,13 +6999,13 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D298" t="s">
-        <v>254</v>
+        <v>376</v>
       </c>
       <c r="E298" t="s">
         <v>8</v>
@@ -7004,13 +7016,13 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D299" t="s">
-        <v>371</v>
+        <v>343</v>
       </c>
       <c r="E299" t="s">
         <v>8</v>
@@ -7021,13 +7033,13 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D300" t="s">
-        <v>228</v>
+        <v>379</v>
       </c>
       <c r="E300" t="s">
         <v>8</v>
@@ -7038,13 +7050,13 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D301" t="s">
-        <v>351</v>
+        <v>381</v>
       </c>
       <c r="E301" t="s">
         <v>8</v>
@@ -7055,13 +7067,13 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D302" t="s">
-        <v>259</v>
+        <v>383</v>
       </c>
       <c r="E302" t="s">
         <v>8</v>
@@ -7072,13 +7084,13 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D303" t="s">
-        <v>376</v>
+        <v>251</v>
       </c>
       <c r="E303" t="s">
         <v>8</v>
@@ -7089,13 +7101,13 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D304" t="s">
-        <v>204</v>
+        <v>386</v>
       </c>
       <c r="E304" t="s">
         <v>8</v>
@@ -7106,13 +7118,13 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D305" t="s">
-        <v>356</v>
+        <v>213</v>
       </c>
       <c r="E305" t="s">
         <v>8</v>
@@ -7123,13 +7135,13 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D306" t="s">
-        <v>331</v>
+        <v>209</v>
       </c>
       <c r="E306" t="s">
         <v>8</v>
@@ -7140,13 +7152,13 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D307" t="s">
-        <v>331</v>
+        <v>390</v>
       </c>
       <c r="E307" t="s">
         <v>8</v>
@@ -7157,13 +7169,13 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D308" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="E308" t="s">
         <v>8</v>
@@ -7174,13 +7186,13 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D309" t="s">
-        <v>384</v>
+        <v>238</v>
       </c>
       <c r="E309" t="s">
         <v>8</v>
@@ -7191,13 +7203,13 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D310" t="s">
-        <v>271</v>
+        <v>395</v>
       </c>
       <c r="E310" t="s">
         <v>8</v>
@@ -7208,13 +7220,13 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D311" t="s">
-        <v>387</v>
+        <v>323</v>
       </c>
       <c r="E311" t="s">
         <v>8</v>
@@ -7225,13 +7237,13 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D312" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="E312" t="s">
         <v>8</v>
@@ -7242,13 +7254,13 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D313" t="s">
-        <v>391</v>
+        <v>190</v>
       </c>
       <c r="E313" t="s">
         <v>8</v>
@@ -7259,13 +7271,13 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D314" t="s">
-        <v>210</v>
+        <v>296</v>
       </c>
       <c r="E314" t="s">
         <v>8</v>
@@ -7276,13 +7288,13 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D315" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="E315" t="s">
         <v>8</v>
@@ -7293,13 +7305,13 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D316" t="s">
-        <v>353</v>
+        <v>392</v>
       </c>
       <c r="E316" t="s">
         <v>8</v>
@@ -7310,13 +7322,13 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D317" t="s">
-        <v>397</v>
+        <v>198</v>
       </c>
       <c r="E317" t="s">
         <v>8</v>
@@ -7327,13 +7339,13 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D318" t="s">
-        <v>252</v>
+        <v>305</v>
       </c>
       <c r="E318" t="s">
         <v>8</v>
@@ -7344,13 +7356,13 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D319" t="s">
-        <v>339</v>
+        <v>406</v>
       </c>
       <c r="E319" t="s">
         <v>8</v>
@@ -7361,13 +7373,13 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D320" t="s">
-        <v>324</v>
+        <v>209</v>
       </c>
       <c r="E320" t="s">
         <v>8</v>
@@ -7378,13 +7390,13 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D321" t="s">
-        <v>349</v>
+        <v>229</v>
       </c>
       <c r="E321" t="s">
         <v>8</v>
@@ -7395,13 +7407,13 @@
         <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D322" t="s">
-        <v>271</v>
+        <v>303</v>
       </c>
       <c r="E322" t="s">
         <v>8</v>
@@ -7412,13 +7424,13 @@
         <v>322</v>
       </c>
       <c r="B323" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D323" t="s">
-        <v>404</v>
+        <v>246</v>
       </c>
       <c r="E323" t="s">
         <v>8</v>
@@ -7429,13 +7441,13 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D324" t="s">
-        <v>267</v>
+        <v>358</v>
       </c>
       <c r="E324" t="s">
         <v>8</v>
@@ -7446,13 +7458,13 @@
         <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D325" t="s">
-        <v>407</v>
+        <v>220</v>
       </c>
       <c r="E325" t="s">
         <v>8</v>
@@ -7463,13 +7475,13 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D326" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="E326" t="s">
         <v>8</v>
@@ -7480,13 +7492,13 @@
         <v>326</v>
       </c>
       <c r="B327" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D327" t="s">
-        <v>281</v>
+        <v>349</v>
       </c>
       <c r="E327" t="s">
         <v>8</v>
@@ -7497,13 +7509,13 @@
         <v>327</v>
       </c>
       <c r="B328" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D328" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="E328" t="s">
         <v>8</v>
@@ -7514,13 +7526,13 @@
         <v>328</v>
       </c>
       <c r="B329" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D329" t="s">
-        <v>210</v>
+        <v>249</v>
       </c>
       <c r="E329" t="s">
         <v>8</v>
@@ -7531,13 +7543,13 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D330" t="s">
-        <v>296</v>
+        <v>351</v>
       </c>
       <c r="E330" t="s">
         <v>8</v>
@@ -7548,7 +7560,7 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>6</v>
@@ -7565,13 +7577,13 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D332" t="s">
-        <v>414</v>
+        <v>213</v>
       </c>
       <c r="E332" t="s">
         <v>8</v>
@@ -7582,13 +7594,13 @@
         <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D333" t="s">
-        <v>349</v>
+        <v>395</v>
       </c>
       <c r="E333" t="s">
         <v>8</v>
@@ -7599,13 +7611,13 @@
         <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D334" t="s">
-        <v>299</v>
+        <v>192</v>
       </c>
       <c r="E334" t="s">
         <v>8</v>
@@ -7616,13 +7628,13 @@
         <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D335" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="E335" t="s">
         <v>8</v>
@@ -7633,13 +7645,13 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D336" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="E336" t="s">
         <v>8</v>
@@ -7650,13 +7662,13 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D337" t="s">
-        <v>208</v>
+        <v>305</v>
       </c>
       <c r="E337" t="s">
         <v>8</v>
@@ -7667,13 +7679,13 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D338" t="s">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="E338" t="s">
         <v>8</v>
@@ -7684,13 +7696,13 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D339" t="s">
-        <v>194</v>
+        <v>428</v>
       </c>
       <c r="E339" t="s">
         <v>8</v>
@@ -7701,13 +7713,13 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D340" t="s">
-        <v>425</v>
+        <v>392</v>
       </c>
       <c r="E340" t="s">
         <v>8</v>
@@ -7718,13 +7730,13 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D341" t="s">
-        <v>351</v>
+        <v>238</v>
       </c>
       <c r="E341" t="s">
         <v>8</v>
@@ -7735,13 +7747,13 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D342" t="s">
-        <v>206</v>
+        <v>354</v>
       </c>
       <c r="E342" t="s">
         <v>8</v>
@@ -7752,13 +7764,13 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D343" t="s">
-        <v>420</v>
+        <v>209</v>
       </c>
       <c r="E343" t="s">
         <v>8</v>
@@ -7769,13 +7781,13 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D344" t="s">
-        <v>274</v>
+        <v>231</v>
       </c>
       <c r="E344" t="s">
         <v>8</v>
@@ -7786,13 +7798,13 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D345" t="s">
-        <v>271</v>
+        <v>305</v>
       </c>
       <c r="E345" t="s">
         <v>8</v>
@@ -7803,13 +7815,13 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D346" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="E346" t="s">
         <v>8</v>
@@ -7820,13 +7832,13 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D347" t="s">
-        <v>206</v>
+        <v>253</v>
       </c>
       <c r="E347" t="s">
         <v>8</v>
@@ -7837,13 +7849,13 @@
         <v>347</v>
       </c>
       <c r="B348" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D348" t="s">
-        <v>334</v>
+        <v>438</v>
       </c>
       <c r="E348" t="s">
         <v>8</v>
@@ -7854,13 +7866,13 @@
         <v>348</v>
       </c>
       <c r="B349" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D349" t="s">
-        <v>233</v>
+        <v>284</v>
       </c>
       <c r="E349" t="s">
         <v>8</v>
@@ -7871,13 +7883,13 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D350" t="s">
-        <v>407</v>
+        <v>196</v>
       </c>
       <c r="E350" t="s">
         <v>8</v>
@@ -7888,13 +7900,13 @@
         <v>350</v>
       </c>
       <c r="B351" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D351" t="s">
-        <v>228</v>
+        <v>358</v>
       </c>
       <c r="E351" t="s">
         <v>8</v>
@@ -7905,13 +7917,13 @@
         <v>351</v>
       </c>
       <c r="B352" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D352" t="s">
-        <v>239</v>
+        <v>296</v>
       </c>
       <c r="E352" t="s">
         <v>8</v>
@@ -7922,13 +7934,13 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D353" t="s">
-        <v>397</v>
+        <v>216</v>
       </c>
       <c r="E353" t="s">
         <v>8</v>
@@ -7939,13 +7951,13 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D354" t="s">
-        <v>404</v>
+        <v>331</v>
       </c>
       <c r="E354" t="s">
         <v>8</v>
@@ -7956,13 +7968,13 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D355" t="s">
-        <v>322</v>
+        <v>349</v>
       </c>
       <c r="E355" t="s">
         <v>8</v>
@@ -7973,13 +7985,13 @@
         <v>355</v>
       </c>
       <c r="B356" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D356" t="s">
-        <v>284</v>
+        <v>369</v>
       </c>
       <c r="E356" t="s">
         <v>8</v>
@@ -7990,13 +8002,13 @@
         <v>356</v>
       </c>
       <c r="B357" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D357" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="E357" t="s">
         <v>8</v>
@@ -8007,13 +8019,13 @@
         <v>357</v>
       </c>
       <c r="B358" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D358" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="E358" t="s">
         <v>8</v>
@@ -8024,13 +8036,13 @@
         <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D359" t="s">
-        <v>248</v>
+        <v>451</v>
       </c>
       <c r="E359" t="s">
         <v>8</v>
@@ -8041,13 +8053,13 @@
         <v>359</v>
       </c>
       <c r="B360" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D360" t="s">
-        <v>384</v>
+        <v>269</v>
       </c>
       <c r="E360" t="s">
         <v>8</v>
@@ -8058,13 +8070,13 @@
         <v>360</v>
       </c>
       <c r="B361" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D361" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="E361" t="s">
         <v>8</v>
@@ -8075,13 +8087,13 @@
         <v>361</v>
       </c>
       <c r="B362" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D362" t="s">
-        <v>449</v>
+        <v>383</v>
       </c>
       <c r="E362" t="s">
         <v>8</v>
@@ -8092,13 +8104,13 @@
         <v>362</v>
       </c>
       <c r="B363" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D363" t="s">
-        <v>364</v>
+        <v>336</v>
       </c>
       <c r="E363" t="s">
         <v>8</v>
@@ -8109,13 +8121,13 @@
         <v>363</v>
       </c>
       <c r="B364" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D364" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="E364" t="s">
         <v>8</v>
@@ -8126,13 +8138,13 @@
         <v>364</v>
       </c>
       <c r="B365" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D365" t="s">
-        <v>274</v>
+        <v>238</v>
       </c>
       <c r="E365" t="s">
         <v>8</v>
@@ -8143,13 +8155,13 @@
         <v>365</v>
       </c>
       <c r="B366" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D366" t="s">
-        <v>220</v>
+        <v>246</v>
       </c>
       <c r="E366" t="s">
         <v>8</v>
@@ -8160,13 +8172,13 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D367" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="E367" t="s">
         <v>8</v>
@@ -8177,13 +8189,13 @@
         <v>367</v>
       </c>
       <c r="B368" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D368" t="s">
-        <v>414</v>
+        <v>303</v>
       </c>
       <c r="E368" t="s">
         <v>8</v>
@@ -8194,13 +8206,13 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D369" t="s">
-        <v>306</v>
+        <v>392</v>
       </c>
       <c r="E369" t="s">
         <v>8</v>
@@ -8211,13 +8223,13 @@
         <v>369</v>
       </c>
       <c r="B370" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D370" t="s">
-        <v>226</v>
+        <v>265</v>
       </c>
       <c r="E370" t="s">
         <v>8</v>
@@ -8228,13 +8240,13 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D371" t="s">
-        <v>274</v>
+        <v>374</v>
       </c>
       <c r="E371" t="s">
         <v>8</v>
@@ -8245,13 +8257,13 @@
         <v>371</v>
       </c>
       <c r="B372" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D372" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E372" t="s">
         <v>8</v>
@@ -8262,13 +8274,13 @@
         <v>372</v>
       </c>
       <c r="B373" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D373" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="E373" t="s">
         <v>8</v>
@@ -8279,13 +8291,13 @@
         <v>373</v>
       </c>
       <c r="B374" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D374" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="E374" t="s">
         <v>8</v>
@@ -8296,13 +8308,13 @@
         <v>374</v>
       </c>
       <c r="B375" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D375" t="s">
-        <v>239</v>
+        <v>194</v>
       </c>
       <c r="E375" t="s">
         <v>8</v>
@@ -8313,13 +8325,13 @@
         <v>375</v>
       </c>
       <c r="B376" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D376" t="s">
-        <v>264</v>
+        <v>381</v>
       </c>
       <c r="E376" t="s">
         <v>8</v>
@@ -8330,13 +8342,13 @@
         <v>376</v>
       </c>
       <c r="B377" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D377" t="s">
-        <v>226</v>
+        <v>303</v>
       </c>
       <c r="E377" t="s">
         <v>8</v>
@@ -8347,13 +8359,13 @@
         <v>377</v>
       </c>
       <c r="B378" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D378" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="E378" t="s">
         <v>8</v>
@@ -8364,13 +8376,13 @@
         <v>378</v>
       </c>
       <c r="B379" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D379" t="s">
-        <v>468</v>
+        <v>303</v>
       </c>
       <c r="E379" t="s">
         <v>8</v>
@@ -8381,13 +8393,13 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D380" t="s">
-        <v>414</v>
+        <v>192</v>
       </c>
       <c r="E380" t="s">
         <v>8</v>
@@ -8398,13 +8410,13 @@
         <v>380</v>
       </c>
       <c r="B381" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D381" t="s">
-        <v>230</v>
+        <v>294</v>
       </c>
       <c r="E381" t="s">
         <v>8</v>
@@ -8415,13 +8427,13 @@
         <v>381</v>
       </c>
       <c r="B382" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D382" t="s">
-        <v>391</v>
+        <v>190</v>
       </c>
       <c r="E382" t="s">
         <v>8</v>
@@ -8432,13 +8444,13 @@
         <v>382</v>
       </c>
       <c r="B383" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D383" t="s">
-        <v>218</v>
+        <v>319</v>
       </c>
       <c r="E383" t="s">
         <v>8</v>
@@ -8449,13 +8461,13 @@
         <v>383</v>
       </c>
       <c r="B384" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D384" t="s">
-        <v>474</v>
+        <v>383</v>
       </c>
       <c r="E384" t="s">
         <v>8</v>
@@ -8466,13 +8478,13 @@
         <v>384</v>
       </c>
       <c r="B385" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D385" t="s">
-        <v>196</v>
+        <v>276</v>
       </c>
       <c r="E385" t="s">
         <v>8</v>
@@ -8483,13 +8495,13 @@
         <v>385</v>
       </c>
       <c r="B386" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D386" t="s">
-        <v>218</v>
+        <v>390</v>
       </c>
       <c r="E386" t="s">
         <v>8</v>
@@ -8500,13 +8512,13 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D387" t="s">
-        <v>334</v>
+        <v>315</v>
       </c>
       <c r="E387" t="s">
         <v>8</v>
@@ -8517,13 +8529,13 @@
         <v>387</v>
       </c>
       <c r="B388" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D388" t="s">
-        <v>479</v>
+        <v>374</v>
       </c>
       <c r="E388" t="s">
         <v>8</v>
@@ -8534,13 +8546,13 @@
         <v>388</v>
       </c>
       <c r="B389" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D389" t="s">
-        <v>364</v>
+        <v>483</v>
       </c>
       <c r="E389" t="s">
         <v>8</v>
@@ -8551,13 +8563,13 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D390" t="s">
-        <v>322</v>
+        <v>398</v>
       </c>
       <c r="E390" t="s">
         <v>8</v>
@@ -8568,13 +8580,13 @@
         <v>390</v>
       </c>
       <c r="B391" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D391" t="s">
-        <v>200</v>
+        <v>287</v>
       </c>
       <c r="E391" t="s">
         <v>8</v>
@@ -8585,13 +8597,13 @@
         <v>391</v>
       </c>
       <c r="B392" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D392" t="s">
-        <v>210</v>
+        <v>487</v>
       </c>
       <c r="E392" t="s">
         <v>8</v>
@@ -8602,13 +8614,13 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D393" t="s">
-        <v>239</v>
+        <v>209</v>
       </c>
       <c r="E393" t="s">
         <v>8</v>
@@ -8619,13 +8631,13 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D394" t="s">
-        <v>267</v>
+        <v>483</v>
       </c>
       <c r="E394" t="s">
         <v>8</v>
@@ -8636,13 +8648,13 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D395" t="s">
-        <v>208</v>
+        <v>491</v>
       </c>
       <c r="E395" t="s">
         <v>8</v>
@@ -8653,13 +8665,13 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D396" t="s">
-        <v>296</v>
+        <v>234</v>
       </c>
       <c r="E396" t="s">
         <v>8</v>
@@ -8670,13 +8682,13 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D397" t="s">
-        <v>311</v>
+        <v>358</v>
       </c>
       <c r="E397" t="s">
         <v>8</v>
@@ -8687,13 +8699,13 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D398" t="s">
-        <v>490</v>
+        <v>265</v>
       </c>
       <c r="E398" t="s">
         <v>8</v>
@@ -8704,13 +8716,13 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D399" t="s">
-        <v>346</v>
+        <v>414</v>
       </c>
       <c r="E399" t="s">
         <v>8</v>
@@ -8721,13 +8733,13 @@
         <v>399</v>
       </c>
       <c r="B400" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D400" t="s">
-        <v>334</v>
+        <v>251</v>
       </c>
       <c r="E400" t="s">
         <v>8</v>
@@ -8738,13 +8750,13 @@
         <v>400</v>
       </c>
       <c r="B401" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D401" t="s">
-        <v>331</v>
+        <v>438</v>
       </c>
       <c r="E401" t="s">
         <v>8</v>
@@ -8763,47 +8775,47 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B1" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="B2" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B3" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B4" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B5" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B6">
         <v>400</v>
@@ -8811,7 +8823,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="B7">
         <v>400</v>
@@ -8819,7 +8831,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -8827,7 +8839,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -8835,10 +8847,10 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B10" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
   </sheetData>

--- a/reports/backend/Excel/Automation_Test_Report.xlsx
+++ b/reports/backend/Excel/Automation_Test_Report.xlsx
@@ -86,12 +86,12 @@
     <t>Smart Admission Backend — Authentication Tests BT-016 | Institutional email domain (.edu/.ac/.sse) is valid</t>
   </si>
   <si>
+    <t>0.001</t>
+  </si>
+  <si>
     <t>Smart Admission Backend — Authentication Tests BT-017 | Email with spaces fails validation</t>
   </si>
   <si>
-    <t>0.001</t>
-  </si>
-  <si>
     <t>Smart Admission Backend — Authentication Tests BT-018 | Email with multiple @ fails validation</t>
   </si>
   <si>
@@ -584,924 +584,924 @@
     <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #180</t>
   </si>
   <si>
+    <t>0.081</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #181</t>
+  </si>
+  <si>
+    <t>0.042</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #182</t>
+  </si>
+  <si>
+    <t>0.055</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #183</t>
+  </si>
+  <si>
+    <t>0.048</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #184</t>
+  </si>
+  <si>
+    <t>0.063</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #185</t>
+  </si>
+  <si>
+    <t>0.118</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #186</t>
+  </si>
+  <si>
+    <t>0.105</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #187</t>
+  </si>
+  <si>
+    <t>0.103</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #188</t>
+  </si>
+  <si>
+    <t>0.101</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #189</t>
+  </si>
+  <si>
+    <t>0.097</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #190</t>
+  </si>
+  <si>
+    <t>0.035</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #191</t>
+  </si>
+  <si>
+    <t>0.083</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #192</t>
+  </si>
+  <si>
+    <t>0.051</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #193</t>
+  </si>
+  <si>
+    <t>0.053</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #194</t>
+  </si>
+  <si>
+    <t>0.070</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #195</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #196</t>
+  </si>
+  <si>
+    <t>0.104</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #197</t>
+  </si>
+  <si>
+    <t>0.111</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #198</t>
+  </si>
+  <si>
+    <t>0.050</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #199</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #200</t>
+  </si>
+  <si>
+    <t>0.043</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #201</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #202</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #203</t>
+  </si>
+  <si>
+    <t>0.089</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #204</t>
+  </si>
+  <si>
+    <t>0.065</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #205</t>
+  </si>
+  <si>
+    <t>0.113</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #206</t>
+  </si>
+  <si>
+    <t>0.039</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #207</t>
+  </si>
+  <si>
+    <t>0.102</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #208</t>
+  </si>
+  <si>
+    <t>0.057</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #209</t>
+  </si>
+  <si>
+    <t>0.077</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #210</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #211</t>
+  </si>
+  <si>
+    <t>0.073</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #212</t>
+  </si>
+  <si>
+    <t>0.038</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #213</t>
+  </si>
+  <si>
+    <t>0.028</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #214</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #215</t>
+  </si>
+  <si>
+    <t>0.075</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #216</t>
+  </si>
+  <si>
+    <t>0.058</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #217</t>
+  </si>
+  <si>
+    <t>0.088</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #218</t>
+  </si>
+  <si>
+    <t>0.047</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #219</t>
+  </si>
+  <si>
+    <t>0.094</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #220</t>
+  </si>
+  <si>
+    <t>0.068</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #221</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #222</t>
+  </si>
+  <si>
+    <t>0.040</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #223</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #224</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #225</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #226</t>
+  </si>
+  <si>
+    <t>0.036</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #227</t>
+  </si>
+  <si>
+    <t>0.069</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #228</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #229</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #230</t>
+  </si>
+  <si>
+    <t>0.029</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #231</t>
+  </si>
+  <si>
+    <t>0.054</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #232</t>
+  </si>
+  <si>
+    <t>0.037</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #233</t>
+  </si>
+  <si>
+    <t>0.044</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #234</t>
+  </si>
+  <si>
+    <t>0.060</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #235</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #236</t>
+  </si>
+  <si>
+    <t>0.046</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #237</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #238</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #239</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #240</t>
+  </si>
+  <si>
+    <t>0.093</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #241</t>
+  </si>
+  <si>
+    <t>0.026</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #242</t>
+  </si>
+  <si>
+    <t>0.033</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #243</t>
+  </si>
+  <si>
+    <t>0.074</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #244</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #245</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #246</t>
+  </si>
+  <si>
+    <t>0.067</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #247</t>
+  </si>
+  <si>
     <t>0.116</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #181</t>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #248</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #249</t>
+  </si>
+  <si>
+    <t>0.090</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #250</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #251</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #252</t>
+  </si>
+  <si>
+    <t>0.092</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #253</t>
+  </si>
+  <si>
+    <t>0.022</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #254</t>
+  </si>
+  <si>
+    <t>0.082</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #255</t>
+  </si>
+  <si>
+    <t>0.114</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #256</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #257</t>
+  </si>
+  <si>
+    <t>0.108</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #258</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #259</t>
+  </si>
+  <si>
+    <t>0.084</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #260</t>
+  </si>
+  <si>
+    <t>0.117</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #261</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #262</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #263</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #264</t>
+  </si>
+  <si>
+    <t>0.099</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #265</t>
+  </si>
+  <si>
+    <t>0.023</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #266</t>
+  </si>
+  <si>
+    <t>0.061</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #267</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #268</t>
+  </si>
+  <si>
+    <t>0.095</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #269</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #270</t>
+  </si>
+  <si>
+    <t>0.086</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #271</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #272</t>
+  </si>
+  <si>
+    <t>0.041</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #273</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #274</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #275</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #276</t>
+  </si>
+  <si>
+    <t>0.020</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #277</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #278</t>
+  </si>
+  <si>
+    <t>0.091</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #279</t>
   </si>
   <si>
     <t>0.085</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #182</t>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #280</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #281</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #282</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #283</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #284</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #285</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #286</t>
+  </si>
+  <si>
+    <t>0.072</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #287</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #288</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #289</t>
+  </si>
+  <si>
+    <t>0.112</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #290</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #291</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #292</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #293</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #294</t>
+  </si>
+  <si>
+    <t>0.079</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #295</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #296</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #297</t>
+  </si>
+  <si>
+    <t>0.032</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #298</t>
+  </si>
+  <si>
+    <t>0.025</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #299</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #300</t>
+  </si>
+  <si>
+    <t>0.115</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #301</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #302</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #303</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #304</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #305</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #306</t>
+  </si>
+  <si>
+    <t>0.021</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #307</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #308</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #309</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #310</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #311</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #312</t>
+  </si>
+  <si>
+    <t>0.064</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #313</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #314</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #315</t>
+  </si>
+  <si>
+    <t>0.049</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #316</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #317</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #318</t>
+  </si>
+  <si>
+    <t>0.052</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #319</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #320</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #321</t>
+  </si>
+  <si>
+    <t>0.119</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #322</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #323</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #324</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #325</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #326</t>
+  </si>
+  <si>
+    <t>0.087</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #327</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #328</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #329</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #330</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #331</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #332</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #333</t>
+  </si>
+  <si>
+    <t>0.107</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #334</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #335</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #336</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #337</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #338</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #339</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #340</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #341</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #342</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #343</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #344</t>
+  </si>
+  <si>
+    <t>0.027</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #345</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #346</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #347</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #348</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #349</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #350</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #351</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #352</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #353</t>
+  </si>
+  <si>
+    <t>0.024</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #354</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #355</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #356</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #357</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #358</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #359</t>
+  </si>
+  <si>
+    <t>0.080</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #360</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #361</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #362</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #363</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #364</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #365</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #366</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #367</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #368</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #369</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #370</t>
+  </si>
+  <si>
+    <t>0.066</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #371</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #372</t>
+  </si>
+  <si>
+    <t>0.106</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #373</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #374</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #375</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #376</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #377</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #378</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #379</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #380</t>
   </si>
   <si>
     <t>0.059</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #183</t>
-  </si>
-  <si>
-    <t>0.110</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #184</t>
-  </si>
-  <si>
-    <t>0.104</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #185</t>
-  </si>
-  <si>
-    <t>0.060</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #186</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #187</t>
-  </si>
-  <si>
-    <t>0.096</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #188</t>
-  </si>
-  <si>
-    <t>0.021</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #189</t>
-  </si>
-  <si>
-    <t>0.103</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #190</t>
-  </si>
-  <si>
-    <t>0.105</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #191</t>
-  </si>
-  <si>
-    <t>0.054</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #192</t>
-  </si>
-  <si>
-    <t>0.057</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #193</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #194</t>
-  </si>
-  <si>
-    <t>0.047</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #195</t>
-  </si>
-  <si>
-    <t>0.093</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #196</t>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #381</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #382</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #383</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #384</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #385</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #386</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #387</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #388</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #389</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #390</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #391</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #392</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #393</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #394</t>
+  </si>
+  <si>
+    <t>0.031</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #395</t>
   </si>
   <si>
     <t>0.034</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #197</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #198</t>
-  </si>
-  <si>
-    <t>0.100</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #199</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #200</t>
-  </si>
-  <si>
-    <t>0.052</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #201</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #202</t>
-  </si>
-  <si>
-    <t>0.111</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #203</t>
-  </si>
-  <si>
-    <t>0.108</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #204</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #205</t>
-  </si>
-  <si>
-    <t>0.113</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #206</t>
-  </si>
-  <si>
-    <t>0.038</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #207</t>
-  </si>
-  <si>
-    <t>0.041</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #208</t>
-  </si>
-  <si>
-    <t>0.076</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #209</t>
-  </si>
-  <si>
-    <t>0.118</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #210</t>
-  </si>
-  <si>
-    <t>0.112</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #211</t>
-  </si>
-  <si>
-    <t>0.091</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #212</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #213</t>
-  </si>
-  <si>
-    <t>0.045</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #214</t>
-  </si>
-  <si>
-    <t>0.061</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #215</t>
-  </si>
-  <si>
-    <t>0.092</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #216</t>
-  </si>
-  <si>
-    <t>0.069</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #217</t>
-  </si>
-  <si>
-    <t>0.078</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #218</t>
-  </si>
-  <si>
-    <t>0.020</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #219</t>
-  </si>
-  <si>
-    <t>0.042</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #220</t>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #396</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #397</t>
   </si>
   <si>
     <t>0.030</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #221</t>
-  </si>
-  <si>
-    <t>0.106</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #222</t>
-  </si>
-  <si>
-    <t>0.075</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #223</t>
-  </si>
-  <si>
-    <t>0.028</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #224</t>
-  </si>
-  <si>
-    <t>0.050</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #225</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #226</t>
-  </si>
-  <si>
-    <t>0.115</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #227</t>
-  </si>
-  <si>
-    <t>0.067</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #228</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #229</t>
-  </si>
-  <si>
-    <t>0.033</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #230</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #231</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #232</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #233</t>
-  </si>
-  <si>
-    <t>0.089</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #234</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #235</t>
-  </si>
-  <si>
-    <t>0.071</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #236</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #237</t>
-  </si>
-  <si>
-    <t>0.077</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #238</t>
-  </si>
-  <si>
-    <t>0.101</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #239</t>
-  </si>
-  <si>
-    <t>0.099</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #240</t>
-  </si>
-  <si>
-    <t>0.079</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #241</t>
-  </si>
-  <si>
-    <t>0.040</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #242</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #243</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #244</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #245</t>
-  </si>
-  <si>
-    <t>0.114</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #246</t>
-  </si>
-  <si>
-    <t>0.024</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #247</t>
-  </si>
-  <si>
-    <t>0.084</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #248</t>
-  </si>
-  <si>
-    <t>0.063</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #249</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #250</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #251</t>
-  </si>
-  <si>
-    <t>0.119</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #252</t>
-  </si>
-  <si>
-    <t>0.025</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #253</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #254</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #255</t>
-  </si>
-  <si>
-    <t>0.068</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #256</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #257</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #258</t>
-  </si>
-  <si>
-    <t>0.053</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #259</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #260</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #261</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #262</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #263</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #264</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #265</t>
-  </si>
-  <si>
-    <t>0.088</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #266</t>
-  </si>
-  <si>
-    <t>0.056</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #267</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #268</t>
-  </si>
-  <si>
-    <t>0.029</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #269</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #270</t>
-  </si>
-  <si>
-    <t>0.031</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #271</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #272</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #273</t>
-  </si>
-  <si>
-    <t>0.073</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #274</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #275</t>
-  </si>
-  <si>
-    <t>0.095</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #276</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #277</t>
-  </si>
-  <si>
-    <t>0.064</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #278</t>
-  </si>
-  <si>
-    <t>0.035</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #279</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #280</t>
-  </si>
-  <si>
-    <t>0.032</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #281</t>
-  </si>
-  <si>
-    <t>0.087</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #282</t>
-  </si>
-  <si>
-    <t>0.098</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #283</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #284</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #285</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #286</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #287</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #288</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #289</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #290</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #291</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #292</t>
-  </si>
-  <si>
-    <t>0.051</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #293</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #294</t>
-  </si>
-  <si>
-    <t>0.043</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #295</t>
-  </si>
-  <si>
-    <t>0.046</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #296</t>
-  </si>
-  <si>
-    <t>0.058</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #297</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #298</t>
-  </si>
-  <si>
-    <t>0.036</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #299</t>
-  </si>
-  <si>
-    <t>0.097</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #300</t>
-  </si>
-  <si>
-    <t>0.062</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #301</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #302</t>
-  </si>
-  <si>
-    <t>0.070</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #303</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #304</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #305</t>
-  </si>
-  <si>
-    <t>0.022</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #306</t>
-  </si>
-  <si>
-    <t>0.086</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #307</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #308</t>
-  </si>
-  <si>
-    <t>0.072</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #309</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #310</t>
-  </si>
-  <si>
-    <t>0.080</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #311</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #312</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #313</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #314</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #315</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #316</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #317</t>
-  </si>
-  <si>
-    <t>0.066</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #318</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #319</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #320</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #321</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #322</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #323</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #324</t>
-  </si>
-  <si>
-    <t>0.083</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #325</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #326</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #327</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #328</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #329</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #330</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #331</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #332</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #333</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #334</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #335</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #336</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #337</t>
-  </si>
-  <si>
-    <t>0.102</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #338</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #339</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #340</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #341</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #342</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #343</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #344</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #345</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #346</t>
-  </si>
-  <si>
-    <t>0.055</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #347</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #348</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #349</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #350</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #351</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #352</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #353</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #354</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #355</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #356</t>
-  </si>
-  <si>
-    <t>0.094</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #357</t>
-  </si>
-  <si>
-    <t>0.109</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #358</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #359</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #360</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #361</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #362</t>
-  </si>
-  <si>
-    <t>0.044</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #363</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #364</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #365</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #366</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #367</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #368</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #369</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #370</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #371</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #372</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #373</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #374</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #375</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #376</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #377</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #378</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #379</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #380</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #381</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #382</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #383</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #384</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #385</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #386</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #387</t>
-  </si>
-  <si>
-    <t>0.081</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #388</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #389</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #390</t>
-  </si>
-  <si>
-    <t>0.023</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #391</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #392</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #393</t>
-  </si>
-  <si>
-    <t>0.039</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #394</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #395</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #396</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #397</t>
-  </si>
-  <si>
     <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #398</t>
   </si>
   <si>
@@ -1517,13 +1517,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>15</t>
+    <t>16</t>
   </si>
   <si>
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 13:46:52 UTC</t>
+    <t>2026-06-23 13:55:06 UTC</t>
   </si>
   <si>
     <t>Branch</t>
@@ -1535,7 +1535,7 @@
     <t>Commit</t>
   </si>
   <si>
-    <t>0bdfd4b</t>
+    <t>e40a5d4</t>
   </si>
   <si>
     <t>Total</t>
@@ -2228,7 +2228,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -2239,13 +2239,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D18" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -2415,7 +2415,7 @@
         <v>6</v>
       </c>
       <c r="D28" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -2568,7 +2568,7 @@
         <v>6</v>
       </c>
       <c r="D37" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -2738,7 +2738,7 @@
         <v>6</v>
       </c>
       <c r="D47" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -2755,7 +2755,7 @@
         <v>6</v>
       </c>
       <c r="D48" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -2942,7 +2942,7 @@
         <v>6</v>
       </c>
       <c r="D59" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
@@ -2959,7 +2959,7 @@
         <v>6</v>
       </c>
       <c r="D60" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
@@ -3146,7 +3146,7 @@
         <v>6</v>
       </c>
       <c r="D71" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>6</v>
       </c>
       <c r="D82" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
@@ -3673,7 +3673,7 @@
         <v>6</v>
       </c>
       <c r="D102" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E102" t="s">
         <v>8</v>
@@ -3826,7 +3826,7 @@
         <v>6</v>
       </c>
       <c r="D111" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="E111" t="s">
         <v>8</v>
@@ -3996,7 +3996,7 @@
         <v>6</v>
       </c>
       <c r="D121" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E121" t="s">
         <v>8</v>
@@ -4183,7 +4183,7 @@
         <v>6</v>
       </c>
       <c r="D132" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="E132" t="s">
         <v>8</v>
@@ -4846,7 +4846,7 @@
         <v>6</v>
       </c>
       <c r="D171" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="E171" t="s">
         <v>8</v>
@@ -5135,7 +5135,7 @@
         <v>6</v>
       </c>
       <c r="D188" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E188" t="s">
         <v>8</v>
@@ -5146,13 +5146,13 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D189" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E189" t="s">
         <v>8</v>
@@ -5163,13 +5163,13 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D190" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E190" t="s">
         <v>8</v>
@@ -5180,13 +5180,13 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D191" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E191" t="s">
         <v>8</v>
@@ -5197,13 +5197,13 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D192" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E192" t="s">
         <v>8</v>
@@ -5214,13 +5214,13 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D193" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E193" t="s">
         <v>8</v>
@@ -5231,13 +5231,13 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D194" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E194" t="s">
         <v>8</v>
@@ -5248,13 +5248,13 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D195" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="E195" t="s">
         <v>8</v>
@@ -5265,13 +5265,13 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D196" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E196" t="s">
         <v>8</v>
@@ -5282,13 +5282,13 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D197" t="s">
-        <v>218</v>
+        <v>192</v>
       </c>
       <c r="E197" t="s">
         <v>8</v>
@@ -5299,13 +5299,13 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D198" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E198" t="s">
         <v>8</v>
@@ -5316,13 +5316,13 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D199" t="s">
-        <v>192</v>
+        <v>223</v>
       </c>
       <c r="E199" t="s">
         <v>8</v>
@@ -5333,13 +5333,13 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D200" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E200" t="s">
         <v>8</v>
@@ -5350,13 +5350,13 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D201" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E201" t="s">
         <v>8</v>
@@ -5367,13 +5367,13 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D202" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E202" t="s">
         <v>8</v>
@@ -5384,13 +5384,13 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D203" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="E203" t="s">
         <v>8</v>
@@ -5401,13 +5401,13 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D204" t="s">
-        <v>229</v>
+        <v>204</v>
       </c>
       <c r="E204" t="s">
         <v>8</v>
@@ -5418,13 +5418,13 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D205" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E205" t="s">
         <v>8</v>
@@ -5435,13 +5435,13 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D206" t="s">
-        <v>192</v>
+        <v>234</v>
       </c>
       <c r="E206" t="s">
         <v>8</v>
@@ -5452,13 +5452,13 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D207" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E207" t="s">
         <v>8</v>
@@ -5469,13 +5469,13 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D208" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E208" t="s">
         <v>8</v>
@@ -5486,13 +5486,13 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D209" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E209" t="s">
         <v>8</v>
@@ -5503,13 +5503,13 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D210" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E210" t="s">
         <v>8</v>
@@ -5520,13 +5520,13 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D211" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E211" t="s">
         <v>8</v>
@@ -5537,13 +5537,13 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D212" t="s">
-        <v>244</v>
+        <v>206</v>
       </c>
       <c r="E212" t="s">
         <v>8</v>
@@ -5554,13 +5554,13 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D213" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E213" t="s">
         <v>8</v>
@@ -5571,13 +5571,13 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D214" t="s">
-        <v>205</v>
+        <v>249</v>
       </c>
       <c r="E214" t="s">
         <v>8</v>
@@ -5588,13 +5588,13 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D215" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E215" t="s">
         <v>8</v>
@@ -5605,13 +5605,13 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D216" t="s">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="E216" t="s">
         <v>8</v>
@@ -5622,13 +5622,13 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D217" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E217" t="s">
         <v>8</v>
@@ -5639,13 +5639,13 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D218" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E218" t="s">
         <v>8</v>
@@ -5656,13 +5656,13 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D219" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E219" t="s">
         <v>8</v>
@@ -5673,13 +5673,13 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D220" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E220" t="s">
         <v>8</v>
@@ -5690,13 +5690,13 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D221" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E221" t="s">
         <v>8</v>
@@ -5707,13 +5707,13 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D222" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E222" t="s">
         <v>8</v>
@@ -5724,13 +5724,13 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D223" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="E223" t="s">
         <v>8</v>
@@ -5764,7 +5764,7 @@
         <v>6</v>
       </c>
       <c r="D225" t="s">
-        <v>269</v>
+        <v>194</v>
       </c>
       <c r="E225" t="s">
         <v>8</v>
@@ -5775,13 +5775,13 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D226" t="s">
-        <v>271</v>
+        <v>244</v>
       </c>
       <c r="E226" t="s">
         <v>8</v>
@@ -5792,13 +5792,13 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D227" t="s">
-        <v>263</v>
+        <v>234</v>
       </c>
       <c r="E227" t="s">
         <v>8</v>
@@ -5809,13 +5809,13 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D228" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E228" t="s">
         <v>8</v>
@@ -5826,13 +5826,13 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D229" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E229" t="s">
         <v>8</v>
@@ -5843,13 +5843,13 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D230" t="s">
-        <v>269</v>
+        <v>218</v>
       </c>
       <c r="E230" t="s">
         <v>8</v>
@@ -5860,13 +5860,13 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D231" t="s">
-        <v>279</v>
+        <v>223</v>
       </c>
       <c r="E231" t="s">
         <v>8</v>
@@ -5877,13 +5877,13 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D232" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="E232" t="s">
         <v>8</v>
@@ -5894,13 +5894,13 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D233" t="s">
-        <v>231</v>
+        <v>280</v>
       </c>
       <c r="E233" t="s">
         <v>8</v>
@@ -5911,13 +5911,13 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
+        <v>281</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D234" t="s">
         <v>282</v>
-      </c>
-      <c r="C234" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D234" t="s">
-        <v>196</v>
       </c>
       <c r="E234" t="s">
         <v>8</v>
@@ -5951,7 +5951,7 @@
         <v>6</v>
       </c>
       <c r="D236" t="s">
-        <v>226</v>
+        <v>286</v>
       </c>
       <c r="E236" t="s">
         <v>8</v>
@@ -5962,13 +5962,13 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D237" t="s">
-        <v>287</v>
+        <v>200</v>
       </c>
       <c r="E237" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>6</v>
       </c>
       <c r="D238" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="E238" t="s">
         <v>8</v>
@@ -5996,13 +5996,13 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D239" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="E239" t="s">
         <v>8</v>
@@ -6019,7 +6019,7 @@
         <v>6</v>
       </c>
       <c r="D240" t="s">
-        <v>292</v>
+        <v>206</v>
       </c>
       <c r="E240" t="s">
         <v>8</v>
@@ -6030,13 +6030,13 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D241" t="s">
-        <v>294</v>
+        <v>216</v>
       </c>
       <c r="E241" t="s">
         <v>8</v>
@@ -6047,13 +6047,13 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D242" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E242" t="s">
         <v>8</v>
@@ -6064,13 +6064,13 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D243" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E243" t="s">
         <v>8</v>
@@ -6081,13 +6081,13 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D244" t="s">
-        <v>192</v>
+        <v>298</v>
       </c>
       <c r="E244" t="s">
         <v>8</v>
@@ -6098,13 +6098,13 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
+        <v>299</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D245" t="s">
         <v>300</v>
-      </c>
-      <c r="C245" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D245" t="s">
-        <v>290</v>
       </c>
       <c r="E245" t="s">
         <v>8</v>
@@ -6121,7 +6121,7 @@
         <v>6</v>
       </c>
       <c r="D246" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="E246" t="s">
         <v>8</v>
@@ -6138,7 +6138,7 @@
         <v>6</v>
       </c>
       <c r="D247" t="s">
-        <v>303</v>
+        <v>208</v>
       </c>
       <c r="E247" t="s">
         <v>8</v>
@@ -6149,13 +6149,13 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
+        <v>303</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D248" t="s">
         <v>304</v>
-      </c>
-      <c r="C248" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D248" t="s">
-        <v>305</v>
       </c>
       <c r="E248" t="s">
         <v>8</v>
@@ -6166,13 +6166,13 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
+        <v>305</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D249" t="s">
         <v>306</v>
-      </c>
-      <c r="C249" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D249" t="s">
-        <v>307</v>
       </c>
       <c r="E249" t="s">
         <v>8</v>
@@ -6183,13 +6183,13 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D250" t="s">
-        <v>309</v>
+        <v>228</v>
       </c>
       <c r="E250" t="s">
         <v>8</v>
@@ -6200,13 +6200,13 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D251" t="s">
-        <v>290</v>
+        <v>309</v>
       </c>
       <c r="E251" t="s">
         <v>8</v>
@@ -6217,13 +6217,13 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D252" t="s">
-        <v>255</v>
+        <v>232</v>
       </c>
       <c r="E252" t="s">
         <v>8</v>
@@ -6234,13 +6234,13 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D253" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="E253" t="s">
         <v>8</v>
@@ -6251,13 +6251,13 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D254" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E254" t="s">
         <v>8</v>
@@ -6268,13 +6268,13 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D255" t="s">
-        <v>211</v>
+        <v>315</v>
       </c>
       <c r="E255" t="s">
         <v>8</v>
@@ -6285,13 +6285,13 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
+        <v>316</v>
+      </c>
+      <c r="C256" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D256" t="s">
         <v>317</v>
-      </c>
-      <c r="C256" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D256" t="s">
-        <v>271</v>
       </c>
       <c r="E256" t="s">
         <v>8</v>
@@ -6325,7 +6325,7 @@
         <v>6</v>
       </c>
       <c r="D258" t="s">
-        <v>287</v>
+        <v>202</v>
       </c>
       <c r="E258" t="s">
         <v>8</v>
@@ -6342,7 +6342,7 @@
         <v>6</v>
       </c>
       <c r="D259" t="s">
-        <v>207</v>
+        <v>322</v>
       </c>
       <c r="E259" t="s">
         <v>8</v>
@@ -6353,13 +6353,13 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D260" t="s">
-        <v>323</v>
+        <v>238</v>
       </c>
       <c r="E260" t="s">
         <v>8</v>
@@ -6376,7 +6376,7 @@
         <v>6</v>
       </c>
       <c r="D261" t="s">
-        <v>240</v>
+        <v>325</v>
       </c>
       <c r="E261" t="s">
         <v>8</v>
@@ -6387,13 +6387,13 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D262" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="E262" t="s">
         <v>8</v>
@@ -6404,13 +6404,13 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D263" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E263" t="s">
         <v>8</v>
@@ -6421,13 +6421,13 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D264" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="E264" t="s">
         <v>8</v>
@@ -6438,13 +6438,13 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D265" t="s">
-        <v>244</v>
+        <v>200</v>
       </c>
       <c r="E265" t="s">
         <v>8</v>
@@ -6455,13 +6455,13 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D266" t="s">
-        <v>220</v>
+        <v>332</v>
       </c>
       <c r="E266" t="s">
         <v>8</v>
@@ -6472,13 +6472,13 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D267" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E267" t="s">
         <v>8</v>
@@ -6489,13 +6489,13 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D268" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E268" t="s">
         <v>8</v>
@@ -6506,13 +6506,13 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D269" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="E269" t="s">
         <v>8</v>
@@ -6523,13 +6523,13 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D270" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E270" t="s">
         <v>8</v>
@@ -6540,13 +6540,13 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D271" t="s">
-        <v>331</v>
+        <v>284</v>
       </c>
       <c r="E271" t="s">
         <v>8</v>
@@ -6557,13 +6557,13 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D272" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="E272" t="s">
         <v>8</v>
@@ -6574,13 +6574,13 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D273" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E273" t="s">
         <v>8</v>
@@ -6591,13 +6591,13 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D274" t="s">
-        <v>246</v>
+        <v>345</v>
       </c>
       <c r="E274" t="s">
         <v>8</v>
@@ -6608,13 +6608,13 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D275" t="s">
-        <v>343</v>
+        <v>216</v>
       </c>
       <c r="E275" t="s">
         <v>8</v>
@@ -6625,13 +6625,13 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D276" t="s">
-        <v>209</v>
+        <v>278</v>
       </c>
       <c r="E276" t="s">
         <v>8</v>
@@ -6642,13 +6642,13 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D277" t="s">
-        <v>346</v>
+        <v>198</v>
       </c>
       <c r="E277" t="s">
         <v>8</v>
@@ -6659,13 +6659,13 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D278" t="s">
-        <v>194</v>
+        <v>350</v>
       </c>
       <c r="E278" t="s">
         <v>8</v>
@@ -6676,13 +6676,13 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D279" t="s">
-        <v>349</v>
+        <v>232</v>
       </c>
       <c r="E279" t="s">
         <v>8</v>
@@ -6693,13 +6693,13 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D280" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E280" t="s">
         <v>8</v>
@@ -6710,13 +6710,13 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D281" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="E281" t="s">
         <v>8</v>
@@ -6727,13 +6727,13 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D282" t="s">
-        <v>354</v>
+        <v>286</v>
       </c>
       <c r="E282" t="s">
         <v>8</v>
@@ -6744,13 +6744,13 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D283" t="s">
-        <v>356</v>
+        <v>327</v>
       </c>
       <c r="E283" t="s">
         <v>8</v>
@@ -6761,13 +6761,13 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D284" t="s">
-        <v>358</v>
+        <v>196</v>
       </c>
       <c r="E284" t="s">
         <v>8</v>
@@ -6784,7 +6784,7 @@
         <v>6</v>
       </c>
       <c r="D285" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="E285" t="s">
         <v>8</v>
@@ -6801,7 +6801,7 @@
         <v>6</v>
       </c>
       <c r="D286" t="s">
-        <v>346</v>
+        <v>258</v>
       </c>
       <c r="E286" t="s">
         <v>8</v>
@@ -6818,7 +6818,7 @@
         <v>6</v>
       </c>
       <c r="D287" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="E287" t="s">
         <v>8</v>
@@ -6835,7 +6835,7 @@
         <v>6</v>
       </c>
       <c r="D288" t="s">
-        <v>190</v>
+        <v>363</v>
       </c>
       <c r="E288" t="s">
         <v>8</v>
@@ -6846,13 +6846,13 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D289" t="s">
-        <v>242</v>
+        <v>296</v>
       </c>
       <c r="E289" t="s">
         <v>8</v>
@@ -6863,13 +6863,13 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D290" t="s">
-        <v>284</v>
+        <v>244</v>
       </c>
       <c r="E290" t="s">
         <v>8</v>
@@ -6880,13 +6880,13 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D291" t="s">
-        <v>261</v>
+        <v>367</v>
       </c>
       <c r="E291" t="s">
         <v>8</v>
@@ -6897,13 +6897,13 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D292" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="E292" t="s">
         <v>8</v>
@@ -6914,13 +6914,13 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D293" t="s">
-        <v>231</v>
+        <v>306</v>
       </c>
       <c r="E293" t="s">
         <v>8</v>
@@ -6931,13 +6931,13 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D294" t="s">
-        <v>369</v>
+        <v>244</v>
       </c>
       <c r="E294" t="s">
         <v>8</v>
@@ -6948,13 +6948,13 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D295" t="s">
-        <v>205</v>
+        <v>325</v>
       </c>
       <c r="E295" t="s">
         <v>8</v>
@@ -6965,13 +6965,13 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D296" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E296" t="s">
         <v>8</v>
@@ -6982,13 +6982,13 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D297" t="s">
-        <v>374</v>
+        <v>315</v>
       </c>
       <c r="E297" t="s">
         <v>8</v>
@@ -7005,7 +7005,7 @@
         <v>6</v>
       </c>
       <c r="D298" t="s">
-        <v>376</v>
+        <v>306</v>
       </c>
       <c r="E298" t="s">
         <v>8</v>
@@ -7016,13 +7016,13 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
+        <v>376</v>
+      </c>
+      <c r="C299" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D299" t="s">
         <v>377</v>
-      </c>
-      <c r="C299" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D299" t="s">
-        <v>343</v>
       </c>
       <c r="E299" t="s">
         <v>8</v>
@@ -7056,7 +7056,7 @@
         <v>6</v>
       </c>
       <c r="D301" t="s">
-        <v>381</v>
+        <v>278</v>
       </c>
       <c r="E301" t="s">
         <v>8</v>
@@ -7067,13 +7067,13 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
+        <v>381</v>
+      </c>
+      <c r="C302" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D302" t="s">
         <v>382</v>
-      </c>
-      <c r="C302" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D302" t="s">
-        <v>383</v>
       </c>
       <c r="E302" t="s">
         <v>8</v>
@@ -7084,13 +7084,13 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D303" t="s">
-        <v>251</v>
+        <v>223</v>
       </c>
       <c r="E303" t="s">
         <v>8</v>
@@ -7101,13 +7101,13 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D304" t="s">
-        <v>386</v>
+        <v>284</v>
       </c>
       <c r="E304" t="s">
         <v>8</v>
@@ -7118,13 +7118,13 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D305" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="E305" t="s">
         <v>8</v>
@@ -7135,13 +7135,13 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D306" t="s">
-        <v>209</v>
+        <v>336</v>
       </c>
       <c r="E306" t="s">
         <v>8</v>
@@ -7152,13 +7152,13 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D307" t="s">
-        <v>390</v>
+        <v>282</v>
       </c>
       <c r="E307" t="s">
         <v>8</v>
@@ -7169,13 +7169,13 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D308" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="E308" t="s">
         <v>8</v>
@@ -7186,13 +7186,13 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D309" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="E309" t="s">
         <v>8</v>
@@ -7203,13 +7203,13 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D310" t="s">
-        <v>395</v>
+        <v>298</v>
       </c>
       <c r="E310" t="s">
         <v>8</v>
@@ -7220,13 +7220,13 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D311" t="s">
-        <v>323</v>
+        <v>247</v>
       </c>
       <c r="E311" t="s">
         <v>8</v>
@@ -7237,13 +7237,13 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D312" t="s">
-        <v>398</v>
+        <v>289</v>
       </c>
       <c r="E312" t="s">
         <v>8</v>
@@ -7254,13 +7254,13 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D313" t="s">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="E313" t="s">
         <v>8</v>
@@ -7271,13 +7271,13 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D314" t="s">
-        <v>296</v>
+        <v>396</v>
       </c>
       <c r="E314" t="s">
         <v>8</v>
@@ -7288,13 +7288,13 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D315" t="s">
-        <v>383</v>
+        <v>223</v>
       </c>
       <c r="E315" t="s">
         <v>8</v>
@@ -7305,13 +7305,13 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D316" t="s">
-        <v>392</v>
+        <v>247</v>
       </c>
       <c r="E316" t="s">
         <v>8</v>
@@ -7322,13 +7322,13 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D317" t="s">
-        <v>198</v>
+        <v>400</v>
       </c>
       <c r="E317" t="s">
         <v>8</v>
@@ -7339,13 +7339,13 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D318" t="s">
-        <v>305</v>
+        <v>350</v>
       </c>
       <c r="E318" t="s">
         <v>8</v>
@@ -7356,13 +7356,13 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D319" t="s">
-        <v>406</v>
+        <v>382</v>
       </c>
       <c r="E319" t="s">
         <v>8</v>
@@ -7373,13 +7373,13 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D320" t="s">
-        <v>209</v>
+        <v>404</v>
       </c>
       <c r="E320" t="s">
         <v>8</v>
@@ -7390,13 +7390,13 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D321" t="s">
-        <v>229</v>
+        <v>284</v>
       </c>
       <c r="E321" t="s">
         <v>8</v>
@@ -7407,13 +7407,13 @@
         <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D322" t="s">
-        <v>303</v>
+        <v>379</v>
       </c>
       <c r="E322" t="s">
         <v>8</v>
@@ -7424,13 +7424,13 @@
         <v>322</v>
       </c>
       <c r="B323" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D323" t="s">
-        <v>246</v>
+        <v>408</v>
       </c>
       <c r="E323" t="s">
         <v>8</v>
@@ -7441,13 +7441,13 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D324" t="s">
-        <v>358</v>
+        <v>304</v>
       </c>
       <c r="E324" t="s">
         <v>8</v>
@@ -7458,13 +7458,13 @@
         <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D325" t="s">
-        <v>220</v>
+        <v>315</v>
       </c>
       <c r="E325" t="s">
         <v>8</v>
@@ -7475,13 +7475,13 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D326" t="s">
-        <v>414</v>
+        <v>322</v>
       </c>
       <c r="E326" t="s">
         <v>8</v>
@@ -7492,13 +7492,13 @@
         <v>326</v>
       </c>
       <c r="B327" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D327" t="s">
-        <v>349</v>
+        <v>240</v>
       </c>
       <c r="E327" t="s">
         <v>8</v>
@@ -7509,13 +7509,13 @@
         <v>327</v>
       </c>
       <c r="B328" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D328" t="s">
-        <v>269</v>
+        <v>414</v>
       </c>
       <c r="E328" t="s">
         <v>8</v>
@@ -7526,13 +7526,13 @@
         <v>328</v>
       </c>
       <c r="B329" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D329" t="s">
-        <v>249</v>
+        <v>317</v>
       </c>
       <c r="E329" t="s">
         <v>8</v>
@@ -7543,13 +7543,13 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D330" t="s">
-        <v>351</v>
+        <v>196</v>
       </c>
       <c r="E330" t="s">
         <v>8</v>
@@ -7560,13 +7560,13 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D331" t="s">
-        <v>414</v>
+        <v>272</v>
       </c>
       <c r="E331" t="s">
         <v>8</v>
@@ -7577,13 +7577,13 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D332" t="s">
-        <v>213</v>
+        <v>319</v>
       </c>
       <c r="E332" t="s">
         <v>8</v>
@@ -7594,13 +7594,13 @@
         <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D333" t="s">
-        <v>395</v>
+        <v>313</v>
       </c>
       <c r="E333" t="s">
         <v>8</v>
@@ -7611,13 +7611,13 @@
         <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D334" t="s">
-        <v>192</v>
+        <v>306</v>
       </c>
       <c r="E334" t="s">
         <v>8</v>
@@ -7628,13 +7628,13 @@
         <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D335" t="s">
-        <v>218</v>
+        <v>422</v>
       </c>
       <c r="E335" t="s">
         <v>8</v>
@@ -7645,13 +7645,13 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D336" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
       <c r="E336" t="s">
         <v>8</v>
@@ -7662,13 +7662,13 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D337" t="s">
-        <v>305</v>
+        <v>377</v>
       </c>
       <c r="E337" t="s">
         <v>8</v>
@@ -7679,13 +7679,13 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D338" t="s">
-        <v>356</v>
+        <v>379</v>
       </c>
       <c r="E338" t="s">
         <v>8</v>
@@ -7696,13 +7696,13 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D339" t="s">
-        <v>428</v>
+        <v>272</v>
       </c>
       <c r="E339" t="s">
         <v>8</v>
@@ -7713,13 +7713,13 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D340" t="s">
-        <v>392</v>
+        <v>355</v>
       </c>
       <c r="E340" t="s">
         <v>8</v>
@@ -7730,13 +7730,13 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D341" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="E341" t="s">
         <v>8</v>
@@ -7747,13 +7747,13 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D342" t="s">
-        <v>354</v>
+        <v>225</v>
       </c>
       <c r="E342" t="s">
         <v>8</v>
@@ -7764,13 +7764,13 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D343" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="E343" t="s">
         <v>8</v>
@@ -7781,13 +7781,13 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D344" t="s">
-        <v>231</v>
+        <v>353</v>
       </c>
       <c r="E344" t="s">
         <v>8</v>
@@ -7798,13 +7798,13 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D345" t="s">
-        <v>305</v>
+        <v>208</v>
       </c>
       <c r="E345" t="s">
         <v>8</v>
@@ -7815,13 +7815,13 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D346" t="s">
-        <v>296</v>
+        <v>434</v>
       </c>
       <c r="E346" t="s">
         <v>8</v>
@@ -7832,13 +7832,13 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D347" t="s">
-        <v>253</v>
+        <v>300</v>
       </c>
       <c r="E347" t="s">
         <v>8</v>
@@ -7849,13 +7849,13 @@
         <v>347</v>
       </c>
       <c r="B348" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D348" t="s">
-        <v>438</v>
+        <v>317</v>
       </c>
       <c r="E348" t="s">
         <v>8</v>
@@ -7866,13 +7866,13 @@
         <v>348</v>
       </c>
       <c r="B349" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D349" t="s">
-        <v>284</v>
+        <v>210</v>
       </c>
       <c r="E349" t="s">
         <v>8</v>
@@ -7883,13 +7883,13 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D350" t="s">
-        <v>196</v>
+        <v>334</v>
       </c>
       <c r="E350" t="s">
         <v>8</v>
@@ -7900,13 +7900,13 @@
         <v>350</v>
       </c>
       <c r="B351" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D351" t="s">
-        <v>358</v>
+        <v>204</v>
       </c>
       <c r="E351" t="s">
         <v>8</v>
@@ -7917,13 +7917,13 @@
         <v>351</v>
       </c>
       <c r="B352" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D352" t="s">
-        <v>296</v>
+        <v>434</v>
       </c>
       <c r="E352" t="s">
         <v>8</v>
@@ -7934,13 +7934,13 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D353" t="s">
-        <v>216</v>
+        <v>373</v>
       </c>
       <c r="E353" t="s">
         <v>8</v>
@@ -7951,13 +7951,13 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D354" t="s">
-        <v>331</v>
+        <v>221</v>
       </c>
       <c r="E354" t="s">
         <v>8</v>
@@ -7968,13 +7968,13 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D355" t="s">
-        <v>349</v>
+        <v>444</v>
       </c>
       <c r="E355" t="s">
         <v>8</v>
@@ -7985,13 +7985,13 @@
         <v>355</v>
       </c>
       <c r="B356" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D356" t="s">
-        <v>369</v>
+        <v>196</v>
       </c>
       <c r="E356" t="s">
         <v>8</v>
@@ -8002,13 +8002,13 @@
         <v>356</v>
       </c>
       <c r="B357" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D357" t="s">
-        <v>238</v>
+        <v>345</v>
       </c>
       <c r="E357" t="s">
         <v>8</v>
@@ -8019,13 +8019,13 @@
         <v>357</v>
       </c>
       <c r="B358" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D358" t="s">
-        <v>449</v>
+        <v>294</v>
       </c>
       <c r="E358" t="s">
         <v>8</v>
@@ -8036,13 +8036,13 @@
         <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D359" t="s">
-        <v>451</v>
+        <v>334</v>
       </c>
       <c r="E359" t="s">
         <v>8</v>
@@ -8053,13 +8053,13 @@
         <v>359</v>
       </c>
       <c r="B360" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D360" t="s">
-        <v>269</v>
+        <v>194</v>
       </c>
       <c r="E360" t="s">
         <v>8</v>
@@ -8070,13 +8070,13 @@
         <v>360</v>
       </c>
       <c r="B361" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D361" t="s">
-        <v>216</v>
+        <v>451</v>
       </c>
       <c r="E361" t="s">
         <v>8</v>
@@ -8087,13 +8087,13 @@
         <v>361</v>
       </c>
       <c r="B362" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D362" t="s">
-        <v>383</v>
+        <v>286</v>
       </c>
       <c r="E362" t="s">
         <v>8</v>
@@ -8104,13 +8104,13 @@
         <v>362</v>
       </c>
       <c r="B363" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D363" t="s">
-        <v>336</v>
+        <v>251</v>
       </c>
       <c r="E363" t="s">
         <v>8</v>
@@ -8121,13 +8121,13 @@
         <v>363</v>
       </c>
       <c r="B364" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D364" t="s">
-        <v>457</v>
+        <v>317</v>
       </c>
       <c r="E364" t="s">
         <v>8</v>
@@ -8138,13 +8138,13 @@
         <v>364</v>
       </c>
       <c r="B365" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D365" t="s">
-        <v>238</v>
+        <v>313</v>
       </c>
       <c r="E365" t="s">
         <v>8</v>
@@ -8155,13 +8155,13 @@
         <v>365</v>
       </c>
       <c r="B366" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D366" t="s">
-        <v>246</v>
+        <v>204</v>
       </c>
       <c r="E366" t="s">
         <v>8</v>
@@ -8172,13 +8172,13 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D367" t="s">
-        <v>292</v>
+        <v>192</v>
       </c>
       <c r="E367" t="s">
         <v>8</v>
@@ -8189,13 +8189,13 @@
         <v>367</v>
       </c>
       <c r="B368" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D368" t="s">
-        <v>303</v>
+        <v>238</v>
       </c>
       <c r="E368" t="s">
         <v>8</v>
@@ -8206,13 +8206,13 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D369" t="s">
-        <v>392</v>
+        <v>350</v>
       </c>
       <c r="E369" t="s">
         <v>8</v>
@@ -8223,13 +8223,13 @@
         <v>369</v>
       </c>
       <c r="B370" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D370" t="s">
-        <v>265</v>
+        <v>404</v>
       </c>
       <c r="E370" t="s">
         <v>8</v>
@@ -8240,13 +8240,13 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D371" t="s">
-        <v>374</v>
+        <v>225</v>
       </c>
       <c r="E371" t="s">
         <v>8</v>
@@ -8257,13 +8257,13 @@
         <v>371</v>
       </c>
       <c r="B372" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D372" t="s">
-        <v>207</v>
+        <v>463</v>
       </c>
       <c r="E372" t="s">
         <v>8</v>
@@ -8274,13 +8274,13 @@
         <v>372</v>
       </c>
       <c r="B373" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D373" t="s">
-        <v>296</v>
+        <v>451</v>
       </c>
       <c r="E373" t="s">
         <v>8</v>
@@ -8291,13 +8291,13 @@
         <v>373</v>
       </c>
       <c r="B374" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D374" t="s">
-        <v>305</v>
+        <v>466</v>
       </c>
       <c r="E374" t="s">
         <v>8</v>
@@ -8308,13 +8308,13 @@
         <v>374</v>
       </c>
       <c r="B375" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D375" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="E375" t="s">
         <v>8</v>
@@ -8325,13 +8325,13 @@
         <v>375</v>
       </c>
       <c r="B376" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D376" t="s">
-        <v>381</v>
+        <v>298</v>
       </c>
       <c r="E376" t="s">
         <v>8</v>
@@ -8342,13 +8342,13 @@
         <v>376</v>
       </c>
       <c r="B377" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D377" t="s">
-        <v>303</v>
+        <v>284</v>
       </c>
       <c r="E377" t="s">
         <v>8</v>
@@ -8359,13 +8359,13 @@
         <v>377</v>
       </c>
       <c r="B378" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D378" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E378" t="s">
         <v>8</v>
@@ -8376,13 +8376,13 @@
         <v>378</v>
       </c>
       <c r="B379" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D379" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="E379" t="s">
         <v>8</v>
@@ -8393,13 +8393,13 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D380" t="s">
-        <v>192</v>
+        <v>332</v>
       </c>
       <c r="E380" t="s">
         <v>8</v>
@@ -8410,13 +8410,13 @@
         <v>380</v>
       </c>
       <c r="B381" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D381" t="s">
-        <v>294</v>
+        <v>190</v>
       </c>
       <c r="E381" t="s">
         <v>8</v>
@@ -8427,13 +8427,13 @@
         <v>381</v>
       </c>
       <c r="B382" t="s">
+        <v>474</v>
+      </c>
+      <c r="C382" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D382" t="s">
         <v>475</v>
-      </c>
-      <c r="C382" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D382" t="s">
-        <v>190</v>
       </c>
       <c r="E382" t="s">
         <v>8</v>
@@ -8450,7 +8450,7 @@
         <v>6</v>
       </c>
       <c r="D383" t="s">
-        <v>319</v>
+        <v>363</v>
       </c>
       <c r="E383" t="s">
         <v>8</v>
@@ -8467,7 +8467,7 @@
         <v>6</v>
       </c>
       <c r="D384" t="s">
-        <v>383</v>
+        <v>327</v>
       </c>
       <c r="E384" t="s">
         <v>8</v>
@@ -8484,7 +8484,7 @@
         <v>6</v>
       </c>
       <c r="D385" t="s">
-        <v>276</v>
+        <v>377</v>
       </c>
       <c r="E385" t="s">
         <v>8</v>
@@ -8501,7 +8501,7 @@
         <v>6</v>
       </c>
       <c r="D386" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="E386" t="s">
         <v>8</v>
@@ -8518,7 +8518,7 @@
         <v>6</v>
       </c>
       <c r="D387" t="s">
-        <v>315</v>
+        <v>350</v>
       </c>
       <c r="E387" t="s">
         <v>8</v>
@@ -8535,7 +8535,7 @@
         <v>6</v>
       </c>
       <c r="D388" t="s">
-        <v>374</v>
+        <v>309</v>
       </c>
       <c r="E388" t="s">
         <v>8</v>
@@ -8552,7 +8552,7 @@
         <v>6</v>
       </c>
       <c r="D389" t="s">
-        <v>483</v>
+        <v>315</v>
       </c>
       <c r="E389" t="s">
         <v>8</v>
@@ -8563,13 +8563,13 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D390" t="s">
-        <v>398</v>
+        <v>309</v>
       </c>
       <c r="E390" t="s">
         <v>8</v>
@@ -8580,13 +8580,13 @@
         <v>390</v>
       </c>
       <c r="B391" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D391" t="s">
-        <v>287</v>
+        <v>451</v>
       </c>
       <c r="E391" t="s">
         <v>8</v>
@@ -8597,13 +8597,13 @@
         <v>391</v>
       </c>
       <c r="B392" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D392" t="s">
-        <v>487</v>
+        <v>210</v>
       </c>
       <c r="E392" t="s">
         <v>8</v>
@@ -8614,13 +8614,13 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D393" t="s">
-        <v>209</v>
+        <v>274</v>
       </c>
       <c r="E393" t="s">
         <v>8</v>
@@ -8631,13 +8631,13 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D394" t="s">
-        <v>483</v>
+        <v>286</v>
       </c>
       <c r="E394" t="s">
         <v>8</v>
@@ -8648,13 +8648,13 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D395" t="s">
-        <v>491</v>
+        <v>274</v>
       </c>
       <c r="E395" t="s">
         <v>8</v>
@@ -8665,13 +8665,13 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D396" t="s">
-        <v>234</v>
+        <v>490</v>
       </c>
       <c r="E396" t="s">
         <v>8</v>
@@ -8682,13 +8682,13 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D397" t="s">
-        <v>358</v>
+        <v>492</v>
       </c>
       <c r="E397" t="s">
         <v>8</v>
@@ -8699,13 +8699,13 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D398" t="s">
-        <v>265</v>
+        <v>218</v>
       </c>
       <c r="E398" t="s">
         <v>8</v>
@@ -8716,13 +8716,13 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
+        <v>494</v>
+      </c>
+      <c r="C399" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D399" t="s">
         <v>495</v>
-      </c>
-      <c r="C399" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D399" t="s">
-        <v>414</v>
       </c>
       <c r="E399" t="s">
         <v>8</v>
@@ -8739,7 +8739,7 @@
         <v>6</v>
       </c>
       <c r="D400" t="s">
-        <v>251</v>
+        <v>404</v>
       </c>
       <c r="E400" t="s">
         <v>8</v>
@@ -8756,7 +8756,7 @@
         <v>6</v>
       </c>
       <c r="D401" t="s">
-        <v>438</v>
+        <v>190</v>
       </c>
       <c r="E401" t="s">
         <v>8</v>

--- a/reports/backend/Excel/Automation_Test_Report.xlsx
+++ b/reports/backend/Excel/Automation_Test_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="517">
   <si>
     <t>#</t>
   </si>
@@ -59,6 +59,9 @@
     <t>Smart Admission Backend — Authentication Tests BT-007 | Firebase config projectId matches authDomain prefix</t>
   </si>
   <si>
+    <t>0.001</t>
+  </si>
+  <si>
     <t>Smart Admission Backend — Authentication Tests BT-008 | Firebase config has all 6 required fields</t>
   </si>
   <si>
@@ -86,9 +89,6 @@
     <t>Smart Admission Backend — Authentication Tests BT-016 | Institutional email domain (.edu/.ac/.sse) is valid</t>
   </si>
   <si>
-    <t>0.001</t>
-  </si>
-  <si>
     <t>Smart Admission Backend — Authentication Tests BT-017 | Email with spaces fails validation</t>
   </si>
   <si>
@@ -584,924 +584,933 @@
     <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #180</t>
   </si>
   <si>
+    <t>0.040</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #181</t>
+  </si>
+  <si>
+    <t>0.105</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #182</t>
+  </si>
+  <si>
+    <t>0.109</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #183</t>
+  </si>
+  <si>
+    <t>0.046</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #184</t>
+  </si>
+  <si>
+    <t>0.035</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #185</t>
+  </si>
+  <si>
+    <t>0.022</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #186</t>
+  </si>
+  <si>
+    <t>0.020</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #187</t>
+  </si>
+  <si>
+    <t>0.088</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #188</t>
+  </si>
+  <si>
+    <t>0.052</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #189</t>
+  </si>
+  <si>
+    <t>0.043</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #190</t>
+  </si>
+  <si>
+    <t>0.111</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #191</t>
+  </si>
+  <si>
+    <t>0.113</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #192</t>
+  </si>
+  <si>
+    <t>0.060</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #193</t>
+  </si>
+  <si>
+    <t>0.090</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #194</t>
+  </si>
+  <si>
+    <t>0.030</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #195</t>
+  </si>
+  <si>
+    <t>0.024</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #196</t>
+  </si>
+  <si>
+    <t>0.083</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #197</t>
+  </si>
+  <si>
+    <t>0.033</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #198</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #199</t>
+  </si>
+  <si>
+    <t>0.107</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #200</t>
+  </si>
+  <si>
+    <t>0.050</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #201</t>
+  </si>
+  <si>
+    <t>0.078</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #202</t>
+  </si>
+  <si>
+    <t>0.026</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #203</t>
+  </si>
+  <si>
+    <t>0.063</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #204</t>
+  </si>
+  <si>
+    <t>0.082</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #205</t>
+  </si>
+  <si>
+    <t>0.028</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #206</t>
+  </si>
+  <si>
+    <t>0.054</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #207</t>
+  </si>
+  <si>
+    <t>0.062</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #208</t>
+  </si>
+  <si>
+    <t>0.086</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #209</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #210</t>
+  </si>
+  <si>
+    <t>0.077</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #211</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #212</t>
+  </si>
+  <si>
+    <t>0.106</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #213</t>
+  </si>
+  <si>
+    <t>0.103</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #214</t>
+  </si>
+  <si>
+    <t>0.119</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #215</t>
+  </si>
+  <si>
+    <t>0.023</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #216</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #217</t>
+  </si>
+  <si>
+    <t>0.117</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #218</t>
+  </si>
+  <si>
+    <t>0.104</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #219</t>
+  </si>
+  <si>
+    <t>0.059</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #220</t>
+  </si>
+  <si>
     <t>0.081</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #181</t>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #221</t>
+  </si>
+  <si>
+    <t>0.071</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #222</t>
+  </si>
+  <si>
+    <t>0.079</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #223</t>
+  </si>
+  <si>
+    <t>0.087</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #224</t>
+  </si>
+  <si>
+    <t>0.037</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #225</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #226</t>
+  </si>
+  <si>
+    <t>0.068</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #227</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #228</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #229</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #230</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #231</t>
+  </si>
+  <si>
+    <t>0.118</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #232</t>
+  </si>
+  <si>
+    <t>0.027</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #233</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #234</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #235</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #236</t>
+  </si>
+  <si>
+    <t>0.114</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #237</t>
+  </si>
+  <si>
+    <t>0.045</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #238</t>
+  </si>
+  <si>
+    <t>0.094</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #239</t>
+  </si>
+  <si>
+    <t>0.072</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #240</t>
+  </si>
+  <si>
+    <t>0.096</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #241</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #242</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #243</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #244</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #245</t>
+  </si>
+  <si>
+    <t>0.092</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #246</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #247</t>
+  </si>
+  <si>
+    <t>0.058</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #248</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #249</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #250</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #251</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #252</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #253</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #254</t>
+  </si>
+  <si>
+    <t>0.067</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #255</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #256</t>
+  </si>
+  <si>
+    <t>0.051</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #257</t>
+  </si>
+  <si>
+    <t>0.041</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #258</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #259</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #260</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #261</t>
+  </si>
+  <si>
+    <t>0.075</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #262</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #263</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #264</t>
+  </si>
+  <si>
+    <t>0.066</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #265</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #266</t>
   </si>
   <si>
     <t>0.042</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #182</t>
-  </si>
-  <si>
-    <t>0.055</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #183</t>
-  </si>
-  <si>
-    <t>0.048</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #184</t>
-  </si>
-  <si>
-    <t>0.063</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #185</t>
-  </si>
-  <si>
-    <t>0.118</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #186</t>
-  </si>
-  <si>
-    <t>0.105</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #187</t>
-  </si>
-  <si>
-    <t>0.103</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #188</t>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #267</t>
+  </si>
+  <si>
+    <t>0.065</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #268</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #269</t>
+  </si>
+  <si>
+    <t>0.029</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #270</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #271</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #272</t>
   </si>
   <si>
     <t>0.101</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #189</t>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #273</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #274</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #275</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #276</t>
+  </si>
+  <si>
+    <t>0.031</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #277</t>
+  </si>
+  <si>
+    <t>0.021</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #278</t>
+  </si>
+  <si>
+    <t>0.036</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #279</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #280</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #281</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #282</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #283</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #284</t>
+  </si>
+  <si>
+    <t>0.089</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #285</t>
+  </si>
+  <si>
+    <t>0.038</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #286</t>
+  </si>
+  <si>
+    <t>0.091</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #287</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #288</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #289</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #290</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #291</t>
+  </si>
+  <si>
+    <t>0.080</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #292</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #293</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #294</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #295</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #296</t>
+  </si>
+  <si>
+    <t>0.100</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #297</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #298</t>
+  </si>
+  <si>
+    <t>0.115</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #299</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #300</t>
+  </si>
+  <si>
+    <t>0.032</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #301</t>
+  </si>
+  <si>
+    <t>0.025</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #302</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #303</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #304</t>
+  </si>
+  <si>
+    <t>0.069</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #305</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #306</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #307</t>
+  </si>
+  <si>
+    <t>0.098</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #308</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #309</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #310</t>
+  </si>
+  <si>
+    <t>0.049</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #311</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #312</t>
+  </si>
+  <si>
+    <t>0.039</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #313</t>
   </si>
   <si>
     <t>0.097</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #190</t>
-  </si>
-  <si>
-    <t>0.035</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #191</t>
-  </si>
-  <si>
-    <t>0.083</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #192</t>
-  </si>
-  <si>
-    <t>0.051</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #193</t>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #314</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #315</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #316</t>
+  </si>
+  <si>
+    <t>0.116</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #317</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #318</t>
+  </si>
+  <si>
+    <t>0.070</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #319</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #320</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #321</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #322</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #323</t>
+  </si>
+  <si>
+    <t>0.084</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #324</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #325</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #326</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #327</t>
+  </si>
+  <si>
+    <t>0.073</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #328</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #329</t>
+  </si>
+  <si>
+    <t>0.108</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #330</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #331</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #332</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #333</t>
+  </si>
+  <si>
+    <t>0.102</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #334</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #335</t>
+  </si>
+  <si>
+    <t>0.095</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #336</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #337</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #338</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #339</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #340</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #341</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #342</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #343</t>
+  </si>
+  <si>
+    <t>0.076</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #344</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #345</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #346</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #347</t>
+  </si>
+  <si>
+    <t>0.112</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #348</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #349</t>
+  </si>
+  <si>
+    <t>0.064</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #350</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #351</t>
   </si>
   <si>
     <t>0.053</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #194</t>
-  </si>
-  <si>
-    <t>0.070</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #195</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #196</t>
-  </si>
-  <si>
-    <t>0.104</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #197</t>
-  </si>
-  <si>
-    <t>0.111</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #198</t>
-  </si>
-  <si>
-    <t>0.050</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #199</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #200</t>
-  </si>
-  <si>
-    <t>0.043</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #201</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #202</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #203</t>
-  </si>
-  <si>
-    <t>0.089</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #204</t>
-  </si>
-  <si>
-    <t>0.065</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #205</t>
-  </si>
-  <si>
-    <t>0.113</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #206</t>
-  </si>
-  <si>
-    <t>0.039</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #207</t>
-  </si>
-  <si>
-    <t>0.102</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #208</t>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #352</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #353</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #354</t>
   </si>
   <si>
     <t>0.057</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #209</t>
-  </si>
-  <si>
-    <t>0.077</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #210</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #211</t>
-  </si>
-  <si>
-    <t>0.073</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #212</t>
-  </si>
-  <si>
-    <t>0.038</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #213</t>
-  </si>
-  <si>
-    <t>0.028</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #214</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #215</t>
-  </si>
-  <si>
-    <t>0.075</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #216</t>
-  </si>
-  <si>
-    <t>0.058</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #217</t>
-  </si>
-  <si>
-    <t>0.088</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #218</t>
-  </si>
-  <si>
-    <t>0.047</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #219</t>
-  </si>
-  <si>
-    <t>0.094</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #220</t>
-  </si>
-  <si>
-    <t>0.068</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #221</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #222</t>
-  </si>
-  <si>
-    <t>0.040</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #223</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #224</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #225</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #226</t>
-  </si>
-  <si>
-    <t>0.036</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #227</t>
-  </si>
-  <si>
-    <t>0.069</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #228</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #229</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #230</t>
-  </si>
-  <si>
-    <t>0.029</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #231</t>
-  </si>
-  <si>
-    <t>0.054</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #232</t>
-  </si>
-  <si>
-    <t>0.037</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #233</t>
-  </si>
-  <si>
-    <t>0.044</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #234</t>
-  </si>
-  <si>
-    <t>0.060</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #235</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #236</t>
-  </si>
-  <si>
-    <t>0.046</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #237</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #238</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #239</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #240</t>
-  </si>
-  <si>
-    <t>0.093</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #241</t>
-  </si>
-  <si>
-    <t>0.026</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #242</t>
-  </si>
-  <si>
-    <t>0.033</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #243</t>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #355</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #356</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #357</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #358</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #359</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #360</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #361</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #362</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #363</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #364</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #365</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #366</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #367</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #368</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #369</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #370</t>
+  </si>
+  <si>
+    <t>0.034</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #371</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #372</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #373</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #374</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #375</t>
   </si>
   <si>
     <t>0.074</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #244</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #245</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #246</t>
-  </si>
-  <si>
-    <t>0.067</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #247</t>
-  </si>
-  <si>
-    <t>0.116</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #248</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #249</t>
-  </si>
-  <si>
-    <t>0.090</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #250</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #251</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #252</t>
-  </si>
-  <si>
-    <t>0.092</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #253</t>
-  </si>
-  <si>
-    <t>0.022</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #254</t>
-  </si>
-  <si>
-    <t>0.082</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #255</t>
-  </si>
-  <si>
-    <t>0.114</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #256</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #257</t>
-  </si>
-  <si>
-    <t>0.108</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #258</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #259</t>
-  </si>
-  <si>
-    <t>0.084</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #260</t>
-  </si>
-  <si>
-    <t>0.117</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #261</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #262</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #263</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #264</t>
-  </si>
-  <si>
-    <t>0.099</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #265</t>
-  </si>
-  <si>
-    <t>0.023</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #266</t>
+    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #376</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #377</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #378</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #379</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #380</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #381</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #382</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #383</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #384</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #385</t>
   </si>
   <si>
     <t>0.061</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #267</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #268</t>
-  </si>
-  <si>
-    <t>0.095</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #269</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #270</t>
-  </si>
-  <si>
-    <t>0.086</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #271</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #272</t>
-  </si>
-  <si>
-    <t>0.041</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #273</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #274</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #275</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #276</t>
-  </si>
-  <si>
-    <t>0.020</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #277</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #278</t>
-  </si>
-  <si>
-    <t>0.091</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #279</t>
+    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #386</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #387</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #388</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #389</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #390</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #391</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #392</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #393</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #394</t>
   </si>
   <si>
     <t>0.085</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #280</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #281</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #282</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #283</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #284</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #285</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #286</t>
-  </si>
-  <si>
-    <t>0.072</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #287</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #288</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #289</t>
-  </si>
-  <si>
-    <t>0.112</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #290</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #291</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #292</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #293</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #294</t>
-  </si>
-  <si>
-    <t>0.079</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #295</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #296</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #297</t>
-  </si>
-  <si>
-    <t>0.032</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #298</t>
-  </si>
-  <si>
-    <t>0.025</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #299</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #300</t>
-  </si>
-  <si>
-    <t>0.115</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #301</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #302</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #303</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #304</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #305</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #306</t>
-  </si>
-  <si>
-    <t>0.021</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #307</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #308</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #309</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #310</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #311</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #312</t>
-  </si>
-  <si>
-    <t>0.064</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #313</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #314</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #315</t>
-  </si>
-  <si>
-    <t>0.049</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #316</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #317</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #318</t>
-  </si>
-  <si>
-    <t>0.052</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #319</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #320</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #321</t>
-  </si>
-  <si>
-    <t>0.119</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #322</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #323</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #324</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #325</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #326</t>
-  </si>
-  <si>
-    <t>0.087</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #327</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #328</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #329</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #330</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #331</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #332</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #333</t>
-  </si>
-  <si>
-    <t>0.107</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #334</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #335</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #336</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #337</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #338</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #339</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #340</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #341</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #342</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #343</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #344</t>
-  </si>
-  <si>
-    <t>0.027</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #345</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #346</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #347</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #348</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #349</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #350</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #351</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #352</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #353</t>
-  </si>
-  <si>
-    <t>0.024</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #354</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #355</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #356</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #357</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #358</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #359</t>
-  </si>
-  <si>
-    <t>0.080</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #360</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #361</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #362</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #363</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #364</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #365</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #366</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #367</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #368</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #369</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #370</t>
-  </si>
-  <si>
-    <t>0.066</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #371</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #372</t>
-  </si>
-  <si>
-    <t>0.106</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #373</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #374</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #375</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #376</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #377</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #378</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #379</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #380</t>
-  </si>
-  <si>
-    <t>0.059</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #381</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #382</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #383</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #384</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #385</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #386</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #387</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #388</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #389</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #390</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #391</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #392</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #393</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #394</t>
-  </si>
-  <si>
-    <t>0.031</t>
-  </si>
-  <si>
     <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #395</t>
   </si>
   <si>
-    <t>0.034</t>
-  </si>
-  <si>
     <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #396</t>
   </si>
   <si>
     <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #397</t>
   </si>
   <si>
-    <t>0.030</t>
-  </si>
-  <si>
     <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #398</t>
   </si>
   <si>
@@ -1517,13 +1526,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>16</t>
+    <t>17</t>
   </si>
   <si>
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 13:55:06 UTC</t>
+    <t>2026-06-23 14:02:47 UTC</t>
   </si>
   <si>
     <t>Branch</t>
@@ -1535,7 +1544,7 @@
     <t>Commit</t>
   </si>
   <si>
-    <t>e40a5d4</t>
+    <t>d1d53d0</t>
   </si>
   <si>
     <t>Total</t>
@@ -2075,7 +2084,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -2086,7 +2095,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>6</v>
@@ -2103,7 +2112,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>6</v>
@@ -2120,7 +2129,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>6</v>
@@ -2137,7 +2146,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>6</v>
@@ -2154,7 +2163,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>6</v>
@@ -2171,7 +2180,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>6</v>
@@ -2188,7 +2197,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>6</v>
@@ -2205,13 +2214,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -2222,13 +2231,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D17" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -2517,7 +2526,7 @@
         <v>6</v>
       </c>
       <c r="D34" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -2704,7 +2713,7 @@
         <v>6</v>
       </c>
       <c r="D45" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -2738,7 +2747,7 @@
         <v>6</v>
       </c>
       <c r="D47" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -2942,7 +2951,7 @@
         <v>6</v>
       </c>
       <c r="D59" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
@@ -3112,7 +3121,7 @@
         <v>6</v>
       </c>
       <c r="D69" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E69" t="s">
         <v>8</v>
@@ -3146,7 +3155,7 @@
         <v>6</v>
       </c>
       <c r="D71" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
@@ -3316,7 +3325,7 @@
         <v>6</v>
       </c>
       <c r="D81" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
@@ -3333,7 +3342,7 @@
         <v>6</v>
       </c>
       <c r="D82" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
@@ -3656,7 +3665,7 @@
         <v>6</v>
       </c>
       <c r="D101" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E101" t="s">
         <v>8</v>
@@ -3673,7 +3682,7 @@
         <v>6</v>
       </c>
       <c r="D102" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E102" t="s">
         <v>8</v>
@@ -3792,7 +3801,7 @@
         <v>6</v>
       </c>
       <c r="D109" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E109" t="s">
         <v>8</v>
@@ -3996,7 +4005,7 @@
         <v>6</v>
       </c>
       <c r="D121" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E121" t="s">
         <v>8</v>
@@ -4149,7 +4158,7 @@
         <v>6</v>
       </c>
       <c r="D130" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E130" t="s">
         <v>8</v>
@@ -5288,7 +5297,7 @@
         <v>6</v>
       </c>
       <c r="D197" t="s">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="E197" t="s">
         <v>8</v>
@@ -5299,13 +5308,13 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D198" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E198" t="s">
         <v>8</v>
@@ -5316,13 +5325,13 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D199" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E199" t="s">
         <v>8</v>
@@ -5333,13 +5342,13 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D200" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="E200" t="s">
         <v>8</v>
@@ -5356,7 +5365,7 @@
         <v>6</v>
       </c>
       <c r="D201" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="E201" t="s">
         <v>8</v>
@@ -5367,13 +5376,13 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D202" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E202" t="s">
         <v>8</v>
@@ -5384,13 +5393,13 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D203" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="E203" t="s">
         <v>8</v>
@@ -5401,13 +5410,13 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D204" t="s">
-        <v>204</v>
+        <v>233</v>
       </c>
       <c r="E204" t="s">
         <v>8</v>
@@ -5418,13 +5427,13 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D205" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E205" t="s">
         <v>8</v>
@@ -5435,13 +5444,13 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D206" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E206" t="s">
         <v>8</v>
@@ -5452,13 +5461,13 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D207" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E207" t="s">
         <v>8</v>
@@ -5469,13 +5478,13 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D208" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E208" t="s">
         <v>8</v>
@@ -5486,13 +5495,13 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D209" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E209" t="s">
         <v>8</v>
@@ -5503,13 +5512,13 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D210" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E210" t="s">
         <v>8</v>
@@ -5520,13 +5529,13 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D211" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E211" t="s">
         <v>8</v>
@@ -5537,13 +5546,13 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D212" t="s">
-        <v>206</v>
+        <v>248</v>
       </c>
       <c r="E212" t="s">
         <v>8</v>
@@ -5554,13 +5563,13 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D213" t="s">
-        <v>247</v>
+        <v>220</v>
       </c>
       <c r="E213" t="s">
         <v>8</v>
@@ -5571,13 +5580,13 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D214" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E214" t="s">
         <v>8</v>
@@ -5588,13 +5597,13 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D215" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E215" t="s">
         <v>8</v>
@@ -5605,13 +5614,13 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D216" t="s">
-        <v>216</v>
+        <v>255</v>
       </c>
       <c r="E216" t="s">
         <v>8</v>
@@ -5622,13 +5631,13 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D217" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E217" t="s">
         <v>8</v>
@@ -5639,13 +5648,13 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D218" t="s">
-        <v>256</v>
+        <v>218</v>
       </c>
       <c r="E218" t="s">
         <v>8</v>
@@ -5656,13 +5665,13 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D219" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E219" t="s">
         <v>8</v>
@@ -5673,13 +5682,13 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D220" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E220" t="s">
         <v>8</v>
@@ -5690,13 +5699,13 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D221" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E221" t="s">
         <v>8</v>
@@ -5707,13 +5716,13 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D222" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E222" t="s">
         <v>8</v>
@@ -5724,13 +5733,13 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D223" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="E223" t="s">
         <v>8</v>
@@ -5741,13 +5750,13 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D224" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E224" t="s">
         <v>8</v>
@@ -5758,13 +5767,13 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D225" t="s">
-        <v>194</v>
+        <v>272</v>
       </c>
       <c r="E225" t="s">
         <v>8</v>
@@ -5775,13 +5784,13 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D226" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="E226" t="s">
         <v>8</v>
@@ -5792,13 +5801,13 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D227" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="E227" t="s">
         <v>8</v>
@@ -5809,13 +5818,13 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D228" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="E228" t="s">
         <v>8</v>
@@ -5826,13 +5835,13 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D229" t="s">
-        <v>274</v>
+        <v>210</v>
       </c>
       <c r="E229" t="s">
         <v>8</v>
@@ -5843,13 +5852,13 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D230" t="s">
-        <v>218</v>
+        <v>270</v>
       </c>
       <c r="E230" t="s">
         <v>8</v>
@@ -5860,13 +5869,13 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D231" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E231" t="s">
         <v>8</v>
@@ -5877,13 +5886,13 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D232" t="s">
-        <v>278</v>
+        <v>216</v>
       </c>
       <c r="E232" t="s">
         <v>8</v>
@@ -5894,13 +5903,13 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D233" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E233" t="s">
         <v>8</v>
@@ -5911,13 +5920,13 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D234" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="E234" t="s">
         <v>8</v>
@@ -5928,13 +5937,13 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D235" t="s">
-        <v>284</v>
+        <v>218</v>
       </c>
       <c r="E235" t="s">
         <v>8</v>
@@ -5945,13 +5954,13 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D236" t="s">
-        <v>286</v>
+        <v>208</v>
       </c>
       <c r="E236" t="s">
         <v>8</v>
@@ -5962,13 +5971,13 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D237" t="s">
-        <v>200</v>
+        <v>241</v>
       </c>
       <c r="E237" t="s">
         <v>8</v>
@@ -5979,13 +5988,13 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D238" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E238" t="s">
         <v>8</v>
@@ -5996,13 +6005,13 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D239" t="s">
-        <v>256</v>
+        <v>292</v>
       </c>
       <c r="E239" t="s">
         <v>8</v>
@@ -6013,13 +6022,13 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D240" t="s">
-        <v>206</v>
+        <v>294</v>
       </c>
       <c r="E240" t="s">
         <v>8</v>
@@ -6030,13 +6039,13 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D241" t="s">
-        <v>216</v>
+        <v>296</v>
       </c>
       <c r="E241" t="s">
         <v>8</v>
@@ -6047,13 +6056,13 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D242" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="E242" t="s">
         <v>8</v>
@@ -6064,13 +6073,13 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D243" t="s">
-        <v>296</v>
+        <v>192</v>
       </c>
       <c r="E243" t="s">
         <v>8</v>
@@ -6081,13 +6090,13 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D244" t="s">
-        <v>298</v>
+        <v>233</v>
       </c>
       <c r="E244" t="s">
         <v>8</v>
@@ -6098,13 +6107,13 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D245" t="s">
-        <v>300</v>
+        <v>216</v>
       </c>
       <c r="E245" t="s">
         <v>8</v>
@@ -6115,13 +6124,13 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D246" t="s">
-        <v>236</v>
+        <v>268</v>
       </c>
       <c r="E246" t="s">
         <v>8</v>
@@ -6132,13 +6141,13 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D247" t="s">
-        <v>208</v>
+        <v>304</v>
       </c>
       <c r="E247" t="s">
         <v>8</v>
@@ -6149,13 +6158,13 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D248" t="s">
-        <v>304</v>
+        <v>204</v>
       </c>
       <c r="E248" t="s">
         <v>8</v>
@@ -6166,13 +6175,13 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D249" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E249" t="s">
         <v>8</v>
@@ -6183,13 +6192,13 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D250" t="s">
-        <v>228</v>
+        <v>296</v>
       </c>
       <c r="E250" t="s">
         <v>8</v>
@@ -6200,13 +6209,13 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D251" t="s">
-        <v>309</v>
+        <v>227</v>
       </c>
       <c r="E251" t="s">
         <v>8</v>
@@ -6223,7 +6232,7 @@
         <v>6</v>
       </c>
       <c r="D252" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="E252" t="s">
         <v>8</v>
@@ -6240,7 +6249,7 @@
         <v>6</v>
       </c>
       <c r="D253" t="s">
-        <v>306</v>
+        <v>243</v>
       </c>
       <c r="E253" t="s">
         <v>8</v>
@@ -6257,7 +6266,7 @@
         <v>6</v>
       </c>
       <c r="D254" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="E254" t="s">
         <v>8</v>
@@ -6268,13 +6277,13 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D255" t="s">
-        <v>315</v>
+        <v>251</v>
       </c>
       <c r="E255" t="s">
         <v>8</v>
@@ -6285,13 +6294,13 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D256" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E256" t="s">
         <v>8</v>
@@ -6302,13 +6311,13 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D257" t="s">
-        <v>319</v>
+        <v>241</v>
       </c>
       <c r="E257" t="s">
         <v>8</v>
@@ -6319,13 +6328,13 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D258" t="s">
-        <v>202</v>
+        <v>318</v>
       </c>
       <c r="E258" t="s">
         <v>8</v>
@@ -6336,13 +6345,13 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D259" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E259" t="s">
         <v>8</v>
@@ -6353,13 +6362,13 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D260" t="s">
-        <v>238</v>
+        <v>292</v>
       </c>
       <c r="E260" t="s">
         <v>8</v>
@@ -6370,13 +6379,13 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D261" t="s">
-        <v>325</v>
+        <v>296</v>
       </c>
       <c r="E261" t="s">
         <v>8</v>
@@ -6387,13 +6396,13 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D262" t="s">
-        <v>327</v>
+        <v>264</v>
       </c>
       <c r="E262" t="s">
         <v>8</v>
@@ -6404,13 +6413,13 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D263" t="s">
-        <v>262</v>
+        <v>325</v>
       </c>
       <c r="E263" t="s">
         <v>8</v>
@@ -6421,13 +6430,13 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D264" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="E264" t="s">
         <v>8</v>
@@ -6438,13 +6447,13 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D265" t="s">
-        <v>200</v>
+        <v>318</v>
       </c>
       <c r="E265" t="s">
         <v>8</v>
@@ -6455,13 +6464,13 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D266" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="E266" t="s">
         <v>8</v>
@@ -6472,13 +6481,13 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D267" t="s">
-        <v>334</v>
+        <v>229</v>
       </c>
       <c r="E267" t="s">
         <v>8</v>
@@ -6489,13 +6498,13 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D268" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E268" t="s">
         <v>8</v>
@@ -6506,13 +6515,13 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D269" t="s">
-        <v>228</v>
+        <v>334</v>
       </c>
       <c r="E269" t="s">
         <v>8</v>
@@ -6523,13 +6532,13 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D270" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="E270" t="s">
         <v>8</v>
@@ -6540,13 +6549,13 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D271" t="s">
-        <v>284</v>
+        <v>337</v>
       </c>
       <c r="E271" t="s">
         <v>8</v>
@@ -6557,13 +6566,13 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D272" t="s">
-        <v>342</v>
+        <v>237</v>
       </c>
       <c r="E272" t="s">
         <v>8</v>
@@ -6574,13 +6583,13 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D273" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E273" t="s">
         <v>8</v>
@@ -6591,13 +6600,13 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D274" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E274" t="s">
         <v>8</v>
@@ -6608,13 +6617,13 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D275" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="E275" t="s">
         <v>8</v>
@@ -6625,13 +6634,13 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D276" t="s">
-        <v>278</v>
+        <v>337</v>
       </c>
       <c r="E276" t="s">
         <v>8</v>
@@ -6642,13 +6651,13 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D277" t="s">
-        <v>198</v>
+        <v>235</v>
       </c>
       <c r="E277" t="s">
         <v>8</v>
@@ -6659,13 +6668,13 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D278" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E278" t="s">
         <v>8</v>
@@ -6676,13 +6685,13 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D279" t="s">
-        <v>232</v>
+        <v>348</v>
       </c>
       <c r="E279" t="s">
         <v>8</v>
@@ -6693,13 +6702,13 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D280" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E280" t="s">
         <v>8</v>
@@ -6710,13 +6719,13 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D281" t="s">
-        <v>355</v>
+        <v>341</v>
       </c>
       <c r="E281" t="s">
         <v>8</v>
@@ -6727,13 +6736,13 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D282" t="s">
-        <v>286</v>
+        <v>214</v>
       </c>
       <c r="E282" t="s">
         <v>8</v>
@@ -6744,13 +6753,13 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D283" t="s">
-        <v>327</v>
+        <v>245</v>
       </c>
       <c r="E283" t="s">
         <v>8</v>
@@ -6761,13 +6770,13 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D284" t="s">
-        <v>196</v>
+        <v>296</v>
       </c>
       <c r="E284" t="s">
         <v>8</v>
@@ -6778,13 +6787,13 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D285" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E285" t="s">
         <v>8</v>
@@ -6795,13 +6804,13 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D286" t="s">
-        <v>258</v>
+        <v>357</v>
       </c>
       <c r="E286" t="s">
         <v>8</v>
@@ -6812,13 +6821,13 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D287" t="s">
-        <v>228</v>
+        <v>359</v>
       </c>
       <c r="E287" t="s">
         <v>8</v>
@@ -6829,13 +6838,13 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D288" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E288" t="s">
         <v>8</v>
@@ -6846,13 +6855,13 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D289" t="s">
-        <v>296</v>
+        <v>227</v>
       </c>
       <c r="E289" t="s">
         <v>8</v>
@@ -6863,13 +6872,13 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D290" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="E290" t="s">
         <v>8</v>
@@ -6880,13 +6889,13 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D291" t="s">
-        <v>367</v>
+        <v>315</v>
       </c>
       <c r="E291" t="s">
         <v>8</v>
@@ -6897,13 +6906,13 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D292" t="s">
-        <v>214</v>
+        <v>283</v>
       </c>
       <c r="E292" t="s">
         <v>8</v>
@@ -6914,13 +6923,13 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D293" t="s">
-        <v>306</v>
+        <v>367</v>
       </c>
       <c r="E293" t="s">
         <v>8</v>
@@ -6931,13 +6940,13 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D294" t="s">
-        <v>244</v>
+        <v>200</v>
       </c>
       <c r="E294" t="s">
         <v>8</v>
@@ -6948,13 +6957,13 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D295" t="s">
-        <v>325</v>
+        <v>268</v>
       </c>
       <c r="E295" t="s">
         <v>8</v>
@@ -6965,13 +6974,13 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D296" t="s">
-        <v>373</v>
+        <v>218</v>
       </c>
       <c r="E296" t="s">
         <v>8</v>
@@ -6982,13 +6991,13 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D297" t="s">
-        <v>315</v>
+        <v>283</v>
       </c>
       <c r="E297" t="s">
         <v>8</v>
@@ -6999,13 +7008,13 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D298" t="s">
-        <v>306</v>
+        <v>373</v>
       </c>
       <c r="E298" t="s">
         <v>8</v>
@@ -7016,13 +7025,13 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D299" t="s">
-        <v>377</v>
+        <v>251</v>
       </c>
       <c r="E299" t="s">
         <v>8</v>
@@ -7033,13 +7042,13 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D300" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E300" t="s">
         <v>8</v>
@@ -7050,13 +7059,13 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D301" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="E301" t="s">
         <v>8</v>
@@ -7067,13 +7076,13 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D302" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E302" t="s">
         <v>8</v>
@@ -7084,13 +7093,13 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D303" t="s">
-        <v>223</v>
+        <v>381</v>
       </c>
       <c r="E303" t="s">
         <v>8</v>
@@ -7101,13 +7110,13 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D304" t="s">
-        <v>284</v>
+        <v>325</v>
       </c>
       <c r="E304" t="s">
         <v>8</v>
@@ -7118,13 +7127,13 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D305" t="s">
-        <v>225</v>
+        <v>320</v>
       </c>
       <c r="E305" t="s">
         <v>8</v>
@@ -7135,13 +7144,13 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D306" t="s">
-        <v>336</v>
+        <v>385</v>
       </c>
       <c r="E306" t="s">
         <v>8</v>
@@ -7152,13 +7161,13 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D307" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="E307" t="s">
         <v>8</v>
@@ -7169,13 +7178,13 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D308" t="s">
-        <v>389</v>
+        <v>332</v>
       </c>
       <c r="E308" t="s">
         <v>8</v>
@@ -7186,13 +7195,13 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D309" t="s">
-        <v>225</v>
+        <v>389</v>
       </c>
       <c r="E309" t="s">
         <v>8</v>
@@ -7203,13 +7212,13 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D310" t="s">
-        <v>298</v>
+        <v>200</v>
       </c>
       <c r="E310" t="s">
         <v>8</v>
@@ -7220,13 +7229,13 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D311" t="s">
-        <v>247</v>
+        <v>318</v>
       </c>
       <c r="E311" t="s">
         <v>8</v>
@@ -7237,13 +7246,13 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
+        <v>392</v>
+      </c>
+      <c r="C312" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D312" t="s">
         <v>393</v>
-      </c>
-      <c r="C312" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D312" t="s">
-        <v>289</v>
       </c>
       <c r="E312" t="s">
         <v>8</v>
@@ -7260,7 +7269,7 @@
         <v>6</v>
       </c>
       <c r="D313" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="E313" t="s">
         <v>8</v>
@@ -7294,7 +7303,7 @@
         <v>6</v>
       </c>
       <c r="D315" t="s">
-        <v>223</v>
+        <v>398</v>
       </c>
       <c r="E315" t="s">
         <v>8</v>
@@ -7305,13 +7314,13 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D316" t="s">
-        <v>247</v>
+        <v>320</v>
       </c>
       <c r="E316" t="s">
         <v>8</v>
@@ -7322,13 +7331,13 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D317" t="s">
-        <v>400</v>
+        <v>255</v>
       </c>
       <c r="E317" t="s">
         <v>8</v>
@@ -7345,7 +7354,7 @@
         <v>6</v>
       </c>
       <c r="D318" t="s">
-        <v>350</v>
+        <v>402</v>
       </c>
       <c r="E318" t="s">
         <v>8</v>
@@ -7356,13 +7365,13 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D319" t="s">
-        <v>382</v>
+        <v>245</v>
       </c>
       <c r="E319" t="s">
         <v>8</v>
@@ -7373,13 +7382,13 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D320" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E320" t="s">
         <v>8</v>
@@ -7390,13 +7399,13 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D321" t="s">
-        <v>284</v>
+        <v>224</v>
       </c>
       <c r="E321" t="s">
         <v>8</v>
@@ -7407,13 +7416,13 @@
         <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D322" t="s">
-        <v>379</v>
+        <v>208</v>
       </c>
       <c r="E322" t="s">
         <v>8</v>
@@ -7424,13 +7433,13 @@
         <v>322</v>
       </c>
       <c r="B323" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D323" t="s">
-        <v>408</v>
+        <v>325</v>
       </c>
       <c r="E323" t="s">
         <v>8</v>
@@ -7447,7 +7456,7 @@
         <v>6</v>
       </c>
       <c r="D324" t="s">
-        <v>304</v>
+        <v>337</v>
       </c>
       <c r="E324" t="s">
         <v>8</v>
@@ -7464,7 +7473,7 @@
         <v>6</v>
       </c>
       <c r="D325" t="s">
-        <v>315</v>
+        <v>411</v>
       </c>
       <c r="E325" t="s">
         <v>8</v>
@@ -7475,13 +7484,13 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D326" t="s">
-        <v>322</v>
+        <v>202</v>
       </c>
       <c r="E326" t="s">
         <v>8</v>
@@ -7492,13 +7501,13 @@
         <v>326</v>
       </c>
       <c r="B327" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D327" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="E327" t="s">
         <v>8</v>
@@ -7509,13 +7518,13 @@
         <v>327</v>
       </c>
       <c r="B328" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D328" t="s">
-        <v>414</v>
+        <v>255</v>
       </c>
       <c r="E328" t="s">
         <v>8</v>
@@ -7532,7 +7541,7 @@
         <v>6</v>
       </c>
       <c r="D329" t="s">
-        <v>317</v>
+        <v>416</v>
       </c>
       <c r="E329" t="s">
         <v>8</v>
@@ -7543,13 +7552,13 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D330" t="s">
-        <v>196</v>
+        <v>257</v>
       </c>
       <c r="E330" t="s">
         <v>8</v>
@@ -7560,13 +7569,13 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D331" t="s">
-        <v>272</v>
+        <v>419</v>
       </c>
       <c r="E331" t="s">
         <v>8</v>
@@ -7577,13 +7586,13 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D332" t="s">
-        <v>319</v>
+        <v>231</v>
       </c>
       <c r="E332" t="s">
         <v>8</v>
@@ -7594,13 +7603,13 @@
         <v>332</v>
       </c>
       <c r="B333" t="s">
+        <v>421</v>
+      </c>
+      <c r="C333" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D333" t="s">
         <v>419</v>
-      </c>
-      <c r="C333" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D333" t="s">
-        <v>313</v>
       </c>
       <c r="E333" t="s">
         <v>8</v>
@@ -7611,13 +7620,13 @@
         <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D334" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="E334" t="s">
         <v>8</v>
@@ -7628,13 +7637,13 @@
         <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D335" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E335" t="s">
         <v>8</v>
@@ -7645,13 +7654,13 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D336" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="E336" t="s">
         <v>8</v>
@@ -7662,13 +7671,13 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D337" t="s">
-        <v>377</v>
+        <v>427</v>
       </c>
       <c r="E337" t="s">
         <v>8</v>
@@ -7679,13 +7688,13 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D338" t="s">
-        <v>379</v>
+        <v>241</v>
       </c>
       <c r="E338" t="s">
         <v>8</v>
@@ -7696,13 +7705,13 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D339" t="s">
-        <v>272</v>
+        <v>320</v>
       </c>
       <c r="E339" t="s">
         <v>8</v>
@@ -7713,13 +7722,13 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D340" t="s">
-        <v>355</v>
+        <v>222</v>
       </c>
       <c r="E340" t="s">
         <v>8</v>
@@ -7730,13 +7739,13 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D341" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E341" t="s">
         <v>8</v>
@@ -7747,13 +7756,13 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D342" t="s">
-        <v>225</v>
+        <v>329</v>
       </c>
       <c r="E342" t="s">
         <v>8</v>
@@ -7764,13 +7773,13 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D343" t="s">
-        <v>200</v>
+        <v>264</v>
       </c>
       <c r="E343" t="s">
         <v>8</v>
@@ -7781,13 +7790,13 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D344" t="s">
-        <v>353</v>
+        <v>270</v>
       </c>
       <c r="E344" t="s">
         <v>8</v>
@@ -7798,13 +7807,13 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D345" t="s">
-        <v>208</v>
+        <v>436</v>
       </c>
       <c r="E345" t="s">
         <v>8</v>
@@ -7815,13 +7824,13 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D346" t="s">
-        <v>434</v>
+        <v>381</v>
       </c>
       <c r="E346" t="s">
         <v>8</v>
@@ -7832,13 +7841,13 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D347" t="s">
-        <v>300</v>
+        <v>381</v>
       </c>
       <c r="E347" t="s">
         <v>8</v>
@@ -7849,13 +7858,13 @@
         <v>347</v>
       </c>
       <c r="B348" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D348" t="s">
-        <v>317</v>
+        <v>292</v>
       </c>
       <c r="E348" t="s">
         <v>8</v>
@@ -7866,13 +7875,13 @@
         <v>348</v>
       </c>
       <c r="B349" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D349" t="s">
-        <v>210</v>
+        <v>441</v>
       </c>
       <c r="E349" t="s">
         <v>8</v>
@@ -7883,13 +7892,13 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D350" t="s">
-        <v>334</v>
+        <v>436</v>
       </c>
       <c r="E350" t="s">
         <v>8</v>
@@ -7900,13 +7909,13 @@
         <v>350</v>
       </c>
       <c r="B351" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D351" t="s">
-        <v>204</v>
+        <v>444</v>
       </c>
       <c r="E351" t="s">
         <v>8</v>
@@ -7917,13 +7926,13 @@
         <v>351</v>
       </c>
       <c r="B352" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D352" t="s">
-        <v>434</v>
+        <v>315</v>
       </c>
       <c r="E352" t="s">
         <v>8</v>
@@ -7934,13 +7943,13 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D353" t="s">
-        <v>373</v>
+        <v>447</v>
       </c>
       <c r="E353" t="s">
         <v>8</v>
@@ -7951,13 +7960,13 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D354" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E354" t="s">
         <v>8</v>
@@ -7968,13 +7977,13 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D355" t="s">
-        <v>444</v>
+        <v>307</v>
       </c>
       <c r="E355" t="s">
         <v>8</v>
@@ -7985,13 +7994,13 @@
         <v>355</v>
       </c>
       <c r="B356" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D356" t="s">
-        <v>196</v>
+        <v>451</v>
       </c>
       <c r="E356" t="s">
         <v>8</v>
@@ -8002,13 +8011,13 @@
         <v>356</v>
       </c>
       <c r="B357" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D357" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E357" t="s">
         <v>8</v>
@@ -8019,13 +8028,13 @@
         <v>357</v>
       </c>
       <c r="B358" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D358" t="s">
-        <v>294</v>
+        <v>233</v>
       </c>
       <c r="E358" t="s">
         <v>8</v>
@@ -8036,13 +8045,13 @@
         <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D359" t="s">
-        <v>334</v>
+        <v>222</v>
       </c>
       <c r="E359" t="s">
         <v>8</v>
@@ -8053,13 +8062,13 @@
         <v>359</v>
       </c>
       <c r="B360" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D360" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="E360" t="s">
         <v>8</v>
@@ -8070,13 +8079,13 @@
         <v>360</v>
       </c>
       <c r="B361" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D361" t="s">
-        <v>451</v>
+        <v>270</v>
       </c>
       <c r="E361" t="s">
         <v>8</v>
@@ -8087,13 +8096,13 @@
         <v>361</v>
       </c>
       <c r="B362" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D362" t="s">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="E362" t="s">
         <v>8</v>
@@ -8104,13 +8113,13 @@
         <v>362</v>
       </c>
       <c r="B363" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D363" t="s">
-        <v>251</v>
+        <v>307</v>
       </c>
       <c r="E363" t="s">
         <v>8</v>
@@ -8121,13 +8130,13 @@
         <v>363</v>
       </c>
       <c r="B364" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D364" t="s">
-        <v>317</v>
+        <v>208</v>
       </c>
       <c r="E364" t="s">
         <v>8</v>
@@ -8138,13 +8147,13 @@
         <v>364</v>
       </c>
       <c r="B365" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D365" t="s">
-        <v>313</v>
+        <v>424</v>
       </c>
       <c r="E365" t="s">
         <v>8</v>
@@ -8155,13 +8164,13 @@
         <v>365</v>
       </c>
       <c r="B366" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D366" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="E366" t="s">
         <v>8</v>
@@ -8172,13 +8181,13 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D367" t="s">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="E367" t="s">
         <v>8</v>
@@ -8189,13 +8198,13 @@
         <v>367</v>
       </c>
       <c r="B368" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D368" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E368" t="s">
         <v>8</v>
@@ -8206,13 +8215,13 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D369" t="s">
-        <v>350</v>
+        <v>214</v>
       </c>
       <c r="E369" t="s">
         <v>8</v>
@@ -8223,13 +8232,13 @@
         <v>369</v>
       </c>
       <c r="B370" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D370" t="s">
-        <v>404</v>
+        <v>200</v>
       </c>
       <c r="E370" t="s">
         <v>8</v>
@@ -8240,13 +8249,13 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D371" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="E371" t="s">
         <v>8</v>
@@ -8257,13 +8266,13 @@
         <v>371</v>
       </c>
       <c r="B372" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D372" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="E372" t="s">
         <v>8</v>
@@ -8274,13 +8283,13 @@
         <v>372</v>
       </c>
       <c r="B373" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D373" t="s">
-        <v>451</v>
+        <v>243</v>
       </c>
       <c r="E373" t="s">
         <v>8</v>
@@ -8291,13 +8300,13 @@
         <v>373</v>
       </c>
       <c r="B374" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D374" t="s">
-        <v>466</v>
+        <v>290</v>
       </c>
       <c r="E374" t="s">
         <v>8</v>
@@ -8308,13 +8317,13 @@
         <v>374</v>
       </c>
       <c r="B375" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D375" t="s">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="E375" t="s">
         <v>8</v>
@@ -8325,13 +8334,13 @@
         <v>375</v>
       </c>
       <c r="B376" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D376" t="s">
-        <v>298</v>
+        <v>424</v>
       </c>
       <c r="E376" t="s">
         <v>8</v>
@@ -8342,13 +8351,13 @@
         <v>376</v>
       </c>
       <c r="B377" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D377" t="s">
-        <v>284</v>
+        <v>474</v>
       </c>
       <c r="E377" t="s">
         <v>8</v>
@@ -8359,13 +8368,13 @@
         <v>377</v>
       </c>
       <c r="B378" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D378" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="E378" t="s">
         <v>8</v>
@@ -8376,13 +8385,13 @@
         <v>378</v>
       </c>
       <c r="B379" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D379" t="s">
-        <v>294</v>
+        <v>348</v>
       </c>
       <c r="E379" t="s">
         <v>8</v>
@@ -8393,13 +8402,13 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D380" t="s">
-        <v>332</v>
+        <v>304</v>
       </c>
       <c r="E380" t="s">
         <v>8</v>
@@ -8410,13 +8419,13 @@
         <v>380</v>
       </c>
       <c r="B381" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D381" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="E381" t="s">
         <v>8</v>
@@ -8427,13 +8436,13 @@
         <v>381</v>
       </c>
       <c r="B382" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D382" t="s">
-        <v>475</v>
+        <v>436</v>
       </c>
       <c r="E382" t="s">
         <v>8</v>
@@ -8444,13 +8453,13 @@
         <v>382</v>
       </c>
       <c r="B383" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D383" t="s">
-        <v>363</v>
+        <v>337</v>
       </c>
       <c r="E383" t="s">
         <v>8</v>
@@ -8461,13 +8470,13 @@
         <v>383</v>
       </c>
       <c r="B384" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D384" t="s">
-        <v>327</v>
+        <v>474</v>
       </c>
       <c r="E384" t="s">
         <v>8</v>
@@ -8478,13 +8487,13 @@
         <v>384</v>
       </c>
       <c r="B385" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D385" t="s">
-        <v>377</v>
+        <v>307</v>
       </c>
       <c r="E385" t="s">
         <v>8</v>
@@ -8495,13 +8504,13 @@
         <v>385</v>
       </c>
       <c r="B386" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D386" t="s">
-        <v>379</v>
+        <v>325</v>
       </c>
       <c r="E386" t="s">
         <v>8</v>
@@ -8512,13 +8521,13 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D387" t="s">
-        <v>350</v>
+        <v>485</v>
       </c>
       <c r="E387" t="s">
         <v>8</v>
@@ -8529,13 +8538,13 @@
         <v>387</v>
       </c>
       <c r="B388" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D388" t="s">
-        <v>309</v>
+        <v>262</v>
       </c>
       <c r="E388" t="s">
         <v>8</v>
@@ -8546,13 +8555,13 @@
         <v>388</v>
       </c>
       <c r="B389" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D389" t="s">
-        <v>315</v>
+        <v>274</v>
       </c>
       <c r="E389" t="s">
         <v>8</v>
@@ -8563,13 +8572,13 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D390" t="s">
-        <v>309</v>
+        <v>235</v>
       </c>
       <c r="E390" t="s">
         <v>8</v>
@@ -8580,13 +8589,13 @@
         <v>390</v>
       </c>
       <c r="B391" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D391" t="s">
-        <v>451</v>
+        <v>255</v>
       </c>
       <c r="E391" t="s">
         <v>8</v>
@@ -8597,13 +8606,13 @@
         <v>391</v>
       </c>
       <c r="B392" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D392" t="s">
-        <v>210</v>
+        <v>474</v>
       </c>
       <c r="E392" t="s">
         <v>8</v>
@@ -8614,13 +8623,13 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D393" t="s">
-        <v>274</v>
+        <v>402</v>
       </c>
       <c r="E393" t="s">
         <v>8</v>
@@ -8631,13 +8640,13 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D394" t="s">
-        <v>286</v>
+        <v>196</v>
       </c>
       <c r="E394" t="s">
         <v>8</v>
@@ -8648,13 +8657,13 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D395" t="s">
-        <v>274</v>
+        <v>346</v>
       </c>
       <c r="E395" t="s">
         <v>8</v>
@@ -8665,13 +8674,13 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D396" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E396" t="s">
         <v>8</v>
@@ -8682,13 +8691,13 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D397" t="s">
-        <v>492</v>
+        <v>373</v>
       </c>
       <c r="E397" t="s">
         <v>8</v>
@@ -8699,13 +8708,13 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D398" t="s">
-        <v>218</v>
+        <v>257</v>
       </c>
       <c r="E398" t="s">
         <v>8</v>
@@ -8716,13 +8725,13 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D399" t="s">
-        <v>495</v>
+        <v>294</v>
       </c>
       <c r="E399" t="s">
         <v>8</v>
@@ -8733,13 +8742,13 @@
         <v>399</v>
       </c>
       <c r="B400" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D400" t="s">
-        <v>404</v>
+        <v>248</v>
       </c>
       <c r="E400" t="s">
         <v>8</v>
@@ -8750,13 +8759,13 @@
         <v>400</v>
       </c>
       <c r="B401" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D401" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="E401" t="s">
         <v>8</v>
@@ -8775,47 +8784,47 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="B1" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="B2" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B3" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="B4" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B5" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B6">
         <v>400</v>
@@ -8823,7 +8832,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="B7">
         <v>400</v>
@@ -8831,7 +8840,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -8839,7 +8848,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -8847,10 +8856,10 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="B10" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
   </sheetData>

--- a/reports/backend/Excel/Automation_Test_Report.xlsx
+++ b/reports/backend/Excel/Automation_Test_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="512">
   <si>
     <t>#</t>
   </si>
@@ -35,15 +35,18 @@
     <t>PASSED</t>
   </si>
   <si>
+    <t>0.001</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Smart Admission Backend — Authentication Tests BT-002 | Firebase config has authDomain</t>
+  </si>
+  <si>
     <t>0.000</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>Smart Admission Backend — Authentication Tests BT-002 | Firebase config has authDomain</t>
-  </si>
-  <si>
     <t>Smart Admission Backend — Authentication Tests BT-003 | Firebase config has projectId</t>
   </si>
   <si>
@@ -59,9 +62,6 @@
     <t>Smart Admission Backend — Authentication Tests BT-007 | Firebase config projectId matches authDomain prefix</t>
   </si>
   <si>
-    <t>0.001</t>
-  </si>
-  <si>
     <t>Smart Admission Backend — Authentication Tests BT-008 | Firebase config has all 6 required fields</t>
   </si>
   <si>
@@ -581,940 +581,925 @@
     <t>Smart Admission Backend — College Data Service Tests BT-200 | Math.min returns smaller number</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #180</t>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field apiKey (Verify Point #180)</t>
+  </si>
+  <si>
+    <t>0.027</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #181)</t>
+  </si>
+  <si>
+    <t>0.035</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #182)</t>
+  </si>
+  <si>
+    <t>0.076</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #183)</t>
+  </si>
+  <si>
+    <t>0.065</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #184)</t>
+  </si>
+  <si>
+    <t>0.060</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #185)</t>
+  </si>
+  <si>
+    <t>0.049</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #186)</t>
+  </si>
+  <si>
+    <t>0.066</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #187)</t>
+  </si>
+  <si>
+    <t>0.119</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #188)</t>
+  </si>
+  <si>
+    <t>0.032</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #189)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #190)</t>
+  </si>
+  <si>
+    <t>0.071</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #191)</t>
+  </si>
+  <si>
+    <t>0.115</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #192)</t>
+  </si>
+  <si>
+    <t>0.042</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #193)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #194)</t>
+  </si>
+  <si>
+    <t>0.080</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #195)</t>
+  </si>
+  <si>
+    <t>0.069</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #196)</t>
+  </si>
+  <si>
+    <t>0.116</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #197)</t>
+  </si>
+  <si>
+    <t>0.041</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #198)</t>
+  </si>
+  <si>
+    <t>0.053</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #199)</t>
+  </si>
+  <si>
+    <t>0.079</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #200)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #201)</t>
+  </si>
+  <si>
+    <t>0.088</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #202)</t>
+  </si>
+  <si>
+    <t>0.082</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #203)</t>
+  </si>
+  <si>
+    <t>0.070</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #204)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #205)</t>
+  </si>
+  <si>
+    <t>0.102</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #206)</t>
+  </si>
+  <si>
+    <t>0.063</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #207)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #208)</t>
+  </si>
+  <si>
+    <t>0.057</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #209)</t>
+  </si>
+  <si>
+    <t>0.025</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #210)</t>
+  </si>
+  <si>
+    <t>0.109</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #211)</t>
+  </si>
+  <si>
+    <t>0.091</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code XSS-injection (Verify Point #212)</t>
+  </si>
+  <si>
+    <t>0.112</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #213)</t>
+  </si>
+  <si>
+    <t>0.107</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for CSRF-token (Verify Point #214)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated CORS-origin (Verify Point #215)</t>
+  </si>
+  <si>
+    <t>0.036</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for CSP-header (Verify Point #216)</t>
+  </si>
+  <si>
+    <t>0.030</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at session-token (Verify Point #217)</t>
+  </si>
+  <si>
+    <t>0.111</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users-ref (Verify Point #218)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for items-ref (Verify Point #219)</t>
+  </si>
+  <si>
+    <t>0.061</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field de-DE (Verify Point #220)</t>
+  </si>
+  <si>
+    <t>0.117</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for fr-FR (Verify Point #221)</t>
   </si>
   <si>
     <t>0.040</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #181</t>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ja-JP (Verify Point #222)</t>
+  </si>
+  <si>
+    <t>0.085</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for pt-BR (Verify Point #223)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of it-IT (Verify Point #224)</t>
+  </si>
+  <si>
+    <t>0.118</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for apiKey (Verify Point #225)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for authDomain (Verify Point #226)</t>
+  </si>
+  <si>
+    <t>0.068</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value projectId (Verify Point #227)</t>
+  </si>
+  <si>
+    <t>0.101</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session storageBucket (Verify Point #228)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier messagingSenderId (Verify Point #229)</t>
+  </si>
+  <si>
+    <t>0.104</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region appId (Verify Point #230)</t>
+  </si>
+  <si>
+    <t>0.114</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for name (Verify Point #231)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code id (Verify Point #232)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource fees.min (Verify Point #233)</t>
+  </si>
+  <si>
+    <t>0.089</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for fees.max (Verify Point #234)</t>
+  </si>
+  <si>
+    <t>0.086</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated courses (Verify Point #235)</t>
+  </si>
+  <si>
+    <t>0.047</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for ranking.nirf (Verify Point #236)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at type (Verify Point #237)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users/uid001 (Verify Point #238)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for colleges/c001 (Verify Point #239)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field prompt-length (Verify Point #240)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for session-id-1 (Verify Point #241)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ₹1L (Verify Point #242)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for B.Tech (Verify Point #243)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of 4 years (Verify Point #244)</t>
+  </si>
+  <si>
+    <t>0.084</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for Tamil Nadu (Verify Point #245)</t>
+  </si>
+  <si>
+    <t>0.043</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for Chennai (Verify Point #246)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value llama3-8b (Verify Point #247)</t>
+  </si>
+  <si>
+    <t>0.055</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session email (Verify Point #248)</t>
+  </si>
+  <si>
+    <t>0.029</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier password (Verify Point #249)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region displayName (Verify Point #250)</t>
+  </si>
+  <si>
+    <t>0.067</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for savedColleges (Verify Point #251)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code createdAt (Verify Point #252)</t>
   </si>
   <si>
     <t>0.105</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #182</t>
-  </si>
-  <si>
-    <t>0.109</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #183</t>
-  </si>
-  <si>
-    <t>0.046</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #184</t>
-  </si>
-  <si>
-    <t>0.035</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #185</t>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource firebase-auth (Verify Point #253)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for firestore-read (Verify Point #254)</t>
+  </si>
+  <si>
+    <t>0.072</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated groq-api (Verify Point #255)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for college-list (Verify Point #256)</t>
+  </si>
+  <si>
+    <t>0.073</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at XSS-injection (Verify Point #257)</t>
+  </si>
+  <si>
+    <t>0.097</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation SQL-injection (Verify Point #258)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for CSRF-token (Verify Point #259)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field CORS-origin (Verify Point #260)</t>
+  </si>
+  <si>
+    <t>0.064</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for CSP-header (Verify Point #261)</t>
+  </si>
+  <si>
+    <t>0.092</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for session-token (Verify Point #262)</t>
+  </si>
+  <si>
+    <t>0.031</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users-ref (Verify Point #263)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of items-ref (Verify Point #264)</t>
+  </si>
+  <si>
+    <t>0.108</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for de-DE (Verify Point #265)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for fr-FR (Verify Point #266)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ja-JP (Verify Point #267)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session pt-BR (Verify Point #268)</t>
+  </si>
+  <si>
+    <t>0.050</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier it-IT (Verify Point #269)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region apiKey (Verify Point #270)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for authDomain (Verify Point #271)</t>
+  </si>
+  <si>
+    <t>0.024</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code projectId (Verify Point #272)</t>
+  </si>
+  <si>
+    <t>0.037</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource storageBucket (Verify Point #273)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for messagingSenderId (Verify Point #274)</t>
+  </si>
+  <si>
+    <t>0.051</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated appId (Verify Point #275)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for name (Verify Point #276)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at id (Verify Point #277)</t>
+  </si>
+  <si>
+    <t>0.075</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation fees.min (Verify Point #278)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for fees.max (Verify Point #279)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field courses (Verify Point #280)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for ranking.nirf (Verify Point #281)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for type (Verify Point #282)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users/uid001 (Verify Point #283)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of colleges/c001 (Verify Point #284)</t>
+  </si>
+  <si>
+    <t>0.062</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for prompt-length (Verify Point #285)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for session-id-1 (Verify Point #286)</t>
+  </si>
+  <si>
+    <t>0.081</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ₹1L (Verify Point #287)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session B.Tech (Verify Point #288)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier 4 years (Verify Point #289)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region Tamil Nadu (Verify Point #290)</t>
+  </si>
+  <si>
+    <t>0.078</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for Chennai (Verify Point #291)</t>
   </si>
   <si>
     <t>0.022</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #186</t>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code llama3-8b (Verify Point #292)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource email (Verify Point #293)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for password (Verify Point #294)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated displayName (Verify Point #295)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for savedColleges (Verify Point #296)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at createdAt (Verify Point #297)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation firebase-auth (Verify Point #298)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for firestore-read (Verify Point #299)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field groq-api (Verify Point #300)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for college-list (Verify Point #301)</t>
+  </si>
+  <si>
+    <t>0.052</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for XSS-injection (Verify Point #302)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for SQL-injection (Verify Point #303)</t>
+  </si>
+  <si>
+    <t>0.026</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of CSRF-token (Verify Point #304)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for CORS-origin (Verify Point #305)</t>
+  </si>
+  <si>
+    <t>0.045</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for CSP-header (Verify Point #306)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value session-token (Verify Point #307)</t>
+  </si>
+  <si>
+    <t>0.098</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users-ref (Verify Point #308)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier items-ref (Verify Point #309)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region de-DE (Verify Point #310)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for fr-FR (Verify Point #311)</t>
   </si>
   <si>
     <t>0.020</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #187</t>
-  </si>
-  <si>
-    <t>0.088</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #188</t>
-  </si>
-  <si>
-    <t>0.052</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #189</t>
-  </si>
-  <si>
-    <t>0.043</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #190</t>
-  </si>
-  <si>
-    <t>0.111</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #191</t>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ja-JP (Verify Point #312)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource pt-BR (Verify Point #313)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for it-IT (Verify Point #314)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated apiKey (Verify Point #315)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for authDomain (Verify Point #316)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at projectId (Verify Point #317)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation storageBucket (Verify Point #318)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for messagingSenderId (Verify Point #319)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field appId (Verify Point #320)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for name (Verify Point #321)</t>
+  </si>
+  <si>
+    <t>0.093</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for id (Verify Point #322)</t>
+  </si>
+  <si>
+    <t>0.077</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for fees.min (Verify Point #323)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of fees.max (Verify Point #324)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for courses (Verify Point #325)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for ranking.nirf (Verify Point #326)</t>
+  </si>
+  <si>
+    <t>0.095</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value type (Verify Point #327)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users/uid001 (Verify Point #328)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier colleges/c001 (Verify Point #329)</t>
+  </si>
+  <si>
+    <t>0.110</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region prompt-length (Verify Point #330)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for session-id-1 (Verify Point #331)</t>
+  </si>
+  <si>
+    <t>0.096</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ₹1L (Verify Point #332)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource B.Tech (Verify Point #333)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for 4 years (Verify Point #334)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated Tamil Nadu (Verify Point #335)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for Chennai (Verify Point #336)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at llama3-8b (Verify Point #337)</t>
+  </si>
+  <si>
+    <t>0.100</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation email (Verify Point #338)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for password (Verify Point #339)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field displayName (Verify Point #340)</t>
+  </si>
+  <si>
+    <t>0.033</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for savedColleges (Verify Point #341)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for createdAt (Verify Point #342)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for firebase-auth (Verify Point #343)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of firestore-read (Verify Point #344)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for groq-api (Verify Point #345)</t>
+  </si>
+  <si>
+    <t>0.099</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for college-list (Verify Point #346)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value XSS-injection (Verify Point #347)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session SQL-injection (Verify Point #348)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier CSRF-token (Verify Point #349)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region CORS-origin (Verify Point #350)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for CSP-header (Verify Point #351)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code session-token (Verify Point #352)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users-ref (Verify Point #353)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for items-ref (Verify Point #354)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated de-DE (Verify Point #355)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for fr-FR (Verify Point #356)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ja-JP (Verify Point #357)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation pt-BR (Verify Point #358)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for it-IT (Verify Point #359)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field apiKey (Verify Point #360)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #361)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #362)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #363)</t>
+  </si>
+  <si>
+    <t>0.034</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #364)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #365)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #366)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #367)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #368)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #369)</t>
+  </si>
+  <si>
+    <t>0.087</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #370)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #371)</t>
+  </si>
+  <si>
+    <t>0.103</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #372)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #373)</t>
+  </si>
+  <si>
+    <t>0.054</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #374)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #375)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #376)</t>
   </si>
   <si>
     <t>0.113</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #192</t>
-  </si>
-  <si>
-    <t>0.060</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #193</t>
-  </si>
-  <si>
-    <t>0.090</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #194</t>
-  </si>
-  <si>
-    <t>0.030</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #195</t>
-  </si>
-  <si>
-    <t>0.024</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #196</t>
-  </si>
-  <si>
-    <t>0.083</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #197</t>
-  </si>
-  <si>
-    <t>0.033</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #198</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #199</t>
-  </si>
-  <si>
-    <t>0.107</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #200</t>
-  </si>
-  <si>
-    <t>0.050</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #201</t>
-  </si>
-  <si>
-    <t>0.078</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #202</t>
-  </si>
-  <si>
-    <t>0.026</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #203</t>
-  </si>
-  <si>
-    <t>0.063</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #204</t>
-  </si>
-  <si>
-    <t>0.082</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #205</t>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #377)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #378)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #379)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #380)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #381)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #382)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #383)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #384)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #385)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #386)</t>
+  </si>
+  <si>
+    <t>0.056</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #387)</t>
   </si>
   <si>
     <t>0.028</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #206</t>
-  </si>
-  <si>
-    <t>0.054</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #207</t>
-  </si>
-  <si>
-    <t>0.062</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #208</t>
-  </si>
-  <si>
-    <t>0.086</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #209</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #210</t>
-  </si>
-  <si>
-    <t>0.077</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #211</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #212</t>
-  </si>
-  <si>
-    <t>0.106</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #213</t>
-  </si>
-  <si>
-    <t>0.103</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #214</t>
-  </si>
-  <si>
-    <t>0.119</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #215</t>
-  </si>
-  <si>
-    <t>0.023</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #216</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #217</t>
-  </si>
-  <si>
-    <t>0.117</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #218</t>
-  </si>
-  <si>
-    <t>0.104</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #219</t>
-  </si>
-  <si>
-    <t>0.059</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #220</t>
-  </si>
-  <si>
-    <t>0.081</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #221</t>
-  </si>
-  <si>
-    <t>0.071</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #222</t>
-  </si>
-  <si>
-    <t>0.079</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #223</t>
-  </si>
-  <si>
-    <t>0.087</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #224</t>
-  </si>
-  <si>
-    <t>0.037</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #225</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #226</t>
-  </si>
-  <si>
-    <t>0.068</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #227</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #228</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #229</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #230</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #231</t>
-  </si>
-  <si>
-    <t>0.118</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #232</t>
-  </si>
-  <si>
-    <t>0.027</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #233</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #234</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #235</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #236</t>
-  </si>
-  <si>
-    <t>0.114</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #237</t>
-  </si>
-  <si>
-    <t>0.045</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #238</t>
-  </si>
-  <si>
-    <t>0.094</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #239</t>
-  </si>
-  <si>
-    <t>0.072</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #240</t>
-  </si>
-  <si>
-    <t>0.096</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #241</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #242</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #243</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #244</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #245</t>
-  </si>
-  <si>
-    <t>0.092</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #246</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #247</t>
-  </si>
-  <si>
-    <t>0.058</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #248</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #249</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #250</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #251</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #252</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #253</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #254</t>
-  </si>
-  <si>
-    <t>0.067</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #255</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #256</t>
-  </si>
-  <si>
-    <t>0.051</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #257</t>
-  </si>
-  <si>
-    <t>0.041</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #258</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #259</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #260</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #261</t>
-  </si>
-  <si>
-    <t>0.075</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #262</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #263</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #264</t>
-  </si>
-  <si>
-    <t>0.066</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #265</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #266</t>
-  </si>
-  <si>
-    <t>0.042</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #267</t>
-  </si>
-  <si>
-    <t>0.065</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #268</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #269</t>
-  </si>
-  <si>
-    <t>0.029</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #270</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #271</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #272</t>
-  </si>
-  <si>
-    <t>0.101</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #273</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #274</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #275</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #276</t>
-  </si>
-  <si>
-    <t>0.031</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #277</t>
-  </si>
-  <si>
-    <t>0.021</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #278</t>
-  </si>
-  <si>
-    <t>0.036</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #279</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #280</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #281</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #282</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #283</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #284</t>
-  </si>
-  <si>
-    <t>0.089</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #285</t>
-  </si>
-  <si>
-    <t>0.038</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #286</t>
-  </si>
-  <si>
-    <t>0.091</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #287</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #288</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #289</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #290</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #291</t>
-  </si>
-  <si>
-    <t>0.080</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #292</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #293</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #294</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #295</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #296</t>
-  </si>
-  <si>
-    <t>0.100</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #297</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #298</t>
-  </si>
-  <si>
-    <t>0.115</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #299</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #300</t>
-  </si>
-  <si>
-    <t>0.032</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #301</t>
-  </si>
-  <si>
-    <t>0.025</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #302</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #303</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #304</t>
-  </si>
-  <si>
-    <t>0.069</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #305</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #306</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #307</t>
-  </si>
-  <si>
-    <t>0.098</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #308</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #309</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #310</t>
-  </si>
-  <si>
-    <t>0.049</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #311</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #312</t>
-  </si>
-  <si>
-    <t>0.039</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #313</t>
-  </si>
-  <si>
-    <t>0.097</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #314</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #315</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #316</t>
-  </si>
-  <si>
-    <t>0.116</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #317</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #318</t>
-  </si>
-  <si>
-    <t>0.070</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #319</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #320</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #321</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #322</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #323</t>
-  </si>
-  <si>
-    <t>0.084</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #324</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #325</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #326</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #327</t>
-  </si>
-  <si>
-    <t>0.073</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #328</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #329</t>
-  </si>
-  <si>
-    <t>0.108</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #330</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #331</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #332</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #333</t>
-  </si>
-  <si>
-    <t>0.102</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #334</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #335</t>
-  </si>
-  <si>
-    <t>0.095</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #336</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #337</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #338</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #339</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #340</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #341</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #342</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #343</t>
-  </si>
-  <si>
-    <t>0.076</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #344</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #345</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #346</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #347</t>
-  </si>
-  <si>
-    <t>0.112</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #348</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #349</t>
-  </si>
-  <si>
-    <t>0.064</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #350</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #351</t>
-  </si>
-  <si>
-    <t>0.053</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #352</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #353</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #354</t>
-  </si>
-  <si>
-    <t>0.057</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #355</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #356</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #357</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #358</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #359</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #360</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #361</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #362</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #363</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #364</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #365</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #366</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #367</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #368</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #369</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #370</t>
-  </si>
-  <si>
-    <t>0.034</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #371</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #372</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #373</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #374</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #375</t>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #388)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #389)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #390)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #391)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code XSS-injection (Verify Point #392)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #393)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for CSRF-token (Verify Point #394)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated CORS-origin (Verify Point #395)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for CSP-header (Verify Point #396)</t>
   </si>
   <si>
     <t>0.074</t>
   </si>
   <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #376</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #377</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #378</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #379</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Auth]: Verify Firebase auth config field apiKey #380</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [College]: Verify college data field constraint for authDomain #381</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Users]: Verify user profile validation for projectId #382</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [AI Service]: Verify AI prompt constraint for name #383</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Validation]: Verify input sanitisation of id #384</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Regex]: Verify regex pattern match for fees.min #385</t>
-  </si>
-  <si>
-    <t>0.061</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Types]: Verify data type coercion for fees.max #386</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Boundary]: Verify boundary condition at courses #387</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Logic]: Verify sort/filter logic for ranking.nirf #388</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Ranking]: Verify search ranking algorithm for type #389</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Firestore]: Verify Firestore collection path for users/uid001 #390</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Compare]: Verify college comparison logic for colleges/c001 #391</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Saved]: Verify saved college list operation prompt-length #392</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Fees]: Verify fee formatting for value session-id-1 #393</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Chat]: Verify chat history append for session ₹1L #394</t>
-  </si>
-  <si>
-    <t>0.085</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Schema]: Verify college accreditation field for B.Tech #395</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [NIRF]: Verify NIRF rank ordering for tier 4 years #396</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Location]: Verify state/city filter for region Tamil Nadu #397</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Groq]: Verify Groq model name validation for Chennai #398</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — E2E [Error Handling]: Verify API error handling for code llama3-8b #399</t>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at session-token (Verify Point #397)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users-ref (Verify Point #398)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for items-ref (Verify Point #399)</t>
   </si>
   <si>
     <t>Field</t>
@@ -1526,13 +1511,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>17</t>
+    <t>18</t>
   </si>
   <si>
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 14:02:47 UTC</t>
+    <t>2026-06-23 14:24:49 UTC</t>
   </si>
   <si>
     <t>Branch</t>
@@ -1544,7 +1529,7 @@
     <t>Commit</t>
   </si>
   <si>
-    <t>d1d53d0</t>
+    <t>04fd2d2</t>
   </si>
   <si>
     <t>Total</t>
@@ -1999,7 +1984,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -2010,13 +1995,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -2027,13 +2012,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -2044,13 +2029,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -2061,13 +2046,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -2078,13 +2063,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -2101,7 +2086,7 @@
         <v>6</v>
       </c>
       <c r="D9" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -2118,7 +2103,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -2135,7 +2120,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -2152,7 +2137,7 @@
         <v>6</v>
       </c>
       <c r="D12" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -2169,7 +2154,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -2186,7 +2171,7 @@
         <v>6</v>
       </c>
       <c r="D14" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -2203,7 +2188,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -2220,7 +2205,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -2254,7 +2239,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -2271,7 +2256,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -2288,7 +2273,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -2305,7 +2290,7 @@
         <v>6</v>
       </c>
       <c r="D21" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -2322,7 +2307,7 @@
         <v>6</v>
       </c>
       <c r="D22" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -2339,7 +2324,7 @@
         <v>6</v>
       </c>
       <c r="D23" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -2356,7 +2341,7 @@
         <v>6</v>
       </c>
       <c r="D24" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -2373,7 +2358,7 @@
         <v>6</v>
       </c>
       <c r="D25" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -2390,7 +2375,7 @@
         <v>6</v>
       </c>
       <c r="D26" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -2407,7 +2392,7 @@
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -2424,7 +2409,7 @@
         <v>6</v>
       </c>
       <c r="D28" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -2441,7 +2426,7 @@
         <v>6</v>
       </c>
       <c r="D29" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -2458,7 +2443,7 @@
         <v>6</v>
       </c>
       <c r="D30" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -2492,7 +2477,7 @@
         <v>6</v>
       </c>
       <c r="D32" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -2509,7 +2494,7 @@
         <v>6</v>
       </c>
       <c r="D33" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -2526,7 +2511,7 @@
         <v>6</v>
       </c>
       <c r="D34" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -2543,7 +2528,7 @@
         <v>6</v>
       </c>
       <c r="D35" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -2560,7 +2545,7 @@
         <v>6</v>
       </c>
       <c r="D36" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -2577,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="D37" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -2594,7 +2579,7 @@
         <v>6</v>
       </c>
       <c r="D38" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -2611,7 +2596,7 @@
         <v>6</v>
       </c>
       <c r="D39" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -2628,7 +2613,7 @@
         <v>6</v>
       </c>
       <c r="D40" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -2645,7 +2630,7 @@
         <v>6</v>
       </c>
       <c r="D41" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -2662,7 +2647,7 @@
         <v>6</v>
       </c>
       <c r="D42" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -2696,7 +2681,7 @@
         <v>6</v>
       </c>
       <c r="D44" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -2713,7 +2698,7 @@
         <v>6</v>
       </c>
       <c r="D45" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -2730,7 +2715,7 @@
         <v>6</v>
       </c>
       <c r="D46" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -2747,7 +2732,7 @@
         <v>6</v>
       </c>
       <c r="D47" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -2764,7 +2749,7 @@
         <v>6</v>
       </c>
       <c r="D48" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -2781,7 +2766,7 @@
         <v>6</v>
       </c>
       <c r="D49" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -2798,7 +2783,7 @@
         <v>6</v>
       </c>
       <c r="D50" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -2815,7 +2800,7 @@
         <v>6</v>
       </c>
       <c r="D51" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -2832,7 +2817,7 @@
         <v>6</v>
       </c>
       <c r="D52" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -2849,7 +2834,7 @@
         <v>6</v>
       </c>
       <c r="D53" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -2866,7 +2851,7 @@
         <v>6</v>
       </c>
       <c r="D54" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -2883,7 +2868,7 @@
         <v>6</v>
       </c>
       <c r="D55" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
@@ -2900,7 +2885,7 @@
         <v>6</v>
       </c>
       <c r="D56" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -2917,7 +2902,7 @@
         <v>6</v>
       </c>
       <c r="D57" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -2934,7 +2919,7 @@
         <v>6</v>
       </c>
       <c r="D58" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -2951,7 +2936,7 @@
         <v>6</v>
       </c>
       <c r="D59" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
@@ -2968,7 +2953,7 @@
         <v>6</v>
       </c>
       <c r="D60" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
@@ -2985,7 +2970,7 @@
         <v>6</v>
       </c>
       <c r="D61" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
@@ -3002,7 +2987,7 @@
         <v>6</v>
       </c>
       <c r="D62" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
@@ -3019,7 +3004,7 @@
         <v>6</v>
       </c>
       <c r="D63" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
@@ -3036,7 +3021,7 @@
         <v>6</v>
       </c>
       <c r="D64" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E64" t="s">
         <v>8</v>
@@ -3053,7 +3038,7 @@
         <v>6</v>
       </c>
       <c r="D65" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E65" t="s">
         <v>8</v>
@@ -3070,7 +3055,7 @@
         <v>6</v>
       </c>
       <c r="D66" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
@@ -3087,7 +3072,7 @@
         <v>6</v>
       </c>
       <c r="D67" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
@@ -3104,7 +3089,7 @@
         <v>6</v>
       </c>
       <c r="D68" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
@@ -3121,7 +3106,7 @@
         <v>6</v>
       </c>
       <c r="D69" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E69" t="s">
         <v>8</v>
@@ -3138,7 +3123,7 @@
         <v>6</v>
       </c>
       <c r="D70" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
@@ -3155,7 +3140,7 @@
         <v>6</v>
       </c>
       <c r="D71" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
@@ -3172,7 +3157,7 @@
         <v>6</v>
       </c>
       <c r="D72" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
@@ -3189,7 +3174,7 @@
         <v>6</v>
       </c>
       <c r="D73" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E73" t="s">
         <v>8</v>
@@ -3206,7 +3191,7 @@
         <v>6</v>
       </c>
       <c r="D74" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E74" t="s">
         <v>8</v>
@@ -3223,7 +3208,7 @@
         <v>6</v>
       </c>
       <c r="D75" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
@@ -3240,7 +3225,7 @@
         <v>6</v>
       </c>
       <c r="D76" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E76" t="s">
         <v>8</v>
@@ -3274,7 +3259,7 @@
         <v>6</v>
       </c>
       <c r="D78" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
@@ -3291,7 +3276,7 @@
         <v>6</v>
       </c>
       <c r="D79" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E79" t="s">
         <v>8</v>
@@ -3308,7 +3293,7 @@
         <v>6</v>
       </c>
       <c r="D80" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E80" t="s">
         <v>8</v>
@@ -3325,7 +3310,7 @@
         <v>6</v>
       </c>
       <c r="D81" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
@@ -3342,7 +3327,7 @@
         <v>6</v>
       </c>
       <c r="D82" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
@@ -3359,7 +3344,7 @@
         <v>6</v>
       </c>
       <c r="D83" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E83" t="s">
         <v>8</v>
@@ -3376,7 +3361,7 @@
         <v>6</v>
       </c>
       <c r="D84" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
@@ -3393,7 +3378,7 @@
         <v>6</v>
       </c>
       <c r="D85" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
@@ -3410,7 +3395,7 @@
         <v>6</v>
       </c>
       <c r="D86" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
@@ -3427,7 +3412,7 @@
         <v>6</v>
       </c>
       <c r="D87" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E87" t="s">
         <v>8</v>
@@ -3444,7 +3429,7 @@
         <v>6</v>
       </c>
       <c r="D88" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E88" t="s">
         <v>8</v>
@@ -3461,7 +3446,7 @@
         <v>6</v>
       </c>
       <c r="D89" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
@@ -3478,7 +3463,7 @@
         <v>6</v>
       </c>
       <c r="D90" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E90" t="s">
         <v>8</v>
@@ -3495,7 +3480,7 @@
         <v>6</v>
       </c>
       <c r="D91" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E91" t="s">
         <v>8</v>
@@ -3512,7 +3497,7 @@
         <v>6</v>
       </c>
       <c r="D92" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E92" t="s">
         <v>8</v>
@@ -3529,7 +3514,7 @@
         <v>6</v>
       </c>
       <c r="D93" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E93" t="s">
         <v>8</v>
@@ -3546,7 +3531,7 @@
         <v>6</v>
       </c>
       <c r="D94" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E94" t="s">
         <v>8</v>
@@ -3563,7 +3548,7 @@
         <v>6</v>
       </c>
       <c r="D95" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E95" t="s">
         <v>8</v>
@@ -3580,7 +3565,7 @@
         <v>6</v>
       </c>
       <c r="D96" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E96" t="s">
         <v>8</v>
@@ -3597,7 +3582,7 @@
         <v>6</v>
       </c>
       <c r="D97" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E97" t="s">
         <v>8</v>
@@ -3614,7 +3599,7 @@
         <v>6</v>
       </c>
       <c r="D98" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E98" t="s">
         <v>8</v>
@@ -3631,7 +3616,7 @@
         <v>6</v>
       </c>
       <c r="D99" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
@@ -3648,7 +3633,7 @@
         <v>6</v>
       </c>
       <c r="D100" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E100" t="s">
         <v>8</v>
@@ -3665,7 +3650,7 @@
         <v>6</v>
       </c>
       <c r="D101" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E101" t="s">
         <v>8</v>
@@ -3682,7 +3667,7 @@
         <v>6</v>
       </c>
       <c r="D102" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E102" t="s">
         <v>8</v>
@@ -3699,7 +3684,7 @@
         <v>6</v>
       </c>
       <c r="D103" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E103" t="s">
         <v>8</v>
@@ -3733,7 +3718,7 @@
         <v>6</v>
       </c>
       <c r="D105" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E105" t="s">
         <v>8</v>
@@ -3750,7 +3735,7 @@
         <v>6</v>
       </c>
       <c r="D106" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E106" t="s">
         <v>8</v>
@@ -3767,7 +3752,7 @@
         <v>6</v>
       </c>
       <c r="D107" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
@@ -3784,7 +3769,7 @@
         <v>6</v>
       </c>
       <c r="D108" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E108" t="s">
         <v>8</v>
@@ -3801,7 +3786,7 @@
         <v>6</v>
       </c>
       <c r="D109" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E109" t="s">
         <v>8</v>
@@ -3818,7 +3803,7 @@
         <v>6</v>
       </c>
       <c r="D110" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E110" t="s">
         <v>8</v>
@@ -3835,7 +3820,7 @@
         <v>6</v>
       </c>
       <c r="D111" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E111" t="s">
         <v>8</v>
@@ -3852,7 +3837,7 @@
         <v>6</v>
       </c>
       <c r="D112" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E112" t="s">
         <v>8</v>
@@ -3869,7 +3854,7 @@
         <v>6</v>
       </c>
       <c r="D113" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E113" t="s">
         <v>8</v>
@@ -3886,7 +3871,7 @@
         <v>6</v>
       </c>
       <c r="D114" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E114" t="s">
         <v>8</v>
@@ -3903,7 +3888,7 @@
         <v>6</v>
       </c>
       <c r="D115" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E115" t="s">
         <v>8</v>
@@ -3920,7 +3905,7 @@
         <v>6</v>
       </c>
       <c r="D116" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E116" t="s">
         <v>8</v>
@@ -3937,7 +3922,7 @@
         <v>6</v>
       </c>
       <c r="D117" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E117" t="s">
         <v>8</v>
@@ -3954,7 +3939,7 @@
         <v>6</v>
       </c>
       <c r="D118" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E118" t="s">
         <v>8</v>
@@ -3971,7 +3956,7 @@
         <v>6</v>
       </c>
       <c r="D119" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E119" t="s">
         <v>8</v>
@@ -3988,7 +3973,7 @@
         <v>6</v>
       </c>
       <c r="D120" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E120" t="s">
         <v>8</v>
@@ -4005,7 +3990,7 @@
         <v>6</v>
       </c>
       <c r="D121" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E121" t="s">
         <v>8</v>
@@ -4022,7 +4007,7 @@
         <v>6</v>
       </c>
       <c r="D122" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E122" t="s">
         <v>8</v>
@@ -4039,7 +4024,7 @@
         <v>6</v>
       </c>
       <c r="D123" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E123" t="s">
         <v>8</v>
@@ -4056,7 +4041,7 @@
         <v>6</v>
       </c>
       <c r="D124" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E124" t="s">
         <v>8</v>
@@ -4073,7 +4058,7 @@
         <v>6</v>
       </c>
       <c r="D125" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E125" t="s">
         <v>8</v>
@@ -4090,7 +4075,7 @@
         <v>6</v>
       </c>
       <c r="D126" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E126" t="s">
         <v>8</v>
@@ -4107,7 +4092,7 @@
         <v>6</v>
       </c>
       <c r="D127" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E127" t="s">
         <v>8</v>
@@ -4124,7 +4109,7 @@
         <v>6</v>
       </c>
       <c r="D128" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E128" t="s">
         <v>8</v>
@@ -4141,7 +4126,7 @@
         <v>6</v>
       </c>
       <c r="D129" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E129" t="s">
         <v>8</v>
@@ -4158,7 +4143,7 @@
         <v>6</v>
       </c>
       <c r="D130" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E130" t="s">
         <v>8</v>
@@ -4175,7 +4160,7 @@
         <v>6</v>
       </c>
       <c r="D131" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E131" t="s">
         <v>8</v>
@@ -4192,7 +4177,7 @@
         <v>6</v>
       </c>
       <c r="D132" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E132" t="s">
         <v>8</v>
@@ -4209,7 +4194,7 @@
         <v>6</v>
       </c>
       <c r="D133" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E133" t="s">
         <v>8</v>
@@ -4226,7 +4211,7 @@
         <v>6</v>
       </c>
       <c r="D134" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E134" t="s">
         <v>8</v>
@@ -4243,7 +4228,7 @@
         <v>6</v>
       </c>
       <c r="D135" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E135" t="s">
         <v>8</v>
@@ -4260,7 +4245,7 @@
         <v>6</v>
       </c>
       <c r="D136" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E136" t="s">
         <v>8</v>
@@ -4277,7 +4262,7 @@
         <v>6</v>
       </c>
       <c r="D137" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E137" t="s">
         <v>8</v>
@@ -4294,7 +4279,7 @@
         <v>6</v>
       </c>
       <c r="D138" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E138" t="s">
         <v>8</v>
@@ -4311,7 +4296,7 @@
         <v>6</v>
       </c>
       <c r="D139" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E139" t="s">
         <v>8</v>
@@ -4328,7 +4313,7 @@
         <v>6</v>
       </c>
       <c r="D140" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E140" t="s">
         <v>8</v>
@@ -4345,7 +4330,7 @@
         <v>6</v>
       </c>
       <c r="D141" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E141" t="s">
         <v>8</v>
@@ -4362,7 +4347,7 @@
         <v>6</v>
       </c>
       <c r="D142" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E142" t="s">
         <v>8</v>
@@ -4379,7 +4364,7 @@
         <v>6</v>
       </c>
       <c r="D143" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E143" t="s">
         <v>8</v>
@@ -4396,7 +4381,7 @@
         <v>6</v>
       </c>
       <c r="D144" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E144" t="s">
         <v>8</v>
@@ -4413,7 +4398,7 @@
         <v>6</v>
       </c>
       <c r="D145" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E145" t="s">
         <v>8</v>
@@ -4430,7 +4415,7 @@
         <v>6</v>
       </c>
       <c r="D146" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E146" t="s">
         <v>8</v>
@@ -4447,7 +4432,7 @@
         <v>6</v>
       </c>
       <c r="D147" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E147" t="s">
         <v>8</v>
@@ -4464,7 +4449,7 @@
         <v>6</v>
       </c>
       <c r="D148" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E148" t="s">
         <v>8</v>
@@ -4481,7 +4466,7 @@
         <v>6</v>
       </c>
       <c r="D149" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E149" t="s">
         <v>8</v>
@@ -4498,7 +4483,7 @@
         <v>6</v>
       </c>
       <c r="D150" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E150" t="s">
         <v>8</v>
@@ -4515,7 +4500,7 @@
         <v>6</v>
       </c>
       <c r="D151" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E151" t="s">
         <v>8</v>
@@ -4532,7 +4517,7 @@
         <v>6</v>
       </c>
       <c r="D152" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E152" t="s">
         <v>8</v>
@@ -4549,7 +4534,7 @@
         <v>6</v>
       </c>
       <c r="D153" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E153" t="s">
         <v>8</v>
@@ -4566,7 +4551,7 @@
         <v>6</v>
       </c>
       <c r="D154" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E154" t="s">
         <v>8</v>
@@ -4583,7 +4568,7 @@
         <v>6</v>
       </c>
       <c r="D155" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E155" t="s">
         <v>8</v>
@@ -4600,7 +4585,7 @@
         <v>6</v>
       </c>
       <c r="D156" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E156" t="s">
         <v>8</v>
@@ -4617,7 +4602,7 @@
         <v>6</v>
       </c>
       <c r="D157" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E157" t="s">
         <v>8</v>
@@ -4634,7 +4619,7 @@
         <v>6</v>
       </c>
       <c r="D158" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E158" t="s">
         <v>8</v>
@@ -4651,7 +4636,7 @@
         <v>6</v>
       </c>
       <c r="D159" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E159" t="s">
         <v>8</v>
@@ -4668,7 +4653,7 @@
         <v>6</v>
       </c>
       <c r="D160" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E160" t="s">
         <v>8</v>
@@ -4685,7 +4670,7 @@
         <v>6</v>
       </c>
       <c r="D161" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E161" t="s">
         <v>8</v>
@@ -4702,7 +4687,7 @@
         <v>6</v>
       </c>
       <c r="D162" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E162" t="s">
         <v>8</v>
@@ -4719,7 +4704,7 @@
         <v>6</v>
       </c>
       <c r="D163" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E163" t="s">
         <v>8</v>
@@ -4736,7 +4721,7 @@
         <v>6</v>
       </c>
       <c r="D164" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E164" t="s">
         <v>8</v>
@@ -4753,7 +4738,7 @@
         <v>6</v>
       </c>
       <c r="D165" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E165" t="s">
         <v>8</v>
@@ -4770,7 +4755,7 @@
         <v>6</v>
       </c>
       <c r="D166" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E166" t="s">
         <v>8</v>
@@ -4787,7 +4772,7 @@
         <v>6</v>
       </c>
       <c r="D167" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E167" t="s">
         <v>8</v>
@@ -4804,7 +4789,7 @@
         <v>6</v>
       </c>
       <c r="D168" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E168" t="s">
         <v>8</v>
@@ -4821,7 +4806,7 @@
         <v>6</v>
       </c>
       <c r="D169" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E169" t="s">
         <v>8</v>
@@ -4838,7 +4823,7 @@
         <v>6</v>
       </c>
       <c r="D170" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E170" t="s">
         <v>8</v>
@@ -4855,7 +4840,7 @@
         <v>6</v>
       </c>
       <c r="D171" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E171" t="s">
         <v>8</v>
@@ -4872,7 +4857,7 @@
         <v>6</v>
       </c>
       <c r="D172" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E172" t="s">
         <v>8</v>
@@ -4889,7 +4874,7 @@
         <v>6</v>
       </c>
       <c r="D173" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E173" t="s">
         <v>8</v>
@@ -4906,7 +4891,7 @@
         <v>6</v>
       </c>
       <c r="D174" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E174" t="s">
         <v>8</v>
@@ -4923,7 +4908,7 @@
         <v>6</v>
       </c>
       <c r="D175" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E175" t="s">
         <v>8</v>
@@ -4940,7 +4925,7 @@
         <v>6</v>
       </c>
       <c r="D176" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E176" t="s">
         <v>8</v>
@@ -4957,7 +4942,7 @@
         <v>6</v>
       </c>
       <c r="D177" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E177" t="s">
         <v>8</v>
@@ -4974,7 +4959,7 @@
         <v>6</v>
       </c>
       <c r="D178" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E178" t="s">
         <v>8</v>
@@ -4991,7 +4976,7 @@
         <v>6</v>
       </c>
       <c r="D179" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E179" t="s">
         <v>8</v>
@@ -5008,7 +4993,7 @@
         <v>6</v>
       </c>
       <c r="D180" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E180" t="s">
         <v>8</v>
@@ -5025,7 +5010,7 @@
         <v>6</v>
       </c>
       <c r="D181" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E181" t="s">
         <v>8</v>
@@ -5195,7 +5180,7 @@
         <v>6</v>
       </c>
       <c r="D191" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="E191" t="s">
         <v>8</v>
@@ -5206,13 +5191,13 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
+        <v>208</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D192" t="s">
         <v>209</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D192" t="s">
-        <v>210</v>
       </c>
       <c r="E192" t="s">
         <v>8</v>
@@ -5223,13 +5208,13 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
+        <v>210</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D193" t="s">
         <v>211</v>
-      </c>
-      <c r="C193" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D193" t="s">
-        <v>212</v>
       </c>
       <c r="E193" t="s">
         <v>8</v>
@@ -5240,13 +5225,13 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
+        <v>212</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D194" t="s">
         <v>213</v>
-      </c>
-      <c r="C194" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D194" t="s">
-        <v>214</v>
       </c>
       <c r="E194" t="s">
         <v>8</v>
@@ -5257,13 +5242,13 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D195" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E195" t="s">
         <v>8</v>
@@ -5274,13 +5259,13 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D196" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E196" t="s">
         <v>8</v>
@@ -5291,13 +5276,13 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D197" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E197" t="s">
         <v>8</v>
@@ -5308,13 +5293,13 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D198" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E198" t="s">
         <v>8</v>
@@ -5325,13 +5310,13 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D199" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E199" t="s">
         <v>8</v>
@@ -5342,13 +5327,13 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D200" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="E200" t="s">
         <v>8</v>
@@ -5359,13 +5344,13 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
+        <v>225</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D201" t="s">
         <v>226</v>
-      </c>
-      <c r="C201" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D201" t="s">
-        <v>227</v>
       </c>
       <c r="E201" t="s">
         <v>8</v>
@@ -5376,13 +5361,13 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D202" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="E202" t="s">
         <v>8</v>
@@ -5393,13 +5378,13 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D203" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E203" t="s">
         <v>8</v>
@@ -5410,13 +5395,13 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D204" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E204" t="s">
         <v>8</v>
@@ -5427,13 +5412,13 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D205" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E205" t="s">
         <v>8</v>
@@ -5444,13 +5429,13 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D206" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="E206" t="s">
         <v>8</v>
@@ -5461,13 +5446,13 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D207" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E207" t="s">
         <v>8</v>
@@ -5478,13 +5463,13 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D208" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="E208" t="s">
         <v>8</v>
@@ -5495,13 +5480,13 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D209" t="s">
-        <v>243</v>
+        <v>213</v>
       </c>
       <c r="E209" t="s">
         <v>8</v>
@@ -5512,13 +5497,13 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D210" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E210" t="s">
         <v>8</v>
@@ -5529,13 +5514,13 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D211" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E211" t="s">
         <v>8</v>
@@ -5546,13 +5531,13 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D212" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E212" t="s">
         <v>8</v>
@@ -5563,13 +5548,13 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D213" t="s">
-        <v>220</v>
+        <v>247</v>
       </c>
       <c r="E213" t="s">
         <v>8</v>
@@ -5580,13 +5565,13 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D214" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E214" t="s">
         <v>8</v>
@@ -5597,13 +5582,13 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D215" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E215" t="s">
         <v>8</v>
@@ -5614,13 +5599,13 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D216" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="E216" t="s">
         <v>8</v>
@@ -5631,13 +5616,13 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D217" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E217" t="s">
         <v>8</v>
@@ -5648,13 +5633,13 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D218" t="s">
-        <v>218</v>
+        <v>256</v>
       </c>
       <c r="E218" t="s">
         <v>8</v>
@@ -5665,13 +5650,13 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D219" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E219" t="s">
         <v>8</v>
@@ -5682,13 +5667,13 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D220" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="E220" t="s">
         <v>8</v>
@@ -5699,13 +5684,13 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D221" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E221" t="s">
         <v>8</v>
@@ -5716,13 +5701,13 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D222" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E222" t="s">
         <v>8</v>
@@ -5733,13 +5718,13 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D223" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="E223" t="s">
         <v>8</v>
@@ -5750,13 +5735,13 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D224" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="E224" t="s">
         <v>8</v>
@@ -5767,13 +5752,13 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D225" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="E225" t="s">
         <v>8</v>
@@ -5784,13 +5769,13 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D226" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="E226" t="s">
         <v>8</v>
@@ -5801,13 +5786,13 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D227" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="E227" t="s">
         <v>8</v>
@@ -5818,13 +5803,13 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D228" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="E228" t="s">
         <v>8</v>
@@ -5835,13 +5820,13 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D229" t="s">
-        <v>210</v>
+        <v>275</v>
       </c>
       <c r="E229" t="s">
         <v>8</v>
@@ -5852,13 +5837,13 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D230" t="s">
-        <v>270</v>
+        <v>192</v>
       </c>
       <c r="E230" t="s">
         <v>8</v>
@@ -5869,13 +5854,13 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D231" t="s">
-        <v>222</v>
+        <v>278</v>
       </c>
       <c r="E231" t="s">
         <v>8</v>
@@ -5886,13 +5871,13 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D232" t="s">
-        <v>216</v>
+        <v>280</v>
       </c>
       <c r="E232" t="s">
         <v>8</v>
@@ -5903,13 +5888,13 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D233" t="s">
-        <v>283</v>
+        <v>251</v>
       </c>
       <c r="E233" t="s">
         <v>8</v>
@@ -5920,13 +5905,13 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D234" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="E234" t="s">
         <v>8</v>
@@ -5937,13 +5922,13 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D235" t="s">
-        <v>218</v>
+        <v>284</v>
       </c>
       <c r="E235" t="s">
         <v>8</v>
@@ -5954,13 +5939,13 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D236" t="s">
-        <v>208</v>
+        <v>286</v>
       </c>
       <c r="E236" t="s">
         <v>8</v>
@@ -5971,13 +5956,13 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
+        <v>287</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D237" t="s">
         <v>288</v>
-      </c>
-      <c r="C237" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D237" t="s">
-        <v>241</v>
       </c>
       <c r="E237" t="s">
         <v>8</v>
@@ -5994,7 +5979,7 @@
         <v>6</v>
       </c>
       <c r="D238" t="s">
-        <v>290</v>
+        <v>220</v>
       </c>
       <c r="E238" t="s">
         <v>8</v>
@@ -6005,13 +5990,13 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D239" t="s">
-        <v>292</v>
+        <v>213</v>
       </c>
       <c r="E239" t="s">
         <v>8</v>
@@ -6022,13 +6007,13 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D240" t="s">
-        <v>294</v>
+        <v>241</v>
       </c>
       <c r="E240" t="s">
         <v>8</v>
@@ -6039,13 +6024,13 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D241" t="s">
-        <v>296</v>
+        <v>236</v>
       </c>
       <c r="E241" t="s">
         <v>8</v>
@@ -6056,13 +6041,13 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D242" t="s">
-        <v>298</v>
+        <v>198</v>
       </c>
       <c r="E242" t="s">
         <v>8</v>
@@ -6073,13 +6058,13 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D243" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="E243" t="s">
         <v>8</v>
@@ -6090,13 +6075,13 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D244" t="s">
-        <v>233</v>
+        <v>267</v>
       </c>
       <c r="E244" t="s">
         <v>8</v>
@@ -6107,13 +6092,13 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D245" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="E245" t="s">
         <v>8</v>
@@ -6124,13 +6109,13 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D246" t="s">
-        <v>268</v>
+        <v>298</v>
       </c>
       <c r="E246" t="s">
         <v>8</v>
@@ -6141,13 +6126,13 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D247" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E247" t="s">
         <v>8</v>
@@ -6158,13 +6143,13 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D248" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="E248" t="s">
         <v>8</v>
@@ -6175,13 +6160,13 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D249" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="E249" t="s">
         <v>8</v>
@@ -6192,13 +6177,13 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D250" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="E250" t="s">
         <v>8</v>
@@ -6209,13 +6194,13 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D251" t="s">
-        <v>227</v>
+        <v>303</v>
       </c>
       <c r="E251" t="s">
         <v>8</v>
@@ -6226,13 +6211,13 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D252" t="s">
-        <v>196</v>
+        <v>308</v>
       </c>
       <c r="E252" t="s">
         <v>8</v>
@@ -6243,13 +6228,13 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D253" t="s">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="E253" t="s">
         <v>8</v>
@@ -6260,13 +6245,13 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D254" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="E254" t="s">
         <v>8</v>
@@ -6277,13 +6262,13 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D255" t="s">
-        <v>251</v>
+        <v>270</v>
       </c>
       <c r="E255" t="s">
         <v>8</v>
@@ -6294,13 +6279,13 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
+        <v>313</v>
+      </c>
+      <c r="C256" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D256" t="s">
         <v>314</v>
-      </c>
-      <c r="C256" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D256" t="s">
-        <v>315</v>
       </c>
       <c r="E256" t="s">
         <v>8</v>
@@ -6311,13 +6296,13 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D257" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="E257" t="s">
         <v>8</v>
@@ -6328,13 +6313,13 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
+        <v>316</v>
+      </c>
+      <c r="C258" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D258" t="s">
         <v>317</v>
-      </c>
-      <c r="C258" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D258" t="s">
-        <v>318</v>
       </c>
       <c r="E258" t="s">
         <v>8</v>
@@ -6345,13 +6330,13 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
+        <v>318</v>
+      </c>
+      <c r="C259" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D259" t="s">
         <v>319</v>
-      </c>
-      <c r="C259" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D259" t="s">
-        <v>320</v>
       </c>
       <c r="E259" t="s">
         <v>8</v>
@@ -6362,13 +6347,13 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D260" t="s">
-        <v>292</v>
+        <v>251</v>
       </c>
       <c r="E260" t="s">
         <v>8</v>
@@ -6379,13 +6364,13 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D261" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="E261" t="s">
         <v>8</v>
@@ -6396,13 +6381,13 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
+        <v>322</v>
+      </c>
+      <c r="C262" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D262" t="s">
         <v>323</v>
-      </c>
-      <c r="C262" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D262" t="s">
-        <v>264</v>
       </c>
       <c r="E262" t="s">
         <v>8</v>
@@ -6436,7 +6421,7 @@
         <v>6</v>
       </c>
       <c r="D264" t="s">
-        <v>210</v>
+        <v>327</v>
       </c>
       <c r="E264" t="s">
         <v>8</v>
@@ -6447,13 +6432,13 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D265" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="E265" t="s">
         <v>8</v>
@@ -6464,13 +6449,13 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D266" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E266" t="s">
         <v>8</v>
@@ -6481,13 +6466,13 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D267" t="s">
-        <v>229</v>
+        <v>273</v>
       </c>
       <c r="E267" t="s">
         <v>8</v>
@@ -6498,13 +6483,13 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D268" t="s">
-        <v>332</v>
+        <v>206</v>
       </c>
       <c r="E268" t="s">
         <v>8</v>
@@ -6521,7 +6506,7 @@
         <v>6</v>
       </c>
       <c r="D269" t="s">
-        <v>334</v>
+        <v>273</v>
       </c>
       <c r="E269" t="s">
         <v>8</v>
@@ -6532,13 +6517,13 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
+        <v>334</v>
+      </c>
+      <c r="C270" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D270" t="s">
         <v>335</v>
-      </c>
-      <c r="C270" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D270" t="s">
-        <v>325</v>
       </c>
       <c r="E270" t="s">
         <v>8</v>
@@ -6555,7 +6540,7 @@
         <v>6</v>
       </c>
       <c r="D271" t="s">
-        <v>337</v>
+        <v>194</v>
       </c>
       <c r="E271" t="s">
         <v>8</v>
@@ -6566,13 +6551,13 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D272" t="s">
-        <v>237</v>
+        <v>275</v>
       </c>
       <c r="E272" t="s">
         <v>8</v>
@@ -6583,13 +6568,13 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
+        <v>338</v>
+      </c>
+      <c r="C273" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D273" t="s">
         <v>339</v>
-      </c>
-      <c r="C273" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D273" t="s">
-        <v>266</v>
       </c>
       <c r="E273" t="s">
         <v>8</v>
@@ -6623,7 +6608,7 @@
         <v>6</v>
       </c>
       <c r="D275" t="s">
-        <v>202</v>
+        <v>288</v>
       </c>
       <c r="E275" t="s">
         <v>8</v>
@@ -6640,7 +6625,7 @@
         <v>6</v>
       </c>
       <c r="D276" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="E276" t="s">
         <v>8</v>
@@ -6651,13 +6636,13 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D277" t="s">
-        <v>235</v>
+        <v>263</v>
       </c>
       <c r="E277" t="s">
         <v>8</v>
@@ -6668,13 +6653,13 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D278" t="s">
-        <v>346</v>
+        <v>254</v>
       </c>
       <c r="E278" t="s">
         <v>8</v>
@@ -6708,7 +6693,7 @@
         <v>6</v>
       </c>
       <c r="D280" t="s">
-        <v>350</v>
+        <v>198</v>
       </c>
       <c r="E280" t="s">
         <v>8</v>
@@ -6719,13 +6704,13 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D281" t="s">
-        <v>341</v>
+        <v>263</v>
       </c>
       <c r="E281" t="s">
         <v>8</v>
@@ -6736,13 +6721,13 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D282" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="E282" t="s">
         <v>8</v>
@@ -6753,13 +6738,13 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D283" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="E283" t="s">
         <v>8</v>
@@ -6770,13 +6755,13 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D284" t="s">
-        <v>296</v>
+        <v>265</v>
       </c>
       <c r="E284" t="s">
         <v>8</v>
@@ -6787,13 +6772,13 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D285" t="s">
-        <v>210</v>
+        <v>263</v>
       </c>
       <c r="E285" t="s">
         <v>8</v>
@@ -6804,13 +6789,13 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
+        <v>355</v>
+      </c>
+      <c r="C286" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D286" t="s">
         <v>356</v>
-      </c>
-      <c r="C286" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D286" t="s">
-        <v>357</v>
       </c>
       <c r="E286" t="s">
         <v>8</v>
@@ -6821,13 +6806,13 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D287" t="s">
-        <v>359</v>
+        <v>263</v>
       </c>
       <c r="E287" t="s">
         <v>8</v>
@@ -6838,13 +6823,13 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D288" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E288" t="s">
         <v>8</v>
@@ -6855,13 +6840,13 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D289" t="s">
-        <v>227</v>
+        <v>270</v>
       </c>
       <c r="E289" t="s">
         <v>8</v>
@@ -6872,13 +6857,13 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D290" t="s">
-        <v>274</v>
+        <v>311</v>
       </c>
       <c r="E290" t="s">
         <v>8</v>
@@ -6889,13 +6874,13 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D291" t="s">
-        <v>315</v>
+        <v>298</v>
       </c>
       <c r="E291" t="s">
         <v>8</v>
@@ -6906,13 +6891,13 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D292" t="s">
-        <v>283</v>
+        <v>364</v>
       </c>
       <c r="E292" t="s">
         <v>8</v>
@@ -6923,13 +6908,13 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
+        <v>365</v>
+      </c>
+      <c r="C293" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D293" t="s">
         <v>366</v>
-      </c>
-      <c r="C293" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D293" t="s">
-        <v>367</v>
       </c>
       <c r="E293" t="s">
         <v>8</v>
@@ -6940,13 +6925,13 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D294" t="s">
-        <v>200</v>
+        <v>286</v>
       </c>
       <c r="E294" t="s">
         <v>8</v>
@@ -6957,13 +6942,13 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D295" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="E295" t="s">
         <v>8</v>
@@ -6974,13 +6959,13 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D296" t="s">
-        <v>218</v>
+        <v>247</v>
       </c>
       <c r="E296" t="s">
         <v>8</v>
@@ -6991,13 +6976,13 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D297" t="s">
-        <v>283</v>
+        <v>218</v>
       </c>
       <c r="E297" t="s">
         <v>8</v>
@@ -7008,13 +6993,13 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D298" t="s">
-        <v>373</v>
+        <v>278</v>
       </c>
       <c r="E298" t="s">
         <v>8</v>
@@ -7025,13 +7010,13 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D299" t="s">
-        <v>251</v>
+        <v>278</v>
       </c>
       <c r="E299" t="s">
         <v>8</v>
@@ -7042,13 +7027,13 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D300" t="s">
-        <v>376</v>
+        <v>213</v>
       </c>
       <c r="E300" t="s">
         <v>8</v>
@@ -7059,13 +7044,13 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D301" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E301" t="s">
         <v>8</v>
@@ -7076,13 +7061,13 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D302" t="s">
-        <v>379</v>
+        <v>236</v>
       </c>
       <c r="E302" t="s">
         <v>8</v>
@@ -7093,13 +7078,13 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D303" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E303" t="s">
         <v>8</v>
@@ -7110,13 +7095,13 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D304" t="s">
-        <v>325</v>
+        <v>298</v>
       </c>
       <c r="E304" t="s">
         <v>8</v>
@@ -7127,13 +7112,13 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D305" t="s">
-        <v>320</v>
+        <v>380</v>
       </c>
       <c r="E305" t="s">
         <v>8</v>
@@ -7144,13 +7129,13 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D306" t="s">
-        <v>385</v>
+        <v>231</v>
       </c>
       <c r="E306" t="s">
         <v>8</v>
@@ -7161,13 +7146,13 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D307" t="s">
-        <v>262</v>
+        <v>383</v>
       </c>
       <c r="E307" t="s">
         <v>8</v>
@@ -7178,13 +7163,13 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D308" t="s">
-        <v>332</v>
+        <v>305</v>
       </c>
       <c r="E308" t="s">
         <v>8</v>
@@ -7195,13 +7180,13 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D309" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E309" t="s">
         <v>8</v>
@@ -7212,13 +7197,13 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D310" t="s">
-        <v>200</v>
+        <v>286</v>
       </c>
       <c r="E310" t="s">
         <v>8</v>
@@ -7229,13 +7214,13 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D311" t="s">
-        <v>318</v>
+        <v>251</v>
       </c>
       <c r="E311" t="s">
         <v>8</v>
@@ -7246,13 +7231,13 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D312" t="s">
-        <v>393</v>
+        <v>261</v>
       </c>
       <c r="E312" t="s">
         <v>8</v>
@@ -7263,13 +7248,13 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D313" t="s">
-        <v>224</v>
+        <v>391</v>
       </c>
       <c r="E313" t="s">
         <v>8</v>
@@ -7280,13 +7265,13 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D314" t="s">
-        <v>396</v>
+        <v>192</v>
       </c>
       <c r="E314" t="s">
         <v>8</v>
@@ -7297,13 +7282,13 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D315" t="s">
-        <v>398</v>
+        <v>238</v>
       </c>
       <c r="E315" t="s">
         <v>8</v>
@@ -7314,13 +7299,13 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D316" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="E316" t="s">
         <v>8</v>
@@ -7331,13 +7316,13 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D317" t="s">
-        <v>255</v>
+        <v>194</v>
       </c>
       <c r="E317" t="s">
         <v>8</v>
@@ -7348,13 +7333,13 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D318" t="s">
-        <v>402</v>
+        <v>202</v>
       </c>
       <c r="E318" t="s">
         <v>8</v>
@@ -7365,13 +7350,13 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D319" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E319" t="s">
         <v>8</v>
@@ -7382,13 +7367,13 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D320" t="s">
-        <v>405</v>
+        <v>211</v>
       </c>
       <c r="E320" t="s">
         <v>8</v>
@@ -7399,13 +7384,13 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D321" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="E321" t="s">
         <v>8</v>
@@ -7416,13 +7401,13 @@
         <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D322" t="s">
-        <v>208</v>
+        <v>359</v>
       </c>
       <c r="E322" t="s">
         <v>8</v>
@@ -7433,13 +7418,13 @@
         <v>322</v>
       </c>
       <c r="B323" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D323" t="s">
-        <v>325</v>
+        <v>402</v>
       </c>
       <c r="E323" t="s">
         <v>8</v>
@@ -7450,13 +7435,13 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D324" t="s">
-        <v>337</v>
+        <v>404</v>
       </c>
       <c r="E324" t="s">
         <v>8</v>
@@ -7467,13 +7452,13 @@
         <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D325" t="s">
-        <v>411</v>
+        <v>220</v>
       </c>
       <c r="E325" t="s">
         <v>8</v>
@@ -7484,13 +7469,13 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D326" t="s">
-        <v>202</v>
+        <v>359</v>
       </c>
       <c r="E326" t="s">
         <v>8</v>
@@ -7501,13 +7486,13 @@
         <v>326</v>
       </c>
       <c r="B327" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D327" t="s">
-        <v>214</v>
+        <v>263</v>
       </c>
       <c r="E327" t="s">
         <v>8</v>
@@ -7518,13 +7503,13 @@
         <v>327</v>
       </c>
       <c r="B328" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D328" t="s">
-        <v>255</v>
+        <v>409</v>
       </c>
       <c r="E328" t="s">
         <v>8</v>
@@ -7535,13 +7520,13 @@
         <v>328</v>
       </c>
       <c r="B329" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D329" t="s">
-        <v>416</v>
+        <v>402</v>
       </c>
       <c r="E329" t="s">
         <v>8</v>
@@ -7552,13 +7537,13 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D330" t="s">
-        <v>257</v>
+        <v>200</v>
       </c>
       <c r="E330" t="s">
         <v>8</v>
@@ -7569,13 +7554,13 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D331" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="E331" t="s">
         <v>8</v>
@@ -7586,13 +7571,13 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D332" t="s">
-        <v>231</v>
+        <v>344</v>
       </c>
       <c r="E332" t="s">
         <v>8</v>
@@ -7603,13 +7588,13 @@
         <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D333" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="E333" t="s">
         <v>8</v>
@@ -7620,13 +7605,13 @@
         <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D334" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E334" t="s">
         <v>8</v>
@@ -7637,13 +7622,13 @@
         <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D335" t="s">
-        <v>424</v>
+        <v>224</v>
       </c>
       <c r="E335" t="s">
         <v>8</v>
@@ -7654,13 +7639,13 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D336" t="s">
-        <v>277</v>
+        <v>245</v>
       </c>
       <c r="E336" t="s">
         <v>8</v>
@@ -7671,13 +7656,13 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D337" t="s">
-        <v>427</v>
+        <v>323</v>
       </c>
       <c r="E337" t="s">
         <v>8</v>
@@ -7688,13 +7673,13 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D338" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="E338" t="s">
         <v>8</v>
@@ -7705,13 +7690,13 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D339" t="s">
-        <v>320</v>
+        <v>423</v>
       </c>
       <c r="E339" t="s">
         <v>8</v>
@@ -7722,13 +7707,13 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D340" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="E340" t="s">
         <v>8</v>
@@ -7739,13 +7724,13 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D341" t="s">
-        <v>257</v>
+        <v>286</v>
       </c>
       <c r="E341" t="s">
         <v>8</v>
@@ -7756,13 +7741,13 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D342" t="s">
-        <v>329</v>
+        <v>427</v>
       </c>
       <c r="E342" t="s">
         <v>8</v>
@@ -7773,13 +7758,13 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D343" t="s">
-        <v>264</v>
+        <v>416</v>
       </c>
       <c r="E343" t="s">
         <v>8</v>
@@ -7790,13 +7775,13 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D344" t="s">
-        <v>270</v>
+        <v>325</v>
       </c>
       <c r="E344" t="s">
         <v>8</v>
@@ -7807,13 +7792,13 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D345" t="s">
-        <v>436</v>
+        <v>416</v>
       </c>
       <c r="E345" t="s">
         <v>8</v>
@@ -7824,13 +7809,13 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D346" t="s">
-        <v>381</v>
+        <v>202</v>
       </c>
       <c r="E346" t="s">
         <v>8</v>
@@ -7841,13 +7826,13 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D347" t="s">
-        <v>381</v>
+        <v>433</v>
       </c>
       <c r="E347" t="s">
         <v>8</v>
@@ -7858,13 +7843,13 @@
         <v>347</v>
       </c>
       <c r="B348" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D348" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="E348" t="s">
         <v>8</v>
@@ -7875,13 +7860,13 @@
         <v>348</v>
       </c>
       <c r="B349" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D349" t="s">
-        <v>441</v>
+        <v>233</v>
       </c>
       <c r="E349" t="s">
         <v>8</v>
@@ -7892,13 +7877,13 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D350" t="s">
-        <v>436</v>
+        <v>247</v>
       </c>
       <c r="E350" t="s">
         <v>8</v>
@@ -7909,13 +7894,13 @@
         <v>350</v>
       </c>
       <c r="B351" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D351" t="s">
-        <v>444</v>
+        <v>391</v>
       </c>
       <c r="E351" t="s">
         <v>8</v>
@@ -7926,13 +7911,13 @@
         <v>351</v>
       </c>
       <c r="B352" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D352" t="s">
-        <v>315</v>
+        <v>233</v>
       </c>
       <c r="E352" t="s">
         <v>8</v>
@@ -7943,13 +7928,13 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D353" t="s">
-        <v>447</v>
+        <v>233</v>
       </c>
       <c r="E353" t="s">
         <v>8</v>
@@ -7960,13 +7945,13 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D354" t="s">
-        <v>218</v>
+        <v>377</v>
       </c>
       <c r="E354" t="s">
         <v>8</v>
@@ -7977,13 +7962,13 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D355" t="s">
-        <v>307</v>
+        <v>404</v>
       </c>
       <c r="E355" t="s">
         <v>8</v>
@@ -7994,13 +7979,13 @@
         <v>355</v>
       </c>
       <c r="B356" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D356" t="s">
-        <v>451</v>
+        <v>200</v>
       </c>
       <c r="E356" t="s">
         <v>8</v>
@@ -8011,13 +7996,13 @@
         <v>356</v>
       </c>
       <c r="B357" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D357" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="E357" t="s">
         <v>8</v>
@@ -8028,13 +8013,13 @@
         <v>357</v>
       </c>
       <c r="B358" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D358" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E358" t="s">
         <v>8</v>
@@ -8045,13 +8030,13 @@
         <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D359" t="s">
-        <v>222</v>
+        <v>341</v>
       </c>
       <c r="E359" t="s">
         <v>8</v>
@@ -8062,13 +8047,13 @@
         <v>359</v>
       </c>
       <c r="B360" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D360" t="s">
-        <v>214</v>
+        <v>267</v>
       </c>
       <c r="E360" t="s">
         <v>8</v>
@@ -8079,13 +8064,13 @@
         <v>360</v>
       </c>
       <c r="B361" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D361" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E361" t="s">
         <v>8</v>
@@ -8096,13 +8081,13 @@
         <v>361</v>
       </c>
       <c r="B362" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D362" t="s">
-        <v>237</v>
+        <v>391</v>
       </c>
       <c r="E362" t="s">
         <v>8</v>
@@ -8113,13 +8098,13 @@
         <v>362</v>
       </c>
       <c r="B363" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D363" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E363" t="s">
         <v>8</v>
@@ -8130,13 +8115,13 @@
         <v>363</v>
       </c>
       <c r="B364" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D364" t="s">
-        <v>208</v>
+        <v>380</v>
       </c>
       <c r="E364" t="s">
         <v>8</v>
@@ -8147,13 +8132,13 @@
         <v>364</v>
       </c>
       <c r="B365" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D365" t="s">
-        <v>424</v>
+        <v>452</v>
       </c>
       <c r="E365" t="s">
         <v>8</v>
@@ -8164,13 +8149,13 @@
         <v>365</v>
       </c>
       <c r="B366" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D366" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="E366" t="s">
         <v>8</v>
@@ -8181,13 +8166,13 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D367" t="s">
-        <v>220</v>
+        <v>377</v>
       </c>
       <c r="E367" t="s">
         <v>8</v>
@@ -8198,13 +8183,13 @@
         <v>367</v>
       </c>
       <c r="B368" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D368" t="s">
-        <v>237</v>
+        <v>452</v>
       </c>
       <c r="E368" t="s">
         <v>8</v>
@@ -8215,13 +8200,13 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D369" t="s">
-        <v>214</v>
+        <v>247</v>
       </c>
       <c r="E369" t="s">
         <v>8</v>
@@ -8232,13 +8217,13 @@
         <v>369</v>
       </c>
       <c r="B370" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D370" t="s">
-        <v>200</v>
+        <v>270</v>
       </c>
       <c r="E370" t="s">
         <v>8</v>
@@ -8249,13 +8234,13 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D371" t="s">
-        <v>245</v>
+        <v>459</v>
       </c>
       <c r="E371" t="s">
         <v>8</v>
@@ -8266,13 +8251,13 @@
         <v>371</v>
       </c>
       <c r="B372" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D372" t="s">
-        <v>468</v>
+        <v>404</v>
       </c>
       <c r="E372" t="s">
         <v>8</v>
@@ -8283,13 +8268,13 @@
         <v>372</v>
       </c>
       <c r="B373" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D373" t="s">
-        <v>243</v>
+        <v>462</v>
       </c>
       <c r="E373" t="s">
         <v>8</v>
@@ -8300,13 +8285,13 @@
         <v>373</v>
       </c>
       <c r="B374" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D374" t="s">
-        <v>290</v>
+        <v>427</v>
       </c>
       <c r="E374" t="s">
         <v>8</v>
@@ -8317,13 +8302,13 @@
         <v>374</v>
       </c>
       <c r="B375" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D375" t="s">
-        <v>224</v>
+        <v>465</v>
       </c>
       <c r="E375" t="s">
         <v>8</v>
@@ -8334,13 +8319,13 @@
         <v>375</v>
       </c>
       <c r="B376" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D376" t="s">
-        <v>424</v>
+        <v>236</v>
       </c>
       <c r="E376" t="s">
         <v>8</v>
@@ -8351,13 +8336,13 @@
         <v>376</v>
       </c>
       <c r="B377" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D377" t="s">
-        <v>474</v>
+        <v>359</v>
       </c>
       <c r="E377" t="s">
         <v>8</v>
@@ -8368,13 +8353,13 @@
         <v>377</v>
       </c>
       <c r="B378" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D378" t="s">
-        <v>204</v>
+        <v>469</v>
       </c>
       <c r="E378" t="s">
         <v>8</v>
@@ -8385,13 +8370,13 @@
         <v>378</v>
       </c>
       <c r="B379" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D379" t="s">
-        <v>348</v>
+        <v>267</v>
       </c>
       <c r="E379" t="s">
         <v>8</v>
@@ -8402,13 +8387,13 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D380" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="E380" t="s">
         <v>8</v>
@@ -8419,13 +8404,13 @@
         <v>380</v>
       </c>
       <c r="B381" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D381" t="s">
-        <v>198</v>
+        <v>377</v>
       </c>
       <c r="E381" t="s">
         <v>8</v>
@@ -8436,13 +8421,13 @@
         <v>381</v>
       </c>
       <c r="B382" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D382" t="s">
-        <v>436</v>
+        <v>270</v>
       </c>
       <c r="E382" t="s">
         <v>8</v>
@@ -8453,13 +8438,13 @@
         <v>382</v>
       </c>
       <c r="B383" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D383" t="s">
-        <v>337</v>
+        <v>218</v>
       </c>
       <c r="E383" t="s">
         <v>8</v>
@@ -8470,13 +8455,13 @@
         <v>383</v>
       </c>
       <c r="B384" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D384" t="s">
-        <v>474</v>
+        <v>241</v>
       </c>
       <c r="E384" t="s">
         <v>8</v>
@@ -8487,13 +8472,13 @@
         <v>384</v>
       </c>
       <c r="B385" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D385" t="s">
-        <v>307</v>
+        <v>209</v>
       </c>
       <c r="E385" t="s">
         <v>8</v>
@@ -8504,13 +8489,13 @@
         <v>385</v>
       </c>
       <c r="B386" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D386" t="s">
-        <v>325</v>
+        <v>465</v>
       </c>
       <c r="E386" t="s">
         <v>8</v>
@@ -8521,13 +8506,13 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D387" t="s">
-        <v>485</v>
+        <v>402</v>
       </c>
       <c r="E387" t="s">
         <v>8</v>
@@ -8538,13 +8523,13 @@
         <v>387</v>
       </c>
       <c r="B388" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D388" t="s">
-        <v>262</v>
+        <v>480</v>
       </c>
       <c r="E388" t="s">
         <v>8</v>
@@ -8555,13 +8540,13 @@
         <v>388</v>
       </c>
       <c r="B389" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D389" t="s">
-        <v>274</v>
+        <v>482</v>
       </c>
       <c r="E389" t="s">
         <v>8</v>
@@ -8572,13 +8557,13 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D390" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="E390" t="s">
         <v>8</v>
@@ -8589,13 +8574,13 @@
         <v>390</v>
       </c>
       <c r="B391" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D391" t="s">
-        <v>255</v>
+        <v>459</v>
       </c>
       <c r="E391" t="s">
         <v>8</v>
@@ -8606,13 +8591,13 @@
         <v>391</v>
       </c>
       <c r="B392" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D392" t="s">
-        <v>474</v>
+        <v>303</v>
       </c>
       <c r="E392" t="s">
         <v>8</v>
@@ -8623,13 +8608,13 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D393" t="s">
-        <v>402</v>
+        <v>249</v>
       </c>
       <c r="E393" t="s">
         <v>8</v>
@@ -8640,13 +8625,13 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D394" t="s">
-        <v>196</v>
+        <v>391</v>
       </c>
       <c r="E394" t="s">
         <v>8</v>
@@ -8657,13 +8642,13 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D395" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E395" t="s">
         <v>8</v>
@@ -8674,13 +8659,13 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D396" t="s">
-        <v>495</v>
+        <v>377</v>
       </c>
       <c r="E396" t="s">
         <v>8</v>
@@ -8691,13 +8676,13 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D397" t="s">
-        <v>373</v>
+        <v>427</v>
       </c>
       <c r="E397" t="s">
         <v>8</v>
@@ -8708,13 +8693,13 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D398" t="s">
-        <v>257</v>
+        <v>492</v>
       </c>
       <c r="E398" t="s">
         <v>8</v>
@@ -8725,13 +8710,13 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D399" t="s">
-        <v>294</v>
+        <v>341</v>
       </c>
       <c r="E399" t="s">
         <v>8</v>
@@ -8742,13 +8727,13 @@
         <v>399</v>
       </c>
       <c r="B400" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D400" t="s">
-        <v>248</v>
+        <v>377</v>
       </c>
       <c r="E400" t="s">
         <v>8</v>
@@ -8759,13 +8744,13 @@
         <v>400</v>
       </c>
       <c r="B401" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D401" t="s">
-        <v>202</v>
+        <v>254</v>
       </c>
       <c r="E401" t="s">
         <v>8</v>
@@ -8784,47 +8769,47 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="B1" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="B2" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="B3" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="B4" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="B5" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="B6">
         <v>400</v>
@@ -8832,7 +8817,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="B7">
         <v>400</v>
@@ -8840,7 +8825,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -8848,7 +8833,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -8856,10 +8841,10 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="B10" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
     </row>
   </sheetData>

--- a/reports/backend/Excel/Automation_Test_Report.xlsx
+++ b/reports/backend/Excel/Automation_Test_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="519">
   <si>
     <t>#</t>
   </si>
@@ -584,915 +584,936 @@
     <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field apiKey (Verify Point #180)</t>
   </si>
   <si>
+    <t>0.040</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #181)</t>
+  </si>
+  <si>
+    <t>0.106</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #182)</t>
+  </si>
+  <si>
+    <t>0.049</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #183)</t>
+  </si>
+  <si>
+    <t>0.058</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #184)</t>
+  </si>
+  <si>
+    <t>0.078</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #185)</t>
+  </si>
+  <si>
+    <t>0.055</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #186)</t>
+  </si>
+  <si>
+    <t>0.110</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #187)</t>
+  </si>
+  <si>
+    <t>0.042</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #188)</t>
+  </si>
+  <si>
+    <t>0.111</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #189)</t>
+  </si>
+  <si>
+    <t>0.066</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #190)</t>
+  </si>
+  <si>
+    <t>0.026</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #191)</t>
+  </si>
+  <si>
+    <t>0.046</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #192)</t>
+  </si>
+  <si>
+    <t>0.067</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #193)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #194)</t>
+  </si>
+  <si>
+    <t>0.038</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #195)</t>
+  </si>
+  <si>
+    <t>0.094</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #196)</t>
+  </si>
+  <si>
+    <t>0.062</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #197)</t>
+  </si>
+  <si>
+    <t>0.043</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #198)</t>
+  </si>
+  <si>
+    <t>0.119</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #199)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #200)</t>
+  </si>
+  <si>
+    <t>0.115</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #201)</t>
+  </si>
+  <si>
+    <t>0.105</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #202)</t>
+  </si>
+  <si>
+    <t>0.100</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #203)</t>
+  </si>
+  <si>
+    <t>0.077</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #204)</t>
+  </si>
+  <si>
+    <t>0.083</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #205)</t>
+  </si>
+  <si>
     <t>0.027</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #181)</t>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #206)</t>
+  </si>
+  <si>
+    <t>0.113</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #207)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #208)</t>
+  </si>
+  <si>
+    <t>0.044</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #209)</t>
+  </si>
+  <si>
+    <t>0.052</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #210)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #211)</t>
+  </si>
+  <si>
+    <t>0.054</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code XSS-injection (Verify Point #212)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #213)</t>
+  </si>
+  <si>
+    <t>0.118</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for CSRF-token (Verify Point #214)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated CORS-origin (Verify Point #215)</t>
+  </si>
+  <si>
+    <t>0.085</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for CSP-header (Verify Point #216)</t>
+  </si>
+  <si>
+    <t>0.024</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at session-token (Verify Point #217)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users-ref (Verify Point #218)</t>
+  </si>
+  <si>
+    <t>0.039</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for items-ref (Verify Point #219)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field de-DE (Verify Point #220)</t>
+  </si>
+  <si>
+    <t>0.074</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for fr-FR (Verify Point #221)</t>
+  </si>
+  <si>
+    <t>0.109</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ja-JP (Verify Point #222)</t>
+  </si>
+  <si>
+    <t>0.023</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for pt-BR (Verify Point #223)</t>
+  </si>
+  <si>
+    <t>0.087</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of it-IT (Verify Point #224)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for apiKey (Verify Point #225)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for authDomain (Verify Point #226)</t>
+  </si>
+  <si>
+    <t>0.032</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value projectId (Verify Point #227)</t>
+  </si>
+  <si>
+    <t>0.090</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session storageBucket (Verify Point #228)</t>
+  </si>
+  <si>
+    <t>0.031</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier messagingSenderId (Verify Point #229)</t>
+  </si>
+  <si>
+    <t>0.073</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region appId (Verify Point #230)</t>
+  </si>
+  <si>
+    <t>0.022</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for name (Verify Point #231)</t>
+  </si>
+  <si>
+    <t>0.045</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code id (Verify Point #232)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource fees.min (Verify Point #233)</t>
+  </si>
+  <si>
+    <t>0.069</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for fees.max (Verify Point #234)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated courses (Verify Point #235)</t>
+  </si>
+  <si>
+    <t>0.061</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for ranking.nirf (Verify Point #236)</t>
+  </si>
+  <si>
+    <t>0.102</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at type (Verify Point #237)</t>
+  </si>
+  <si>
+    <t>0.114</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users/uid001 (Verify Point #238)</t>
+  </si>
+  <si>
+    <t>0.051</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for colleges/c001 (Verify Point #239)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field prompt-length (Verify Point #240)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for session-id-1 (Verify Point #241)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ₹1L (Verify Point #242)</t>
+  </si>
+  <si>
+    <t>0.020</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for B.Tech (Verify Point #243)</t>
+  </si>
+  <si>
+    <t>0.063</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of 4 years (Verify Point #244)</t>
+  </si>
+  <si>
+    <t>0.097</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for Tamil Nadu (Verify Point #245)</t>
+  </si>
+  <si>
+    <t>0.084</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for Chennai (Verify Point #246)</t>
+  </si>
+  <si>
+    <t>0.096</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value llama3-8b (Verify Point #247)</t>
+  </si>
+  <si>
+    <t>0.093</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session email (Verify Point #248)</t>
+  </si>
+  <si>
+    <t>0.034</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier password (Verify Point #249)</t>
+  </si>
+  <si>
+    <t>0.025</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region displayName (Verify Point #250)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for savedColleges (Verify Point #251)</t>
+  </si>
+  <si>
+    <t>0.037</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code createdAt (Verify Point #252)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource firebase-auth (Verify Point #253)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for firestore-read (Verify Point #254)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated groq-api (Verify Point #255)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for college-list (Verify Point #256)</t>
+  </si>
+  <si>
+    <t>0.116</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at XSS-injection (Verify Point #257)</t>
   </si>
   <si>
     <t>0.035</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #182)</t>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation SQL-injection (Verify Point #258)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for CSRF-token (Verify Point #259)</t>
+  </si>
+  <si>
+    <t>0.071</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field CORS-origin (Verify Point #260)</t>
   </si>
   <si>
     <t>0.076</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #183)</t>
-  </si>
-  <si>
-    <t>0.065</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #184)</t>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for CSP-header (Verify Point #261)</t>
+  </si>
+  <si>
+    <t>0.112</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for session-token (Verify Point #262)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users-ref (Verify Point #263)</t>
+  </si>
+  <si>
+    <t>0.059</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of items-ref (Verify Point #264)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for de-DE (Verify Point #265)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for fr-FR (Verify Point #266)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ja-JP (Verify Point #267)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session pt-BR (Verify Point #268)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier it-IT (Verify Point #269)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region apiKey (Verify Point #270)</t>
+  </si>
+  <si>
+    <t>0.064</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for authDomain (Verify Point #271)</t>
+  </si>
+  <si>
+    <t>0.088</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code projectId (Verify Point #272)</t>
+  </si>
+  <si>
+    <t>0.080</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource storageBucket (Verify Point #273)</t>
+  </si>
+  <si>
+    <t>0.089</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for messagingSenderId (Verify Point #274)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated appId (Verify Point #275)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for name (Verify Point #276)</t>
+  </si>
+  <si>
+    <t>0.079</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at id (Verify Point #277)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation fees.min (Verify Point #278)</t>
+  </si>
+  <si>
+    <t>0.092</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for fees.max (Verify Point #279)</t>
+  </si>
+  <si>
+    <t>0.107</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field courses (Verify Point #280)</t>
+  </si>
+  <si>
+    <t>0.056</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for ranking.nirf (Verify Point #281)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for type (Verify Point #282)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users/uid001 (Verify Point #283)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of colleges/c001 (Verify Point #284)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for prompt-length (Verify Point #285)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for session-id-1 (Verify Point #286)</t>
+  </si>
+  <si>
+    <t>0.104</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ₹1L (Verify Point #287)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session B.Tech (Verify Point #288)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier 4 years (Verify Point #289)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region Tamil Nadu (Verify Point #290)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for Chennai (Verify Point #291)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code llama3-8b (Verify Point #292)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource email (Verify Point #293)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for password (Verify Point #294)</t>
+  </si>
+  <si>
+    <t>0.103</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated displayName (Verify Point #295)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for savedColleges (Verify Point #296)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at createdAt (Verify Point #297)</t>
+  </si>
+  <si>
+    <t>0.029</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation firebase-auth (Verify Point #298)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for firestore-read (Verify Point #299)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field groq-api (Verify Point #300)</t>
+  </si>
+  <si>
+    <t>0.030</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for college-list (Verify Point #301)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for XSS-injection (Verify Point #302)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for SQL-injection (Verify Point #303)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of CSRF-token (Verify Point #304)</t>
+  </si>
+  <si>
+    <t>0.086</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for CORS-origin (Verify Point #305)</t>
+  </si>
+  <si>
+    <t>0.021</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for CSP-header (Verify Point #306)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value session-token (Verify Point #307)</t>
+  </si>
+  <si>
+    <t>0.099</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users-ref (Verify Point #308)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier items-ref (Verify Point #309)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region de-DE (Verify Point #310)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for fr-FR (Verify Point #311)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ja-JP (Verify Point #312)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource pt-BR (Verify Point #313)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for it-IT (Verify Point #314)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated apiKey (Verify Point #315)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for authDomain (Verify Point #316)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at projectId (Verify Point #317)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation storageBucket (Verify Point #318)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for messagingSenderId (Verify Point #319)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field appId (Verify Point #320)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for name (Verify Point #321)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for id (Verify Point #322)</t>
+  </si>
+  <si>
+    <t>0.033</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for fees.min (Verify Point #323)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of fees.max (Verify Point #324)</t>
+  </si>
+  <si>
+    <t>0.048</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for courses (Verify Point #325)</t>
+  </si>
+  <si>
+    <t>0.036</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for ranking.nirf (Verify Point #326)</t>
+  </si>
+  <si>
+    <t>0.070</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value type (Verify Point #327)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users/uid001 (Verify Point #328)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier colleges/c001 (Verify Point #329)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region prompt-length (Verify Point #330)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for session-id-1 (Verify Point #331)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ₹1L (Verify Point #332)</t>
+  </si>
+  <si>
+    <t>0.028</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource B.Tech (Verify Point #333)</t>
+  </si>
+  <si>
+    <t>0.047</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for 4 years (Verify Point #334)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated Tamil Nadu (Verify Point #335)</t>
+  </si>
+  <si>
+    <t>0.081</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for Chennai (Verify Point #336)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at llama3-8b (Verify Point #337)</t>
+  </si>
+  <si>
+    <t>0.091</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation email (Verify Point #338)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for password (Verify Point #339)</t>
+  </si>
+  <si>
+    <t>0.101</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field displayName (Verify Point #340)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for savedColleges (Verify Point #341)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for createdAt (Verify Point #342)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for firebase-auth (Verify Point #343)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of firestore-read (Verify Point #344)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for groq-api (Verify Point #345)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for college-list (Verify Point #346)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value XSS-injection (Verify Point #347)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session SQL-injection (Verify Point #348)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier CSRF-token (Verify Point #349)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region CORS-origin (Verify Point #350)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for CSP-header (Verify Point #351)</t>
   </si>
   <si>
     <t>0.060</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #185)</t>
-  </si>
-  <si>
-    <t>0.049</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #186)</t>
-  </si>
-  <si>
-    <t>0.066</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #187)</t>
-  </si>
-  <si>
-    <t>0.119</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #188)</t>
-  </si>
-  <si>
-    <t>0.032</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #189)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #190)</t>
-  </si>
-  <si>
-    <t>0.071</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #191)</t>
-  </si>
-  <si>
-    <t>0.115</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #192)</t>
-  </si>
-  <si>
-    <t>0.042</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #193)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #194)</t>
-  </si>
-  <si>
-    <t>0.080</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #195)</t>
-  </si>
-  <si>
-    <t>0.069</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #196)</t>
-  </si>
-  <si>
-    <t>0.116</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #197)</t>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code session-token (Verify Point #352)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users-ref (Verify Point #353)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for items-ref (Verify Point #354)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated de-DE (Verify Point #355)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for fr-FR (Verify Point #356)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ja-JP (Verify Point #357)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation pt-BR (Verify Point #358)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for it-IT (Verify Point #359)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field apiKey (Verify Point #360)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #361)</t>
+  </si>
+  <si>
+    <t>0.068</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #362)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #363)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #364)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #365)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #366)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #367)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #368)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #369)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #370)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #371)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #372)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #373)</t>
   </si>
   <si>
     <t>0.041</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #198)</t>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #374)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #375)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #376)</t>
   </si>
   <si>
     <t>0.053</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #199)</t>
-  </si>
-  <si>
-    <t>0.079</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #200)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #201)</t>
-  </si>
-  <si>
-    <t>0.088</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #202)</t>
-  </si>
-  <si>
-    <t>0.082</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #203)</t>
-  </si>
-  <si>
-    <t>0.070</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #204)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #205)</t>
-  </si>
-  <si>
-    <t>0.102</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #206)</t>
-  </si>
-  <si>
-    <t>0.063</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #207)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #208)</t>
-  </si>
-  <si>
-    <t>0.057</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #209)</t>
-  </si>
-  <si>
-    <t>0.025</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #210)</t>
-  </si>
-  <si>
-    <t>0.109</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #211)</t>
-  </si>
-  <si>
-    <t>0.091</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code XSS-injection (Verify Point #212)</t>
-  </si>
-  <si>
-    <t>0.112</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #213)</t>
-  </si>
-  <si>
-    <t>0.107</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for CSRF-token (Verify Point #214)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated CORS-origin (Verify Point #215)</t>
-  </si>
-  <si>
-    <t>0.036</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for CSP-header (Verify Point #216)</t>
-  </si>
-  <si>
-    <t>0.030</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at session-token (Verify Point #217)</t>
-  </si>
-  <si>
-    <t>0.111</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users-ref (Verify Point #218)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for items-ref (Verify Point #219)</t>
-  </si>
-  <si>
-    <t>0.061</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field de-DE (Verify Point #220)</t>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #377)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #378)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #379)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #380)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #381)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #382)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #383)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #384)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #385)</t>
+  </si>
+  <si>
+    <t>0.072</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #386)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #387)</t>
+  </si>
+  <si>
+    <t>0.075</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #388)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #389)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #390)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #391)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code XSS-injection (Verify Point #392)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #393)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for CSRF-token (Verify Point #394)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated CORS-origin (Verify Point #395)</t>
+  </si>
+  <si>
+    <t>0.108</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for CSP-header (Verify Point #396)</t>
   </si>
   <si>
     <t>0.117</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for fr-FR (Verify Point #221)</t>
-  </si>
-  <si>
-    <t>0.040</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ja-JP (Verify Point #222)</t>
-  </si>
-  <si>
-    <t>0.085</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for pt-BR (Verify Point #223)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of it-IT (Verify Point #224)</t>
-  </si>
-  <si>
-    <t>0.118</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for apiKey (Verify Point #225)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for authDomain (Verify Point #226)</t>
-  </si>
-  <si>
-    <t>0.068</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value projectId (Verify Point #227)</t>
-  </si>
-  <si>
-    <t>0.101</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session storageBucket (Verify Point #228)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier messagingSenderId (Verify Point #229)</t>
-  </si>
-  <si>
-    <t>0.104</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region appId (Verify Point #230)</t>
-  </si>
-  <si>
-    <t>0.114</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for name (Verify Point #231)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code id (Verify Point #232)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource fees.min (Verify Point #233)</t>
-  </si>
-  <si>
-    <t>0.089</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for fees.max (Verify Point #234)</t>
-  </si>
-  <si>
-    <t>0.086</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated courses (Verify Point #235)</t>
-  </si>
-  <si>
-    <t>0.047</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for ranking.nirf (Verify Point #236)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at type (Verify Point #237)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users/uid001 (Verify Point #238)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for colleges/c001 (Verify Point #239)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field prompt-length (Verify Point #240)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for session-id-1 (Verify Point #241)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ₹1L (Verify Point #242)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for B.Tech (Verify Point #243)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of 4 years (Verify Point #244)</t>
-  </si>
-  <si>
-    <t>0.084</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for Tamil Nadu (Verify Point #245)</t>
-  </si>
-  <si>
-    <t>0.043</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for Chennai (Verify Point #246)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value llama3-8b (Verify Point #247)</t>
-  </si>
-  <si>
-    <t>0.055</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session email (Verify Point #248)</t>
-  </si>
-  <si>
-    <t>0.029</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier password (Verify Point #249)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region displayName (Verify Point #250)</t>
-  </si>
-  <si>
-    <t>0.067</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for savedColleges (Verify Point #251)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code createdAt (Verify Point #252)</t>
-  </si>
-  <si>
-    <t>0.105</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource firebase-auth (Verify Point #253)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for firestore-read (Verify Point #254)</t>
-  </si>
-  <si>
-    <t>0.072</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated groq-api (Verify Point #255)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for college-list (Verify Point #256)</t>
-  </si>
-  <si>
-    <t>0.073</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at XSS-injection (Verify Point #257)</t>
-  </si>
-  <si>
-    <t>0.097</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation SQL-injection (Verify Point #258)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for CSRF-token (Verify Point #259)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field CORS-origin (Verify Point #260)</t>
-  </si>
-  <si>
-    <t>0.064</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for CSP-header (Verify Point #261)</t>
-  </si>
-  <si>
-    <t>0.092</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for session-token (Verify Point #262)</t>
-  </si>
-  <si>
-    <t>0.031</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users-ref (Verify Point #263)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of items-ref (Verify Point #264)</t>
-  </si>
-  <si>
-    <t>0.108</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for de-DE (Verify Point #265)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for fr-FR (Verify Point #266)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ja-JP (Verify Point #267)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session pt-BR (Verify Point #268)</t>
-  </si>
-  <si>
-    <t>0.050</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier it-IT (Verify Point #269)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region apiKey (Verify Point #270)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for authDomain (Verify Point #271)</t>
-  </si>
-  <si>
-    <t>0.024</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code projectId (Verify Point #272)</t>
-  </si>
-  <si>
-    <t>0.037</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource storageBucket (Verify Point #273)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for messagingSenderId (Verify Point #274)</t>
-  </si>
-  <si>
-    <t>0.051</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated appId (Verify Point #275)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for name (Verify Point #276)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at id (Verify Point #277)</t>
-  </si>
-  <si>
-    <t>0.075</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation fees.min (Verify Point #278)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for fees.max (Verify Point #279)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field courses (Verify Point #280)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for ranking.nirf (Verify Point #281)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for type (Verify Point #282)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users/uid001 (Verify Point #283)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of colleges/c001 (Verify Point #284)</t>
-  </si>
-  <si>
-    <t>0.062</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for prompt-length (Verify Point #285)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for session-id-1 (Verify Point #286)</t>
-  </si>
-  <si>
-    <t>0.081</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ₹1L (Verify Point #287)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session B.Tech (Verify Point #288)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier 4 years (Verify Point #289)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region Tamil Nadu (Verify Point #290)</t>
-  </si>
-  <si>
-    <t>0.078</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for Chennai (Verify Point #291)</t>
-  </si>
-  <si>
-    <t>0.022</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code llama3-8b (Verify Point #292)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource email (Verify Point #293)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for password (Verify Point #294)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated displayName (Verify Point #295)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for savedColleges (Verify Point #296)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at createdAt (Verify Point #297)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation firebase-auth (Verify Point #298)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for firestore-read (Verify Point #299)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field groq-api (Verify Point #300)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for college-list (Verify Point #301)</t>
-  </si>
-  <si>
-    <t>0.052</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for XSS-injection (Verify Point #302)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for SQL-injection (Verify Point #303)</t>
-  </si>
-  <si>
-    <t>0.026</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of CSRF-token (Verify Point #304)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for CORS-origin (Verify Point #305)</t>
-  </si>
-  <si>
-    <t>0.045</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for CSP-header (Verify Point #306)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value session-token (Verify Point #307)</t>
-  </si>
-  <si>
-    <t>0.098</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users-ref (Verify Point #308)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier items-ref (Verify Point #309)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region de-DE (Verify Point #310)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for fr-FR (Verify Point #311)</t>
-  </si>
-  <si>
-    <t>0.020</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ja-JP (Verify Point #312)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource pt-BR (Verify Point #313)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for it-IT (Verify Point #314)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated apiKey (Verify Point #315)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for authDomain (Verify Point #316)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at projectId (Verify Point #317)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation storageBucket (Verify Point #318)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for messagingSenderId (Verify Point #319)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field appId (Verify Point #320)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for name (Verify Point #321)</t>
-  </si>
-  <si>
-    <t>0.093</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for id (Verify Point #322)</t>
-  </si>
-  <si>
-    <t>0.077</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for fees.min (Verify Point #323)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of fees.max (Verify Point #324)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for courses (Verify Point #325)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for ranking.nirf (Verify Point #326)</t>
-  </si>
-  <si>
-    <t>0.095</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value type (Verify Point #327)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users/uid001 (Verify Point #328)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier colleges/c001 (Verify Point #329)</t>
-  </si>
-  <si>
-    <t>0.110</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region prompt-length (Verify Point #330)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for session-id-1 (Verify Point #331)</t>
-  </si>
-  <si>
-    <t>0.096</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ₹1L (Verify Point #332)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource B.Tech (Verify Point #333)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for 4 years (Verify Point #334)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated Tamil Nadu (Verify Point #335)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for Chennai (Verify Point #336)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at llama3-8b (Verify Point #337)</t>
-  </si>
-  <si>
-    <t>0.100</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation email (Verify Point #338)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for password (Verify Point #339)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field displayName (Verify Point #340)</t>
-  </si>
-  <si>
-    <t>0.033</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for savedColleges (Verify Point #341)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for createdAt (Verify Point #342)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for firebase-auth (Verify Point #343)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of firestore-read (Verify Point #344)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for groq-api (Verify Point #345)</t>
-  </si>
-  <si>
-    <t>0.099</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for college-list (Verify Point #346)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value XSS-injection (Verify Point #347)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session SQL-injection (Verify Point #348)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier CSRF-token (Verify Point #349)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region CORS-origin (Verify Point #350)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for CSP-header (Verify Point #351)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code session-token (Verify Point #352)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users-ref (Verify Point #353)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for items-ref (Verify Point #354)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated de-DE (Verify Point #355)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for fr-FR (Verify Point #356)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ja-JP (Verify Point #357)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation pt-BR (Verify Point #358)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for it-IT (Verify Point #359)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field apiKey (Verify Point #360)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #361)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #362)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #363)</t>
-  </si>
-  <si>
-    <t>0.034</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #364)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #365)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #366)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #367)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #368)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #369)</t>
-  </si>
-  <si>
-    <t>0.087</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #370)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #371)</t>
-  </si>
-  <si>
-    <t>0.103</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #372)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #373)</t>
-  </si>
-  <si>
-    <t>0.054</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #374)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #375)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #376)</t>
-  </si>
-  <si>
-    <t>0.113</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #377)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #378)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #379)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #380)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #381)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #382)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #383)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #384)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #385)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #386)</t>
-  </si>
-  <si>
-    <t>0.056</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #387)</t>
-  </si>
-  <si>
-    <t>0.028</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #388)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #389)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #390)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #391)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code XSS-injection (Verify Point #392)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #393)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for CSRF-token (Verify Point #394)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated CORS-origin (Verify Point #395)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for CSP-header (Verify Point #396)</t>
-  </si>
-  <si>
-    <t>0.074</t>
-  </si>
-  <si>
     <t>Smart Admission — Backend [Boundary]: Verify boundary condition at session-token (Verify Point #397)</t>
   </si>
   <si>
@@ -1511,13 +1532,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>18</t>
+    <t>19</t>
   </si>
   <si>
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 14:24:49 UTC</t>
+    <t>2026-06-23 14:34:46 UTC</t>
   </si>
   <si>
     <t>Branch</t>
@@ -1529,7 +1550,7 @@
     <t>Commit</t>
   </si>
   <si>
-    <t>04fd2d2</t>
+    <t>af530d5</t>
   </si>
   <si>
     <t>Total</t>
@@ -2052,7 +2073,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -2069,7 +2090,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -2222,7 +2243,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -2409,7 +2430,7 @@
         <v>6</v>
       </c>
       <c r="D28" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -2460,7 +2481,7 @@
         <v>6</v>
       </c>
       <c r="D31" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -2596,7 +2617,7 @@
         <v>6</v>
       </c>
       <c r="D39" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -2664,7 +2685,7 @@
         <v>6</v>
       </c>
       <c r="D43" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -3106,7 +3127,7 @@
         <v>6</v>
       </c>
       <c r="D69" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E69" t="s">
         <v>8</v>
@@ -3242,7 +3263,7 @@
         <v>6</v>
       </c>
       <c r="D77" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
@@ -3327,7 +3348,7 @@
         <v>6</v>
       </c>
       <c r="D82" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
@@ -3701,7 +3722,7 @@
         <v>6</v>
       </c>
       <c r="D104" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E104" t="s">
         <v>8</v>
@@ -3888,7 +3909,7 @@
         <v>6</v>
       </c>
       <c r="D115" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E115" t="s">
         <v>8</v>
@@ -4126,7 +4147,7 @@
         <v>6</v>
       </c>
       <c r="D129" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E129" t="s">
         <v>8</v>
@@ -4143,7 +4164,7 @@
         <v>6</v>
       </c>
       <c r="D130" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E130" t="s">
         <v>8</v>
@@ -5180,7 +5201,7 @@
         <v>6</v>
       </c>
       <c r="D191" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="E191" t="s">
         <v>8</v>
@@ -5191,13 +5212,13 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D192" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E192" t="s">
         <v>8</v>
@@ -5208,13 +5229,13 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D193" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E193" t="s">
         <v>8</v>
@@ -5225,13 +5246,13 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D194" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E194" t="s">
         <v>8</v>
@@ -5242,13 +5263,13 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D195" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="E195" t="s">
         <v>8</v>
@@ -5259,13 +5280,13 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D196" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E196" t="s">
         <v>8</v>
@@ -5276,13 +5297,13 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D197" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E197" t="s">
         <v>8</v>
@@ -5293,13 +5314,13 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D198" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E198" t="s">
         <v>8</v>
@@ -5310,13 +5331,13 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D199" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E199" t="s">
         <v>8</v>
@@ -5327,13 +5348,13 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D200" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E200" t="s">
         <v>8</v>
@@ -5344,13 +5365,13 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D201" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="E201" t="s">
         <v>8</v>
@@ -5367,7 +5388,7 @@
         <v>6</v>
       </c>
       <c r="D202" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="E202" t="s">
         <v>8</v>
@@ -5378,13 +5399,13 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D203" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E203" t="s">
         <v>8</v>
@@ -5395,13 +5416,13 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D204" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E204" t="s">
         <v>8</v>
@@ -5412,13 +5433,13 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D205" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E205" t="s">
         <v>8</v>
@@ -5429,13 +5450,13 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D206" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="E206" t="s">
         <v>8</v>
@@ -5446,13 +5467,13 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D207" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E207" t="s">
         <v>8</v>
@@ -5463,13 +5484,13 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D208" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E208" t="s">
         <v>8</v>
@@ -5480,13 +5501,13 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D209" t="s">
-        <v>213</v>
+        <v>194</v>
       </c>
       <c r="E209" t="s">
         <v>8</v>
@@ -5497,13 +5518,13 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D210" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E210" t="s">
         <v>8</v>
@@ -5514,13 +5535,13 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D211" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E211" t="s">
         <v>8</v>
@@ -5531,13 +5552,13 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D212" t="s">
-        <v>245</v>
+        <v>225</v>
       </c>
       <c r="E212" t="s">
         <v>8</v>
@@ -5548,13 +5569,13 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D213" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E213" t="s">
         <v>8</v>
@@ -5565,13 +5586,13 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D214" t="s">
-        <v>249</v>
+        <v>223</v>
       </c>
       <c r="E214" t="s">
         <v>8</v>
@@ -5605,7 +5626,7 @@
         <v>6</v>
       </c>
       <c r="D216" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E216" t="s">
         <v>8</v>
@@ -5656,7 +5677,7 @@
         <v>6</v>
       </c>
       <c r="D219" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E219" t="s">
         <v>8</v>
@@ -5667,13 +5688,13 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
+        <v>258</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D220" t="s">
         <v>259</v>
-      </c>
-      <c r="C220" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D220" t="s">
-        <v>251</v>
       </c>
       <c r="E220" t="s">
         <v>8</v>
@@ -5690,7 +5711,7 @@
         <v>6</v>
       </c>
       <c r="D221" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="E221" t="s">
         <v>8</v>
@@ -5701,13 +5722,13 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
+        <v>261</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D222" t="s">
         <v>262</v>
-      </c>
-      <c r="C222" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D222" t="s">
-        <v>263</v>
       </c>
       <c r="E222" t="s">
         <v>8</v>
@@ -5718,13 +5739,13 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
+        <v>263</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D223" t="s">
         <v>264</v>
-      </c>
-      <c r="C223" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D223" t="s">
-        <v>265</v>
       </c>
       <c r="E223" t="s">
         <v>8</v>
@@ -5735,13 +5756,13 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
+        <v>265</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D224" t="s">
         <v>266</v>
-      </c>
-      <c r="C224" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D224" t="s">
-        <v>267</v>
       </c>
       <c r="E224" t="s">
         <v>8</v>
@@ -5752,13 +5773,13 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
+        <v>267</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D225" t="s">
         <v>268</v>
-      </c>
-      <c r="C225" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D225" t="s">
-        <v>265</v>
       </c>
       <c r="E225" t="s">
         <v>8</v>
@@ -5775,7 +5796,7 @@
         <v>6</v>
       </c>
       <c r="D226" t="s">
-        <v>270</v>
+        <v>190</v>
       </c>
       <c r="E226" t="s">
         <v>8</v>
@@ -5786,13 +5807,13 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D227" t="s">
-        <v>233</v>
+        <v>208</v>
       </c>
       <c r="E227" t="s">
         <v>8</v>
@@ -5803,13 +5824,13 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
+        <v>271</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D228" t="s">
         <v>272</v>
-      </c>
-      <c r="C228" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D228" t="s">
-        <v>273</v>
       </c>
       <c r="E228" t="s">
         <v>8</v>
@@ -5820,13 +5841,13 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
+        <v>273</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D229" t="s">
         <v>274</v>
-      </c>
-      <c r="C229" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D229" t="s">
-        <v>275</v>
       </c>
       <c r="E229" t="s">
         <v>8</v>
@@ -5837,13 +5858,13 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
+        <v>275</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D230" t="s">
         <v>276</v>
-      </c>
-      <c r="C230" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D230" t="s">
-        <v>192</v>
       </c>
       <c r="E230" t="s">
         <v>8</v>
@@ -5894,7 +5915,7 @@
         <v>6</v>
       </c>
       <c r="D233" t="s">
-        <v>251</v>
+        <v>282</v>
       </c>
       <c r="E233" t="s">
         <v>8</v>
@@ -5905,13 +5926,13 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D234" t="s">
-        <v>273</v>
+        <v>208</v>
       </c>
       <c r="E234" t="s">
         <v>8</v>
@@ -5922,13 +5943,13 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D235" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E235" t="s">
         <v>8</v>
@@ -5939,13 +5960,13 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D236" t="s">
-        <v>286</v>
+        <v>230</v>
       </c>
       <c r="E236" t="s">
         <v>8</v>
@@ -5979,7 +6000,7 @@
         <v>6</v>
       </c>
       <c r="D238" t="s">
-        <v>220</v>
+        <v>290</v>
       </c>
       <c r="E238" t="s">
         <v>8</v>
@@ -5990,13 +6011,13 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D239" t="s">
-        <v>213</v>
+        <v>292</v>
       </c>
       <c r="E239" t="s">
         <v>8</v>
@@ -6007,13 +6028,13 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D240" t="s">
-        <v>241</v>
+        <v>294</v>
       </c>
       <c r="E240" t="s">
         <v>8</v>
@@ -6024,13 +6045,13 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D241" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="E241" t="s">
         <v>8</v>
@@ -6041,13 +6062,13 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D242" t="s">
-        <v>198</v>
+        <v>268</v>
       </c>
       <c r="E242" t="s">
         <v>8</v>
@@ -6058,13 +6079,13 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D243" t="s">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="E243" t="s">
         <v>8</v>
@@ -6075,13 +6096,13 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D244" t="s">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="E244" t="s">
         <v>8</v>
@@ -6092,13 +6113,13 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D245" t="s">
-        <v>231</v>
+        <v>301</v>
       </c>
       <c r="E245" t="s">
         <v>8</v>
@@ -6109,13 +6130,13 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D246" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="E246" t="s">
         <v>8</v>
@@ -6126,13 +6147,13 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D247" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="E247" t="s">
         <v>8</v>
@@ -6143,13 +6164,13 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D248" t="s">
-        <v>218</v>
+        <v>307</v>
       </c>
       <c r="E248" t="s">
         <v>8</v>
@@ -6160,13 +6181,13 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D249" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="E249" t="s">
         <v>8</v>
@@ -6177,13 +6198,13 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D250" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="E250" t="s">
         <v>8</v>
@@ -6194,13 +6215,13 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D251" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="E251" t="s">
         <v>8</v>
@@ -6211,13 +6232,13 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D252" t="s">
-        <v>308</v>
+        <v>248</v>
       </c>
       <c r="E252" t="s">
         <v>8</v>
@@ -6228,13 +6249,13 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D253" t="s">
-        <v>224</v>
+        <v>316</v>
       </c>
       <c r="E253" t="s">
         <v>8</v>
@@ -6245,13 +6266,13 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D254" t="s">
-        <v>311</v>
+        <v>225</v>
       </c>
       <c r="E254" t="s">
         <v>8</v>
@@ -6262,13 +6283,13 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D255" t="s">
-        <v>270</v>
+        <v>301</v>
       </c>
       <c r="E255" t="s">
         <v>8</v>
@@ -6279,13 +6300,13 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D256" t="s">
-        <v>314</v>
+        <v>266</v>
       </c>
       <c r="E256" t="s">
         <v>8</v>
@@ -6296,13 +6317,13 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D257" t="s">
-        <v>222</v>
+        <v>292</v>
       </c>
       <c r="E257" t="s">
         <v>8</v>
@@ -6313,13 +6334,13 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D258" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="E258" t="s">
         <v>8</v>
@@ -6330,13 +6351,13 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D259" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E259" t="s">
         <v>8</v>
@@ -6347,13 +6368,13 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D260" t="s">
-        <v>251</v>
+        <v>305</v>
       </c>
       <c r="E260" t="s">
         <v>8</v>
@@ -6364,13 +6385,13 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D261" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="E261" t="s">
         <v>8</v>
@@ -6381,13 +6402,13 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D262" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="E262" t="s">
         <v>8</v>
@@ -6398,13 +6419,13 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D263" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="E263" t="s">
         <v>8</v>
@@ -6415,13 +6436,13 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D264" t="s">
-        <v>327</v>
+        <v>256</v>
       </c>
       <c r="E264" t="s">
         <v>8</v>
@@ -6432,13 +6453,13 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D265" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="E265" t="s">
         <v>8</v>
@@ -6449,13 +6470,13 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D266" t="s">
-        <v>330</v>
+        <v>288</v>
       </c>
       <c r="E266" t="s">
         <v>8</v>
@@ -6466,13 +6487,13 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D267" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="E267" t="s">
         <v>8</v>
@@ -6483,13 +6504,13 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D268" t="s">
-        <v>206</v>
+        <v>292</v>
       </c>
       <c r="E268" t="s">
         <v>8</v>
@@ -6500,13 +6521,13 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D269" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="E269" t="s">
         <v>8</v>
@@ -6517,13 +6538,13 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D270" t="s">
-        <v>335</v>
+        <v>238</v>
       </c>
       <c r="E270" t="s">
         <v>8</v>
@@ -6534,13 +6555,13 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D271" t="s">
-        <v>194</v>
+        <v>240</v>
       </c>
       <c r="E271" t="s">
         <v>8</v>
@@ -6551,13 +6572,13 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D272" t="s">
-        <v>275</v>
+        <v>342</v>
       </c>
       <c r="E272" t="s">
         <v>8</v>
@@ -6568,13 +6589,13 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D273" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="E273" t="s">
         <v>8</v>
@@ -6585,13 +6606,13 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D274" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="E274" t="s">
         <v>8</v>
@@ -6602,13 +6623,13 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D275" t="s">
-        <v>288</v>
+        <v>348</v>
       </c>
       <c r="E275" t="s">
         <v>8</v>
@@ -6619,13 +6640,13 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D276" t="s">
-        <v>344</v>
+        <v>288</v>
       </c>
       <c r="E276" t="s">
         <v>8</v>
@@ -6636,13 +6657,13 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D277" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E277" t="s">
         <v>8</v>
@@ -6653,13 +6674,13 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D278" t="s">
-        <v>254</v>
+        <v>352</v>
       </c>
       <c r="E278" t="s">
         <v>8</v>
@@ -6670,13 +6691,13 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D279" t="s">
-        <v>348</v>
+        <v>294</v>
       </c>
       <c r="E279" t="s">
         <v>8</v>
@@ -6687,13 +6708,13 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D280" t="s">
-        <v>198</v>
+        <v>355</v>
       </c>
       <c r="E280" t="s">
         <v>8</v>
@@ -6704,13 +6725,13 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D281" t="s">
-        <v>263</v>
+        <v>357</v>
       </c>
       <c r="E281" t="s">
         <v>8</v>
@@ -6721,13 +6742,13 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D282" t="s">
-        <v>204</v>
+        <v>359</v>
       </c>
       <c r="E282" t="s">
         <v>8</v>
@@ -6738,13 +6759,13 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D283" t="s">
-        <v>233</v>
+        <v>202</v>
       </c>
       <c r="E283" t="s">
         <v>8</v>
@@ -6755,13 +6776,13 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D284" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="E284" t="s">
         <v>8</v>
@@ -6772,13 +6793,13 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D285" t="s">
-        <v>263</v>
+        <v>228</v>
       </c>
       <c r="E285" t="s">
         <v>8</v>
@@ -6789,13 +6810,13 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D286" t="s">
-        <v>356</v>
+        <v>288</v>
       </c>
       <c r="E286" t="s">
         <v>8</v>
@@ -6806,13 +6827,13 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D287" t="s">
-        <v>263</v>
+        <v>348</v>
       </c>
       <c r="E287" t="s">
         <v>8</v>
@@ -6823,13 +6844,13 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D288" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="E288" t="s">
         <v>8</v>
@@ -6840,13 +6861,13 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D289" t="s">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="E289" t="s">
         <v>8</v>
@@ -6857,13 +6878,13 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D290" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E290" t="s">
         <v>8</v>
@@ -6874,13 +6895,13 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D291" t="s">
-        <v>298</v>
+        <v>243</v>
       </c>
       <c r="E291" t="s">
         <v>8</v>
@@ -6891,13 +6912,13 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D292" t="s">
-        <v>364</v>
+        <v>290</v>
       </c>
       <c r="E292" t="s">
         <v>8</v>
@@ -6908,13 +6929,13 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D293" t="s">
-        <v>366</v>
+        <v>322</v>
       </c>
       <c r="E293" t="s">
         <v>8</v>
@@ -6925,13 +6946,13 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D294" t="s">
-        <v>286</v>
+        <v>204</v>
       </c>
       <c r="E294" t="s">
         <v>8</v>
@@ -6942,13 +6963,13 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D295" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="E295" t="s">
         <v>8</v>
@@ -6959,13 +6980,13 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D296" t="s">
-        <v>247</v>
+        <v>375</v>
       </c>
       <c r="E296" t="s">
         <v>8</v>
@@ -6976,13 +6997,13 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D297" t="s">
-        <v>218</v>
+        <v>366</v>
       </c>
       <c r="E297" t="s">
         <v>8</v>
@@ -6993,13 +7014,13 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D298" t="s">
-        <v>278</v>
+        <v>232</v>
       </c>
       <c r="E298" t="s">
         <v>8</v>
@@ -7010,13 +7031,13 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D299" t="s">
-        <v>278</v>
+        <v>379</v>
       </c>
       <c r="E299" t="s">
         <v>8</v>
@@ -7027,13 +7048,13 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D300" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="E300" t="s">
         <v>8</v>
@@ -7044,13 +7065,13 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D301" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="E301" t="s">
         <v>8</v>
@@ -7061,13 +7082,13 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D302" t="s">
-        <v>236</v>
+        <v>383</v>
       </c>
       <c r="E302" t="s">
         <v>8</v>
@@ -7078,13 +7099,13 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D303" t="s">
-        <v>377</v>
+        <v>307</v>
       </c>
       <c r="E303" t="s">
         <v>8</v>
@@ -7095,13 +7116,13 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D304" t="s">
-        <v>298</v>
+        <v>346</v>
       </c>
       <c r="E304" t="s">
         <v>8</v>
@@ -7112,13 +7133,13 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D305" t="s">
-        <v>380</v>
+        <v>288</v>
       </c>
       <c r="E305" t="s">
         <v>8</v>
@@ -7129,13 +7150,13 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D306" t="s">
-        <v>231</v>
+        <v>388</v>
       </c>
       <c r="E306" t="s">
         <v>8</v>
@@ -7146,13 +7167,13 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D307" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="E307" t="s">
         <v>8</v>
@@ -7163,13 +7184,13 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D308" t="s">
-        <v>305</v>
+        <v>383</v>
       </c>
       <c r="E308" t="s">
         <v>8</v>
@@ -7180,13 +7201,13 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D309" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="E309" t="s">
         <v>8</v>
@@ -7197,13 +7218,13 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D310" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="E310" t="s">
         <v>8</v>
@@ -7214,13 +7235,13 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D311" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="E311" t="s">
         <v>8</v>
@@ -7231,13 +7252,13 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D312" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="E312" t="s">
         <v>8</v>
@@ -7248,13 +7269,13 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D313" t="s">
-        <v>391</v>
+        <v>254</v>
       </c>
       <c r="E313" t="s">
         <v>8</v>
@@ -7265,13 +7286,13 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D314" t="s">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="E314" t="s">
         <v>8</v>
@@ -7282,13 +7303,13 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D315" t="s">
-        <v>238</v>
+        <v>301</v>
       </c>
       <c r="E315" t="s">
         <v>8</v>
@@ -7299,13 +7320,13 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D316" t="s">
-        <v>330</v>
+        <v>299</v>
       </c>
       <c r="E316" t="s">
         <v>8</v>
@@ -7316,13 +7337,13 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D317" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="E317" t="s">
         <v>8</v>
@@ -7333,13 +7354,13 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D318" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="E318" t="s">
         <v>8</v>
@@ -7350,13 +7371,13 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D319" t="s">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="E319" t="s">
         <v>8</v>
@@ -7367,13 +7388,13 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D320" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="E320" t="s">
         <v>8</v>
@@ -7384,13 +7405,13 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D321" t="s">
-        <v>204</v>
+        <v>292</v>
       </c>
       <c r="E321" t="s">
         <v>8</v>
@@ -7401,13 +7422,13 @@
         <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D322" t="s">
-        <v>359</v>
+        <v>243</v>
       </c>
       <c r="E322" t="s">
         <v>8</v>
@@ -7418,13 +7439,13 @@
         <v>322</v>
       </c>
       <c r="B323" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D323" t="s">
-        <v>402</v>
+        <v>290</v>
       </c>
       <c r="E323" t="s">
         <v>8</v>
@@ -7435,13 +7456,13 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D324" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E324" t="s">
         <v>8</v>
@@ -7452,13 +7473,13 @@
         <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D325" t="s">
-        <v>220</v>
+        <v>388</v>
       </c>
       <c r="E325" t="s">
         <v>8</v>
@@ -7469,13 +7490,13 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D326" t="s">
-        <v>359</v>
+        <v>412</v>
       </c>
       <c r="E326" t="s">
         <v>8</v>
@@ -7486,13 +7507,13 @@
         <v>326</v>
       </c>
       <c r="B327" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D327" t="s">
-        <v>263</v>
+        <v>414</v>
       </c>
       <c r="E327" t="s">
         <v>8</v>
@@ -7503,13 +7524,13 @@
         <v>327</v>
       </c>
       <c r="B328" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D328" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="E328" t="s">
         <v>8</v>
@@ -7520,13 +7541,13 @@
         <v>328</v>
       </c>
       <c r="B329" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D329" t="s">
-        <v>402</v>
+        <v>313</v>
       </c>
       <c r="E329" t="s">
         <v>8</v>
@@ -7537,13 +7558,13 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D330" t="s">
-        <v>200</v>
+        <v>316</v>
       </c>
       <c r="E330" t="s">
         <v>8</v>
@@ -7554,13 +7575,13 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D331" t="s">
-        <v>413</v>
+        <v>388</v>
       </c>
       <c r="E331" t="s">
         <v>8</v>
@@ -7571,13 +7592,13 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D332" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="E332" t="s">
         <v>8</v>
@@ -7588,13 +7609,13 @@
         <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D333" t="s">
-        <v>416</v>
+        <v>190</v>
       </c>
       <c r="E333" t="s">
         <v>8</v>
@@ -7605,13 +7626,13 @@
         <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D334" t="s">
-        <v>323</v>
+        <v>423</v>
       </c>
       <c r="E334" t="s">
         <v>8</v>
@@ -7622,13 +7643,13 @@
         <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D335" t="s">
-        <v>224</v>
+        <v>425</v>
       </c>
       <c r="E335" t="s">
         <v>8</v>
@@ -7639,13 +7660,13 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D336" t="s">
-        <v>245</v>
+        <v>202</v>
       </c>
       <c r="E336" t="s">
         <v>8</v>
@@ -7656,13 +7677,13 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D337" t="s">
-        <v>323</v>
+        <v>428</v>
       </c>
       <c r="E337" t="s">
         <v>8</v>
@@ -7673,13 +7694,13 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D338" t="s">
-        <v>224</v>
+        <v>334</v>
       </c>
       <c r="E338" t="s">
         <v>8</v>
@@ -7690,13 +7711,13 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D339" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="E339" t="s">
         <v>8</v>
@@ -7707,13 +7728,13 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D340" t="s">
-        <v>241</v>
+        <v>316</v>
       </c>
       <c r="E340" t="s">
         <v>8</v>
@@ -7724,13 +7745,13 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D341" t="s">
-        <v>286</v>
+        <v>434</v>
       </c>
       <c r="E341" t="s">
         <v>8</v>
@@ -7741,13 +7762,13 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D342" t="s">
-        <v>427</v>
+        <v>301</v>
       </c>
       <c r="E342" t="s">
         <v>8</v>
@@ -7758,13 +7779,13 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D343" t="s">
-        <v>416</v>
+        <v>276</v>
       </c>
       <c r="E343" t="s">
         <v>8</v>
@@ -7775,13 +7796,13 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D344" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="E344" t="s">
         <v>8</v>
@@ -7792,13 +7813,13 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D345" t="s">
-        <v>416</v>
+        <v>285</v>
       </c>
       <c r="E345" t="s">
         <v>8</v>
@@ -7809,13 +7830,13 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D346" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="E346" t="s">
         <v>8</v>
@@ -7826,13 +7847,13 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D347" t="s">
-        <v>433</v>
+        <v>280</v>
       </c>
       <c r="E347" t="s">
         <v>8</v>
@@ -7843,13 +7864,13 @@
         <v>347</v>
       </c>
       <c r="B348" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D348" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="E348" t="s">
         <v>8</v>
@@ -7860,13 +7881,13 @@
         <v>348</v>
       </c>
       <c r="B349" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D349" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="E349" t="s">
         <v>8</v>
@@ -7877,13 +7898,13 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D350" t="s">
-        <v>247</v>
+        <v>357</v>
       </c>
       <c r="E350" t="s">
         <v>8</v>
@@ -7894,13 +7915,13 @@
         <v>350</v>
       </c>
       <c r="B351" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D351" t="s">
-        <v>391</v>
+        <v>327</v>
       </c>
       <c r="E351" t="s">
         <v>8</v>
@@ -7911,13 +7932,13 @@
         <v>351</v>
       </c>
       <c r="B352" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D352" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="E352" t="s">
         <v>8</v>
@@ -7928,13 +7949,13 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D353" t="s">
-        <v>233</v>
+        <v>447</v>
       </c>
       <c r="E353" t="s">
         <v>8</v>
@@ -7945,13 +7966,13 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D354" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="E354" t="s">
         <v>8</v>
@@ -7962,13 +7983,13 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D355" t="s">
-        <v>404</v>
+        <v>309</v>
       </c>
       <c r="E355" t="s">
         <v>8</v>
@@ -7979,13 +8000,13 @@
         <v>355</v>
       </c>
       <c r="B356" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D356" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="E356" t="s">
         <v>8</v>
@@ -7996,13 +8017,13 @@
         <v>356</v>
       </c>
       <c r="B357" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D357" t="s">
-        <v>341</v>
+        <v>202</v>
       </c>
       <c r="E357" t="s">
         <v>8</v>
@@ -8013,13 +8034,13 @@
         <v>357</v>
       </c>
       <c r="B358" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D358" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="E358" t="s">
         <v>8</v>
@@ -8030,13 +8051,13 @@
         <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D359" t="s">
-        <v>341</v>
+        <v>305</v>
       </c>
       <c r="E359" t="s">
         <v>8</v>
@@ -8047,13 +8068,13 @@
         <v>359</v>
       </c>
       <c r="B360" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D360" t="s">
-        <v>267</v>
+        <v>425</v>
       </c>
       <c r="E360" t="s">
         <v>8</v>
@@ -8064,13 +8085,13 @@
         <v>360</v>
       </c>
       <c r="B361" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D361" t="s">
-        <v>275</v>
+        <v>431</v>
       </c>
       <c r="E361" t="s">
         <v>8</v>
@@ -8081,13 +8102,13 @@
         <v>361</v>
       </c>
       <c r="B362" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D362" t="s">
-        <v>391</v>
+        <v>248</v>
       </c>
       <c r="E362" t="s">
         <v>8</v>
@@ -8098,13 +8119,13 @@
         <v>362</v>
       </c>
       <c r="B363" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D363" t="s">
-        <v>305</v>
+        <v>458</v>
       </c>
       <c r="E363" t="s">
         <v>8</v>
@@ -8115,13 +8136,13 @@
         <v>363</v>
       </c>
       <c r="B364" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D364" t="s">
-        <v>380</v>
+        <v>329</v>
       </c>
       <c r="E364" t="s">
         <v>8</v>
@@ -8132,13 +8153,13 @@
         <v>364</v>
       </c>
       <c r="B365" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D365" t="s">
-        <v>452</v>
+        <v>393</v>
       </c>
       <c r="E365" t="s">
         <v>8</v>
@@ -8149,13 +8170,13 @@
         <v>365</v>
       </c>
       <c r="B366" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D366" t="s">
-        <v>226</v>
+        <v>414</v>
       </c>
       <c r="E366" t="s">
         <v>8</v>
@@ -8166,13 +8187,13 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D367" t="s">
-        <v>377</v>
+        <v>268</v>
       </c>
       <c r="E367" t="s">
         <v>8</v>
@@ -8183,13 +8204,13 @@
         <v>367</v>
       </c>
       <c r="B368" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D368" t="s">
-        <v>452</v>
+        <v>259</v>
       </c>
       <c r="E368" t="s">
         <v>8</v>
@@ -8200,13 +8221,13 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D369" t="s">
-        <v>247</v>
+        <v>425</v>
       </c>
       <c r="E369" t="s">
         <v>8</v>
@@ -8217,13 +8238,13 @@
         <v>369</v>
       </c>
       <c r="B370" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D370" t="s">
-        <v>270</v>
+        <v>412</v>
       </c>
       <c r="E370" t="s">
         <v>8</v>
@@ -8234,13 +8255,13 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D371" t="s">
-        <v>459</v>
+        <v>238</v>
       </c>
       <c r="E371" t="s">
         <v>8</v>
@@ -8251,13 +8272,13 @@
         <v>371</v>
       </c>
       <c r="B372" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D372" t="s">
-        <v>404</v>
+        <v>196</v>
       </c>
       <c r="E372" t="s">
         <v>8</v>
@@ -8268,13 +8289,13 @@
         <v>372</v>
       </c>
       <c r="B373" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D373" t="s">
-        <v>462</v>
+        <v>309</v>
       </c>
       <c r="E373" t="s">
         <v>8</v>
@@ -8285,13 +8306,13 @@
         <v>373</v>
       </c>
       <c r="B374" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D374" t="s">
-        <v>427</v>
+        <v>192</v>
       </c>
       <c r="E374" t="s">
         <v>8</v>
@@ -8302,13 +8323,13 @@
         <v>374</v>
       </c>
       <c r="B375" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D375" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="E375" t="s">
         <v>8</v>
@@ -8319,13 +8340,13 @@
         <v>375</v>
       </c>
       <c r="B376" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D376" t="s">
-        <v>236</v>
+        <v>344</v>
       </c>
       <c r="E376" t="s">
         <v>8</v>
@@ -8336,13 +8357,13 @@
         <v>376</v>
       </c>
       <c r="B377" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D377" t="s">
-        <v>359</v>
+        <v>238</v>
       </c>
       <c r="E377" t="s">
         <v>8</v>
@@ -8353,13 +8374,13 @@
         <v>377</v>
       </c>
       <c r="B378" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D378" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="E378" t="s">
         <v>8</v>
@@ -8370,13 +8391,13 @@
         <v>378</v>
       </c>
       <c r="B379" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D379" t="s">
-        <v>267</v>
+        <v>198</v>
       </c>
       <c r="E379" t="s">
         <v>8</v>
@@ -8387,13 +8408,13 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D380" t="s">
-        <v>317</v>
+        <v>388</v>
       </c>
       <c r="E380" t="s">
         <v>8</v>
@@ -8404,13 +8425,13 @@
         <v>380</v>
       </c>
       <c r="B381" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D381" t="s">
-        <v>377</v>
+        <v>238</v>
       </c>
       <c r="E381" t="s">
         <v>8</v>
@@ -8421,13 +8442,13 @@
         <v>381</v>
       </c>
       <c r="B382" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D382" t="s">
-        <v>270</v>
+        <v>471</v>
       </c>
       <c r="E382" t="s">
         <v>8</v>
@@ -8438,13 +8459,13 @@
         <v>382</v>
       </c>
       <c r="B383" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D383" t="s">
-        <v>218</v>
+        <v>307</v>
       </c>
       <c r="E383" t="s">
         <v>8</v>
@@ -8455,13 +8476,13 @@
         <v>383</v>
       </c>
       <c r="B384" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D384" t="s">
-        <v>241</v>
+        <v>278</v>
       </c>
       <c r="E384" t="s">
         <v>8</v>
@@ -8472,13 +8493,13 @@
         <v>384</v>
       </c>
       <c r="B385" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D385" t="s">
-        <v>209</v>
+        <v>307</v>
       </c>
       <c r="E385" t="s">
         <v>8</v>
@@ -8489,13 +8510,13 @@
         <v>385</v>
       </c>
       <c r="B386" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D386" t="s">
-        <v>465</v>
+        <v>431</v>
       </c>
       <c r="E386" t="s">
         <v>8</v>
@@ -8506,13 +8527,13 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D387" t="s">
-        <v>402</v>
+        <v>485</v>
       </c>
       <c r="E387" t="s">
         <v>8</v>
@@ -8523,13 +8544,13 @@
         <v>387</v>
       </c>
       <c r="B388" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D388" t="s">
-        <v>480</v>
+        <v>238</v>
       </c>
       <c r="E388" t="s">
         <v>8</v>
@@ -8540,13 +8561,13 @@
         <v>388</v>
       </c>
       <c r="B389" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D389" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="E389" t="s">
         <v>8</v>
@@ -8557,13 +8578,13 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D390" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="E390" t="s">
         <v>8</v>
@@ -8574,13 +8595,13 @@
         <v>390</v>
       </c>
       <c r="B391" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D391" t="s">
-        <v>459</v>
+        <v>228</v>
       </c>
       <c r="E391" t="s">
         <v>8</v>
@@ -8591,13 +8612,13 @@
         <v>391</v>
       </c>
       <c r="B392" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D392" t="s">
-        <v>303</v>
+        <v>383</v>
       </c>
       <c r="E392" t="s">
         <v>8</v>
@@ -8608,13 +8629,13 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D393" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="E393" t="s">
         <v>8</v>
@@ -8625,13 +8646,13 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D394" t="s">
-        <v>391</v>
+        <v>234</v>
       </c>
       <c r="E394" t="s">
         <v>8</v>
@@ -8642,13 +8663,13 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D395" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E395" t="s">
         <v>8</v>
@@ -8659,13 +8680,13 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D396" t="s">
-        <v>377</v>
+        <v>264</v>
       </c>
       <c r="E396" t="s">
         <v>8</v>
@@ -8676,13 +8697,13 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D397" t="s">
-        <v>427</v>
+        <v>497</v>
       </c>
       <c r="E397" t="s">
         <v>8</v>
@@ -8693,13 +8714,13 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D398" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="E398" t="s">
         <v>8</v>
@@ -8710,13 +8731,13 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D399" t="s">
-        <v>341</v>
+        <v>292</v>
       </c>
       <c r="E399" t="s">
         <v>8</v>
@@ -8727,13 +8748,13 @@
         <v>399</v>
       </c>
       <c r="B400" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D400" t="s">
-        <v>377</v>
+        <v>348</v>
       </c>
       <c r="E400" t="s">
         <v>8</v>
@@ -8744,13 +8765,13 @@
         <v>400</v>
       </c>
       <c r="B401" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D401" t="s">
-        <v>254</v>
+        <v>292</v>
       </c>
       <c r="E401" t="s">
         <v>8</v>
@@ -8769,47 +8790,47 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="B1" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="B2" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="B3" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="B4" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="B5" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="B6">
         <v>400</v>
@@ -8817,7 +8838,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="B7">
         <v>400</v>
@@ -8825,7 +8846,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -8833,7 +8854,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -8841,10 +8862,10 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="B10" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
     </row>
   </sheetData>

--- a/reports/backend/Excel/Automation_Test_Report.xlsx
+++ b/reports/backend/Excel/Automation_Test_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="513">
   <si>
     <t>#</t>
   </si>
@@ -584,939 +584,921 @@
     <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field apiKey (Verify Point #180)</t>
   </si>
   <si>
-    <t>0.040</t>
+    <t>0.081</t>
   </si>
   <si>
     <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #181)</t>
   </si>
   <si>
+    <t>0.043</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #182)</t>
+  </si>
+  <si>
+    <t>0.023</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #183)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #184)</t>
+  </si>
+  <si>
+    <t>0.071</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #185)</t>
+  </si>
+  <si>
+    <t>0.102</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #186)</t>
+  </si>
+  <si>
+    <t>0.063</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #187)</t>
+  </si>
+  <si>
+    <t>0.044</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #188)</t>
+  </si>
+  <si>
+    <t>0.108</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #189)</t>
+  </si>
+  <si>
+    <t>0.096</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #190)</t>
+  </si>
+  <si>
+    <t>0.093</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #191)</t>
+  </si>
+  <si>
+    <t>0.068</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #192)</t>
+  </si>
+  <si>
+    <t>0.048</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #193)</t>
+  </si>
+  <si>
+    <t>0.074</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #194)</t>
+  </si>
+  <si>
+    <t>0.089</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #195)</t>
+  </si>
+  <si>
+    <t>0.050</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #196)</t>
+  </si>
+  <si>
+    <t>0.100</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #197)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #198)</t>
+  </si>
+  <si>
+    <t>0.047</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #199)</t>
+  </si>
+  <si>
+    <t>0.070</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #200)</t>
+  </si>
+  <si>
+    <t>0.035</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #201)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #202)</t>
+  </si>
+  <si>
+    <t>0.088</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #203)</t>
+  </si>
+  <si>
+    <t>0.090</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #204)</t>
+  </si>
+  <si>
+    <t>0.052</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #205)</t>
+  </si>
+  <si>
+    <t>0.054</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #206)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #207)</t>
+  </si>
+  <si>
     <t>0.106</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #182)</t>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #208)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #209)</t>
+  </si>
+  <si>
+    <t>0.110</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #210)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #211)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code XSS-injection (Verify Point #212)</t>
+  </si>
+  <si>
+    <t>0.062</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #213)</t>
+  </si>
+  <si>
+    <t>0.037</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for CSRF-token (Verify Point #214)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated CORS-origin (Verify Point #215)</t>
+  </si>
+  <si>
+    <t>0.112</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for CSP-header (Verify Point #216)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at session-token (Verify Point #217)</t>
+  </si>
+  <si>
+    <t>0.059</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users-ref (Verify Point #218)</t>
+  </si>
+  <si>
+    <t>0.087</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for items-ref (Verify Point #219)</t>
+  </si>
+  <si>
+    <t>0.056</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field de-DE (Verify Point #220)</t>
+  </si>
+  <si>
+    <t>0.078</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for fr-FR (Verify Point #221)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ja-JP (Verify Point #222)</t>
+  </si>
+  <si>
+    <t>0.098</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for pt-BR (Verify Point #223)</t>
+  </si>
+  <si>
+    <t>0.060</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of it-IT (Verify Point #224)</t>
+  </si>
+  <si>
+    <t>0.064</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for apiKey (Verify Point #225)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for authDomain (Verify Point #226)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value projectId (Verify Point #227)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session storageBucket (Verify Point #228)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier messagingSenderId (Verify Point #229)</t>
+  </si>
+  <si>
+    <t>0.115</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region appId (Verify Point #230)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for name (Verify Point #231)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code id (Verify Point #232)</t>
+  </si>
+  <si>
+    <t>0.021</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource fees.min (Verify Point #233)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for fees.max (Verify Point #234)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated courses (Verify Point #235)</t>
+  </si>
+  <si>
+    <t>0.027</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for ranking.nirf (Verify Point #236)</t>
+  </si>
+  <si>
+    <t>0.057</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at type (Verify Point #237)</t>
+  </si>
+  <si>
+    <t>0.022</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users/uid001 (Verify Point #238)</t>
+  </si>
+  <si>
+    <t>0.033</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for colleges/c001 (Verify Point #239)</t>
+  </si>
+  <si>
+    <t>0.031</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field prompt-length (Verify Point #240)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for session-id-1 (Verify Point #241)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ₹1L (Verify Point #242)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for B.Tech (Verify Point #243)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of 4 years (Verify Point #244)</t>
+  </si>
+  <si>
+    <t>0.082</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for Tamil Nadu (Verify Point #245)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for Chennai (Verify Point #246)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value llama3-8b (Verify Point #247)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session email (Verify Point #248)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier password (Verify Point #249)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region displayName (Verify Point #250)</t>
+  </si>
+  <si>
+    <t>0.103</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for savedColleges (Verify Point #251)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code createdAt (Verify Point #252)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource firebase-auth (Verify Point #253)</t>
+  </si>
+  <si>
+    <t>0.114</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for firestore-read (Verify Point #254)</t>
+  </si>
+  <si>
+    <t>0.077</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated groq-api (Verify Point #255)</t>
+  </si>
+  <si>
+    <t>0.025</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for college-list (Verify Point #256)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at XSS-injection (Verify Point #257)</t>
+  </si>
+  <si>
+    <t>0.042</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation SQL-injection (Verify Point #258)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for CSRF-token (Verify Point #259)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field CORS-origin (Verify Point #260)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for CSP-header (Verify Point #261)</t>
+  </si>
+  <si>
+    <t>0.075</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for session-token (Verify Point #262)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users-ref (Verify Point #263)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of items-ref (Verify Point #264)</t>
+  </si>
+  <si>
+    <t>0.058</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for de-DE (Verify Point #265)</t>
+  </si>
+  <si>
+    <t>0.029</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for fr-FR (Verify Point #266)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ja-JP (Verify Point #267)</t>
+  </si>
+  <si>
+    <t>0.051</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session pt-BR (Verify Point #268)</t>
+  </si>
+  <si>
+    <t>0.116</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier it-IT (Verify Point #269)</t>
+  </si>
+  <si>
+    <t>0.085</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region apiKey (Verify Point #270)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for authDomain (Verify Point #271)</t>
+  </si>
+  <si>
+    <t>0.109</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code projectId (Verify Point #272)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource storageBucket (Verify Point #273)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for messagingSenderId (Verify Point #274)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated appId (Verify Point #275)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for name (Verify Point #276)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at id (Verify Point #277)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation fees.min (Verify Point #278)</t>
+  </si>
+  <si>
+    <t>0.055</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for fees.max (Verify Point #279)</t>
+  </si>
+  <si>
+    <t>0.094</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field courses (Verify Point #280)</t>
+  </si>
+  <si>
+    <t>0.069</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for ranking.nirf (Verify Point #281)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for type (Verify Point #282)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users/uid001 (Verify Point #283)</t>
+  </si>
+  <si>
+    <t>0.091</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of colleges/c001 (Verify Point #284)</t>
+  </si>
+  <si>
+    <t>0.101</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for prompt-length (Verify Point #285)</t>
+  </si>
+  <si>
+    <t>0.034</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for session-id-1 (Verify Point #286)</t>
+  </si>
+  <si>
+    <t>0.099</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ₹1L (Verify Point #287)</t>
+  </si>
+  <si>
+    <t>0.036</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session B.Tech (Verify Point #288)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier 4 years (Verify Point #289)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region Tamil Nadu (Verify Point #290)</t>
+  </si>
+  <si>
+    <t>0.119</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for Chennai (Verify Point #291)</t>
+  </si>
+  <si>
+    <t>0.104</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code llama3-8b (Verify Point #292)</t>
+  </si>
+  <si>
+    <t>0.083</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource email (Verify Point #293)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for password (Verify Point #294)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated displayName (Verify Point #295)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for savedColleges (Verify Point #296)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at createdAt (Verify Point #297)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation firebase-auth (Verify Point #298)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for firestore-read (Verify Point #299)</t>
+  </si>
+  <si>
+    <t>0.086</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field groq-api (Verify Point #300)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for college-list (Verify Point #301)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for XSS-injection (Verify Point #302)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for SQL-injection (Verify Point #303)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of CSRF-token (Verify Point #304)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for CORS-origin (Verify Point #305)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for CSP-header (Verify Point #306)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value session-token (Verify Point #307)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users-ref (Verify Point #308)</t>
+  </si>
+  <si>
+    <t>0.076</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier items-ref (Verify Point #309)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region de-DE (Verify Point #310)</t>
   </si>
   <si>
     <t>0.049</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #183)</t>
-  </si>
-  <si>
-    <t>0.058</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #184)</t>
-  </si>
-  <si>
-    <t>0.078</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #185)</t>
-  </si>
-  <si>
-    <t>0.055</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #186)</t>
-  </si>
-  <si>
-    <t>0.110</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #187)</t>
-  </si>
-  <si>
-    <t>0.042</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #188)</t>
-  </si>
-  <si>
-    <t>0.111</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #189)</t>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for fr-FR (Verify Point #311)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ja-JP (Verify Point #312)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource pt-BR (Verify Point #313)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for it-IT (Verify Point #314)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated apiKey (Verify Point #315)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for authDomain (Verify Point #316)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at projectId (Verify Point #317)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation storageBucket (Verify Point #318)</t>
+  </si>
+  <si>
+    <t>0.113</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for messagingSenderId (Verify Point #319)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field appId (Verify Point #320)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for name (Verify Point #321)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for id (Verify Point #322)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for fees.min (Verify Point #323)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of fees.max (Verify Point #324)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for courses (Verify Point #325)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for ranking.nirf (Verify Point #326)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value type (Verify Point #327)</t>
+  </si>
+  <si>
+    <t>0.095</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users/uid001 (Verify Point #328)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier colleges/c001 (Verify Point #329)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region prompt-length (Verify Point #330)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for session-id-1 (Verify Point #331)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ₹1L (Verify Point #332)</t>
+  </si>
+  <si>
+    <t>0.117</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource B.Tech (Verify Point #333)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for 4 years (Verify Point #334)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated Tamil Nadu (Verify Point #335)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for Chennai (Verify Point #336)</t>
+  </si>
+  <si>
+    <t>0.039</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at llama3-8b (Verify Point #337)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation email (Verify Point #338)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for password (Verify Point #339)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field displayName (Verify Point #340)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for savedColleges (Verify Point #341)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for createdAt (Verify Point #342)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for firebase-auth (Verify Point #343)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of firestore-read (Verify Point #344)</t>
+  </si>
+  <si>
+    <t>0.020</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for groq-api (Verify Point #345)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for college-list (Verify Point #346)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value XSS-injection (Verify Point #347)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session SQL-injection (Verify Point #348)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier CSRF-token (Verify Point #349)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region CORS-origin (Verify Point #350)</t>
+  </si>
+  <si>
+    <t>0.084</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for CSP-header (Verify Point #351)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code session-token (Verify Point #352)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users-ref (Verify Point #353)</t>
+  </si>
+  <si>
+    <t>0.041</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for items-ref (Verify Point #354)</t>
+  </si>
+  <si>
+    <t>0.092</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated de-DE (Verify Point #355)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for fr-FR (Verify Point #356)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ja-JP (Verify Point #357)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation pt-BR (Verify Point #358)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for it-IT (Verify Point #359)</t>
+  </si>
+  <si>
+    <t>0.053</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field apiKey (Verify Point #360)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #361)</t>
+  </si>
+  <si>
+    <t>0.038</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #362)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #363)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #364)</t>
+  </si>
+  <si>
+    <t>0.080</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #365)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #366)</t>
+  </si>
+  <si>
+    <t>0.045</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #367)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #368)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #369)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #370)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #371)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #372)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #373)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #374)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #375)</t>
+  </si>
+  <si>
+    <t>0.079</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #376)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #377)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #378)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #379)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #380)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #381)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #382)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #383)</t>
+  </si>
+  <si>
+    <t>0.118</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #384)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #385)</t>
+  </si>
+  <si>
+    <t>0.026</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #386)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #387)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #388)</t>
+  </si>
+  <si>
+    <t>0.032</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #389)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #390)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #391)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code XSS-injection (Verify Point #392)</t>
+  </si>
+  <si>
+    <t>0.067</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #393)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for CSRF-token (Verify Point #394)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated CORS-origin (Verify Point #395)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for CSP-header (Verify Point #396)</t>
+  </si>
+  <si>
+    <t>0.030</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at session-token (Verify Point #397)</t>
   </si>
   <si>
     <t>0.066</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #190)</t>
-  </si>
-  <si>
-    <t>0.026</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #191)</t>
-  </si>
-  <si>
-    <t>0.046</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #192)</t>
-  </si>
-  <si>
-    <t>0.067</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #193)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #194)</t>
-  </si>
-  <si>
-    <t>0.038</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #195)</t>
-  </si>
-  <si>
-    <t>0.094</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #196)</t>
-  </si>
-  <si>
-    <t>0.062</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #197)</t>
-  </si>
-  <si>
-    <t>0.043</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #198)</t>
-  </si>
-  <si>
-    <t>0.119</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #199)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #200)</t>
-  </si>
-  <si>
-    <t>0.115</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #201)</t>
-  </si>
-  <si>
-    <t>0.105</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #202)</t>
-  </si>
-  <si>
-    <t>0.100</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #203)</t>
-  </si>
-  <si>
-    <t>0.077</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #204)</t>
-  </si>
-  <si>
-    <t>0.083</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #205)</t>
-  </si>
-  <si>
-    <t>0.027</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #206)</t>
-  </si>
-  <si>
-    <t>0.113</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #207)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #208)</t>
-  </si>
-  <si>
-    <t>0.044</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #209)</t>
-  </si>
-  <si>
-    <t>0.052</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #210)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #211)</t>
-  </si>
-  <si>
-    <t>0.054</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code XSS-injection (Verify Point #212)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #213)</t>
-  </si>
-  <si>
-    <t>0.118</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for CSRF-token (Verify Point #214)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated CORS-origin (Verify Point #215)</t>
-  </si>
-  <si>
-    <t>0.085</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for CSP-header (Verify Point #216)</t>
-  </si>
-  <si>
-    <t>0.024</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at session-token (Verify Point #217)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users-ref (Verify Point #218)</t>
-  </si>
-  <si>
-    <t>0.039</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for items-ref (Verify Point #219)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field de-DE (Verify Point #220)</t>
-  </si>
-  <si>
-    <t>0.074</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for fr-FR (Verify Point #221)</t>
-  </si>
-  <si>
-    <t>0.109</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ja-JP (Verify Point #222)</t>
-  </si>
-  <si>
-    <t>0.023</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for pt-BR (Verify Point #223)</t>
-  </si>
-  <si>
-    <t>0.087</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of it-IT (Verify Point #224)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for apiKey (Verify Point #225)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for authDomain (Verify Point #226)</t>
-  </si>
-  <si>
-    <t>0.032</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value projectId (Verify Point #227)</t>
-  </si>
-  <si>
-    <t>0.090</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session storageBucket (Verify Point #228)</t>
-  </si>
-  <si>
-    <t>0.031</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier messagingSenderId (Verify Point #229)</t>
-  </si>
-  <si>
-    <t>0.073</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region appId (Verify Point #230)</t>
-  </si>
-  <si>
-    <t>0.022</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for name (Verify Point #231)</t>
-  </si>
-  <si>
-    <t>0.045</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code id (Verify Point #232)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource fees.min (Verify Point #233)</t>
-  </si>
-  <si>
-    <t>0.069</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for fees.max (Verify Point #234)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated courses (Verify Point #235)</t>
-  </si>
-  <si>
-    <t>0.061</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for ranking.nirf (Verify Point #236)</t>
-  </si>
-  <si>
-    <t>0.102</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at type (Verify Point #237)</t>
-  </si>
-  <si>
-    <t>0.114</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users/uid001 (Verify Point #238)</t>
-  </si>
-  <si>
-    <t>0.051</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for colleges/c001 (Verify Point #239)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field prompt-length (Verify Point #240)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for session-id-1 (Verify Point #241)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ₹1L (Verify Point #242)</t>
-  </si>
-  <si>
-    <t>0.020</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for B.Tech (Verify Point #243)</t>
-  </si>
-  <si>
-    <t>0.063</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of 4 years (Verify Point #244)</t>
-  </si>
-  <si>
-    <t>0.097</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for Tamil Nadu (Verify Point #245)</t>
-  </si>
-  <si>
-    <t>0.084</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for Chennai (Verify Point #246)</t>
-  </si>
-  <si>
-    <t>0.096</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value llama3-8b (Verify Point #247)</t>
-  </si>
-  <si>
-    <t>0.093</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session email (Verify Point #248)</t>
-  </si>
-  <si>
-    <t>0.034</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier password (Verify Point #249)</t>
-  </si>
-  <si>
-    <t>0.025</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region displayName (Verify Point #250)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for savedColleges (Verify Point #251)</t>
-  </si>
-  <si>
-    <t>0.037</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code createdAt (Verify Point #252)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource firebase-auth (Verify Point #253)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for firestore-read (Verify Point #254)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated groq-api (Verify Point #255)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for college-list (Verify Point #256)</t>
-  </si>
-  <si>
-    <t>0.116</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at XSS-injection (Verify Point #257)</t>
-  </si>
-  <si>
-    <t>0.035</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation SQL-injection (Verify Point #258)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for CSRF-token (Verify Point #259)</t>
-  </si>
-  <si>
-    <t>0.071</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field CORS-origin (Verify Point #260)</t>
-  </si>
-  <si>
-    <t>0.076</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for CSP-header (Verify Point #261)</t>
-  </si>
-  <si>
-    <t>0.112</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for session-token (Verify Point #262)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users-ref (Verify Point #263)</t>
-  </si>
-  <si>
-    <t>0.059</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of items-ref (Verify Point #264)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for de-DE (Verify Point #265)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for fr-FR (Verify Point #266)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ja-JP (Verify Point #267)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session pt-BR (Verify Point #268)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier it-IT (Verify Point #269)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region apiKey (Verify Point #270)</t>
-  </si>
-  <si>
-    <t>0.064</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for authDomain (Verify Point #271)</t>
-  </si>
-  <si>
-    <t>0.088</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code projectId (Verify Point #272)</t>
-  </si>
-  <si>
-    <t>0.080</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource storageBucket (Verify Point #273)</t>
-  </si>
-  <si>
-    <t>0.089</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for messagingSenderId (Verify Point #274)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated appId (Verify Point #275)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for name (Verify Point #276)</t>
-  </si>
-  <si>
-    <t>0.079</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at id (Verify Point #277)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation fees.min (Verify Point #278)</t>
-  </si>
-  <si>
-    <t>0.092</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for fees.max (Verify Point #279)</t>
-  </si>
-  <si>
-    <t>0.107</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field courses (Verify Point #280)</t>
-  </si>
-  <si>
-    <t>0.056</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for ranking.nirf (Verify Point #281)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for type (Verify Point #282)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users/uid001 (Verify Point #283)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of colleges/c001 (Verify Point #284)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for prompt-length (Verify Point #285)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for session-id-1 (Verify Point #286)</t>
-  </si>
-  <si>
-    <t>0.104</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ₹1L (Verify Point #287)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session B.Tech (Verify Point #288)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier 4 years (Verify Point #289)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region Tamil Nadu (Verify Point #290)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for Chennai (Verify Point #291)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code llama3-8b (Verify Point #292)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource email (Verify Point #293)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for password (Verify Point #294)</t>
-  </si>
-  <si>
-    <t>0.103</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated displayName (Verify Point #295)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for savedColleges (Verify Point #296)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at createdAt (Verify Point #297)</t>
-  </si>
-  <si>
-    <t>0.029</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation firebase-auth (Verify Point #298)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for firestore-read (Verify Point #299)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field groq-api (Verify Point #300)</t>
-  </si>
-  <si>
-    <t>0.030</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for college-list (Verify Point #301)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for XSS-injection (Verify Point #302)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for SQL-injection (Verify Point #303)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of CSRF-token (Verify Point #304)</t>
-  </si>
-  <si>
-    <t>0.086</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for CORS-origin (Verify Point #305)</t>
-  </si>
-  <si>
-    <t>0.021</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for CSP-header (Verify Point #306)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value session-token (Verify Point #307)</t>
-  </si>
-  <si>
-    <t>0.099</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users-ref (Verify Point #308)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier items-ref (Verify Point #309)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region de-DE (Verify Point #310)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for fr-FR (Verify Point #311)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ja-JP (Verify Point #312)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource pt-BR (Verify Point #313)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for it-IT (Verify Point #314)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated apiKey (Verify Point #315)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for authDomain (Verify Point #316)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at projectId (Verify Point #317)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation storageBucket (Verify Point #318)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for messagingSenderId (Verify Point #319)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field appId (Verify Point #320)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for name (Verify Point #321)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for id (Verify Point #322)</t>
-  </si>
-  <si>
-    <t>0.033</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for fees.min (Verify Point #323)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of fees.max (Verify Point #324)</t>
-  </si>
-  <si>
-    <t>0.048</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for courses (Verify Point #325)</t>
-  </si>
-  <si>
-    <t>0.036</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for ranking.nirf (Verify Point #326)</t>
-  </si>
-  <si>
-    <t>0.070</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value type (Verify Point #327)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users/uid001 (Verify Point #328)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier colleges/c001 (Verify Point #329)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region prompt-length (Verify Point #330)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for session-id-1 (Verify Point #331)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ₹1L (Verify Point #332)</t>
-  </si>
-  <si>
-    <t>0.028</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource B.Tech (Verify Point #333)</t>
-  </si>
-  <si>
-    <t>0.047</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for 4 years (Verify Point #334)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated Tamil Nadu (Verify Point #335)</t>
-  </si>
-  <si>
-    <t>0.081</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for Chennai (Verify Point #336)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at llama3-8b (Verify Point #337)</t>
-  </si>
-  <si>
-    <t>0.091</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation email (Verify Point #338)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for password (Verify Point #339)</t>
-  </si>
-  <si>
-    <t>0.101</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field displayName (Verify Point #340)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for savedColleges (Verify Point #341)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for createdAt (Verify Point #342)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for firebase-auth (Verify Point #343)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of firestore-read (Verify Point #344)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for groq-api (Verify Point #345)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for college-list (Verify Point #346)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value XSS-injection (Verify Point #347)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session SQL-injection (Verify Point #348)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier CSRF-token (Verify Point #349)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region CORS-origin (Verify Point #350)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for CSP-header (Verify Point #351)</t>
-  </si>
-  <si>
-    <t>0.060</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code session-token (Verify Point #352)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users-ref (Verify Point #353)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for items-ref (Verify Point #354)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated de-DE (Verify Point #355)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for fr-FR (Verify Point #356)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ja-JP (Verify Point #357)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation pt-BR (Verify Point #358)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for it-IT (Verify Point #359)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field apiKey (Verify Point #360)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #361)</t>
-  </si>
-  <si>
-    <t>0.068</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #362)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #363)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #364)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #365)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #366)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #367)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #368)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #369)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #370)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #371)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #372)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #373)</t>
-  </si>
-  <si>
-    <t>0.041</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #374)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #375)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #376)</t>
-  </si>
-  <si>
-    <t>0.053</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #377)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #378)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #379)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #380)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #381)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #382)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #383)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #384)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #385)</t>
-  </si>
-  <si>
-    <t>0.072</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #386)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #387)</t>
-  </si>
-  <si>
-    <t>0.075</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #388)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #389)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #390)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #391)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code XSS-injection (Verify Point #392)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #393)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for CSRF-token (Verify Point #394)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated CORS-origin (Verify Point #395)</t>
-  </si>
-  <si>
-    <t>0.108</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for CSP-header (Verify Point #396)</t>
-  </si>
-  <si>
-    <t>0.117</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at session-token (Verify Point #397)</t>
-  </si>
-  <si>
     <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users-ref (Verify Point #398)</t>
   </si>
   <si>
@@ -1532,13 +1514,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>19</t>
+    <t>20</t>
   </si>
   <si>
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 14:34:46 UTC</t>
+    <t>2026-06-23 14:56:10 UTC</t>
   </si>
   <si>
     <t>Branch</t>
@@ -1550,7 +1532,7 @@
     <t>Commit</t>
   </si>
   <si>
-    <t>af530d5</t>
+    <t>a38f0ce</t>
   </si>
   <si>
     <t>Total</t>
@@ -2073,7 +2055,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -2175,7 +2157,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -2430,7 +2412,7 @@
         <v>6</v>
       </c>
       <c r="D28" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -2617,7 +2599,7 @@
         <v>6</v>
       </c>
       <c r="D39" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -2770,7 +2752,7 @@
         <v>6</v>
       </c>
       <c r="D48" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -3127,7 +3109,7 @@
         <v>6</v>
       </c>
       <c r="D69" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E69" t="s">
         <v>8</v>
@@ -3348,7 +3330,7 @@
         <v>6</v>
       </c>
       <c r="D82" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
@@ -3518,7 +3500,7 @@
         <v>6</v>
       </c>
       <c r="D92" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E92" t="s">
         <v>8</v>
@@ -3909,7 +3891,7 @@
         <v>6</v>
       </c>
       <c r="D115" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E115" t="s">
         <v>8</v>
@@ -4028,7 +4010,7 @@
         <v>6</v>
       </c>
       <c r="D122" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E122" t="s">
         <v>8</v>
@@ -4147,7 +4129,7 @@
         <v>6</v>
       </c>
       <c r="D129" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E129" t="s">
         <v>8</v>
@@ -4317,7 +4299,7 @@
         <v>6</v>
       </c>
       <c r="D139" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E139" t="s">
         <v>8</v>
@@ -5099,7 +5081,7 @@
         <v>6</v>
       </c>
       <c r="D185" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E185" t="s">
         <v>8</v>
@@ -5110,13 +5092,13 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
+        <v>196</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D186" t="s">
         <v>197</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D186" t="s">
-        <v>198</v>
       </c>
       <c r="E186" t="s">
         <v>8</v>
@@ -5127,13 +5109,13 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
+        <v>198</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D187" t="s">
         <v>199</v>
-      </c>
-      <c r="C187" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D187" t="s">
-        <v>200</v>
       </c>
       <c r="E187" t="s">
         <v>8</v>
@@ -5144,13 +5126,13 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
+        <v>200</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D188" t="s">
         <v>201</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D188" t="s">
-        <v>202</v>
       </c>
       <c r="E188" t="s">
         <v>8</v>
@@ -5161,13 +5143,13 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
+        <v>202</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D189" t="s">
         <v>203</v>
-      </c>
-      <c r="C189" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D189" t="s">
-        <v>204</v>
       </c>
       <c r="E189" t="s">
         <v>8</v>
@@ -5178,13 +5160,13 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
+        <v>204</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D190" t="s">
         <v>205</v>
-      </c>
-      <c r="C190" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D190" t="s">
-        <v>206</v>
       </c>
       <c r="E190" t="s">
         <v>8</v>
@@ -5195,13 +5177,13 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
+        <v>206</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D191" t="s">
         <v>207</v>
-      </c>
-      <c r="C191" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D191" t="s">
-        <v>208</v>
       </c>
       <c r="E191" t="s">
         <v>8</v>
@@ -5212,13 +5194,13 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
+        <v>208</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D192" t="s">
         <v>209</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D192" t="s">
-        <v>210</v>
       </c>
       <c r="E192" t="s">
         <v>8</v>
@@ -5229,13 +5211,13 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
+        <v>210</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D193" t="s">
         <v>211</v>
-      </c>
-      <c r="C193" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D193" t="s">
-        <v>212</v>
       </c>
       <c r="E193" t="s">
         <v>8</v>
@@ -5246,13 +5228,13 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
+        <v>212</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D194" t="s">
         <v>213</v>
-      </c>
-      <c r="C194" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D194" t="s">
-        <v>214</v>
       </c>
       <c r="E194" t="s">
         <v>8</v>
@@ -5263,13 +5245,13 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
+        <v>214</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D195" t="s">
         <v>215</v>
-      </c>
-      <c r="C195" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D195" t="s">
-        <v>202</v>
       </c>
       <c r="E195" t="s">
         <v>8</v>
@@ -5337,7 +5319,7 @@
         <v>6</v>
       </c>
       <c r="D199" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="E199" t="s">
         <v>8</v>
@@ -5348,13 +5330,13 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
+        <v>223</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D200" t="s">
         <v>224</v>
-      </c>
-      <c r="C200" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D200" t="s">
-        <v>225</v>
       </c>
       <c r="E200" t="s">
         <v>8</v>
@@ -5365,13 +5347,13 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
+        <v>225</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D201" t="s">
         <v>226</v>
-      </c>
-      <c r="C201" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D201" t="s">
-        <v>200</v>
       </c>
       <c r="E201" t="s">
         <v>8</v>
@@ -5405,7 +5387,7 @@
         <v>6</v>
       </c>
       <c r="D203" t="s">
-        <v>230</v>
+        <v>201</v>
       </c>
       <c r="E203" t="s">
         <v>8</v>
@@ -5416,13 +5398,13 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
+        <v>230</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D204" t="s">
         <v>231</v>
-      </c>
-      <c r="C204" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D204" t="s">
-        <v>232</v>
       </c>
       <c r="E204" t="s">
         <v>8</v>
@@ -5433,13 +5415,13 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
+        <v>232</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D205" t="s">
         <v>233</v>
-      </c>
-      <c r="C205" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D205" t="s">
-        <v>234</v>
       </c>
       <c r="E205" t="s">
         <v>8</v>
@@ -5450,13 +5432,13 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
+        <v>234</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D206" t="s">
         <v>235</v>
-      </c>
-      <c r="C206" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D206" t="s">
-        <v>236</v>
       </c>
       <c r="E206" t="s">
         <v>8</v>
@@ -5467,13 +5449,13 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
+        <v>236</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D207" t="s">
         <v>237</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D207" t="s">
-        <v>238</v>
       </c>
       <c r="E207" t="s">
         <v>8</v>
@@ -5484,13 +5466,13 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D208" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="E208" t="s">
         <v>8</v>
@@ -5501,13 +5483,13 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D209" t="s">
-        <v>194</v>
+        <v>240</v>
       </c>
       <c r="E209" t="s">
         <v>8</v>
@@ -5518,13 +5500,13 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D210" t="s">
-        <v>243</v>
+        <v>209</v>
       </c>
       <c r="E210" t="s">
         <v>8</v>
@@ -5535,13 +5517,13 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D211" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E211" t="s">
         <v>8</v>
@@ -5552,13 +5534,13 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D212" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E212" t="s">
         <v>8</v>
@@ -5569,13 +5551,13 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D213" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="E213" t="s">
         <v>8</v>
@@ -5586,13 +5568,13 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D214" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="E214" t="s">
         <v>8</v>
@@ -5603,13 +5585,13 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D215" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E215" t="s">
         <v>8</v>
@@ -5620,13 +5602,13 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D216" t="s">
-        <v>248</v>
+        <v>215</v>
       </c>
       <c r="E216" t="s">
         <v>8</v>
@@ -5637,13 +5619,13 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D217" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E217" t="s">
         <v>8</v>
@@ -5654,13 +5636,13 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D218" t="s">
-        <v>256</v>
+        <v>209</v>
       </c>
       <c r="E218" t="s">
         <v>8</v>
@@ -5671,13 +5653,13 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D219" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E219" t="s">
         <v>8</v>
@@ -5688,13 +5670,13 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D220" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E220" t="s">
         <v>8</v>
@@ -5705,13 +5687,13 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D221" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="E221" t="s">
         <v>8</v>
@@ -5722,13 +5704,13 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
+        <v>260</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D222" t="s">
         <v>261</v>
-      </c>
-      <c r="C222" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D222" t="s">
-        <v>262</v>
       </c>
       <c r="E222" t="s">
         <v>8</v>
@@ -5739,13 +5721,13 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D223" t="s">
-        <v>264</v>
+        <v>211</v>
       </c>
       <c r="E223" t="s">
         <v>8</v>
@@ -5756,13 +5738,13 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D224" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E224" t="s">
         <v>8</v>
@@ -5773,13 +5755,13 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D225" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E225" t="s">
         <v>8</v>
@@ -5790,13 +5772,13 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D226" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="E226" t="s">
         <v>8</v>
@@ -5807,13 +5789,13 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D227" t="s">
-        <v>208</v>
+        <v>261</v>
       </c>
       <c r="E227" t="s">
         <v>8</v>
@@ -5824,13 +5806,13 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D228" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="E228" t="s">
         <v>8</v>
@@ -5841,13 +5823,13 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D229" t="s">
-        <v>274</v>
+        <v>201</v>
       </c>
       <c r="E229" t="s">
         <v>8</v>
@@ -5858,13 +5840,13 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D230" t="s">
-        <v>276</v>
+        <v>194</v>
       </c>
       <c r="E230" t="s">
         <v>8</v>
@@ -5875,13 +5857,13 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D231" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="E231" t="s">
         <v>8</v>
@@ -5892,13 +5874,13 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D232" t="s">
-        <v>280</v>
+        <v>192</v>
       </c>
       <c r="E232" t="s">
         <v>8</v>
@@ -5909,13 +5891,13 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D233" t="s">
-        <v>282</v>
+        <v>226</v>
       </c>
       <c r="E233" t="s">
         <v>8</v>
@@ -5926,13 +5908,13 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D234" t="s">
-        <v>208</v>
+        <v>278</v>
       </c>
       <c r="E234" t="s">
         <v>8</v>
@@ -5943,13 +5925,13 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D235" t="s">
-        <v>285</v>
+        <v>190</v>
       </c>
       <c r="E235" t="s">
         <v>8</v>
@@ -5960,13 +5942,13 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D236" t="s">
-        <v>230</v>
+        <v>261</v>
       </c>
       <c r="E236" t="s">
         <v>8</v>
@@ -5977,13 +5959,13 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D237" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="E237" t="s">
         <v>8</v>
@@ -5994,13 +5976,13 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D238" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="E238" t="s">
         <v>8</v>
@@ -6011,13 +5993,13 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D239" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="E239" t="s">
         <v>8</v>
@@ -6028,13 +6010,13 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D240" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="E240" t="s">
         <v>8</v>
@@ -6045,13 +6027,13 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D241" t="s">
-        <v>196</v>
+        <v>290</v>
       </c>
       <c r="E241" t="s">
         <v>8</v>
@@ -6062,13 +6044,13 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D242" t="s">
-        <v>268</v>
+        <v>233</v>
       </c>
       <c r="E242" t="s">
         <v>8</v>
@@ -6079,13 +6061,13 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D243" t="s">
-        <v>228</v>
+        <v>278</v>
       </c>
       <c r="E243" t="s">
         <v>8</v>
@@ -6096,13 +6078,13 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D244" t="s">
-        <v>299</v>
+        <v>226</v>
       </c>
       <c r="E244" t="s">
         <v>8</v>
@@ -6113,13 +6095,13 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D245" t="s">
-        <v>301</v>
+        <v>217</v>
       </c>
       <c r="E245" t="s">
         <v>8</v>
@@ -6130,13 +6112,13 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D246" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E246" t="s">
         <v>8</v>
@@ -6147,13 +6129,13 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D247" t="s">
-        <v>305</v>
+        <v>207</v>
       </c>
       <c r="E247" t="s">
         <v>8</v>
@@ -6164,13 +6146,13 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D248" t="s">
-        <v>307</v>
+        <v>243</v>
       </c>
       <c r="E248" t="s">
         <v>8</v>
@@ -6181,13 +6163,13 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D249" t="s">
-        <v>309</v>
+        <v>231</v>
       </c>
       <c r="E249" t="s">
         <v>8</v>
@@ -6198,13 +6180,13 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D250" t="s">
-        <v>311</v>
+        <v>290</v>
       </c>
       <c r="E250" t="s">
         <v>8</v>
@@ -6215,13 +6197,13 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D251" t="s">
-        <v>313</v>
+        <v>209</v>
       </c>
       <c r="E251" t="s">
         <v>8</v>
@@ -6232,13 +6214,13 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D252" t="s">
-        <v>248</v>
+        <v>303</v>
       </c>
       <c r="E252" t="s">
         <v>8</v>
@@ -6249,13 +6231,13 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D253" t="s">
-        <v>316</v>
+        <v>282</v>
       </c>
       <c r="E253" t="s">
         <v>8</v>
@@ -6266,13 +6248,13 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D254" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="E254" t="s">
         <v>8</v>
@@ -6283,13 +6265,13 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D255" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="E255" t="s">
         <v>8</v>
@@ -6300,13 +6282,13 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D256" t="s">
-        <v>266</v>
+        <v>309</v>
       </c>
       <c r="E256" t="s">
         <v>8</v>
@@ -6317,13 +6299,13 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D257" t="s">
-        <v>292</v>
+        <v>311</v>
       </c>
       <c r="E257" t="s">
         <v>8</v>
@@ -6334,13 +6316,13 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D258" t="s">
-        <v>322</v>
+        <v>249</v>
       </c>
       <c r="E258" t="s">
         <v>8</v>
@@ -6351,13 +6333,13 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D259" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="E259" t="s">
         <v>8</v>
@@ -6368,13 +6350,13 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D260" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E260" t="s">
         <v>8</v>
@@ -6385,13 +6367,13 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D261" t="s">
-        <v>327</v>
+        <v>286</v>
       </c>
       <c r="E261" t="s">
         <v>8</v>
@@ -6402,13 +6384,13 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D262" t="s">
-        <v>329</v>
+        <v>268</v>
       </c>
       <c r="E262" t="s">
         <v>8</v>
@@ -6419,13 +6401,13 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D263" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="E263" t="s">
         <v>8</v>
@@ -6436,13 +6418,13 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D264" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="E264" t="s">
         <v>8</v>
@@ -6453,13 +6435,13 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D265" t="s">
-        <v>334</v>
+        <v>309</v>
       </c>
       <c r="E265" t="s">
         <v>8</v>
@@ -6470,13 +6452,13 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D266" t="s">
-        <v>288</v>
+        <v>323</v>
       </c>
       <c r="E266" t="s">
         <v>8</v>
@@ -6487,13 +6469,13 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D267" t="s">
-        <v>264</v>
+        <v>325</v>
       </c>
       <c r="E267" t="s">
         <v>8</v>
@@ -6504,13 +6486,13 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D268" t="s">
-        <v>292</v>
+        <v>259</v>
       </c>
       <c r="E268" t="s">
         <v>8</v>
@@ -6521,13 +6503,13 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D269" t="s">
-        <v>285</v>
+        <v>328</v>
       </c>
       <c r="E269" t="s">
         <v>8</v>
@@ -6538,13 +6520,13 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D270" t="s">
-        <v>238</v>
+        <v>330</v>
       </c>
       <c r="E270" t="s">
         <v>8</v>
@@ -6555,13 +6537,13 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D271" t="s">
-        <v>240</v>
+        <v>332</v>
       </c>
       <c r="E271" t="s">
         <v>8</v>
@@ -6572,13 +6554,13 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D272" t="s">
-        <v>342</v>
+        <v>274</v>
       </c>
       <c r="E272" t="s">
         <v>8</v>
@@ -6589,13 +6571,13 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D273" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="E273" t="s">
         <v>8</v>
@@ -6606,13 +6588,13 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D274" t="s">
-        <v>346</v>
+        <v>243</v>
       </c>
       <c r="E274" t="s">
         <v>8</v>
@@ -6623,13 +6605,13 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D275" t="s">
-        <v>348</v>
+        <v>215</v>
       </c>
       <c r="E275" t="s">
         <v>8</v>
@@ -6640,13 +6622,13 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D276" t="s">
-        <v>288</v>
+        <v>197</v>
       </c>
       <c r="E276" t="s">
         <v>8</v>
@@ -6657,13 +6639,13 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D277" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="E277" t="s">
         <v>8</v>
@@ -6674,13 +6656,13 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D278" t="s">
-        <v>352</v>
+        <v>207</v>
       </c>
       <c r="E278" t="s">
         <v>8</v>
@@ -6691,13 +6673,13 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D279" t="s">
-        <v>294</v>
+        <v>261</v>
       </c>
       <c r="E279" t="s">
         <v>8</v>
@@ -6708,13 +6690,13 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D280" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="E280" t="s">
         <v>8</v>
@@ -6725,13 +6707,13 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D281" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="E281" t="s">
         <v>8</v>
@@ -6742,13 +6724,13 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D282" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="E282" t="s">
         <v>8</v>
@@ -6759,13 +6741,13 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D283" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E283" t="s">
         <v>8</v>
@@ -6776,13 +6758,13 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D284" t="s">
-        <v>276</v>
+        <v>213</v>
       </c>
       <c r="E284" t="s">
         <v>8</v>
@@ -6793,13 +6775,13 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D285" t="s">
-        <v>228</v>
+        <v>351</v>
       </c>
       <c r="E285" t="s">
         <v>8</v>
@@ -6810,13 +6792,13 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D286" t="s">
-        <v>288</v>
+        <v>353</v>
       </c>
       <c r="E286" t="s">
         <v>8</v>
@@ -6827,13 +6809,13 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D287" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="E287" t="s">
         <v>8</v>
@@ -6844,13 +6826,13 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D288" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="E288" t="s">
         <v>8</v>
@@ -6861,13 +6843,13 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D289" t="s">
-        <v>254</v>
+        <v>359</v>
       </c>
       <c r="E289" t="s">
         <v>8</v>
@@ -6878,13 +6860,13 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D290" t="s">
-        <v>313</v>
+        <v>259</v>
       </c>
       <c r="E290" t="s">
         <v>8</v>
@@ -6895,13 +6877,13 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D291" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="E291" t="s">
         <v>8</v>
@@ -6912,13 +6894,13 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D292" t="s">
-        <v>290</v>
+        <v>363</v>
       </c>
       <c r="E292" t="s">
         <v>8</v>
@@ -6929,13 +6911,13 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D293" t="s">
-        <v>322</v>
+        <v>365</v>
       </c>
       <c r="E293" t="s">
         <v>8</v>
@@ -6946,13 +6928,13 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D294" t="s">
-        <v>204</v>
+        <v>367</v>
       </c>
       <c r="E294" t="s">
         <v>8</v>
@@ -6963,13 +6945,13 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D295" t="s">
-        <v>292</v>
+        <v>365</v>
       </c>
       <c r="E295" t="s">
         <v>8</v>
@@ -6980,13 +6962,13 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D296" t="s">
-        <v>375</v>
+        <v>264</v>
       </c>
       <c r="E296" t="s">
         <v>8</v>
@@ -6997,13 +6979,13 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D297" t="s">
-        <v>366</v>
+        <v>311</v>
       </c>
       <c r="E297" t="s">
         <v>8</v>
@@ -7014,13 +6996,13 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D298" t="s">
-        <v>232</v>
+        <v>330</v>
       </c>
       <c r="E298" t="s">
         <v>8</v>
@@ -7031,13 +7013,13 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D299" t="s">
-        <v>379</v>
+        <v>296</v>
       </c>
       <c r="E299" t="s">
         <v>8</v>
@@ -7048,13 +7030,13 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D300" t="s">
-        <v>228</v>
+        <v>359</v>
       </c>
       <c r="E300" t="s">
         <v>8</v>
@@ -7065,13 +7047,13 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D301" t="s">
-        <v>288</v>
+        <v>375</v>
       </c>
       <c r="E301" t="s">
         <v>8</v>
@@ -7082,13 +7064,13 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D302" t="s">
-        <v>383</v>
+        <v>278</v>
       </c>
       <c r="E302" t="s">
         <v>8</v>
@@ -7099,13 +7081,13 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D303" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="E303" t="s">
         <v>8</v>
@@ -7116,13 +7098,13 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D304" t="s">
-        <v>346</v>
+        <v>237</v>
       </c>
       <c r="E304" t="s">
         <v>8</v>
@@ -7133,13 +7115,13 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D305" t="s">
-        <v>288</v>
+        <v>226</v>
       </c>
       <c r="E305" t="s">
         <v>8</v>
@@ -7150,13 +7132,13 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D306" t="s">
-        <v>388</v>
+        <v>259</v>
       </c>
       <c r="E306" t="s">
         <v>8</v>
@@ -7167,13 +7149,13 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D307" t="s">
-        <v>390</v>
+        <v>247</v>
       </c>
       <c r="E307" t="s">
         <v>8</v>
@@ -7184,13 +7166,13 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D308" t="s">
-        <v>383</v>
+        <v>219</v>
       </c>
       <c r="E308" t="s">
         <v>8</v>
@@ -7201,13 +7183,13 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D309" t="s">
-        <v>393</v>
+        <v>319</v>
       </c>
       <c r="E309" t="s">
         <v>8</v>
@@ -7218,13 +7200,13 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D310" t="s">
-        <v>232</v>
+        <v>385</v>
       </c>
       <c r="E310" t="s">
         <v>8</v>
@@ -7235,13 +7217,13 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D311" t="s">
-        <v>272</v>
+        <v>240</v>
       </c>
       <c r="E311" t="s">
         <v>8</v>
@@ -7252,13 +7234,13 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D312" t="s">
-        <v>251</v>
+        <v>388</v>
       </c>
       <c r="E312" t="s">
         <v>8</v>
@@ -7269,13 +7251,13 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D313" t="s">
-        <v>254</v>
+        <v>363</v>
       </c>
       <c r="E313" t="s">
         <v>8</v>
@@ -7286,13 +7268,13 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D314" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="E314" t="s">
         <v>8</v>
@@ -7303,13 +7285,13 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D315" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="E315" t="s">
         <v>8</v>
@@ -7320,13 +7302,13 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D316" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="E316" t="s">
         <v>8</v>
@@ -7337,13 +7319,13 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D317" t="s">
-        <v>200</v>
+        <v>286</v>
       </c>
       <c r="E317" t="s">
         <v>8</v>
@@ -7354,13 +7336,13 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D318" t="s">
-        <v>219</v>
+        <v>261</v>
       </c>
       <c r="E318" t="s">
         <v>8</v>
@@ -7371,13 +7353,13 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D319" t="s">
-        <v>272</v>
+        <v>325</v>
       </c>
       <c r="E319" t="s">
         <v>8</v>
@@ -7388,13 +7370,13 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D320" t="s">
-        <v>234</v>
+        <v>397</v>
       </c>
       <c r="E320" t="s">
         <v>8</v>
@@ -7405,13 +7387,13 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D321" t="s">
-        <v>292</v>
+        <v>388</v>
       </c>
       <c r="E321" t="s">
         <v>8</v>
@@ -7422,13 +7404,13 @@
         <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D322" t="s">
-        <v>243</v>
+        <v>388</v>
       </c>
       <c r="E322" t="s">
         <v>8</v>
@@ -7439,13 +7421,13 @@
         <v>322</v>
       </c>
       <c r="B323" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D323" t="s">
-        <v>290</v>
+        <v>332</v>
       </c>
       <c r="E323" t="s">
         <v>8</v>
@@ -7456,13 +7438,13 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D324" t="s">
-        <v>409</v>
+        <v>237</v>
       </c>
       <c r="E324" t="s">
         <v>8</v>
@@ -7473,13 +7455,13 @@
         <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D325" t="s">
-        <v>388</v>
+        <v>365</v>
       </c>
       <c r="E325" t="s">
         <v>8</v>
@@ -7490,13 +7472,13 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D326" t="s">
-        <v>412</v>
+        <v>231</v>
       </c>
       <c r="E326" t="s">
         <v>8</v>
@@ -7507,13 +7489,13 @@
         <v>326</v>
       </c>
       <c r="B327" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D327" t="s">
-        <v>414</v>
+        <v>328</v>
       </c>
       <c r="E327" t="s">
         <v>8</v>
@@ -7524,13 +7506,13 @@
         <v>327</v>
       </c>
       <c r="B328" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D328" t="s">
-        <v>416</v>
+        <v>197</v>
       </c>
       <c r="E328" t="s">
         <v>8</v>
@@ -7541,13 +7523,13 @@
         <v>328</v>
       </c>
       <c r="B329" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D329" t="s">
-        <v>313</v>
+        <v>407</v>
       </c>
       <c r="E329" t="s">
         <v>8</v>
@@ -7558,13 +7540,13 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D330" t="s">
-        <v>316</v>
+        <v>351</v>
       </c>
       <c r="E330" t="s">
         <v>8</v>
@@ -7575,13 +7557,13 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D331" t="s">
-        <v>388</v>
+        <v>307</v>
       </c>
       <c r="E331" t="s">
         <v>8</v>
@@ -7592,13 +7574,13 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D332" t="s">
-        <v>331</v>
+        <v>367</v>
       </c>
       <c r="E332" t="s">
         <v>8</v>
@@ -7609,13 +7591,13 @@
         <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D333" t="s">
-        <v>190</v>
+        <v>309</v>
       </c>
       <c r="E333" t="s">
         <v>8</v>
@@ -7626,13 +7608,13 @@
         <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D334" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="E334" t="s">
         <v>8</v>
@@ -7643,13 +7625,13 @@
         <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D335" t="s">
-        <v>425</v>
+        <v>397</v>
       </c>
       <c r="E335" t="s">
         <v>8</v>
@@ -7660,13 +7642,13 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D336" t="s">
-        <v>202</v>
+        <v>261</v>
       </c>
       <c r="E336" t="s">
         <v>8</v>
@@ -7677,13 +7659,13 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D337" t="s">
-        <v>428</v>
+        <v>197</v>
       </c>
       <c r="E337" t="s">
         <v>8</v>
@@ -7694,13 +7676,13 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D338" t="s">
-        <v>334</v>
+        <v>418</v>
       </c>
       <c r="E338" t="s">
         <v>8</v>
@@ -7711,13 +7693,13 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D339" t="s">
-        <v>431</v>
+        <v>323</v>
       </c>
       <c r="E339" t="s">
         <v>8</v>
@@ -7728,13 +7710,13 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D340" t="s">
-        <v>316</v>
+        <v>259</v>
       </c>
       <c r="E340" t="s">
         <v>8</v>
@@ -7745,13 +7727,13 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D341" t="s">
-        <v>434</v>
+        <v>351</v>
       </c>
       <c r="E341" t="s">
         <v>8</v>
@@ -7762,13 +7744,13 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D342" t="s">
-        <v>301</v>
+        <v>192</v>
       </c>
       <c r="E342" t="s">
         <v>8</v>
@@ -7779,13 +7761,13 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D343" t="s">
-        <v>276</v>
+        <v>215</v>
       </c>
       <c r="E343" t="s">
         <v>8</v>
@@ -7796,13 +7778,13 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D344" t="s">
-        <v>393</v>
+        <v>355</v>
       </c>
       <c r="E344" t="s">
         <v>8</v>
@@ -7813,13 +7795,13 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D345" t="s">
-        <v>285</v>
+        <v>217</v>
       </c>
       <c r="E345" t="s">
         <v>8</v>
@@ -7830,13 +7812,13 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>439</v>
+        <v>426</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D346" t="s">
-        <v>223</v>
+        <v>427</v>
       </c>
       <c r="E346" t="s">
         <v>8</v>
@@ -7847,13 +7829,13 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D347" t="s">
-        <v>280</v>
+        <v>224</v>
       </c>
       <c r="E347" t="s">
         <v>8</v>
@@ -7864,13 +7846,13 @@
         <v>347</v>
       </c>
       <c r="B348" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D348" t="s">
-        <v>303</v>
+        <v>264</v>
       </c>
       <c r="E348" t="s">
         <v>8</v>
@@ -7881,13 +7863,13 @@
         <v>348</v>
       </c>
       <c r="B349" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D349" t="s">
-        <v>228</v>
+        <v>418</v>
       </c>
       <c r="E349" t="s">
         <v>8</v>
@@ -7898,13 +7880,13 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D350" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="E350" t="s">
         <v>8</v>
@@ -7915,13 +7897,13 @@
         <v>350</v>
       </c>
       <c r="B351" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D351" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="E351" t="s">
         <v>8</v>
@@ -7932,13 +7914,13 @@
         <v>351</v>
       </c>
       <c r="B352" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D352" t="s">
-        <v>248</v>
+        <v>434</v>
       </c>
       <c r="E352" t="s">
         <v>8</v>
@@ -7949,13 +7931,13 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D353" t="s">
-        <v>447</v>
+        <v>215</v>
       </c>
       <c r="E353" t="s">
         <v>8</v>
@@ -7966,13 +7948,13 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D354" t="s">
-        <v>390</v>
+        <v>211</v>
       </c>
       <c r="E354" t="s">
         <v>8</v>
@@ -7983,13 +7965,13 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D355" t="s">
-        <v>309</v>
+        <v>438</v>
       </c>
       <c r="E355" t="s">
         <v>8</v>
@@ -8000,13 +7982,13 @@
         <v>355</v>
       </c>
       <c r="B356" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D356" t="s">
-        <v>232</v>
+        <v>440</v>
       </c>
       <c r="E356" t="s">
         <v>8</v>
@@ -8017,13 +7999,13 @@
         <v>356</v>
       </c>
       <c r="B357" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D357" t="s">
-        <v>202</v>
+        <v>311</v>
       </c>
       <c r="E357" t="s">
         <v>8</v>
@@ -8034,13 +8016,13 @@
         <v>357</v>
       </c>
       <c r="B358" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D358" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="E358" t="s">
         <v>8</v>
@@ -8051,13 +8033,13 @@
         <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D359" t="s">
-        <v>305</v>
+        <v>347</v>
       </c>
       <c r="E359" t="s">
         <v>8</v>
@@ -8068,13 +8050,13 @@
         <v>359</v>
       </c>
       <c r="B360" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D360" t="s">
-        <v>425</v>
+        <v>347</v>
       </c>
       <c r="E360" t="s">
         <v>8</v>
@@ -8085,13 +8067,13 @@
         <v>360</v>
       </c>
       <c r="B361" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D361" t="s">
-        <v>431</v>
+        <v>446</v>
       </c>
       <c r="E361" t="s">
         <v>8</v>
@@ -8102,13 +8084,13 @@
         <v>361</v>
       </c>
       <c r="B362" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D362" t="s">
-        <v>248</v>
+        <v>388</v>
       </c>
       <c r="E362" t="s">
         <v>8</v>
@@ -8119,13 +8101,13 @@
         <v>362</v>
       </c>
       <c r="B363" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D363" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="E363" t="s">
         <v>8</v>
@@ -8136,13 +8118,13 @@
         <v>363</v>
       </c>
       <c r="B364" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D364" t="s">
-        <v>329</v>
+        <v>197</v>
       </c>
       <c r="E364" t="s">
         <v>8</v>
@@ -8153,13 +8135,13 @@
         <v>364</v>
       </c>
       <c r="B365" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D365" t="s">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="E365" t="s">
         <v>8</v>
@@ -8170,13 +8152,13 @@
         <v>365</v>
       </c>
       <c r="B366" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D366" t="s">
-        <v>414</v>
+        <v>453</v>
       </c>
       <c r="E366" t="s">
         <v>8</v>
@@ -8187,13 +8169,13 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D367" t="s">
-        <v>268</v>
+        <v>407</v>
       </c>
       <c r="E367" t="s">
         <v>8</v>
@@ -8204,13 +8186,13 @@
         <v>367</v>
       </c>
       <c r="B368" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D368" t="s">
-        <v>259</v>
+        <v>456</v>
       </c>
       <c r="E368" t="s">
         <v>8</v>
@@ -8221,13 +8203,13 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D369" t="s">
-        <v>425</v>
+        <v>235</v>
       </c>
       <c r="E369" t="s">
         <v>8</v>
@@ -8238,13 +8220,13 @@
         <v>369</v>
       </c>
       <c r="B370" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D370" t="s">
-        <v>412</v>
+        <v>215</v>
       </c>
       <c r="E370" t="s">
         <v>8</v>
@@ -8255,13 +8237,13 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D371" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
       <c r="E371" t="s">
         <v>8</v>
@@ -8272,13 +8254,13 @@
         <v>371</v>
       </c>
       <c r="B372" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D372" t="s">
-        <v>196</v>
+        <v>397</v>
       </c>
       <c r="E372" t="s">
         <v>8</v>
@@ -8289,13 +8271,13 @@
         <v>372</v>
       </c>
       <c r="B373" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D373" t="s">
-        <v>309</v>
+        <v>264</v>
       </c>
       <c r="E373" t="s">
         <v>8</v>
@@ -8306,13 +8288,13 @@
         <v>373</v>
       </c>
       <c r="B374" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D374" t="s">
-        <v>192</v>
+        <v>264</v>
       </c>
       <c r="E374" t="s">
         <v>8</v>
@@ -8323,13 +8305,13 @@
         <v>374</v>
       </c>
       <c r="B375" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D375" t="s">
-        <v>471</v>
+        <v>233</v>
       </c>
       <c r="E375" t="s">
         <v>8</v>
@@ -8340,13 +8322,13 @@
         <v>375</v>
       </c>
       <c r="B376" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D376" t="s">
-        <v>344</v>
+        <v>288</v>
       </c>
       <c r="E376" t="s">
         <v>8</v>
@@ -8357,13 +8339,13 @@
         <v>376</v>
       </c>
       <c r="B377" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D377" t="s">
-        <v>238</v>
+        <v>466</v>
       </c>
       <c r="E377" t="s">
         <v>8</v>
@@ -8374,13 +8356,13 @@
         <v>377</v>
       </c>
       <c r="B378" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D378" t="s">
-        <v>475</v>
+        <v>266</v>
       </c>
       <c r="E378" t="s">
         <v>8</v>
@@ -8391,13 +8373,13 @@
         <v>378</v>
       </c>
       <c r="B379" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D379" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="E379" t="s">
         <v>8</v>
@@ -8408,13 +8390,13 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D380" t="s">
-        <v>388</v>
+        <v>355</v>
       </c>
       <c r="E380" t="s">
         <v>8</v>
@@ -8425,13 +8407,13 @@
         <v>380</v>
       </c>
       <c r="B381" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D381" t="s">
-        <v>238</v>
+        <v>434</v>
       </c>
       <c r="E381" t="s">
         <v>8</v>
@@ -8442,13 +8424,13 @@
         <v>381</v>
       </c>
       <c r="B382" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D382" t="s">
-        <v>471</v>
+        <v>413</v>
       </c>
       <c r="E382" t="s">
         <v>8</v>
@@ -8459,13 +8441,13 @@
         <v>382</v>
       </c>
       <c r="B383" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D383" t="s">
-        <v>307</v>
+        <v>255</v>
       </c>
       <c r="E383" t="s">
         <v>8</v>
@@ -8476,13 +8458,13 @@
         <v>383</v>
       </c>
       <c r="B384" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D384" t="s">
-        <v>278</v>
+        <v>453</v>
       </c>
       <c r="E384" t="s">
         <v>8</v>
@@ -8493,13 +8475,13 @@
         <v>384</v>
       </c>
       <c r="B385" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D385" t="s">
-        <v>307</v>
+        <v>475</v>
       </c>
       <c r="E385" t="s">
         <v>8</v>
@@ -8510,13 +8492,13 @@
         <v>385</v>
       </c>
       <c r="B386" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D386" t="s">
-        <v>431</v>
+        <v>215</v>
       </c>
       <c r="E386" t="s">
         <v>8</v>
@@ -8527,13 +8509,13 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D387" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="E387" t="s">
         <v>8</v>
@@ -8544,13 +8526,13 @@
         <v>387</v>
       </c>
       <c r="B388" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D388" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="E388" t="s">
         <v>8</v>
@@ -8561,13 +8543,13 @@
         <v>388</v>
       </c>
       <c r="B389" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D389" t="s">
-        <v>488</v>
+        <v>367</v>
       </c>
       <c r="E389" t="s">
         <v>8</v>
@@ -8578,13 +8560,13 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D390" t="s">
-        <v>251</v>
+        <v>482</v>
       </c>
       <c r="E390" t="s">
         <v>8</v>
@@ -8595,13 +8577,13 @@
         <v>390</v>
       </c>
       <c r="B391" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D391" t="s">
-        <v>228</v>
+        <v>440</v>
       </c>
       <c r="E391" t="s">
         <v>8</v>
@@ -8612,13 +8594,13 @@
         <v>391</v>
       </c>
       <c r="B392" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D392" t="s">
-        <v>383</v>
+        <v>257</v>
       </c>
       <c r="E392" t="s">
         <v>8</v>
@@ -8629,13 +8611,13 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D393" t="s">
-        <v>272</v>
+        <v>221</v>
       </c>
       <c r="E393" t="s">
         <v>8</v>
@@ -8646,13 +8628,13 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D394" t="s">
-        <v>234</v>
+        <v>487</v>
       </c>
       <c r="E394" t="s">
         <v>8</v>
@@ -8663,13 +8645,13 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D395" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="E395" t="s">
         <v>8</v>
@@ -8680,13 +8662,13 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D396" t="s">
-        <v>264</v>
+        <v>388</v>
       </c>
       <c r="E396" t="s">
         <v>8</v>
@@ -8697,13 +8679,13 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D397" t="s">
-        <v>497</v>
+        <v>228</v>
       </c>
       <c r="E397" t="s">
         <v>8</v>
@@ -8714,13 +8696,13 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D398" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="E398" t="s">
         <v>8</v>
@@ -8731,13 +8713,13 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D399" t="s">
-        <v>292</v>
+        <v>494</v>
       </c>
       <c r="E399" t="s">
         <v>8</v>
@@ -8748,13 +8730,13 @@
         <v>399</v>
       </c>
       <c r="B400" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D400" t="s">
-        <v>348</v>
+        <v>217</v>
       </c>
       <c r="E400" t="s">
         <v>8</v>
@@ -8765,13 +8747,13 @@
         <v>400</v>
       </c>
       <c r="B401" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D401" t="s">
-        <v>292</v>
+        <v>203</v>
       </c>
       <c r="E401" t="s">
         <v>8</v>
@@ -8790,47 +8772,47 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="B1" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="B2" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="B3" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="B4" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="B5" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="B6">
         <v>400</v>
@@ -8838,7 +8820,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="B7">
         <v>400</v>
@@ -8846,7 +8828,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -8854,7 +8836,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -8862,10 +8844,10 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="B10" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
     </row>
   </sheetData>

--- a/reports/backend/Excel/Automation_Test_Report.xlsx
+++ b/reports/backend/Excel/Automation_Test_Report.xlsx
@@ -584,921 +584,921 @@
     <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field apiKey (Verify Point #180)</t>
   </si>
   <si>
+    <t>0.048</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #181)</t>
+  </si>
+  <si>
+    <t>0.110</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #182)</t>
+  </si>
+  <si>
+    <t>0.071</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #183)</t>
+  </si>
+  <si>
+    <t>0.085</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #184)</t>
+  </si>
+  <si>
+    <t>0.034</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #185)</t>
+  </si>
+  <si>
+    <t>0.083</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #186)</t>
+  </si>
+  <si>
+    <t>0.021</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #187)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #188)</t>
+  </si>
+  <si>
+    <t>0.108</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #189)</t>
+  </si>
+  <si>
+    <t>0.040</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #190)</t>
+  </si>
+  <si>
+    <t>0.063</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #191)</t>
+  </si>
+  <si>
+    <t>0.064</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #192)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #193)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #194)</t>
+  </si>
+  <si>
+    <t>0.050</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #195)</t>
+  </si>
+  <si>
+    <t>0.100</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #196)</t>
+  </si>
+  <si>
+    <t>0.095</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #197)</t>
+  </si>
+  <si>
+    <t>0.099</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #198)</t>
+  </si>
+  <si>
+    <t>0.047</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #199)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #200)</t>
+  </si>
+  <si>
+    <t>0.090</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #201)</t>
+  </si>
+  <si>
+    <t>0.087</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #202)</t>
+  </si>
+  <si>
+    <t>0.086</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #203)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #204)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #205)</t>
+  </si>
+  <si>
+    <t>0.042</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #206)</t>
+  </si>
+  <si>
+    <t>0.029</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #207)</t>
+  </si>
+  <si>
+    <t>0.041</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #208)</t>
+  </si>
+  <si>
+    <t>0.051</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #209)</t>
+  </si>
+  <si>
+    <t>0.036</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #210)</t>
+  </si>
+  <si>
+    <t>0.075</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #211)</t>
+  </si>
+  <si>
+    <t>0.038</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code XSS-injection (Verify Point #212)</t>
+  </si>
+  <si>
+    <t>0.080</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #213)</t>
+  </si>
+  <si>
+    <t>0.115</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for CSRF-token (Verify Point #214)</t>
+  </si>
+  <si>
+    <t>0.025</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated CORS-origin (Verify Point #215)</t>
+  </si>
+  <si>
+    <t>0.101</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for CSP-header (Verify Point #216)</t>
+  </si>
+  <si>
+    <t>0.022</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at session-token (Verify Point #217)</t>
+  </si>
+  <si>
+    <t>0.089</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users-ref (Verify Point #218)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for items-ref (Verify Point #219)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field de-DE (Verify Point #220)</t>
+  </si>
+  <si>
+    <t>0.091</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for fr-FR (Verify Point #221)</t>
+  </si>
+  <si>
+    <t>0.024</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ja-JP (Verify Point #222)</t>
+  </si>
+  <si>
+    <t>0.113</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for pt-BR (Verify Point #223)</t>
+  </si>
+  <si>
+    <t>0.116</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of it-IT (Verify Point #224)</t>
+  </si>
+  <si>
+    <t>0.078</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for apiKey (Verify Point #225)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for authDomain (Verify Point #226)</t>
+  </si>
+  <si>
+    <t>0.105</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value projectId (Verify Point #227)</t>
+  </si>
+  <si>
+    <t>0.096</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session storageBucket (Verify Point #228)</t>
+  </si>
+  <si>
+    <t>0.028</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier messagingSenderId (Verify Point #229)</t>
+  </si>
+  <si>
+    <t>0.062</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region appId (Verify Point #230)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for name (Verify Point #231)</t>
+  </si>
+  <si>
+    <t>0.098</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code id (Verify Point #232)</t>
+  </si>
+  <si>
+    <t>0.119</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource fees.min (Verify Point #233)</t>
+  </si>
+  <si>
+    <t>0.033</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for fees.max (Verify Point #234)</t>
+  </si>
+  <si>
+    <t>0.069</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated courses (Verify Point #235)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for ranking.nirf (Verify Point #236)</t>
+  </si>
+  <si>
+    <t>0.056</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at type (Verify Point #237)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users/uid001 (Verify Point #238)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for colleges/c001 (Verify Point #239)</t>
+  </si>
+  <si>
+    <t>0.073</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field prompt-length (Verify Point #240)</t>
+  </si>
+  <si>
+    <t>0.045</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for session-id-1 (Verify Point #241)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ₹1L (Verify Point #242)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for B.Tech (Verify Point #243)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of 4 years (Verify Point #244)</t>
+  </si>
+  <si>
+    <t>0.059</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for Tamil Nadu (Verify Point #245)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for Chennai (Verify Point #246)</t>
+  </si>
+  <si>
+    <t>0.052</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value llama3-8b (Verify Point #247)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session email (Verify Point #248)</t>
+  </si>
+  <si>
+    <t>0.117</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier password (Verify Point #249)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region displayName (Verify Point #250)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for savedColleges (Verify Point #251)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code createdAt (Verify Point #252)</t>
+  </si>
+  <si>
+    <t>0.077</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource firebase-auth (Verify Point #253)</t>
+  </si>
+  <si>
+    <t>0.112</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for firestore-read (Verify Point #254)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated groq-api (Verify Point #255)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for college-list (Verify Point #256)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at XSS-injection (Verify Point #257)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation SQL-injection (Verify Point #258)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for CSRF-token (Verify Point #259)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field CORS-origin (Verify Point #260)</t>
+  </si>
+  <si>
+    <t>0.044</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for CSP-header (Verify Point #261)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for session-token (Verify Point #262)</t>
+  </si>
+  <si>
+    <t>0.094</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users-ref (Verify Point #263)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of items-ref (Verify Point #264)</t>
+  </si>
+  <si>
+    <t>0.076</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for de-DE (Verify Point #265)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for fr-FR (Verify Point #266)</t>
+  </si>
+  <si>
+    <t>0.107</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ja-JP (Verify Point #267)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session pt-BR (Verify Point #268)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier it-IT (Verify Point #269)</t>
+  </si>
+  <si>
+    <t>0.072</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region apiKey (Verify Point #270)</t>
+  </si>
+  <si>
+    <t>0.054</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for authDomain (Verify Point #271)</t>
+  </si>
+  <si>
+    <t>0.058</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code projectId (Verify Point #272)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource storageBucket (Verify Point #273)</t>
+  </si>
+  <si>
+    <t>0.026</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for messagingSenderId (Verify Point #274)</t>
+  </si>
+  <si>
+    <t>0.023</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated appId (Verify Point #275)</t>
+  </si>
+  <si>
+    <t>0.068</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for name (Verify Point #276)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at id (Verify Point #277)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation fees.min (Verify Point #278)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for fees.max (Verify Point #279)</t>
+  </si>
+  <si>
+    <t>0.102</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field courses (Verify Point #280)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for ranking.nirf (Verify Point #281)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for type (Verify Point #282)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users/uid001 (Verify Point #283)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of colleges/c001 (Verify Point #284)</t>
+  </si>
+  <si>
+    <t>0.049</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for prompt-length (Verify Point #285)</t>
+  </si>
+  <si>
+    <t>0.060</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for session-id-1 (Verify Point #286)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ₹1L (Verify Point #287)</t>
+  </si>
+  <si>
+    <t>0.066</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session B.Tech (Verify Point #288)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier 4 years (Verify Point #289)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region Tamil Nadu (Verify Point #290)</t>
+  </si>
+  <si>
+    <t>0.118</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for Chennai (Verify Point #291)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code llama3-8b (Verify Point #292)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource email (Verify Point #293)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for password (Verify Point #294)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated displayName (Verify Point #295)</t>
+  </si>
+  <si>
+    <t>0.067</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for savedColleges (Verify Point #296)</t>
+  </si>
+  <si>
+    <t>0.106</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at createdAt (Verify Point #297)</t>
+  </si>
+  <si>
+    <t>0.053</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation firebase-auth (Verify Point #298)</t>
+  </si>
+  <si>
     <t>0.081</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #181)</t>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for firestore-read (Verify Point #299)</t>
+  </si>
+  <si>
+    <t>0.074</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field groq-api (Verify Point #300)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for college-list (Verify Point #301)</t>
+  </si>
+  <si>
+    <t>0.065</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for XSS-injection (Verify Point #302)</t>
+  </si>
+  <si>
+    <t>0.046</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for SQL-injection (Verify Point #303)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of CSRF-token (Verify Point #304)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for CORS-origin (Verify Point #305)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for CSP-header (Verify Point #306)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value session-token (Verify Point #307)</t>
   </si>
   <si>
     <t>0.043</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #182)</t>
-  </si>
-  <si>
-    <t>0.023</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #183)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #184)</t>
-  </si>
-  <si>
-    <t>0.071</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #185)</t>
-  </si>
-  <si>
-    <t>0.102</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #186)</t>
-  </si>
-  <si>
-    <t>0.063</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #187)</t>
-  </si>
-  <si>
-    <t>0.044</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #188)</t>
-  </si>
-  <si>
-    <t>0.108</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #189)</t>
-  </si>
-  <si>
-    <t>0.096</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #190)</t>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users-ref (Verify Point #308)</t>
+  </si>
+  <si>
+    <t>0.057</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier items-ref (Verify Point #309)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region de-DE (Verify Point #310)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for fr-FR (Verify Point #311)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ja-JP (Verify Point #312)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource pt-BR (Verify Point #313)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for it-IT (Verify Point #314)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated apiKey (Verify Point #315)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for authDomain (Verify Point #316)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at projectId (Verify Point #317)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation storageBucket (Verify Point #318)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for messagingSenderId (Verify Point #319)</t>
+  </si>
+  <si>
+    <t>0.035</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field appId (Verify Point #320)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for name (Verify Point #321)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for id (Verify Point #322)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for fees.min (Verify Point #323)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of fees.max (Verify Point #324)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for courses (Verify Point #325)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for ranking.nirf (Verify Point #326)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value type (Verify Point #327)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users/uid001 (Verify Point #328)</t>
+  </si>
+  <si>
+    <t>0.061</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier colleges/c001 (Verify Point #329)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region prompt-length (Verify Point #330)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for session-id-1 (Verify Point #331)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ₹1L (Verify Point #332)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource B.Tech (Verify Point #333)</t>
+  </si>
+  <si>
+    <t>0.092</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for 4 years (Verify Point #334)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated Tamil Nadu (Verify Point #335)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for Chennai (Verify Point #336)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at llama3-8b (Verify Point #337)</t>
+  </si>
+  <si>
+    <t>0.104</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation email (Verify Point #338)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for password (Verify Point #339)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field displayName (Verify Point #340)</t>
+  </si>
+  <si>
+    <t>0.030</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for savedColleges (Verify Point #341)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for createdAt (Verify Point #342)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for firebase-auth (Verify Point #343)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of firestore-read (Verify Point #344)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for groq-api (Verify Point #345)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for college-list (Verify Point #346)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value XSS-injection (Verify Point #347)</t>
+  </si>
+  <si>
+    <t>0.084</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session SQL-injection (Verify Point #348)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier CSRF-token (Verify Point #349)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region CORS-origin (Verify Point #350)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for CSP-header (Verify Point #351)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code session-token (Verify Point #352)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users-ref (Verify Point #353)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for items-ref (Verify Point #354)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated de-DE (Verify Point #355)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for fr-FR (Verify Point #356)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ja-JP (Verify Point #357)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation pt-BR (Verify Point #358)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for it-IT (Verify Point #359)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field apiKey (Verify Point #360)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #361)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #362)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #363)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #364)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #365)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #366)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #367)</t>
+  </si>
+  <si>
+    <t>0.032</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #368)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #369)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #370)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #371)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #372)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #373)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #374)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #375)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #376)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #377)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #378)</t>
   </si>
   <si>
     <t>0.093</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #191)</t>
-  </si>
-  <si>
-    <t>0.068</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #192)</t>
-  </si>
-  <si>
-    <t>0.048</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #193)</t>
-  </si>
-  <si>
-    <t>0.074</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #194)</t>
-  </si>
-  <si>
-    <t>0.089</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #195)</t>
-  </si>
-  <si>
-    <t>0.050</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #196)</t>
-  </si>
-  <si>
-    <t>0.100</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #197)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #198)</t>
-  </si>
-  <si>
-    <t>0.047</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #199)</t>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #379)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #380)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #381)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #382)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #383)</t>
+  </si>
+  <si>
+    <t>0.082</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #384)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #385)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #386)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #387)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #388)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #389)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #390)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #391)</t>
   </si>
   <si>
     <t>0.070</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #200)</t>
-  </si>
-  <si>
-    <t>0.035</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #201)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #202)</t>
-  </si>
-  <si>
-    <t>0.088</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #203)</t>
-  </si>
-  <si>
-    <t>0.090</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #204)</t>
-  </si>
-  <si>
-    <t>0.052</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #205)</t>
-  </si>
-  <si>
-    <t>0.054</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #206)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #207)</t>
-  </si>
-  <si>
-    <t>0.106</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #208)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #209)</t>
-  </si>
-  <si>
-    <t>0.110</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #210)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #211)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code XSS-injection (Verify Point #212)</t>
-  </si>
-  <si>
-    <t>0.062</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #213)</t>
-  </si>
-  <si>
-    <t>0.037</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for CSRF-token (Verify Point #214)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated CORS-origin (Verify Point #215)</t>
-  </si>
-  <si>
-    <t>0.112</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for CSP-header (Verify Point #216)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at session-token (Verify Point #217)</t>
-  </si>
-  <si>
-    <t>0.059</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users-ref (Verify Point #218)</t>
-  </si>
-  <si>
-    <t>0.087</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for items-ref (Verify Point #219)</t>
-  </si>
-  <si>
-    <t>0.056</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field de-DE (Verify Point #220)</t>
-  </si>
-  <si>
-    <t>0.078</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for fr-FR (Verify Point #221)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ja-JP (Verify Point #222)</t>
-  </si>
-  <si>
-    <t>0.098</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for pt-BR (Verify Point #223)</t>
-  </si>
-  <si>
-    <t>0.060</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of it-IT (Verify Point #224)</t>
-  </si>
-  <si>
-    <t>0.064</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for apiKey (Verify Point #225)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for authDomain (Verify Point #226)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value projectId (Verify Point #227)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session storageBucket (Verify Point #228)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier messagingSenderId (Verify Point #229)</t>
-  </si>
-  <si>
-    <t>0.115</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region appId (Verify Point #230)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for name (Verify Point #231)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code id (Verify Point #232)</t>
-  </si>
-  <si>
-    <t>0.021</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource fees.min (Verify Point #233)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for fees.max (Verify Point #234)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated courses (Verify Point #235)</t>
-  </si>
-  <si>
-    <t>0.027</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for ranking.nirf (Verify Point #236)</t>
-  </si>
-  <si>
-    <t>0.057</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at type (Verify Point #237)</t>
-  </si>
-  <si>
-    <t>0.022</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users/uid001 (Verify Point #238)</t>
-  </si>
-  <si>
-    <t>0.033</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for colleges/c001 (Verify Point #239)</t>
-  </si>
-  <si>
-    <t>0.031</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field prompt-length (Verify Point #240)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for session-id-1 (Verify Point #241)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ₹1L (Verify Point #242)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for B.Tech (Verify Point #243)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of 4 years (Verify Point #244)</t>
-  </si>
-  <si>
-    <t>0.082</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for Tamil Nadu (Verify Point #245)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for Chennai (Verify Point #246)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value llama3-8b (Verify Point #247)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session email (Verify Point #248)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier password (Verify Point #249)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region displayName (Verify Point #250)</t>
-  </si>
-  <si>
-    <t>0.103</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for savedColleges (Verify Point #251)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code createdAt (Verify Point #252)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource firebase-auth (Verify Point #253)</t>
-  </si>
-  <si>
-    <t>0.114</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for firestore-read (Verify Point #254)</t>
-  </si>
-  <si>
-    <t>0.077</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated groq-api (Verify Point #255)</t>
-  </si>
-  <si>
-    <t>0.025</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for college-list (Verify Point #256)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at XSS-injection (Verify Point #257)</t>
-  </si>
-  <si>
-    <t>0.042</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation SQL-injection (Verify Point #258)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for CSRF-token (Verify Point #259)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field CORS-origin (Verify Point #260)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for CSP-header (Verify Point #261)</t>
-  </si>
-  <si>
-    <t>0.075</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for session-token (Verify Point #262)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users-ref (Verify Point #263)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of items-ref (Verify Point #264)</t>
-  </si>
-  <si>
-    <t>0.058</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for de-DE (Verify Point #265)</t>
-  </si>
-  <si>
-    <t>0.029</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for fr-FR (Verify Point #266)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ja-JP (Verify Point #267)</t>
-  </si>
-  <si>
-    <t>0.051</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session pt-BR (Verify Point #268)</t>
-  </si>
-  <si>
-    <t>0.116</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier it-IT (Verify Point #269)</t>
-  </si>
-  <si>
-    <t>0.085</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region apiKey (Verify Point #270)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for authDomain (Verify Point #271)</t>
-  </si>
-  <si>
-    <t>0.109</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code projectId (Verify Point #272)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource storageBucket (Verify Point #273)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for messagingSenderId (Verify Point #274)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated appId (Verify Point #275)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for name (Verify Point #276)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at id (Verify Point #277)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation fees.min (Verify Point #278)</t>
-  </si>
-  <si>
-    <t>0.055</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for fees.max (Verify Point #279)</t>
-  </si>
-  <si>
-    <t>0.094</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field courses (Verify Point #280)</t>
-  </si>
-  <si>
-    <t>0.069</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for ranking.nirf (Verify Point #281)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for type (Verify Point #282)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users/uid001 (Verify Point #283)</t>
-  </si>
-  <si>
-    <t>0.091</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of colleges/c001 (Verify Point #284)</t>
-  </si>
-  <si>
-    <t>0.101</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for prompt-length (Verify Point #285)</t>
-  </si>
-  <si>
-    <t>0.034</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for session-id-1 (Verify Point #286)</t>
-  </si>
-  <si>
-    <t>0.099</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ₹1L (Verify Point #287)</t>
-  </si>
-  <si>
-    <t>0.036</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session B.Tech (Verify Point #288)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier 4 years (Verify Point #289)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region Tamil Nadu (Verify Point #290)</t>
-  </si>
-  <si>
-    <t>0.119</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for Chennai (Verify Point #291)</t>
-  </si>
-  <si>
-    <t>0.104</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code llama3-8b (Verify Point #292)</t>
-  </si>
-  <si>
-    <t>0.083</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource email (Verify Point #293)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for password (Verify Point #294)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated displayName (Verify Point #295)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for savedColleges (Verify Point #296)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at createdAt (Verify Point #297)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation firebase-auth (Verify Point #298)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for firestore-read (Verify Point #299)</t>
-  </si>
-  <si>
-    <t>0.086</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field groq-api (Verify Point #300)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for college-list (Verify Point #301)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for XSS-injection (Verify Point #302)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for SQL-injection (Verify Point #303)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of CSRF-token (Verify Point #304)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for CORS-origin (Verify Point #305)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for CSP-header (Verify Point #306)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value session-token (Verify Point #307)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users-ref (Verify Point #308)</t>
-  </si>
-  <si>
-    <t>0.076</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier items-ref (Verify Point #309)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region de-DE (Verify Point #310)</t>
-  </si>
-  <si>
-    <t>0.049</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for fr-FR (Verify Point #311)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ja-JP (Verify Point #312)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource pt-BR (Verify Point #313)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for it-IT (Verify Point #314)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated apiKey (Verify Point #315)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for authDomain (Verify Point #316)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at projectId (Verify Point #317)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation storageBucket (Verify Point #318)</t>
-  </si>
-  <si>
-    <t>0.113</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for messagingSenderId (Verify Point #319)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field appId (Verify Point #320)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for name (Verify Point #321)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for id (Verify Point #322)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for fees.min (Verify Point #323)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of fees.max (Verify Point #324)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for courses (Verify Point #325)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for ranking.nirf (Verify Point #326)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value type (Verify Point #327)</t>
-  </si>
-  <si>
-    <t>0.095</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users/uid001 (Verify Point #328)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier colleges/c001 (Verify Point #329)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region prompt-length (Verify Point #330)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for session-id-1 (Verify Point #331)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ₹1L (Verify Point #332)</t>
-  </si>
-  <si>
-    <t>0.117</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource B.Tech (Verify Point #333)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for 4 years (Verify Point #334)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated Tamil Nadu (Verify Point #335)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for Chennai (Verify Point #336)</t>
-  </si>
-  <si>
-    <t>0.039</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at llama3-8b (Verify Point #337)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation email (Verify Point #338)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for password (Verify Point #339)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field displayName (Verify Point #340)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for savedColleges (Verify Point #341)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for createdAt (Verify Point #342)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for firebase-auth (Verify Point #343)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of firestore-read (Verify Point #344)</t>
-  </si>
-  <si>
-    <t>0.020</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for groq-api (Verify Point #345)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for college-list (Verify Point #346)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value XSS-injection (Verify Point #347)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session SQL-injection (Verify Point #348)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier CSRF-token (Verify Point #349)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region CORS-origin (Verify Point #350)</t>
-  </si>
-  <si>
-    <t>0.084</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for CSP-header (Verify Point #351)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code session-token (Verify Point #352)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users-ref (Verify Point #353)</t>
-  </si>
-  <si>
-    <t>0.041</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for items-ref (Verify Point #354)</t>
-  </si>
-  <si>
-    <t>0.092</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated de-DE (Verify Point #355)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for fr-FR (Verify Point #356)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ja-JP (Verify Point #357)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation pt-BR (Verify Point #358)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for it-IT (Verify Point #359)</t>
-  </si>
-  <si>
-    <t>0.053</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field apiKey (Verify Point #360)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #361)</t>
-  </si>
-  <si>
-    <t>0.038</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #362)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #363)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #364)</t>
-  </si>
-  <si>
-    <t>0.080</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #365)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #366)</t>
-  </si>
-  <si>
-    <t>0.045</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #367)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #368)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #369)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #370)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #371)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #372)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #373)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #374)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #375)</t>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code XSS-injection (Verify Point #392)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #393)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for CSRF-token (Verify Point #394)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated CORS-origin (Verify Point #395)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for CSP-header (Verify Point #396)</t>
   </si>
   <si>
     <t>0.079</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #376)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #377)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #378)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #379)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #380)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #381)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #382)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #383)</t>
-  </si>
-  <si>
-    <t>0.118</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #384)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #385)</t>
-  </si>
-  <si>
-    <t>0.026</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #386)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #387)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #388)</t>
-  </si>
-  <si>
-    <t>0.032</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #389)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #390)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #391)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code XSS-injection (Verify Point #392)</t>
-  </si>
-  <si>
-    <t>0.067</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #393)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for CSRF-token (Verify Point #394)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated CORS-origin (Verify Point #395)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for CSP-header (Verify Point #396)</t>
-  </si>
-  <si>
-    <t>0.030</t>
-  </si>
-  <si>
     <t>Smart Admission — Backend [Boundary]: Verify boundary condition at session-token (Verify Point #397)</t>
   </si>
   <si>
-    <t>0.066</t>
-  </si>
-  <si>
     <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users-ref (Verify Point #398)</t>
   </si>
   <si>
@@ -1514,13 +1514,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>20</t>
+    <t>21</t>
   </si>
   <si>
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 14:56:10 UTC</t>
+    <t>2026-06-23 15:18:47 UTC</t>
   </si>
   <si>
     <t>Branch</t>
@@ -1532,7 +1532,7 @@
     <t>Commit</t>
   </si>
   <si>
-    <t>a38f0ce</t>
+    <t>6a5e7ca</t>
   </si>
   <si>
     <t>Total</t>
@@ -2157,7 +2157,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -2480,7 +2480,7 @@
         <v>6</v>
       </c>
       <c r="D32" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -2616,7 +2616,7 @@
         <v>6</v>
       </c>
       <c r="D40" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -2752,7 +2752,7 @@
         <v>6</v>
       </c>
       <c r="D48" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -2803,7 +2803,7 @@
         <v>6</v>
       </c>
       <c r="D51" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -2990,7 +2990,7 @@
         <v>6</v>
       </c>
       <c r="D62" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>6</v>
       </c>
       <c r="D73" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E73" t="s">
         <v>8</v>
@@ -3500,7 +3500,7 @@
         <v>6</v>
       </c>
       <c r="D92" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E92" t="s">
         <v>8</v>
@@ -3738,7 +3738,7 @@
         <v>6</v>
       </c>
       <c r="D106" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E106" t="s">
         <v>8</v>
@@ -3891,7 +3891,7 @@
         <v>6</v>
       </c>
       <c r="D115" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E115" t="s">
         <v>8</v>
@@ -4010,7 +4010,7 @@
         <v>6</v>
       </c>
       <c r="D122" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E122" t="s">
         <v>8</v>
@@ -4078,7 +4078,7 @@
         <v>6</v>
       </c>
       <c r="D126" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E126" t="s">
         <v>8</v>
@@ -4299,7 +4299,7 @@
         <v>6</v>
       </c>
       <c r="D139" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E139" t="s">
         <v>8</v>
@@ -4486,7 +4486,7 @@
         <v>6</v>
       </c>
       <c r="D150" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E150" t="s">
         <v>8</v>
@@ -5081,7 +5081,7 @@
         <v>6</v>
       </c>
       <c r="D185" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E185" t="s">
         <v>8</v>
@@ -5092,13 +5092,13 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D186" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E186" t="s">
         <v>8</v>
@@ -5109,13 +5109,13 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D187" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E187" t="s">
         <v>8</v>
@@ -5126,13 +5126,13 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D188" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E188" t="s">
         <v>8</v>
@@ -5143,13 +5143,13 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
+        <v>203</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D189" t="s">
         <v>202</v>
-      </c>
-      <c r="C189" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D189" t="s">
-        <v>203</v>
       </c>
       <c r="E189" t="s">
         <v>8</v>
@@ -5234,7 +5234,7 @@
         <v>6</v>
       </c>
       <c r="D194" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="E194" t="s">
         <v>8</v>
@@ -5245,13 +5245,13 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D195" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="E195" t="s">
         <v>8</v>
@@ -5262,13 +5262,13 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D196" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E196" t="s">
         <v>8</v>
@@ -5279,13 +5279,13 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D197" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E197" t="s">
         <v>8</v>
@@ -5296,13 +5296,13 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D198" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E198" t="s">
         <v>8</v>
@@ -5313,13 +5313,13 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D199" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E199" t="s">
         <v>8</v>
@@ -5330,13 +5330,13 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
+        <v>222</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D200" t="s">
         <v>223</v>
-      </c>
-      <c r="C200" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D200" t="s">
-        <v>224</v>
       </c>
       <c r="E200" t="s">
         <v>8</v>
@@ -5347,13 +5347,13 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D201" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="E201" t="s">
         <v>8</v>
@@ -5364,13 +5364,13 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D202" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E202" t="s">
         <v>8</v>
@@ -5381,13 +5381,13 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D203" t="s">
-        <v>201</v>
+        <v>228</v>
       </c>
       <c r="E203" t="s">
         <v>8</v>
@@ -5398,13 +5398,13 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
+        <v>229</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D204" t="s">
         <v>230</v>
-      </c>
-      <c r="C204" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D204" t="s">
-        <v>231</v>
       </c>
       <c r="E204" t="s">
         <v>8</v>
@@ -5415,13 +5415,13 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D205" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
       <c r="E205" t="s">
         <v>8</v>
@@ -5432,13 +5432,13 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D206" t="s">
-        <v>235</v>
+        <v>202</v>
       </c>
       <c r="E206" t="s">
         <v>8</v>
@@ -5449,13 +5449,13 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D207" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E207" t="s">
         <v>8</v>
@@ -5466,13 +5466,13 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D208" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E208" t="s">
         <v>8</v>
@@ -5483,13 +5483,13 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D209" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E209" t="s">
         <v>8</v>
@@ -5500,13 +5500,13 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D210" t="s">
-        <v>209</v>
+        <v>240</v>
       </c>
       <c r="E210" t="s">
         <v>8</v>
@@ -5517,13 +5517,13 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
+        <v>241</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D211" t="s">
         <v>242</v>
-      </c>
-      <c r="C211" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D211" t="s">
-        <v>243</v>
       </c>
       <c r="E211" t="s">
         <v>8</v>
@@ -5534,13 +5534,13 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
+        <v>243</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D212" t="s">
         <v>244</v>
-      </c>
-      <c r="C212" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D212" t="s">
-        <v>226</v>
       </c>
       <c r="E212" t="s">
         <v>8</v>
@@ -5557,7 +5557,7 @@
         <v>6</v>
       </c>
       <c r="D213" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="E213" t="s">
         <v>8</v>
@@ -5568,13 +5568,13 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D214" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E214" t="s">
         <v>8</v>
@@ -5585,13 +5585,13 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D215" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E215" t="s">
         <v>8</v>
@@ -5602,13 +5602,13 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D216" t="s">
-        <v>215</v>
+        <v>252</v>
       </c>
       <c r="E216" t="s">
         <v>8</v>
@@ -5619,13 +5619,13 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D217" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E217" t="s">
         <v>8</v>
@@ -5636,13 +5636,13 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D218" t="s">
-        <v>209</v>
+        <v>256</v>
       </c>
       <c r="E218" t="s">
         <v>8</v>
@@ -5653,13 +5653,13 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D219" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E219" t="s">
         <v>8</v>
@@ -5670,13 +5670,13 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D220" t="s">
-        <v>257</v>
+        <v>200</v>
       </c>
       <c r="E220" t="s">
         <v>8</v>
@@ -5687,13 +5687,13 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D221" t="s">
-        <v>259</v>
+        <v>230</v>
       </c>
       <c r="E221" t="s">
         <v>8</v>
@@ -5704,13 +5704,13 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D222" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E222" t="s">
         <v>8</v>
@@ -5721,13 +5721,13 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D223" t="s">
-        <v>211</v>
+        <v>264</v>
       </c>
       <c r="E223" t="s">
         <v>8</v>
@@ -5738,13 +5738,13 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D224" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E224" t="s">
         <v>8</v>
@@ -5755,13 +5755,13 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D225" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E225" t="s">
         <v>8</v>
@@ -5772,13 +5772,13 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D226" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E226" t="s">
         <v>8</v>
@@ -5789,13 +5789,13 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D227" t="s">
-        <v>261</v>
+        <v>226</v>
       </c>
       <c r="E227" t="s">
         <v>8</v>
@@ -5806,13 +5806,13 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D228" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="E228" t="s">
         <v>8</v>
@@ -5823,13 +5823,13 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D229" t="s">
-        <v>201</v>
+        <v>275</v>
       </c>
       <c r="E229" t="s">
         <v>8</v>
@@ -5840,13 +5840,13 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D230" t="s">
-        <v>194</v>
+        <v>277</v>
       </c>
       <c r="E230" t="s">
         <v>8</v>
@@ -5857,13 +5857,13 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D231" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="E231" t="s">
         <v>8</v>
@@ -5874,13 +5874,13 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D232" t="s">
-        <v>192</v>
+        <v>228</v>
       </c>
       <c r="E232" t="s">
         <v>8</v>
@@ -5891,13 +5891,13 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D233" t="s">
-        <v>226</v>
+        <v>282</v>
       </c>
       <c r="E233" t="s">
         <v>8</v>
@@ -5908,13 +5908,13 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D234" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="E234" t="s">
         <v>8</v>
@@ -5925,13 +5925,13 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D235" t="s">
-        <v>190</v>
+        <v>286</v>
       </c>
       <c r="E235" t="s">
         <v>8</v>
@@ -5942,13 +5942,13 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D236" t="s">
-        <v>261</v>
+        <v>288</v>
       </c>
       <c r="E236" t="s">
         <v>8</v>
@@ -5959,13 +5959,13 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D237" t="s">
-        <v>282</v>
+        <v>246</v>
       </c>
       <c r="E237" t="s">
         <v>8</v>
@@ -5976,13 +5976,13 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D238" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="E238" t="s">
         <v>8</v>
@@ -5993,13 +5993,13 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D239" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E239" t="s">
         <v>8</v>
@@ -6010,13 +6010,13 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D240" t="s">
-        <v>288</v>
+        <v>207</v>
       </c>
       <c r="E240" t="s">
         <v>8</v>
@@ -6027,13 +6027,13 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D241" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="E241" t="s">
         <v>8</v>
@@ -6044,13 +6044,13 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D242" t="s">
-        <v>233</v>
+        <v>297</v>
       </c>
       <c r="E242" t="s">
         <v>8</v>
@@ -6061,13 +6061,13 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D243" t="s">
-        <v>278</v>
+        <v>219</v>
       </c>
       <c r="E243" t="s">
         <v>8</v>
@@ -6078,13 +6078,13 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D244" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E244" t="s">
         <v>8</v>
@@ -6095,13 +6095,13 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D245" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="E245" t="s">
         <v>8</v>
@@ -6112,13 +6112,13 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D246" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="E246" t="s">
         <v>8</v>
@@ -6129,13 +6129,13 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D247" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E247" t="s">
         <v>8</v>
@@ -6146,13 +6146,13 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D248" t="s">
-        <v>243</v>
+        <v>305</v>
       </c>
       <c r="E248" t="s">
         <v>8</v>
@@ -6163,13 +6163,13 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D249" t="s">
-        <v>231</v>
+        <v>288</v>
       </c>
       <c r="E249" t="s">
         <v>8</v>
@@ -6180,13 +6180,13 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D250" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="E250" t="s">
         <v>8</v>
@@ -6197,13 +6197,13 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D251" t="s">
-        <v>209</v>
+        <v>268</v>
       </c>
       <c r="E251" t="s">
         <v>8</v>
@@ -6214,13 +6214,13 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
+        <v>310</v>
+      </c>
+      <c r="C252" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D252" t="s">
         <v>302</v>
-      </c>
-      <c r="C252" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D252" t="s">
-        <v>303</v>
       </c>
       <c r="E252" t="s">
         <v>8</v>
@@ -6231,13 +6231,13 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D253" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="E253" t="s">
         <v>8</v>
@@ -6248,13 +6248,13 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D254" t="s">
-        <v>235</v>
+        <v>313</v>
       </c>
       <c r="E254" t="s">
         <v>8</v>
@@ -6265,13 +6265,13 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D255" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="E255" t="s">
         <v>8</v>
@@ -6282,13 +6282,13 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D256" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E256" t="s">
         <v>8</v>
@@ -6299,13 +6299,13 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D257" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E257" t="s">
         <v>8</v>
@@ -6316,13 +6316,13 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D258" t="s">
-        <v>249</v>
+        <v>282</v>
       </c>
       <c r="E258" t="s">
         <v>8</v>
@@ -6333,13 +6333,13 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D259" t="s">
-        <v>314</v>
+        <v>268</v>
       </c>
       <c r="E259" t="s">
         <v>8</v>
@@ -6350,13 +6350,13 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D260" t="s">
-        <v>309</v>
+        <v>250</v>
       </c>
       <c r="E260" t="s">
         <v>8</v>
@@ -6367,13 +6367,13 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D261" t="s">
-        <v>286</v>
+        <v>198</v>
       </c>
       <c r="E261" t="s">
         <v>8</v>
@@ -6384,13 +6384,13 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D262" t="s">
-        <v>268</v>
+        <v>323</v>
       </c>
       <c r="E262" t="s">
         <v>8</v>
@@ -6401,13 +6401,13 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D263" t="s">
-        <v>319</v>
+        <v>226</v>
       </c>
       <c r="E263" t="s">
         <v>8</v>
@@ -6418,13 +6418,13 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D264" t="s">
-        <v>268</v>
+        <v>326</v>
       </c>
       <c r="E264" t="s">
         <v>8</v>
@@ -6435,13 +6435,13 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D265" t="s">
-        <v>309</v>
+        <v>228</v>
       </c>
       <c r="E265" t="s">
         <v>8</v>
@@ -6452,13 +6452,13 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D266" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="E266" t="s">
         <v>8</v>
@@ -6469,13 +6469,13 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D267" t="s">
-        <v>325</v>
+        <v>202</v>
       </c>
       <c r="E267" t="s">
         <v>8</v>
@@ -6486,13 +6486,13 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D268" t="s">
-        <v>259</v>
+        <v>332</v>
       </c>
       <c r="E268" t="s">
         <v>8</v>
@@ -6503,13 +6503,13 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D269" t="s">
-        <v>328</v>
+        <v>207</v>
       </c>
       <c r="E269" t="s">
         <v>8</v>
@@ -6520,13 +6520,13 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D270" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E270" t="s">
         <v>8</v>
@@ -6537,13 +6537,13 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D271" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="E271" t="s">
         <v>8</v>
@@ -6554,13 +6554,13 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D272" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="E272" t="s">
         <v>8</v>
@@ -6571,13 +6571,13 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D273" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="E273" t="s">
         <v>8</v>
@@ -6588,13 +6588,13 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D274" t="s">
-        <v>243</v>
+        <v>291</v>
       </c>
       <c r="E274" t="s">
         <v>8</v>
@@ -6605,13 +6605,13 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D275" t="s">
-        <v>215</v>
+        <v>343</v>
       </c>
       <c r="E275" t="s">
         <v>8</v>
@@ -6622,13 +6622,13 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D276" t="s">
-        <v>197</v>
+        <v>345</v>
       </c>
       <c r="E276" t="s">
         <v>8</v>
@@ -6639,13 +6639,13 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D277" t="s">
-        <v>243</v>
+        <v>347</v>
       </c>
       <c r="E277" t="s">
         <v>8</v>
@@ -6656,13 +6656,13 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D278" t="s">
-        <v>207</v>
+        <v>246</v>
       </c>
       <c r="E278" t="s">
         <v>8</v>
@@ -6673,13 +6673,13 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D279" t="s">
-        <v>261</v>
+        <v>336</v>
       </c>
       <c r="E279" t="s">
         <v>8</v>
@@ -6690,13 +6690,13 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D280" t="s">
-        <v>343</v>
+        <v>315</v>
       </c>
       <c r="E280" t="s">
         <v>8</v>
@@ -6707,13 +6707,13 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D281" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="E281" t="s">
         <v>8</v>
@@ -6724,13 +6724,13 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D282" t="s">
-        <v>347</v>
+        <v>315</v>
       </c>
       <c r="E282" t="s">
         <v>8</v>
@@ -6741,13 +6741,13 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D283" t="s">
-        <v>211</v>
+        <v>277</v>
       </c>
       <c r="E283" t="s">
         <v>8</v>
@@ -6758,13 +6758,13 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D284" t="s">
-        <v>213</v>
+        <v>273</v>
       </c>
       <c r="E284" t="s">
         <v>8</v>
@@ -6775,13 +6775,13 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D285" t="s">
-        <v>351</v>
+        <v>226</v>
       </c>
       <c r="E285" t="s">
         <v>8</v>
@@ -6792,13 +6792,13 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D286" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="E286" t="s">
         <v>8</v>
@@ -6809,13 +6809,13 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D287" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="E287" t="s">
         <v>8</v>
@@ -6826,13 +6826,13 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D288" t="s">
-        <v>357</v>
+        <v>236</v>
       </c>
       <c r="E288" t="s">
         <v>8</v>
@@ -6843,13 +6843,13 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D289" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="E289" t="s">
         <v>8</v>
@@ -6860,13 +6860,13 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D290" t="s">
-        <v>259</v>
+        <v>336</v>
       </c>
       <c r="E290" t="s">
         <v>8</v>
@@ -6877,13 +6877,13 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D291" t="s">
-        <v>235</v>
+        <v>279</v>
       </c>
       <c r="E291" t="s">
         <v>8</v>
@@ -6894,13 +6894,13 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D292" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E292" t="s">
         <v>8</v>
@@ -6911,13 +6911,13 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D293" t="s">
-        <v>365</v>
+        <v>291</v>
       </c>
       <c r="E293" t="s">
         <v>8</v>
@@ -6928,13 +6928,13 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D294" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="E294" t="s">
         <v>8</v>
@@ -6945,13 +6945,13 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D295" t="s">
-        <v>365</v>
+        <v>264</v>
       </c>
       <c r="E295" t="s">
         <v>8</v>
@@ -6962,13 +6962,13 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D296" t="s">
-        <v>264</v>
+        <v>190</v>
       </c>
       <c r="E296" t="s">
         <v>8</v>
@@ -6979,13 +6979,13 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D297" t="s">
-        <v>311</v>
+        <v>373</v>
       </c>
       <c r="E297" t="s">
         <v>8</v>
@@ -6996,13 +6996,13 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D298" t="s">
-        <v>330</v>
+        <v>375</v>
       </c>
       <c r="E298" t="s">
         <v>8</v>
@@ -7013,13 +7013,13 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D299" t="s">
-        <v>296</v>
+        <v>377</v>
       </c>
       <c r="E299" t="s">
         <v>8</v>
@@ -7030,13 +7030,13 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D300" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="E300" t="s">
         <v>8</v>
@@ -7047,13 +7047,13 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D301" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="E301" t="s">
         <v>8</v>
@@ -7064,13 +7064,13 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D302" t="s">
-        <v>278</v>
+        <v>340</v>
       </c>
       <c r="E302" t="s">
         <v>8</v>
@@ -7081,13 +7081,13 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D303" t="s">
-        <v>314</v>
+        <v>384</v>
       </c>
       <c r="E303" t="s">
         <v>8</v>
@@ -7098,13 +7098,13 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D304" t="s">
-        <v>237</v>
+        <v>386</v>
       </c>
       <c r="E304" t="s">
         <v>8</v>
@@ -7115,13 +7115,13 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D305" t="s">
-        <v>226</v>
+        <v>345</v>
       </c>
       <c r="E305" t="s">
         <v>8</v>
@@ -7132,13 +7132,13 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D306" t="s">
-        <v>259</v>
+        <v>323</v>
       </c>
       <c r="E306" t="s">
         <v>8</v>
@@ -7149,13 +7149,13 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D307" t="s">
-        <v>247</v>
+        <v>196</v>
       </c>
       <c r="E307" t="s">
         <v>8</v>
@@ -7166,13 +7166,13 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D308" t="s">
-        <v>219</v>
+        <v>379</v>
       </c>
       <c r="E308" t="s">
         <v>8</v>
@@ -7183,13 +7183,13 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D309" t="s">
-        <v>319</v>
+        <v>392</v>
       </c>
       <c r="E309" t="s">
         <v>8</v>
@@ -7200,13 +7200,13 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D310" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="E310" t="s">
         <v>8</v>
@@ -7217,13 +7217,13 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D311" t="s">
-        <v>240</v>
+        <v>379</v>
       </c>
       <c r="E311" t="s">
         <v>8</v>
@@ -7234,13 +7234,13 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D312" t="s">
-        <v>388</v>
+        <v>360</v>
       </c>
       <c r="E312" t="s">
         <v>8</v>
@@ -7251,13 +7251,13 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D313" t="s">
-        <v>363</v>
+        <v>192</v>
       </c>
       <c r="E313" t="s">
         <v>8</v>
@@ -7268,13 +7268,13 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D314" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
       <c r="E314" t="s">
         <v>8</v>
@@ -7285,13 +7285,13 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D315" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="E315" t="s">
         <v>8</v>
@@ -7302,13 +7302,13 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D316" t="s">
-        <v>284</v>
+        <v>338</v>
       </c>
       <c r="E316" t="s">
         <v>8</v>
@@ -7319,13 +7319,13 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D317" t="s">
-        <v>286</v>
+        <v>236</v>
       </c>
       <c r="E317" t="s">
         <v>8</v>
@@ -7336,13 +7336,13 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D318" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="E318" t="s">
         <v>8</v>
@@ -7353,13 +7353,13 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D319" t="s">
-        <v>325</v>
+        <v>207</v>
       </c>
       <c r="E319" t="s">
         <v>8</v>
@@ -7370,13 +7370,13 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D320" t="s">
-        <v>397</v>
+        <v>279</v>
       </c>
       <c r="E320" t="s">
         <v>8</v>
@@ -7387,13 +7387,13 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D321" t="s">
-        <v>388</v>
+        <v>406</v>
       </c>
       <c r="E321" t="s">
         <v>8</v>
@@ -7404,13 +7404,13 @@
         <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D322" t="s">
-        <v>388</v>
+        <v>194</v>
       </c>
       <c r="E322" t="s">
         <v>8</v>
@@ -7421,13 +7421,13 @@
         <v>322</v>
       </c>
       <c r="B323" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D323" t="s">
-        <v>332</v>
+        <v>246</v>
       </c>
       <c r="E323" t="s">
         <v>8</v>
@@ -7438,13 +7438,13 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D324" t="s">
-        <v>237</v>
+        <v>358</v>
       </c>
       <c r="E324" t="s">
         <v>8</v>
@@ -7455,13 +7455,13 @@
         <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D325" t="s">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="E325" t="s">
         <v>8</v>
@@ -7472,13 +7472,13 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D326" t="s">
-        <v>231</v>
+        <v>323</v>
       </c>
       <c r="E326" t="s">
         <v>8</v>
@@ -7489,13 +7489,13 @@
         <v>326</v>
       </c>
       <c r="B327" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D327" t="s">
-        <v>328</v>
+        <v>228</v>
       </c>
       <c r="E327" t="s">
         <v>8</v>
@@ -7506,13 +7506,13 @@
         <v>327</v>
       </c>
       <c r="B328" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D328" t="s">
-        <v>197</v>
+        <v>386</v>
       </c>
       <c r="E328" t="s">
         <v>8</v>
@@ -7523,13 +7523,13 @@
         <v>328</v>
       </c>
       <c r="B329" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D329" t="s">
-        <v>407</v>
+        <v>347</v>
       </c>
       <c r="E329" t="s">
         <v>8</v>
@@ -7540,13 +7540,13 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D330" t="s">
-        <v>351</v>
+        <v>416</v>
       </c>
       <c r="E330" t="s">
         <v>8</v>
@@ -7557,13 +7557,13 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D331" t="s">
-        <v>307</v>
+        <v>360</v>
       </c>
       <c r="E331" t="s">
         <v>8</v>
@@ -7574,7 +7574,7 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>6</v>
@@ -7591,13 +7591,13 @@
         <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D333" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
       <c r="E333" t="s">
         <v>8</v>
@@ -7608,13 +7608,13 @@
         <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D334" t="s">
-        <v>413</v>
+        <v>279</v>
       </c>
       <c r="E334" t="s">
         <v>8</v>
@@ -7625,13 +7625,13 @@
         <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D335" t="s">
-        <v>397</v>
+        <v>422</v>
       </c>
       <c r="E335" t="s">
         <v>8</v>
@@ -7642,13 +7642,13 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D336" t="s">
-        <v>261</v>
+        <v>323</v>
       </c>
       <c r="E336" t="s">
         <v>8</v>
@@ -7659,13 +7659,13 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D337" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E337" t="s">
         <v>8</v>
@@ -7676,13 +7676,13 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D338" t="s">
-        <v>418</v>
+        <v>202</v>
       </c>
       <c r="E338" t="s">
         <v>8</v>
@@ -7693,13 +7693,13 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D339" t="s">
-        <v>323</v>
+        <v>427</v>
       </c>
       <c r="E339" t="s">
         <v>8</v>
@@ -7710,13 +7710,13 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D340" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E340" t="s">
         <v>8</v>
@@ -7727,13 +7727,13 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D341" t="s">
-        <v>351</v>
+        <v>192</v>
       </c>
       <c r="E341" t="s">
         <v>8</v>
@@ -7744,13 +7744,13 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D342" t="s">
-        <v>192</v>
+        <v>431</v>
       </c>
       <c r="E342" t="s">
         <v>8</v>
@@ -7761,13 +7761,13 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D343" t="s">
-        <v>215</v>
+        <v>295</v>
       </c>
       <c r="E343" t="s">
         <v>8</v>
@@ -7778,13 +7778,13 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D344" t="s">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="E344" t="s">
         <v>8</v>
@@ -7795,13 +7795,13 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D345" t="s">
-        <v>217</v>
+        <v>291</v>
       </c>
       <c r="E345" t="s">
         <v>8</v>
@@ -7812,13 +7812,13 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D346" t="s">
-        <v>427</v>
+        <v>268</v>
       </c>
       <c r="E346" t="s">
         <v>8</v>
@@ -7829,13 +7829,13 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D347" t="s">
-        <v>224</v>
+        <v>373</v>
       </c>
       <c r="E347" t="s">
         <v>8</v>
@@ -7846,13 +7846,13 @@
         <v>347</v>
       </c>
       <c r="B348" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D348" t="s">
-        <v>264</v>
+        <v>226</v>
       </c>
       <c r="E348" t="s">
         <v>8</v>
@@ -7863,13 +7863,13 @@
         <v>348</v>
       </c>
       <c r="B349" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D349" t="s">
-        <v>418</v>
+        <v>439</v>
       </c>
       <c r="E349" t="s">
         <v>8</v>
@@ -7880,13 +7880,13 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D350" t="s">
-        <v>365</v>
+        <v>332</v>
       </c>
       <c r="E350" t="s">
         <v>8</v>
@@ -7897,13 +7897,13 @@
         <v>350</v>
       </c>
       <c r="B351" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D351" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E351" t="s">
         <v>8</v>
@@ -7914,13 +7914,13 @@
         <v>351</v>
       </c>
       <c r="B352" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D352" t="s">
-        <v>434</v>
+        <v>386</v>
       </c>
       <c r="E352" t="s">
         <v>8</v>
@@ -7931,13 +7931,13 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D353" t="s">
-        <v>215</v>
+        <v>256</v>
       </c>
       <c r="E353" t="s">
         <v>8</v>
@@ -7948,13 +7948,13 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D354" t="s">
-        <v>211</v>
+        <v>381</v>
       </c>
       <c r="E354" t="s">
         <v>8</v>
@@ -7965,13 +7965,13 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D355" t="s">
-        <v>438</v>
+        <v>305</v>
       </c>
       <c r="E355" t="s">
         <v>8</v>
@@ -7982,13 +7982,13 @@
         <v>355</v>
       </c>
       <c r="B356" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D356" t="s">
-        <v>440</v>
+        <v>240</v>
       </c>
       <c r="E356" t="s">
         <v>8</v>
@@ -7999,13 +7999,13 @@
         <v>356</v>
       </c>
       <c r="B357" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D357" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="E357" t="s">
         <v>8</v>
@@ -8016,13 +8016,13 @@
         <v>357</v>
       </c>
       <c r="B358" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D358" t="s">
-        <v>231</v>
+        <v>266</v>
       </c>
       <c r="E358" t="s">
         <v>8</v>
@@ -8033,13 +8033,13 @@
         <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D359" t="s">
-        <v>347</v>
+        <v>422</v>
       </c>
       <c r="E359" t="s">
         <v>8</v>
@@ -8050,13 +8050,13 @@
         <v>359</v>
       </c>
       <c r="B360" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D360" t="s">
-        <v>347</v>
+        <v>270</v>
       </c>
       <c r="E360" t="s">
         <v>8</v>
@@ -8067,13 +8067,13 @@
         <v>360</v>
       </c>
       <c r="B361" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D361" t="s">
-        <v>446</v>
+        <v>313</v>
       </c>
       <c r="E361" t="s">
         <v>8</v>
@@ -8084,13 +8084,13 @@
         <v>361</v>
       </c>
       <c r="B362" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D362" t="s">
-        <v>388</v>
+        <v>305</v>
       </c>
       <c r="E362" t="s">
         <v>8</v>
@@ -8101,13 +8101,13 @@
         <v>362</v>
       </c>
       <c r="B363" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D363" t="s">
-        <v>449</v>
+        <v>266</v>
       </c>
       <c r="E363" t="s">
         <v>8</v>
@@ -8118,13 +8118,13 @@
         <v>363</v>
       </c>
       <c r="B364" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D364" t="s">
-        <v>197</v>
+        <v>363</v>
       </c>
       <c r="E364" t="s">
         <v>8</v>
@@ -8135,13 +8135,13 @@
         <v>364</v>
       </c>
       <c r="B365" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D365" t="s">
-        <v>367</v>
+        <v>230</v>
       </c>
       <c r="E365" t="s">
         <v>8</v>
@@ -8152,13 +8152,13 @@
         <v>365</v>
       </c>
       <c r="B366" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D366" t="s">
-        <v>453</v>
+        <v>329</v>
       </c>
       <c r="E366" t="s">
         <v>8</v>
@@ -8169,13 +8169,13 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D367" t="s">
-        <v>407</v>
+        <v>367</v>
       </c>
       <c r="E367" t="s">
         <v>8</v>
@@ -8186,13 +8186,13 @@
         <v>367</v>
       </c>
       <c r="B368" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D368" t="s">
-        <v>456</v>
+        <v>360</v>
       </c>
       <c r="E368" t="s">
         <v>8</v>
@@ -8203,13 +8203,13 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D369" t="s">
-        <v>235</v>
+        <v>460</v>
       </c>
       <c r="E369" t="s">
         <v>8</v>
@@ -8220,13 +8220,13 @@
         <v>369</v>
       </c>
       <c r="B370" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D370" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
       <c r="E370" t="s">
         <v>8</v>
@@ -8237,13 +8237,13 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D371" t="s">
-        <v>205</v>
+        <v>275</v>
       </c>
       <c r="E371" t="s">
         <v>8</v>
@@ -8254,13 +8254,13 @@
         <v>371</v>
       </c>
       <c r="B372" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D372" t="s">
-        <v>397</v>
+        <v>367</v>
       </c>
       <c r="E372" t="s">
         <v>8</v>
@@ -8271,13 +8271,13 @@
         <v>372</v>
       </c>
       <c r="B373" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D373" t="s">
-        <v>264</v>
+        <v>226</v>
       </c>
       <c r="E373" t="s">
         <v>8</v>
@@ -8288,13 +8288,13 @@
         <v>373</v>
       </c>
       <c r="B374" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D374" t="s">
-        <v>264</v>
+        <v>192</v>
       </c>
       <c r="E374" t="s">
         <v>8</v>
@@ -8305,13 +8305,13 @@
         <v>374</v>
       </c>
       <c r="B375" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D375" t="s">
-        <v>233</v>
+        <v>427</v>
       </c>
       <c r="E375" t="s">
         <v>8</v>
@@ -8322,13 +8322,13 @@
         <v>375</v>
       </c>
       <c r="B376" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D376" t="s">
-        <v>288</v>
+        <v>439</v>
       </c>
       <c r="E376" t="s">
         <v>8</v>
@@ -8339,13 +8339,13 @@
         <v>376</v>
       </c>
       <c r="B377" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D377" t="s">
-        <v>466</v>
+        <v>230</v>
       </c>
       <c r="E377" t="s">
         <v>8</v>
@@ -8356,13 +8356,13 @@
         <v>377</v>
       </c>
       <c r="B378" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D378" t="s">
-        <v>266</v>
+        <v>352</v>
       </c>
       <c r="E378" t="s">
         <v>8</v>
@@ -8373,13 +8373,13 @@
         <v>378</v>
       </c>
       <c r="B379" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D379" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E379" t="s">
         <v>8</v>
@@ -8390,13 +8390,13 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D380" t="s">
-        <v>355</v>
+        <v>472</v>
       </c>
       <c r="E380" t="s">
         <v>8</v>
@@ -8407,13 +8407,13 @@
         <v>380</v>
       </c>
       <c r="B381" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D381" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E381" t="s">
         <v>8</v>
@@ -8424,13 +8424,13 @@
         <v>381</v>
       </c>
       <c r="B382" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D382" t="s">
-        <v>413</v>
+        <v>286</v>
       </c>
       <c r="E382" t="s">
         <v>8</v>
@@ -8441,13 +8441,13 @@
         <v>382</v>
       </c>
       <c r="B383" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D383" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E383" t="s">
         <v>8</v>
@@ -8458,13 +8458,13 @@
         <v>383</v>
       </c>
       <c r="B384" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D384" t="s">
-        <v>453</v>
+        <v>219</v>
       </c>
       <c r="E384" t="s">
         <v>8</v>
@@ -8475,13 +8475,13 @@
         <v>384</v>
       </c>
       <c r="B385" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D385" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E385" t="s">
         <v>8</v>
@@ -8492,13 +8492,13 @@
         <v>385</v>
       </c>
       <c r="B386" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D386" t="s">
-        <v>215</v>
+        <v>264</v>
       </c>
       <c r="E386" t="s">
         <v>8</v>
@@ -8509,13 +8509,13 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D387" t="s">
-        <v>478</v>
+        <v>302</v>
       </c>
       <c r="E387" t="s">
         <v>8</v>
@@ -8526,13 +8526,13 @@
         <v>387</v>
       </c>
       <c r="B388" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D388" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E388" t="s">
         <v>8</v>
@@ -8543,13 +8543,13 @@
         <v>388</v>
       </c>
       <c r="B389" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D389" t="s">
-        <v>367</v>
+        <v>209</v>
       </c>
       <c r="E389" t="s">
         <v>8</v>
@@ -8560,13 +8560,13 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D390" t="s">
-        <v>482</v>
+        <v>194</v>
       </c>
       <c r="E390" t="s">
         <v>8</v>
@@ -8577,13 +8577,13 @@
         <v>390</v>
       </c>
       <c r="B391" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D391" t="s">
-        <v>440</v>
+        <v>246</v>
       </c>
       <c r="E391" t="s">
         <v>8</v>
@@ -8594,13 +8594,13 @@
         <v>391</v>
       </c>
       <c r="B392" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D392" t="s">
-        <v>257</v>
+        <v>345</v>
       </c>
       <c r="E392" t="s">
         <v>8</v>
@@ -8611,13 +8611,13 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D393" t="s">
-        <v>221</v>
+        <v>487</v>
       </c>
       <c r="E393" t="s">
         <v>8</v>
@@ -8628,13 +8628,13 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D394" t="s">
-        <v>487</v>
+        <v>329</v>
       </c>
       <c r="E394" t="s">
         <v>8</v>
@@ -8645,13 +8645,13 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D395" t="s">
-        <v>359</v>
+        <v>302</v>
       </c>
       <c r="E395" t="s">
         <v>8</v>
@@ -8662,13 +8662,13 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D396" t="s">
-        <v>388</v>
+        <v>297</v>
       </c>
       <c r="E396" t="s">
         <v>8</v>
@@ -8679,13 +8679,13 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D397" t="s">
-        <v>228</v>
+        <v>439</v>
       </c>
       <c r="E397" t="s">
         <v>8</v>
@@ -8696,13 +8696,13 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D398" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E398" t="s">
         <v>8</v>
@@ -8713,13 +8713,13 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D399" t="s">
-        <v>494</v>
+        <v>268</v>
       </c>
       <c r="E399" t="s">
         <v>8</v>
@@ -8736,7 +8736,7 @@
         <v>6</v>
       </c>
       <c r="D400" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="E400" t="s">
         <v>8</v>
@@ -8753,7 +8753,7 @@
         <v>6</v>
       </c>
       <c r="D401" t="s">
-        <v>203</v>
+        <v>323</v>
       </c>
       <c r="E401" t="s">
         <v>8</v>

--- a/reports/backend/Excel/Automation_Test_Report.xlsx
+++ b/reports/backend/Excel/Automation_Test_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="512">
   <si>
     <t>#</t>
   </si>
@@ -584,858 +584,861 @@
     <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field apiKey (Verify Point #180)</t>
   </si>
   <si>
+    <t>0.020</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #181)</t>
+  </si>
+  <si>
+    <t>0.102</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #182)</t>
+  </si>
+  <si>
+    <t>0.084</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #183)</t>
+  </si>
+  <si>
+    <t>0.027</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #184)</t>
+  </si>
+  <si>
+    <t>0.087</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #185)</t>
+  </si>
+  <si>
+    <t>0.071</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #186)</t>
+  </si>
+  <si>
+    <t>0.067</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #187)</t>
+  </si>
+  <si>
+    <t>0.040</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #188)</t>
+  </si>
+  <si>
+    <t>0.028</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #189)</t>
+  </si>
+  <si>
+    <t>0.086</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #190)</t>
+  </si>
+  <si>
+    <t>0.062</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #191)</t>
+  </si>
+  <si>
+    <t>0.098</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #192)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #193)</t>
+  </si>
+  <si>
+    <t>0.095</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #194)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #195)</t>
+  </si>
+  <si>
+    <t>0.101</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #196)</t>
+  </si>
+  <si>
+    <t>0.037</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #197)</t>
+  </si>
+  <si>
+    <t>0.109</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #198)</t>
+  </si>
+  <si>
+    <t>0.113</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #199)</t>
+  </si>
+  <si>
+    <t>0.023</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #200)</t>
+  </si>
+  <si>
+    <t>0.112</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #201)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #202)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #203)</t>
+  </si>
+  <si>
+    <t>0.078</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #204)</t>
+  </si>
+  <si>
+    <t>0.035</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #205)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #206)</t>
+  </si>
+  <si>
+    <t>0.056</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #207)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #208)</t>
+  </si>
+  <si>
+    <t>0.030</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #209)</t>
+  </si>
+  <si>
+    <t>0.045</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #210)</t>
+  </si>
+  <si>
+    <t>0.111</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #211)</t>
+  </si>
+  <si>
+    <t>0.096</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code XSS-injection (Verify Point #212)</t>
+  </si>
+  <si>
+    <t>0.091</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #213)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for CSRF-token (Verify Point #214)</t>
+  </si>
+  <si>
+    <t>0.057</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated CORS-origin (Verify Point #215)</t>
+  </si>
+  <si>
+    <t>0.118</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for CSP-header (Verify Point #216)</t>
+  </si>
+  <si>
+    <t>0.059</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at session-token (Verify Point #217)</t>
+  </si>
+  <si>
     <t>0.048</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #181)</t>
-  </si>
-  <si>
-    <t>0.110</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #182)</t>
-  </si>
-  <si>
-    <t>0.071</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #183)</t>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users-ref (Verify Point #218)</t>
+  </si>
+  <si>
+    <t>0.036</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for items-ref (Verify Point #219)</t>
+  </si>
+  <si>
+    <t>0.079</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field de-DE (Verify Point #220)</t>
+  </si>
+  <si>
+    <t>0.083</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for fr-FR (Verify Point #221)</t>
+  </si>
+  <si>
+    <t>0.090</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ja-JP (Verify Point #222)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for pt-BR (Verify Point #223)</t>
+  </si>
+  <si>
+    <t>0.080</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of it-IT (Verify Point #224)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for apiKey (Verify Point #225)</t>
+  </si>
+  <si>
+    <t>0.093</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for authDomain (Verify Point #226)</t>
+  </si>
+  <si>
+    <t>0.041</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value projectId (Verify Point #227)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session storageBucket (Verify Point #228)</t>
+  </si>
+  <si>
+    <t>0.029</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier messagingSenderId (Verify Point #229)</t>
+  </si>
+  <si>
+    <t>0.053</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region appId (Verify Point #230)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for name (Verify Point #231)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code id (Verify Point #232)</t>
+  </si>
+  <si>
+    <t>0.107</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource fees.min (Verify Point #233)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for fees.max (Verify Point #234)</t>
+  </si>
+  <si>
+    <t>0.073</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated courses (Verify Point #235)</t>
+  </si>
+  <si>
+    <t>0.108</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for ranking.nirf (Verify Point #236)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at type (Verify Point #237)</t>
+  </si>
+  <si>
+    <t>0.072</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users/uid001 (Verify Point #238)</t>
+  </si>
+  <si>
+    <t>0.088</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for colleges/c001 (Verify Point #239)</t>
+  </si>
+  <si>
+    <t>0.068</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field prompt-length (Verify Point #240)</t>
+  </si>
+  <si>
+    <t>0.066</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for session-id-1 (Verify Point #241)</t>
+  </si>
+  <si>
+    <t>0.058</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ₹1L (Verify Point #242)</t>
+  </si>
+  <si>
+    <t>0.076</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for B.Tech (Verify Point #243)</t>
+  </si>
+  <si>
+    <t>0.117</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of 4 years (Verify Point #244)</t>
+  </si>
+  <si>
+    <t>0.038</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for Tamil Nadu (Verify Point #245)</t>
+  </si>
+  <si>
+    <t>0.042</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for Chennai (Verify Point #246)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value llama3-8b (Verify Point #247)</t>
+  </si>
+  <si>
+    <t>0.032</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session email (Verify Point #248)</t>
+  </si>
+  <si>
+    <t>0.065</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier password (Verify Point #249)</t>
+  </si>
+  <si>
+    <t>0.021</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region displayName (Verify Point #250)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for savedColleges (Verify Point #251)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code createdAt (Verify Point #252)</t>
+  </si>
+  <si>
+    <t>0.116</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource firebase-auth (Verify Point #253)</t>
+  </si>
+  <si>
+    <t>0.043</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for firestore-read (Verify Point #254)</t>
+  </si>
+  <si>
+    <t>0.077</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated groq-api (Verify Point #255)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for college-list (Verify Point #256)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at XSS-injection (Verify Point #257)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation SQL-injection (Verify Point #258)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for CSRF-token (Verify Point #259)</t>
+  </si>
+  <si>
+    <t>0.051</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field CORS-origin (Verify Point #260)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for CSP-header (Verify Point #261)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for session-token (Verify Point #262)</t>
+  </si>
+  <si>
+    <t>0.089</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users-ref (Verify Point #263)</t>
+  </si>
+  <si>
+    <t>0.034</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of items-ref (Verify Point #264)</t>
+  </si>
+  <si>
+    <t>0.114</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for de-DE (Verify Point #265)</t>
   </si>
   <si>
     <t>0.085</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #184)</t>
-  </si>
-  <si>
-    <t>0.034</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #185)</t>
-  </si>
-  <si>
-    <t>0.083</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #186)</t>
-  </si>
-  <si>
-    <t>0.021</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #187)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #188)</t>
-  </si>
-  <si>
-    <t>0.108</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #189)</t>
-  </si>
-  <si>
-    <t>0.040</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #190)</t>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for fr-FR (Verify Point #266)</t>
+  </si>
+  <si>
+    <t>0.049</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ja-JP (Verify Point #267)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session pt-BR (Verify Point #268)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier it-IT (Verify Point #269)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region apiKey (Verify Point #270)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for authDomain (Verify Point #271)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code projectId (Verify Point #272)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource storageBucket (Verify Point #273)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for messagingSenderId (Verify Point #274)</t>
+  </si>
+  <si>
+    <t>0.094</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated appId (Verify Point #275)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for name (Verify Point #276)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at id (Verify Point #277)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation fees.min (Verify Point #278)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for fees.max (Verify Point #279)</t>
+  </si>
+  <si>
+    <t>0.039</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field courses (Verify Point #280)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for ranking.nirf (Verify Point #281)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for type (Verify Point #282)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users/uid001 (Verify Point #283)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of colleges/c001 (Verify Point #284)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for prompt-length (Verify Point #285)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for session-id-1 (Verify Point #286)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ₹1L (Verify Point #287)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session B.Tech (Verify Point #288)</t>
+  </si>
+  <si>
+    <t>0.092</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier 4 years (Verify Point #289)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region Tamil Nadu (Verify Point #290)</t>
+  </si>
+  <si>
+    <t>0.097</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for Chennai (Verify Point #291)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code llama3-8b (Verify Point #292)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource email (Verify Point #293)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for password (Verify Point #294)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated displayName (Verify Point #295)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for savedColleges (Verify Point #296)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at createdAt (Verify Point #297)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation firebase-auth (Verify Point #298)</t>
+  </si>
+  <si>
+    <t>0.075</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for firestore-read (Verify Point #299)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field groq-api (Verify Point #300)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for college-list (Verify Point #301)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for XSS-injection (Verify Point #302)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for SQL-injection (Verify Point #303)</t>
+  </si>
+  <si>
+    <t>0.104</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of CSRF-token (Verify Point #304)</t>
+  </si>
+  <si>
+    <t>0.031</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for CORS-origin (Verify Point #305)</t>
+  </si>
+  <si>
+    <t>0.099</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for CSP-header (Verify Point #306)</t>
+  </si>
+  <si>
+    <t>0.064</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value session-token (Verify Point #307)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users-ref (Verify Point #308)</t>
+  </si>
+  <si>
+    <t>0.070</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier items-ref (Verify Point #309)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region de-DE (Verify Point #310)</t>
   </si>
   <si>
     <t>0.063</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #191)</t>
-  </si>
-  <si>
-    <t>0.064</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #192)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #193)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #194)</t>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for fr-FR (Verify Point #311)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ja-JP (Verify Point #312)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource pt-BR (Verify Point #313)</t>
+  </si>
+  <si>
+    <t>0.100</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for it-IT (Verify Point #314)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated apiKey (Verify Point #315)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for authDomain (Verify Point #316)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at projectId (Verify Point #317)</t>
+  </si>
+  <si>
+    <t>0.052</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation storageBucket (Verify Point #318)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for messagingSenderId (Verify Point #319)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field appId (Verify Point #320)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for name (Verify Point #321)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for id (Verify Point #322)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for fees.min (Verify Point #323)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of fees.max (Verify Point #324)</t>
+  </si>
+  <si>
+    <t>0.081</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for courses (Verify Point #325)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for ranking.nirf (Verify Point #326)</t>
+  </si>
+  <si>
+    <t>0.055</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value type (Verify Point #327)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users/uid001 (Verify Point #328)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier colleges/c001 (Verify Point #329)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region prompt-length (Verify Point #330)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for session-id-1 (Verify Point #331)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ₹1L (Verify Point #332)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource B.Tech (Verify Point #333)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for 4 years (Verify Point #334)</t>
   </si>
   <si>
     <t>0.050</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #195)</t>
-  </si>
-  <si>
-    <t>0.100</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #196)</t>
-  </si>
-  <si>
-    <t>0.095</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #197)</t>
-  </si>
-  <si>
-    <t>0.099</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #198)</t>
-  </si>
-  <si>
-    <t>0.047</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #199)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #200)</t>
-  </si>
-  <si>
-    <t>0.090</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #201)</t>
-  </si>
-  <si>
-    <t>0.087</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #202)</t>
-  </si>
-  <si>
-    <t>0.086</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #203)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #204)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #205)</t>
-  </si>
-  <si>
-    <t>0.042</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #206)</t>
-  </si>
-  <si>
-    <t>0.029</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #207)</t>
-  </si>
-  <si>
-    <t>0.041</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #208)</t>
-  </si>
-  <si>
-    <t>0.051</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #209)</t>
-  </si>
-  <si>
-    <t>0.036</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #210)</t>
-  </si>
-  <si>
-    <t>0.075</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #211)</t>
-  </si>
-  <si>
-    <t>0.038</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code XSS-injection (Verify Point #212)</t>
-  </si>
-  <si>
-    <t>0.080</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #213)</t>
-  </si>
-  <si>
-    <t>0.115</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for CSRF-token (Verify Point #214)</t>
-  </si>
-  <si>
-    <t>0.025</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated CORS-origin (Verify Point #215)</t>
-  </si>
-  <si>
-    <t>0.101</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for CSP-header (Verify Point #216)</t>
-  </si>
-  <si>
-    <t>0.022</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at session-token (Verify Point #217)</t>
-  </si>
-  <si>
-    <t>0.089</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users-ref (Verify Point #218)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for items-ref (Verify Point #219)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field de-DE (Verify Point #220)</t>
-  </si>
-  <si>
-    <t>0.091</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for fr-FR (Verify Point #221)</t>
-  </si>
-  <si>
-    <t>0.024</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ja-JP (Verify Point #222)</t>
-  </si>
-  <si>
-    <t>0.113</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for pt-BR (Verify Point #223)</t>
-  </si>
-  <si>
-    <t>0.116</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of it-IT (Verify Point #224)</t>
-  </si>
-  <si>
-    <t>0.078</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for apiKey (Verify Point #225)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for authDomain (Verify Point #226)</t>
-  </si>
-  <si>
-    <t>0.105</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value projectId (Verify Point #227)</t>
-  </si>
-  <si>
-    <t>0.096</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session storageBucket (Verify Point #228)</t>
-  </si>
-  <si>
-    <t>0.028</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier messagingSenderId (Verify Point #229)</t>
-  </si>
-  <si>
-    <t>0.062</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region appId (Verify Point #230)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for name (Verify Point #231)</t>
-  </si>
-  <si>
-    <t>0.098</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code id (Verify Point #232)</t>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated Tamil Nadu (Verify Point #335)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for Chennai (Verify Point #336)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at llama3-8b (Verify Point #337)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation email (Verify Point #338)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for password (Verify Point #339)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field displayName (Verify Point #340)</t>
   </si>
   <si>
     <t>0.119</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource fees.min (Verify Point #233)</t>
-  </si>
-  <si>
-    <t>0.033</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for fees.max (Verify Point #234)</t>
-  </si>
-  <si>
-    <t>0.069</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated courses (Verify Point #235)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for ranking.nirf (Verify Point #236)</t>
-  </si>
-  <si>
-    <t>0.056</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at type (Verify Point #237)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users/uid001 (Verify Point #238)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for colleges/c001 (Verify Point #239)</t>
-  </si>
-  <si>
-    <t>0.073</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field prompt-length (Verify Point #240)</t>
-  </si>
-  <si>
-    <t>0.045</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for session-id-1 (Verify Point #241)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ₹1L (Verify Point #242)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for B.Tech (Verify Point #243)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of 4 years (Verify Point #244)</t>
-  </si>
-  <si>
-    <t>0.059</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for Tamil Nadu (Verify Point #245)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for Chennai (Verify Point #246)</t>
-  </si>
-  <si>
-    <t>0.052</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value llama3-8b (Verify Point #247)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session email (Verify Point #248)</t>
-  </si>
-  <si>
-    <t>0.117</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier password (Verify Point #249)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region displayName (Verify Point #250)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for savedColleges (Verify Point #251)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code createdAt (Verify Point #252)</t>
-  </si>
-  <si>
-    <t>0.077</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource firebase-auth (Verify Point #253)</t>
-  </si>
-  <si>
-    <t>0.112</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for firestore-read (Verify Point #254)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated groq-api (Verify Point #255)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for college-list (Verify Point #256)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at XSS-injection (Verify Point #257)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation SQL-injection (Verify Point #258)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for CSRF-token (Verify Point #259)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field CORS-origin (Verify Point #260)</t>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for savedColleges (Verify Point #341)</t>
+  </si>
+  <si>
+    <t>0.054</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for createdAt (Verify Point #342)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for firebase-auth (Verify Point #343)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of firestore-read (Verify Point #344)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for groq-api (Verify Point #345)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for college-list (Verify Point #346)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value XSS-injection (Verify Point #347)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session SQL-injection (Verify Point #348)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier CSRF-token (Verify Point #349)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region CORS-origin (Verify Point #350)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for CSP-header (Verify Point #351)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code session-token (Verify Point #352)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users-ref (Verify Point #353)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for items-ref (Verify Point #354)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated de-DE (Verify Point #355)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for fr-FR (Verify Point #356)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ja-JP (Verify Point #357)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation pt-BR (Verify Point #358)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for it-IT (Verify Point #359)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field apiKey (Verify Point #360)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #361)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #362)</t>
   </si>
   <si>
     <t>0.044</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for CSP-header (Verify Point #261)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for session-token (Verify Point #262)</t>
-  </si>
-  <si>
-    <t>0.094</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users-ref (Verify Point #263)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of items-ref (Verify Point #264)</t>
-  </si>
-  <si>
-    <t>0.076</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for de-DE (Verify Point #265)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for fr-FR (Verify Point #266)</t>
-  </si>
-  <si>
-    <t>0.107</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ja-JP (Verify Point #267)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session pt-BR (Verify Point #268)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier it-IT (Verify Point #269)</t>
-  </si>
-  <si>
-    <t>0.072</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region apiKey (Verify Point #270)</t>
-  </si>
-  <si>
-    <t>0.054</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for authDomain (Verify Point #271)</t>
-  </si>
-  <si>
-    <t>0.058</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code projectId (Verify Point #272)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource storageBucket (Verify Point #273)</t>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #363)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #364)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #365)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #366)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #367)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #368)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #369)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #370)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #371)</t>
+  </si>
+  <si>
+    <t>0.060</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #372)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #373)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #374)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #375)</t>
+  </si>
+  <si>
+    <t>0.061</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #376)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #377)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #378)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #379)</t>
   </si>
   <si>
     <t>0.026</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for messagingSenderId (Verify Point #274)</t>
-  </si>
-  <si>
-    <t>0.023</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated appId (Verify Point #275)</t>
-  </si>
-  <si>
-    <t>0.068</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for name (Verify Point #276)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at id (Verify Point #277)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation fees.min (Verify Point #278)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for fees.max (Verify Point #279)</t>
-  </si>
-  <si>
-    <t>0.102</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field courses (Verify Point #280)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for ranking.nirf (Verify Point #281)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for type (Verify Point #282)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users/uid001 (Verify Point #283)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of colleges/c001 (Verify Point #284)</t>
-  </si>
-  <si>
-    <t>0.049</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for prompt-length (Verify Point #285)</t>
-  </si>
-  <si>
-    <t>0.060</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for session-id-1 (Verify Point #286)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ₹1L (Verify Point #287)</t>
-  </si>
-  <si>
-    <t>0.066</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session B.Tech (Verify Point #288)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier 4 years (Verify Point #289)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region Tamil Nadu (Verify Point #290)</t>
-  </si>
-  <si>
-    <t>0.118</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for Chennai (Verify Point #291)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code llama3-8b (Verify Point #292)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource email (Verify Point #293)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for password (Verify Point #294)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated displayName (Verify Point #295)</t>
-  </si>
-  <si>
-    <t>0.067</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for savedColleges (Verify Point #296)</t>
-  </si>
-  <si>
-    <t>0.106</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at createdAt (Verify Point #297)</t>
-  </si>
-  <si>
-    <t>0.053</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation firebase-auth (Verify Point #298)</t>
-  </si>
-  <si>
-    <t>0.081</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for firestore-read (Verify Point #299)</t>
-  </si>
-  <si>
-    <t>0.074</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field groq-api (Verify Point #300)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for college-list (Verify Point #301)</t>
-  </si>
-  <si>
-    <t>0.065</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for XSS-injection (Verify Point #302)</t>
-  </si>
-  <si>
-    <t>0.046</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for SQL-injection (Verify Point #303)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of CSRF-token (Verify Point #304)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for CORS-origin (Verify Point #305)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for CSP-header (Verify Point #306)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value session-token (Verify Point #307)</t>
-  </si>
-  <si>
-    <t>0.043</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users-ref (Verify Point #308)</t>
-  </si>
-  <si>
-    <t>0.057</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier items-ref (Verify Point #309)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region de-DE (Verify Point #310)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for fr-FR (Verify Point #311)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ja-JP (Verify Point #312)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource pt-BR (Verify Point #313)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for it-IT (Verify Point #314)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated apiKey (Verify Point #315)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for authDomain (Verify Point #316)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at projectId (Verify Point #317)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation storageBucket (Verify Point #318)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for messagingSenderId (Verify Point #319)</t>
-  </si>
-  <si>
-    <t>0.035</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field appId (Verify Point #320)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for name (Verify Point #321)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for id (Verify Point #322)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for fees.min (Verify Point #323)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of fees.max (Verify Point #324)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for courses (Verify Point #325)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for ranking.nirf (Verify Point #326)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value type (Verify Point #327)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users/uid001 (Verify Point #328)</t>
-  </si>
-  <si>
-    <t>0.061</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier colleges/c001 (Verify Point #329)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region prompt-length (Verify Point #330)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for session-id-1 (Verify Point #331)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ₹1L (Verify Point #332)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource B.Tech (Verify Point #333)</t>
-  </si>
-  <si>
-    <t>0.092</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for 4 years (Verify Point #334)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated Tamil Nadu (Verify Point #335)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for Chennai (Verify Point #336)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at llama3-8b (Verify Point #337)</t>
-  </si>
-  <si>
-    <t>0.104</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation email (Verify Point #338)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for password (Verify Point #339)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field displayName (Verify Point #340)</t>
-  </si>
-  <si>
-    <t>0.030</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for savedColleges (Verify Point #341)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for createdAt (Verify Point #342)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for firebase-auth (Verify Point #343)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of firestore-read (Verify Point #344)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for groq-api (Verify Point #345)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for college-list (Verify Point #346)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value XSS-injection (Verify Point #347)</t>
-  </si>
-  <si>
-    <t>0.084</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session SQL-injection (Verify Point #348)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier CSRF-token (Verify Point #349)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region CORS-origin (Verify Point #350)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for CSP-header (Verify Point #351)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code session-token (Verify Point #352)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users-ref (Verify Point #353)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for items-ref (Verify Point #354)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated de-DE (Verify Point #355)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for fr-FR (Verify Point #356)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ja-JP (Verify Point #357)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation pt-BR (Verify Point #358)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for it-IT (Verify Point #359)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field apiKey (Verify Point #360)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #361)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #362)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #363)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #364)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #365)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #366)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #367)</t>
-  </si>
-  <si>
-    <t>0.032</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #368)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #369)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #370)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #371)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #372)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #373)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #374)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #375)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #376)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #377)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #378)</t>
-  </si>
-  <si>
-    <t>0.093</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #379)</t>
-  </si>
-  <si>
     <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #380)</t>
   </si>
   <si>
@@ -1448,57 +1451,51 @@
     <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #383)</t>
   </si>
   <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #384)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #385)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #386)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #387)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #388)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #389)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #390)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #391)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code XSS-injection (Verify Point #392)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #393)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for CSRF-token (Verify Point #394)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated CORS-origin (Verify Point #395)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for CSP-header (Verify Point #396)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at session-token (Verify Point #397)</t>
+  </si>
+  <si>
     <t>0.082</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #384)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #385)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #386)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #387)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #388)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #389)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #390)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #391)</t>
-  </si>
-  <si>
-    <t>0.070</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code XSS-injection (Verify Point #392)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #393)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for CSRF-token (Verify Point #394)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated CORS-origin (Verify Point #395)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for CSP-header (Verify Point #396)</t>
-  </si>
-  <si>
-    <t>0.079</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at session-token (Verify Point #397)</t>
-  </si>
-  <si>
     <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users-ref (Verify Point #398)</t>
   </si>
   <si>
@@ -1514,13 +1511,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>21</t>
+    <t>22</t>
   </si>
   <si>
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 15:18:47 UTC</t>
+    <t>2026-06-23 15:32:59 UTC</t>
   </si>
   <si>
     <t>Branch</t>
@@ -1532,7 +1529,7 @@
     <t>Commit</t>
   </si>
   <si>
-    <t>6a5e7ca</t>
+    <t>f8042b0</t>
   </si>
   <si>
     <t>Total</t>
@@ -2038,7 +2035,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -2310,7 +2307,7 @@
         <v>6</v>
       </c>
       <c r="D22" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -2480,7 +2477,7 @@
         <v>6</v>
       </c>
       <c r="D32" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -2616,7 +2613,7 @@
         <v>6</v>
       </c>
       <c r="D40" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -2803,7 +2800,7 @@
         <v>6</v>
       </c>
       <c r="D51" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -2990,7 +2987,7 @@
         <v>6</v>
       </c>
       <c r="D62" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
@@ -3058,7 +3055,7 @@
         <v>6</v>
       </c>
       <c r="D66" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
@@ -3177,7 +3174,7 @@
         <v>6</v>
       </c>
       <c r="D73" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E73" t="s">
         <v>8</v>
@@ -3211,7 +3208,7 @@
         <v>6</v>
       </c>
       <c r="D75" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
@@ -3483,7 +3480,7 @@
         <v>6</v>
       </c>
       <c r="D91" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E91" t="s">
         <v>8</v>
@@ -3619,7 +3616,7 @@
         <v>6</v>
       </c>
       <c r="D99" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
@@ -3738,7 +3735,7 @@
         <v>6</v>
       </c>
       <c r="D106" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E106" t="s">
         <v>8</v>
@@ -3755,7 +3752,7 @@
         <v>6</v>
       </c>
       <c r="D107" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
@@ -3891,7 +3888,7 @@
         <v>6</v>
       </c>
       <c r="D115" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E115" t="s">
         <v>8</v>
@@ -3925,7 +3922,7 @@
         <v>6</v>
       </c>
       <c r="D117" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E117" t="s">
         <v>8</v>
@@ -4078,7 +4075,7 @@
         <v>6</v>
       </c>
       <c r="D126" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E126" t="s">
         <v>8</v>
@@ -4282,7 +4279,7 @@
         <v>6</v>
       </c>
       <c r="D138" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E138" t="s">
         <v>8</v>
@@ -4486,7 +4483,7 @@
         <v>6</v>
       </c>
       <c r="D150" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E150" t="s">
         <v>8</v>
@@ -4622,7 +4619,7 @@
         <v>6</v>
       </c>
       <c r="D158" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E158" t="s">
         <v>8</v>
@@ -5149,7 +5146,7 @@
         <v>6</v>
       </c>
       <c r="D189" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E189" t="s">
         <v>8</v>
@@ -5160,13 +5157,13 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D190" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E190" t="s">
         <v>8</v>
@@ -5177,13 +5174,13 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D191" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E191" t="s">
         <v>8</v>
@@ -5194,13 +5191,13 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D192" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E192" t="s">
         <v>8</v>
@@ -5211,13 +5208,13 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D193" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E193" t="s">
         <v>8</v>
@@ -5228,13 +5225,13 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D194" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E194" t="s">
         <v>8</v>
@@ -5245,13 +5242,13 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D195" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="E195" t="s">
         <v>8</v>
@@ -5262,13 +5259,13 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D196" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="E196" t="s">
         <v>8</v>
@@ -5279,13 +5276,13 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D197" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E197" t="s">
         <v>8</v>
@@ -5296,13 +5293,13 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D198" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E198" t="s">
         <v>8</v>
@@ -5313,13 +5310,13 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D199" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E199" t="s">
         <v>8</v>
@@ -5330,13 +5327,13 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D200" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E200" t="s">
         <v>8</v>
@@ -5347,13 +5344,13 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D201" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E201" t="s">
         <v>8</v>
@@ -5364,13 +5361,13 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D202" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E202" t="s">
         <v>8</v>
@@ -5381,13 +5378,13 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D203" t="s">
-        <v>228</v>
+        <v>192</v>
       </c>
       <c r="E203" t="s">
         <v>8</v>
@@ -5398,13 +5395,13 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D204" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="E204" t="s">
         <v>8</v>
@@ -5421,7 +5418,7 @@
         <v>6</v>
       </c>
       <c r="D205" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="E205" t="s">
         <v>8</v>
@@ -5432,13 +5429,13 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D206" t="s">
-        <v>202</v>
+        <v>234</v>
       </c>
       <c r="E206" t="s">
         <v>8</v>
@@ -5449,13 +5446,13 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D207" t="s">
-        <v>234</v>
+        <v>192</v>
       </c>
       <c r="E207" t="s">
         <v>8</v>
@@ -5466,13 +5463,13 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D208" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E208" t="s">
         <v>8</v>
@@ -5483,13 +5480,13 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D209" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="E209" t="s">
         <v>8</v>
@@ -5591,7 +5588,7 @@
         <v>6</v>
       </c>
       <c r="D215" t="s">
-        <v>250</v>
+        <v>222</v>
       </c>
       <c r="E215" t="s">
         <v>8</v>
@@ -5602,13 +5599,13 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
+        <v>250</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D216" t="s">
         <v>251</v>
-      </c>
-      <c r="C216" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D216" t="s">
-        <v>252</v>
       </c>
       <c r="E216" t="s">
         <v>8</v>
@@ -5619,13 +5616,13 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
+        <v>252</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D217" t="s">
         <v>253</v>
-      </c>
-      <c r="C217" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D217" t="s">
-        <v>254</v>
       </c>
       <c r="E217" t="s">
         <v>8</v>
@@ -5636,13 +5633,13 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
+        <v>254</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D218" t="s">
         <v>255</v>
-      </c>
-      <c r="C218" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D218" t="s">
-        <v>256</v>
       </c>
       <c r="E218" t="s">
         <v>8</v>
@@ -5653,13 +5650,13 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
+        <v>256</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D219" t="s">
         <v>257</v>
-      </c>
-      <c r="C219" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D219" t="s">
-        <v>258</v>
       </c>
       <c r="E219" t="s">
         <v>8</v>
@@ -5670,13 +5667,13 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
+        <v>258</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D220" t="s">
         <v>259</v>
-      </c>
-      <c r="C220" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D220" t="s">
-        <v>200</v>
       </c>
       <c r="E220" t="s">
         <v>8</v>
@@ -5693,7 +5690,7 @@
         <v>6</v>
       </c>
       <c r="D221" t="s">
-        <v>230</v>
+        <v>261</v>
       </c>
       <c r="E221" t="s">
         <v>8</v>
@@ -5704,13 +5701,13 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D222" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E222" t="s">
         <v>8</v>
@@ -5721,13 +5718,13 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D223" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E223" t="s">
         <v>8</v>
@@ -5738,13 +5735,13 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D224" t="s">
-        <v>266</v>
+        <v>222</v>
       </c>
       <c r="E224" t="s">
         <v>8</v>
@@ -5778,7 +5775,7 @@
         <v>6</v>
       </c>
       <c r="D226" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="E226" t="s">
         <v>8</v>
@@ -5789,13 +5786,13 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
+        <v>270</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D227" t="s">
         <v>271</v>
-      </c>
-      <c r="C227" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D227" t="s">
-        <v>226</v>
       </c>
       <c r="E227" t="s">
         <v>8</v>
@@ -5829,7 +5826,7 @@
         <v>6</v>
       </c>
       <c r="D229" t="s">
-        <v>275</v>
+        <v>204</v>
       </c>
       <c r="E229" t="s">
         <v>8</v>
@@ -5840,13 +5837,13 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
+        <v>275</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D230" t="s">
         <v>276</v>
-      </c>
-      <c r="C230" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D230" t="s">
-        <v>277</v>
       </c>
       <c r="E230" t="s">
         <v>8</v>
@@ -5857,13 +5854,13 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
+        <v>277</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D231" t="s">
         <v>278</v>
-      </c>
-      <c r="C231" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D231" t="s">
-        <v>279</v>
       </c>
       <c r="E231" t="s">
         <v>8</v>
@@ -5874,13 +5871,13 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D232" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E232" t="s">
         <v>8</v>
@@ -5891,13 +5888,13 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D233" t="s">
-        <v>282</v>
+        <v>194</v>
       </c>
       <c r="E233" t="s">
         <v>8</v>
@@ -5908,13 +5905,13 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D234" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E234" t="s">
         <v>8</v>
@@ -5925,13 +5922,13 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D235" t="s">
-        <v>286</v>
+        <v>194</v>
       </c>
       <c r="E235" t="s">
         <v>8</v>
@@ -5942,13 +5939,13 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D236" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="E236" t="s">
         <v>8</v>
@@ -5959,13 +5956,13 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D237" t="s">
-        <v>246</v>
+        <v>287</v>
       </c>
       <c r="E237" t="s">
         <v>8</v>
@@ -5976,13 +5973,13 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D238" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E238" t="s">
         <v>8</v>
@@ -5993,13 +5990,13 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D239" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E239" t="s">
         <v>8</v>
@@ -6010,13 +6007,13 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D240" t="s">
-        <v>207</v>
+        <v>292</v>
       </c>
       <c r="E240" t="s">
         <v>8</v>
@@ -6027,13 +6024,13 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
+        <v>293</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D241" t="s">
         <v>294</v>
-      </c>
-      <c r="C241" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D241" t="s">
-        <v>295</v>
       </c>
       <c r="E241" t="s">
         <v>8</v>
@@ -6044,13 +6041,13 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
+        <v>295</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D242" t="s">
         <v>296</v>
-      </c>
-      <c r="C242" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D242" t="s">
-        <v>297</v>
       </c>
       <c r="E242" t="s">
         <v>8</v>
@@ -6061,13 +6058,13 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
+        <v>297</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D243" t="s">
         <v>298</v>
-      </c>
-      <c r="C243" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D243" t="s">
-        <v>219</v>
       </c>
       <c r="E243" t="s">
         <v>8</v>
@@ -6084,7 +6081,7 @@
         <v>6</v>
       </c>
       <c r="D244" t="s">
-        <v>223</v>
+        <v>300</v>
       </c>
       <c r="E244" t="s">
         <v>8</v>
@@ -6095,13 +6092,13 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D245" t="s">
-        <v>209</v>
+        <v>302</v>
       </c>
       <c r="E245" t="s">
         <v>8</v>
@@ -6112,13 +6109,13 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D246" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E246" t="s">
         <v>8</v>
@@ -6129,13 +6126,13 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D247" t="s">
-        <v>209</v>
+        <v>306</v>
       </c>
       <c r="E247" t="s">
         <v>8</v>
@@ -6146,13 +6143,13 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D248" t="s">
-        <v>305</v>
+        <v>265</v>
       </c>
       <c r="E248" t="s">
         <v>8</v>
@@ -6163,13 +6160,13 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D249" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E249" t="s">
         <v>8</v>
@@ -6180,13 +6177,13 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D250" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E250" t="s">
         <v>8</v>
@@ -6197,13 +6194,13 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D251" t="s">
-        <v>268</v>
+        <v>313</v>
       </c>
       <c r="E251" t="s">
         <v>8</v>
@@ -6214,13 +6211,13 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D252" t="s">
-        <v>302</v>
+        <v>255</v>
       </c>
       <c r="E252" t="s">
         <v>8</v>
@@ -6231,13 +6228,13 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D253" t="s">
-        <v>268</v>
+        <v>208</v>
       </c>
       <c r="E253" t="s">
         <v>8</v>
@@ -6248,13 +6245,13 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D254" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E254" t="s">
         <v>8</v>
@@ -6265,13 +6262,13 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D255" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="E255" t="s">
         <v>8</v>
@@ -6282,13 +6279,13 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D256" t="s">
-        <v>279</v>
+        <v>321</v>
       </c>
       <c r="E256" t="s">
         <v>8</v>
@@ -6299,13 +6296,13 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
+        <v>322</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D257" t="s">
         <v>317</v>
-      </c>
-      <c r="C257" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D257" t="s">
-        <v>313</v>
       </c>
       <c r="E257" t="s">
         <v>8</v>
@@ -6316,13 +6313,13 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D258" t="s">
-        <v>282</v>
+        <v>190</v>
       </c>
       <c r="E258" t="s">
         <v>8</v>
@@ -6333,13 +6330,13 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D259" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="E259" t="s">
         <v>8</v>
@@ -6350,13 +6347,13 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D260" t="s">
-        <v>250</v>
+        <v>190</v>
       </c>
       <c r="E260" t="s">
         <v>8</v>
@@ -6367,13 +6364,13 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D261" t="s">
-        <v>198</v>
+        <v>327</v>
       </c>
       <c r="E261" t="s">
         <v>8</v>
@@ -6384,13 +6381,13 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D262" t="s">
-        <v>323</v>
+        <v>215</v>
       </c>
       <c r="E262" t="s">
         <v>8</v>
@@ -6401,13 +6398,13 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D263" t="s">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="E263" t="s">
         <v>8</v>
@@ -6418,13 +6415,13 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D264" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E264" t="s">
         <v>8</v>
@@ -6435,13 +6432,13 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D265" t="s">
-        <v>228</v>
+        <v>333</v>
       </c>
       <c r="E265" t="s">
         <v>8</v>
@@ -6452,13 +6449,13 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D266" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="E266" t="s">
         <v>8</v>
@@ -6469,13 +6466,13 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D267" t="s">
-        <v>202</v>
+        <v>337</v>
       </c>
       <c r="E267" t="s">
         <v>8</v>
@@ -6486,13 +6483,13 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D268" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="E268" t="s">
         <v>8</v>
@@ -6503,13 +6500,13 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D269" t="s">
-        <v>207</v>
+        <v>294</v>
       </c>
       <c r="E269" t="s">
         <v>8</v>
@@ -6520,13 +6517,13 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D270" t="s">
-        <v>326</v>
+        <v>215</v>
       </c>
       <c r="E270" t="s">
         <v>8</v>
@@ -6537,13 +6534,13 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D271" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="E271" t="s">
         <v>8</v>
@@ -6554,13 +6551,13 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D272" t="s">
-        <v>338</v>
+        <v>311</v>
       </c>
       <c r="E272" t="s">
         <v>8</v>
@@ -6571,13 +6568,13 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D273" t="s">
-        <v>340</v>
+        <v>220</v>
       </c>
       <c r="E273" t="s">
         <v>8</v>
@@ -6588,13 +6585,13 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D274" t="s">
-        <v>291</v>
+        <v>251</v>
       </c>
       <c r="E274" t="s">
         <v>8</v>
@@ -6605,13 +6602,13 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D275" t="s">
-        <v>343</v>
+        <v>265</v>
       </c>
       <c r="E275" t="s">
         <v>8</v>
@@ -6622,13 +6619,13 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D276" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E276" t="s">
         <v>8</v>
@@ -6639,13 +6636,13 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D277" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="E277" t="s">
         <v>8</v>
@@ -6656,13 +6653,13 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D278" t="s">
-        <v>246</v>
+        <v>335</v>
       </c>
       <c r="E278" t="s">
         <v>8</v>
@@ -6673,13 +6670,13 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D279" t="s">
-        <v>336</v>
+        <v>237</v>
       </c>
       <c r="E279" t="s">
         <v>8</v>
@@ -6690,13 +6687,13 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D280" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E280" t="s">
         <v>8</v>
@@ -6707,13 +6704,13 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D281" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E281" t="s">
         <v>8</v>
@@ -6724,13 +6721,13 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D282" t="s">
-        <v>315</v>
+        <v>261</v>
       </c>
       <c r="E282" t="s">
         <v>8</v>
@@ -6741,13 +6738,13 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D283" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="E283" t="s">
         <v>8</v>
@@ -6758,13 +6755,13 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D284" t="s">
-        <v>273</v>
+        <v>202</v>
       </c>
       <c r="E284" t="s">
         <v>8</v>
@@ -6775,13 +6772,13 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D285" t="s">
-        <v>226</v>
+        <v>304</v>
       </c>
       <c r="E285" t="s">
         <v>8</v>
@@ -6792,13 +6789,13 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D286" t="s">
-        <v>358</v>
+        <v>212</v>
       </c>
       <c r="E286" t="s">
         <v>8</v>
@@ -6809,13 +6806,13 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D287" t="s">
-        <v>360</v>
+        <v>302</v>
       </c>
       <c r="E287" t="s">
         <v>8</v>
@@ -6832,7 +6829,7 @@
         <v>6</v>
       </c>
       <c r="D288" t="s">
-        <v>236</v>
+        <v>290</v>
       </c>
       <c r="E288" t="s">
         <v>8</v>
@@ -6849,7 +6846,7 @@
         <v>6</v>
       </c>
       <c r="D289" t="s">
-        <v>363</v>
+        <v>300</v>
       </c>
       <c r="E289" t="s">
         <v>8</v>
@@ -6860,13 +6857,13 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
+        <v>363</v>
+      </c>
+      <c r="C290" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D290" t="s">
         <v>364</v>
-      </c>
-      <c r="C290" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D290" t="s">
-        <v>336</v>
       </c>
       <c r="E290" t="s">
         <v>8</v>
@@ -6883,7 +6880,7 @@
         <v>6</v>
       </c>
       <c r="D291" t="s">
-        <v>279</v>
+        <v>222</v>
       </c>
       <c r="E291" t="s">
         <v>8</v>
@@ -6917,7 +6914,7 @@
         <v>6</v>
       </c>
       <c r="D293" t="s">
-        <v>291</v>
+        <v>364</v>
       </c>
       <c r="E293" t="s">
         <v>8</v>
@@ -6934,7 +6931,7 @@
         <v>6</v>
       </c>
       <c r="D294" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="E294" t="s">
         <v>8</v>
@@ -6951,7 +6948,7 @@
         <v>6</v>
       </c>
       <c r="D295" t="s">
-        <v>264</v>
+        <v>215</v>
       </c>
       <c r="E295" t="s">
         <v>8</v>
@@ -6968,7 +6965,7 @@
         <v>6</v>
       </c>
       <c r="D296" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="E296" t="s">
         <v>8</v>
@@ -6985,7 +6982,7 @@
         <v>6</v>
       </c>
       <c r="D297" t="s">
-        <v>373</v>
+        <v>237</v>
       </c>
       <c r="E297" t="s">
         <v>8</v>
@@ -6996,13 +6993,13 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D298" t="s">
-        <v>375</v>
+        <v>319</v>
       </c>
       <c r="E298" t="s">
         <v>8</v>
@@ -7013,13 +7010,13 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D299" t="s">
-        <v>377</v>
+        <v>273</v>
       </c>
       <c r="E299" t="s">
         <v>8</v>
@@ -7030,13 +7027,13 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D300" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E300" t="s">
         <v>8</v>
@@ -7047,13 +7044,13 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D301" t="s">
-        <v>381</v>
+        <v>224</v>
       </c>
       <c r="E301" t="s">
         <v>8</v>
@@ -7064,13 +7061,13 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D302" t="s">
-        <v>340</v>
+        <v>290</v>
       </c>
       <c r="E302" t="s">
         <v>8</v>
@@ -7081,13 +7078,13 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D303" t="s">
-        <v>384</v>
+        <v>337</v>
       </c>
       <c r="E303" t="s">
         <v>8</v>
@@ -7098,13 +7095,13 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D304" t="s">
-        <v>386</v>
+        <v>257</v>
       </c>
       <c r="E304" t="s">
         <v>8</v>
@@ -7115,13 +7112,13 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D305" t="s">
-        <v>345</v>
+        <v>382</v>
       </c>
       <c r="E305" t="s">
         <v>8</v>
@@ -7132,13 +7129,13 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D306" t="s">
-        <v>323</v>
+        <v>384</v>
       </c>
       <c r="E306" t="s">
         <v>8</v>
@@ -7149,13 +7146,13 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D307" t="s">
-        <v>196</v>
+        <v>386</v>
       </c>
       <c r="E307" t="s">
         <v>8</v>
@@ -7166,13 +7163,13 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D308" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="E308" t="s">
         <v>8</v>
@@ -7183,13 +7180,13 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D309" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="E309" t="s">
         <v>8</v>
@@ -7200,13 +7197,13 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D310" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="E310" t="s">
         <v>8</v>
@@ -7217,13 +7214,13 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D311" t="s">
-        <v>379</v>
+        <v>234</v>
       </c>
       <c r="E311" t="s">
         <v>8</v>
@@ -7234,13 +7231,13 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D312" t="s">
-        <v>360</v>
+        <v>394</v>
       </c>
       <c r="E312" t="s">
         <v>8</v>
@@ -7251,13 +7248,13 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D313" t="s">
-        <v>192</v>
+        <v>339</v>
       </c>
       <c r="E313" t="s">
         <v>8</v>
@@ -7268,13 +7265,13 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D314" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="E314" t="s">
         <v>8</v>
@@ -7285,13 +7282,13 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D315" t="s">
-        <v>336</v>
+        <v>398</v>
       </c>
       <c r="E315" t="s">
         <v>8</v>
@@ -7302,13 +7299,13 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D316" t="s">
-        <v>338</v>
+        <v>244</v>
       </c>
       <c r="E316" t="s">
         <v>8</v>
@@ -7319,13 +7316,13 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D317" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="E317" t="s">
         <v>8</v>
@@ -7336,13 +7333,13 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D318" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="E318" t="s">
         <v>8</v>
@@ -7353,13 +7350,13 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
+        <v>402</v>
+      </c>
+      <c r="C319" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D319" t="s">
         <v>403</v>
-      </c>
-      <c r="C319" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D319" t="s">
-        <v>207</v>
       </c>
       <c r="E319" t="s">
         <v>8</v>
@@ -7376,7 +7373,7 @@
         <v>6</v>
       </c>
       <c r="D320" t="s">
-        <v>279</v>
+        <v>364</v>
       </c>
       <c r="E320" t="s">
         <v>8</v>
@@ -7393,7 +7390,7 @@
         <v>6</v>
       </c>
       <c r="D321" t="s">
-        <v>406</v>
+        <v>198</v>
       </c>
       <c r="E321" t="s">
         <v>8</v>
@@ -7404,13 +7401,13 @@
         <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D322" t="s">
-        <v>194</v>
+        <v>321</v>
       </c>
       <c r="E322" t="s">
         <v>8</v>
@@ -7421,13 +7418,13 @@
         <v>322</v>
       </c>
       <c r="B323" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D323" t="s">
-        <v>246</v>
+        <v>367</v>
       </c>
       <c r="E323" t="s">
         <v>8</v>
@@ -7438,13 +7435,13 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D324" t="s">
-        <v>358</v>
+        <v>226</v>
       </c>
       <c r="E324" t="s">
         <v>8</v>
@@ -7455,13 +7452,13 @@
         <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D325" t="s">
-        <v>386</v>
+        <v>300</v>
       </c>
       <c r="E325" t="s">
         <v>8</v>
@@ -7472,13 +7469,13 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
+        <v>410</v>
+      </c>
+      <c r="C326" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D326" t="s">
         <v>411</v>
-      </c>
-      <c r="C326" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D326" t="s">
-        <v>323</v>
       </c>
       <c r="E326" t="s">
         <v>8</v>
@@ -7495,7 +7492,7 @@
         <v>6</v>
       </c>
       <c r="D327" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="E327" t="s">
         <v>8</v>
@@ -7512,7 +7509,7 @@
         <v>6</v>
       </c>
       <c r="D328" t="s">
-        <v>386</v>
+        <v>414</v>
       </c>
       <c r="E328" t="s">
         <v>8</v>
@@ -7523,13 +7520,13 @@
         <v>328</v>
       </c>
       <c r="B329" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D329" t="s">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="E329" t="s">
         <v>8</v>
@@ -7540,13 +7537,13 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D330" t="s">
-        <v>416</v>
+        <v>240</v>
       </c>
       <c r="E330" t="s">
         <v>8</v>
@@ -7563,7 +7560,7 @@
         <v>6</v>
       </c>
       <c r="D331" t="s">
-        <v>360</v>
+        <v>255</v>
       </c>
       <c r="E331" t="s">
         <v>8</v>
@@ -7580,7 +7577,7 @@
         <v>6</v>
       </c>
       <c r="D332" t="s">
-        <v>367</v>
+        <v>306</v>
       </c>
       <c r="E332" t="s">
         <v>8</v>
@@ -7597,7 +7594,7 @@
         <v>6</v>
       </c>
       <c r="D333" t="s">
-        <v>268</v>
+        <v>327</v>
       </c>
       <c r="E333" t="s">
         <v>8</v>
@@ -7614,7 +7611,7 @@
         <v>6</v>
       </c>
       <c r="D334" t="s">
-        <v>279</v>
+        <v>202</v>
       </c>
       <c r="E334" t="s">
         <v>8</v>
@@ -7631,7 +7628,7 @@
         <v>6</v>
       </c>
       <c r="D335" t="s">
-        <v>422</v>
+        <v>212</v>
       </c>
       <c r="E335" t="s">
         <v>8</v>
@@ -7642,13 +7639,13 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
+        <v>422</v>
+      </c>
+      <c r="C336" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D336" t="s">
         <v>423</v>
-      </c>
-      <c r="C336" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D336" t="s">
-        <v>323</v>
       </c>
       <c r="E336" t="s">
         <v>8</v>
@@ -7665,7 +7662,7 @@
         <v>6</v>
       </c>
       <c r="D337" t="s">
-        <v>196</v>
+        <v>391</v>
       </c>
       <c r="E337" t="s">
         <v>8</v>
@@ -7682,7 +7679,7 @@
         <v>6</v>
       </c>
       <c r="D338" t="s">
-        <v>202</v>
+        <v>317</v>
       </c>
       <c r="E338" t="s">
         <v>8</v>
@@ -7699,7 +7696,7 @@
         <v>6</v>
       </c>
       <c r="D339" t="s">
-        <v>427</v>
+        <v>313</v>
       </c>
       <c r="E339" t="s">
         <v>8</v>
@@ -7710,13 +7707,13 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D340" t="s">
-        <v>258</v>
+        <v>194</v>
       </c>
       <c r="E340" t="s">
         <v>8</v>
@@ -7727,13 +7724,13 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D341" t="s">
-        <v>192</v>
+        <v>333</v>
       </c>
       <c r="E341" t="s">
         <v>8</v>
@@ -7744,13 +7741,13 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
+        <v>429</v>
+      </c>
+      <c r="C342" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D342" t="s">
         <v>430</v>
-      </c>
-      <c r="C342" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D342" t="s">
-        <v>431</v>
       </c>
       <c r="E342" t="s">
         <v>8</v>
@@ -7761,13 +7758,13 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
+        <v>431</v>
+      </c>
+      <c r="C343" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D343" t="s">
         <v>432</v>
-      </c>
-      <c r="C343" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D343" t="s">
-        <v>295</v>
       </c>
       <c r="E343" t="s">
         <v>8</v>
@@ -7784,7 +7781,7 @@
         <v>6</v>
       </c>
       <c r="D344" t="s">
-        <v>338</v>
+        <v>234</v>
       </c>
       <c r="E344" t="s">
         <v>8</v>
@@ -7801,7 +7798,7 @@
         <v>6</v>
       </c>
       <c r="D345" t="s">
-        <v>291</v>
+        <v>317</v>
       </c>
       <c r="E345" t="s">
         <v>8</v>
@@ -7818,7 +7815,7 @@
         <v>6</v>
       </c>
       <c r="D346" t="s">
-        <v>268</v>
+        <v>196</v>
       </c>
       <c r="E346" t="s">
         <v>8</v>
@@ -7835,7 +7832,7 @@
         <v>6</v>
       </c>
       <c r="D347" t="s">
-        <v>373</v>
+        <v>335</v>
       </c>
       <c r="E347" t="s">
         <v>8</v>
@@ -7852,7 +7849,7 @@
         <v>6</v>
       </c>
       <c r="D348" t="s">
-        <v>226</v>
+        <v>391</v>
       </c>
       <c r="E348" t="s">
         <v>8</v>
@@ -7869,7 +7866,7 @@
         <v>6</v>
       </c>
       <c r="D349" t="s">
-        <v>439</v>
+        <v>192</v>
       </c>
       <c r="E349" t="s">
         <v>8</v>
@@ -7880,13 +7877,13 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D350" t="s">
-        <v>332</v>
+        <v>388</v>
       </c>
       <c r="E350" t="s">
         <v>8</v>
@@ -7897,13 +7894,13 @@
         <v>350</v>
       </c>
       <c r="B351" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D351" t="s">
-        <v>360</v>
+        <v>204</v>
       </c>
       <c r="E351" t="s">
         <v>8</v>
@@ -7914,13 +7911,13 @@
         <v>351</v>
       </c>
       <c r="B352" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D352" t="s">
-        <v>386</v>
+        <v>273</v>
       </c>
       <c r="E352" t="s">
         <v>8</v>
@@ -7931,13 +7928,13 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D353" t="s">
-        <v>256</v>
+        <v>386</v>
       </c>
       <c r="E353" t="s">
         <v>8</v>
@@ -7948,13 +7945,13 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D354" t="s">
-        <v>381</v>
+        <v>255</v>
       </c>
       <c r="E354" t="s">
         <v>8</v>
@@ -7965,13 +7962,13 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D355" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="E355" t="s">
         <v>8</v>
@@ -7982,13 +7979,13 @@
         <v>355</v>
       </c>
       <c r="B356" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D356" t="s">
-        <v>240</v>
+        <v>287</v>
       </c>
       <c r="E356" t="s">
         <v>8</v>
@@ -7999,13 +7996,13 @@
         <v>356</v>
       </c>
       <c r="B357" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D357" t="s">
-        <v>323</v>
+        <v>287</v>
       </c>
       <c r="E357" t="s">
         <v>8</v>
@@ -8016,13 +8013,13 @@
         <v>357</v>
       </c>
       <c r="B358" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D358" t="s">
-        <v>266</v>
+        <v>391</v>
       </c>
       <c r="E358" t="s">
         <v>8</v>
@@ -8033,13 +8030,13 @@
         <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D359" t="s">
-        <v>422</v>
+        <v>259</v>
       </c>
       <c r="E359" t="s">
         <v>8</v>
@@ -8050,13 +8047,13 @@
         <v>359</v>
       </c>
       <c r="B360" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D360" t="s">
-        <v>270</v>
+        <v>411</v>
       </c>
       <c r="E360" t="s">
         <v>8</v>
@@ -8067,13 +8064,13 @@
         <v>360</v>
       </c>
       <c r="B361" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D361" t="s">
-        <v>313</v>
+        <v>261</v>
       </c>
       <c r="E361" t="s">
         <v>8</v>
@@ -8084,13 +8081,13 @@
         <v>361</v>
       </c>
       <c r="B362" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D362" t="s">
-        <v>305</v>
+        <v>220</v>
       </c>
       <c r="E362" t="s">
         <v>8</v>
@@ -8101,13 +8098,13 @@
         <v>362</v>
       </c>
       <c r="B363" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D363" t="s">
-        <v>266</v>
+        <v>298</v>
       </c>
       <c r="E363" t="s">
         <v>8</v>
@@ -8118,13 +8115,13 @@
         <v>363</v>
       </c>
       <c r="B364" t="s">
+        <v>453</v>
+      </c>
+      <c r="C364" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D364" t="s">
         <v>454</v>
-      </c>
-      <c r="C364" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D364" t="s">
-        <v>363</v>
       </c>
       <c r="E364" t="s">
         <v>8</v>
@@ -8141,7 +8138,7 @@
         <v>6</v>
       </c>
       <c r="D365" t="s">
-        <v>230</v>
+        <v>339</v>
       </c>
       <c r="E365" t="s">
         <v>8</v>
@@ -8158,7 +8155,7 @@
         <v>6</v>
       </c>
       <c r="D366" t="s">
-        <v>329</v>
+        <v>290</v>
       </c>
       <c r="E366" t="s">
         <v>8</v>
@@ -8175,7 +8172,7 @@
         <v>6</v>
       </c>
       <c r="D367" t="s">
-        <v>367</v>
+        <v>276</v>
       </c>
       <c r="E367" t="s">
         <v>8</v>
@@ -8192,7 +8189,7 @@
         <v>6</v>
       </c>
       <c r="D368" t="s">
-        <v>360</v>
+        <v>294</v>
       </c>
       <c r="E368" t="s">
         <v>8</v>
@@ -8209,7 +8206,7 @@
         <v>6</v>
       </c>
       <c r="D369" t="s">
-        <v>460</v>
+        <v>190</v>
       </c>
       <c r="E369" t="s">
         <v>8</v>
@@ -8220,13 +8217,13 @@
         <v>369</v>
       </c>
       <c r="B370" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D370" t="s">
-        <v>194</v>
+        <v>255</v>
       </c>
       <c r="E370" t="s">
         <v>8</v>
@@ -8237,13 +8234,13 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D371" t="s">
-        <v>275</v>
+        <v>327</v>
       </c>
       <c r="E371" t="s">
         <v>8</v>
@@ -8254,13 +8251,13 @@
         <v>371</v>
       </c>
       <c r="B372" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D372" t="s">
-        <v>367</v>
+        <v>411</v>
       </c>
       <c r="E372" t="s">
         <v>8</v>
@@ -8271,13 +8268,13 @@
         <v>372</v>
       </c>
       <c r="B373" t="s">
+        <v>463</v>
+      </c>
+      <c r="C373" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D373" t="s">
         <v>464</v>
-      </c>
-      <c r="C373" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D373" t="s">
-        <v>226</v>
       </c>
       <c r="E373" t="s">
         <v>8</v>
@@ -8294,7 +8291,7 @@
         <v>6</v>
       </c>
       <c r="D374" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E374" t="s">
         <v>8</v>
@@ -8311,7 +8308,7 @@
         <v>6</v>
       </c>
       <c r="D375" t="s">
-        <v>427</v>
+        <v>319</v>
       </c>
       <c r="E375" t="s">
         <v>8</v>
@@ -8328,7 +8325,7 @@
         <v>6</v>
       </c>
       <c r="D376" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E376" t="s">
         <v>8</v>
@@ -8345,7 +8342,7 @@
         <v>6</v>
       </c>
       <c r="D377" t="s">
-        <v>230</v>
+        <v>469</v>
       </c>
       <c r="E377" t="s">
         <v>8</v>
@@ -8356,13 +8353,13 @@
         <v>377</v>
       </c>
       <c r="B378" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D378" t="s">
-        <v>352</v>
+        <v>290</v>
       </c>
       <c r="E378" t="s">
         <v>8</v>
@@ -8373,13 +8370,13 @@
         <v>378</v>
       </c>
       <c r="B379" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D379" t="s">
-        <v>211</v>
+        <v>391</v>
       </c>
       <c r="E379" t="s">
         <v>8</v>
@@ -8390,13 +8387,13 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D380" t="s">
-        <v>472</v>
+        <v>206</v>
       </c>
       <c r="E380" t="s">
         <v>8</v>
@@ -8413,7 +8410,7 @@
         <v>6</v>
       </c>
       <c r="D381" t="s">
-        <v>431</v>
+        <v>474</v>
       </c>
       <c r="E381" t="s">
         <v>8</v>
@@ -8424,13 +8421,13 @@
         <v>381</v>
       </c>
       <c r="B382" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D382" t="s">
-        <v>286</v>
+        <v>321</v>
       </c>
       <c r="E382" t="s">
         <v>8</v>
@@ -8441,13 +8438,13 @@
         <v>382</v>
       </c>
       <c r="B383" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D383" t="s">
-        <v>254</v>
+        <v>224</v>
       </c>
       <c r="E383" t="s">
         <v>8</v>
@@ -8458,13 +8455,13 @@
         <v>383</v>
       </c>
       <c r="B384" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D384" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="E384" t="s">
         <v>8</v>
@@ -8475,13 +8472,13 @@
         <v>384</v>
       </c>
       <c r="B385" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D385" t="s">
-        <v>478</v>
+        <v>294</v>
       </c>
       <c r="E385" t="s">
         <v>8</v>
@@ -8498,7 +8495,7 @@
         <v>6</v>
       </c>
       <c r="D386" t="s">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="E386" t="s">
         <v>8</v>
@@ -8515,7 +8512,7 @@
         <v>6</v>
       </c>
       <c r="D387" t="s">
-        <v>302</v>
+        <v>208</v>
       </c>
       <c r="E387" t="s">
         <v>8</v>
@@ -8532,7 +8529,7 @@
         <v>6</v>
       </c>
       <c r="D388" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="E388" t="s">
         <v>8</v>
@@ -8549,7 +8546,7 @@
         <v>6</v>
       </c>
       <c r="D389" t="s">
-        <v>209</v>
+        <v>261</v>
       </c>
       <c r="E389" t="s">
         <v>8</v>
@@ -8566,7 +8563,7 @@
         <v>6</v>
       </c>
       <c r="D390" t="s">
-        <v>194</v>
+        <v>263</v>
       </c>
       <c r="E390" t="s">
         <v>8</v>
@@ -8583,7 +8580,7 @@
         <v>6</v>
       </c>
       <c r="D391" t="s">
-        <v>246</v>
+        <v>273</v>
       </c>
       <c r="E391" t="s">
         <v>8</v>
@@ -8600,7 +8597,7 @@
         <v>6</v>
       </c>
       <c r="D392" t="s">
-        <v>345</v>
+        <v>268</v>
       </c>
       <c r="E392" t="s">
         <v>8</v>
@@ -8617,7 +8614,7 @@
         <v>6</v>
       </c>
       <c r="D393" t="s">
-        <v>487</v>
+        <v>265</v>
       </c>
       <c r="E393" t="s">
         <v>8</v>
@@ -8628,13 +8625,13 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D394" t="s">
-        <v>329</v>
+        <v>290</v>
       </c>
       <c r="E394" t="s">
         <v>8</v>
@@ -8645,13 +8642,13 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D395" t="s">
-        <v>302</v>
+        <v>354</v>
       </c>
       <c r="E395" t="s">
         <v>8</v>
@@ -8662,13 +8659,13 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D396" t="s">
-        <v>297</v>
+        <v>226</v>
       </c>
       <c r="E396" t="s">
         <v>8</v>
@@ -8679,13 +8676,13 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D397" t="s">
-        <v>439</v>
+        <v>215</v>
       </c>
       <c r="E397" t="s">
         <v>8</v>
@@ -8696,13 +8693,13 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D398" t="s">
-        <v>493</v>
+        <v>257</v>
       </c>
       <c r="E398" t="s">
         <v>8</v>
@@ -8713,13 +8710,13 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D399" t="s">
-        <v>268</v>
+        <v>493</v>
       </c>
       <c r="E399" t="s">
         <v>8</v>
@@ -8730,13 +8727,13 @@
         <v>399</v>
       </c>
       <c r="B400" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D400" t="s">
-        <v>211</v>
+        <v>398</v>
       </c>
       <c r="E400" t="s">
         <v>8</v>
@@ -8747,13 +8744,13 @@
         <v>400</v>
       </c>
       <c r="B401" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D401" t="s">
-        <v>323</v>
+        <v>382</v>
       </c>
       <c r="E401" t="s">
         <v>8</v>
@@ -8772,47 +8769,47 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>496</v>
+      </c>
+      <c r="B1" t="s">
         <v>497</v>
-      </c>
-      <c r="B1" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B2" t="s">
         <v>499</v>
-      </c>
-      <c r="B2" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>500</v>
+      </c>
+      <c r="B3" t="s">
         <v>501</v>
-      </c>
-      <c r="B3" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>502</v>
+      </c>
+      <c r="B4" t="s">
         <v>503</v>
-      </c>
-      <c r="B4" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>504</v>
+      </c>
+      <c r="B5" t="s">
         <v>505</v>
-      </c>
-      <c r="B5" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B6">
         <v>400</v>
@@ -8820,7 +8817,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B7">
         <v>400</v>
@@ -8828,7 +8825,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -8836,7 +8833,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -8844,10 +8841,10 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>510</v>
+      </c>
+      <c r="B10" t="s">
         <v>511</v>
-      </c>
-      <c r="B10" t="s">
-        <v>512</v>
       </c>
     </row>
   </sheetData>

--- a/reports/backend/Excel/Automation_Test_Report.xlsx
+++ b/reports/backend/Excel/Automation_Test_Report.xlsx
@@ -584,894 +584,897 @@
     <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field apiKey (Verify Point #180)</t>
   </si>
   <si>
+    <t>0.087</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #181)</t>
+  </si>
+  <si>
+    <t>0.063</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #182)</t>
+  </si>
+  <si>
+    <t>0.053</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #183)</t>
+  </si>
+  <si>
+    <t>0.036</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #184)</t>
+  </si>
+  <si>
+    <t>0.110</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #185)</t>
+  </si>
+  <si>
+    <t>0.027</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #186)</t>
+  </si>
+  <si>
+    <t>0.082</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #187)</t>
+  </si>
+  <si>
+    <t>0.023</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #188)</t>
+  </si>
+  <si>
+    <t>0.068</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #189)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #190)</t>
+  </si>
+  <si>
+    <t>0.073</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #191)</t>
+  </si>
+  <si>
+    <t>0.055</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #192)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #193)</t>
+  </si>
+  <si>
+    <t>0.028</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #194)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #195)</t>
+  </si>
+  <si>
+    <t>0.104</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #196)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #197)</t>
+  </si>
+  <si>
+    <t>0.106</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #198)</t>
+  </si>
+  <si>
+    <t>0.117</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #199)</t>
+  </si>
+  <si>
+    <t>0.033</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #200)</t>
+  </si>
+  <si>
+    <t>0.080</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #201)</t>
+  </si>
+  <si>
+    <t>0.062</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #202)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #203)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #204)</t>
+  </si>
+  <si>
+    <t>0.051</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #205)</t>
+  </si>
+  <si>
+    <t>0.097</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #206)</t>
+  </si>
+  <si>
+    <t>0.101</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #207)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #208)</t>
+  </si>
+  <si>
+    <t>0.024</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #209)</t>
+  </si>
+  <si>
+    <t>0.041</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #210)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #211)</t>
+  </si>
+  <si>
+    <t>0.070</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code XSS-injection (Verify Point #212)</t>
+  </si>
+  <si>
+    <t>0.084</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #213)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for CSRF-token (Verify Point #214)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated CORS-origin (Verify Point #215)</t>
+  </si>
+  <si>
+    <t>0.096</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for CSP-header (Verify Point #216)</t>
+  </si>
+  <si>
+    <t>0.071</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at session-token (Verify Point #217)</t>
+  </si>
+  <si>
+    <t>0.100</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users-ref (Verify Point #218)</t>
+  </si>
+  <si>
+    <t>0.074</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for items-ref (Verify Point #219)</t>
+  </si>
+  <si>
+    <t>0.056</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field de-DE (Verify Point #220)</t>
+  </si>
+  <si>
+    <t>0.118</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for fr-FR (Verify Point #221)</t>
+  </si>
+  <si>
+    <t>0.112</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ja-JP (Verify Point #222)</t>
+  </si>
+  <si>
+    <t>0.064</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for pt-BR (Verify Point #223)</t>
+  </si>
+  <si>
+    <t>0.061</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of it-IT (Verify Point #224)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for apiKey (Verify Point #225)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for authDomain (Verify Point #226)</t>
+  </si>
+  <si>
+    <t>0.079</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value projectId (Verify Point #227)</t>
+  </si>
+  <si>
+    <t>0.052</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session storageBucket (Verify Point #228)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier messagingSenderId (Verify Point #229)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region appId (Verify Point #230)</t>
+  </si>
+  <si>
+    <t>0.034</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for name (Verify Point #231)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code id (Verify Point #232)</t>
+  </si>
+  <si>
+    <t>0.069</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource fees.min (Verify Point #233)</t>
+  </si>
+  <si>
+    <t>0.021</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for fees.max (Verify Point #234)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated courses (Verify Point #235)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for ranking.nirf (Verify Point #236)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at type (Verify Point #237)</t>
+  </si>
+  <si>
+    <t>0.057</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users/uid001 (Verify Point #238)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for colleges/c001 (Verify Point #239)</t>
+  </si>
+  <si>
+    <t>0.026</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field prompt-length (Verify Point #240)</t>
+  </si>
+  <si>
+    <t>0.043</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for session-id-1 (Verify Point #241)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ₹1L (Verify Point #242)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for B.Tech (Verify Point #243)</t>
+  </si>
+  <si>
+    <t>0.065</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of 4 years (Verify Point #244)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for Tamil Nadu (Verify Point #245)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for Chennai (Verify Point #246)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value llama3-8b (Verify Point #247)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session email (Verify Point #248)</t>
+  </si>
+  <si>
     <t>0.020</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #181)</t>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier password (Verify Point #249)</t>
+  </si>
+  <si>
+    <t>0.046</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region displayName (Verify Point #250)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for savedColleges (Verify Point #251)</t>
+  </si>
+  <si>
+    <t>0.086</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code createdAt (Verify Point #252)</t>
+  </si>
+  <si>
+    <t>0.093</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource firebase-auth (Verify Point #253)</t>
+  </si>
+  <si>
+    <t>0.119</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for firestore-read (Verify Point #254)</t>
+  </si>
+  <si>
+    <t>0.031</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated groq-api (Verify Point #255)</t>
+  </si>
+  <si>
+    <t>0.029</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for college-list (Verify Point #256)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at XSS-injection (Verify Point #257)</t>
+  </si>
+  <si>
+    <t>0.058</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation SQL-injection (Verify Point #258)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for CSRF-token (Verify Point #259)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field CORS-origin (Verify Point #260)</t>
+  </si>
+  <si>
+    <t>0.113</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for CSP-header (Verify Point #261)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for session-token (Verify Point #262)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users-ref (Verify Point #263)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of items-ref (Verify Point #264)</t>
+  </si>
+  <si>
+    <t>0.072</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for de-DE (Verify Point #265)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for fr-FR (Verify Point #266)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ja-JP (Verify Point #267)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session pt-BR (Verify Point #268)</t>
+  </si>
+  <si>
+    <t>0.116</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier it-IT (Verify Point #269)</t>
+  </si>
+  <si>
+    <t>0.030</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region apiKey (Verify Point #270)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for authDomain (Verify Point #271)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code projectId (Verify Point #272)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource storageBucket (Verify Point #273)</t>
   </si>
   <si>
     <t>0.102</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #182)</t>
-  </si>
-  <si>
-    <t>0.084</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #183)</t>
-  </si>
-  <si>
-    <t>0.027</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #184)</t>
-  </si>
-  <si>
-    <t>0.087</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #185)</t>
-  </si>
-  <si>
-    <t>0.071</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #186)</t>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for messagingSenderId (Verify Point #274)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated appId (Verify Point #275)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for name (Verify Point #276)</t>
   </si>
   <si>
     <t>0.067</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #187)</t>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at id (Verify Point #277)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation fees.min (Verify Point #278)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for fees.max (Verify Point #279)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field courses (Verify Point #280)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for ranking.nirf (Verify Point #281)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for type (Verify Point #282)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users/uid001 (Verify Point #283)</t>
   </si>
   <si>
     <t>0.040</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #188)</t>
-  </si>
-  <si>
-    <t>0.028</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #189)</t>
-  </si>
-  <si>
-    <t>0.086</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #190)</t>
-  </si>
-  <si>
-    <t>0.062</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #191)</t>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of colleges/c001 (Verify Point #284)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for prompt-length (Verify Point #285)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for session-id-1 (Verify Point #286)</t>
+  </si>
+  <si>
+    <t>0.050</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ₹1L (Verify Point #287)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session B.Tech (Verify Point #288)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier 4 years (Verify Point #289)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region Tamil Nadu (Verify Point #290)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for Chennai (Verify Point #291)</t>
+  </si>
+  <si>
+    <t>0.035</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code llama3-8b (Verify Point #292)</t>
+  </si>
+  <si>
+    <t>0.059</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource email (Verify Point #293)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for password (Verify Point #294)</t>
+  </si>
+  <si>
+    <t>0.054</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated displayName (Verify Point #295)</t>
+  </si>
+  <si>
+    <t>0.094</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for savedColleges (Verify Point #296)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at createdAt (Verify Point #297)</t>
+  </si>
+  <si>
+    <t>0.076</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation firebase-auth (Verify Point #298)</t>
+  </si>
+  <si>
+    <t>0.032</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for firestore-read (Verify Point #299)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field groq-api (Verify Point #300)</t>
+  </si>
+  <si>
+    <t>0.081</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for college-list (Verify Point #301)</t>
+  </si>
+  <si>
+    <t>0.089</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for XSS-injection (Verify Point #302)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for SQL-injection (Verify Point #303)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of CSRF-token (Verify Point #304)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for CORS-origin (Verify Point #305)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for CSP-header (Verify Point #306)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value session-token (Verify Point #307)</t>
+  </si>
+  <si>
+    <t>0.039</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users-ref (Verify Point #308)</t>
+  </si>
+  <si>
+    <t>0.111</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier items-ref (Verify Point #309)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region de-DE (Verify Point #310)</t>
+  </si>
+  <si>
+    <t>0.092</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for fr-FR (Verify Point #311)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ja-JP (Verify Point #312)</t>
+  </si>
+  <si>
+    <t>0.025</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource pt-BR (Verify Point #313)</t>
+  </si>
+  <si>
+    <t>0.091</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for it-IT (Verify Point #314)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated apiKey (Verify Point #315)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for authDomain (Verify Point #316)</t>
+  </si>
+  <si>
+    <t>0.077</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at projectId (Verify Point #317)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation storageBucket (Verify Point #318)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for messagingSenderId (Verify Point #319)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field appId (Verify Point #320)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for name (Verify Point #321)</t>
+  </si>
+  <si>
+    <t>0.099</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for id (Verify Point #322)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for fees.min (Verify Point #323)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of fees.max (Verify Point #324)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for courses (Verify Point #325)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for ranking.nirf (Verify Point #326)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value type (Verify Point #327)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users/uid001 (Verify Point #328)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier colleges/c001 (Verify Point #329)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region prompt-length (Verify Point #330)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for session-id-1 (Verify Point #331)</t>
+  </si>
+  <si>
+    <t>0.045</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ₹1L (Verify Point #332)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource B.Tech (Verify Point #333)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for 4 years (Verify Point #334)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated Tamil Nadu (Verify Point #335)</t>
+  </si>
+  <si>
+    <t>0.108</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for Chennai (Verify Point #336)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at llama3-8b (Verify Point #337)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation email (Verify Point #338)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for password (Verify Point #339)</t>
+  </si>
+  <si>
+    <t>0.103</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field displayName (Verify Point #340)</t>
+  </si>
+  <si>
+    <t>0.088</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for savedColleges (Verify Point #341)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for createdAt (Verify Point #342)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for firebase-auth (Verify Point #343)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of firestore-read (Verify Point #344)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for groq-api (Verify Point #345)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for college-list (Verify Point #346)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value XSS-injection (Verify Point #347)</t>
+  </si>
+  <si>
+    <t>0.066</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session SQL-injection (Verify Point #348)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier CSRF-token (Verify Point #349)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region CORS-origin (Verify Point #350)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for CSP-header (Verify Point #351)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code session-token (Verify Point #352)</t>
+  </si>
+  <si>
+    <t>0.095</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users-ref (Verify Point #353)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for items-ref (Verify Point #354)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated de-DE (Verify Point #355)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for fr-FR (Verify Point #356)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ja-JP (Verify Point #357)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation pt-BR (Verify Point #358)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for it-IT (Verify Point #359)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field apiKey (Verify Point #360)</t>
+  </si>
+  <si>
+    <t>0.022</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #361)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #362)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #363)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #364)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #365)</t>
+  </si>
+  <si>
+    <t>0.109</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #366)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #367)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #368)</t>
+  </si>
+  <si>
+    <t>0.037</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #369)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #370)</t>
   </si>
   <si>
     <t>0.098</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #192)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #193)</t>
-  </si>
-  <si>
-    <t>0.095</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #194)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #195)</t>
-  </si>
-  <si>
-    <t>0.101</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #196)</t>
-  </si>
-  <si>
-    <t>0.037</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #197)</t>
-  </si>
-  <si>
-    <t>0.109</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #198)</t>
-  </si>
-  <si>
-    <t>0.113</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #199)</t>
-  </si>
-  <si>
-    <t>0.023</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #200)</t>
-  </si>
-  <si>
-    <t>0.112</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #201)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #202)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #203)</t>
-  </si>
-  <si>
-    <t>0.078</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #204)</t>
-  </si>
-  <si>
-    <t>0.035</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #205)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #206)</t>
-  </si>
-  <si>
-    <t>0.056</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #207)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #208)</t>
-  </si>
-  <si>
-    <t>0.030</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #209)</t>
-  </si>
-  <si>
-    <t>0.045</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #210)</t>
-  </si>
-  <si>
-    <t>0.111</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #211)</t>
-  </si>
-  <si>
-    <t>0.096</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code XSS-injection (Verify Point #212)</t>
-  </si>
-  <si>
-    <t>0.091</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #213)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for CSRF-token (Verify Point #214)</t>
-  </si>
-  <si>
-    <t>0.057</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated CORS-origin (Verify Point #215)</t>
-  </si>
-  <si>
-    <t>0.118</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for CSP-header (Verify Point #216)</t>
-  </si>
-  <si>
-    <t>0.059</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at session-token (Verify Point #217)</t>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #371)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #372)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #373)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #374)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #375)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #376)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #377)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #378)</t>
+  </si>
+  <si>
+    <t>0.114</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #379)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #380)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #381)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #382)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #383)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #384)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #385)</t>
+  </si>
+  <si>
+    <t>0.049</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #386)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #387)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #388)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #389)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #390)</t>
   </si>
   <si>
     <t>0.048</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users-ref (Verify Point #218)</t>
-  </si>
-  <si>
-    <t>0.036</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for items-ref (Verify Point #219)</t>
-  </si>
-  <si>
-    <t>0.079</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field de-DE (Verify Point #220)</t>
-  </si>
-  <si>
-    <t>0.083</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for fr-FR (Verify Point #221)</t>
-  </si>
-  <si>
-    <t>0.090</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ja-JP (Verify Point #222)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for pt-BR (Verify Point #223)</t>
-  </si>
-  <si>
-    <t>0.080</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of it-IT (Verify Point #224)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for apiKey (Verify Point #225)</t>
-  </si>
-  <si>
-    <t>0.093</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for authDomain (Verify Point #226)</t>
-  </si>
-  <si>
-    <t>0.041</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value projectId (Verify Point #227)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session storageBucket (Verify Point #228)</t>
-  </si>
-  <si>
-    <t>0.029</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier messagingSenderId (Verify Point #229)</t>
-  </si>
-  <si>
-    <t>0.053</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region appId (Verify Point #230)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for name (Verify Point #231)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code id (Verify Point #232)</t>
-  </si>
-  <si>
-    <t>0.107</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource fees.min (Verify Point #233)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for fees.max (Verify Point #234)</t>
-  </si>
-  <si>
-    <t>0.073</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated courses (Verify Point #235)</t>
-  </si>
-  <si>
-    <t>0.108</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for ranking.nirf (Verify Point #236)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at type (Verify Point #237)</t>
-  </si>
-  <si>
-    <t>0.072</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users/uid001 (Verify Point #238)</t>
-  </si>
-  <si>
-    <t>0.088</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for colleges/c001 (Verify Point #239)</t>
-  </si>
-  <si>
-    <t>0.068</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field prompt-length (Verify Point #240)</t>
-  </si>
-  <si>
-    <t>0.066</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for session-id-1 (Verify Point #241)</t>
-  </si>
-  <si>
-    <t>0.058</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ₹1L (Verify Point #242)</t>
-  </si>
-  <si>
-    <t>0.076</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for B.Tech (Verify Point #243)</t>
-  </si>
-  <si>
-    <t>0.117</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of 4 years (Verify Point #244)</t>
-  </si>
-  <si>
-    <t>0.038</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for Tamil Nadu (Verify Point #245)</t>
-  </si>
-  <si>
-    <t>0.042</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for Chennai (Verify Point #246)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value llama3-8b (Verify Point #247)</t>
-  </si>
-  <si>
-    <t>0.032</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session email (Verify Point #248)</t>
-  </si>
-  <si>
-    <t>0.065</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier password (Verify Point #249)</t>
-  </si>
-  <si>
-    <t>0.021</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region displayName (Verify Point #250)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for savedColleges (Verify Point #251)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code createdAt (Verify Point #252)</t>
-  </si>
-  <si>
-    <t>0.116</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource firebase-auth (Verify Point #253)</t>
-  </si>
-  <si>
-    <t>0.043</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for firestore-read (Verify Point #254)</t>
-  </si>
-  <si>
-    <t>0.077</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated groq-api (Verify Point #255)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for college-list (Verify Point #256)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at XSS-injection (Verify Point #257)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation SQL-injection (Verify Point #258)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for CSRF-token (Verify Point #259)</t>
-  </si>
-  <si>
-    <t>0.051</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field CORS-origin (Verify Point #260)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for CSP-header (Verify Point #261)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for session-token (Verify Point #262)</t>
-  </si>
-  <si>
-    <t>0.089</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users-ref (Verify Point #263)</t>
-  </si>
-  <si>
-    <t>0.034</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of items-ref (Verify Point #264)</t>
-  </si>
-  <si>
-    <t>0.114</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for de-DE (Verify Point #265)</t>
-  </si>
-  <si>
-    <t>0.085</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for fr-FR (Verify Point #266)</t>
-  </si>
-  <si>
-    <t>0.049</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ja-JP (Verify Point #267)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session pt-BR (Verify Point #268)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier it-IT (Verify Point #269)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region apiKey (Verify Point #270)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for authDomain (Verify Point #271)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code projectId (Verify Point #272)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource storageBucket (Verify Point #273)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for messagingSenderId (Verify Point #274)</t>
-  </si>
-  <si>
-    <t>0.094</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated appId (Verify Point #275)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for name (Verify Point #276)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at id (Verify Point #277)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation fees.min (Verify Point #278)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for fees.max (Verify Point #279)</t>
-  </si>
-  <si>
-    <t>0.039</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field courses (Verify Point #280)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for ranking.nirf (Verify Point #281)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for type (Verify Point #282)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users/uid001 (Verify Point #283)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of colleges/c001 (Verify Point #284)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for prompt-length (Verify Point #285)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for session-id-1 (Verify Point #286)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ₹1L (Verify Point #287)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session B.Tech (Verify Point #288)</t>
-  </si>
-  <si>
-    <t>0.092</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier 4 years (Verify Point #289)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region Tamil Nadu (Verify Point #290)</t>
-  </si>
-  <si>
-    <t>0.097</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for Chennai (Verify Point #291)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code llama3-8b (Verify Point #292)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource email (Verify Point #293)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for password (Verify Point #294)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated displayName (Verify Point #295)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for savedColleges (Verify Point #296)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at createdAt (Verify Point #297)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation firebase-auth (Verify Point #298)</t>
-  </si>
-  <si>
-    <t>0.075</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for firestore-read (Verify Point #299)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field groq-api (Verify Point #300)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for college-list (Verify Point #301)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for XSS-injection (Verify Point #302)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for SQL-injection (Verify Point #303)</t>
-  </si>
-  <si>
-    <t>0.104</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of CSRF-token (Verify Point #304)</t>
-  </si>
-  <si>
-    <t>0.031</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for CORS-origin (Verify Point #305)</t>
-  </si>
-  <si>
-    <t>0.099</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for CSP-header (Verify Point #306)</t>
-  </si>
-  <si>
-    <t>0.064</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value session-token (Verify Point #307)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users-ref (Verify Point #308)</t>
-  </si>
-  <si>
-    <t>0.070</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier items-ref (Verify Point #309)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region de-DE (Verify Point #310)</t>
-  </si>
-  <si>
-    <t>0.063</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for fr-FR (Verify Point #311)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ja-JP (Verify Point #312)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource pt-BR (Verify Point #313)</t>
-  </si>
-  <si>
-    <t>0.100</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for it-IT (Verify Point #314)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated apiKey (Verify Point #315)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for authDomain (Verify Point #316)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at projectId (Verify Point #317)</t>
-  </si>
-  <si>
-    <t>0.052</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation storageBucket (Verify Point #318)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for messagingSenderId (Verify Point #319)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field appId (Verify Point #320)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for name (Verify Point #321)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for id (Verify Point #322)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for fees.min (Verify Point #323)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of fees.max (Verify Point #324)</t>
-  </si>
-  <si>
-    <t>0.081</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for courses (Verify Point #325)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for ranking.nirf (Verify Point #326)</t>
-  </si>
-  <si>
-    <t>0.055</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value type (Verify Point #327)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users/uid001 (Verify Point #328)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier colleges/c001 (Verify Point #329)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region prompt-length (Verify Point #330)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for session-id-1 (Verify Point #331)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ₹1L (Verify Point #332)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource B.Tech (Verify Point #333)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for 4 years (Verify Point #334)</t>
-  </si>
-  <si>
-    <t>0.050</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated Tamil Nadu (Verify Point #335)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for Chennai (Verify Point #336)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at llama3-8b (Verify Point #337)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation email (Verify Point #338)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for password (Verify Point #339)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field displayName (Verify Point #340)</t>
-  </si>
-  <si>
-    <t>0.119</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for savedColleges (Verify Point #341)</t>
-  </si>
-  <si>
-    <t>0.054</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for createdAt (Verify Point #342)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for firebase-auth (Verify Point #343)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of firestore-read (Verify Point #344)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for groq-api (Verify Point #345)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for college-list (Verify Point #346)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value XSS-injection (Verify Point #347)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session SQL-injection (Verify Point #348)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier CSRF-token (Verify Point #349)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region CORS-origin (Verify Point #350)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for CSP-header (Verify Point #351)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code session-token (Verify Point #352)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users-ref (Verify Point #353)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for items-ref (Verify Point #354)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated de-DE (Verify Point #355)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for fr-FR (Verify Point #356)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ja-JP (Verify Point #357)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation pt-BR (Verify Point #358)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for it-IT (Verify Point #359)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field apiKey (Verify Point #360)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #361)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #362)</t>
-  </si>
-  <si>
-    <t>0.044</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #363)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #364)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #365)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #366)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #367)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #368)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #369)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #370)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #371)</t>
-  </si>
-  <si>
-    <t>0.060</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #372)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #373)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #374)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #375)</t>
-  </si>
-  <si>
-    <t>0.061</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #376)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #377)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #378)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #379)</t>
-  </si>
-  <si>
-    <t>0.026</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #380)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #381)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #382)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #383)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #384)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #385)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #386)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #387)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #388)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #389)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #390)</t>
-  </si>
-  <si>
     <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #391)</t>
   </si>
   <si>
@@ -1493,9 +1496,6 @@
     <t>Smart Admission — Backend [Boundary]: Verify boundary condition at session-token (Verify Point #397)</t>
   </si>
   <si>
-    <t>0.082</t>
-  </si>
-  <si>
     <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users-ref (Verify Point #398)</t>
   </si>
   <si>
@@ -1511,13 +1511,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>22</t>
+    <t>23</t>
   </si>
   <si>
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 15:32:59 UTC</t>
+    <t>2026-06-23 15:39:53 UTC</t>
   </si>
   <si>
     <t>Branch</t>
@@ -1529,7 +1529,7 @@
     <t>Commit</t>
   </si>
   <si>
-    <t>f8042b0</t>
+    <t>19701a0</t>
   </si>
   <si>
     <t>Total</t>
@@ -2154,7 +2154,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -2290,7 +2290,7 @@
         <v>6</v>
       </c>
       <c r="D21" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -2307,7 +2307,7 @@
         <v>6</v>
       </c>
       <c r="D22" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -2443,7 +2443,7 @@
         <v>6</v>
       </c>
       <c r="D30" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -2596,7 +2596,7 @@
         <v>6</v>
       </c>
       <c r="D39" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -2783,7 +2783,7 @@
         <v>6</v>
       </c>
       <c r="D50" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -3055,7 +3055,7 @@
         <v>6</v>
       </c>
       <c r="D66" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
@@ -3208,7 +3208,7 @@
         <v>6</v>
       </c>
       <c r="D75" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
@@ -3327,7 +3327,7 @@
         <v>6</v>
       </c>
       <c r="D82" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
@@ -3480,7 +3480,7 @@
         <v>6</v>
       </c>
       <c r="D91" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E91" t="s">
         <v>8</v>
@@ -3497,7 +3497,7 @@
         <v>6</v>
       </c>
       <c r="D92" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E92" t="s">
         <v>8</v>
@@ -3599,7 +3599,7 @@
         <v>6</v>
       </c>
       <c r="D98" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E98" t="s">
         <v>8</v>
@@ -3616,7 +3616,7 @@
         <v>6</v>
       </c>
       <c r="D99" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
@@ -3718,7 +3718,7 @@
         <v>6</v>
       </c>
       <c r="D105" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E105" t="s">
         <v>8</v>
@@ -3752,7 +3752,7 @@
         <v>6</v>
       </c>
       <c r="D107" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
@@ -3922,7 +3922,7 @@
         <v>6</v>
       </c>
       <c r="D117" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E117" t="s">
         <v>8</v>
@@ -3973,7 +3973,7 @@
         <v>6</v>
       </c>
       <c r="D120" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E120" t="s">
         <v>8</v>
@@ -4262,7 +4262,7 @@
         <v>6</v>
       </c>
       <c r="D137" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E137" t="s">
         <v>8</v>
@@ -4279,7 +4279,7 @@
         <v>6</v>
       </c>
       <c r="D138" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E138" t="s">
         <v>8</v>
@@ -4415,7 +4415,7 @@
         <v>6</v>
       </c>
       <c r="D146" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E146" t="s">
         <v>8</v>
@@ -4619,7 +4619,7 @@
         <v>6</v>
       </c>
       <c r="D158" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E158" t="s">
         <v>8</v>
@@ -5180,7 +5180,7 @@
         <v>6</v>
       </c>
       <c r="D191" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="E191" t="s">
         <v>8</v>
@@ -5191,13 +5191,13 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
+        <v>208</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D192" t="s">
         <v>209</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D192" t="s">
-        <v>210</v>
       </c>
       <c r="E192" t="s">
         <v>8</v>
@@ -5208,13 +5208,13 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
+        <v>210</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D193" t="s">
         <v>211</v>
-      </c>
-      <c r="C193" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D193" t="s">
-        <v>212</v>
       </c>
       <c r="E193" t="s">
         <v>8</v>
@@ -5225,13 +5225,13 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D194" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="E194" t="s">
         <v>8</v>
@@ -5242,13 +5242,13 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
+        <v>213</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D195" t="s">
         <v>214</v>
-      </c>
-      <c r="C195" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D195" t="s">
-        <v>215</v>
       </c>
       <c r="E195" t="s">
         <v>8</v>
@@ -5259,13 +5259,13 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D196" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E196" t="s">
         <v>8</v>
@@ -5276,13 +5276,13 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
+        <v>216</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D197" t="s">
         <v>217</v>
-      </c>
-      <c r="C197" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D197" t="s">
-        <v>218</v>
       </c>
       <c r="E197" t="s">
         <v>8</v>
@@ -5293,13 +5293,13 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D198" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="E198" t="s">
         <v>8</v>
@@ -5310,13 +5310,13 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D199" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E199" t="s">
         <v>8</v>
@@ -5327,13 +5327,13 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D200" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E200" t="s">
         <v>8</v>
@@ -5344,13 +5344,13 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D201" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E201" t="s">
         <v>8</v>
@@ -5361,13 +5361,13 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D202" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E202" t="s">
         <v>8</v>
@@ -5378,13 +5378,13 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D203" t="s">
-        <v>192</v>
+        <v>228</v>
       </c>
       <c r="E203" t="s">
         <v>8</v>
@@ -5395,13 +5395,13 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D204" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="E204" t="s">
         <v>8</v>
@@ -5412,13 +5412,13 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D205" t="s">
-        <v>232</v>
+        <v>194</v>
       </c>
       <c r="E205" t="s">
         <v>8</v>
@@ -5429,13 +5429,13 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D206" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E206" t="s">
         <v>8</v>
@@ -5446,13 +5446,13 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D207" t="s">
-        <v>192</v>
+        <v>234</v>
       </c>
       <c r="E207" t="s">
         <v>8</v>
@@ -5463,13 +5463,13 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
+        <v>235</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D208" t="s">
         <v>236</v>
-      </c>
-      <c r="C208" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D208" t="s">
-        <v>237</v>
       </c>
       <c r="E208" t="s">
         <v>8</v>
@@ -5480,13 +5480,13 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D209" t="s">
-        <v>234</v>
+        <v>190</v>
       </c>
       <c r="E209" t="s">
         <v>8</v>
@@ -5497,13 +5497,13 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
+        <v>238</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D210" t="s">
         <v>239</v>
-      </c>
-      <c r="C210" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D210" t="s">
-        <v>240</v>
       </c>
       <c r="E210" t="s">
         <v>8</v>
@@ -5514,13 +5514,13 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
+        <v>240</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D211" t="s">
         <v>241</v>
-      </c>
-      <c r="C211" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D211" t="s">
-        <v>242</v>
       </c>
       <c r="E211" t="s">
         <v>8</v>
@@ -5531,13 +5531,13 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D212" t="s">
-        <v>244</v>
+        <v>206</v>
       </c>
       <c r="E212" t="s">
         <v>8</v>
@@ -5548,13 +5548,13 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D213" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E213" t="s">
         <v>8</v>
@@ -5565,13 +5565,13 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D214" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E214" t="s">
         <v>8</v>
@@ -5582,13 +5582,13 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D215" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E215" t="s">
         <v>8</v>
@@ -5599,13 +5599,13 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D216" t="s">
-        <v>251</v>
+        <v>192</v>
       </c>
       <c r="E216" t="s">
         <v>8</v>
@@ -5616,13 +5616,13 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D217" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E217" t="s">
         <v>8</v>
@@ -5633,13 +5633,13 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D218" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E218" t="s">
         <v>8</v>
@@ -5650,13 +5650,13 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D219" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E219" t="s">
         <v>8</v>
@@ -5667,13 +5667,13 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D220" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E220" t="s">
         <v>8</v>
@@ -5684,13 +5684,13 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D221" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E221" t="s">
         <v>8</v>
@@ -5701,13 +5701,13 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D222" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E222" t="s">
         <v>8</v>
@@ -5718,13 +5718,13 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D223" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="E223" t="s">
         <v>8</v>
@@ -5735,13 +5735,13 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D224" t="s">
-        <v>222</v>
+        <v>264</v>
       </c>
       <c r="E224" t="s">
         <v>8</v>
@@ -5752,13 +5752,13 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D225" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E225" t="s">
         <v>8</v>
@@ -5769,13 +5769,13 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D226" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="E226" t="s">
         <v>8</v>
@@ -5786,13 +5786,13 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D227" t="s">
-        <v>271</v>
+        <v>224</v>
       </c>
       <c r="E227" t="s">
         <v>8</v>
@@ -5803,13 +5803,13 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D228" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E228" t="s">
         <v>8</v>
@@ -5820,13 +5820,13 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D229" t="s">
-        <v>204</v>
+        <v>272</v>
       </c>
       <c r="E229" t="s">
         <v>8</v>
@@ -5837,13 +5837,13 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D230" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="E230" t="s">
         <v>8</v>
@@ -5854,13 +5854,13 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D231" t="s">
-        <v>278</v>
+        <v>244</v>
       </c>
       <c r="E231" t="s">
         <v>8</v>
@@ -5871,13 +5871,13 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D232" t="s">
-        <v>232</v>
+        <v>276</v>
       </c>
       <c r="E232" t="s">
         <v>8</v>
@@ -5888,13 +5888,13 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D233" t="s">
-        <v>194</v>
+        <v>246</v>
       </c>
       <c r="E233" t="s">
         <v>8</v>
@@ -5905,13 +5905,13 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D234" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E234" t="s">
         <v>8</v>
@@ -5922,13 +5922,13 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D235" t="s">
-        <v>194</v>
+        <v>281</v>
       </c>
       <c r="E235" t="s">
         <v>8</v>
@@ -5939,13 +5939,13 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D236" t="s">
-        <v>285</v>
+        <v>252</v>
       </c>
       <c r="E236" t="s">
         <v>8</v>
@@ -5956,13 +5956,13 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D237" t="s">
-        <v>287</v>
+        <v>206</v>
       </c>
       <c r="E237" t="s">
         <v>8</v>
@@ -5973,13 +5973,13 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D238" t="s">
-        <v>287</v>
+        <v>250</v>
       </c>
       <c r="E238" t="s">
         <v>8</v>
@@ -5990,13 +5990,13 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D239" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E239" t="s">
         <v>8</v>
@@ -6007,13 +6007,13 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D240" t="s">
-        <v>292</v>
+        <v>224</v>
       </c>
       <c r="E240" t="s">
         <v>8</v>
@@ -6024,13 +6024,13 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D241" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="E241" t="s">
         <v>8</v>
@@ -6041,13 +6041,13 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D242" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="E242" t="s">
         <v>8</v>
@@ -6058,13 +6058,13 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D243" t="s">
-        <v>298</v>
+        <v>226</v>
       </c>
       <c r="E243" t="s">
         <v>8</v>
@@ -6075,13 +6075,13 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D244" t="s">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="E244" t="s">
         <v>8</v>
@@ -6092,13 +6092,13 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D245" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="E245" t="s">
         <v>8</v>
@@ -6109,13 +6109,13 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D246" t="s">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="E246" t="s">
         <v>8</v>
@@ -6126,13 +6126,13 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D247" t="s">
-        <v>306</v>
+        <v>217</v>
       </c>
       <c r="E247" t="s">
         <v>8</v>
@@ -6143,13 +6143,13 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D248" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="E248" t="s">
         <v>8</v>
@@ -6160,13 +6160,13 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D249" t="s">
-        <v>309</v>
+        <v>224</v>
       </c>
       <c r="E249" t="s">
         <v>8</v>
@@ -6177,13 +6177,13 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D250" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="E250" t="s">
         <v>8</v>
@@ -6194,13 +6194,13 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D251" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="E251" t="s">
         <v>8</v>
@@ -6211,13 +6211,13 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D252" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="E252" t="s">
         <v>8</v>
@@ -6228,13 +6228,13 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D253" t="s">
-        <v>208</v>
+        <v>306</v>
       </c>
       <c r="E253" t="s">
         <v>8</v>
@@ -6245,13 +6245,13 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D254" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="E254" t="s">
         <v>8</v>
@@ -6262,13 +6262,13 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D255" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="E255" t="s">
         <v>8</v>
@@ -6279,13 +6279,13 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D256" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="E256" t="s">
         <v>8</v>
@@ -6296,13 +6296,13 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D257" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="E257" t="s">
         <v>8</v>
@@ -6313,13 +6313,13 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D258" t="s">
-        <v>190</v>
+        <v>232</v>
       </c>
       <c r="E258" t="s">
         <v>8</v>
@@ -6330,13 +6330,13 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D259" t="s">
-        <v>282</v>
+        <v>317</v>
       </c>
       <c r="E259" t="s">
         <v>8</v>
@@ -6347,13 +6347,13 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D260" t="s">
-        <v>190</v>
+        <v>310</v>
       </c>
       <c r="E260" t="s">
         <v>8</v>
@@ -6364,13 +6364,13 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D261" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="E261" t="s">
         <v>8</v>
@@ -6381,13 +6381,13 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D262" t="s">
-        <v>215</v>
+        <v>321</v>
       </c>
       <c r="E262" t="s">
         <v>8</v>
@@ -6398,13 +6398,13 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D263" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
       <c r="E263" t="s">
         <v>8</v>
@@ -6415,13 +6415,13 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D264" t="s">
-        <v>331</v>
+        <v>276</v>
       </c>
       <c r="E264" t="s">
         <v>8</v>
@@ -6432,13 +6432,13 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D265" t="s">
-        <v>333</v>
+        <v>310</v>
       </c>
       <c r="E265" t="s">
         <v>8</v>
@@ -6449,13 +6449,13 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D266" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="E266" t="s">
         <v>8</v>
@@ -6466,13 +6466,13 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D267" t="s">
-        <v>337</v>
+        <v>246</v>
       </c>
       <c r="E267" t="s">
         <v>8</v>
@@ -6483,13 +6483,13 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D268" t="s">
-        <v>339</v>
+        <v>192</v>
       </c>
       <c r="E268" t="s">
         <v>8</v>
@@ -6500,13 +6500,13 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D269" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="E269" t="s">
         <v>8</v>
@@ -6517,13 +6517,13 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D270" t="s">
-        <v>215</v>
+        <v>331</v>
       </c>
       <c r="E270" t="s">
         <v>8</v>
@@ -6534,13 +6534,13 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D271" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="E271" t="s">
         <v>8</v>
@@ -6551,13 +6551,13 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D272" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="E272" t="s">
         <v>8</v>
@@ -6568,13 +6568,13 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D273" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="E273" t="s">
         <v>8</v>
@@ -6585,13 +6585,13 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D274" t="s">
-        <v>251</v>
+        <v>331</v>
       </c>
       <c r="E274" t="s">
         <v>8</v>
@@ -6602,13 +6602,13 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D275" t="s">
-        <v>265</v>
+        <v>338</v>
       </c>
       <c r="E275" t="s">
         <v>8</v>
@@ -6619,13 +6619,13 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D276" t="s">
-        <v>348</v>
+        <v>270</v>
       </c>
       <c r="E276" t="s">
         <v>8</v>
@@ -6636,13 +6636,13 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D277" t="s">
-        <v>335</v>
+        <v>317</v>
       </c>
       <c r="E277" t="s">
         <v>8</v>
@@ -6653,13 +6653,13 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D278" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="E278" t="s">
         <v>8</v>
@@ -6670,13 +6670,13 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D279" t="s">
-        <v>237</v>
+        <v>209</v>
       </c>
       <c r="E279" t="s">
         <v>8</v>
@@ -6687,13 +6687,13 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D280" t="s">
-        <v>313</v>
+        <v>206</v>
       </c>
       <c r="E280" t="s">
         <v>8</v>
@@ -6704,13 +6704,13 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D281" t="s">
-        <v>354</v>
+        <v>222</v>
       </c>
       <c r="E281" t="s">
         <v>8</v>
@@ -6721,13 +6721,13 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D282" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E282" t="s">
         <v>8</v>
@@ -6738,13 +6738,13 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D283" t="s">
-        <v>294</v>
+        <v>338</v>
       </c>
       <c r="E283" t="s">
         <v>8</v>
@@ -6755,13 +6755,13 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D284" t="s">
-        <v>202</v>
+        <v>252</v>
       </c>
       <c r="E284" t="s">
         <v>8</v>
@@ -6772,13 +6772,13 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D285" t="s">
-        <v>304</v>
+        <v>350</v>
       </c>
       <c r="E285" t="s">
         <v>8</v>
@@ -6789,13 +6789,13 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D286" t="s">
-        <v>212</v>
+        <v>312</v>
       </c>
       <c r="E286" t="s">
         <v>8</v>
@@ -6806,13 +6806,13 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D287" t="s">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="E287" t="s">
         <v>8</v>
@@ -6823,13 +6823,13 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D288" t="s">
-        <v>290</v>
+        <v>354</v>
       </c>
       <c r="E288" t="s">
         <v>8</v>
@@ -6840,13 +6840,13 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D289" t="s">
-        <v>300</v>
+        <v>276</v>
       </c>
       <c r="E289" t="s">
         <v>8</v>
@@ -6857,13 +6857,13 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D290" t="s">
-        <v>364</v>
+        <v>232</v>
       </c>
       <c r="E290" t="s">
         <v>8</v>
@@ -6874,13 +6874,13 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D291" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="E291" t="s">
         <v>8</v>
@@ -6891,13 +6891,13 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D292" t="s">
-        <v>367</v>
+        <v>209</v>
       </c>
       <c r="E292" t="s">
         <v>8</v>
@@ -6908,13 +6908,13 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D293" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E293" t="s">
         <v>8</v>
@@ -6925,13 +6925,13 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D294" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="E294" t="s">
         <v>8</v>
@@ -6942,13 +6942,13 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D295" t="s">
-        <v>215</v>
+        <v>260</v>
       </c>
       <c r="E295" t="s">
         <v>8</v>
@@ -6959,13 +6959,13 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D296" t="s">
-        <v>198</v>
+        <v>365</v>
       </c>
       <c r="E296" t="s">
         <v>8</v>
@@ -6976,13 +6976,13 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D297" t="s">
-        <v>237</v>
+        <v>367</v>
       </c>
       <c r="E297" t="s">
         <v>8</v>
@@ -6993,13 +6993,13 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D298" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="E298" t="s">
         <v>8</v>
@@ -7010,13 +7010,13 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D299" t="s">
-        <v>273</v>
+        <v>370</v>
       </c>
       <c r="E299" t="s">
         <v>8</v>
@@ -7027,13 +7027,13 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D300" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="E300" t="s">
         <v>8</v>
@@ -7044,13 +7044,13 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D301" t="s">
-        <v>224</v>
+        <v>333</v>
       </c>
       <c r="E301" t="s">
         <v>8</v>
@@ -7061,13 +7061,13 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D302" t="s">
-        <v>290</v>
+        <v>375</v>
       </c>
       <c r="E302" t="s">
         <v>8</v>
@@ -7078,13 +7078,13 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D303" t="s">
-        <v>337</v>
+        <v>377</v>
       </c>
       <c r="E303" t="s">
         <v>8</v>
@@ -7095,13 +7095,13 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D304" t="s">
-        <v>257</v>
+        <v>236</v>
       </c>
       <c r="E304" t="s">
         <v>8</v>
@@ -7112,13 +7112,13 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D305" t="s">
-        <v>382</v>
+        <v>190</v>
       </c>
       <c r="E305" t="s">
         <v>8</v>
@@ -7129,13 +7129,13 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D306" t="s">
-        <v>384</v>
+        <v>222</v>
       </c>
       <c r="E306" t="s">
         <v>8</v>
@@ -7146,13 +7146,13 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D307" t="s">
-        <v>386</v>
+        <v>236</v>
       </c>
       <c r="E307" t="s">
         <v>8</v>
@@ -7163,13 +7163,13 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D308" t="s">
-        <v>388</v>
+        <v>224</v>
       </c>
       <c r="E308" t="s">
         <v>8</v>
@@ -7180,13 +7180,13 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D309" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E309" t="s">
         <v>8</v>
@@ -7197,13 +7197,13 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D310" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="E310" t="s">
         <v>8</v>
@@ -7214,13 +7214,13 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D311" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="E311" t="s">
         <v>8</v>
@@ -7231,13 +7231,13 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D312" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E312" t="s">
         <v>8</v>
@@ -7248,13 +7248,13 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D313" t="s">
-        <v>339</v>
+        <v>244</v>
       </c>
       <c r="E313" t="s">
         <v>8</v>
@@ -7265,13 +7265,13 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D314" t="s">
-        <v>220</v>
+        <v>392</v>
       </c>
       <c r="E314" t="s">
         <v>8</v>
@@ -7282,13 +7282,13 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D315" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E315" t="s">
         <v>8</v>
@@ -7299,13 +7299,13 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D316" t="s">
-        <v>244</v>
+        <v>342</v>
       </c>
       <c r="E316" t="s">
         <v>8</v>
@@ -7316,13 +7316,13 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D317" t="s">
-        <v>255</v>
+        <v>192</v>
       </c>
       <c r="E317" t="s">
         <v>8</v>
@@ -7333,13 +7333,13 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D318" t="s">
-        <v>234</v>
+        <v>398</v>
       </c>
       <c r="E318" t="s">
         <v>8</v>
@@ -7350,13 +7350,13 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D319" t="s">
-        <v>403</v>
+        <v>342</v>
       </c>
       <c r="E319" t="s">
         <v>8</v>
@@ -7367,13 +7367,13 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D320" t="s">
-        <v>364</v>
+        <v>224</v>
       </c>
       <c r="E320" t="s">
         <v>8</v>
@@ -7384,13 +7384,13 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D321" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="E321" t="s">
         <v>8</v>
@@ -7401,13 +7401,13 @@
         <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D322" t="s">
-        <v>321</v>
+        <v>206</v>
       </c>
       <c r="E322" t="s">
         <v>8</v>
@@ -7418,13 +7418,13 @@
         <v>322</v>
       </c>
       <c r="B323" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D323" t="s">
-        <v>367</v>
+        <v>404</v>
       </c>
       <c r="E323" t="s">
         <v>8</v>
@@ -7435,13 +7435,13 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D324" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="E324" t="s">
         <v>8</v>
@@ -7452,13 +7452,13 @@
         <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D325" t="s">
-        <v>300</v>
+        <v>386</v>
       </c>
       <c r="E325" t="s">
         <v>8</v>
@@ -7469,13 +7469,13 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D326" t="s">
-        <v>411</v>
+        <v>362</v>
       </c>
       <c r="E326" t="s">
         <v>8</v>
@@ -7486,13 +7486,13 @@
         <v>326</v>
       </c>
       <c r="B327" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D327" t="s">
-        <v>242</v>
+        <v>342</v>
       </c>
       <c r="E327" t="s">
         <v>8</v>
@@ -7503,13 +7503,13 @@
         <v>327</v>
       </c>
       <c r="B328" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D328" t="s">
-        <v>414</v>
+        <v>342</v>
       </c>
       <c r="E328" t="s">
         <v>8</v>
@@ -7520,13 +7520,13 @@
         <v>328</v>
       </c>
       <c r="B329" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D329" t="s">
-        <v>394</v>
+        <v>314</v>
       </c>
       <c r="E329" t="s">
         <v>8</v>
@@ -7537,13 +7537,13 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D330" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="E330" t="s">
         <v>8</v>
@@ -7554,13 +7554,13 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D331" t="s">
-        <v>255</v>
+        <v>281</v>
       </c>
       <c r="E331" t="s">
         <v>8</v>
@@ -7571,13 +7571,13 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D332" t="s">
-        <v>306</v>
+        <v>370</v>
       </c>
       <c r="E332" t="s">
         <v>8</v>
@@ -7588,13 +7588,13 @@
         <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D333" t="s">
-        <v>327</v>
+        <v>415</v>
       </c>
       <c r="E333" t="s">
         <v>8</v>
@@ -7605,13 +7605,13 @@
         <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D334" t="s">
-        <v>202</v>
+        <v>295</v>
       </c>
       <c r="E334" t="s">
         <v>8</v>
@@ -7622,13 +7622,13 @@
         <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D335" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="E335" t="s">
         <v>8</v>
@@ -7639,13 +7639,13 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D336" t="s">
-        <v>423</v>
+        <v>321</v>
       </c>
       <c r="E336" t="s">
         <v>8</v>
@@ -7656,13 +7656,13 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D337" t="s">
-        <v>391</v>
+        <v>420</v>
       </c>
       <c r="E337" t="s">
         <v>8</v>
@@ -7673,13 +7673,13 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D338" t="s">
-        <v>317</v>
+        <v>415</v>
       </c>
       <c r="E338" t="s">
         <v>8</v>
@@ -7690,13 +7690,13 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D339" t="s">
-        <v>313</v>
+        <v>252</v>
       </c>
       <c r="E339" t="s">
         <v>8</v>
@@ -7707,13 +7707,13 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D340" t="s">
-        <v>194</v>
+        <v>362</v>
       </c>
       <c r="E340" t="s">
         <v>8</v>
@@ -7724,13 +7724,13 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D341" t="s">
-        <v>333</v>
+        <v>425</v>
       </c>
       <c r="E341" t="s">
         <v>8</v>
@@ -7741,13 +7741,13 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D342" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E342" t="s">
         <v>8</v>
@@ -7758,13 +7758,13 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D343" t="s">
-        <v>432</v>
+        <v>226</v>
       </c>
       <c r="E343" t="s">
         <v>8</v>
@@ -7775,7 +7775,7 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>6</v>
@@ -7792,13 +7792,13 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D345" t="s">
-        <v>317</v>
+        <v>279</v>
       </c>
       <c r="E345" t="s">
         <v>8</v>
@@ -7809,13 +7809,13 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D346" t="s">
-        <v>196</v>
+        <v>239</v>
       </c>
       <c r="E346" t="s">
         <v>8</v>
@@ -7826,13 +7826,13 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D347" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="E347" t="s">
         <v>8</v>
@@ -7843,13 +7843,13 @@
         <v>347</v>
       </c>
       <c r="B348" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D348" t="s">
-        <v>391</v>
+        <v>241</v>
       </c>
       <c r="E348" t="s">
         <v>8</v>
@@ -7860,13 +7860,13 @@
         <v>348</v>
       </c>
       <c r="B349" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D349" t="s">
-        <v>192</v>
+        <v>435</v>
       </c>
       <c r="E349" t="s">
         <v>8</v>
@@ -7877,13 +7877,13 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D350" t="s">
-        <v>388</v>
+        <v>354</v>
       </c>
       <c r="E350" t="s">
         <v>8</v>
@@ -7894,13 +7894,13 @@
         <v>350</v>
       </c>
       <c r="B351" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D351" t="s">
-        <v>204</v>
+        <v>241</v>
       </c>
       <c r="E351" t="s">
         <v>8</v>
@@ -7911,13 +7911,13 @@
         <v>351</v>
       </c>
       <c r="B352" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D352" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E352" t="s">
         <v>8</v>
@@ -7928,13 +7928,13 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D353" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="E353" t="s">
         <v>8</v>
@@ -7945,13 +7945,13 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D354" t="s">
-        <v>255</v>
+        <v>441</v>
       </c>
       <c r="E354" t="s">
         <v>8</v>
@@ -7962,13 +7962,13 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D355" t="s">
-        <v>311</v>
+        <v>394</v>
       </c>
       <c r="E355" t="s">
         <v>8</v>
@@ -7979,13 +7979,13 @@
         <v>355</v>
       </c>
       <c r="B356" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D356" t="s">
-        <v>287</v>
+        <v>314</v>
       </c>
       <c r="E356" t="s">
         <v>8</v>
@@ -7996,13 +7996,13 @@
         <v>356</v>
       </c>
       <c r="B357" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D357" t="s">
-        <v>287</v>
+        <v>306</v>
       </c>
       <c r="E357" t="s">
         <v>8</v>
@@ -8013,13 +8013,13 @@
         <v>357</v>
       </c>
       <c r="B358" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D358" t="s">
-        <v>391</v>
+        <v>262</v>
       </c>
       <c r="E358" t="s">
         <v>8</v>
@@ -8030,13 +8030,13 @@
         <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D359" t="s">
-        <v>259</v>
+        <v>362</v>
       </c>
       <c r="E359" t="s">
         <v>8</v>
@@ -8047,13 +8047,13 @@
         <v>359</v>
       </c>
       <c r="B360" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D360" t="s">
-        <v>411</v>
+        <v>308</v>
       </c>
       <c r="E360" t="s">
         <v>8</v>
@@ -8064,13 +8064,13 @@
         <v>360</v>
       </c>
       <c r="B361" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D361" t="s">
-        <v>261</v>
+        <v>372</v>
       </c>
       <c r="E361" t="s">
         <v>8</v>
@@ -8081,13 +8081,13 @@
         <v>361</v>
       </c>
       <c r="B362" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D362" t="s">
-        <v>220</v>
+        <v>450</v>
       </c>
       <c r="E362" t="s">
         <v>8</v>
@@ -8098,13 +8098,13 @@
         <v>362</v>
       </c>
       <c r="B363" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D363" t="s">
-        <v>298</v>
+        <v>377</v>
       </c>
       <c r="E363" t="s">
         <v>8</v>
@@ -8115,13 +8115,13 @@
         <v>363</v>
       </c>
       <c r="B364" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D364" t="s">
-        <v>454</v>
+        <v>228</v>
       </c>
       <c r="E364" t="s">
         <v>8</v>
@@ -8132,13 +8132,13 @@
         <v>364</v>
       </c>
       <c r="B365" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D365" t="s">
-        <v>339</v>
+        <v>404</v>
       </c>
       <c r="E365" t="s">
         <v>8</v>
@@ -8149,13 +8149,13 @@
         <v>365</v>
       </c>
       <c r="B366" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D366" t="s">
-        <v>290</v>
+        <v>333</v>
       </c>
       <c r="E366" t="s">
         <v>8</v>
@@ -8166,13 +8166,13 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D367" t="s">
-        <v>276</v>
+        <v>456</v>
       </c>
       <c r="E367" t="s">
         <v>8</v>
@@ -8183,13 +8183,13 @@
         <v>367</v>
       </c>
       <c r="B368" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D368" t="s">
-        <v>294</v>
+        <v>425</v>
       </c>
       <c r="E368" t="s">
         <v>8</v>
@@ -8200,13 +8200,13 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D369" t="s">
-        <v>190</v>
+        <v>441</v>
       </c>
       <c r="E369" t="s">
         <v>8</v>
@@ -8217,13 +8217,13 @@
         <v>369</v>
       </c>
       <c r="B370" t="s">
+        <v>459</v>
+      </c>
+      <c r="C370" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D370" t="s">
         <v>460</v>
-      </c>
-      <c r="C370" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D370" t="s">
-        <v>255</v>
       </c>
       <c r="E370" t="s">
         <v>8</v>
@@ -8240,7 +8240,7 @@
         <v>6</v>
       </c>
       <c r="D371" t="s">
-        <v>327</v>
+        <v>264</v>
       </c>
       <c r="E371" t="s">
         <v>8</v>
@@ -8257,7 +8257,7 @@
         <v>6</v>
       </c>
       <c r="D372" t="s">
-        <v>411</v>
+        <v>463</v>
       </c>
       <c r="E372" t="s">
         <v>8</v>
@@ -8268,13 +8268,13 @@
         <v>372</v>
       </c>
       <c r="B373" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D373" t="s">
-        <v>464</v>
+        <v>252</v>
       </c>
       <c r="E373" t="s">
         <v>8</v>
@@ -8291,7 +8291,7 @@
         <v>6</v>
       </c>
       <c r="D374" t="s">
-        <v>196</v>
+        <v>295</v>
       </c>
       <c r="E374" t="s">
         <v>8</v>
@@ -8308,7 +8308,7 @@
         <v>6</v>
       </c>
       <c r="D375" t="s">
-        <v>319</v>
+        <v>198</v>
       </c>
       <c r="E375" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>6</v>
       </c>
       <c r="D376" t="s">
-        <v>222</v>
+        <v>270</v>
       </c>
       <c r="E376" t="s">
         <v>8</v>
@@ -8342,7 +8342,7 @@
         <v>6</v>
       </c>
       <c r="D377" t="s">
-        <v>469</v>
+        <v>279</v>
       </c>
       <c r="E377" t="s">
         <v>8</v>
@@ -8353,13 +8353,13 @@
         <v>377</v>
       </c>
       <c r="B378" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D378" t="s">
-        <v>290</v>
+        <v>317</v>
       </c>
       <c r="E378" t="s">
         <v>8</v>
@@ -8370,13 +8370,13 @@
         <v>378</v>
       </c>
       <c r="B379" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D379" t="s">
-        <v>391</v>
+        <v>338</v>
       </c>
       <c r="E379" t="s">
         <v>8</v>
@@ -8387,13 +8387,13 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
+        <v>471</v>
+      </c>
+      <c r="C380" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D380" t="s">
         <v>472</v>
-      </c>
-      <c r="C380" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D380" t="s">
-        <v>206</v>
       </c>
       <c r="E380" t="s">
         <v>8</v>
@@ -8410,7 +8410,7 @@
         <v>6</v>
       </c>
       <c r="D381" t="s">
-        <v>474</v>
+        <v>220</v>
       </c>
       <c r="E381" t="s">
         <v>8</v>
@@ -8421,13 +8421,13 @@
         <v>381</v>
       </c>
       <c r="B382" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D382" t="s">
-        <v>321</v>
+        <v>392</v>
       </c>
       <c r="E382" t="s">
         <v>8</v>
@@ -8438,13 +8438,13 @@
         <v>382</v>
       </c>
       <c r="B383" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D383" t="s">
-        <v>224</v>
+        <v>192</v>
       </c>
       <c r="E383" t="s">
         <v>8</v>
@@ -8455,13 +8455,13 @@
         <v>383</v>
       </c>
       <c r="B384" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D384" t="s">
-        <v>234</v>
+        <v>196</v>
       </c>
       <c r="E384" t="s">
         <v>8</v>
@@ -8472,13 +8472,13 @@
         <v>384</v>
       </c>
       <c r="B385" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D385" t="s">
-        <v>294</v>
+        <v>232</v>
       </c>
       <c r="E385" t="s">
         <v>8</v>
@@ -8489,13 +8489,13 @@
         <v>385</v>
       </c>
       <c r="B386" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D386" t="s">
-        <v>240</v>
+        <v>295</v>
       </c>
       <c r="E386" t="s">
         <v>8</v>
@@ -8506,13 +8506,13 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
+        <v>479</v>
+      </c>
+      <c r="C387" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D387" t="s">
         <v>480</v>
-      </c>
-      <c r="C387" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D387" t="s">
-        <v>208</v>
       </c>
       <c r="E387" t="s">
         <v>8</v>
@@ -8529,7 +8529,7 @@
         <v>6</v>
       </c>
       <c r="D388" t="s">
-        <v>222</v>
+        <v>310</v>
       </c>
       <c r="E388" t="s">
         <v>8</v>
@@ -8546,7 +8546,7 @@
         <v>6</v>
       </c>
       <c r="D389" t="s">
-        <v>261</v>
+        <v>354</v>
       </c>
       <c r="E389" t="s">
         <v>8</v>
@@ -8563,7 +8563,7 @@
         <v>6</v>
       </c>
       <c r="D390" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="E390" t="s">
         <v>8</v>
@@ -8580,7 +8580,7 @@
         <v>6</v>
       </c>
       <c r="D391" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="E391" t="s">
         <v>8</v>
@@ -8597,7 +8597,7 @@
         <v>6</v>
       </c>
       <c r="D392" t="s">
-        <v>268</v>
+        <v>486</v>
       </c>
       <c r="E392" t="s">
         <v>8</v>
@@ -8608,13 +8608,13 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D393" t="s">
-        <v>265</v>
+        <v>228</v>
       </c>
       <c r="E393" t="s">
         <v>8</v>
@@ -8625,13 +8625,13 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D394" t="s">
-        <v>290</v>
+        <v>220</v>
       </c>
       <c r="E394" t="s">
         <v>8</v>
@@ -8642,13 +8642,13 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D395" t="s">
-        <v>354</v>
+        <v>276</v>
       </c>
       <c r="E395" t="s">
         <v>8</v>
@@ -8659,13 +8659,13 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D396" t="s">
-        <v>226</v>
+        <v>281</v>
       </c>
       <c r="E396" t="s">
         <v>8</v>
@@ -8676,13 +8676,13 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D397" t="s">
-        <v>215</v>
+        <v>241</v>
       </c>
       <c r="E397" t="s">
         <v>8</v>
@@ -8693,13 +8693,13 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D398" t="s">
-        <v>257</v>
+        <v>192</v>
       </c>
       <c r="E398" t="s">
         <v>8</v>
@@ -8710,13 +8710,13 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D399" t="s">
-        <v>493</v>
+        <v>331</v>
       </c>
       <c r="E399" t="s">
         <v>8</v>
@@ -8733,7 +8733,7 @@
         <v>6</v>
       </c>
       <c r="D400" t="s">
-        <v>398</v>
+        <v>190</v>
       </c>
       <c r="E400" t="s">
         <v>8</v>
@@ -8750,7 +8750,7 @@
         <v>6</v>
       </c>
       <c r="D401" t="s">
-        <v>382</v>
+        <v>291</v>
       </c>
       <c r="E401" t="s">
         <v>8</v>

--- a/reports/backend/Excel/Automation_Test_Report.xlsx
+++ b/reports/backend/Excel/Automation_Test_Report.xlsx
@@ -35,36 +35,36 @@
     <t>PASSED</t>
   </si>
   <si>
+    <t>0.000</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Smart Admission Backend — Authentication Tests BT-002 | Firebase config has authDomain</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — Authentication Tests BT-003 | Firebase config has projectId</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — Authentication Tests BT-004 | Firebase config has storageBucket</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — Authentication Tests BT-005 | Firebase config has messagingSenderId</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — Authentication Tests BT-006 | Firebase config has appId</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — Authentication Tests BT-007 | Firebase config projectId matches authDomain prefix</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — Authentication Tests BT-008 | Firebase config has all 6 required fields</t>
+  </si>
+  <si>
     <t>0.001</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>Smart Admission Backend — Authentication Tests BT-002 | Firebase config has authDomain</t>
-  </si>
-  <si>
-    <t>0.000</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — Authentication Tests BT-003 | Firebase config has projectId</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — Authentication Tests BT-004 | Firebase config has storageBucket</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — Authentication Tests BT-005 | Firebase config has messagingSenderId</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — Authentication Tests BT-006 | Firebase config has appId</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — Authentication Tests BT-007 | Firebase config projectId matches authDomain prefix</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — Authentication Tests BT-008 | Firebase config has all 6 required fields</t>
-  </si>
-  <si>
     <t>Smart Admission Backend — Authentication Tests BT-009 | Firebase config fields are non-empty strings</t>
   </si>
   <si>
@@ -584,885 +584,885 @@
     <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field apiKey (Verify Point #180)</t>
   </si>
   <si>
+    <t>0.060</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #181)</t>
+  </si>
+  <si>
+    <t>0.022</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #182)</t>
+  </si>
+  <si>
+    <t>0.074</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #183)</t>
+  </si>
+  <si>
+    <t>0.070</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #184)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #185)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #186)</t>
+  </si>
+  <si>
+    <t>0.104</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #187)</t>
+  </si>
+  <si>
+    <t>0.072</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #188)</t>
+  </si>
+  <si>
+    <t>0.102</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #189)</t>
+  </si>
+  <si>
+    <t>0.092</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #190)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #191)</t>
+  </si>
+  <si>
+    <t>0.082</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #192)</t>
+  </si>
+  <si>
+    <t>0.076</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #193)</t>
+  </si>
+  <si>
+    <t>0.068</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #194)</t>
+  </si>
+  <si>
+    <t>0.106</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #195)</t>
+  </si>
+  <si>
+    <t>0.118</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #196)</t>
+  </si>
+  <si>
+    <t>0.071</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #197)</t>
+  </si>
+  <si>
+    <t>0.093</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #198)</t>
+  </si>
+  <si>
+    <t>0.115</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #199)</t>
+  </si>
+  <si>
+    <t>0.105</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #200)</t>
+  </si>
+  <si>
+    <t>0.095</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #201)</t>
+  </si>
+  <si>
+    <t>0.054</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #202)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #203)</t>
+  </si>
+  <si>
+    <t>0.108</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #204)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #205)</t>
+  </si>
+  <si>
+    <t>0.036</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #206)</t>
+  </si>
+  <si>
+    <t>0.051</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #207)</t>
+  </si>
+  <si>
+    <t>0.065</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #208)</t>
+  </si>
+  <si>
     <t>0.087</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #181)</t>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #209)</t>
+  </si>
+  <si>
+    <t>0.038</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #210)</t>
+  </si>
+  <si>
+    <t>0.067</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #211)</t>
+  </si>
+  <si>
+    <t>0.061</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code XSS-injection (Verify Point #212)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #213)</t>
+  </si>
+  <si>
+    <t>0.062</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for CSRF-token (Verify Point #214)</t>
+  </si>
+  <si>
+    <t>0.040</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated CORS-origin (Verify Point #215)</t>
+  </si>
+  <si>
+    <t>0.097</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for CSP-header (Verify Point #216)</t>
+  </si>
+  <si>
+    <t>0.081</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at session-token (Verify Point #217)</t>
+  </si>
+  <si>
+    <t>0.025</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users-ref (Verify Point #218)</t>
+  </si>
+  <si>
+    <t>0.048</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for items-ref (Verify Point #219)</t>
+  </si>
+  <si>
+    <t>0.066</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field de-DE (Verify Point #220)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for fr-FR (Verify Point #221)</t>
+  </si>
+  <si>
+    <t>0.116</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ja-JP (Verify Point #222)</t>
+  </si>
+  <si>
+    <t>0.112</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for pt-BR (Verify Point #223)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of it-IT (Verify Point #224)</t>
+  </si>
+  <si>
+    <t>0.098</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for apiKey (Verify Point #225)</t>
   </si>
   <si>
     <t>0.063</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #182)</t>
-  </si>
-  <si>
-    <t>0.053</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #183)</t>
-  </si>
-  <si>
-    <t>0.036</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #184)</t>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for authDomain (Verify Point #226)</t>
+  </si>
+  <si>
+    <t>0.047</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value projectId (Verify Point #227)</t>
+  </si>
+  <si>
+    <t>0.088</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session storageBucket (Verify Point #228)</t>
+  </si>
+  <si>
+    <t>0.049</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier messagingSenderId (Verify Point #229)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region appId (Verify Point #230)</t>
+  </si>
+  <si>
+    <t>0.035</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for name (Verify Point #231)</t>
+  </si>
+  <si>
+    <t>0.058</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code id (Verify Point #232)</t>
+  </si>
+  <si>
+    <t>0.107</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource fees.min (Verify Point #233)</t>
+  </si>
+  <si>
+    <t>0.101</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for fees.max (Verify Point #234)</t>
+  </si>
+  <si>
+    <t>0.045</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated courses (Verify Point #235)</t>
+  </si>
+  <si>
+    <t>0.083</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for ranking.nirf (Verify Point #236)</t>
+  </si>
+  <si>
+    <t>0.039</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at type (Verify Point #237)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users/uid001 (Verify Point #238)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for colleges/c001 (Verify Point #239)</t>
+  </si>
+  <si>
+    <t>0.100</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field prompt-length (Verify Point #240)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for session-id-1 (Verify Point #241)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ₹1L (Verify Point #242)</t>
+  </si>
+  <si>
+    <t>0.055</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for B.Tech (Verify Point #243)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of 4 years (Verify Point #244)</t>
+  </si>
+  <si>
+    <t>0.113</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for Tamil Nadu (Verify Point #245)</t>
+  </si>
+  <si>
+    <t>0.034</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for Chennai (Verify Point #246)</t>
+  </si>
+  <si>
+    <t>0.020</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value llama3-8b (Verify Point #247)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session email (Verify Point #248)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier password (Verify Point #249)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region displayName (Verify Point #250)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for savedColleges (Verify Point #251)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code createdAt (Verify Point #252)</t>
+  </si>
+  <si>
+    <t>0.031</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource firebase-auth (Verify Point #253)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for firestore-read (Verify Point #254)</t>
+  </si>
+  <si>
+    <t>0.064</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated groq-api (Verify Point #255)</t>
+  </si>
+  <si>
+    <t>0.024</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for college-list (Verify Point #256)</t>
+  </si>
+  <si>
+    <t>0.032</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at XSS-injection (Verify Point #257)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation SQL-injection (Verify Point #258)</t>
+  </si>
+  <si>
+    <t>0.026</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for CSRF-token (Verify Point #259)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field CORS-origin (Verify Point #260)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for CSP-header (Verify Point #261)</t>
+  </si>
+  <si>
+    <t>0.027</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for session-token (Verify Point #262)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users-ref (Verify Point #263)</t>
+  </si>
+  <si>
+    <t>0.090</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of items-ref (Verify Point #264)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for de-DE (Verify Point #265)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for fr-FR (Verify Point #266)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ja-JP (Verify Point #267)</t>
+  </si>
+  <si>
+    <t>0.030</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session pt-BR (Verify Point #268)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier it-IT (Verify Point #269)</t>
+  </si>
+  <si>
+    <t>0.084</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region apiKey (Verify Point #270)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for authDomain (Verify Point #271)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code projectId (Verify Point #272)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource storageBucket (Verify Point #273)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for messagingSenderId (Verify Point #274)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated appId (Verify Point #275)</t>
+  </si>
+  <si>
+    <t>0.078</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for name (Verify Point #276)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at id (Verify Point #277)</t>
+  </si>
+  <si>
+    <t>0.059</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation fees.min (Verify Point #278)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for fees.max (Verify Point #279)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field courses (Verify Point #280)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for ranking.nirf (Verify Point #281)</t>
+  </si>
+  <si>
+    <t>0.050</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for type (Verify Point #282)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users/uid001 (Verify Point #283)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of colleges/c001 (Verify Point #284)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for prompt-length (Verify Point #285)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for session-id-1 (Verify Point #286)</t>
+  </si>
+  <si>
+    <t>0.094</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ₹1L (Verify Point #287)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session B.Tech (Verify Point #288)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier 4 years (Verify Point #289)</t>
+  </si>
+  <si>
+    <t>0.037</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region Tamil Nadu (Verify Point #290)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for Chennai (Verify Point #291)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code llama3-8b (Verify Point #292)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource email (Verify Point #293)</t>
   </si>
   <si>
     <t>0.110</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #185)</t>
-  </si>
-  <si>
-    <t>0.027</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #186)</t>
-  </si>
-  <si>
-    <t>0.082</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #187)</t>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for password (Verify Point #294)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated displayName (Verify Point #295)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for savedColleges (Verify Point #296)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at createdAt (Verify Point #297)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation firebase-auth (Verify Point #298)</t>
+  </si>
+  <si>
+    <t>0.077</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for firestore-read (Verify Point #299)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field groq-api (Verify Point #300)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for college-list (Verify Point #301)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for XSS-injection (Verify Point #302)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for SQL-injection (Verify Point #303)</t>
+  </si>
+  <si>
+    <t>0.096</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of CSRF-token (Verify Point #304)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for CORS-origin (Verify Point #305)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for CSP-header (Verify Point #306)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value session-token (Verify Point #307)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users-ref (Verify Point #308)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier items-ref (Verify Point #309)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region de-DE (Verify Point #310)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for fr-FR (Verify Point #311)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ja-JP (Verify Point #312)</t>
+  </si>
+  <si>
+    <t>0.042</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource pt-BR (Verify Point #313)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for it-IT (Verify Point #314)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated apiKey (Verify Point #315)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for authDomain (Verify Point #316)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at projectId (Verify Point #317)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation storageBucket (Verify Point #318)</t>
+  </si>
+  <si>
+    <t>0.057</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for messagingSenderId (Verify Point #319)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field appId (Verify Point #320)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for name (Verify Point #321)</t>
+  </si>
+  <si>
+    <t>0.103</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for id (Verify Point #322)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for fees.min (Verify Point #323)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of fees.max (Verify Point #324)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for courses (Verify Point #325)</t>
+  </si>
+  <si>
+    <t>0.041</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for ranking.nirf (Verify Point #326)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value type (Verify Point #327)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users/uid001 (Verify Point #328)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier colleges/c001 (Verify Point #329)</t>
+  </si>
+  <si>
+    <t>0.085</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region prompt-length (Verify Point #330)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for session-id-1 (Verify Point #331)</t>
+  </si>
+  <si>
+    <t>0.044</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ₹1L (Verify Point #332)</t>
+  </si>
+  <si>
+    <t>0.029</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource B.Tech (Verify Point #333)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for 4 years (Verify Point #334)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated Tamil Nadu (Verify Point #335)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for Chennai (Verify Point #336)</t>
+  </si>
+  <si>
+    <t>0.111</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at llama3-8b (Verify Point #337)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation email (Verify Point #338)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for password (Verify Point #339)</t>
+  </si>
+  <si>
+    <t>0.089</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field displayName (Verify Point #340)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for savedColleges (Verify Point #341)</t>
+  </si>
+  <si>
+    <t>0.079</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for createdAt (Verify Point #342)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for firebase-auth (Verify Point #343)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of firestore-read (Verify Point #344)</t>
+  </si>
+  <si>
+    <t>0.033</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for groq-api (Verify Point #345)</t>
   </si>
   <si>
     <t>0.023</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #188)</t>
-  </si>
-  <si>
-    <t>0.068</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #189)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #190)</t>
-  </si>
-  <si>
-    <t>0.073</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #191)</t>
-  </si>
-  <si>
-    <t>0.055</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #192)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #193)</t>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for college-list (Verify Point #346)</t>
+  </si>
+  <si>
+    <t>0.109</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value XSS-injection (Verify Point #347)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session SQL-injection (Verify Point #348)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier CSRF-token (Verify Point #349)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region CORS-origin (Verify Point #350)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for CSP-header (Verify Point #351)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code session-token (Verify Point #352)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users-ref (Verify Point #353)</t>
   </si>
   <si>
     <t>0.028</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #194)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #195)</t>
-  </si>
-  <si>
-    <t>0.104</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #196)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #197)</t>
-  </si>
-  <si>
-    <t>0.106</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #198)</t>
-  </si>
-  <si>
-    <t>0.117</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #199)</t>
-  </si>
-  <si>
-    <t>0.033</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #200)</t>
-  </si>
-  <si>
-    <t>0.080</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #201)</t>
-  </si>
-  <si>
-    <t>0.062</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #202)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #203)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #204)</t>
-  </si>
-  <si>
-    <t>0.051</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #205)</t>
-  </si>
-  <si>
-    <t>0.097</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #206)</t>
-  </si>
-  <si>
-    <t>0.101</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #207)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #208)</t>
-  </si>
-  <si>
-    <t>0.024</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #209)</t>
-  </si>
-  <si>
-    <t>0.041</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #210)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #211)</t>
-  </si>
-  <si>
-    <t>0.070</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code XSS-injection (Verify Point #212)</t>
-  </si>
-  <si>
-    <t>0.084</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #213)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for CSRF-token (Verify Point #214)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated CORS-origin (Verify Point #215)</t>
-  </si>
-  <si>
-    <t>0.096</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for CSP-header (Verify Point #216)</t>
-  </si>
-  <si>
-    <t>0.071</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at session-token (Verify Point #217)</t>
-  </si>
-  <si>
-    <t>0.100</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users-ref (Verify Point #218)</t>
-  </si>
-  <si>
-    <t>0.074</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for items-ref (Verify Point #219)</t>
-  </si>
-  <si>
-    <t>0.056</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field de-DE (Verify Point #220)</t>
-  </si>
-  <si>
-    <t>0.118</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for fr-FR (Verify Point #221)</t>
-  </si>
-  <si>
-    <t>0.112</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ja-JP (Verify Point #222)</t>
-  </si>
-  <si>
-    <t>0.064</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for pt-BR (Verify Point #223)</t>
-  </si>
-  <si>
-    <t>0.061</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of it-IT (Verify Point #224)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for apiKey (Verify Point #225)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for authDomain (Verify Point #226)</t>
-  </si>
-  <si>
-    <t>0.079</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value projectId (Verify Point #227)</t>
-  </si>
-  <si>
-    <t>0.052</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session storageBucket (Verify Point #228)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier messagingSenderId (Verify Point #229)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region appId (Verify Point #230)</t>
-  </si>
-  <si>
-    <t>0.034</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for name (Verify Point #231)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code id (Verify Point #232)</t>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for items-ref (Verify Point #354)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated de-DE (Verify Point #355)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for fr-FR (Verify Point #356)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ja-JP (Verify Point #357)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation pt-BR (Verify Point #358)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for it-IT (Verify Point #359)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field apiKey (Verify Point #360)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #361)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #362)</t>
   </si>
   <si>
     <t>0.069</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource fees.min (Verify Point #233)</t>
-  </si>
-  <si>
-    <t>0.021</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for fees.max (Verify Point #234)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated courses (Verify Point #235)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for ranking.nirf (Verify Point #236)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at type (Verify Point #237)</t>
-  </si>
-  <si>
-    <t>0.057</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users/uid001 (Verify Point #238)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for colleges/c001 (Verify Point #239)</t>
-  </si>
-  <si>
-    <t>0.026</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field prompt-length (Verify Point #240)</t>
-  </si>
-  <si>
-    <t>0.043</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for session-id-1 (Verify Point #241)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ₹1L (Verify Point #242)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for B.Tech (Verify Point #243)</t>
-  </si>
-  <si>
-    <t>0.065</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of 4 years (Verify Point #244)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for Tamil Nadu (Verify Point #245)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for Chennai (Verify Point #246)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value llama3-8b (Verify Point #247)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session email (Verify Point #248)</t>
-  </si>
-  <si>
-    <t>0.020</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier password (Verify Point #249)</t>
-  </si>
-  <si>
-    <t>0.046</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region displayName (Verify Point #250)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for savedColleges (Verify Point #251)</t>
-  </si>
-  <si>
-    <t>0.086</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code createdAt (Verify Point #252)</t>
-  </si>
-  <si>
-    <t>0.093</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource firebase-auth (Verify Point #253)</t>
-  </si>
-  <si>
-    <t>0.119</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for firestore-read (Verify Point #254)</t>
-  </si>
-  <si>
-    <t>0.031</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated groq-api (Verify Point #255)</t>
-  </si>
-  <si>
-    <t>0.029</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for college-list (Verify Point #256)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at XSS-injection (Verify Point #257)</t>
-  </si>
-  <si>
-    <t>0.058</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation SQL-injection (Verify Point #258)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for CSRF-token (Verify Point #259)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field CORS-origin (Verify Point #260)</t>
-  </si>
-  <si>
-    <t>0.113</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for CSP-header (Verify Point #261)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for session-token (Verify Point #262)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users-ref (Verify Point #263)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of items-ref (Verify Point #264)</t>
-  </si>
-  <si>
-    <t>0.072</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for de-DE (Verify Point #265)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for fr-FR (Verify Point #266)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ja-JP (Verify Point #267)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session pt-BR (Verify Point #268)</t>
-  </si>
-  <si>
-    <t>0.116</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier it-IT (Verify Point #269)</t>
-  </si>
-  <si>
-    <t>0.030</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region apiKey (Verify Point #270)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for authDomain (Verify Point #271)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code projectId (Verify Point #272)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource storageBucket (Verify Point #273)</t>
-  </si>
-  <si>
-    <t>0.102</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for messagingSenderId (Verify Point #274)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated appId (Verify Point #275)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for name (Verify Point #276)</t>
-  </si>
-  <si>
-    <t>0.067</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at id (Verify Point #277)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation fees.min (Verify Point #278)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for fees.max (Verify Point #279)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field courses (Verify Point #280)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for ranking.nirf (Verify Point #281)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for type (Verify Point #282)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users/uid001 (Verify Point #283)</t>
-  </si>
-  <si>
-    <t>0.040</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of colleges/c001 (Verify Point #284)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for prompt-length (Verify Point #285)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for session-id-1 (Verify Point #286)</t>
-  </si>
-  <si>
-    <t>0.050</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ₹1L (Verify Point #287)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session B.Tech (Verify Point #288)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier 4 years (Verify Point #289)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region Tamil Nadu (Verify Point #290)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for Chennai (Verify Point #291)</t>
-  </si>
-  <si>
-    <t>0.035</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code llama3-8b (Verify Point #292)</t>
-  </si>
-  <si>
-    <t>0.059</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource email (Verify Point #293)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for password (Verify Point #294)</t>
-  </si>
-  <si>
-    <t>0.054</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated displayName (Verify Point #295)</t>
-  </si>
-  <si>
-    <t>0.094</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for savedColleges (Verify Point #296)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at createdAt (Verify Point #297)</t>
-  </si>
-  <si>
-    <t>0.076</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation firebase-auth (Verify Point #298)</t>
-  </si>
-  <si>
-    <t>0.032</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for firestore-read (Verify Point #299)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field groq-api (Verify Point #300)</t>
-  </si>
-  <si>
-    <t>0.081</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for college-list (Verify Point #301)</t>
-  </si>
-  <si>
-    <t>0.089</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for XSS-injection (Verify Point #302)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for SQL-injection (Verify Point #303)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of CSRF-token (Verify Point #304)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for CORS-origin (Verify Point #305)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for CSP-header (Verify Point #306)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value session-token (Verify Point #307)</t>
-  </si>
-  <si>
-    <t>0.039</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users-ref (Verify Point #308)</t>
-  </si>
-  <si>
-    <t>0.111</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier items-ref (Verify Point #309)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region de-DE (Verify Point #310)</t>
-  </si>
-  <si>
-    <t>0.092</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for fr-FR (Verify Point #311)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ja-JP (Verify Point #312)</t>
-  </si>
-  <si>
-    <t>0.025</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource pt-BR (Verify Point #313)</t>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #363)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #364)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #365)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #366)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #367)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #368)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #369)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #370)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #371)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #372)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #373)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #374)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #375)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #376)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #377)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #378)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #379)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #380)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #381)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #382)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #383)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #384)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #385)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #386)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #387)</t>
   </si>
   <si>
     <t>0.091</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for it-IT (Verify Point #314)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated apiKey (Verify Point #315)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for authDomain (Verify Point #316)</t>
-  </si>
-  <si>
-    <t>0.077</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at projectId (Verify Point #317)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation storageBucket (Verify Point #318)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for messagingSenderId (Verify Point #319)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field appId (Verify Point #320)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for name (Verify Point #321)</t>
-  </si>
-  <si>
-    <t>0.099</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for id (Verify Point #322)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for fees.min (Verify Point #323)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of fees.max (Verify Point #324)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for courses (Verify Point #325)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for ranking.nirf (Verify Point #326)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value type (Verify Point #327)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users/uid001 (Verify Point #328)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier colleges/c001 (Verify Point #329)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region prompt-length (Verify Point #330)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for session-id-1 (Verify Point #331)</t>
-  </si>
-  <si>
-    <t>0.045</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ₹1L (Verify Point #332)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource B.Tech (Verify Point #333)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for 4 years (Verify Point #334)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated Tamil Nadu (Verify Point #335)</t>
-  </si>
-  <si>
-    <t>0.108</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for Chennai (Verify Point #336)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at llama3-8b (Verify Point #337)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation email (Verify Point #338)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for password (Verify Point #339)</t>
-  </si>
-  <si>
-    <t>0.103</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field displayName (Verify Point #340)</t>
-  </si>
-  <si>
-    <t>0.088</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for savedColleges (Verify Point #341)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for createdAt (Verify Point #342)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for firebase-auth (Verify Point #343)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of firestore-read (Verify Point #344)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for groq-api (Verify Point #345)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for college-list (Verify Point #346)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value XSS-injection (Verify Point #347)</t>
-  </si>
-  <si>
-    <t>0.066</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session SQL-injection (Verify Point #348)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier CSRF-token (Verify Point #349)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region CORS-origin (Verify Point #350)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for CSP-header (Verify Point #351)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code session-token (Verify Point #352)</t>
-  </si>
-  <si>
-    <t>0.095</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users-ref (Verify Point #353)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for items-ref (Verify Point #354)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated de-DE (Verify Point #355)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for fr-FR (Verify Point #356)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ja-JP (Verify Point #357)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation pt-BR (Verify Point #358)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for it-IT (Verify Point #359)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field apiKey (Verify Point #360)</t>
-  </si>
-  <si>
-    <t>0.022</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #361)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #362)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #363)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #364)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #365)</t>
-  </si>
-  <si>
-    <t>0.109</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #366)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #367)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #368)</t>
-  </si>
-  <si>
-    <t>0.037</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #369)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #370)</t>
-  </si>
-  <si>
-    <t>0.098</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #371)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #372)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #373)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #374)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #375)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #376)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #377)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #378)</t>
-  </si>
-  <si>
-    <t>0.114</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #379)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #380)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #381)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #382)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #383)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #384)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #385)</t>
-  </si>
-  <si>
-    <t>0.049</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #386)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #387)</t>
-  </si>
-  <si>
     <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #388)</t>
   </si>
   <si>
@@ -1472,9 +1472,6 @@
     <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #390)</t>
   </si>
   <si>
-    <t>0.048</t>
-  </si>
-  <si>
     <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #391)</t>
   </si>
   <si>
@@ -1496,6 +1493,9 @@
     <t>Smart Admission — Backend [Boundary]: Verify boundary condition at session-token (Verify Point #397)</t>
   </si>
   <si>
+    <t>0.075</t>
+  </si>
+  <si>
     <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users-ref (Verify Point #398)</t>
   </si>
   <si>
@@ -1511,13 +1511,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>23</t>
+    <t>24</t>
   </si>
   <si>
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 15:39:53 UTC</t>
+    <t>2026-06-24 03:32:51 UTC</t>
   </si>
   <si>
     <t>Branch</t>
@@ -1984,7 +1984,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1995,13 +1995,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -2012,13 +2012,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -2029,7 +2029,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>6</v>
@@ -2046,13 +2046,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -2063,13 +2063,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -2080,13 +2080,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" t="s">
         <v>16</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" t="s">
-        <v>10</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -2103,7 +2103,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -2120,7 +2120,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>6</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -2171,7 +2171,7 @@
         <v>6</v>
       </c>
       <c r="D14" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -2188,7 +2188,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -2205,7 +2205,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -2222,7 +2222,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -2239,7 +2239,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -2256,7 +2256,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -2273,7 +2273,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -2307,7 +2307,7 @@
         <v>6</v>
       </c>
       <c r="D22" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -2324,7 +2324,7 @@
         <v>6</v>
       </c>
       <c r="D23" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -2341,7 +2341,7 @@
         <v>6</v>
       </c>
       <c r="D24" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -2358,7 +2358,7 @@
         <v>6</v>
       </c>
       <c r="D25" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -2375,7 +2375,7 @@
         <v>6</v>
       </c>
       <c r="D26" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -2392,7 +2392,7 @@
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -2409,7 +2409,7 @@
         <v>6</v>
       </c>
       <c r="D28" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -2426,7 +2426,7 @@
         <v>6</v>
       </c>
       <c r="D29" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -2460,7 +2460,7 @@
         <v>6</v>
       </c>
       <c r="D31" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -2477,7 +2477,7 @@
         <v>6</v>
       </c>
       <c r="D32" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -2494,7 +2494,7 @@
         <v>6</v>
       </c>
       <c r="D33" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -2511,7 +2511,7 @@
         <v>6</v>
       </c>
       <c r="D34" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -2528,7 +2528,7 @@
         <v>6</v>
       </c>
       <c r="D35" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -2545,7 +2545,7 @@
         <v>6</v>
       </c>
       <c r="D36" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="D37" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>6</v>
       </c>
       <c r="D38" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -2613,7 +2613,7 @@
         <v>6</v>
       </c>
       <c r="D40" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -2630,7 +2630,7 @@
         <v>6</v>
       </c>
       <c r="D41" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -2647,7 +2647,7 @@
         <v>6</v>
       </c>
       <c r="D42" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -2664,7 +2664,7 @@
         <v>6</v>
       </c>
       <c r="D43" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -2681,7 +2681,7 @@
         <v>6</v>
       </c>
       <c r="D44" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -2698,7 +2698,7 @@
         <v>6</v>
       </c>
       <c r="D45" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -2715,7 +2715,7 @@
         <v>6</v>
       </c>
       <c r="D46" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -2732,7 +2732,7 @@
         <v>6</v>
       </c>
       <c r="D47" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -2749,7 +2749,7 @@
         <v>6</v>
       </c>
       <c r="D48" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -2766,7 +2766,7 @@
         <v>6</v>
       </c>
       <c r="D49" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -2800,7 +2800,7 @@
         <v>6</v>
       </c>
       <c r="D51" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -2817,7 +2817,7 @@
         <v>6</v>
       </c>
       <c r="D52" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -2834,7 +2834,7 @@
         <v>6</v>
       </c>
       <c r="D53" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -2851,7 +2851,7 @@
         <v>6</v>
       </c>
       <c r="D54" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -2868,7 +2868,7 @@
         <v>6</v>
       </c>
       <c r="D55" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
@@ -2885,7 +2885,7 @@
         <v>6</v>
       </c>
       <c r="D56" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -2902,7 +2902,7 @@
         <v>6</v>
       </c>
       <c r="D57" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -2919,7 +2919,7 @@
         <v>6</v>
       </c>
       <c r="D58" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -2936,7 +2936,7 @@
         <v>6</v>
       </c>
       <c r="D59" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
@@ -2953,7 +2953,7 @@
         <v>6</v>
       </c>
       <c r="D60" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
@@ -2970,7 +2970,7 @@
         <v>6</v>
       </c>
       <c r="D61" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
@@ -2987,7 +2987,7 @@
         <v>6</v>
       </c>
       <c r="D62" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
@@ -3004,7 +3004,7 @@
         <v>6</v>
       </c>
       <c r="D63" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>6</v>
       </c>
       <c r="D64" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E64" t="s">
         <v>8</v>
@@ -3038,7 +3038,7 @@
         <v>6</v>
       </c>
       <c r="D65" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E65" t="s">
         <v>8</v>
@@ -3055,7 +3055,7 @@
         <v>6</v>
       </c>
       <c r="D66" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
@@ -3072,7 +3072,7 @@
         <v>6</v>
       </c>
       <c r="D67" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
@@ -3089,7 +3089,7 @@
         <v>6</v>
       </c>
       <c r="D68" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
@@ -3106,7 +3106,7 @@
         <v>6</v>
       </c>
       <c r="D69" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E69" t="s">
         <v>8</v>
@@ -3123,7 +3123,7 @@
         <v>6</v>
       </c>
       <c r="D70" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
@@ -3140,7 +3140,7 @@
         <v>6</v>
       </c>
       <c r="D71" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
@@ -3157,7 +3157,7 @@
         <v>6</v>
       </c>
       <c r="D72" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
@@ -3174,7 +3174,7 @@
         <v>6</v>
       </c>
       <c r="D73" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E73" t="s">
         <v>8</v>
@@ -3191,7 +3191,7 @@
         <v>6</v>
       </c>
       <c r="D74" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E74" t="s">
         <v>8</v>
@@ -3208,7 +3208,7 @@
         <v>6</v>
       </c>
       <c r="D75" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
@@ -3225,7 +3225,7 @@
         <v>6</v>
       </c>
       <c r="D76" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E76" t="s">
         <v>8</v>
@@ -3242,7 +3242,7 @@
         <v>6</v>
       </c>
       <c r="D77" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
@@ -3259,7 +3259,7 @@
         <v>6</v>
       </c>
       <c r="D78" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
@@ -3276,7 +3276,7 @@
         <v>6</v>
       </c>
       <c r="D79" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E79" t="s">
         <v>8</v>
@@ -3293,7 +3293,7 @@
         <v>6</v>
       </c>
       <c r="D80" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E80" t="s">
         <v>8</v>
@@ -3310,7 +3310,7 @@
         <v>6</v>
       </c>
       <c r="D81" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
@@ -3344,7 +3344,7 @@
         <v>6</v>
       </c>
       <c r="D83" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E83" t="s">
         <v>8</v>
@@ -3361,7 +3361,7 @@
         <v>6</v>
       </c>
       <c r="D84" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
@@ -3378,7 +3378,7 @@
         <v>6</v>
       </c>
       <c r="D85" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
@@ -3395,7 +3395,7 @@
         <v>6</v>
       </c>
       <c r="D86" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
@@ -3412,7 +3412,7 @@
         <v>6</v>
       </c>
       <c r="D87" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E87" t="s">
         <v>8</v>
@@ -3429,7 +3429,7 @@
         <v>6</v>
       </c>
       <c r="D88" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E88" t="s">
         <v>8</v>
@@ -3446,7 +3446,7 @@
         <v>6</v>
       </c>
       <c r="D89" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>6</v>
       </c>
       <c r="D90" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E90" t="s">
         <v>8</v>
@@ -3480,7 +3480,7 @@
         <v>6</v>
       </c>
       <c r="D91" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E91" t="s">
         <v>8</v>
@@ -3514,7 +3514,7 @@
         <v>6</v>
       </c>
       <c r="D93" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E93" t="s">
         <v>8</v>
@@ -3531,7 +3531,7 @@
         <v>6</v>
       </c>
       <c r="D94" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E94" t="s">
         <v>8</v>
@@ -3548,7 +3548,7 @@
         <v>6</v>
       </c>
       <c r="D95" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E95" t="s">
         <v>8</v>
@@ -3565,7 +3565,7 @@
         <v>6</v>
       </c>
       <c r="D96" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E96" t="s">
         <v>8</v>
@@ -3582,7 +3582,7 @@
         <v>6</v>
       </c>
       <c r="D97" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E97" t="s">
         <v>8</v>
@@ -3616,7 +3616,7 @@
         <v>6</v>
       </c>
       <c r="D99" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
@@ -3633,7 +3633,7 @@
         <v>6</v>
       </c>
       <c r="D100" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E100" t="s">
         <v>8</v>
@@ -3650,7 +3650,7 @@
         <v>6</v>
       </c>
       <c r="D101" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E101" t="s">
         <v>8</v>
@@ -3667,7 +3667,7 @@
         <v>6</v>
       </c>
       <c r="D102" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E102" t="s">
         <v>8</v>
@@ -3684,7 +3684,7 @@
         <v>6</v>
       </c>
       <c r="D103" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E103" t="s">
         <v>8</v>
@@ -3701,7 +3701,7 @@
         <v>6</v>
       </c>
       <c r="D104" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E104" t="s">
         <v>8</v>
@@ -3735,7 +3735,7 @@
         <v>6</v>
       </c>
       <c r="D106" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E106" t="s">
         <v>8</v>
@@ -3752,7 +3752,7 @@
         <v>6</v>
       </c>
       <c r="D107" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
@@ -3769,7 +3769,7 @@
         <v>6</v>
       </c>
       <c r="D108" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E108" t="s">
         <v>8</v>
@@ -3786,7 +3786,7 @@
         <v>6</v>
       </c>
       <c r="D109" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E109" t="s">
         <v>8</v>
@@ -3803,7 +3803,7 @@
         <v>6</v>
       </c>
       <c r="D110" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E110" t="s">
         <v>8</v>
@@ -3820,7 +3820,7 @@
         <v>6</v>
       </c>
       <c r="D111" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E111" t="s">
         <v>8</v>
@@ -3837,7 +3837,7 @@
         <v>6</v>
       </c>
       <c r="D112" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E112" t="s">
         <v>8</v>
@@ -3854,7 +3854,7 @@
         <v>6</v>
       </c>
       <c r="D113" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E113" t="s">
         <v>8</v>
@@ -3871,7 +3871,7 @@
         <v>6</v>
       </c>
       <c r="D114" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E114" t="s">
         <v>8</v>
@@ -3888,7 +3888,7 @@
         <v>6</v>
       </c>
       <c r="D115" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E115" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>6</v>
       </c>
       <c r="D116" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E116" t="s">
         <v>8</v>
@@ -3922,7 +3922,7 @@
         <v>6</v>
       </c>
       <c r="D117" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E117" t="s">
         <v>8</v>
@@ -3939,7 +3939,7 @@
         <v>6</v>
       </c>
       <c r="D118" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E118" t="s">
         <v>8</v>
@@ -3956,7 +3956,7 @@
         <v>6</v>
       </c>
       <c r="D119" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E119" t="s">
         <v>8</v>
@@ -3990,7 +3990,7 @@
         <v>6</v>
       </c>
       <c r="D121" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E121" t="s">
         <v>8</v>
@@ -4007,7 +4007,7 @@
         <v>6</v>
       </c>
       <c r="D122" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E122" t="s">
         <v>8</v>
@@ -4024,7 +4024,7 @@
         <v>6</v>
       </c>
       <c r="D123" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E123" t="s">
         <v>8</v>
@@ -4041,7 +4041,7 @@
         <v>6</v>
       </c>
       <c r="D124" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E124" t="s">
         <v>8</v>
@@ -4058,7 +4058,7 @@
         <v>6</v>
       </c>
       <c r="D125" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E125" t="s">
         <v>8</v>
@@ -4075,7 +4075,7 @@
         <v>6</v>
       </c>
       <c r="D126" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E126" t="s">
         <v>8</v>
@@ -4092,7 +4092,7 @@
         <v>6</v>
       </c>
       <c r="D127" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E127" t="s">
         <v>8</v>
@@ -4109,7 +4109,7 @@
         <v>6</v>
       </c>
       <c r="D128" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E128" t="s">
         <v>8</v>
@@ -4126,7 +4126,7 @@
         <v>6</v>
       </c>
       <c r="D129" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E129" t="s">
         <v>8</v>
@@ -4143,7 +4143,7 @@
         <v>6</v>
       </c>
       <c r="D130" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E130" t="s">
         <v>8</v>
@@ -4160,7 +4160,7 @@
         <v>6</v>
       </c>
       <c r="D131" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E131" t="s">
         <v>8</v>
@@ -4177,7 +4177,7 @@
         <v>6</v>
       </c>
       <c r="D132" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E132" t="s">
         <v>8</v>
@@ -4194,7 +4194,7 @@
         <v>6</v>
       </c>
       <c r="D133" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E133" t="s">
         <v>8</v>
@@ -4211,7 +4211,7 @@
         <v>6</v>
       </c>
       <c r="D134" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E134" t="s">
         <v>8</v>
@@ -4228,7 +4228,7 @@
         <v>6</v>
       </c>
       <c r="D135" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E135" t="s">
         <v>8</v>
@@ -4245,7 +4245,7 @@
         <v>6</v>
       </c>
       <c r="D136" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E136" t="s">
         <v>8</v>
@@ -4279,7 +4279,7 @@
         <v>6</v>
       </c>
       <c r="D138" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E138" t="s">
         <v>8</v>
@@ -4296,7 +4296,7 @@
         <v>6</v>
       </c>
       <c r="D139" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E139" t="s">
         <v>8</v>
@@ -4313,7 +4313,7 @@
         <v>6</v>
       </c>
       <c r="D140" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E140" t="s">
         <v>8</v>
@@ -4330,7 +4330,7 @@
         <v>6</v>
       </c>
       <c r="D141" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E141" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>6</v>
       </c>
       <c r="D142" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E142" t="s">
         <v>8</v>
@@ -4364,7 +4364,7 @@
         <v>6</v>
       </c>
       <c r="D143" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E143" t="s">
         <v>8</v>
@@ -4381,7 +4381,7 @@
         <v>6</v>
       </c>
       <c r="D144" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E144" t="s">
         <v>8</v>
@@ -4398,7 +4398,7 @@
         <v>6</v>
       </c>
       <c r="D145" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E145" t="s">
         <v>8</v>
@@ -4415,7 +4415,7 @@
         <v>6</v>
       </c>
       <c r="D146" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E146" t="s">
         <v>8</v>
@@ -4432,7 +4432,7 @@
         <v>6</v>
       </c>
       <c r="D147" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E147" t="s">
         <v>8</v>
@@ -4449,7 +4449,7 @@
         <v>6</v>
       </c>
       <c r="D148" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E148" t="s">
         <v>8</v>
@@ -4466,7 +4466,7 @@
         <v>6</v>
       </c>
       <c r="D149" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E149" t="s">
         <v>8</v>
@@ -4483,7 +4483,7 @@
         <v>6</v>
       </c>
       <c r="D150" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E150" t="s">
         <v>8</v>
@@ -4500,7 +4500,7 @@
         <v>6</v>
       </c>
       <c r="D151" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E151" t="s">
         <v>8</v>
@@ -4517,7 +4517,7 @@
         <v>6</v>
       </c>
       <c r="D152" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E152" t="s">
         <v>8</v>
@@ -4534,7 +4534,7 @@
         <v>6</v>
       </c>
       <c r="D153" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E153" t="s">
         <v>8</v>
@@ -4551,7 +4551,7 @@
         <v>6</v>
       </c>
       <c r="D154" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E154" t="s">
         <v>8</v>
@@ -4568,7 +4568,7 @@
         <v>6</v>
       </c>
       <c r="D155" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E155" t="s">
         <v>8</v>
@@ -4585,7 +4585,7 @@
         <v>6</v>
       </c>
       <c r="D156" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E156" t="s">
         <v>8</v>
@@ -4602,7 +4602,7 @@
         <v>6</v>
       </c>
       <c r="D157" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E157" t="s">
         <v>8</v>
@@ -4619,7 +4619,7 @@
         <v>6</v>
       </c>
       <c r="D158" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E158" t="s">
         <v>8</v>
@@ -4636,7 +4636,7 @@
         <v>6</v>
       </c>
       <c r="D159" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E159" t="s">
         <v>8</v>
@@ -4653,7 +4653,7 @@
         <v>6</v>
       </c>
       <c r="D160" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E160" t="s">
         <v>8</v>
@@ -4670,7 +4670,7 @@
         <v>6</v>
       </c>
       <c r="D161" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E161" t="s">
         <v>8</v>
@@ -4687,7 +4687,7 @@
         <v>6</v>
       </c>
       <c r="D162" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E162" t="s">
         <v>8</v>
@@ -4704,7 +4704,7 @@
         <v>6</v>
       </c>
       <c r="D163" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E163" t="s">
         <v>8</v>
@@ -4721,7 +4721,7 @@
         <v>6</v>
       </c>
       <c r="D164" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E164" t="s">
         <v>8</v>
@@ -4738,7 +4738,7 @@
         <v>6</v>
       </c>
       <c r="D165" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E165" t="s">
         <v>8</v>
@@ -4755,7 +4755,7 @@
         <v>6</v>
       </c>
       <c r="D166" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E166" t="s">
         <v>8</v>
@@ -4772,7 +4772,7 @@
         <v>6</v>
       </c>
       <c r="D167" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E167" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>6</v>
       </c>
       <c r="D168" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E168" t="s">
         <v>8</v>
@@ -4806,7 +4806,7 @@
         <v>6</v>
       </c>
       <c r="D169" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E169" t="s">
         <v>8</v>
@@ -4823,7 +4823,7 @@
         <v>6</v>
       </c>
       <c r="D170" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E170" t="s">
         <v>8</v>
@@ -4840,7 +4840,7 @@
         <v>6</v>
       </c>
       <c r="D171" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E171" t="s">
         <v>8</v>
@@ -4857,7 +4857,7 @@
         <v>6</v>
       </c>
       <c r="D172" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E172" t="s">
         <v>8</v>
@@ -4874,7 +4874,7 @@
         <v>6</v>
       </c>
       <c r="D173" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E173" t="s">
         <v>8</v>
@@ -4891,7 +4891,7 @@
         <v>6</v>
       </c>
       <c r="D174" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E174" t="s">
         <v>8</v>
@@ -4908,7 +4908,7 @@
         <v>6</v>
       </c>
       <c r="D175" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E175" t="s">
         <v>8</v>
@@ -4925,7 +4925,7 @@
         <v>6</v>
       </c>
       <c r="D176" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E176" t="s">
         <v>8</v>
@@ -4942,7 +4942,7 @@
         <v>6</v>
       </c>
       <c r="D177" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E177" t="s">
         <v>8</v>
@@ -4959,7 +4959,7 @@
         <v>6</v>
       </c>
       <c r="D178" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E178" t="s">
         <v>8</v>
@@ -4976,7 +4976,7 @@
         <v>6</v>
       </c>
       <c r="D179" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E179" t="s">
         <v>8</v>
@@ -4993,7 +4993,7 @@
         <v>6</v>
       </c>
       <c r="D180" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E180" t="s">
         <v>8</v>
@@ -5010,7 +5010,7 @@
         <v>6</v>
       </c>
       <c r="D181" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E181" t="s">
         <v>8</v>
@@ -5095,7 +5095,7 @@
         <v>6</v>
       </c>
       <c r="D186" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="E186" t="s">
         <v>8</v>
@@ -5106,13 +5106,13 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D187" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="E187" t="s">
         <v>8</v>
@@ -5123,13 +5123,13 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D188" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E188" t="s">
         <v>8</v>
@@ -5140,13 +5140,13 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D189" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E189" t="s">
         <v>8</v>
@@ -5157,13 +5157,13 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D190" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E190" t="s">
         <v>8</v>
@@ -5174,13 +5174,13 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D191" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E191" t="s">
         <v>8</v>
@@ -5191,13 +5191,13 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D192" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="E192" t="s">
         <v>8</v>
@@ -5208,13 +5208,13 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D193" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E193" t="s">
         <v>8</v>
@@ -5225,7 +5225,7 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>6</v>
@@ -5242,13 +5242,13 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
+        <v>212</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D195" t="s">
         <v>213</v>
-      </c>
-      <c r="C195" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D195" t="s">
-        <v>214</v>
       </c>
       <c r="E195" t="s">
         <v>8</v>
@@ -5259,13 +5259,13 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
+        <v>214</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D196" t="s">
         <v>215</v>
-      </c>
-      <c r="C196" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D196" t="s">
-        <v>202</v>
       </c>
       <c r="E196" t="s">
         <v>8</v>
@@ -5299,7 +5299,7 @@
         <v>6</v>
       </c>
       <c r="D198" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="E198" t="s">
         <v>8</v>
@@ -5310,13 +5310,13 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D199" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E199" t="s">
         <v>8</v>
@@ -5327,13 +5327,13 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D200" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E200" t="s">
         <v>8</v>
@@ -5344,13 +5344,13 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D201" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E201" t="s">
         <v>8</v>
@@ -5361,13 +5361,13 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D202" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E202" t="s">
         <v>8</v>
@@ -5378,13 +5378,13 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D203" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E203" t="s">
         <v>8</v>
@@ -5395,13 +5395,13 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D204" t="s">
-        <v>220</v>
+        <v>192</v>
       </c>
       <c r="E204" t="s">
         <v>8</v>
@@ -5412,13 +5412,13 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D205" t="s">
-        <v>194</v>
+        <v>232</v>
       </c>
       <c r="E205" t="s">
         <v>8</v>
@@ -5429,13 +5429,13 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D206" t="s">
-        <v>232</v>
+        <v>194</v>
       </c>
       <c r="E206" t="s">
         <v>8</v>
@@ -5446,13 +5446,13 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D207" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E207" t="s">
         <v>8</v>
@@ -5463,13 +5463,13 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D208" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E208" t="s">
         <v>8</v>
@@ -5480,13 +5480,13 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D209" t="s">
-        <v>190</v>
+        <v>239</v>
       </c>
       <c r="E209" t="s">
         <v>8</v>
@@ -5497,13 +5497,13 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D210" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E210" t="s">
         <v>8</v>
@@ -5514,13 +5514,13 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D211" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E211" t="s">
         <v>8</v>
@@ -5531,13 +5531,13 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D212" t="s">
-        <v>206</v>
+        <v>245</v>
       </c>
       <c r="E212" t="s">
         <v>8</v>
@@ -5548,13 +5548,13 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D213" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E213" t="s">
         <v>8</v>
@@ -5565,13 +5565,13 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D214" t="s">
-        <v>246</v>
+        <v>225</v>
       </c>
       <c r="E214" t="s">
         <v>8</v>
@@ -5582,13 +5582,13 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D215" t="s">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="E215" t="s">
         <v>8</v>
@@ -5599,13 +5599,13 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D216" t="s">
-        <v>192</v>
+        <v>252</v>
       </c>
       <c r="E216" t="s">
         <v>8</v>
@@ -5616,13 +5616,13 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D217" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E217" t="s">
         <v>8</v>
@@ -5633,13 +5633,13 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D218" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E218" t="s">
         <v>8</v>
@@ -5650,13 +5650,13 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D219" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E219" t="s">
         <v>8</v>
@@ -5667,13 +5667,13 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D220" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="E220" t="s">
         <v>8</v>
@@ -5684,13 +5684,13 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D221" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="E221" t="s">
         <v>8</v>
@@ -5701,13 +5701,13 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D222" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E222" t="s">
         <v>8</v>
@@ -5718,13 +5718,13 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D223" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E223" t="s">
         <v>8</v>
@@ -5735,13 +5735,13 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D224" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E224" t="s">
         <v>8</v>
@@ -5752,13 +5752,13 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D225" t="s">
-        <v>266</v>
+        <v>204</v>
       </c>
       <c r="E225" t="s">
         <v>8</v>
@@ -5769,13 +5769,13 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D226" t="s">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="E226" t="s">
         <v>8</v>
@@ -5786,13 +5786,13 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D227" t="s">
-        <v>224</v>
+        <v>272</v>
       </c>
       <c r="E227" t="s">
         <v>8</v>
@@ -5803,13 +5803,13 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D228" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="E228" t="s">
         <v>8</v>
@@ -5820,13 +5820,13 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D229" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="E229" t="s">
         <v>8</v>
@@ -5837,13 +5837,13 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D230" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="E230" t="s">
         <v>8</v>
@@ -5854,13 +5854,13 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D231" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="E231" t="s">
         <v>8</v>
@@ -5871,13 +5871,13 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D232" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="E232" t="s">
         <v>8</v>
@@ -5888,13 +5888,13 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D233" t="s">
-        <v>246</v>
+        <v>283</v>
       </c>
       <c r="E233" t="s">
         <v>8</v>
@@ -5905,13 +5905,13 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D234" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E234" t="s">
         <v>8</v>
@@ -5922,13 +5922,13 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D235" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="E235" t="s">
         <v>8</v>
@@ -5939,13 +5939,13 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D236" t="s">
-        <v>252</v>
+        <v>289</v>
       </c>
       <c r="E236" t="s">
         <v>8</v>
@@ -5956,13 +5956,13 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D237" t="s">
-        <v>206</v>
+        <v>291</v>
       </c>
       <c r="E237" t="s">
         <v>8</v>
@@ -5973,13 +5973,13 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D238" t="s">
-        <v>250</v>
+        <v>293</v>
       </c>
       <c r="E238" t="s">
         <v>8</v>
@@ -5990,13 +5990,13 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D239" t="s">
-        <v>286</v>
+        <v>190</v>
       </c>
       <c r="E239" t="s">
         <v>8</v>
@@ -6007,13 +6007,13 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D240" t="s">
-        <v>224</v>
+        <v>190</v>
       </c>
       <c r="E240" t="s">
         <v>8</v>
@@ -6024,13 +6024,13 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D241" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="E241" t="s">
         <v>8</v>
@@ -6041,13 +6041,13 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D242" t="s">
-        <v>291</v>
+        <v>267</v>
       </c>
       <c r="E242" t="s">
         <v>8</v>
@@ -6058,13 +6058,13 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D243" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="E243" t="s">
         <v>8</v>
@@ -6075,13 +6075,13 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D244" t="s">
-        <v>224</v>
+        <v>301</v>
       </c>
       <c r="E244" t="s">
         <v>8</v>
@@ -6092,13 +6092,13 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D245" t="s">
-        <v>295</v>
+        <v>227</v>
       </c>
       <c r="E245" t="s">
         <v>8</v>
@@ -6109,13 +6109,13 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D246" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="E246" t="s">
         <v>8</v>
@@ -6126,13 +6126,13 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D247" t="s">
-        <v>217</v>
+        <v>306</v>
       </c>
       <c r="E247" t="s">
         <v>8</v>
@@ -6143,13 +6143,13 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D248" t="s">
-        <v>256</v>
+        <v>308</v>
       </c>
       <c r="E248" t="s">
         <v>8</v>
@@ -6160,13 +6160,13 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D249" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E249" t="s">
         <v>8</v>
@@ -6177,7 +6177,7 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>6</v>
@@ -6194,13 +6194,13 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D251" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="E251" t="s">
         <v>8</v>
@@ -6211,13 +6211,13 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D252" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="E252" t="s">
         <v>8</v>
@@ -6228,13 +6228,13 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D253" t="s">
-        <v>306</v>
+        <v>223</v>
       </c>
       <c r="E253" t="s">
         <v>8</v>
@@ -6245,13 +6245,13 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D254" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="E254" t="s">
         <v>8</v>
@@ -6262,13 +6262,13 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D255" t="s">
-        <v>310</v>
+        <v>247</v>
       </c>
       <c r="E255" t="s">
         <v>8</v>
@@ -6279,13 +6279,13 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D256" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="E256" t="s">
         <v>8</v>
@@ -6296,13 +6296,13 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D257" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="E257" t="s">
         <v>8</v>
@@ -6313,13 +6313,13 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D258" t="s">
-        <v>232</v>
+        <v>322</v>
       </c>
       <c r="E258" t="s">
         <v>8</v>
@@ -6330,13 +6330,13 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D259" t="s">
-        <v>317</v>
+        <v>202</v>
       </c>
       <c r="E259" t="s">
         <v>8</v>
@@ -6347,13 +6347,13 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D260" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="E260" t="s">
         <v>8</v>
@@ -6364,13 +6364,13 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D261" t="s">
-        <v>303</v>
+        <v>206</v>
       </c>
       <c r="E261" t="s">
         <v>8</v>
@@ -6381,13 +6381,13 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D262" t="s">
-        <v>321</v>
+        <v>276</v>
       </c>
       <c r="E262" t="s">
         <v>8</v>
@@ -6398,13 +6398,13 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D263" t="s">
-        <v>222</v>
+        <v>329</v>
       </c>
       <c r="E263" t="s">
         <v>8</v>
@@ -6415,13 +6415,13 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D264" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="E264" t="s">
         <v>8</v>
@@ -6432,13 +6432,13 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D265" t="s">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="E265" t="s">
         <v>8</v>
@@ -6449,13 +6449,13 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D266" t="s">
-        <v>326</v>
+        <v>291</v>
       </c>
       <c r="E266" t="s">
         <v>8</v>
@@ -6466,13 +6466,13 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D267" t="s">
-        <v>246</v>
+        <v>219</v>
       </c>
       <c r="E267" t="s">
         <v>8</v>
@@ -6483,13 +6483,13 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D268" t="s">
-        <v>192</v>
+        <v>318</v>
       </c>
       <c r="E268" t="s">
         <v>8</v>
@@ -6500,13 +6500,13 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D269" t="s">
-        <v>303</v>
+        <v>337</v>
       </c>
       <c r="E269" t="s">
         <v>8</v>
@@ -6517,13 +6517,13 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D270" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="E270" t="s">
         <v>8</v>
@@ -6534,13 +6534,13 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D271" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="E271" t="s">
         <v>8</v>
@@ -6551,13 +6551,13 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D272" t="s">
-        <v>317</v>
+        <v>239</v>
       </c>
       <c r="E272" t="s">
         <v>8</v>
@@ -6568,13 +6568,13 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D273" t="s">
-        <v>209</v>
+        <v>308</v>
       </c>
       <c r="E273" t="s">
         <v>8</v>
@@ -6585,13 +6585,13 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D274" t="s">
-        <v>331</v>
+        <v>223</v>
       </c>
       <c r="E274" t="s">
         <v>8</v>
@@ -6602,13 +6602,13 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D275" t="s">
-        <v>338</v>
+        <v>196</v>
       </c>
       <c r="E275" t="s">
         <v>8</v>
@@ -6619,13 +6619,13 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D276" t="s">
-        <v>270</v>
+        <v>297</v>
       </c>
       <c r="E276" t="s">
         <v>8</v>
@@ -6636,13 +6636,13 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D277" t="s">
-        <v>317</v>
+        <v>347</v>
       </c>
       <c r="E277" t="s">
         <v>8</v>
@@ -6653,13 +6653,13 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D278" t="s">
-        <v>342</v>
+        <v>239</v>
       </c>
       <c r="E278" t="s">
         <v>8</v>
@@ -6670,13 +6670,13 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D279" t="s">
-        <v>209</v>
+        <v>350</v>
       </c>
       <c r="E279" t="s">
         <v>8</v>
@@ -6687,13 +6687,13 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D280" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="E280" t="s">
         <v>8</v>
@@ -6704,13 +6704,13 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D281" t="s">
-        <v>222</v>
+        <v>262</v>
       </c>
       <c r="E281" t="s">
         <v>8</v>
@@ -6721,13 +6721,13 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D282" t="s">
-        <v>258</v>
+        <v>239</v>
       </c>
       <c r="E282" t="s">
         <v>8</v>
@@ -6738,13 +6738,13 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D283" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="E283" t="s">
         <v>8</v>
@@ -6755,13 +6755,13 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D284" t="s">
-        <v>252</v>
+        <v>337</v>
       </c>
       <c r="E284" t="s">
         <v>8</v>
@@ -6772,13 +6772,13 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D285" t="s">
-        <v>350</v>
+        <v>235</v>
       </c>
       <c r="E285" t="s">
         <v>8</v>
@@ -6789,13 +6789,13 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D286" t="s">
-        <v>312</v>
+        <v>206</v>
       </c>
       <c r="E286" t="s">
         <v>8</v>
@@ -6806,13 +6806,13 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D287" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E287" t="s">
         <v>8</v>
@@ -6823,13 +6823,13 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D288" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="E288" t="s">
         <v>8</v>
@@ -6840,13 +6840,13 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D289" t="s">
-        <v>276</v>
+        <v>211</v>
       </c>
       <c r="E289" t="s">
         <v>8</v>
@@ -6857,13 +6857,13 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D290" t="s">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="E290" t="s">
         <v>8</v>
@@ -6874,13 +6874,13 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D291" t="s">
-        <v>232</v>
+        <v>365</v>
       </c>
       <c r="E291" t="s">
         <v>8</v>
@@ -6891,13 +6891,13 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D292" t="s">
-        <v>209</v>
+        <v>276</v>
       </c>
       <c r="E292" t="s">
         <v>8</v>
@@ -6908,13 +6908,13 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D293" t="s">
-        <v>360</v>
+        <v>308</v>
       </c>
       <c r="E293" t="s">
         <v>8</v>
@@ -6925,13 +6925,13 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D294" t="s">
-        <v>362</v>
+        <v>239</v>
       </c>
       <c r="E294" t="s">
         <v>8</v>
@@ -6942,13 +6942,13 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D295" t="s">
-        <v>260</v>
+        <v>370</v>
       </c>
       <c r="E295" t="s">
         <v>8</v>
@@ -6959,13 +6959,13 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D296" t="s">
-        <v>365</v>
+        <v>235</v>
       </c>
       <c r="E296" t="s">
         <v>8</v>
@@ -6976,13 +6976,13 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D297" t="s">
-        <v>367</v>
+        <v>192</v>
       </c>
       <c r="E297" t="s">
         <v>8</v>
@@ -6993,13 +6993,13 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D298" t="s">
-        <v>310</v>
+        <v>225</v>
       </c>
       <c r="E298" t="s">
         <v>8</v>
@@ -7010,13 +7010,13 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D299" t="s">
-        <v>370</v>
+        <v>211</v>
       </c>
       <c r="E299" t="s">
         <v>8</v>
@@ -7027,13 +7027,13 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D300" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="E300" t="s">
         <v>8</v>
@@ -7044,13 +7044,13 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D301" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="E301" t="s">
         <v>8</v>
@@ -7061,13 +7061,13 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D302" t="s">
-        <v>375</v>
+        <v>262</v>
       </c>
       <c r="E302" t="s">
         <v>8</v>
@@ -7078,13 +7078,13 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D303" t="s">
-        <v>377</v>
+        <v>337</v>
       </c>
       <c r="E303" t="s">
         <v>8</v>
@@ -7095,13 +7095,13 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D304" t="s">
-        <v>236</v>
+        <v>278</v>
       </c>
       <c r="E304" t="s">
         <v>8</v>
@@ -7112,13 +7112,13 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D305" t="s">
-        <v>190</v>
+        <v>382</v>
       </c>
       <c r="E305" t="s">
         <v>8</v>
@@ -7129,13 +7129,13 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D306" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E306" t="s">
         <v>8</v>
@@ -7146,13 +7146,13 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D307" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E307" t="s">
         <v>8</v>
@@ -7163,13 +7163,13 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D308" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E308" t="s">
         <v>8</v>
@@ -7180,13 +7180,13 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D309" t="s">
-        <v>384</v>
+        <v>223</v>
       </c>
       <c r="E309" t="s">
         <v>8</v>
@@ -7197,13 +7197,13 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D310" t="s">
-        <v>386</v>
+        <v>247</v>
       </c>
       <c r="E310" t="s">
         <v>8</v>
@@ -7214,13 +7214,13 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D311" t="s">
-        <v>217</v>
+        <v>350</v>
       </c>
       <c r="E311" t="s">
         <v>8</v>
@@ -7231,13 +7231,13 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D312" t="s">
-        <v>389</v>
+        <v>260</v>
       </c>
       <c r="E312" t="s">
         <v>8</v>
@@ -7254,7 +7254,7 @@
         <v>6</v>
       </c>
       <c r="D313" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E313" t="s">
         <v>8</v>
@@ -7288,7 +7288,7 @@
         <v>6</v>
       </c>
       <c r="D315" t="s">
-        <v>394</v>
+        <v>192</v>
       </c>
       <c r="E315" t="s">
         <v>8</v>
@@ -7299,13 +7299,13 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D316" t="s">
-        <v>342</v>
+        <v>223</v>
       </c>
       <c r="E316" t="s">
         <v>8</v>
@@ -7316,13 +7316,13 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D317" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="E317" t="s">
         <v>8</v>
@@ -7333,13 +7333,13 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D318" t="s">
-        <v>398</v>
+        <v>237</v>
       </c>
       <c r="E318" t="s">
         <v>8</v>
@@ -7350,13 +7350,13 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D319" t="s">
-        <v>342</v>
+        <v>308</v>
       </c>
       <c r="E319" t="s">
         <v>8</v>
@@ -7367,13 +7367,13 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D320" t="s">
-        <v>224</v>
+        <v>399</v>
       </c>
       <c r="E320" t="s">
         <v>8</v>
@@ -7384,13 +7384,13 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D321" t="s">
-        <v>206</v>
+        <v>329</v>
       </c>
       <c r="E321" t="s">
         <v>8</v>
@@ -7401,13 +7401,13 @@
         <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D322" t="s">
-        <v>206</v>
+        <v>241</v>
       </c>
       <c r="E322" t="s">
         <v>8</v>
@@ -7418,13 +7418,13 @@
         <v>322</v>
       </c>
       <c r="B323" t="s">
+        <v>402</v>
+      </c>
+      <c r="C323" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D323" t="s">
         <v>403</v>
-      </c>
-      <c r="C323" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D323" t="s">
-        <v>404</v>
       </c>
       <c r="E323" t="s">
         <v>8</v>
@@ -7435,13 +7435,13 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D324" t="s">
-        <v>206</v>
+        <v>270</v>
       </c>
       <c r="E324" t="s">
         <v>8</v>
@@ -7452,13 +7452,13 @@
         <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D325" t="s">
-        <v>386</v>
+        <v>315</v>
       </c>
       <c r="E325" t="s">
         <v>8</v>
@@ -7469,13 +7469,13 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D326" t="s">
-        <v>362</v>
+        <v>227</v>
       </c>
       <c r="E326" t="s">
         <v>8</v>
@@ -7486,13 +7486,13 @@
         <v>326</v>
       </c>
       <c r="B327" t="s">
+        <v>407</v>
+      </c>
+      <c r="C327" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D327" t="s">
         <v>408</v>
-      </c>
-      <c r="C327" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D327" t="s">
-        <v>342</v>
       </c>
       <c r="E327" t="s">
         <v>8</v>
@@ -7509,7 +7509,7 @@
         <v>6</v>
       </c>
       <c r="D328" t="s">
-        <v>342</v>
+        <v>278</v>
       </c>
       <c r="E328" t="s">
         <v>8</v>
@@ -7526,7 +7526,7 @@
         <v>6</v>
       </c>
       <c r="D329" t="s">
-        <v>314</v>
+        <v>355</v>
       </c>
       <c r="E329" t="s">
         <v>8</v>
@@ -7543,7 +7543,7 @@
         <v>6</v>
       </c>
       <c r="D330" t="s">
-        <v>224</v>
+        <v>267</v>
       </c>
       <c r="E330" t="s">
         <v>8</v>
@@ -7560,7 +7560,7 @@
         <v>6</v>
       </c>
       <c r="D331" t="s">
-        <v>281</v>
+        <v>413</v>
       </c>
       <c r="E331" t="s">
         <v>8</v>
@@ -7571,13 +7571,13 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D332" t="s">
-        <v>370</v>
+        <v>260</v>
       </c>
       <c r="E332" t="s">
         <v>8</v>
@@ -7588,13 +7588,13 @@
         <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D333" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E333" t="s">
         <v>8</v>
@@ -7605,13 +7605,13 @@
         <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D334" t="s">
-        <v>295</v>
+        <v>418</v>
       </c>
       <c r="E334" t="s">
         <v>8</v>
@@ -7622,13 +7622,13 @@
         <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D335" t="s">
-        <v>232</v>
+        <v>289</v>
       </c>
       <c r="E335" t="s">
         <v>8</v>
@@ -7639,13 +7639,13 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D336" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="E336" t="s">
         <v>8</v>
@@ -7656,13 +7656,13 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D337" t="s">
-        <v>420</v>
+        <v>392</v>
       </c>
       <c r="E337" t="s">
         <v>8</v>
@@ -7673,13 +7673,13 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D338" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="E338" t="s">
         <v>8</v>
@@ -7690,13 +7690,13 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D339" t="s">
-        <v>252</v>
+        <v>413</v>
       </c>
       <c r="E339" t="s">
         <v>8</v>
@@ -7707,13 +7707,13 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D340" t="s">
-        <v>362</v>
+        <v>306</v>
       </c>
       <c r="E340" t="s">
         <v>8</v>
@@ -7724,13 +7724,13 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D341" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E341" t="s">
         <v>8</v>
@@ -7741,13 +7741,13 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D342" t="s">
-        <v>427</v>
+        <v>315</v>
       </c>
       <c r="E342" t="s">
         <v>8</v>
@@ -7758,13 +7758,13 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D343" t="s">
-        <v>226</v>
+        <v>430</v>
       </c>
       <c r="E343" t="s">
         <v>8</v>
@@ -7775,13 +7775,13 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D344" t="s">
-        <v>234</v>
+        <v>192</v>
       </c>
       <c r="E344" t="s">
         <v>8</v>
@@ -7792,13 +7792,13 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D345" t="s">
-        <v>279</v>
+        <v>239</v>
       </c>
       <c r="E345" t="s">
         <v>8</v>
@@ -7809,13 +7809,13 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D346" t="s">
-        <v>239</v>
+        <v>434</v>
       </c>
       <c r="E346" t="s">
         <v>8</v>
@@ -7826,13 +7826,13 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D347" t="s">
-        <v>326</v>
+        <v>436</v>
       </c>
       <c r="E347" t="s">
         <v>8</v>
@@ -7843,13 +7843,13 @@
         <v>347</v>
       </c>
       <c r="B348" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D348" t="s">
-        <v>241</v>
+        <v>438</v>
       </c>
       <c r="E348" t="s">
         <v>8</v>
@@ -7860,13 +7860,13 @@
         <v>348</v>
       </c>
       <c r="B349" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D349" t="s">
-        <v>435</v>
+        <v>213</v>
       </c>
       <c r="E349" t="s">
         <v>8</v>
@@ -7877,13 +7877,13 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D350" t="s">
-        <v>354</v>
+        <v>315</v>
       </c>
       <c r="E350" t="s">
         <v>8</v>
@@ -7894,13 +7894,13 @@
         <v>350</v>
       </c>
       <c r="B351" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D351" t="s">
-        <v>241</v>
+        <v>217</v>
       </c>
       <c r="E351" t="s">
         <v>8</v>
@@ -7911,13 +7911,13 @@
         <v>351</v>
       </c>
       <c r="B352" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D352" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="E352" t="s">
         <v>8</v>
@@ -7928,13 +7928,13 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D353" t="s">
-        <v>375</v>
+        <v>423</v>
       </c>
       <c r="E353" t="s">
         <v>8</v>
@@ -7945,13 +7945,13 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D354" t="s">
-        <v>441</v>
+        <v>211</v>
       </c>
       <c r="E354" t="s">
         <v>8</v>
@@ -7962,13 +7962,13 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D355" t="s">
-        <v>394</v>
+        <v>446</v>
       </c>
       <c r="E355" t="s">
         <v>8</v>
@@ -7979,13 +7979,13 @@
         <v>355</v>
       </c>
       <c r="B356" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D356" t="s">
-        <v>314</v>
+        <v>413</v>
       </c>
       <c r="E356" t="s">
         <v>8</v>
@@ -7996,13 +7996,13 @@
         <v>356</v>
       </c>
       <c r="B357" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D357" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="E357" t="s">
         <v>8</v>
@@ -8013,13 +8013,13 @@
         <v>357</v>
       </c>
       <c r="B358" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D358" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E358" t="s">
         <v>8</v>
@@ -8030,13 +8030,13 @@
         <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D359" t="s">
-        <v>362</v>
+        <v>325</v>
       </c>
       <c r="E359" t="s">
         <v>8</v>
@@ -8047,7 +8047,7 @@
         <v>359</v>
       </c>
       <c r="B360" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>6</v>
@@ -8064,13 +8064,13 @@
         <v>360</v>
       </c>
       <c r="B361" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D361" t="s">
-        <v>372</v>
+        <v>308</v>
       </c>
       <c r="E361" t="s">
         <v>8</v>
@@ -8081,13 +8081,13 @@
         <v>361</v>
       </c>
       <c r="B362" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D362" t="s">
-        <v>450</v>
+        <v>293</v>
       </c>
       <c r="E362" t="s">
         <v>8</v>
@@ -8098,13 +8098,13 @@
         <v>362</v>
       </c>
       <c r="B363" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D363" t="s">
-        <v>377</v>
+        <v>239</v>
       </c>
       <c r="E363" t="s">
         <v>8</v>
@@ -8115,13 +8115,13 @@
         <v>363</v>
       </c>
       <c r="B364" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D364" t="s">
-        <v>228</v>
+        <v>456</v>
       </c>
       <c r="E364" t="s">
         <v>8</v>
@@ -8132,13 +8132,13 @@
         <v>364</v>
       </c>
       <c r="B365" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D365" t="s">
-        <v>404</v>
+        <v>332</v>
       </c>
       <c r="E365" t="s">
         <v>8</v>
@@ -8149,13 +8149,13 @@
         <v>365</v>
       </c>
       <c r="B366" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D366" t="s">
-        <v>333</v>
+        <v>287</v>
       </c>
       <c r="E366" t="s">
         <v>8</v>
@@ -8166,13 +8166,13 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D367" t="s">
-        <v>456</v>
+        <v>262</v>
       </c>
       <c r="E367" t="s">
         <v>8</v>
@@ -8183,13 +8183,13 @@
         <v>367</v>
       </c>
       <c r="B368" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D368" t="s">
-        <v>425</v>
+        <v>256</v>
       </c>
       <c r="E368" t="s">
         <v>8</v>
@@ -8200,13 +8200,13 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D369" t="s">
-        <v>441</v>
+        <v>350</v>
       </c>
       <c r="E369" t="s">
         <v>8</v>
@@ -8217,13 +8217,13 @@
         <v>369</v>
       </c>
       <c r="B370" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D370" t="s">
-        <v>460</v>
+        <v>239</v>
       </c>
       <c r="E370" t="s">
         <v>8</v>
@@ -8234,13 +8234,13 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D371" t="s">
-        <v>264</v>
+        <v>416</v>
       </c>
       <c r="E371" t="s">
         <v>8</v>
@@ -8251,13 +8251,13 @@
         <v>371</v>
       </c>
       <c r="B372" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D372" t="s">
-        <v>463</v>
+        <v>355</v>
       </c>
       <c r="E372" t="s">
         <v>8</v>
@@ -8268,13 +8268,13 @@
         <v>372</v>
       </c>
       <c r="B373" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D373" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="E373" t="s">
         <v>8</v>
@@ -8285,13 +8285,13 @@
         <v>373</v>
       </c>
       <c r="B374" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D374" t="s">
-        <v>295</v>
+        <v>456</v>
       </c>
       <c r="E374" t="s">
         <v>8</v>
@@ -8302,13 +8302,13 @@
         <v>374</v>
       </c>
       <c r="B375" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D375" t="s">
-        <v>198</v>
+        <v>297</v>
       </c>
       <c r="E375" t="s">
         <v>8</v>
@@ -8319,13 +8319,13 @@
         <v>375</v>
       </c>
       <c r="B376" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D376" t="s">
-        <v>270</v>
+        <v>416</v>
       </c>
       <c r="E376" t="s">
         <v>8</v>
@@ -8336,13 +8336,13 @@
         <v>376</v>
       </c>
       <c r="B377" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D377" t="s">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="E377" t="s">
         <v>8</v>
@@ -8353,13 +8353,13 @@
         <v>377</v>
       </c>
       <c r="B378" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D378" t="s">
-        <v>317</v>
+        <v>202</v>
       </c>
       <c r="E378" t="s">
         <v>8</v>
@@ -8370,13 +8370,13 @@
         <v>378</v>
       </c>
       <c r="B379" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D379" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="E379" t="s">
         <v>8</v>
@@ -8387,13 +8387,13 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D380" t="s">
-        <v>472</v>
+        <v>258</v>
       </c>
       <c r="E380" t="s">
         <v>8</v>
@@ -8410,7 +8410,7 @@
         <v>6</v>
       </c>
       <c r="D381" t="s">
-        <v>220</v>
+        <v>361</v>
       </c>
       <c r="E381" t="s">
         <v>8</v>
@@ -8427,7 +8427,7 @@
         <v>6</v>
       </c>
       <c r="D382" t="s">
-        <v>392</v>
+        <v>308</v>
       </c>
       <c r="E382" t="s">
         <v>8</v>
@@ -8444,7 +8444,7 @@
         <v>6</v>
       </c>
       <c r="D383" t="s">
-        <v>192</v>
+        <v>276</v>
       </c>
       <c r="E383" t="s">
         <v>8</v>
@@ -8461,7 +8461,7 @@
         <v>6</v>
       </c>
       <c r="D384" t="s">
-        <v>196</v>
+        <v>430</v>
       </c>
       <c r="E384" t="s">
         <v>8</v>
@@ -8478,7 +8478,7 @@
         <v>6</v>
       </c>
       <c r="D385" t="s">
-        <v>232</v>
+        <v>206</v>
       </c>
       <c r="E385" t="s">
         <v>8</v>
@@ -8495,7 +8495,7 @@
         <v>6</v>
       </c>
       <c r="D386" t="s">
-        <v>295</v>
+        <v>241</v>
       </c>
       <c r="E386" t="s">
         <v>8</v>
@@ -8512,7 +8512,7 @@
         <v>6</v>
       </c>
       <c r="D387" t="s">
-        <v>480</v>
+        <v>365</v>
       </c>
       <c r="E387" t="s">
         <v>8</v>
@@ -8523,13 +8523,13 @@
         <v>387</v>
       </c>
       <c r="B388" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D388" t="s">
-        <v>310</v>
+        <v>278</v>
       </c>
       <c r="E388" t="s">
         <v>8</v>
@@ -8540,13 +8540,13 @@
         <v>388</v>
       </c>
       <c r="B389" t="s">
+        <v>481</v>
+      </c>
+      <c r="C389" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D389" t="s">
         <v>482</v>
-      </c>
-      <c r="C389" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D389" t="s">
-        <v>354</v>
       </c>
       <c r="E389" t="s">
         <v>8</v>
@@ -8563,7 +8563,7 @@
         <v>6</v>
       </c>
       <c r="D390" t="s">
-        <v>270</v>
+        <v>209</v>
       </c>
       <c r="E390" t="s">
         <v>8</v>
@@ -8580,7 +8580,7 @@
         <v>6</v>
       </c>
       <c r="D391" t="s">
-        <v>258</v>
+        <v>301</v>
       </c>
       <c r="E391" t="s">
         <v>8</v>
@@ -8597,7 +8597,7 @@
         <v>6</v>
       </c>
       <c r="D392" t="s">
-        <v>486</v>
+        <v>281</v>
       </c>
       <c r="E392" t="s">
         <v>8</v>
@@ -8608,13 +8608,13 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D393" t="s">
-        <v>228</v>
+        <v>340</v>
       </c>
       <c r="E393" t="s">
         <v>8</v>
@@ -8625,13 +8625,13 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D394" t="s">
-        <v>220</v>
+        <v>436</v>
       </c>
       <c r="E394" t="s">
         <v>8</v>
@@ -8642,13 +8642,13 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D395" t="s">
-        <v>276</v>
+        <v>241</v>
       </c>
       <c r="E395" t="s">
         <v>8</v>
@@ -8659,13 +8659,13 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D396" t="s">
-        <v>281</v>
+        <v>245</v>
       </c>
       <c r="E396" t="s">
         <v>8</v>
@@ -8676,13 +8676,13 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D397" t="s">
-        <v>241</v>
+        <v>337</v>
       </c>
       <c r="E397" t="s">
         <v>8</v>
@@ -8693,13 +8693,13 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D398" t="s">
-        <v>192</v>
+        <v>337</v>
       </c>
       <c r="E398" t="s">
         <v>8</v>
@@ -8710,13 +8710,13 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
+        <v>492</v>
+      </c>
+      <c r="C399" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D399" t="s">
         <v>493</v>
-      </c>
-      <c r="C399" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D399" t="s">
-        <v>331</v>
       </c>
       <c r="E399" t="s">
         <v>8</v>
@@ -8733,7 +8733,7 @@
         <v>6</v>
       </c>
       <c r="D400" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="E400" t="s">
         <v>8</v>
@@ -8750,7 +8750,7 @@
         <v>6</v>
       </c>
       <c r="D401" t="s">
-        <v>291</v>
+        <v>438</v>
       </c>
       <c r="E401" t="s">
         <v>8</v>

--- a/reports/backend/Excel/Automation_Test_Report.xlsx
+++ b/reports/backend/Excel/Automation_Test_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="511">
   <si>
     <t>#</t>
   </si>
@@ -44,6 +44,9 @@
     <t>Smart Admission Backend — Authentication Tests BT-002 | Firebase config has authDomain</t>
   </si>
   <si>
+    <t>0.001</t>
+  </si>
+  <si>
     <t>Smart Admission Backend — Authentication Tests BT-003 | Firebase config has projectId</t>
   </si>
   <si>
@@ -62,9 +65,6 @@
     <t>Smart Admission Backend — Authentication Tests BT-008 | Firebase config has all 6 required fields</t>
   </si>
   <si>
-    <t>0.001</t>
-  </si>
-  <si>
     <t>Smart Admission Backend — Authentication Tests BT-009 | Firebase config fields are non-empty strings</t>
   </si>
   <si>
@@ -584,906 +584,906 @@
     <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field apiKey (Verify Point #180)</t>
   </si>
   <si>
+    <t>0.096</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #181)</t>
+  </si>
+  <si>
+    <t>0.076</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #182)</t>
+  </si>
+  <si>
+    <t>0.038</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #183)</t>
+  </si>
+  <si>
+    <t>0.035</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #184)</t>
+  </si>
+  <si>
+    <t>0.046</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #185)</t>
+  </si>
+  <si>
+    <t>0.048</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #186)</t>
+  </si>
+  <si>
+    <t>0.088</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #187)</t>
+  </si>
+  <si>
+    <t>0.098</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #188)</t>
+  </si>
+  <si>
+    <t>0.059</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #189)</t>
+  </si>
+  <si>
+    <t>0.036</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #190)</t>
+  </si>
+  <si>
+    <t>0.105</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #191)</t>
+  </si>
+  <si>
+    <t>0.112</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #192)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #193)</t>
+  </si>
+  <si>
+    <t>0.078</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #194)</t>
+  </si>
+  <si>
+    <t>0.119</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #195)</t>
+  </si>
+  <si>
+    <t>0.114</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #196)</t>
+  </si>
+  <si>
+    <t>0.054</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #197)</t>
+  </si>
+  <si>
+    <t>0.068</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #198)</t>
+  </si>
+  <si>
+    <t>0.117</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #199)</t>
+  </si>
+  <si>
+    <t>0.101</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #200)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #201)</t>
+  </si>
+  <si>
+    <t>0.081</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #202)</t>
+  </si>
+  <si>
+    <t>0.066</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #203)</t>
+  </si>
+  <si>
+    <t>0.070</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #204)</t>
+  </si>
+  <si>
+    <t>0.030</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #205)</t>
+  </si>
+  <si>
+    <t>0.034</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #206)</t>
+  </si>
+  <si>
+    <t>0.072</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #207)</t>
+  </si>
+  <si>
+    <t>0.104</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #208)</t>
+  </si>
+  <si>
+    <t>0.073</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #209)</t>
+  </si>
+  <si>
+    <t>0.065</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #210)</t>
+  </si>
+  <si>
+    <t>0.061</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #211)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code XSS-injection (Verify Point #212)</t>
+  </si>
+  <si>
+    <t>0.050</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #213)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for CSRF-token (Verify Point #214)</t>
+  </si>
+  <si>
+    <t>0.067</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated CORS-origin (Verify Point #215)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for CSP-header (Verify Point #216)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at session-token (Verify Point #217)</t>
+  </si>
+  <si>
+    <t>0.045</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users-ref (Verify Point #218)</t>
+  </si>
+  <si>
+    <t>0.058</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for items-ref (Verify Point #219)</t>
+  </si>
+  <si>
+    <t>0.020</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field de-DE (Verify Point #220)</t>
+  </si>
+  <si>
+    <t>0.113</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for fr-FR (Verify Point #221)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ja-JP (Verify Point #222)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for pt-BR (Verify Point #223)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of it-IT (Verify Point #224)</t>
+  </si>
+  <si>
+    <t>0.108</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for apiKey (Verify Point #225)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for authDomain (Verify Point #226)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value projectId (Verify Point #227)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session storageBucket (Verify Point #228)</t>
+  </si>
+  <si>
+    <t>0.103</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier messagingSenderId (Verify Point #229)</t>
+  </si>
+  <si>
+    <t>0.055</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region appId (Verify Point #230)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for name (Verify Point #231)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code id (Verify Point #232)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource fees.min (Verify Point #233)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for fees.max (Verify Point #234)</t>
+  </si>
+  <si>
+    <t>0.063</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated courses (Verify Point #235)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for ranking.nirf (Verify Point #236)</t>
+  </si>
+  <si>
+    <t>0.100</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at type (Verify Point #237)</t>
+  </si>
+  <si>
+    <t>0.023</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users/uid001 (Verify Point #238)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for colleges/c001 (Verify Point #239)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field prompt-length (Verify Point #240)</t>
+  </si>
+  <si>
+    <t>0.109</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for session-id-1 (Verify Point #241)</t>
+  </si>
+  <si>
+    <t>0.086</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ₹1L (Verify Point #242)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for B.Tech (Verify Point #243)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of 4 years (Verify Point #244)</t>
+  </si>
+  <si>
+    <t>0.049</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for Tamil Nadu (Verify Point #245)</t>
+  </si>
+  <si>
+    <t>0.039</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for Chennai (Verify Point #246)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value llama3-8b (Verify Point #247)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session email (Verify Point #248)</t>
+  </si>
+  <si>
+    <t>0.087</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier password (Verify Point #249)</t>
+  </si>
+  <si>
+    <t>0.069</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region displayName (Verify Point #250)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for savedColleges (Verify Point #251)</t>
+  </si>
+  <si>
+    <t>0.062</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code createdAt (Verify Point #252)</t>
+  </si>
+  <si>
+    <t>0.064</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource firebase-auth (Verify Point #253)</t>
+  </si>
+  <si>
+    <t>0.116</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for firestore-read (Verify Point #254)</t>
+  </si>
+  <si>
+    <t>0.082</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated groq-api (Verify Point #255)</t>
+  </si>
+  <si>
+    <t>0.021</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for college-list (Verify Point #256)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at XSS-injection (Verify Point #257)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation SQL-injection (Verify Point #258)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for CSRF-token (Verify Point #259)</t>
+  </si>
+  <si>
+    <t>0.074</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field CORS-origin (Verify Point #260)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for CSP-header (Verify Point #261)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for session-token (Verify Point #262)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users-ref (Verify Point #263)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of items-ref (Verify Point #264)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for de-DE (Verify Point #265)</t>
+  </si>
+  <si>
+    <t>0.041</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for fr-FR (Verify Point #266)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ja-JP (Verify Point #267)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session pt-BR (Verify Point #268)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier it-IT (Verify Point #269)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region apiKey (Verify Point #270)</t>
+  </si>
+  <si>
+    <t>0.106</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for authDomain (Verify Point #271)</t>
+  </si>
+  <si>
+    <t>0.042</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code projectId (Verify Point #272)</t>
+  </si>
+  <si>
+    <t>0.043</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource storageBucket (Verify Point #273)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for messagingSenderId (Verify Point #274)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated appId (Verify Point #275)</t>
+  </si>
+  <si>
+    <t>0.097</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for name (Verify Point #276)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at id (Verify Point #277)</t>
+  </si>
+  <si>
+    <t>0.092</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation fees.min (Verify Point #278)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for fees.max (Verify Point #279)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field courses (Verify Point #280)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for ranking.nirf (Verify Point #281)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for type (Verify Point #282)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users/uid001 (Verify Point #283)</t>
+  </si>
+  <si>
+    <t>0.057</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of colleges/c001 (Verify Point #284)</t>
+  </si>
+  <si>
+    <t>0.077</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for prompt-length (Verify Point #285)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for session-id-1 (Verify Point #286)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ₹1L (Verify Point #287)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session B.Tech (Verify Point #288)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier 4 years (Verify Point #289)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region Tamil Nadu (Verify Point #290)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for Chennai (Verify Point #291)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code llama3-8b (Verify Point #292)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource email (Verify Point #293)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for password (Verify Point #294)</t>
+  </si>
+  <si>
+    <t>0.085</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated displayName (Verify Point #295)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for savedColleges (Verify Point #296)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at createdAt (Verify Point #297)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation firebase-auth (Verify Point #298)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for firestore-read (Verify Point #299)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field groq-api (Verify Point #300)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for college-list (Verify Point #301)</t>
+  </si>
+  <si>
+    <t>0.026</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for XSS-injection (Verify Point #302)</t>
+  </si>
+  <si>
+    <t>0.025</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for SQL-injection (Verify Point #303)</t>
+  </si>
+  <si>
+    <t>0.084</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of CSRF-token (Verify Point #304)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for CORS-origin (Verify Point #305)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for CSP-header (Verify Point #306)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value session-token (Verify Point #307)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users-ref (Verify Point #308)</t>
+  </si>
+  <si>
+    <t>0.091</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier items-ref (Verify Point #309)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region de-DE (Verify Point #310)</t>
+  </si>
+  <si>
+    <t>0.056</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for fr-FR (Verify Point #311)</t>
+  </si>
+  <si>
+    <t>0.099</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ja-JP (Verify Point #312)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource pt-BR (Verify Point #313)</t>
+  </si>
+  <si>
+    <t>0.032</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for it-IT (Verify Point #314)</t>
+  </si>
+  <si>
+    <t>0.083</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated apiKey (Verify Point #315)</t>
+  </si>
+  <si>
+    <t>0.095</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for authDomain (Verify Point #316)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at projectId (Verify Point #317)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation storageBucket (Verify Point #318)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for messagingSenderId (Verify Point #319)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field appId (Verify Point #320)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for name (Verify Point #321)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for id (Verify Point #322)</t>
+  </si>
+  <si>
+    <t>0.047</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for fees.min (Verify Point #323)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of fees.max (Verify Point #324)</t>
+  </si>
+  <si>
+    <t>0.080</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for courses (Verify Point #325)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for ranking.nirf (Verify Point #326)</t>
+  </si>
+  <si>
+    <t>0.044</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value type (Verify Point #327)</t>
+  </si>
+  <si>
+    <t>0.079</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users/uid001 (Verify Point #328)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier colleges/c001 (Verify Point #329)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region prompt-length (Verify Point #330)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for session-id-1 (Verify Point #331)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ₹1L (Verify Point #332)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource B.Tech (Verify Point #333)</t>
+  </si>
+  <si>
     <t>0.060</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #181)</t>
-  </si>
-  <si>
-    <t>0.022</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #182)</t>
-  </si>
-  <si>
-    <t>0.074</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #183)</t>
-  </si>
-  <si>
-    <t>0.070</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #184)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #185)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #186)</t>
-  </si>
-  <si>
-    <t>0.104</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #187)</t>
-  </si>
-  <si>
-    <t>0.072</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #188)</t>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for 4 years (Verify Point #334)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated Tamil Nadu (Verify Point #335)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for Chennai (Verify Point #336)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at llama3-8b (Verify Point #337)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation email (Verify Point #338)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for password (Verify Point #339)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field displayName (Verify Point #340)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for savedColleges (Verify Point #341)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for createdAt (Verify Point #342)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for firebase-auth (Verify Point #343)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of firestore-read (Verify Point #344)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for groq-api (Verify Point #345)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for college-list (Verify Point #346)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value XSS-injection (Verify Point #347)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session SQL-injection (Verify Point #348)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier CSRF-token (Verify Point #349)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region CORS-origin (Verify Point #350)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for CSP-header (Verify Point #351)</t>
+  </si>
+  <si>
+    <t>0.118</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code session-token (Verify Point #352)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users-ref (Verify Point #353)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for items-ref (Verify Point #354)</t>
+  </si>
+  <si>
+    <t>0.051</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated de-DE (Verify Point #355)</t>
   </si>
   <si>
     <t>0.102</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #189)</t>
-  </si>
-  <si>
-    <t>0.092</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #190)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #191)</t>
-  </si>
-  <si>
-    <t>0.082</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #192)</t>
-  </si>
-  <si>
-    <t>0.076</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #193)</t>
-  </si>
-  <si>
-    <t>0.068</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #194)</t>
-  </si>
-  <si>
-    <t>0.106</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #195)</t>
-  </si>
-  <si>
-    <t>0.118</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #196)</t>
-  </si>
-  <si>
-    <t>0.071</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #197)</t>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for fr-FR (Verify Point #356)</t>
+  </si>
+  <si>
+    <t>0.053</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ja-JP (Verify Point #357)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation pt-BR (Verify Point #358)</t>
+  </si>
+  <si>
+    <t>0.033</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for it-IT (Verify Point #359)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field apiKey (Verify Point #360)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #361)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #362)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #363)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #364)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #365)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #366)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #367)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #368)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #369)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #370)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #371)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #372)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #373)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #374)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #375)</t>
+  </si>
+  <si>
+    <t>0.111</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #376)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #377)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #378)</t>
+  </si>
+  <si>
+    <t>0.029</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #379)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #380)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #381)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #382)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #383)</t>
+  </si>
+  <si>
+    <t>0.075</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #384)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #385)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #386)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #387)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #388)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #389)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #390)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #391)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code XSS-injection (Verify Point #392)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #393)</t>
   </si>
   <si>
     <t>0.093</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #198)</t>
-  </si>
-  <si>
-    <t>0.115</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #199)</t>
-  </si>
-  <si>
-    <t>0.105</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #200)</t>
-  </si>
-  <si>
-    <t>0.095</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #201)</t>
-  </si>
-  <si>
-    <t>0.054</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #202)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #203)</t>
-  </si>
-  <si>
-    <t>0.108</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #204)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #205)</t>
-  </si>
-  <si>
-    <t>0.036</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #206)</t>
-  </si>
-  <si>
-    <t>0.051</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #207)</t>
-  </si>
-  <si>
-    <t>0.065</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #208)</t>
-  </si>
-  <si>
-    <t>0.087</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #209)</t>
-  </si>
-  <si>
-    <t>0.038</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #210)</t>
-  </si>
-  <si>
-    <t>0.067</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #211)</t>
-  </si>
-  <si>
-    <t>0.061</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code XSS-injection (Verify Point #212)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #213)</t>
-  </si>
-  <si>
-    <t>0.062</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for CSRF-token (Verify Point #214)</t>
-  </si>
-  <si>
-    <t>0.040</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated CORS-origin (Verify Point #215)</t>
-  </si>
-  <si>
-    <t>0.097</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for CSP-header (Verify Point #216)</t>
-  </si>
-  <si>
-    <t>0.081</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at session-token (Verify Point #217)</t>
-  </si>
-  <si>
-    <t>0.025</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users-ref (Verify Point #218)</t>
-  </si>
-  <si>
-    <t>0.048</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for items-ref (Verify Point #219)</t>
-  </si>
-  <si>
-    <t>0.066</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field de-DE (Verify Point #220)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for fr-FR (Verify Point #221)</t>
-  </si>
-  <si>
-    <t>0.116</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ja-JP (Verify Point #222)</t>
-  </si>
-  <si>
-    <t>0.112</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for pt-BR (Verify Point #223)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of it-IT (Verify Point #224)</t>
-  </si>
-  <si>
-    <t>0.098</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for apiKey (Verify Point #225)</t>
-  </si>
-  <si>
-    <t>0.063</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for authDomain (Verify Point #226)</t>
-  </si>
-  <si>
-    <t>0.047</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value projectId (Verify Point #227)</t>
-  </si>
-  <si>
-    <t>0.088</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session storageBucket (Verify Point #228)</t>
-  </si>
-  <si>
-    <t>0.049</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier messagingSenderId (Verify Point #229)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region appId (Verify Point #230)</t>
-  </si>
-  <si>
-    <t>0.035</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for name (Verify Point #231)</t>
-  </si>
-  <si>
-    <t>0.058</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code id (Verify Point #232)</t>
-  </si>
-  <si>
-    <t>0.107</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource fees.min (Verify Point #233)</t>
-  </si>
-  <si>
-    <t>0.101</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for fees.max (Verify Point #234)</t>
-  </si>
-  <si>
-    <t>0.045</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated courses (Verify Point #235)</t>
-  </si>
-  <si>
-    <t>0.083</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for ranking.nirf (Verify Point #236)</t>
-  </si>
-  <si>
-    <t>0.039</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at type (Verify Point #237)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users/uid001 (Verify Point #238)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for colleges/c001 (Verify Point #239)</t>
-  </si>
-  <si>
-    <t>0.100</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field prompt-length (Verify Point #240)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for session-id-1 (Verify Point #241)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ₹1L (Verify Point #242)</t>
-  </si>
-  <si>
-    <t>0.055</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for B.Tech (Verify Point #243)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of 4 years (Verify Point #244)</t>
-  </si>
-  <si>
-    <t>0.113</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for Tamil Nadu (Verify Point #245)</t>
-  </si>
-  <si>
-    <t>0.034</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for Chennai (Verify Point #246)</t>
-  </si>
-  <si>
-    <t>0.020</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value llama3-8b (Verify Point #247)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session email (Verify Point #248)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier password (Verify Point #249)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region displayName (Verify Point #250)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for savedColleges (Verify Point #251)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code createdAt (Verify Point #252)</t>
-  </si>
-  <si>
-    <t>0.031</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource firebase-auth (Verify Point #253)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for firestore-read (Verify Point #254)</t>
-  </si>
-  <si>
-    <t>0.064</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated groq-api (Verify Point #255)</t>
-  </si>
-  <si>
-    <t>0.024</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for college-list (Verify Point #256)</t>
-  </si>
-  <si>
-    <t>0.032</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at XSS-injection (Verify Point #257)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation SQL-injection (Verify Point #258)</t>
-  </si>
-  <si>
-    <t>0.026</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for CSRF-token (Verify Point #259)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field CORS-origin (Verify Point #260)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for CSP-header (Verify Point #261)</t>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for CSRF-token (Verify Point #394)</t>
   </si>
   <si>
     <t>0.027</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for session-token (Verify Point #262)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users-ref (Verify Point #263)</t>
-  </si>
-  <si>
-    <t>0.090</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of items-ref (Verify Point #264)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for de-DE (Verify Point #265)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for fr-FR (Verify Point #266)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ja-JP (Verify Point #267)</t>
-  </si>
-  <si>
-    <t>0.030</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session pt-BR (Verify Point #268)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier it-IT (Verify Point #269)</t>
-  </si>
-  <si>
-    <t>0.084</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region apiKey (Verify Point #270)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for authDomain (Verify Point #271)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code projectId (Verify Point #272)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource storageBucket (Verify Point #273)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for messagingSenderId (Verify Point #274)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated appId (Verify Point #275)</t>
-  </si>
-  <si>
-    <t>0.078</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for name (Verify Point #276)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at id (Verify Point #277)</t>
-  </si>
-  <si>
-    <t>0.059</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation fees.min (Verify Point #278)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for fees.max (Verify Point #279)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field courses (Verify Point #280)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for ranking.nirf (Verify Point #281)</t>
-  </si>
-  <si>
-    <t>0.050</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for type (Verify Point #282)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users/uid001 (Verify Point #283)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of colleges/c001 (Verify Point #284)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for prompt-length (Verify Point #285)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for session-id-1 (Verify Point #286)</t>
-  </si>
-  <si>
-    <t>0.094</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ₹1L (Verify Point #287)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session B.Tech (Verify Point #288)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier 4 years (Verify Point #289)</t>
-  </si>
-  <si>
-    <t>0.037</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region Tamil Nadu (Verify Point #290)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for Chennai (Verify Point #291)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code llama3-8b (Verify Point #292)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource email (Verify Point #293)</t>
-  </si>
-  <si>
-    <t>0.110</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for password (Verify Point #294)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated displayName (Verify Point #295)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for savedColleges (Verify Point #296)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at createdAt (Verify Point #297)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation firebase-auth (Verify Point #298)</t>
-  </si>
-  <si>
-    <t>0.077</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for firestore-read (Verify Point #299)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field groq-api (Verify Point #300)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for college-list (Verify Point #301)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for XSS-injection (Verify Point #302)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for SQL-injection (Verify Point #303)</t>
-  </si>
-  <si>
-    <t>0.096</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of CSRF-token (Verify Point #304)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for CORS-origin (Verify Point #305)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for CSP-header (Verify Point #306)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value session-token (Verify Point #307)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users-ref (Verify Point #308)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier items-ref (Verify Point #309)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region de-DE (Verify Point #310)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for fr-FR (Verify Point #311)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ja-JP (Verify Point #312)</t>
-  </si>
-  <si>
-    <t>0.042</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource pt-BR (Verify Point #313)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for it-IT (Verify Point #314)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated apiKey (Verify Point #315)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for authDomain (Verify Point #316)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at projectId (Verify Point #317)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation storageBucket (Verify Point #318)</t>
-  </si>
-  <si>
-    <t>0.057</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for messagingSenderId (Verify Point #319)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field appId (Verify Point #320)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for name (Verify Point #321)</t>
-  </si>
-  <si>
-    <t>0.103</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for id (Verify Point #322)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for fees.min (Verify Point #323)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of fees.max (Verify Point #324)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for courses (Verify Point #325)</t>
-  </si>
-  <si>
-    <t>0.041</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for ranking.nirf (Verify Point #326)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value type (Verify Point #327)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users/uid001 (Verify Point #328)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier colleges/c001 (Verify Point #329)</t>
-  </si>
-  <si>
-    <t>0.085</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region prompt-length (Verify Point #330)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for session-id-1 (Verify Point #331)</t>
-  </si>
-  <si>
-    <t>0.044</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ₹1L (Verify Point #332)</t>
-  </si>
-  <si>
-    <t>0.029</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource B.Tech (Verify Point #333)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for 4 years (Verify Point #334)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated Tamil Nadu (Verify Point #335)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for Chennai (Verify Point #336)</t>
-  </si>
-  <si>
-    <t>0.111</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at llama3-8b (Verify Point #337)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation email (Verify Point #338)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for password (Verify Point #339)</t>
-  </si>
-  <si>
-    <t>0.089</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field displayName (Verify Point #340)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for savedColleges (Verify Point #341)</t>
-  </si>
-  <si>
-    <t>0.079</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for createdAt (Verify Point #342)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for firebase-auth (Verify Point #343)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of firestore-read (Verify Point #344)</t>
-  </si>
-  <si>
-    <t>0.033</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for groq-api (Verify Point #345)</t>
-  </si>
-  <si>
-    <t>0.023</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for college-list (Verify Point #346)</t>
-  </si>
-  <si>
-    <t>0.109</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value XSS-injection (Verify Point #347)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session SQL-injection (Verify Point #348)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier CSRF-token (Verify Point #349)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region CORS-origin (Verify Point #350)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for CSP-header (Verify Point #351)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code session-token (Verify Point #352)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users-ref (Verify Point #353)</t>
-  </si>
-  <si>
-    <t>0.028</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for items-ref (Verify Point #354)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated de-DE (Verify Point #355)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for fr-FR (Verify Point #356)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ja-JP (Verify Point #357)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation pt-BR (Verify Point #358)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for it-IT (Verify Point #359)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field apiKey (Verify Point #360)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #361)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #362)</t>
-  </si>
-  <si>
-    <t>0.069</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #363)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #364)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #365)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #366)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #367)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #368)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #369)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #370)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #371)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #372)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #373)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #374)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #375)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #376)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #377)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #378)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #379)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #380)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #381)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #382)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #383)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #384)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #385)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #386)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #387)</t>
-  </si>
-  <si>
-    <t>0.091</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #388)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #389)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #390)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #391)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code XSS-injection (Verify Point #392)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #393)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for CSRF-token (Verify Point #394)</t>
-  </si>
-  <si>
     <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated CORS-origin (Verify Point #395)</t>
   </si>
   <si>
@@ -1493,9 +1493,6 @@
     <t>Smart Admission — Backend [Boundary]: Verify boundary condition at session-token (Verify Point #397)</t>
   </si>
   <si>
-    <t>0.075</t>
-  </si>
-  <si>
     <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users-ref (Verify Point #398)</t>
   </si>
   <si>
@@ -1511,13 +1508,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>24</t>
+    <t>25</t>
   </si>
   <si>
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-24 03:32:51 UTC</t>
+    <t>2026-06-24 04:39:15 UTC</t>
   </si>
   <si>
     <t>Branch</t>
@@ -1529,7 +1526,7 @@
     <t>Commit</t>
   </si>
   <si>
-    <t>19701a0</t>
+    <t>f6dc91b</t>
   </si>
   <si>
     <t>Total</t>
@@ -1984,7 +1981,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1995,7 +1992,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>6</v>
@@ -2012,7 +2009,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>6</v>
@@ -2029,7 +2026,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>6</v>
@@ -2046,7 +2043,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>6</v>
@@ -2063,7 +2060,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>6</v>
@@ -2080,13 +2077,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -2477,7 +2474,7 @@
         <v>6</v>
       </c>
       <c r="D32" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -2528,7 +2525,7 @@
         <v>6</v>
       </c>
       <c r="D35" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -2647,7 +2644,7 @@
         <v>6</v>
       </c>
       <c r="D42" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -2919,7 +2916,7 @@
         <v>6</v>
       </c>
       <c r="D58" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -3191,7 +3188,7 @@
         <v>6</v>
       </c>
       <c r="D74" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E74" t="s">
         <v>8</v>
@@ -3310,7 +3307,7 @@
         <v>6</v>
       </c>
       <c r="D81" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
@@ -3327,7 +3324,7 @@
         <v>6</v>
       </c>
       <c r="D82" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
@@ -3361,7 +3358,7 @@
         <v>6</v>
       </c>
       <c r="D84" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
@@ -3582,7 +3579,7 @@
         <v>6</v>
       </c>
       <c r="D97" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E97" t="s">
         <v>8</v>
@@ -3854,7 +3851,7 @@
         <v>6</v>
       </c>
       <c r="D113" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E113" t="s">
         <v>8</v>
@@ -4041,7 +4038,7 @@
         <v>6</v>
       </c>
       <c r="D124" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E124" t="s">
         <v>8</v>
@@ -4296,7 +4293,7 @@
         <v>6</v>
       </c>
       <c r="D139" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E139" t="s">
         <v>8</v>
@@ -4415,7 +4412,7 @@
         <v>6</v>
       </c>
       <c r="D146" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E146" t="s">
         <v>8</v>
@@ -5095,7 +5092,7 @@
         <v>6</v>
       </c>
       <c r="D186" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="E186" t="s">
         <v>8</v>
@@ -5106,13 +5103,13 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D187" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="E187" t="s">
         <v>8</v>
@@ -5123,13 +5120,13 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D188" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E188" t="s">
         <v>8</v>
@@ -5140,13 +5137,13 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D189" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E189" t="s">
         <v>8</v>
@@ -5157,13 +5154,13 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D190" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E190" t="s">
         <v>8</v>
@@ -5174,13 +5171,13 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D191" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E191" t="s">
         <v>8</v>
@@ -5191,13 +5188,13 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D192" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="E192" t="s">
         <v>8</v>
@@ -5208,13 +5205,13 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D193" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E193" t="s">
         <v>8</v>
@@ -5225,13 +5222,13 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D194" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="E194" t="s">
         <v>8</v>
@@ -5242,13 +5239,13 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D195" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E195" t="s">
         <v>8</v>
@@ -5259,13 +5256,13 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D196" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E196" t="s">
         <v>8</v>
@@ -5276,13 +5273,13 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D197" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E197" t="s">
         <v>8</v>
@@ -5293,13 +5290,13 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D198" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E198" t="s">
         <v>8</v>
@@ -5310,13 +5307,13 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D199" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E199" t="s">
         <v>8</v>
@@ -5327,13 +5324,13 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D200" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E200" t="s">
         <v>8</v>
@@ -5344,13 +5341,13 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D201" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E201" t="s">
         <v>8</v>
@@ -5361,7 +5358,7 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>6</v>
@@ -5378,13 +5375,13 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D203" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E203" t="s">
         <v>8</v>
@@ -5395,13 +5392,13 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D204" t="s">
-        <v>192</v>
+        <v>232</v>
       </c>
       <c r="E204" t="s">
         <v>8</v>
@@ -5412,13 +5409,13 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D205" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E205" t="s">
         <v>8</v>
@@ -5429,13 +5426,13 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D206" t="s">
-        <v>194</v>
+        <v>236</v>
       </c>
       <c r="E206" t="s">
         <v>8</v>
@@ -5446,13 +5443,13 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D207" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E207" t="s">
         <v>8</v>
@@ -5463,13 +5460,13 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D208" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E208" t="s">
         <v>8</v>
@@ -5480,13 +5477,13 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D209" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E209" t="s">
         <v>8</v>
@@ -5497,13 +5494,13 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D210" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E210" t="s">
         <v>8</v>
@@ -5514,13 +5511,13 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D211" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E211" t="s">
         <v>8</v>
@@ -5531,13 +5528,13 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D212" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E212" t="s">
         <v>8</v>
@@ -5548,13 +5545,13 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D213" t="s">
-        <v>247</v>
+        <v>210</v>
       </c>
       <c r="E213" t="s">
         <v>8</v>
@@ -5565,13 +5562,13 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D214" t="s">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E214" t="s">
         <v>8</v>
@@ -5582,13 +5579,13 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D215" t="s">
-        <v>250</v>
+        <v>208</v>
       </c>
       <c r="E215" t="s">
         <v>8</v>
@@ -5599,13 +5596,13 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D216" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E216" t="s">
         <v>8</v>
@@ -5616,13 +5613,13 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D217" t="s">
-        <v>254</v>
+        <v>227</v>
       </c>
       <c r="E217" t="s">
         <v>8</v>
@@ -5633,13 +5630,13 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D218" t="s">
-        <v>256</v>
+        <v>221</v>
       </c>
       <c r="E218" t="s">
         <v>8</v>
@@ -5707,7 +5704,7 @@
         <v>6</v>
       </c>
       <c r="D222" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="E222" t="s">
         <v>8</v>
@@ -5718,13 +5715,13 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D223" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="E223" t="s">
         <v>8</v>
@@ -5741,7 +5738,7 @@
         <v>6</v>
       </c>
       <c r="D224" t="s">
-        <v>267</v>
+        <v>242</v>
       </c>
       <c r="E224" t="s">
         <v>8</v>
@@ -5752,13 +5749,13 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D225" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="E225" t="s">
         <v>8</v>
@@ -5769,13 +5766,13 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
+        <v>268</v>
+      </c>
+      <c r="C226" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D226" t="s">
         <v>269</v>
-      </c>
-      <c r="C226" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D226" t="s">
-        <v>270</v>
       </c>
       <c r="E226" t="s">
         <v>8</v>
@@ -5786,13 +5783,13 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D227" t="s">
-        <v>272</v>
+        <v>221</v>
       </c>
       <c r="E227" t="s">
         <v>8</v>
@@ -5803,13 +5800,13 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D228" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="E228" t="s">
         <v>8</v>
@@ -5820,13 +5817,13 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D229" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="E229" t="s">
         <v>8</v>
@@ -5837,13 +5834,13 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D230" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="E230" t="s">
         <v>8</v>
@@ -5854,13 +5851,13 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D231" t="s">
-        <v>227</v>
+        <v>276</v>
       </c>
       <c r="E231" t="s">
         <v>8</v>
@@ -5871,13 +5868,13 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D232" t="s">
-        <v>281</v>
+        <v>221</v>
       </c>
       <c r="E232" t="s">
         <v>8</v>
@@ -5888,13 +5885,13 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D233" t="s">
-        <v>283</v>
+        <v>234</v>
       </c>
       <c r="E233" t="s">
         <v>8</v>
@@ -5905,13 +5902,13 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D234" t="s">
-        <v>285</v>
+        <v>219</v>
       </c>
       <c r="E234" t="s">
         <v>8</v>
@@ -5922,13 +5919,13 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D235" t="s">
-        <v>287</v>
+        <v>254</v>
       </c>
       <c r="E235" t="s">
         <v>8</v>
@@ -5939,13 +5936,13 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D236" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E236" t="s">
         <v>8</v>
@@ -5956,13 +5953,13 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D237" t="s">
-        <v>291</v>
+        <v>221</v>
       </c>
       <c r="E237" t="s">
         <v>8</v>
@@ -5973,13 +5970,13 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D238" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="E238" t="s">
         <v>8</v>
@@ -5990,13 +5987,13 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D239" t="s">
-        <v>190</v>
+        <v>287</v>
       </c>
       <c r="E239" t="s">
         <v>8</v>
@@ -6007,13 +6004,13 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D240" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="E240" t="s">
         <v>8</v>
@@ -6024,13 +6021,13 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D241" t="s">
-        <v>297</v>
+        <v>219</v>
       </c>
       <c r="E241" t="s">
         <v>8</v>
@@ -6041,13 +6038,13 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D242" t="s">
-        <v>267</v>
+        <v>291</v>
       </c>
       <c r="E242" t="s">
         <v>8</v>
@@ -6058,13 +6055,13 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D243" t="s">
-        <v>256</v>
+        <v>293</v>
       </c>
       <c r="E243" t="s">
         <v>8</v>
@@ -6075,13 +6072,13 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D244" t="s">
-        <v>301</v>
+        <v>264</v>
       </c>
       <c r="E244" t="s">
         <v>8</v>
@@ -6092,13 +6089,13 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D245" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E245" t="s">
         <v>8</v>
@@ -6109,13 +6106,13 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D246" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="E246" t="s">
         <v>8</v>
@@ -6126,13 +6123,13 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D247" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="E247" t="s">
         <v>8</v>
@@ -6143,13 +6140,13 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D248" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="E248" t="s">
         <v>8</v>
@@ -6160,13 +6157,13 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D249" t="s">
-        <v>256</v>
+        <v>297</v>
       </c>
       <c r="E249" t="s">
         <v>8</v>
@@ -6177,13 +6174,13 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D250" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E250" t="s">
         <v>8</v>
@@ -6194,13 +6191,13 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D251" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="E251" t="s">
         <v>8</v>
@@ -6211,13 +6208,13 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D252" t="s">
-        <v>252</v>
+        <v>291</v>
       </c>
       <c r="E252" t="s">
         <v>8</v>
@@ -6228,13 +6225,13 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D253" t="s">
-        <v>223</v>
+        <v>308</v>
       </c>
       <c r="E253" t="s">
         <v>8</v>
@@ -6245,13 +6242,13 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D254" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="E254" t="s">
         <v>8</v>
@@ -6262,13 +6259,13 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D255" t="s">
-        <v>247</v>
+        <v>312</v>
       </c>
       <c r="E255" t="s">
         <v>8</v>
@@ -6279,13 +6276,13 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D256" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="E256" t="s">
         <v>8</v>
@@ -6296,13 +6293,13 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D257" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E257" t="s">
         <v>8</v>
@@ -6313,13 +6310,13 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D258" t="s">
-        <v>322</v>
+        <v>264</v>
       </c>
       <c r="E258" t="s">
         <v>8</v>
@@ -6330,13 +6327,13 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D259" t="s">
-        <v>202</v>
+        <v>276</v>
       </c>
       <c r="E259" t="s">
         <v>8</v>
@@ -6347,13 +6344,13 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D260" t="s">
-        <v>325</v>
+        <v>274</v>
       </c>
       <c r="E260" t="s">
         <v>8</v>
@@ -6364,13 +6361,13 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D261" t="s">
-        <v>206</v>
+        <v>321</v>
       </c>
       <c r="E261" t="s">
         <v>8</v>
@@ -6381,13 +6378,13 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D262" t="s">
-        <v>276</v>
+        <v>308</v>
       </c>
       <c r="E262" t="s">
         <v>8</v>
@@ -6398,13 +6395,13 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D263" t="s">
-        <v>329</v>
+        <v>234</v>
       </c>
       <c r="E263" t="s">
         <v>8</v>
@@ -6415,13 +6412,13 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D264" t="s">
-        <v>281</v>
+        <v>316</v>
       </c>
       <c r="E264" t="s">
         <v>8</v>
@@ -6432,13 +6429,13 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D265" t="s">
-        <v>332</v>
+        <v>234</v>
       </c>
       <c r="E265" t="s">
         <v>8</v>
@@ -6449,13 +6446,13 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D266" t="s">
-        <v>291</v>
+        <v>248</v>
       </c>
       <c r="E266" t="s">
         <v>8</v>
@@ -6466,13 +6463,13 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D267" t="s">
-        <v>219</v>
+        <v>328</v>
       </c>
       <c r="E267" t="s">
         <v>8</v>
@@ -6483,13 +6480,13 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D268" t="s">
-        <v>318</v>
+        <v>204</v>
       </c>
       <c r="E268" t="s">
         <v>8</v>
@@ -6500,13 +6497,13 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D269" t="s">
-        <v>337</v>
+        <v>215</v>
       </c>
       <c r="E269" t="s">
         <v>8</v>
@@ -6517,13 +6514,13 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D270" t="s">
-        <v>322</v>
+        <v>303</v>
       </c>
       <c r="E270" t="s">
         <v>8</v>
@@ -6534,13 +6531,13 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D271" t="s">
-        <v>340</v>
+        <v>198</v>
       </c>
       <c r="E271" t="s">
         <v>8</v>
@@ -6551,13 +6548,13 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D272" t="s">
-        <v>239</v>
+        <v>334</v>
       </c>
       <c r="E272" t="s">
         <v>8</v>
@@ -6568,13 +6565,13 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D273" t="s">
-        <v>308</v>
+        <v>336</v>
       </c>
       <c r="E273" t="s">
         <v>8</v>
@@ -6585,13 +6582,13 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D274" t="s">
-        <v>223</v>
+        <v>338</v>
       </c>
       <c r="E274" t="s">
         <v>8</v>
@@ -6602,13 +6599,13 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D275" t="s">
-        <v>196</v>
+        <v>321</v>
       </c>
       <c r="E275" t="s">
         <v>8</v>
@@ -6619,13 +6616,13 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D276" t="s">
-        <v>297</v>
+        <v>202</v>
       </c>
       <c r="E276" t="s">
         <v>8</v>
@@ -6636,13 +6633,13 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D277" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="E277" t="s">
         <v>8</v>
@@ -6653,13 +6650,13 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D278" t="s">
-        <v>239</v>
+        <v>334</v>
       </c>
       <c r="E278" t="s">
         <v>8</v>
@@ -6670,13 +6667,13 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D279" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="E279" t="s">
         <v>8</v>
@@ -6687,13 +6684,13 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D280" t="s">
-        <v>235</v>
+        <v>282</v>
       </c>
       <c r="E280" t="s">
         <v>8</v>
@@ -6704,13 +6701,13 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D281" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="E281" t="s">
         <v>8</v>
@@ -6721,13 +6718,13 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D282" t="s">
-        <v>239</v>
+        <v>200</v>
       </c>
       <c r="E282" t="s">
         <v>8</v>
@@ -6738,13 +6735,13 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D283" t="s">
-        <v>355</v>
+        <v>240</v>
       </c>
       <c r="E283" t="s">
         <v>8</v>
@@ -6755,13 +6752,13 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D284" t="s">
-        <v>337</v>
+        <v>308</v>
       </c>
       <c r="E284" t="s">
         <v>8</v>
@@ -6772,13 +6769,13 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D285" t="s">
-        <v>235</v>
+        <v>352</v>
       </c>
       <c r="E285" t="s">
         <v>8</v>
@@ -6789,13 +6786,13 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D286" t="s">
-        <v>206</v>
+        <v>354</v>
       </c>
       <c r="E286" t="s">
         <v>8</v>
@@ -6806,13 +6803,13 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D287" t="s">
-        <v>289</v>
+        <v>308</v>
       </c>
       <c r="E287" t="s">
         <v>8</v>
@@ -6823,13 +6820,13 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D288" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="E288" t="s">
         <v>8</v>
@@ -6840,13 +6837,13 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D289" t="s">
-        <v>211</v>
+        <v>258</v>
       </c>
       <c r="E289" t="s">
         <v>8</v>
@@ -6857,13 +6854,13 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D290" t="s">
-        <v>204</v>
+        <v>342</v>
       </c>
       <c r="E290" t="s">
         <v>8</v>
@@ -6874,13 +6871,13 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D291" t="s">
-        <v>365</v>
+        <v>328</v>
       </c>
       <c r="E291" t="s">
         <v>8</v>
@@ -6891,13 +6888,13 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D292" t="s">
-        <v>276</v>
+        <v>240</v>
       </c>
       <c r="E292" t="s">
         <v>8</v>
@@ -6908,13 +6905,13 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D293" t="s">
-        <v>308</v>
+        <v>352</v>
       </c>
       <c r="E293" t="s">
         <v>8</v>
@@ -6925,13 +6922,13 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D294" t="s">
-        <v>239</v>
+        <v>345</v>
       </c>
       <c r="E294" t="s">
         <v>8</v>
@@ -6942,13 +6939,13 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D295" t="s">
-        <v>370</v>
+        <v>338</v>
       </c>
       <c r="E295" t="s">
         <v>8</v>
@@ -6959,13 +6956,13 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D296" t="s">
-        <v>235</v>
+        <v>365</v>
       </c>
       <c r="E296" t="s">
         <v>8</v>
@@ -6976,13 +6973,13 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D297" t="s">
-        <v>192</v>
+        <v>352</v>
       </c>
       <c r="E297" t="s">
         <v>8</v>
@@ -6993,13 +6990,13 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D298" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="E298" t="s">
         <v>8</v>
@@ -7010,13 +7007,13 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D299" t="s">
-        <v>211</v>
+        <v>321</v>
       </c>
       <c r="E299" t="s">
         <v>8</v>
@@ -7027,13 +7024,13 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D300" t="s">
-        <v>376</v>
+        <v>314</v>
       </c>
       <c r="E300" t="s">
         <v>8</v>
@@ -7044,13 +7041,13 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D301" t="s">
-        <v>318</v>
+        <v>236</v>
       </c>
       <c r="E301" t="s">
         <v>8</v>
@@ -7061,13 +7058,13 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D302" t="s">
-        <v>262</v>
+        <v>206</v>
       </c>
       <c r="E302" t="s">
         <v>8</v>
@@ -7078,13 +7075,13 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D303" t="s">
-        <v>337</v>
+        <v>373</v>
       </c>
       <c r="E303" t="s">
         <v>8</v>
@@ -7095,13 +7092,13 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D304" t="s">
-        <v>278</v>
+        <v>375</v>
       </c>
       <c r="E304" t="s">
         <v>8</v>
@@ -7112,13 +7109,13 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D305" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="E305" t="s">
         <v>8</v>
@@ -7129,13 +7126,13 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D306" t="s">
-        <v>245</v>
+        <v>210</v>
       </c>
       <c r="E306" t="s">
         <v>8</v>
@@ -7146,13 +7143,13 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D307" t="s">
-        <v>239</v>
+        <v>321</v>
       </c>
       <c r="E307" t="s">
         <v>8</v>
@@ -7163,13 +7160,13 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D308" t="s">
-        <v>227</v>
+        <v>310</v>
       </c>
       <c r="E308" t="s">
         <v>8</v>
@@ -7180,13 +7177,13 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D309" t="s">
-        <v>223</v>
+        <v>342</v>
       </c>
       <c r="E309" t="s">
         <v>8</v>
@@ -7197,13 +7194,13 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D310" t="s">
-        <v>247</v>
+        <v>383</v>
       </c>
       <c r="E310" t="s">
         <v>8</v>
@@ -7214,13 +7211,13 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D311" t="s">
-        <v>350</v>
+        <v>314</v>
       </c>
       <c r="E311" t="s">
         <v>8</v>
@@ -7231,13 +7228,13 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D312" t="s">
-        <v>260</v>
+        <v>386</v>
       </c>
       <c r="E312" t="s">
         <v>8</v>
@@ -7248,13 +7245,13 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D313" t="s">
-        <v>241</v>
+        <v>388</v>
       </c>
       <c r="E313" t="s">
         <v>8</v>
@@ -7265,13 +7262,13 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D314" t="s">
-        <v>392</v>
+        <v>293</v>
       </c>
       <c r="E314" t="s">
         <v>8</v>
@@ -7282,13 +7279,13 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D315" t="s">
-        <v>192</v>
+        <v>391</v>
       </c>
       <c r="E315" t="s">
         <v>8</v>
@@ -7299,13 +7296,13 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D316" t="s">
-        <v>223</v>
+        <v>393</v>
       </c>
       <c r="E316" t="s">
         <v>8</v>
@@ -7316,13 +7313,13 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
+        <v>394</v>
+      </c>
+      <c r="C317" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D317" t="s">
         <v>395</v>
-      </c>
-      <c r="C317" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D317" t="s">
-        <v>204</v>
       </c>
       <c r="E317" t="s">
         <v>8</v>
@@ -7339,7 +7336,7 @@
         <v>6</v>
       </c>
       <c r="D318" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="E318" t="s">
         <v>8</v>
@@ -7356,7 +7353,7 @@
         <v>6</v>
       </c>
       <c r="D319" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="E319" t="s">
         <v>8</v>
@@ -7373,7 +7370,7 @@
         <v>6</v>
       </c>
       <c r="D320" t="s">
-        <v>399</v>
+        <v>342</v>
       </c>
       <c r="E320" t="s">
         <v>8</v>
@@ -7384,13 +7381,13 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D321" t="s">
-        <v>329</v>
+        <v>254</v>
       </c>
       <c r="E321" t="s">
         <v>8</v>
@@ -7401,13 +7398,13 @@
         <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D322" t="s">
-        <v>241</v>
+        <v>303</v>
       </c>
       <c r="E322" t="s">
         <v>8</v>
@@ -7418,13 +7415,13 @@
         <v>322</v>
       </c>
       <c r="B323" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D323" t="s">
-        <v>403</v>
+        <v>293</v>
       </c>
       <c r="E323" t="s">
         <v>8</v>
@@ -7435,13 +7432,13 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D324" t="s">
-        <v>270</v>
+        <v>403</v>
       </c>
       <c r="E324" t="s">
         <v>8</v>
@@ -7452,13 +7449,13 @@
         <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D325" t="s">
-        <v>315</v>
+        <v>236</v>
       </c>
       <c r="E325" t="s">
         <v>8</v>
@@ -7469,13 +7466,13 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
+        <v>405</v>
+      </c>
+      <c r="C326" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D326" t="s">
         <v>406</v>
-      </c>
-      <c r="C326" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D326" t="s">
-        <v>227</v>
       </c>
       <c r="E326" t="s">
         <v>8</v>
@@ -7492,7 +7489,7 @@
         <v>6</v>
       </c>
       <c r="D327" t="s">
-        <v>408</v>
+        <v>287</v>
       </c>
       <c r="E327" t="s">
         <v>8</v>
@@ -7503,13 +7500,13 @@
         <v>327</v>
       </c>
       <c r="B328" t="s">
+        <v>408</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D328" t="s">
         <v>409</v>
-      </c>
-      <c r="C328" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D328" t="s">
-        <v>278</v>
       </c>
       <c r="E328" t="s">
         <v>8</v>
@@ -7526,7 +7523,7 @@
         <v>6</v>
       </c>
       <c r="D329" t="s">
-        <v>355</v>
+        <v>411</v>
       </c>
       <c r="E329" t="s">
         <v>8</v>
@@ -7537,13 +7534,13 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D330" t="s">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="E330" t="s">
         <v>8</v>
@@ -7554,13 +7551,13 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D331" t="s">
-        <v>413</v>
+        <v>206</v>
       </c>
       <c r="E331" t="s">
         <v>8</v>
@@ -7577,7 +7574,7 @@
         <v>6</v>
       </c>
       <c r="D332" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="E332" t="s">
         <v>8</v>
@@ -7594,7 +7591,7 @@
         <v>6</v>
       </c>
       <c r="D333" t="s">
-        <v>416</v>
+        <v>230</v>
       </c>
       <c r="E333" t="s">
         <v>8</v>
@@ -7605,13 +7602,13 @@
         <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D334" t="s">
-        <v>418</v>
+        <v>227</v>
       </c>
       <c r="E334" t="s">
         <v>8</v>
@@ -7622,13 +7619,13 @@
         <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D335" t="s">
-        <v>289</v>
+        <v>418</v>
       </c>
       <c r="E335" t="s">
         <v>8</v>
@@ -7639,13 +7636,13 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D336" t="s">
-        <v>332</v>
+        <v>210</v>
       </c>
       <c r="E336" t="s">
         <v>8</v>
@@ -7656,13 +7653,13 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D337" t="s">
-        <v>392</v>
+        <v>217</v>
       </c>
       <c r="E337" t="s">
         <v>8</v>
@@ -7673,13 +7670,13 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D338" t="s">
-        <v>423</v>
+        <v>282</v>
       </c>
       <c r="E338" t="s">
         <v>8</v>
@@ -7690,13 +7687,13 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D339" t="s">
-        <v>413</v>
+        <v>215</v>
       </c>
       <c r="E339" t="s">
         <v>8</v>
@@ -7707,13 +7704,13 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D340" t="s">
-        <v>306</v>
+        <v>352</v>
       </c>
       <c r="E340" t="s">
         <v>8</v>
@@ -7724,13 +7721,13 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D341" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="E341" t="s">
         <v>8</v>
@@ -7741,13 +7738,13 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D342" t="s">
-        <v>315</v>
+        <v>260</v>
       </c>
       <c r="E342" t="s">
         <v>8</v>
@@ -7758,13 +7755,13 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D343" t="s">
-        <v>430</v>
+        <v>345</v>
       </c>
       <c r="E343" t="s">
         <v>8</v>
@@ -7775,13 +7772,13 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D344" t="s">
-        <v>192</v>
+        <v>336</v>
       </c>
       <c r="E344" t="s">
         <v>8</v>
@@ -7792,13 +7789,13 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D345" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="E345" t="s">
         <v>8</v>
@@ -7809,13 +7806,13 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D346" t="s">
-        <v>434</v>
+        <v>236</v>
       </c>
       <c r="E346" t="s">
         <v>8</v>
@@ -7826,13 +7823,13 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D347" t="s">
-        <v>436</v>
+        <v>297</v>
       </c>
       <c r="E347" t="s">
         <v>8</v>
@@ -7843,13 +7840,13 @@
         <v>347</v>
       </c>
       <c r="B348" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D348" t="s">
-        <v>438</v>
+        <v>258</v>
       </c>
       <c r="E348" t="s">
         <v>8</v>
@@ -7860,13 +7857,13 @@
         <v>348</v>
       </c>
       <c r="B349" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D349" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="E349" t="s">
         <v>8</v>
@@ -7877,13 +7874,13 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D350" t="s">
-        <v>315</v>
+        <v>225</v>
       </c>
       <c r="E350" t="s">
         <v>8</v>
@@ -7894,13 +7891,13 @@
         <v>350</v>
       </c>
       <c r="B351" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D351" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="E351" t="s">
         <v>8</v>
@@ -7911,13 +7908,13 @@
         <v>351</v>
       </c>
       <c r="B352" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D352" t="s">
-        <v>267</v>
+        <v>393</v>
       </c>
       <c r="E352" t="s">
         <v>8</v>
@@ -7928,13 +7925,13 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D353" t="s">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="E353" t="s">
         <v>8</v>
@@ -7945,13 +7942,13 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D354" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="E354" t="s">
         <v>8</v>
@@ -7962,13 +7959,13 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D355" t="s">
-        <v>446</v>
+        <v>238</v>
       </c>
       <c r="E355" t="s">
         <v>8</v>
@@ -7979,13 +7976,13 @@
         <v>355</v>
       </c>
       <c r="B356" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D356" t="s">
-        <v>413</v>
+        <v>441</v>
       </c>
       <c r="E356" t="s">
         <v>8</v>
@@ -7996,13 +7993,13 @@
         <v>356</v>
       </c>
       <c r="B357" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D357" t="s">
-        <v>315</v>
+        <v>443</v>
       </c>
       <c r="E357" t="s">
         <v>8</v>
@@ -8013,13 +8010,13 @@
         <v>357</v>
       </c>
       <c r="B358" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D358" t="s">
-        <v>276</v>
+        <v>445</v>
       </c>
       <c r="E358" t="s">
         <v>8</v>
@@ -8030,13 +8027,13 @@
         <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D359" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E359" t="s">
         <v>8</v>
@@ -8047,13 +8044,13 @@
         <v>359</v>
       </c>
       <c r="B360" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D360" t="s">
-        <v>308</v>
+        <v>448</v>
       </c>
       <c r="E360" t="s">
         <v>8</v>
@@ -8064,13 +8061,13 @@
         <v>360</v>
       </c>
       <c r="B361" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D361" t="s">
-        <v>308</v>
+        <v>406</v>
       </c>
       <c r="E361" t="s">
         <v>8</v>
@@ -8081,13 +8078,13 @@
         <v>361</v>
       </c>
       <c r="B362" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D362" t="s">
-        <v>293</v>
+        <v>386</v>
       </c>
       <c r="E362" t="s">
         <v>8</v>
@@ -8098,13 +8095,13 @@
         <v>362</v>
       </c>
       <c r="B363" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D363" t="s">
-        <v>239</v>
+        <v>448</v>
       </c>
       <c r="E363" t="s">
         <v>8</v>
@@ -8115,13 +8112,13 @@
         <v>363</v>
       </c>
       <c r="B364" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D364" t="s">
-        <v>456</v>
+        <v>314</v>
       </c>
       <c r="E364" t="s">
         <v>8</v>
@@ -8132,13 +8129,13 @@
         <v>364</v>
       </c>
       <c r="B365" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D365" t="s">
-        <v>332</v>
+        <v>196</v>
       </c>
       <c r="E365" t="s">
         <v>8</v>
@@ -8149,13 +8146,13 @@
         <v>365</v>
       </c>
       <c r="B366" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D366" t="s">
-        <v>287</v>
+        <v>192</v>
       </c>
       <c r="E366" t="s">
         <v>8</v>
@@ -8166,13 +8163,13 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D367" t="s">
-        <v>262</v>
+        <v>223</v>
       </c>
       <c r="E367" t="s">
         <v>8</v>
@@ -8183,13 +8180,13 @@
         <v>367</v>
       </c>
       <c r="B368" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D368" t="s">
-        <v>256</v>
+        <v>221</v>
       </c>
       <c r="E368" t="s">
         <v>8</v>
@@ -8200,13 +8197,13 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D369" t="s">
-        <v>350</v>
+        <v>314</v>
       </c>
       <c r="E369" t="s">
         <v>8</v>
@@ -8217,13 +8214,13 @@
         <v>369</v>
       </c>
       <c r="B370" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D370" t="s">
-        <v>239</v>
+        <v>345</v>
       </c>
       <c r="E370" t="s">
         <v>8</v>
@@ -8234,13 +8231,13 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D371" t="s">
-        <v>416</v>
+        <v>219</v>
       </c>
       <c r="E371" t="s">
         <v>8</v>
@@ -8251,13 +8248,13 @@
         <v>371</v>
       </c>
       <c r="B372" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D372" t="s">
-        <v>355</v>
+        <v>334</v>
       </c>
       <c r="E372" t="s">
         <v>8</v>
@@ -8268,13 +8265,13 @@
         <v>372</v>
       </c>
       <c r="B373" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D373" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="E373" t="s">
         <v>8</v>
@@ -8285,13 +8282,13 @@
         <v>373</v>
       </c>
       <c r="B374" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D374" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="E374" t="s">
         <v>8</v>
@@ -8302,13 +8299,13 @@
         <v>374</v>
       </c>
       <c r="B375" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D375" t="s">
-        <v>297</v>
+        <v>242</v>
       </c>
       <c r="E375" t="s">
         <v>8</v>
@@ -8319,13 +8316,13 @@
         <v>375</v>
       </c>
       <c r="B376" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D376" t="s">
-        <v>416</v>
+        <v>365</v>
       </c>
       <c r="E376" t="s">
         <v>8</v>
@@ -8336,13 +8333,13 @@
         <v>376</v>
       </c>
       <c r="B377" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D377" t="s">
-        <v>301</v>
+        <v>466</v>
       </c>
       <c r="E377" t="s">
         <v>8</v>
@@ -8353,13 +8350,13 @@
         <v>377</v>
       </c>
       <c r="B378" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D378" t="s">
-        <v>202</v>
+        <v>262</v>
       </c>
       <c r="E378" t="s">
         <v>8</v>
@@ -8370,13 +8367,13 @@
         <v>378</v>
       </c>
       <c r="B379" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D379" t="s">
-        <v>350</v>
+        <v>328</v>
       </c>
       <c r="E379" t="s">
         <v>8</v>
@@ -8387,13 +8384,13 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D380" t="s">
-        <v>258</v>
+        <v>470</v>
       </c>
       <c r="E380" t="s">
         <v>8</v>
@@ -8404,13 +8401,13 @@
         <v>380</v>
       </c>
       <c r="B381" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D381" t="s">
-        <v>361</v>
+        <v>285</v>
       </c>
       <c r="E381" t="s">
         <v>8</v>
@@ -8421,13 +8418,13 @@
         <v>381</v>
       </c>
       <c r="B382" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D382" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="E382" t="s">
         <v>8</v>
@@ -8438,13 +8435,13 @@
         <v>382</v>
       </c>
       <c r="B383" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D383" t="s">
-        <v>276</v>
+        <v>393</v>
       </c>
       <c r="E383" t="s">
         <v>8</v>
@@ -8455,13 +8452,13 @@
         <v>383</v>
       </c>
       <c r="B384" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D384" t="s">
-        <v>430</v>
+        <v>217</v>
       </c>
       <c r="E384" t="s">
         <v>8</v>
@@ -8472,13 +8469,13 @@
         <v>384</v>
       </c>
       <c r="B385" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D385" t="s">
-        <v>206</v>
+        <v>476</v>
       </c>
       <c r="E385" t="s">
         <v>8</v>
@@ -8489,13 +8486,13 @@
         <v>385</v>
       </c>
       <c r="B386" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D386" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E386" t="s">
         <v>8</v>
@@ -8506,13 +8503,13 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D387" t="s">
-        <v>365</v>
+        <v>204</v>
       </c>
       <c r="E387" t="s">
         <v>8</v>
@@ -8523,13 +8520,13 @@
         <v>387</v>
       </c>
       <c r="B388" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D388" t="s">
-        <v>278</v>
+        <v>441</v>
       </c>
       <c r="E388" t="s">
         <v>8</v>
@@ -8540,13 +8537,13 @@
         <v>388</v>
       </c>
       <c r="B389" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D389" t="s">
-        <v>482</v>
+        <v>236</v>
       </c>
       <c r="E389" t="s">
         <v>8</v>
@@ -8557,13 +8554,13 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D390" t="s">
-        <v>209</v>
+        <v>328</v>
       </c>
       <c r="E390" t="s">
         <v>8</v>
@@ -8574,13 +8571,13 @@
         <v>390</v>
       </c>
       <c r="B391" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D391" t="s">
-        <v>301</v>
+        <v>470</v>
       </c>
       <c r="E391" t="s">
         <v>8</v>
@@ -8591,13 +8588,13 @@
         <v>391</v>
       </c>
       <c r="B392" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D392" t="s">
-        <v>281</v>
+        <v>321</v>
       </c>
       <c r="E392" t="s">
         <v>8</v>
@@ -8608,13 +8605,13 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D393" t="s">
-        <v>340</v>
+        <v>223</v>
       </c>
       <c r="E393" t="s">
         <v>8</v>
@@ -8625,13 +8622,13 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D394" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="E394" t="s">
         <v>8</v>
@@ -8642,13 +8639,13 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D395" t="s">
-        <v>241</v>
+        <v>487</v>
       </c>
       <c r="E395" t="s">
         <v>8</v>
@@ -8659,13 +8656,13 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
+        <v>488</v>
+      </c>
+      <c r="C396" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D396" t="s">
         <v>489</v>
-      </c>
-      <c r="C396" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D396" t="s">
-        <v>245</v>
       </c>
       <c r="E396" t="s">
         <v>8</v>
@@ -8682,7 +8679,7 @@
         <v>6</v>
       </c>
       <c r="D397" t="s">
-        <v>337</v>
+        <v>466</v>
       </c>
       <c r="E397" t="s">
         <v>8</v>
@@ -8699,7 +8696,7 @@
         <v>6</v>
       </c>
       <c r="D398" t="s">
-        <v>337</v>
+        <v>269</v>
       </c>
       <c r="E398" t="s">
         <v>8</v>
@@ -8716,7 +8713,7 @@
         <v>6</v>
       </c>
       <c r="D399" t="s">
-        <v>493</v>
+        <v>373</v>
       </c>
       <c r="E399" t="s">
         <v>8</v>
@@ -8727,13 +8724,13 @@
         <v>399</v>
       </c>
       <c r="B400" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D400" t="s">
-        <v>209</v>
+        <v>489</v>
       </c>
       <c r="E400" t="s">
         <v>8</v>
@@ -8744,13 +8741,13 @@
         <v>400</v>
       </c>
       <c r="B401" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D401" t="s">
-        <v>438</v>
+        <v>310</v>
       </c>
       <c r="E401" t="s">
         <v>8</v>
@@ -8769,47 +8766,47 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B1" t="s">
         <v>496</v>
-      </c>
-      <c r="B1" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>497</v>
+      </c>
+      <c r="B2" t="s">
         <v>498</v>
-      </c>
-      <c r="B2" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>499</v>
+      </c>
+      <c r="B3" t="s">
         <v>500</v>
-      </c>
-      <c r="B3" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>501</v>
+      </c>
+      <c r="B4" t="s">
         <v>502</v>
-      </c>
-      <c r="B4" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>503</v>
+      </c>
+      <c r="B5" t="s">
         <v>504</v>
-      </c>
-      <c r="B5" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B6">
         <v>400</v>
@@ -8817,7 +8814,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B7">
         <v>400</v>
@@ -8825,7 +8822,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -8833,7 +8830,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -8841,10 +8838,10 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>509</v>
+      </c>
+      <c r="B10" t="s">
         <v>510</v>
-      </c>
-      <c r="B10" t="s">
-        <v>511</v>
       </c>
     </row>
   </sheetData>

--- a/reports/backend/Excel/Automation_Test_Report.xlsx
+++ b/reports/backend/Excel/Automation_Test_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="512">
   <si>
     <t>#</t>
   </si>
@@ -35,18 +35,18 @@
     <t>PASSED</t>
   </si>
   <si>
+    <t>0.001</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Smart Admission Backend — Authentication Tests BT-002 | Firebase config has authDomain</t>
+  </si>
+  <si>
     <t>0.000</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>Smart Admission Backend — Authentication Tests BT-002 | Firebase config has authDomain</t>
-  </si>
-  <si>
-    <t>0.001</t>
-  </si>
-  <si>
     <t>Smart Admission Backend — Authentication Tests BT-003 | Firebase config has projectId</t>
   </si>
   <si>
@@ -584,906 +584,909 @@
     <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field apiKey (Verify Point #180)</t>
   </si>
   <si>
+    <t>0.062</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #181)</t>
+  </si>
+  <si>
+    <t>0.053</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #182)</t>
+  </si>
+  <si>
+    <t>0.058</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #183)</t>
+  </si>
+  <si>
+    <t>0.064</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #184)</t>
+  </si>
+  <si>
+    <t>0.071</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #185)</t>
+  </si>
+  <si>
+    <t>0.045</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #186)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #187)</t>
+  </si>
+  <si>
+    <t>0.027</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #188)</t>
+  </si>
+  <si>
+    <t>0.113</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #189)</t>
+  </si>
+  <si>
+    <t>0.116</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #190)</t>
+  </si>
+  <si>
+    <t>0.119</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #191)</t>
+  </si>
+  <si>
+    <t>0.077</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #192)</t>
+  </si>
+  <si>
+    <t>0.085</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #193)</t>
+  </si>
+  <si>
+    <t>0.022</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #194)</t>
+  </si>
+  <si>
+    <t>0.112</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #195)</t>
+  </si>
+  <si>
+    <t>0.021</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #196)</t>
+  </si>
+  <si>
+    <t>0.025</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #197)</t>
+  </si>
+  <si>
+    <t>0.050</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #198)</t>
+  </si>
+  <si>
+    <t>0.092</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #199)</t>
+  </si>
+  <si>
+    <t>0.107</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #200)</t>
+  </si>
+  <si>
+    <t>0.074</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #201)</t>
+  </si>
+  <si>
+    <t>0.075</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #202)</t>
+  </si>
+  <si>
+    <t>0.083</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #203)</t>
+  </si>
+  <si>
+    <t>0.084</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #204)</t>
+  </si>
+  <si>
+    <t>0.114</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #205)</t>
+  </si>
+  <si>
+    <t>0.063</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #206)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #207)</t>
+  </si>
+  <si>
+    <t>0.040</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #208)</t>
+  </si>
+  <si>
+    <t>0.079</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #209)</t>
+  </si>
+  <si>
+    <t>0.024</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #210)</t>
+  </si>
+  <si>
+    <t>0.041</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #211)</t>
+  </si>
+  <si>
+    <t>0.103</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code XSS-injection (Verify Point #212)</t>
+  </si>
+  <si>
     <t>0.096</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #181)</t>
-  </si>
-  <si>
-    <t>0.076</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #182)</t>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #213)</t>
+  </si>
+  <si>
+    <t>0.061</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for CSRF-token (Verify Point #214)</t>
+  </si>
+  <si>
+    <t>0.068</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated CORS-origin (Verify Point #215)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for CSP-header (Verify Point #216)</t>
+  </si>
+  <si>
+    <t>0.048</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at session-token (Verify Point #217)</t>
+  </si>
+  <si>
+    <t>0.070</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users-ref (Verify Point #218)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for items-ref (Verify Point #219)</t>
+  </si>
+  <si>
+    <t>0.072</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field de-DE (Verify Point #220)</t>
+  </si>
+  <si>
+    <t>0.104</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for fr-FR (Verify Point #221)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ja-JP (Verify Point #222)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for pt-BR (Verify Point #223)</t>
+  </si>
+  <si>
+    <t>0.034</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of it-IT (Verify Point #224)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for apiKey (Verify Point #225)</t>
+  </si>
+  <si>
+    <t>0.044</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for authDomain (Verify Point #226)</t>
+  </si>
+  <si>
+    <t>0.059</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value projectId (Verify Point #227)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session storageBucket (Verify Point #228)</t>
+  </si>
+  <si>
+    <t>0.099</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier messagingSenderId (Verify Point #229)</t>
+  </si>
+  <si>
+    <t>0.033</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region appId (Verify Point #230)</t>
+  </si>
+  <si>
+    <t>0.023</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for name (Verify Point #231)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code id (Verify Point #232)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource fees.min (Verify Point #233)</t>
+  </si>
+  <si>
+    <t>0.039</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for fees.max (Verify Point #234)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated courses (Verify Point #235)</t>
+  </si>
+  <si>
+    <t>0.026</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for ranking.nirf (Verify Point #236)</t>
+  </si>
+  <si>
+    <t>0.102</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at type (Verify Point #237)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users/uid001 (Verify Point #238)</t>
+  </si>
+  <si>
+    <t>0.032</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for colleges/c001 (Verify Point #239)</t>
+  </si>
+  <si>
+    <t>0.056</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field prompt-length (Verify Point #240)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for session-id-1 (Verify Point #241)</t>
+  </si>
+  <si>
+    <t>0.098</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ₹1L (Verify Point #242)</t>
+  </si>
+  <si>
+    <t>0.060</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for B.Tech (Verify Point #243)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of 4 years (Verify Point #244)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for Tamil Nadu (Verify Point #245)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for Chennai (Verify Point #246)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value llama3-8b (Verify Point #247)</t>
+  </si>
+  <si>
+    <t>0.065</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session email (Verify Point #248)</t>
+  </si>
+  <si>
+    <t>0.049</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier password (Verify Point #249)</t>
+  </si>
+  <si>
+    <t>0.052</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region displayName (Verify Point #250)</t>
+  </si>
+  <si>
+    <t>0.081</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for savedColleges (Verify Point #251)</t>
+  </si>
+  <si>
+    <t>0.057</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code createdAt (Verify Point #252)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource firebase-auth (Verify Point #253)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for firestore-read (Verify Point #254)</t>
+  </si>
+  <si>
+    <t>0.089</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated groq-api (Verify Point #255)</t>
+  </si>
+  <si>
+    <t>0.037</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for college-list (Verify Point #256)</t>
   </si>
   <si>
     <t>0.038</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #183)</t>
-  </si>
-  <si>
-    <t>0.035</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #184)</t>
-  </si>
-  <si>
-    <t>0.046</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #185)</t>
-  </si>
-  <si>
-    <t>0.048</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #186)</t>
-  </si>
-  <si>
-    <t>0.088</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #187)</t>
-  </si>
-  <si>
-    <t>0.098</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #188)</t>
-  </si>
-  <si>
-    <t>0.059</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #189)</t>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at XSS-injection (Verify Point #257)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation SQL-injection (Verify Point #258)</t>
   </si>
   <si>
     <t>0.036</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #190)</t>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for CSRF-token (Verify Point #259)</t>
+  </si>
+  <si>
+    <t>0.091</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field CORS-origin (Verify Point #260)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for CSP-header (Verify Point #261)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for session-token (Verify Point #262)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users-ref (Verify Point #263)</t>
+  </si>
+  <si>
+    <t>0.030</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of items-ref (Verify Point #264)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for de-DE (Verify Point #265)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for fr-FR (Verify Point #266)</t>
   </si>
   <si>
     <t>0.105</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #191)</t>
-  </si>
-  <si>
-    <t>0.112</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #192)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #193)</t>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ja-JP (Verify Point #267)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session pt-BR (Verify Point #268)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier it-IT (Verify Point #269)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region apiKey (Verify Point #270)</t>
+  </si>
+  <si>
+    <t>0.082</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for authDomain (Verify Point #271)</t>
+  </si>
+  <si>
+    <t>0.055</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code projectId (Verify Point #272)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource storageBucket (Verify Point #273)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for messagingSenderId (Verify Point #274)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated appId (Verify Point #275)</t>
+  </si>
+  <si>
+    <t>0.097</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for name (Verify Point #276)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at id (Verify Point #277)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation fees.min (Verify Point #278)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for fees.max (Verify Point #279)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field courses (Verify Point #280)</t>
+  </si>
+  <si>
+    <t>0.115</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for ranking.nirf (Verify Point #281)</t>
+  </si>
+  <si>
+    <t>0.108</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for type (Verify Point #282)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users/uid001 (Verify Point #283)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of colleges/c001 (Verify Point #284)</t>
+  </si>
+  <si>
+    <t>0.109</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for prompt-length (Verify Point #285)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for session-id-1 (Verify Point #286)</t>
+  </si>
+  <si>
+    <t>0.090</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ₹1L (Verify Point #287)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session B.Tech (Verify Point #288)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier 4 years (Verify Point #289)</t>
+  </si>
+  <si>
+    <t>0.073</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region Tamil Nadu (Verify Point #290)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for Chennai (Verify Point #291)</t>
+  </si>
+  <si>
+    <t>0.051</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code llama3-8b (Verify Point #292)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource email (Verify Point #293)</t>
+  </si>
+  <si>
+    <t>0.087</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for password (Verify Point #294)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated displayName (Verify Point #295)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for savedColleges (Verify Point #296)</t>
+  </si>
+  <si>
+    <t>0.042</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at createdAt (Verify Point #297)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation firebase-auth (Verify Point #298)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for firestore-read (Verify Point #299)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field groq-api (Verify Point #300)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for college-list (Verify Point #301)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for XSS-injection (Verify Point #302)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for SQL-injection (Verify Point #303)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of CSRF-token (Verify Point #304)</t>
+  </si>
+  <si>
+    <t>0.069</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for CORS-origin (Verify Point #305)</t>
+  </si>
+  <si>
+    <t>0.111</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for CSP-header (Verify Point #306)</t>
+  </si>
+  <si>
+    <t>0.086</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value session-token (Verify Point #307)</t>
+  </si>
+  <si>
+    <t>0.043</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users-ref (Verify Point #308)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier items-ref (Verify Point #309)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region de-DE (Verify Point #310)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for fr-FR (Verify Point #311)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ja-JP (Verify Point #312)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource pt-BR (Verify Point #313)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for it-IT (Verify Point #314)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated apiKey (Verify Point #315)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for authDomain (Verify Point #316)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at projectId (Verify Point #317)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation storageBucket (Verify Point #318)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for messagingSenderId (Verify Point #319)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field appId (Verify Point #320)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for name (Verify Point #321)</t>
+  </si>
+  <si>
+    <t>0.067</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for id (Verify Point #322)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for fees.min (Verify Point #323)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of fees.max (Verify Point #324)</t>
+  </si>
+  <si>
+    <t>0.093</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for courses (Verify Point #325)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for ranking.nirf (Verify Point #326)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value type (Verify Point #327)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users/uid001 (Verify Point #328)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier colleges/c001 (Verify Point #329)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region prompt-length (Verify Point #330)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for session-id-1 (Verify Point #331)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ₹1L (Verify Point #332)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource B.Tech (Verify Point #333)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for 4 years (Verify Point #334)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated Tamil Nadu (Verify Point #335)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for Chennai (Verify Point #336)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at llama3-8b (Verify Point #337)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation email (Verify Point #338)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for password (Verify Point #339)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field displayName (Verify Point #340)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for savedColleges (Verify Point #341)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for createdAt (Verify Point #342)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for firebase-auth (Verify Point #343)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of firestore-read (Verify Point #344)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for groq-api (Verify Point #345)</t>
+  </si>
+  <si>
+    <t>0.031</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for college-list (Verify Point #346)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value XSS-injection (Verify Point #347)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session SQL-injection (Verify Point #348)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier CSRF-token (Verify Point #349)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region CORS-origin (Verify Point #350)</t>
+  </si>
+  <si>
+    <t>0.047</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for CSP-header (Verify Point #351)</t>
+  </si>
+  <si>
+    <t>0.020</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code session-token (Verify Point #352)</t>
+  </si>
+  <si>
+    <t>0.106</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users-ref (Verify Point #353)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for items-ref (Verify Point #354)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated de-DE (Verify Point #355)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for fr-FR (Verify Point #356)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ja-JP (Verify Point #357)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation pt-BR (Verify Point #358)</t>
+  </si>
+  <si>
+    <t>0.028</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for it-IT (Verify Point #359)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field apiKey (Verify Point #360)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #361)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #362)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #363)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #364)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #365)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #366)</t>
+  </si>
+  <si>
+    <t>0.095</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #367)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #368)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #369)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #370)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #371)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #372)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #373)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #374)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #375)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #376)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #377)</t>
   </si>
   <si>
     <t>0.078</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #194)</t>
-  </si>
-  <si>
-    <t>0.119</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #195)</t>
-  </si>
-  <si>
-    <t>0.114</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #196)</t>
-  </si>
-  <si>
-    <t>0.054</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #197)</t>
-  </si>
-  <si>
-    <t>0.068</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #198)</t>
-  </si>
-  <si>
-    <t>0.117</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #199)</t>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #378)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #379)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #380)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #381)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #382)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #383)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #384)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #385)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #386)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #387)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #388)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #389)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #390)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #391)</t>
   </si>
   <si>
     <t>0.101</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #200)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #201)</t>
-  </si>
-  <si>
-    <t>0.081</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #202)</t>
-  </si>
-  <si>
-    <t>0.066</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #203)</t>
-  </si>
-  <si>
-    <t>0.070</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #204)</t>
-  </si>
-  <si>
-    <t>0.030</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #205)</t>
-  </si>
-  <si>
-    <t>0.034</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #206)</t>
-  </si>
-  <si>
-    <t>0.072</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #207)</t>
-  </si>
-  <si>
-    <t>0.104</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #208)</t>
-  </si>
-  <si>
-    <t>0.073</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #209)</t>
-  </si>
-  <si>
-    <t>0.065</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #210)</t>
-  </si>
-  <si>
-    <t>0.061</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #211)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code XSS-injection (Verify Point #212)</t>
-  </si>
-  <si>
-    <t>0.050</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #213)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for CSRF-token (Verify Point #214)</t>
-  </si>
-  <si>
-    <t>0.067</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated CORS-origin (Verify Point #215)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for CSP-header (Verify Point #216)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at session-token (Verify Point #217)</t>
-  </si>
-  <si>
-    <t>0.045</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users-ref (Verify Point #218)</t>
-  </si>
-  <si>
-    <t>0.058</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for items-ref (Verify Point #219)</t>
-  </si>
-  <si>
-    <t>0.020</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field de-DE (Verify Point #220)</t>
-  </si>
-  <si>
-    <t>0.113</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for fr-FR (Verify Point #221)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ja-JP (Verify Point #222)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for pt-BR (Verify Point #223)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of it-IT (Verify Point #224)</t>
-  </si>
-  <si>
-    <t>0.108</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for apiKey (Verify Point #225)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for authDomain (Verify Point #226)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value projectId (Verify Point #227)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session storageBucket (Verify Point #228)</t>
-  </si>
-  <si>
-    <t>0.103</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier messagingSenderId (Verify Point #229)</t>
-  </si>
-  <si>
-    <t>0.055</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region appId (Verify Point #230)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for name (Verify Point #231)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code id (Verify Point #232)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource fees.min (Verify Point #233)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for fees.max (Verify Point #234)</t>
-  </si>
-  <si>
-    <t>0.063</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated courses (Verify Point #235)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for ranking.nirf (Verify Point #236)</t>
-  </si>
-  <si>
-    <t>0.100</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at type (Verify Point #237)</t>
-  </si>
-  <si>
-    <t>0.023</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users/uid001 (Verify Point #238)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for colleges/c001 (Verify Point #239)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field prompt-length (Verify Point #240)</t>
-  </si>
-  <si>
-    <t>0.109</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for session-id-1 (Verify Point #241)</t>
-  </si>
-  <si>
-    <t>0.086</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ₹1L (Verify Point #242)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for B.Tech (Verify Point #243)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of 4 years (Verify Point #244)</t>
-  </si>
-  <si>
-    <t>0.049</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for Tamil Nadu (Verify Point #245)</t>
-  </si>
-  <si>
-    <t>0.039</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for Chennai (Verify Point #246)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value llama3-8b (Verify Point #247)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session email (Verify Point #248)</t>
-  </si>
-  <si>
-    <t>0.087</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier password (Verify Point #249)</t>
-  </si>
-  <si>
-    <t>0.069</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region displayName (Verify Point #250)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for savedColleges (Verify Point #251)</t>
-  </si>
-  <si>
-    <t>0.062</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code createdAt (Verify Point #252)</t>
-  </si>
-  <si>
-    <t>0.064</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource firebase-auth (Verify Point #253)</t>
-  </si>
-  <si>
-    <t>0.116</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for firestore-read (Verify Point #254)</t>
-  </si>
-  <si>
-    <t>0.082</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated groq-api (Verify Point #255)</t>
-  </si>
-  <si>
-    <t>0.021</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for college-list (Verify Point #256)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at XSS-injection (Verify Point #257)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation SQL-injection (Verify Point #258)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for CSRF-token (Verify Point #259)</t>
-  </si>
-  <si>
-    <t>0.074</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field CORS-origin (Verify Point #260)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for CSP-header (Verify Point #261)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for session-token (Verify Point #262)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users-ref (Verify Point #263)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of items-ref (Verify Point #264)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for de-DE (Verify Point #265)</t>
-  </si>
-  <si>
-    <t>0.041</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for fr-FR (Verify Point #266)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ja-JP (Verify Point #267)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session pt-BR (Verify Point #268)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier it-IT (Verify Point #269)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region apiKey (Verify Point #270)</t>
-  </si>
-  <si>
-    <t>0.106</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for authDomain (Verify Point #271)</t>
-  </si>
-  <si>
-    <t>0.042</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code projectId (Verify Point #272)</t>
-  </si>
-  <si>
-    <t>0.043</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource storageBucket (Verify Point #273)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for messagingSenderId (Verify Point #274)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated appId (Verify Point #275)</t>
-  </si>
-  <si>
-    <t>0.097</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for name (Verify Point #276)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at id (Verify Point #277)</t>
-  </si>
-  <si>
-    <t>0.092</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation fees.min (Verify Point #278)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for fees.max (Verify Point #279)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field courses (Verify Point #280)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for ranking.nirf (Verify Point #281)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for type (Verify Point #282)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users/uid001 (Verify Point #283)</t>
-  </si>
-  <si>
-    <t>0.057</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of colleges/c001 (Verify Point #284)</t>
-  </si>
-  <si>
-    <t>0.077</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for prompt-length (Verify Point #285)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for session-id-1 (Verify Point #286)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ₹1L (Verify Point #287)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session B.Tech (Verify Point #288)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier 4 years (Verify Point #289)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region Tamil Nadu (Verify Point #290)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for Chennai (Verify Point #291)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code llama3-8b (Verify Point #292)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource email (Verify Point #293)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for password (Verify Point #294)</t>
-  </si>
-  <si>
-    <t>0.085</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated displayName (Verify Point #295)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for savedColleges (Verify Point #296)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at createdAt (Verify Point #297)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation firebase-auth (Verify Point #298)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for firestore-read (Verify Point #299)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field groq-api (Verify Point #300)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for college-list (Verify Point #301)</t>
-  </si>
-  <si>
-    <t>0.026</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for XSS-injection (Verify Point #302)</t>
-  </si>
-  <si>
-    <t>0.025</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for SQL-injection (Verify Point #303)</t>
-  </si>
-  <si>
-    <t>0.084</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of CSRF-token (Verify Point #304)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for CORS-origin (Verify Point #305)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for CSP-header (Verify Point #306)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value session-token (Verify Point #307)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users-ref (Verify Point #308)</t>
-  </si>
-  <si>
-    <t>0.091</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier items-ref (Verify Point #309)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region de-DE (Verify Point #310)</t>
-  </si>
-  <si>
-    <t>0.056</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for fr-FR (Verify Point #311)</t>
-  </si>
-  <si>
-    <t>0.099</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ja-JP (Verify Point #312)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource pt-BR (Verify Point #313)</t>
-  </si>
-  <si>
-    <t>0.032</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for it-IT (Verify Point #314)</t>
-  </si>
-  <si>
-    <t>0.083</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated apiKey (Verify Point #315)</t>
-  </si>
-  <si>
-    <t>0.095</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for authDomain (Verify Point #316)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at projectId (Verify Point #317)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation storageBucket (Verify Point #318)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for messagingSenderId (Verify Point #319)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field appId (Verify Point #320)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for name (Verify Point #321)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for id (Verify Point #322)</t>
-  </si>
-  <si>
-    <t>0.047</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for fees.min (Verify Point #323)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of fees.max (Verify Point #324)</t>
-  </si>
-  <si>
-    <t>0.080</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for courses (Verify Point #325)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for ranking.nirf (Verify Point #326)</t>
-  </si>
-  <si>
-    <t>0.044</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value type (Verify Point #327)</t>
-  </si>
-  <si>
-    <t>0.079</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users/uid001 (Verify Point #328)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier colleges/c001 (Verify Point #329)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region prompt-length (Verify Point #330)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for session-id-1 (Verify Point #331)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ₹1L (Verify Point #332)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource B.Tech (Verify Point #333)</t>
-  </si>
-  <si>
-    <t>0.060</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for 4 years (Verify Point #334)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated Tamil Nadu (Verify Point #335)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for Chennai (Verify Point #336)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at llama3-8b (Verify Point #337)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation email (Verify Point #338)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for password (Verify Point #339)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field displayName (Verify Point #340)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for savedColleges (Verify Point #341)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for createdAt (Verify Point #342)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for firebase-auth (Verify Point #343)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of firestore-read (Verify Point #344)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for groq-api (Verify Point #345)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for college-list (Verify Point #346)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value XSS-injection (Verify Point #347)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session SQL-injection (Verify Point #348)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier CSRF-token (Verify Point #349)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region CORS-origin (Verify Point #350)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for CSP-header (Verify Point #351)</t>
-  </si>
-  <si>
-    <t>0.118</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code session-token (Verify Point #352)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users-ref (Verify Point #353)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for items-ref (Verify Point #354)</t>
-  </si>
-  <si>
-    <t>0.051</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated de-DE (Verify Point #355)</t>
-  </si>
-  <si>
-    <t>0.102</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for fr-FR (Verify Point #356)</t>
-  </si>
-  <si>
-    <t>0.053</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ja-JP (Verify Point #357)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation pt-BR (Verify Point #358)</t>
-  </si>
-  <si>
-    <t>0.033</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for it-IT (Verify Point #359)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field apiKey (Verify Point #360)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #361)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #362)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #363)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #364)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #365)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #366)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #367)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #368)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #369)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #370)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #371)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #372)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #373)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #374)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #375)</t>
-  </si>
-  <si>
-    <t>0.111</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #376)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #377)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #378)</t>
-  </si>
-  <si>
-    <t>0.029</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #379)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #380)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #381)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #382)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #383)</t>
-  </si>
-  <si>
-    <t>0.075</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #384)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #385)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #386)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #387)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #388)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #389)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #390)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #391)</t>
-  </si>
-  <si>
     <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code XSS-injection (Verify Point #392)</t>
   </si>
   <si>
     <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #393)</t>
   </si>
   <si>
-    <t>0.093</t>
-  </si>
-  <si>
     <t>Smart Admission — Backend [Search]: Verify search results filtering for CSRF-token (Verify Point #394)</t>
   </si>
   <si>
-    <t>0.027</t>
-  </si>
-  <si>
     <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated CORS-origin (Verify Point #395)</t>
   </si>
   <si>
@@ -1508,13 +1511,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>25</t>
+    <t>26</t>
   </si>
   <si>
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-24 04:39:15 UTC</t>
+    <t>2026-06-30 08:35:27 UTC</t>
   </si>
   <si>
     <t>Branch</t>
@@ -1526,7 +1529,7 @@
     <t>Commit</t>
   </si>
   <si>
-    <t>f6dc91b</t>
+    <t>1b19601</t>
   </si>
   <si>
     <t>Total</t>
@@ -1998,7 +2001,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -2015,7 +2018,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -2032,7 +2035,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -2049,7 +2052,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -2066,7 +2069,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -2083,7 +2086,7 @@
         <v>6</v>
       </c>
       <c r="D9" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -2100,7 +2103,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -2117,7 +2120,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -2134,7 +2137,7 @@
         <v>6</v>
       </c>
       <c r="D12" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -2151,7 +2154,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -2185,7 +2188,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -2202,7 +2205,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -2219,7 +2222,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -2236,7 +2239,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -2253,7 +2256,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -2270,7 +2273,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -2287,7 +2290,7 @@
         <v>6</v>
       </c>
       <c r="D21" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -2304,7 +2307,7 @@
         <v>6</v>
       </c>
       <c r="D22" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -2321,7 +2324,7 @@
         <v>6</v>
       </c>
       <c r="D23" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -2338,7 +2341,7 @@
         <v>6</v>
       </c>
       <c r="D24" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -2355,7 +2358,7 @@
         <v>6</v>
       </c>
       <c r="D25" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -2372,7 +2375,7 @@
         <v>6</v>
       </c>
       <c r="D26" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -2389,7 +2392,7 @@
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -2406,7 +2409,7 @@
         <v>6</v>
       </c>
       <c r="D28" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -2423,7 +2426,7 @@
         <v>6</v>
       </c>
       <c r="D29" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -2440,7 +2443,7 @@
         <v>6</v>
       </c>
       <c r="D30" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -2457,7 +2460,7 @@
         <v>6</v>
       </c>
       <c r="D31" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -2474,7 +2477,7 @@
         <v>6</v>
       </c>
       <c r="D32" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -2491,7 +2494,7 @@
         <v>6</v>
       </c>
       <c r="D33" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -2508,7 +2511,7 @@
         <v>6</v>
       </c>
       <c r="D34" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -2525,7 +2528,7 @@
         <v>6</v>
       </c>
       <c r="D35" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -2542,7 +2545,7 @@
         <v>6</v>
       </c>
       <c r="D36" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -2559,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="D37" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -2576,7 +2579,7 @@
         <v>6</v>
       </c>
       <c r="D38" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -2593,7 +2596,7 @@
         <v>6</v>
       </c>
       <c r="D39" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -2610,7 +2613,7 @@
         <v>6</v>
       </c>
       <c r="D40" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -2661,7 +2664,7 @@
         <v>6</v>
       </c>
       <c r="D43" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -2678,7 +2681,7 @@
         <v>6</v>
       </c>
       <c r="D44" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -2695,7 +2698,7 @@
         <v>6</v>
       </c>
       <c r="D45" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -2712,7 +2715,7 @@
         <v>6</v>
       </c>
       <c r="D46" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -2729,7 +2732,7 @@
         <v>6</v>
       </c>
       <c r="D47" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -2746,7 +2749,7 @@
         <v>6</v>
       </c>
       <c r="D48" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -2763,7 +2766,7 @@
         <v>6</v>
       </c>
       <c r="D49" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -2780,7 +2783,7 @@
         <v>6</v>
       </c>
       <c r="D50" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -2797,7 +2800,7 @@
         <v>6</v>
       </c>
       <c r="D51" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -2814,7 +2817,7 @@
         <v>6</v>
       </c>
       <c r="D52" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -2831,7 +2834,7 @@
         <v>6</v>
       </c>
       <c r="D53" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -2848,7 +2851,7 @@
         <v>6</v>
       </c>
       <c r="D54" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -2865,7 +2868,7 @@
         <v>6</v>
       </c>
       <c r="D55" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
@@ -2882,7 +2885,7 @@
         <v>6</v>
       </c>
       <c r="D56" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -2899,7 +2902,7 @@
         <v>6</v>
       </c>
       <c r="D57" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -2916,7 +2919,7 @@
         <v>6</v>
       </c>
       <c r="D58" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -2933,7 +2936,7 @@
         <v>6</v>
       </c>
       <c r="D59" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
@@ -2950,7 +2953,7 @@
         <v>6</v>
       </c>
       <c r="D60" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
@@ -2967,7 +2970,7 @@
         <v>6</v>
       </c>
       <c r="D61" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
@@ -2984,7 +2987,7 @@
         <v>6</v>
       </c>
       <c r="D62" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
@@ -3001,7 +3004,7 @@
         <v>6</v>
       </c>
       <c r="D63" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
@@ -3035,7 +3038,7 @@
         <v>6</v>
       </c>
       <c r="D65" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E65" t="s">
         <v>8</v>
@@ -3052,7 +3055,7 @@
         <v>6</v>
       </c>
       <c r="D66" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
@@ -3069,7 +3072,7 @@
         <v>6</v>
       </c>
       <c r="D67" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
@@ -3086,7 +3089,7 @@
         <v>6</v>
       </c>
       <c r="D68" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
@@ -3103,7 +3106,7 @@
         <v>6</v>
       </c>
       <c r="D69" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E69" t="s">
         <v>8</v>
@@ -3120,7 +3123,7 @@
         <v>6</v>
       </c>
       <c r="D70" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
@@ -3137,7 +3140,7 @@
         <v>6</v>
       </c>
       <c r="D71" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
@@ -3154,7 +3157,7 @@
         <v>6</v>
       </c>
       <c r="D72" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
@@ -3171,7 +3174,7 @@
         <v>6</v>
       </c>
       <c r="D73" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E73" t="s">
         <v>8</v>
@@ -3205,7 +3208,7 @@
         <v>6</v>
       </c>
       <c r="D75" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
@@ -3222,7 +3225,7 @@
         <v>6</v>
       </c>
       <c r="D76" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E76" t="s">
         <v>8</v>
@@ -3239,7 +3242,7 @@
         <v>6</v>
       </c>
       <c r="D77" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
@@ -3256,7 +3259,7 @@
         <v>6</v>
       </c>
       <c r="D78" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
@@ -3273,7 +3276,7 @@
         <v>6</v>
       </c>
       <c r="D79" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E79" t="s">
         <v>8</v>
@@ -3290,7 +3293,7 @@
         <v>6</v>
       </c>
       <c r="D80" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E80" t="s">
         <v>8</v>
@@ -3307,7 +3310,7 @@
         <v>6</v>
       </c>
       <c r="D81" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
@@ -3341,7 +3344,7 @@
         <v>6</v>
       </c>
       <c r="D83" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E83" t="s">
         <v>8</v>
@@ -3375,7 +3378,7 @@
         <v>6</v>
       </c>
       <c r="D85" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
@@ -3392,7 +3395,7 @@
         <v>6</v>
       </c>
       <c r="D86" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
@@ -3409,7 +3412,7 @@
         <v>6</v>
       </c>
       <c r="D87" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E87" t="s">
         <v>8</v>
@@ -3426,7 +3429,7 @@
         <v>6</v>
       </c>
       <c r="D88" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E88" t="s">
         <v>8</v>
@@ -3443,7 +3446,7 @@
         <v>6</v>
       </c>
       <c r="D89" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
@@ -3460,7 +3463,7 @@
         <v>6</v>
       </c>
       <c r="D90" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E90" t="s">
         <v>8</v>
@@ -3477,7 +3480,7 @@
         <v>6</v>
       </c>
       <c r="D91" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E91" t="s">
         <v>8</v>
@@ -3494,7 +3497,7 @@
         <v>6</v>
       </c>
       <c r="D92" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E92" t="s">
         <v>8</v>
@@ -3511,7 +3514,7 @@
         <v>6</v>
       </c>
       <c r="D93" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E93" t="s">
         <v>8</v>
@@ -3528,7 +3531,7 @@
         <v>6</v>
       </c>
       <c r="D94" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E94" t="s">
         <v>8</v>
@@ -3545,7 +3548,7 @@
         <v>6</v>
       </c>
       <c r="D95" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E95" t="s">
         <v>8</v>
@@ -3562,7 +3565,7 @@
         <v>6</v>
       </c>
       <c r="D96" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E96" t="s">
         <v>8</v>
@@ -3579,7 +3582,7 @@
         <v>6</v>
       </c>
       <c r="D97" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E97" t="s">
         <v>8</v>
@@ -3596,7 +3599,7 @@
         <v>6</v>
       </c>
       <c r="D98" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E98" t="s">
         <v>8</v>
@@ -3613,7 +3616,7 @@
         <v>6</v>
       </c>
       <c r="D99" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
@@ -3630,7 +3633,7 @@
         <v>6</v>
       </c>
       <c r="D100" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E100" t="s">
         <v>8</v>
@@ -3647,7 +3650,7 @@
         <v>6</v>
       </c>
       <c r="D101" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E101" t="s">
         <v>8</v>
@@ -3664,7 +3667,7 @@
         <v>6</v>
       </c>
       <c r="D102" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E102" t="s">
         <v>8</v>
@@ -3681,7 +3684,7 @@
         <v>6</v>
       </c>
       <c r="D103" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E103" t="s">
         <v>8</v>
@@ -3715,7 +3718,7 @@
         <v>6</v>
       </c>
       <c r="D105" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E105" t="s">
         <v>8</v>
@@ -3732,7 +3735,7 @@
         <v>6</v>
       </c>
       <c r="D106" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E106" t="s">
         <v>8</v>
@@ -3749,7 +3752,7 @@
         <v>6</v>
       </c>
       <c r="D107" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
@@ -3766,7 +3769,7 @@
         <v>6</v>
       </c>
       <c r="D108" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E108" t="s">
         <v>8</v>
@@ -3783,7 +3786,7 @@
         <v>6</v>
       </c>
       <c r="D109" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E109" t="s">
         <v>8</v>
@@ -3800,7 +3803,7 @@
         <v>6</v>
       </c>
       <c r="D110" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E110" t="s">
         <v>8</v>
@@ -3817,7 +3820,7 @@
         <v>6</v>
       </c>
       <c r="D111" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E111" t="s">
         <v>8</v>
@@ -3834,7 +3837,7 @@
         <v>6</v>
       </c>
       <c r="D112" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E112" t="s">
         <v>8</v>
@@ -3868,7 +3871,7 @@
         <v>6</v>
       </c>
       <c r="D114" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E114" t="s">
         <v>8</v>
@@ -3885,7 +3888,7 @@
         <v>6</v>
       </c>
       <c r="D115" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E115" t="s">
         <v>8</v>
@@ -3902,7 +3905,7 @@
         <v>6</v>
       </c>
       <c r="D116" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E116" t="s">
         <v>8</v>
@@ -3919,7 +3922,7 @@
         <v>6</v>
       </c>
       <c r="D117" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E117" t="s">
         <v>8</v>
@@ -3936,7 +3939,7 @@
         <v>6</v>
       </c>
       <c r="D118" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E118" t="s">
         <v>8</v>
@@ -3953,7 +3956,7 @@
         <v>6</v>
       </c>
       <c r="D119" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E119" t="s">
         <v>8</v>
@@ -3970,7 +3973,7 @@
         <v>6</v>
       </c>
       <c r="D120" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E120" t="s">
         <v>8</v>
@@ -3987,7 +3990,7 @@
         <v>6</v>
       </c>
       <c r="D121" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E121" t="s">
         <v>8</v>
@@ -4004,7 +4007,7 @@
         <v>6</v>
       </c>
       <c r="D122" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E122" t="s">
         <v>8</v>
@@ -4021,7 +4024,7 @@
         <v>6</v>
       </c>
       <c r="D123" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E123" t="s">
         <v>8</v>
@@ -4038,7 +4041,7 @@
         <v>6</v>
       </c>
       <c r="D124" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E124" t="s">
         <v>8</v>
@@ -4055,7 +4058,7 @@
         <v>6</v>
       </c>
       <c r="D125" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E125" t="s">
         <v>8</v>
@@ -4072,7 +4075,7 @@
         <v>6</v>
       </c>
       <c r="D126" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E126" t="s">
         <v>8</v>
@@ -4089,7 +4092,7 @@
         <v>6</v>
       </c>
       <c r="D127" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E127" t="s">
         <v>8</v>
@@ -4106,7 +4109,7 @@
         <v>6</v>
       </c>
       <c r="D128" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E128" t="s">
         <v>8</v>
@@ -4123,7 +4126,7 @@
         <v>6</v>
       </c>
       <c r="D129" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E129" t="s">
         <v>8</v>
@@ -4140,7 +4143,7 @@
         <v>6</v>
       </c>
       <c r="D130" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E130" t="s">
         <v>8</v>
@@ -4157,7 +4160,7 @@
         <v>6</v>
       </c>
       <c r="D131" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E131" t="s">
         <v>8</v>
@@ -4174,7 +4177,7 @@
         <v>6</v>
       </c>
       <c r="D132" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E132" t="s">
         <v>8</v>
@@ -4191,7 +4194,7 @@
         <v>6</v>
       </c>
       <c r="D133" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E133" t="s">
         <v>8</v>
@@ -4208,7 +4211,7 @@
         <v>6</v>
       </c>
       <c r="D134" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E134" t="s">
         <v>8</v>
@@ -4225,7 +4228,7 @@
         <v>6</v>
       </c>
       <c r="D135" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E135" t="s">
         <v>8</v>
@@ -4242,7 +4245,7 @@
         <v>6</v>
       </c>
       <c r="D136" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E136" t="s">
         <v>8</v>
@@ -4259,7 +4262,7 @@
         <v>6</v>
       </c>
       <c r="D137" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E137" t="s">
         <v>8</v>
@@ -4276,7 +4279,7 @@
         <v>6</v>
       </c>
       <c r="D138" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E138" t="s">
         <v>8</v>
@@ -4310,7 +4313,7 @@
         <v>6</v>
       </c>
       <c r="D140" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E140" t="s">
         <v>8</v>
@@ -4327,7 +4330,7 @@
         <v>6</v>
       </c>
       <c r="D141" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E141" t="s">
         <v>8</v>
@@ -4344,7 +4347,7 @@
         <v>6</v>
       </c>
       <c r="D142" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E142" t="s">
         <v>8</v>
@@ -4361,7 +4364,7 @@
         <v>6</v>
       </c>
       <c r="D143" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E143" t="s">
         <v>8</v>
@@ -4395,7 +4398,7 @@
         <v>6</v>
       </c>
       <c r="D145" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E145" t="s">
         <v>8</v>
@@ -4412,7 +4415,7 @@
         <v>6</v>
       </c>
       <c r="D146" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E146" t="s">
         <v>8</v>
@@ -4429,7 +4432,7 @@
         <v>6</v>
       </c>
       <c r="D147" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E147" t="s">
         <v>8</v>
@@ -4446,7 +4449,7 @@
         <v>6</v>
       </c>
       <c r="D148" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E148" t="s">
         <v>8</v>
@@ -4463,7 +4466,7 @@
         <v>6</v>
       </c>
       <c r="D149" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E149" t="s">
         <v>8</v>
@@ -4480,7 +4483,7 @@
         <v>6</v>
       </c>
       <c r="D150" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E150" t="s">
         <v>8</v>
@@ -4497,7 +4500,7 @@
         <v>6</v>
       </c>
       <c r="D151" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E151" t="s">
         <v>8</v>
@@ -4514,7 +4517,7 @@
         <v>6</v>
       </c>
       <c r="D152" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E152" t="s">
         <v>8</v>
@@ -4531,7 +4534,7 @@
         <v>6</v>
       </c>
       <c r="D153" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E153" t="s">
         <v>8</v>
@@ -4548,7 +4551,7 @@
         <v>6</v>
       </c>
       <c r="D154" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E154" t="s">
         <v>8</v>
@@ -4565,7 +4568,7 @@
         <v>6</v>
       </c>
       <c r="D155" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E155" t="s">
         <v>8</v>
@@ -4582,7 +4585,7 @@
         <v>6</v>
       </c>
       <c r="D156" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E156" t="s">
         <v>8</v>
@@ -4599,7 +4602,7 @@
         <v>6</v>
       </c>
       <c r="D157" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E157" t="s">
         <v>8</v>
@@ -4616,7 +4619,7 @@
         <v>6</v>
       </c>
       <c r="D158" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E158" t="s">
         <v>8</v>
@@ -4633,7 +4636,7 @@
         <v>6</v>
       </c>
       <c r="D159" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E159" t="s">
         <v>8</v>
@@ -4650,7 +4653,7 @@
         <v>6</v>
       </c>
       <c r="D160" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E160" t="s">
         <v>8</v>
@@ -4667,7 +4670,7 @@
         <v>6</v>
       </c>
       <c r="D161" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E161" t="s">
         <v>8</v>
@@ -4684,7 +4687,7 @@
         <v>6</v>
       </c>
       <c r="D162" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E162" t="s">
         <v>8</v>
@@ -4701,7 +4704,7 @@
         <v>6</v>
       </c>
       <c r="D163" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E163" t="s">
         <v>8</v>
@@ -4718,7 +4721,7 @@
         <v>6</v>
       </c>
       <c r="D164" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E164" t="s">
         <v>8</v>
@@ -4735,7 +4738,7 @@
         <v>6</v>
       </c>
       <c r="D165" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E165" t="s">
         <v>8</v>
@@ -4752,7 +4755,7 @@
         <v>6</v>
       </c>
       <c r="D166" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E166" t="s">
         <v>8</v>
@@ -4769,7 +4772,7 @@
         <v>6</v>
       </c>
       <c r="D167" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E167" t="s">
         <v>8</v>
@@ -4786,7 +4789,7 @@
         <v>6</v>
       </c>
       <c r="D168" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E168" t="s">
         <v>8</v>
@@ -4803,7 +4806,7 @@
         <v>6</v>
       </c>
       <c r="D169" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E169" t="s">
         <v>8</v>
@@ -4820,7 +4823,7 @@
         <v>6</v>
       </c>
       <c r="D170" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E170" t="s">
         <v>8</v>
@@ -4837,7 +4840,7 @@
         <v>6</v>
       </c>
       <c r="D171" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E171" t="s">
         <v>8</v>
@@ -4854,7 +4857,7 @@
         <v>6</v>
       </c>
       <c r="D172" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E172" t="s">
         <v>8</v>
@@ -4871,7 +4874,7 @@
         <v>6</v>
       </c>
       <c r="D173" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E173" t="s">
         <v>8</v>
@@ -4888,7 +4891,7 @@
         <v>6</v>
       </c>
       <c r="D174" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E174" t="s">
         <v>8</v>
@@ -4905,7 +4908,7 @@
         <v>6</v>
       </c>
       <c r="D175" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E175" t="s">
         <v>8</v>
@@ -4922,7 +4925,7 @@
         <v>6</v>
       </c>
       <c r="D176" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E176" t="s">
         <v>8</v>
@@ -4939,7 +4942,7 @@
         <v>6</v>
       </c>
       <c r="D177" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E177" t="s">
         <v>8</v>
@@ -4956,7 +4959,7 @@
         <v>6</v>
       </c>
       <c r="D178" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E178" t="s">
         <v>8</v>
@@ -4973,7 +4976,7 @@
         <v>6</v>
       </c>
       <c r="D179" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E179" t="s">
         <v>8</v>
@@ -4990,7 +4993,7 @@
         <v>6</v>
       </c>
       <c r="D180" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E180" t="s">
         <v>8</v>
@@ -5007,7 +5010,7 @@
         <v>6</v>
       </c>
       <c r="D181" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E181" t="s">
         <v>8</v>
@@ -5126,7 +5129,7 @@
         <v>6</v>
       </c>
       <c r="D188" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E188" t="s">
         <v>8</v>
@@ -5137,13 +5140,13 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
+        <v>202</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D189" t="s">
         <v>203</v>
-      </c>
-      <c r="C189" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D189" t="s">
-        <v>204</v>
       </c>
       <c r="E189" t="s">
         <v>8</v>
@@ -5154,13 +5157,13 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
+        <v>204</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D190" t="s">
         <v>205</v>
-      </c>
-      <c r="C190" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D190" t="s">
-        <v>206</v>
       </c>
       <c r="E190" t="s">
         <v>8</v>
@@ -5171,13 +5174,13 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
+        <v>206</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D191" t="s">
         <v>207</v>
-      </c>
-      <c r="C191" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D191" t="s">
-        <v>208</v>
       </c>
       <c r="E191" t="s">
         <v>8</v>
@@ -5188,13 +5191,13 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
+        <v>208</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D192" t="s">
         <v>209</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D192" t="s">
-        <v>210</v>
       </c>
       <c r="E192" t="s">
         <v>8</v>
@@ -5205,13 +5208,13 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
+        <v>210</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D193" t="s">
         <v>211</v>
-      </c>
-      <c r="C193" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D193" t="s">
-        <v>212</v>
       </c>
       <c r="E193" t="s">
         <v>8</v>
@@ -5222,13 +5225,13 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
+        <v>212</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D194" t="s">
         <v>213</v>
-      </c>
-      <c r="C194" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D194" t="s">
-        <v>192</v>
       </c>
       <c r="E194" t="s">
         <v>8</v>
@@ -5364,7 +5367,7 @@
         <v>6</v>
       </c>
       <c r="D202" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E202" t="s">
         <v>8</v>
@@ -5375,13 +5378,13 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D203" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E203" t="s">
         <v>8</v>
@@ -5392,13 +5395,13 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D204" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E204" t="s">
         <v>8</v>
@@ -5409,13 +5412,13 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D205" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E205" t="s">
         <v>8</v>
@@ -5426,13 +5429,13 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D206" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E206" t="s">
         <v>8</v>
@@ -5443,13 +5446,13 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D207" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E207" t="s">
         <v>8</v>
@@ -5460,13 +5463,13 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D208" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="E208" t="s">
         <v>8</v>
@@ -5551,7 +5554,7 @@
         <v>6</v>
       </c>
       <c r="D213" t="s">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="E213" t="s">
         <v>8</v>
@@ -5562,13 +5565,13 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D214" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E214" t="s">
         <v>8</v>
@@ -5579,13 +5582,13 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D215" t="s">
-        <v>208</v>
+        <v>254</v>
       </c>
       <c r="E215" t="s">
         <v>8</v>
@@ -5596,13 +5599,13 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D216" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E216" t="s">
         <v>8</v>
@@ -5613,13 +5616,13 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D217" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="E217" t="s">
         <v>8</v>
@@ -5630,13 +5633,13 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D218" t="s">
-        <v>221</v>
+        <v>259</v>
       </c>
       <c r="E218" t="s">
         <v>8</v>
@@ -5647,13 +5650,13 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D219" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E219" t="s">
         <v>8</v>
@@ -5664,13 +5667,13 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D220" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="E220" t="s">
         <v>8</v>
@@ -5681,13 +5684,13 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D221" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E221" t="s">
         <v>8</v>
@@ -5698,13 +5701,13 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D222" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E222" t="s">
         <v>8</v>
@@ -5715,13 +5718,13 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D223" t="s">
-        <v>230</v>
+        <v>256</v>
       </c>
       <c r="E223" t="s">
         <v>8</v>
@@ -5732,13 +5735,13 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D224" t="s">
-        <v>242</v>
+        <v>200</v>
       </c>
       <c r="E224" t="s">
         <v>8</v>
@@ -5749,13 +5752,13 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D225" t="s">
-        <v>196</v>
+        <v>270</v>
       </c>
       <c r="E225" t="s">
         <v>8</v>
@@ -5766,13 +5769,13 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D226" t="s">
-        <v>269</v>
+        <v>237</v>
       </c>
       <c r="E226" t="s">
         <v>8</v>
@@ -5783,13 +5786,13 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D227" t="s">
-        <v>221</v>
+        <v>273</v>
       </c>
       <c r="E227" t="s">
         <v>8</v>
@@ -5800,13 +5803,13 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D228" t="s">
-        <v>208</v>
+        <v>275</v>
       </c>
       <c r="E228" t="s">
         <v>8</v>
@@ -5817,13 +5820,13 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D229" t="s">
-        <v>262</v>
+        <v>200</v>
       </c>
       <c r="E229" t="s">
         <v>8</v>
@@ -5834,13 +5837,13 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D230" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E230" t="s">
         <v>8</v>
@@ -5851,13 +5854,13 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D231" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="E231" t="s">
         <v>8</v>
@@ -5868,13 +5871,13 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D232" t="s">
-        <v>221</v>
+        <v>282</v>
       </c>
       <c r="E232" t="s">
         <v>8</v>
@@ -5885,13 +5888,13 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D233" t="s">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="E233" t="s">
         <v>8</v>
@@ -5902,13 +5905,13 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D234" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="E234" t="s">
         <v>8</v>
@@ -5919,13 +5922,13 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D235" t="s">
-        <v>254</v>
+        <v>286</v>
       </c>
       <c r="E235" t="s">
         <v>8</v>
@@ -5936,13 +5939,13 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D236" t="s">
-        <v>282</v>
+        <v>227</v>
       </c>
       <c r="E236" t="s">
         <v>8</v>
@@ -5953,13 +5956,13 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D237" t="s">
-        <v>221</v>
+        <v>289</v>
       </c>
       <c r="E237" t="s">
         <v>8</v>
@@ -5970,13 +5973,13 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D238" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="E238" t="s">
         <v>8</v>
@@ -5987,13 +5990,13 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D239" t="s">
-        <v>287</v>
+        <v>248</v>
       </c>
       <c r="E239" t="s">
         <v>8</v>
@@ -6004,13 +6007,13 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D240" t="s">
-        <v>194</v>
+        <v>294</v>
       </c>
       <c r="E240" t="s">
         <v>8</v>
@@ -6021,13 +6024,13 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D241" t="s">
-        <v>219</v>
+        <v>296</v>
       </c>
       <c r="E241" t="s">
         <v>8</v>
@@ -6038,13 +6041,13 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D242" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="E242" t="s">
         <v>8</v>
@@ -6055,13 +6058,13 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D243" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="E243" t="s">
         <v>8</v>
@@ -6072,13 +6075,13 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D244" t="s">
-        <v>264</v>
+        <v>301</v>
       </c>
       <c r="E244" t="s">
         <v>8</v>
@@ -6089,13 +6092,13 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D245" t="s">
-        <v>230</v>
+        <v>301</v>
       </c>
       <c r="E245" t="s">
         <v>8</v>
@@ -6106,13 +6109,13 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D246" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="E246" t="s">
         <v>8</v>
@@ -6123,13 +6126,13 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D247" t="s">
-        <v>299</v>
+        <v>259</v>
       </c>
       <c r="E247" t="s">
         <v>8</v>
@@ -6140,13 +6143,13 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D248" t="s">
-        <v>299</v>
+        <v>250</v>
       </c>
       <c r="E248" t="s">
         <v>8</v>
@@ -6157,13 +6160,13 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D249" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="E249" t="s">
         <v>8</v>
@@ -6174,13 +6177,13 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D250" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="E250" t="s">
         <v>8</v>
@@ -6191,13 +6194,13 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D251" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="E251" t="s">
         <v>8</v>
@@ -6208,13 +6211,13 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D252" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="E252" t="s">
         <v>8</v>
@@ -6225,13 +6228,13 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D253" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="E253" t="s">
         <v>8</v>
@@ -6242,13 +6245,13 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D254" t="s">
-        <v>310</v>
+        <v>207</v>
       </c>
       <c r="E254" t="s">
         <v>8</v>
@@ -6259,13 +6262,13 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D255" t="s">
-        <v>312</v>
+        <v>207</v>
       </c>
       <c r="E255" t="s">
         <v>8</v>
@@ -6276,13 +6279,13 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D256" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="E256" t="s">
         <v>8</v>
@@ -6293,13 +6296,13 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D257" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="E257" t="s">
         <v>8</v>
@@ -6310,13 +6313,13 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D258" t="s">
-        <v>264</v>
+        <v>323</v>
       </c>
       <c r="E258" t="s">
         <v>8</v>
@@ -6327,13 +6330,13 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D259" t="s">
-        <v>276</v>
+        <v>215</v>
       </c>
       <c r="E259" t="s">
         <v>8</v>
@@ -6344,13 +6347,13 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D260" t="s">
-        <v>274</v>
+        <v>326</v>
       </c>
       <c r="E260" t="s">
         <v>8</v>
@@ -6361,13 +6364,13 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D261" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="E261" t="s">
         <v>8</v>
@@ -6378,13 +6381,13 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D262" t="s">
-        <v>308</v>
+        <v>259</v>
       </c>
       <c r="E262" t="s">
         <v>8</v>
@@ -6395,13 +6398,13 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D263" t="s">
-        <v>234</v>
+        <v>200</v>
       </c>
       <c r="E263" t="s">
         <v>8</v>
@@ -6412,13 +6415,13 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D264" t="s">
-        <v>316</v>
+        <v>227</v>
       </c>
       <c r="E264" t="s">
         <v>8</v>
@@ -6429,13 +6432,13 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D265" t="s">
-        <v>234</v>
+        <v>333</v>
       </c>
       <c r="E265" t="s">
         <v>8</v>
@@ -6446,13 +6449,13 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D266" t="s">
-        <v>248</v>
+        <v>223</v>
       </c>
       <c r="E266" t="s">
         <v>8</v>
@@ -6463,13 +6466,13 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D267" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="E267" t="s">
         <v>8</v>
@@ -6480,13 +6483,13 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D268" t="s">
-        <v>204</v>
+        <v>337</v>
       </c>
       <c r="E268" t="s">
         <v>8</v>
@@ -6497,13 +6500,13 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D269" t="s">
-        <v>215</v>
+        <v>289</v>
       </c>
       <c r="E269" t="s">
         <v>8</v>
@@ -6514,13 +6517,13 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D270" t="s">
-        <v>303</v>
+        <v>239</v>
       </c>
       <c r="E270" t="s">
         <v>8</v>
@@ -6531,13 +6534,13 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D271" t="s">
-        <v>198</v>
+        <v>237</v>
       </c>
       <c r="E271" t="s">
         <v>8</v>
@@ -6548,13 +6551,13 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D272" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="E272" t="s">
         <v>8</v>
@@ -6565,13 +6568,13 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D273" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="E273" t="s">
         <v>8</v>
@@ -6582,13 +6585,13 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D274" t="s">
-        <v>338</v>
+        <v>259</v>
       </c>
       <c r="E274" t="s">
         <v>8</v>
@@ -6599,13 +6602,13 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D275" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E275" t="s">
         <v>8</v>
@@ -6616,13 +6619,13 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D276" t="s">
-        <v>202</v>
+        <v>233</v>
       </c>
       <c r="E276" t="s">
         <v>8</v>
@@ -6633,13 +6636,13 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D277" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="E277" t="s">
         <v>8</v>
@@ -6650,13 +6653,13 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D278" t="s">
-        <v>334</v>
+        <v>315</v>
       </c>
       <c r="E278" t="s">
         <v>8</v>
@@ -6667,13 +6670,13 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D279" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="E279" t="s">
         <v>8</v>
@@ -6684,13 +6687,13 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D280" t="s">
-        <v>282</v>
+        <v>309</v>
       </c>
       <c r="E280" t="s">
         <v>8</v>
@@ -6701,13 +6704,13 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D281" t="s">
-        <v>240</v>
+        <v>273</v>
       </c>
       <c r="E281" t="s">
         <v>8</v>
@@ -6718,13 +6721,13 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D282" t="s">
-        <v>200</v>
+        <v>355</v>
       </c>
       <c r="E282" t="s">
         <v>8</v>
@@ -6735,13 +6738,13 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D283" t="s">
-        <v>240</v>
+        <v>357</v>
       </c>
       <c r="E283" t="s">
         <v>8</v>
@@ -6752,13 +6755,13 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D284" t="s">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="E284" t="s">
         <v>8</v>
@@ -6769,13 +6772,13 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D285" t="s">
-        <v>352</v>
+        <v>289</v>
       </c>
       <c r="E285" t="s">
         <v>8</v>
@@ -6786,13 +6789,13 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D286" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="E286" t="s">
         <v>8</v>
@@ -6803,13 +6806,13 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D287" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E287" t="s">
         <v>8</v>
@@ -6820,13 +6823,13 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D288" t="s">
-        <v>338</v>
+        <v>364</v>
       </c>
       <c r="E288" t="s">
         <v>8</v>
@@ -6837,13 +6840,13 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D289" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="E289" t="s">
         <v>8</v>
@@ -6854,13 +6857,13 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D290" t="s">
-        <v>342</v>
+        <v>319</v>
       </c>
       <c r="E290" t="s">
         <v>8</v>
@@ -6871,13 +6874,13 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D291" t="s">
-        <v>328</v>
+        <v>368</v>
       </c>
       <c r="E291" t="s">
         <v>8</v>
@@ -6888,13 +6891,13 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D292" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E292" t="s">
         <v>8</v>
@@ -6905,13 +6908,13 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D293" t="s">
-        <v>352</v>
+        <v>371</v>
       </c>
       <c r="E293" t="s">
         <v>8</v>
@@ -6922,13 +6925,13 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D294" t="s">
-        <v>345</v>
+        <v>242</v>
       </c>
       <c r="E294" t="s">
         <v>8</v>
@@ -6939,13 +6942,13 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D295" t="s">
-        <v>338</v>
+        <v>374</v>
       </c>
       <c r="E295" t="s">
         <v>8</v>
@@ -6956,13 +6959,13 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D296" t="s">
-        <v>365</v>
+        <v>307</v>
       </c>
       <c r="E296" t="s">
         <v>8</v>
@@ -6973,13 +6976,13 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D297" t="s">
-        <v>352</v>
+        <v>231</v>
       </c>
       <c r="E297" t="s">
         <v>8</v>
@@ -6990,13 +6993,13 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D298" t="s">
-        <v>208</v>
+        <v>378</v>
       </c>
       <c r="E298" t="s">
         <v>8</v>
@@ -7007,13 +7010,13 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D299" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="E299" t="s">
         <v>8</v>
@@ -7024,13 +7027,13 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D300" t="s">
-        <v>314</v>
+        <v>282</v>
       </c>
       <c r="E300" t="s">
         <v>8</v>
@@ -7041,13 +7044,13 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D301" t="s">
-        <v>236</v>
+        <v>192</v>
       </c>
       <c r="E301" t="s">
         <v>8</v>
@@ -7058,13 +7061,13 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D302" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="E302" t="s">
         <v>8</v>
@@ -7075,13 +7078,13 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D303" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E303" t="s">
         <v>8</v>
@@ -7092,13 +7095,13 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D304" t="s">
-        <v>375</v>
+        <v>311</v>
       </c>
       <c r="E304" t="s">
         <v>8</v>
@@ -7109,13 +7112,13 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D305" t="s">
-        <v>377</v>
+        <v>242</v>
       </c>
       <c r="E305" t="s">
         <v>8</v>
@@ -7126,13 +7129,13 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D306" t="s">
-        <v>210</v>
+        <v>387</v>
       </c>
       <c r="E306" t="s">
         <v>8</v>
@@ -7143,13 +7146,13 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D307" t="s">
-        <v>321</v>
+        <v>389</v>
       </c>
       <c r="E307" t="s">
         <v>8</v>
@@ -7160,13 +7163,13 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D308" t="s">
-        <v>310</v>
+        <v>391</v>
       </c>
       <c r="E308" t="s">
         <v>8</v>
@@ -7177,13 +7180,13 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D309" t="s">
-        <v>342</v>
+        <v>393</v>
       </c>
       <c r="E309" t="s">
         <v>8</v>
@@ -7194,13 +7197,13 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D310" t="s">
-        <v>383</v>
+        <v>215</v>
       </c>
       <c r="E310" t="s">
         <v>8</v>
@@ -7211,13 +7214,13 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D311" t="s">
-        <v>314</v>
+        <v>364</v>
       </c>
       <c r="E311" t="s">
         <v>8</v>
@@ -7228,13 +7231,13 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D312" t="s">
-        <v>386</v>
+        <v>231</v>
       </c>
       <c r="E312" t="s">
         <v>8</v>
@@ -7245,13 +7248,13 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D313" t="s">
-        <v>388</v>
+        <v>291</v>
       </c>
       <c r="E313" t="s">
         <v>8</v>
@@ -7262,13 +7265,13 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D314" t="s">
-        <v>293</v>
+        <v>194</v>
       </c>
       <c r="E314" t="s">
         <v>8</v>
@@ -7279,13 +7282,13 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D315" t="s">
-        <v>391</v>
+        <v>198</v>
       </c>
       <c r="E315" t="s">
         <v>8</v>
@@ -7296,13 +7299,13 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D316" t="s">
-        <v>393</v>
+        <v>192</v>
       </c>
       <c r="E316" t="s">
         <v>8</v>
@@ -7313,13 +7316,13 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D317" t="s">
-        <v>395</v>
+        <v>203</v>
       </c>
       <c r="E317" t="s">
         <v>8</v>
@@ -7330,13 +7333,13 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D318" t="s">
-        <v>246</v>
+        <v>364</v>
       </c>
       <c r="E318" t="s">
         <v>8</v>
@@ -7347,13 +7350,13 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D319" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="E319" t="s">
         <v>8</v>
@@ -7364,13 +7367,13 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D320" t="s">
-        <v>342</v>
+        <v>207</v>
       </c>
       <c r="E320" t="s">
         <v>8</v>
@@ -7381,13 +7384,13 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D321" t="s">
-        <v>254</v>
+        <v>391</v>
       </c>
       <c r="E321" t="s">
         <v>8</v>
@@ -7398,13 +7401,13 @@
         <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D322" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E322" t="s">
         <v>8</v>
@@ -7415,13 +7418,13 @@
         <v>322</v>
       </c>
       <c r="B323" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D323" t="s">
-        <v>293</v>
+        <v>408</v>
       </c>
       <c r="E323" t="s">
         <v>8</v>
@@ -7432,13 +7435,13 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D324" t="s">
-        <v>403</v>
+        <v>333</v>
       </c>
       <c r="E324" t="s">
         <v>8</v>
@@ -7449,13 +7452,13 @@
         <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D325" t="s">
-        <v>236</v>
+        <v>349</v>
       </c>
       <c r="E325" t="s">
         <v>8</v>
@@ -7466,13 +7469,13 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D326" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="E326" t="s">
         <v>8</v>
@@ -7483,13 +7486,13 @@
         <v>326</v>
       </c>
       <c r="B327" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D327" t="s">
-        <v>287</v>
+        <v>200</v>
       </c>
       <c r="E327" t="s">
         <v>8</v>
@@ -7500,13 +7503,13 @@
         <v>327</v>
       </c>
       <c r="B328" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D328" t="s">
-        <v>409</v>
+        <v>261</v>
       </c>
       <c r="E328" t="s">
         <v>8</v>
@@ -7517,13 +7520,13 @@
         <v>328</v>
       </c>
       <c r="B329" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D329" t="s">
-        <v>411</v>
+        <v>203</v>
       </c>
       <c r="E329" t="s">
         <v>8</v>
@@ -7534,13 +7537,13 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D330" t="s">
-        <v>285</v>
+        <v>217</v>
       </c>
       <c r="E330" t="s">
         <v>8</v>
@@ -7551,13 +7554,13 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D331" t="s">
-        <v>206</v>
+        <v>378</v>
       </c>
       <c r="E331" t="s">
         <v>8</v>
@@ -7568,13 +7571,13 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D332" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
       <c r="E332" t="s">
         <v>8</v>
@@ -7585,13 +7588,13 @@
         <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D333" t="s">
-        <v>230</v>
+        <v>387</v>
       </c>
       <c r="E333" t="s">
         <v>8</v>
@@ -7602,7 +7605,7 @@
         <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>6</v>
@@ -7619,13 +7622,13 @@
         <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D335" t="s">
-        <v>418</v>
+        <v>273</v>
       </c>
       <c r="E335" t="s">
         <v>8</v>
@@ -7636,13 +7639,13 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D336" t="s">
-        <v>210</v>
+        <v>412</v>
       </c>
       <c r="E336" t="s">
         <v>8</v>
@@ -7653,13 +7656,13 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D337" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="E337" t="s">
         <v>8</v>
@@ -7670,13 +7673,13 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D338" t="s">
-        <v>282</v>
+        <v>227</v>
       </c>
       <c r="E338" t="s">
         <v>8</v>
@@ -7687,13 +7690,13 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D339" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="E339" t="s">
         <v>8</v>
@@ -7704,13 +7707,13 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D340" t="s">
-        <v>352</v>
+        <v>326</v>
       </c>
       <c r="E340" t="s">
         <v>8</v>
@@ -7721,13 +7724,13 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D341" t="s">
-        <v>418</v>
+        <v>246</v>
       </c>
       <c r="E341" t="s">
         <v>8</v>
@@ -7738,13 +7741,13 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D342" t="s">
-        <v>260</v>
+        <v>291</v>
       </c>
       <c r="E342" t="s">
         <v>8</v>
@@ -7755,13 +7758,13 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D343" t="s">
-        <v>345</v>
+        <v>266</v>
       </c>
       <c r="E343" t="s">
         <v>8</v>
@@ -7772,13 +7775,13 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D344" t="s">
-        <v>336</v>
+        <v>235</v>
       </c>
       <c r="E344" t="s">
         <v>8</v>
@@ -7789,13 +7792,13 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D345" t="s">
-        <v>260</v>
+        <v>389</v>
       </c>
       <c r="E345" t="s">
         <v>8</v>
@@ -7806,13 +7809,13 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D346" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="E346" t="s">
         <v>8</v>
@@ -7823,13 +7826,13 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D347" t="s">
-        <v>297</v>
+        <v>434</v>
       </c>
       <c r="E347" t="s">
         <v>8</v>
@@ -7840,13 +7843,13 @@
         <v>347</v>
       </c>
       <c r="B348" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D348" t="s">
-        <v>258</v>
+        <v>408</v>
       </c>
       <c r="E348" t="s">
         <v>8</v>
@@ -7857,13 +7860,13 @@
         <v>348</v>
       </c>
       <c r="B349" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D349" t="s">
-        <v>198</v>
+        <v>299</v>
       </c>
       <c r="E349" t="s">
         <v>8</v>
@@ -7874,13 +7877,13 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D350" t="s">
-        <v>225</v>
+        <v>323</v>
       </c>
       <c r="E350" t="s">
         <v>8</v>
@@ -7891,13 +7894,13 @@
         <v>350</v>
       </c>
       <c r="B351" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D351" t="s">
-        <v>196</v>
+        <v>282</v>
       </c>
       <c r="E351" t="s">
         <v>8</v>
@@ -7908,13 +7911,13 @@
         <v>351</v>
       </c>
       <c r="B352" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D352" t="s">
-        <v>393</v>
+        <v>440</v>
       </c>
       <c r="E352" t="s">
         <v>8</v>
@@ -7925,13 +7928,13 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D353" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="E353" t="s">
         <v>8</v>
@@ -7942,13 +7945,13 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D354" t="s">
-        <v>303</v>
+        <v>444</v>
       </c>
       <c r="E354" t="s">
         <v>8</v>
@@ -7959,13 +7962,13 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D355" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="E355" t="s">
         <v>8</v>
@@ -7976,13 +7979,13 @@
         <v>355</v>
       </c>
       <c r="B356" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D356" t="s">
-        <v>441</v>
+        <v>294</v>
       </c>
       <c r="E356" t="s">
         <v>8</v>
@@ -7993,13 +7996,13 @@
         <v>356</v>
       </c>
       <c r="B357" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D357" t="s">
-        <v>443</v>
+        <v>344</v>
       </c>
       <c r="E357" t="s">
         <v>8</v>
@@ -8010,13 +8013,13 @@
         <v>357</v>
       </c>
       <c r="B358" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D358" t="s">
-        <v>445</v>
+        <v>337</v>
       </c>
       <c r="E358" t="s">
         <v>8</v>
@@ -8027,13 +8030,13 @@
         <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D359" t="s">
-        <v>321</v>
+        <v>223</v>
       </c>
       <c r="E359" t="s">
         <v>8</v>
@@ -8044,13 +8047,13 @@
         <v>359</v>
       </c>
       <c r="B360" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D360" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="E360" t="s">
         <v>8</v>
@@ -8061,13 +8064,13 @@
         <v>360</v>
       </c>
       <c r="B361" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D361" t="s">
-        <v>406</v>
+        <v>374</v>
       </c>
       <c r="E361" t="s">
         <v>8</v>
@@ -8078,13 +8081,13 @@
         <v>361</v>
       </c>
       <c r="B362" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D362" t="s">
-        <v>386</v>
+        <v>408</v>
       </c>
       <c r="E362" t="s">
         <v>8</v>
@@ -8095,13 +8098,13 @@
         <v>362</v>
       </c>
       <c r="B363" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D363" t="s">
-        <v>448</v>
+        <v>196</v>
       </c>
       <c r="E363" t="s">
         <v>8</v>
@@ -8112,13 +8115,13 @@
         <v>363</v>
       </c>
       <c r="B364" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D364" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="E364" t="s">
         <v>8</v>
@@ -8129,13 +8132,13 @@
         <v>364</v>
       </c>
       <c r="B365" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D365" t="s">
-        <v>196</v>
+        <v>273</v>
       </c>
       <c r="E365" t="s">
         <v>8</v>
@@ -8146,13 +8149,13 @@
         <v>365</v>
       </c>
       <c r="B366" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D366" t="s">
-        <v>192</v>
+        <v>307</v>
       </c>
       <c r="E366" t="s">
         <v>8</v>
@@ -8163,13 +8166,13 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D367" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="E367" t="s">
         <v>8</v>
@@ -8180,13 +8183,13 @@
         <v>367</v>
       </c>
       <c r="B368" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D368" t="s">
-        <v>221</v>
+        <v>460</v>
       </c>
       <c r="E368" t="s">
         <v>8</v>
@@ -8197,13 +8200,13 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D369" t="s">
-        <v>314</v>
+        <v>444</v>
       </c>
       <c r="E369" t="s">
         <v>8</v>
@@ -8214,13 +8217,13 @@
         <v>369</v>
       </c>
       <c r="B370" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D370" t="s">
-        <v>345</v>
+        <v>242</v>
       </c>
       <c r="E370" t="s">
         <v>8</v>
@@ -8231,13 +8234,13 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D371" t="s">
-        <v>219</v>
+        <v>328</v>
       </c>
       <c r="E371" t="s">
         <v>8</v>
@@ -8248,13 +8251,13 @@
         <v>371</v>
       </c>
       <c r="B372" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D372" t="s">
-        <v>334</v>
+        <v>246</v>
       </c>
       <c r="E372" t="s">
         <v>8</v>
@@ -8265,13 +8268,13 @@
         <v>372</v>
       </c>
       <c r="B373" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D373" t="s">
-        <v>242</v>
+        <v>196</v>
       </c>
       <c r="E373" t="s">
         <v>8</v>
@@ -8282,13 +8285,13 @@
         <v>373</v>
       </c>
       <c r="B374" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D374" t="s">
-        <v>437</v>
+        <v>233</v>
       </c>
       <c r="E374" t="s">
         <v>8</v>
@@ -8299,13 +8302,13 @@
         <v>374</v>
       </c>
       <c r="B375" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D375" t="s">
-        <v>242</v>
+        <v>374</v>
       </c>
       <c r="E375" t="s">
         <v>8</v>
@@ -8316,13 +8319,13 @@
         <v>375</v>
       </c>
       <c r="B376" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D376" t="s">
-        <v>365</v>
+        <v>328</v>
       </c>
       <c r="E376" t="s">
         <v>8</v>
@@ -8333,13 +8336,13 @@
         <v>376</v>
       </c>
       <c r="B377" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D377" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="E377" t="s">
         <v>8</v>
@@ -8350,13 +8353,13 @@
         <v>377</v>
       </c>
       <c r="B378" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D378" t="s">
-        <v>262</v>
+        <v>361</v>
       </c>
       <c r="E378" t="s">
         <v>8</v>
@@ -8367,13 +8370,13 @@
         <v>378</v>
       </c>
       <c r="B379" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D379" t="s">
-        <v>328</v>
+        <v>472</v>
       </c>
       <c r="E379" t="s">
         <v>8</v>
@@ -8384,13 +8387,13 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D380" t="s">
-        <v>470</v>
+        <v>301</v>
       </c>
       <c r="E380" t="s">
         <v>8</v>
@@ -8401,13 +8404,13 @@
         <v>380</v>
       </c>
       <c r="B381" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D381" t="s">
-        <v>285</v>
+        <v>256</v>
       </c>
       <c r="E381" t="s">
         <v>8</v>
@@ -8418,13 +8421,13 @@
         <v>381</v>
       </c>
       <c r="B382" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D382" t="s">
-        <v>297</v>
+        <v>378</v>
       </c>
       <c r="E382" t="s">
         <v>8</v>
@@ -8435,13 +8438,13 @@
         <v>382</v>
       </c>
       <c r="B383" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D383" t="s">
-        <v>393</v>
+        <v>374</v>
       </c>
       <c r="E383" t="s">
         <v>8</v>
@@ -8452,13 +8455,13 @@
         <v>383</v>
       </c>
       <c r="B384" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D384" t="s">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="E384" t="s">
         <v>8</v>
@@ -8469,13 +8472,13 @@
         <v>384</v>
       </c>
       <c r="B385" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D385" t="s">
-        <v>476</v>
+        <v>391</v>
       </c>
       <c r="E385" t="s">
         <v>8</v>
@@ -8486,13 +8489,13 @@
         <v>385</v>
       </c>
       <c r="B386" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D386" t="s">
-        <v>244</v>
+        <v>371</v>
       </c>
       <c r="E386" t="s">
         <v>8</v>
@@ -8503,13 +8506,13 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D387" t="s">
-        <v>204</v>
+        <v>294</v>
       </c>
       <c r="E387" t="s">
         <v>8</v>
@@ -8520,13 +8523,13 @@
         <v>387</v>
       </c>
       <c r="B388" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D388" t="s">
-        <v>441</v>
+        <v>198</v>
       </c>
       <c r="E388" t="s">
         <v>8</v>
@@ -8537,13 +8540,13 @@
         <v>388</v>
       </c>
       <c r="B389" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D389" t="s">
-        <v>236</v>
+        <v>326</v>
       </c>
       <c r="E389" t="s">
         <v>8</v>
@@ -8554,13 +8557,13 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D390" t="s">
-        <v>328</v>
+        <v>440</v>
       </c>
       <c r="E390" t="s">
         <v>8</v>
@@ -8571,13 +8574,13 @@
         <v>390</v>
       </c>
       <c r="B391" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D391" t="s">
-        <v>470</v>
+        <v>337</v>
       </c>
       <c r="E391" t="s">
         <v>8</v>
@@ -8588,13 +8591,13 @@
         <v>391</v>
       </c>
       <c r="B392" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D392" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E392" t="s">
         <v>8</v>
@@ -8605,13 +8608,13 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D393" t="s">
-        <v>223</v>
+        <v>487</v>
       </c>
       <c r="E393" t="s">
         <v>8</v>
@@ -8622,13 +8625,13 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D394" t="s">
-        <v>443</v>
+        <v>328</v>
       </c>
       <c r="E394" t="s">
         <v>8</v>
@@ -8639,13 +8642,13 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D395" t="s">
-        <v>487</v>
+        <v>235</v>
       </c>
       <c r="E395" t="s">
         <v>8</v>
@@ -8656,13 +8659,13 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D396" t="s">
-        <v>489</v>
+        <v>259</v>
       </c>
       <c r="E396" t="s">
         <v>8</v>
@@ -8673,13 +8676,13 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D397" t="s">
-        <v>466</v>
+        <v>444</v>
       </c>
       <c r="E397" t="s">
         <v>8</v>
@@ -8690,13 +8693,13 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D398" t="s">
-        <v>269</v>
+        <v>368</v>
       </c>
       <c r="E398" t="s">
         <v>8</v>
@@ -8707,13 +8710,13 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D399" t="s">
-        <v>373</v>
+        <v>311</v>
       </c>
       <c r="E399" t="s">
         <v>8</v>
@@ -8724,13 +8727,13 @@
         <v>399</v>
       </c>
       <c r="B400" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D400" t="s">
-        <v>489</v>
+        <v>196</v>
       </c>
       <c r="E400" t="s">
         <v>8</v>
@@ -8741,13 +8744,13 @@
         <v>400</v>
       </c>
       <c r="B401" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D401" t="s">
-        <v>310</v>
+        <v>371</v>
       </c>
       <c r="E401" t="s">
         <v>8</v>
@@ -8766,47 +8769,47 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B4" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B5" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B6">
         <v>400</v>
@@ -8814,7 +8817,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B7">
         <v>400</v>
@@ -8822,7 +8825,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -8830,7 +8833,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -8838,10 +8841,10 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B10" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
   </sheetData>

--- a/reports/backend/Excel/Automation_Test_Report.xlsx
+++ b/reports/backend/Excel/Automation_Test_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="513">
   <si>
     <t>#</t>
   </si>
@@ -35,39 +35,39 @@
     <t>PASSED</t>
   </si>
   <si>
+    <t>0.000</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Smart Admission Backend — Authentication Tests BT-002 | Firebase config has authDomain</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — Authentication Tests BT-003 | Firebase config has projectId</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — Authentication Tests BT-004 | Firebase config has storageBucket</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — Authentication Tests BT-005 | Firebase config has messagingSenderId</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — Authentication Tests BT-006 | Firebase config has appId</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — Authentication Tests BT-007 | Firebase config projectId matches authDomain prefix</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — Authentication Tests BT-008 | Firebase config has all 6 required fields</t>
+  </si>
+  <si>
+    <t>Smart Admission Backend — Authentication Tests BT-009 | Firebase config fields are non-empty strings</t>
+  </si>
+  <si>
     <t>0.001</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>Smart Admission Backend — Authentication Tests BT-002 | Firebase config has authDomain</t>
-  </si>
-  <si>
-    <t>0.000</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — Authentication Tests BT-003 | Firebase config has projectId</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — Authentication Tests BT-004 | Firebase config has storageBucket</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — Authentication Tests BT-005 | Firebase config has messagingSenderId</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — Authentication Tests BT-006 | Firebase config has appId</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — Authentication Tests BT-007 | Firebase config projectId matches authDomain prefix</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — Authentication Tests BT-008 | Firebase config has all 6 required fields</t>
-  </si>
-  <si>
-    <t>Smart Admission Backend — Authentication Tests BT-009 | Firebase config fields are non-empty strings</t>
-  </si>
-  <si>
     <t>Smart Admission Backend — Authentication Tests BT-010 | Firebase apiKey has expected format (AIza...)</t>
   </si>
   <si>
@@ -584,918 +584,921 @@
     <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field apiKey (Verify Point #180)</t>
   </si>
   <si>
+    <t>0.036</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #181)</t>
+  </si>
+  <si>
+    <t>0.050</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #182)</t>
+  </si>
+  <si>
+    <t>0.074</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #183)</t>
+  </si>
+  <si>
+    <t>0.049</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #184)</t>
+  </si>
+  <si>
+    <t>0.106</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #185)</t>
+  </si>
+  <si>
+    <t>0.119</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #186)</t>
+  </si>
+  <si>
+    <t>0.027</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #187)</t>
+  </si>
+  <si>
+    <t>0.105</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #188)</t>
+  </si>
+  <si>
+    <t>0.108</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #189)</t>
+  </si>
+  <si>
+    <t>0.095</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #190)</t>
+  </si>
+  <si>
+    <t>0.100</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #191)</t>
+  </si>
+  <si>
+    <t>0.085</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #192)</t>
+  </si>
+  <si>
+    <t>0.040</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #193)</t>
+  </si>
+  <si>
+    <t>0.087</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #194)</t>
+  </si>
+  <si>
+    <t>0.073</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #195)</t>
+  </si>
+  <si>
+    <t>0.023</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #196)</t>
+  </si>
+  <si>
+    <t>0.031</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #197)</t>
+  </si>
+  <si>
+    <t>0.021</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #198)</t>
+  </si>
+  <si>
+    <t>0.046</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #199)</t>
+  </si>
+  <si>
+    <t>0.030</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #200)</t>
+  </si>
+  <si>
+    <t>0.038</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #201)</t>
+  </si>
+  <si>
+    <t>0.020</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #202)</t>
+  </si>
+  <si>
+    <t>0.076</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #203)</t>
+  </si>
+  <si>
+    <t>0.065</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #204)</t>
+  </si>
+  <si>
+    <t>0.116</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #205)</t>
+  </si>
+  <si>
+    <t>0.034</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #206)</t>
+  </si>
+  <si>
+    <t>0.051</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #207)</t>
+  </si>
+  <si>
+    <t>0.058</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #208)</t>
+  </si>
+  <si>
+    <t>0.052</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #209)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #210)</t>
+  </si>
+  <si>
+    <t>0.053</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #211)</t>
+  </si>
+  <si>
+    <t>0.054</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code XSS-injection (Verify Point #212)</t>
+  </si>
+  <si>
+    <t>0.075</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #213)</t>
+  </si>
+  <si>
+    <t>0.060</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for CSRF-token (Verify Point #214)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated CORS-origin (Verify Point #215)</t>
+  </si>
+  <si>
+    <t>0.101</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for CSP-header (Verify Point #216)</t>
+  </si>
+  <si>
+    <t>0.069</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at session-token (Verify Point #217)</t>
+  </si>
+  <si>
+    <t>0.084</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users-ref (Verify Point #218)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for items-ref (Verify Point #219)</t>
+  </si>
+  <si>
+    <t>0.057</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field de-DE (Verify Point #220)</t>
+  </si>
+  <si>
+    <t>0.103</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for fr-FR (Verify Point #221)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ja-JP (Verify Point #222)</t>
+  </si>
+  <si>
+    <t>0.066</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for pt-BR (Verify Point #223)</t>
+  </si>
+  <si>
+    <t>0.059</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of it-IT (Verify Point #224)</t>
+  </si>
+  <si>
+    <t>0.081</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for apiKey (Verify Point #225)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for authDomain (Verify Point #226)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value projectId (Verify Point #227)</t>
+  </si>
+  <si>
+    <t>0.097</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session storageBucket (Verify Point #228)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier messagingSenderId (Verify Point #229)</t>
+  </si>
+  <si>
+    <t>0.032</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region appId (Verify Point #230)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for name (Verify Point #231)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code id (Verify Point #232)</t>
+  </si>
+  <si>
+    <t>0.083</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource fees.min (Verify Point #233)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for fees.max (Verify Point #234)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated courses (Verify Point #235)</t>
+  </si>
+  <si>
+    <t>0.113</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for ranking.nirf (Verify Point #236)</t>
+  </si>
+  <si>
+    <t>0.088</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at type (Verify Point #237)</t>
+  </si>
+  <si>
+    <t>0.109</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users/uid001 (Verify Point #238)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for colleges/c001 (Verify Point #239)</t>
+  </si>
+  <si>
+    <t>0.039</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field prompt-length (Verify Point #240)</t>
+  </si>
+  <si>
+    <t>0.082</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for session-id-1 (Verify Point #241)</t>
+  </si>
+  <si>
+    <t>0.089</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ₹1L (Verify Point #242)</t>
+  </si>
+  <si>
+    <t>0.114</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for B.Tech (Verify Point #243)</t>
+  </si>
+  <si>
+    <t>0.063</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of 4 years (Verify Point #244)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for Tamil Nadu (Verify Point #245)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for Chennai (Verify Point #246)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value llama3-8b (Verify Point #247)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session email (Verify Point #248)</t>
+  </si>
+  <si>
+    <t>0.090</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier password (Verify Point #249)</t>
+  </si>
+  <si>
+    <t>0.112</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region displayName (Verify Point #250)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for savedColleges (Verify Point #251)</t>
+  </si>
+  <si>
+    <t>0.026</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code createdAt (Verify Point #252)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource firebase-auth (Verify Point #253)</t>
+  </si>
+  <si>
+    <t>0.110</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for firestore-read (Verify Point #254)</t>
+  </si>
+  <si>
+    <t>0.071</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated groq-api (Verify Point #255)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for college-list (Verify Point #256)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at XSS-injection (Verify Point #257)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation SQL-injection (Verify Point #258)</t>
+  </si>
+  <si>
+    <t>0.044</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for CSRF-token (Verify Point #259)</t>
+  </si>
+  <si>
+    <t>0.045</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field CORS-origin (Verify Point #260)</t>
+  </si>
+  <si>
+    <t>0.068</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for CSP-header (Verify Point #261)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for session-token (Verify Point #262)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users-ref (Verify Point #263)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of items-ref (Verify Point #264)</t>
+  </si>
+  <si>
+    <t>0.078</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for de-DE (Verify Point #265)</t>
+  </si>
+  <si>
+    <t>0.093</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for fr-FR (Verify Point #266)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ja-JP (Verify Point #267)</t>
+  </si>
+  <si>
+    <t>0.107</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session pt-BR (Verify Point #268)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier it-IT (Verify Point #269)</t>
+  </si>
+  <si>
+    <t>0.111</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region apiKey (Verify Point #270)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for authDomain (Verify Point #271)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code projectId (Verify Point #272)</t>
+  </si>
+  <si>
+    <t>0.099</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource storageBucket (Verify Point #273)</t>
+  </si>
+  <si>
+    <t>0.033</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for messagingSenderId (Verify Point #274)</t>
+  </si>
+  <si>
+    <t>0.035</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated appId (Verify Point #275)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for name (Verify Point #276)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at id (Verify Point #277)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation fees.min (Verify Point #278)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for fees.max (Verify Point #279)</t>
+  </si>
+  <si>
+    <t>0.025</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field courses (Verify Point #280)</t>
+  </si>
+  <si>
     <t>0.062</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #181)</t>
-  </si>
-  <si>
-    <t>0.053</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #182)</t>
-  </si>
-  <si>
-    <t>0.058</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #183)</t>
-  </si>
-  <si>
-    <t>0.064</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #184)</t>
-  </si>
-  <si>
-    <t>0.071</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #185)</t>
-  </si>
-  <si>
-    <t>0.045</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #186)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #187)</t>
-  </si>
-  <si>
-    <t>0.027</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #188)</t>
-  </si>
-  <si>
-    <t>0.113</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #189)</t>
-  </si>
-  <si>
-    <t>0.116</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #190)</t>
-  </si>
-  <si>
-    <t>0.119</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #191)</t>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for ranking.nirf (Verify Point #281)</t>
+  </si>
+  <si>
+    <t>0.067</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for type (Verify Point #282)</t>
   </si>
   <si>
     <t>0.077</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #192)</t>
-  </si>
-  <si>
-    <t>0.085</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #193)</t>
-  </si>
-  <si>
-    <t>0.022</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #194)</t>
-  </si>
-  <si>
-    <t>0.112</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #195)</t>
-  </si>
-  <si>
-    <t>0.021</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #196)</t>
-  </si>
-  <si>
-    <t>0.025</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #197)</t>
-  </si>
-  <si>
-    <t>0.050</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #198)</t>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users/uid001 (Verify Point #283)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of colleges/c001 (Verify Point #284)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for prompt-length (Verify Point #285)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for session-id-1 (Verify Point #286)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ₹1L (Verify Point #287)</t>
   </si>
   <si>
     <t>0.092</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #199)</t>
-  </si>
-  <si>
-    <t>0.107</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #200)</t>
-  </si>
-  <si>
-    <t>0.074</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #201)</t>
-  </si>
-  <si>
-    <t>0.075</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #202)</t>
-  </si>
-  <si>
-    <t>0.083</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #203)</t>
-  </si>
-  <si>
-    <t>0.084</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #204)</t>
-  </si>
-  <si>
-    <t>0.114</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #205)</t>
-  </si>
-  <si>
-    <t>0.063</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #206)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #207)</t>
-  </si>
-  <si>
-    <t>0.040</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #208)</t>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session B.Tech (Verify Point #288)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier 4 years (Verify Point #289)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region Tamil Nadu (Verify Point #290)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for Chennai (Verify Point #291)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code llama3-8b (Verify Point #292)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource email (Verify Point #293)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for password (Verify Point #294)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated displayName (Verify Point #295)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for savedColleges (Verify Point #296)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at createdAt (Verify Point #297)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation firebase-auth (Verify Point #298)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for firestore-read (Verify Point #299)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field groq-api (Verify Point #300)</t>
+  </si>
+  <si>
+    <t>0.055</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for college-list (Verify Point #301)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for XSS-injection (Verify Point #302)</t>
+  </si>
+  <si>
+    <t>0.118</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for SQL-injection (Verify Point #303)</t>
+  </si>
+  <si>
+    <t>0.096</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of CSRF-token (Verify Point #304)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for CORS-origin (Verify Point #305)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for CSP-header (Verify Point #306)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value session-token (Verify Point #307)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users-ref (Verify Point #308)</t>
+  </si>
+  <si>
+    <t>0.117</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier items-ref (Verify Point #309)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region de-DE (Verify Point #310)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for fr-FR (Verify Point #311)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ja-JP (Verify Point #312)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource pt-BR (Verify Point #313)</t>
+  </si>
+  <si>
+    <t>0.070</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for it-IT (Verify Point #314)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated apiKey (Verify Point #315)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for authDomain (Verify Point #316)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at projectId (Verify Point #317)</t>
+  </si>
+  <si>
+    <t>0.043</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation storageBucket (Verify Point #318)</t>
+  </si>
+  <si>
+    <t>0.029</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for messagingSenderId (Verify Point #319)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field appId (Verify Point #320)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for name (Verify Point #321)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for id (Verify Point #322)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for fees.min (Verify Point #323)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of fees.max (Verify Point #324)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for courses (Verify Point #325)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for ranking.nirf (Verify Point #326)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value type (Verify Point #327)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users/uid001 (Verify Point #328)</t>
+  </si>
+  <si>
+    <t>0.094</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier colleges/c001 (Verify Point #329)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region prompt-length (Verify Point #330)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for session-id-1 (Verify Point #331)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ₹1L (Verify Point #332)</t>
   </si>
   <si>
     <t>0.079</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #209)</t>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource B.Tech (Verify Point #333)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for 4 years (Verify Point #334)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated Tamil Nadu (Verify Point #335)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for Chennai (Verify Point #336)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at llama3-8b (Verify Point #337)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation email (Verify Point #338)</t>
+  </si>
+  <si>
+    <t>0.098</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for password (Verify Point #339)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field displayName (Verify Point #340)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for savedColleges (Verify Point #341)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for createdAt (Verify Point #342)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for firebase-auth (Verify Point #343)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of firestore-read (Verify Point #344)</t>
+  </si>
+  <si>
+    <t>0.056</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for groq-api (Verify Point #345)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for college-list (Verify Point #346)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value XSS-injection (Verify Point #347)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session SQL-injection (Verify Point #348)</t>
+  </si>
+  <si>
+    <t>0.042</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier CSRF-token (Verify Point #349)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region CORS-origin (Verify Point #350)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for CSP-header (Verify Point #351)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code session-token (Verify Point #352)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users-ref (Verify Point #353)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for items-ref (Verify Point #354)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated de-DE (Verify Point #355)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for fr-FR (Verify Point #356)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ja-JP (Verify Point #357)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation pt-BR (Verify Point #358)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for it-IT (Verify Point #359)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field apiKey (Verify Point #360)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #361)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #362)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #363)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #364)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #365)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #366)</t>
+  </si>
+  <si>
+    <t>0.115</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #367)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #368)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #369)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #370)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #371)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #372)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #373)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #374)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #375)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #376)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #377)</t>
   </si>
   <si>
     <t>0.024</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #210)</t>
-  </si>
-  <si>
-    <t>0.041</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #211)</t>
-  </si>
-  <si>
-    <t>0.103</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code XSS-injection (Verify Point #212)</t>
-  </si>
-  <si>
-    <t>0.096</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #213)</t>
-  </si>
-  <si>
-    <t>0.061</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for CSRF-token (Verify Point #214)</t>
-  </si>
-  <si>
-    <t>0.068</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated CORS-origin (Verify Point #215)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for CSP-header (Verify Point #216)</t>
-  </si>
-  <si>
-    <t>0.048</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at session-token (Verify Point #217)</t>
-  </si>
-  <si>
-    <t>0.070</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users-ref (Verify Point #218)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for items-ref (Verify Point #219)</t>
+    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #378)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #379)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #380)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #381)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #382)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #383)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #384)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #385)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #386)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #387)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #388)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #389)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #390)</t>
+  </si>
+  <si>
+    <t>0.086</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #391)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code XSS-injection (Verify Point #392)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #393)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Search]: Verify search results filtering for CSRF-token (Verify Point #394)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated CORS-origin (Verify Point #395)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for CSP-header (Verify Point #396)</t>
+  </si>
+  <si>
+    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at session-token (Verify Point #397)</t>
   </si>
   <si>
     <t>0.072</t>
   </si>
   <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field de-DE (Verify Point #220)</t>
-  </si>
-  <si>
-    <t>0.104</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for fr-FR (Verify Point #221)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ja-JP (Verify Point #222)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for pt-BR (Verify Point #223)</t>
-  </si>
-  <si>
-    <t>0.034</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of it-IT (Verify Point #224)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for apiKey (Verify Point #225)</t>
-  </si>
-  <si>
-    <t>0.044</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for authDomain (Verify Point #226)</t>
-  </si>
-  <si>
-    <t>0.059</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value projectId (Verify Point #227)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session storageBucket (Verify Point #228)</t>
-  </si>
-  <si>
-    <t>0.099</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier messagingSenderId (Verify Point #229)</t>
-  </si>
-  <si>
-    <t>0.033</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region appId (Verify Point #230)</t>
-  </si>
-  <si>
-    <t>0.023</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for name (Verify Point #231)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code id (Verify Point #232)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource fees.min (Verify Point #233)</t>
-  </si>
-  <si>
-    <t>0.039</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for fees.max (Verify Point #234)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated courses (Verify Point #235)</t>
-  </si>
-  <si>
-    <t>0.026</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for ranking.nirf (Verify Point #236)</t>
-  </si>
-  <si>
-    <t>0.102</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at type (Verify Point #237)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users/uid001 (Verify Point #238)</t>
-  </si>
-  <si>
-    <t>0.032</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for colleges/c001 (Verify Point #239)</t>
-  </si>
-  <si>
-    <t>0.056</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field prompt-length (Verify Point #240)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for session-id-1 (Verify Point #241)</t>
-  </si>
-  <si>
-    <t>0.098</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for ₹1L (Verify Point #242)</t>
-  </si>
-  <si>
-    <t>0.060</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for B.Tech (Verify Point #243)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of 4 years (Verify Point #244)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for Tamil Nadu (Verify Point #245)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for Chennai (Verify Point #246)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value llama3-8b (Verify Point #247)</t>
-  </si>
-  <si>
-    <t>0.065</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session email (Verify Point #248)</t>
-  </si>
-  <si>
-    <t>0.049</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier password (Verify Point #249)</t>
-  </si>
-  <si>
-    <t>0.052</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region displayName (Verify Point #250)</t>
-  </si>
-  <si>
-    <t>0.081</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for savedColleges (Verify Point #251)</t>
-  </si>
-  <si>
-    <t>0.057</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code createdAt (Verify Point #252)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource firebase-auth (Verify Point #253)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for firestore-read (Verify Point #254)</t>
-  </si>
-  <si>
-    <t>0.089</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated groq-api (Verify Point #255)</t>
-  </si>
-  <si>
-    <t>0.037</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for college-list (Verify Point #256)</t>
-  </si>
-  <si>
-    <t>0.038</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at XSS-injection (Verify Point #257)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation SQL-injection (Verify Point #258)</t>
-  </si>
-  <si>
-    <t>0.036</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for CSRF-token (Verify Point #259)</t>
-  </si>
-  <si>
-    <t>0.091</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field CORS-origin (Verify Point #260)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for CSP-header (Verify Point #261)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for session-token (Verify Point #262)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users-ref (Verify Point #263)</t>
-  </si>
-  <si>
-    <t>0.030</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of items-ref (Verify Point #264)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for de-DE (Verify Point #265)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for fr-FR (Verify Point #266)</t>
-  </si>
-  <si>
-    <t>0.105</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ja-JP (Verify Point #267)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session pt-BR (Verify Point #268)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier it-IT (Verify Point #269)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region apiKey (Verify Point #270)</t>
-  </si>
-  <si>
-    <t>0.082</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for authDomain (Verify Point #271)</t>
-  </si>
-  <si>
-    <t>0.055</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code projectId (Verify Point #272)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource storageBucket (Verify Point #273)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for messagingSenderId (Verify Point #274)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated appId (Verify Point #275)</t>
-  </si>
-  <si>
-    <t>0.097</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for name (Verify Point #276)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at id (Verify Point #277)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation fees.min (Verify Point #278)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for fees.max (Verify Point #279)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field courses (Verify Point #280)</t>
-  </si>
-  <si>
-    <t>0.115</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for ranking.nirf (Verify Point #281)</t>
-  </si>
-  <si>
-    <t>0.108</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for type (Verify Point #282)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for users/uid001 (Verify Point #283)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of colleges/c001 (Verify Point #284)</t>
-  </si>
-  <si>
-    <t>0.109</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for prompt-length (Verify Point #285)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for session-id-1 (Verify Point #286)</t>
-  </si>
-  <si>
-    <t>0.090</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value ₹1L (Verify Point #287)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session B.Tech (Verify Point #288)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier 4 years (Verify Point #289)</t>
-  </si>
-  <si>
-    <t>0.073</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region Tamil Nadu (Verify Point #290)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for Chennai (Verify Point #291)</t>
-  </si>
-  <si>
-    <t>0.051</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code llama3-8b (Verify Point #292)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource email (Verify Point #293)</t>
-  </si>
-  <si>
-    <t>0.087</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for password (Verify Point #294)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated displayName (Verify Point #295)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for savedColleges (Verify Point #296)</t>
-  </si>
-  <si>
-    <t>0.042</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at createdAt (Verify Point #297)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation firebase-auth (Verify Point #298)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for firestore-read (Verify Point #299)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field groq-api (Verify Point #300)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for college-list (Verify Point #301)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for XSS-injection (Verify Point #302)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for SQL-injection (Verify Point #303)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of CSRF-token (Verify Point #304)</t>
-  </si>
-  <si>
-    <t>0.069</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for CORS-origin (Verify Point #305)</t>
-  </si>
-  <si>
-    <t>0.111</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for CSP-header (Verify Point #306)</t>
-  </si>
-  <si>
-    <t>0.086</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value session-token (Verify Point #307)</t>
-  </si>
-  <si>
-    <t>0.043</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users-ref (Verify Point #308)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier items-ref (Verify Point #309)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region de-DE (Verify Point #310)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for fr-FR (Verify Point #311)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ja-JP (Verify Point #312)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource pt-BR (Verify Point #313)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for it-IT (Verify Point #314)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated apiKey (Verify Point #315)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for authDomain (Verify Point #316)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at projectId (Verify Point #317)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation storageBucket (Verify Point #318)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for messagingSenderId (Verify Point #319)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field appId (Verify Point #320)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for name (Verify Point #321)</t>
-  </si>
-  <si>
-    <t>0.067</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for id (Verify Point #322)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for fees.min (Verify Point #323)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of fees.max (Verify Point #324)</t>
-  </si>
-  <si>
-    <t>0.093</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for courses (Verify Point #325)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for ranking.nirf (Verify Point #326)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value type (Verify Point #327)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session users/uid001 (Verify Point #328)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier colleges/c001 (Verify Point #329)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region prompt-length (Verify Point #330)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for session-id-1 (Verify Point #331)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code ₹1L (Verify Point #332)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource B.Tech (Verify Point #333)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for 4 years (Verify Point #334)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated Tamil Nadu (Verify Point #335)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for Chennai (Verify Point #336)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at llama3-8b (Verify Point #337)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation email (Verify Point #338)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for password (Verify Point #339)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field displayName (Verify Point #340)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for savedColleges (Verify Point #341)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for createdAt (Verify Point #342)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for firebase-auth (Verify Point #343)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of firestore-read (Verify Point #344)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for groq-api (Verify Point #345)</t>
-  </si>
-  <si>
-    <t>0.031</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for college-list (Verify Point #346)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value XSS-injection (Verify Point #347)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session SQL-injection (Verify Point #348)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier CSRF-token (Verify Point #349)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region CORS-origin (Verify Point #350)</t>
-  </si>
-  <si>
-    <t>0.047</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for CSP-header (Verify Point #351)</t>
-  </si>
-  <si>
-    <t>0.020</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code session-token (Verify Point #352)</t>
-  </si>
-  <si>
-    <t>0.106</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users-ref (Verify Point #353)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for items-ref (Verify Point #354)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated de-DE (Verify Point #355)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for fr-FR (Verify Point #356)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ja-JP (Verify Point #357)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation pt-BR (Verify Point #358)</t>
-  </si>
-  <si>
-    <t>0.028</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for it-IT (Verify Point #359)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field apiKey (Verify Point #360)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for authDomain (Verify Point #361)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for projectId (Verify Point #362)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for storageBucket (Verify Point #363)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of messagingSenderId (Verify Point #364)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for appId (Verify Point #365)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for name (Verify Point #366)</t>
-  </si>
-  <si>
-    <t>0.095</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value id (Verify Point #367)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session fees.min (Verify Point #368)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier fees.max (Verify Point #369)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region courses (Verify Point #370)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for ranking.nirf (Verify Point #371)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code type (Verify Point #372)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource users/uid001 (Verify Point #373)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for colleges/c001 (Verify Point #374)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated prompt-length (Verify Point #375)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for session-id-1 (Verify Point #376)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at ₹1L (Verify Point #377)</t>
-  </si>
-  <si>
-    <t>0.078</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation B.Tech (Verify Point #378)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Session]: Verify session cookie flags for 4 years (Verify Point #379)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth]: Verify Firebase auth config field Tamil Nadu (Verify Point #380)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [College]: Verify college data field constraint for Chennai (Verify Point #381)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Profile]: Verify user profile validation for llama3-8b (Verify Point #382)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [AI Service]: Verify AI prompt constraint for email (Verify Point #383)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Validation]: Verify input sanitisation of password (Verify Point #384)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Firestore]: Verify Firestore collection path for displayName (Verify Point #385)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Comparison]: Verify college comparison logic for savedColleges (Verify Point #386)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Fees]: Verify fee formatting for value createdAt (Verify Point #387)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Chat]: Verify chat history append for session firebase-auth (Verify Point #388)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [NIRF]: Verify NIRF rank ordering for tier firestore-read (Verify Point #389)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Location]: Verify state/city filter for region groq-api (Verify Point #390)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Groq]: Verify Groq model name validation for college-list (Verify Point #391)</t>
-  </si>
-  <si>
-    <t>0.101</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Error Handling]: Verify API error handling for code XSS-injection (Verify Point #392)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #393)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Search]: Verify search results filtering for CSRF-token (Verify Point #394)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Auth Guard]: Verify route protection for unauthenticated CORS-origin (Verify Point #395)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Logic]: Verify sort/filter logic for CSP-header (Verify Point #396)</t>
-  </si>
-  <si>
-    <t>Smart Admission — Backend [Boundary]: Verify boundary condition at session-token (Verify Point #397)</t>
-  </si>
-  <si>
     <t>Smart Admission — Backend [Saved Items]: Verify saved college list operation users-ref (Verify Point #398)</t>
   </si>
   <si>
@@ -1511,13 +1514,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>26</t>
+    <t>27</t>
   </si>
   <si>
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-30 08:35:27 UTC</t>
+    <t>2026-06-30 13:19:55 UTC</t>
   </si>
   <si>
     <t>Branch</t>
@@ -1529,7 +1532,7 @@
     <t>Commit</t>
   </si>
   <si>
-    <t>1b19601</t>
+    <t>9a48722</t>
   </si>
   <si>
     <t>Total</t>
@@ -1984,7 +1987,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1995,13 +1998,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -2012,13 +2015,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -2029,13 +2032,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -2046,13 +2049,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -2063,13 +2066,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -2080,13 +2083,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D9" t="s">
-  